--- a/players_ratings.xlsx
+++ b/players_ratings.xlsx
@@ -591,49 +591,49 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D5" t="n">
         <v>7.6</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="E5" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>6.3</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="I5" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="H5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I5" s="1" t="n">
+      <c r="J5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>45936</v>
       </c>
-      <c r="J5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>6.4</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="O5" s="1" t="n">
         <v>45920</v>
       </c>
-      <c r="N5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>45910</v>
-      </c>
       <c r="P5" t="n">
-        <v>6.67</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="6">
@@ -641,49 +641,49 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D6" t="n">
         <v>6.8</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="E6" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>7.3</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F6" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G6" s="1" t="n">
+      <c r="H6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I6" s="1" t="n">
         <v>45995</v>
       </c>
-      <c r="H6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I6" s="1" t="n">
+      <c r="J6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K6" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>6.8</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="M6" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>6.4</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="O6" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="N6" t="n">
-        <v>6</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>45962</v>
-      </c>
       <c r="P6" t="n">
-        <v>6.66</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="7">
@@ -767,49 +767,49 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D9" t="n">
         <v>6.3</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="E9" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>8.6</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="G9" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>6.1</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="I9" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>6.3</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="K9" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>6.8</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="M9" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>7</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="O9" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P9" t="n">
-        <v>6.83</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="10">
@@ -817,49 +817,49 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C10" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E10" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>6.4</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="G10" s="1" t="n">
         <v>45935</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>7.1</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="I10" s="1" t="n">
         <v>45898</v>
       </c>
-      <c r="H10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I10" s="1" t="n">
+      <c r="J10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K10" s="1" t="n">
         <v>45893</v>
-      </c>
-      <c r="J10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>45887</v>
       </c>
       <c r="L10" t="n">
         <v>6.8</v>
       </c>
       <c r="M10" s="1" t="n">
+        <v>45887</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O10" s="1" t="n">
         <v>45871</v>
       </c>
-      <c r="N10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O10" s="1" t="n">
-        <v>45859</v>
-      </c>
       <c r="P10" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="11">
@@ -1199,49 +1199,49 @@
         <v>34</v>
       </c>
       <c r="B20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D20" t="n">
         <v>6.3</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="E20" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>8.1</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="G20" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
         <v>7.6</v>
       </c>
-      <c r="G20" s="1" t="n">
+      <c r="I20" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>7</v>
       </c>
-      <c r="I20" s="1" t="n">
+      <c r="K20" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>7.8</v>
       </c>
-      <c r="K20" s="1" t="n">
+      <c r="M20" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>6.2</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="O20" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N20" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P20" t="n">
-        <v>7.1</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="21">
@@ -1249,49 +1249,49 @@
         <v>36</v>
       </c>
       <c r="B21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D21" t="n">
         <v>7.4</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="E21" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E21" s="1" t="n">
+      <c r="F21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G21" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G21" s="1" t="n">
+      <c r="H21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I21" s="1" t="n">
         <v>45991</v>
-      </c>
-      <c r="H21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I21" s="1" t="n">
-        <v>45970</v>
       </c>
       <c r="J21" t="n">
         <v>6.4</v>
       </c>
       <c r="K21" s="1" t="n">
+        <v>45970</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M21" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>7</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="O21" s="1" t="n">
         <v>45949</v>
       </c>
-      <c r="N21" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O21" s="1" t="n">
-        <v>45935</v>
-      </c>
       <c r="P21" t="n">
-        <v>6.74</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="22">
@@ -1475,49 +1475,49 @@
         <v>42</v>
       </c>
       <c r="B26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D26" t="n">
         <v>6.4</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="E26" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>7.4</v>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="G26" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="F26" t="n">
+      <c r="H26" t="n">
         <v>6.2</v>
       </c>
-      <c r="G26" s="1" t="n">
+      <c r="I26" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I26" s="1" t="n">
+      <c r="J26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K26" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>6.8</v>
       </c>
-      <c r="K26" s="1" t="n">
+      <c r="M26" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="L26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M26" s="1" t="n">
+      <c r="N26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O26" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="N26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O26" s="1" t="n">
-        <v>45935</v>
-      </c>
       <c r="P26" t="n">
-        <v>6.67</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="27">
@@ -1625,46 +1625,46 @@
         <v>46</v>
       </c>
       <c r="B29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D29" t="n">
         <v>6.3</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="E29" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E29" s="1" t="n">
+      <c r="F29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F29" t="n">
+      <c r="H29" t="n">
         <v>7.4</v>
       </c>
-      <c r="G29" s="1" t="n">
+      <c r="I29" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="H29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I29" s="1" t="n">
+      <c r="J29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K29" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="J29" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K29" s="1" t="n">
+      <c r="L29" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M29" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>7.9</v>
       </c>
-      <c r="M29" s="1" t="n">
+      <c r="O29" s="1" t="n">
         <v>45994</v>
-      </c>
-      <c r="N29" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O29" s="1" t="n">
-        <v>45991</v>
       </c>
       <c r="P29" t="n">
         <v>6.89</v>
@@ -2437,49 +2437,49 @@
         <v>75</v>
       </c>
       <c r="B50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="D50" t="n">
         <v>6.4</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="E50" s="1" t="n">
         <v>46055</v>
       </c>
-      <c r="D50" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E50" s="1" t="n">
+      <c r="F50" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G50" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="F50" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G50" s="1" t="n">
+      <c r="H50" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I50" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="H50" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I50" s="1" t="n">
+      <c r="J50" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K50" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>6.3</v>
       </c>
-      <c r="K50" s="1" t="n">
+      <c r="M50" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>6.8</v>
       </c>
-      <c r="M50" s="1" t="n">
+      <c r="O50" s="1" t="n">
         <v>45976</v>
       </c>
-      <c r="N50" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O50" s="1" t="n">
-        <v>45954</v>
-      </c>
       <c r="P50" t="n">
-        <v>6.64</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="51">
@@ -2487,49 +2487,49 @@
         <v>80</v>
       </c>
       <c r="B51" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D51" t="n">
         <v>6.8</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="E51" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D51" t="n">
+      <c r="F51" t="n">
         <v>7.3</v>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="G51" s="1" t="n">
         <v>46060</v>
-      </c>
-      <c r="F51" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="G51" s="1" t="n">
-        <v>46054</v>
       </c>
       <c r="H51" t="n">
         <v>6.8</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>46047</v>
+        <v>46054</v>
       </c>
       <c r="J51" t="n">
         <v>6.8</v>
       </c>
       <c r="K51" s="1" t="n">
+        <v>46047</v>
+      </c>
+      <c r="L51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M51" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M51" s="1" t="n">
+      <c r="O51" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="N51" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O51" s="1" t="n">
-        <v>46004</v>
-      </c>
       <c r="P51" t="n">
-        <v>7.06</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="52">
@@ -2733,49 +2733,49 @@
         <v>91</v>
       </c>
       <c r="B58" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C58" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D58" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E58" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="D58" t="n">
+      <c r="F58" t="n">
         <v>6.3</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="G58" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="F58" t="n">
+      <c r="H58" t="n">
         <v>7</v>
       </c>
-      <c r="G58" s="1" t="n">
+      <c r="I58" s="1" t="n">
         <v>45919</v>
       </c>
-      <c r="H58" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I58" s="1" t="n">
+      <c r="J58" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K58" s="1" t="n">
         <v>45906</v>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>6.8</v>
       </c>
-      <c r="K58" s="1" t="n">
+      <c r="M58" s="1" t="n">
         <v>45898</v>
       </c>
-      <c r="L58" t="n">
+      <c r="N58" t="n">
         <v>6.9</v>
       </c>
-      <c r="M58" s="1" t="n">
+      <c r="O58" s="1" t="n">
         <v>45891</v>
       </c>
-      <c r="N58" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O58" s="1" t="n">
-        <v>45879</v>
-      </c>
       <c r="P58" t="n">
-        <v>6.63</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="59">
@@ -3833,49 +3833,49 @@
         <v>124</v>
       </c>
       <c r="B86" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D86" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>46068</v>
+      </c>
+      <c r="F86" t="n">
         <v>6.4</v>
       </c>
-      <c r="C86" s="1" t="n">
-        <v>46068</v>
-      </c>
-      <c r="D86" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E86" s="1" t="n">
+      <c r="G86" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="F86" t="n">
+      <c r="H86" t="n">
         <v>7</v>
       </c>
-      <c r="G86" s="1" t="n">
+      <c r="I86" s="1" t="n">
         <v>45992</v>
-      </c>
-      <c r="H86" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I86" s="1" t="n">
-        <v>45983</v>
       </c>
       <c r="J86" t="n">
         <v>7.1</v>
       </c>
       <c r="K86" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="L86" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M86" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="L86" t="n">
+      <c r="N86" t="n">
         <v>7.3</v>
       </c>
-      <c r="M86" s="1" t="n">
+      <c r="O86" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="N86" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O86" s="1" t="n">
-        <v>45948</v>
-      </c>
       <c r="P86" t="n">
-        <v>6.89</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="87">
@@ -4037,49 +4037,49 @@
         <v>132</v>
       </c>
       <c r="B92" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D92" t="n">
         <v>6.4</v>
       </c>
-      <c r="C92" s="1" t="n">
+      <c r="E92" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D92" t="n">
+      <c r="F92" t="n">
         <v>7</v>
       </c>
-      <c r="E92" s="1" t="n">
+      <c r="G92" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="F92" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G92" s="1" t="n">
+      <c r="H92" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I92" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="H92" t="n">
+      <c r="J92" t="n">
         <v>7.5</v>
       </c>
-      <c r="I92" s="1" t="n">
+      <c r="K92" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="J92" t="n">
+      <c r="L92" t="n">
         <v>7.7</v>
       </c>
-      <c r="K92" s="1" t="n">
+      <c r="M92" s="1" t="n">
         <v>45983</v>
-      </c>
-      <c r="L92" t="n">
-        <v>7</v>
-      </c>
-      <c r="M92" s="1" t="n">
-        <v>45969</v>
       </c>
       <c r="N92" t="n">
         <v>7</v>
       </c>
       <c r="O92" s="1" t="n">
-        <v>45963</v>
+        <v>45969</v>
       </c>
       <c r="P92" t="n">
-        <v>7.03</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="93">
@@ -4087,49 +4087,49 @@
         <v>133</v>
       </c>
       <c r="B93" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D93" t="n">
         <v>6.9</v>
       </c>
-      <c r="C93" s="1" t="n">
+      <c r="E93" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D93" t="n">
+      <c r="F93" t="n">
         <v>7.3</v>
       </c>
-      <c r="E93" s="1" t="n">
+      <c r="G93" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F93" t="n">
+      <c r="H93" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G93" s="1" t="n">
+      <c r="I93" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="H93" t="n">
+      <c r="J93" t="n">
         <v>6.1</v>
       </c>
-      <c r="I93" s="1" t="n">
+      <c r="K93" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J93" t="n">
+      <c r="L93" t="n">
         <v>7.7</v>
       </c>
-      <c r="K93" s="1" t="n">
+      <c r="M93" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="L93" t="n">
+      <c r="N93" t="n">
         <v>7.4</v>
       </c>
-      <c r="M93" s="1" t="n">
+      <c r="O93" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N93" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O93" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P93" t="n">
-        <v>7.11</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="94">
@@ -4187,49 +4187,49 @@
         <v>135</v>
       </c>
       <c r="B95" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="C95" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D95" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E95" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D95" t="n">
+      <c r="F95" t="n">
         <v>7.5</v>
       </c>
-      <c r="E95" s="1" t="n">
+      <c r="G95" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="F95" t="n">
+      <c r="H95" t="n">
         <v>8.1</v>
       </c>
-      <c r="G95" s="1" t="n">
+      <c r="I95" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="H95" t="n">
+      <c r="J95" t="n">
         <v>7.7</v>
       </c>
-      <c r="I95" s="1" t="n">
+      <c r="K95" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="J95" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K95" s="1" t="n">
+      <c r="L95" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M95" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="L95" t="n">
+      <c r="N95" t="n">
         <v>7.1</v>
       </c>
-      <c r="M95" s="1" t="n">
+      <c r="O95" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="N95" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O95" s="1" t="n">
-        <v>45956</v>
-      </c>
       <c r="P95" t="n">
-        <v>7.21</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="96">
@@ -4361,49 +4361,49 @@
         <v>143</v>
       </c>
       <c r="B100" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="D100" t="n">
         <v>7</v>
       </c>
-      <c r="C100" s="1" t="n">
+      <c r="E100" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D100" t="n">
+      <c r="F100" t="n">
         <v>6</v>
       </c>
-      <c r="E100" s="1" t="n">
+      <c r="G100" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F100" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G100" s="1" t="n">
+      <c r="H100" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I100" s="1" t="n">
         <v>46057</v>
       </c>
-      <c r="H100" t="n">
+      <c r="J100" t="n">
         <v>5.7</v>
       </c>
-      <c r="I100" s="1" t="n">
+      <c r="K100" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="J100" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K100" s="1" t="n">
+      <c r="L100" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M100" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="L100" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M100" s="1" t="n">
+      <c r="N100" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O100" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="N100" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O100" s="1" t="n">
-        <v>45948</v>
-      </c>
       <c r="P100" t="n">
-        <v>6.41</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="101">
@@ -4411,49 +4411,49 @@
         <v>144</v>
       </c>
       <c r="B101" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="C101" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D101" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E101" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="D101" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E101" s="1" t="n">
+      <c r="F101" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G101" s="1" t="n">
         <v>45972</v>
       </c>
-      <c r="F101" t="n">
+      <c r="H101" t="n">
         <v>7.1</v>
       </c>
-      <c r="G101" s="1" t="n">
+      <c r="I101" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="H101" t="n">
+      <c r="J101" t="n">
         <v>6.4</v>
       </c>
-      <c r="I101" s="1" t="n">
+      <c r="K101" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="J101" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K101" s="1" t="n">
+      <c r="L101" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M101" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="L101" t="n">
+      <c r="N101" t="n">
         <v>6.4</v>
       </c>
-      <c r="M101" s="1" t="n">
+      <c r="O101" s="1" t="n">
         <v>45923</v>
       </c>
-      <c r="N101" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O101" s="1" t="n">
-        <v>45913</v>
-      </c>
       <c r="P101" t="n">
-        <v>6.63</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="102">
@@ -4461,46 +4461,46 @@
         <v>145</v>
       </c>
       <c r="B102" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C102" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D102" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F102" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G102" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="D102" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E102" s="1" t="n">
+      <c r="H102" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I102" s="1" t="n">
         <v>46057</v>
       </c>
-      <c r="F102" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G102" s="1" t="n">
+      <c r="J102" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K102" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="H102" t="n">
+      <c r="L102" t="n">
         <v>6.3</v>
       </c>
-      <c r="I102" s="1" t="n">
+      <c r="M102" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="J102" t="n">
+      <c r="N102" t="n">
         <v>8.1</v>
       </c>
-      <c r="K102" s="1" t="n">
+      <c r="O102" s="1" t="n">
         <v>46005</v>
-      </c>
-      <c r="L102" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M102" s="1" t="n">
-        <v>45969</v>
-      </c>
-      <c r="N102" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O102" s="1" t="n">
-        <v>45954</v>
       </c>
       <c r="P102" t="n">
         <v>6.79</v>
@@ -4511,49 +4511,49 @@
         <v>146</v>
       </c>
       <c r="B103" t="n">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="C103" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D103" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E103" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D103" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E103" s="1" t="n">
+      <c r="F103" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G103" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F103" t="n">
+      <c r="H103" t="n">
         <v>6</v>
       </c>
-      <c r="G103" s="1" t="n">
+      <c r="I103" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="H103" t="n">
+      <c r="J103" t="n">
         <v>7.1</v>
       </c>
-      <c r="I103" s="1" t="n">
+      <c r="K103" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J103" t="n">
+      <c r="L103" t="n">
         <v>7.3</v>
       </c>
-      <c r="K103" s="1" t="n">
+      <c r="M103" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="L103" t="n">
+      <c r="N103" t="n">
         <v>6.8</v>
       </c>
-      <c r="M103" s="1" t="n">
+      <c r="O103" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="N103" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O103" s="1" t="n">
-        <v>46004</v>
-      </c>
       <c r="P103" t="n">
-        <v>6.81</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="104">
@@ -4561,49 +4561,49 @@
         <v>147</v>
       </c>
       <c r="B104" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D104" t="n">
         <v>6.2</v>
       </c>
-      <c r="C104" s="1" t="n">
+      <c r="E104" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D104" t="n">
+      <c r="F104" t="n">
         <v>7.1</v>
       </c>
-      <c r="E104" s="1" t="n">
+      <c r="G104" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F104" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G104" s="1" t="n">
+      <c r="H104" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I104" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="H104" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I104" s="1" t="n">
+      <c r="J104" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K104" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J104" t="n">
+      <c r="L104" t="n">
         <v>6.2</v>
       </c>
-      <c r="K104" s="1" t="n">
+      <c r="M104" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="L104" t="n">
+      <c r="N104" t="n">
         <v>7.6</v>
       </c>
-      <c r="M104" s="1" t="n">
+      <c r="O104" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="N104" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O104" s="1" t="n">
-        <v>46011</v>
-      </c>
       <c r="P104" t="n">
-        <v>6.69</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="105">
@@ -5073,49 +5073,49 @@
         <v>167</v>
       </c>
       <c r="B116" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D116" t="n">
         <v>8.1</v>
       </c>
-      <c r="C116" s="1" t="n">
+      <c r="E116" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D116" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E116" s="1" t="n">
+      <c r="F116" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G116" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F116" t="n">
+      <c r="H116" t="n">
         <v>7.1</v>
       </c>
-      <c r="G116" s="1" t="n">
+      <c r="I116" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="H116" t="n">
+      <c r="J116" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I116" s="1" t="n">
+      <c r="K116" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J116" t="n">
+      <c r="L116" t="n">
         <v>7.8</v>
       </c>
-      <c r="K116" s="1" t="n">
+      <c r="M116" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="L116" t="n">
+      <c r="N116" t="n">
         <v>7.1</v>
       </c>
-      <c r="M116" s="1" t="n">
+      <c r="O116" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="N116" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O116" s="1" t="n">
-        <v>45968</v>
-      </c>
       <c r="P116" t="n">
-        <v>7.39</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="117">
@@ -5473,49 +5473,49 @@
         <v>175</v>
       </c>
       <c r="B124" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C124" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D124" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E124" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F124" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G124" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="D124" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E124" s="1" t="n">
+      <c r="H124" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I124" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="F124" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G124" s="1" t="n">
+      <c r="J124" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K124" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H124" t="n">
+      <c r="L124" t="n">
         <v>7.3</v>
       </c>
-      <c r="I124" s="1" t="n">
+      <c r="M124" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J124" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K124" s="1" t="n">
+      <c r="N124" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O124" s="1" t="n">
         <v>45985</v>
       </c>
-      <c r="L124" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M124" s="1" t="n">
-        <v>45970</v>
-      </c>
-      <c r="N124" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O124" s="1" t="n">
-        <v>45962</v>
-      </c>
       <c r="P124" t="n">
-        <v>6.76</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="125">
@@ -5699,49 +5699,49 @@
         <v>181</v>
       </c>
       <c r="B129" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D129" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E129" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F129" t="n">
         <v>7.1</v>
       </c>
-      <c r="C129" s="1" t="n">
+      <c r="G129" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="D129" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E129" s="1" t="n">
+      <c r="H129" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I129" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="F129" t="n">
+      <c r="J129" t="n">
         <v>7</v>
       </c>
-      <c r="G129" s="1" t="n">
+      <c r="K129" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H129" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I129" s="1" t="n">
+      <c r="L129" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M129" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J129" t="n">
+      <c r="N129" t="n">
         <v>6.8</v>
       </c>
-      <c r="K129" s="1" t="n">
+      <c r="O129" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L129" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M129" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="N129" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O129" s="1" t="n">
-        <v>45962</v>
-      </c>
       <c r="P129" t="n">
-        <v>6.89</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="130">
@@ -5929,49 +5929,49 @@
         <v>186</v>
       </c>
       <c r="B134" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D134" t="n">
         <v>6.2</v>
       </c>
-      <c r="C134" s="1" t="n">
+      <c r="E134" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="D134" t="n">
+      <c r="F134" t="n">
         <v>7.2</v>
       </c>
-      <c r="E134" s="1" t="n">
+      <c r="G134" s="1" t="n">
         <v>46051</v>
       </c>
-      <c r="F134" t="n">
+      <c r="H134" t="n">
         <v>6</v>
       </c>
-      <c r="G134" s="1" t="n">
+      <c r="I134" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="H134" t="n">
+      <c r="J134" t="n">
         <v>6.8</v>
       </c>
-      <c r="I134" s="1" t="n">
+      <c r="K134" s="1" t="n">
         <v>46028</v>
       </c>
-      <c r="J134" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K134" s="1" t="n">
+      <c r="L134" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M134" s="1" t="n">
         <v>46024</v>
       </c>
-      <c r="L134" t="n">
+      <c r="N134" t="n">
         <v>8.1</v>
       </c>
-      <c r="M134" s="1" t="n">
+      <c r="O134" s="1" t="n">
         <v>46020</v>
       </c>
-      <c r="N134" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O134" s="1" t="n">
-        <v>46011</v>
-      </c>
       <c r="P134" t="n">
-        <v>6.74</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="135">
@@ -6049,49 +6049,49 @@
         <v>190</v>
       </c>
       <c r="B137" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="C137" s="1" t="n">
+        <v>46067</v>
+      </c>
+      <c r="D137" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E137" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="D137" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E137" s="1" t="n">
+      <c r="F137" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G137" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="F137" t="n">
+      <c r="H137" t="n">
         <v>7.2</v>
       </c>
-      <c r="G137" s="1" t="n">
+      <c r="I137" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="H137" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I137" s="1" t="n">
+      <c r="J137" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K137" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="J137" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K137" s="1" t="n">
+      <c r="L137" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M137" s="1" t="n">
         <v>45914</v>
       </c>
-      <c r="L137" t="n">
+      <c r="N137" t="n">
         <v>6.4</v>
       </c>
-      <c r="M137" s="1" t="n">
+      <c r="O137" s="1" t="n">
         <v>45906</v>
       </c>
-      <c r="N137" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O137" s="1" t="n">
-        <v>45899</v>
-      </c>
       <c r="P137" t="n">
-        <v>6.63</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="138">
@@ -6099,46 +6099,46 @@
         <v>191</v>
       </c>
       <c r="B138" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="C138" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D138" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E138" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="D138" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E138" s="1" t="n">
+      <c r="F138" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G138" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="F138" t="n">
+      <c r="H138" t="n">
         <v>6.2</v>
       </c>
-      <c r="G138" s="1" t="n">
+      <c r="I138" s="1" t="n">
         <v>45920</v>
       </c>
-      <c r="H138" t="n">
+      <c r="J138" t="n">
         <v>6.9</v>
       </c>
-      <c r="I138" s="1" t="n">
+      <c r="K138" s="1" t="n">
         <v>45899</v>
       </c>
-      <c r="J138" t="n">
+      <c r="L138" t="n">
         <v>6.1</v>
       </c>
-      <c r="K138" s="1" t="n">
+      <c r="M138" s="1" t="n">
         <v>45892</v>
       </c>
-      <c r="L138" t="n">
+      <c r="N138" t="n">
         <v>6.8</v>
       </c>
-      <c r="M138" s="1" t="n">
+      <c r="O138" s="1" t="n">
         <v>45885</v>
-      </c>
-      <c r="N138" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O138" s="1" t="n">
-        <v>45878</v>
       </c>
       <c r="P138" t="n">
         <v>6.53</v>
@@ -6283,49 +6283,49 @@
         <v>195</v>
       </c>
       <c r="B142" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D142" t="n">
         <v>7.7</v>
       </c>
-      <c r="C142" s="1" t="n">
+      <c r="E142" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D142" t="n">
+      <c r="F142" t="n">
         <v>5.8</v>
       </c>
-      <c r="E142" s="1" t="n">
+      <c r="G142" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="F142" t="n">
+      <c r="H142" t="n">
         <v>6.4</v>
       </c>
-      <c r="G142" s="1" t="n">
+      <c r="I142" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="H142" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I142" s="1" t="n">
+      <c r="J142" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K142" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="J142" t="n">
+      <c r="L142" t="n">
         <v>7.1</v>
       </c>
-      <c r="K142" s="1" t="n">
+      <c r="M142" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="L142" t="n">
+      <c r="N142" t="n">
         <v>7</v>
       </c>
-      <c r="M142" s="1" t="n">
+      <c r="O142" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="N142" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O142" s="1" t="n">
-        <v>45995</v>
-      </c>
       <c r="P142" t="n">
-        <v>6.77</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="143">
@@ -6409,49 +6409,49 @@
         <v>198</v>
       </c>
       <c r="B145" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D145" t="n">
         <v>6.4</v>
       </c>
-      <c r="C145" s="1" t="n">
+      <c r="E145" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="D145" t="n">
+      <c r="F145" t="n">
         <v>7</v>
       </c>
-      <c r="E145" s="1" t="n">
+      <c r="G145" s="1" t="n">
         <v>46013</v>
       </c>
-      <c r="F145" t="n">
+      <c r="H145" t="n">
         <v>6.9</v>
       </c>
-      <c r="G145" s="1" t="n">
+      <c r="I145" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H145" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I145" s="1" t="n">
+      <c r="J145" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K145" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="J145" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K145" s="1" t="n">
+      <c r="L145" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M145" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L145" t="n">
+      <c r="N145" t="n">
         <v>6.9</v>
       </c>
-      <c r="M145" s="1" t="n">
+      <c r="O145" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="N145" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O145" s="1" t="n">
-        <v>45948</v>
-      </c>
       <c r="P145" t="n">
-        <v>6.61</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="146">
@@ -6459,49 +6459,49 @@
         <v>200</v>
       </c>
       <c r="B146" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D146" t="n">
         <v>7.9</v>
       </c>
-      <c r="C146" s="1" t="n">
+      <c r="E146" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D146" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E146" s="1" t="n">
+      <c r="F146" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G146" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F146" t="n">
+      <c r="H146" t="n">
         <v>6.3</v>
       </c>
-      <c r="G146" s="1" t="n">
+      <c r="I146" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H146" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I146" s="1" t="n">
+      <c r="J146" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K146" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="J146" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K146" s="1" t="n">
+      <c r="L146" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M146" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="L146" t="n">
+      <c r="N146" t="n">
         <v>6.8</v>
       </c>
-      <c r="M146" s="1" t="n">
+      <c r="O146" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="N146" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O146" s="1" t="n">
-        <v>45934</v>
-      </c>
       <c r="P146" t="n">
-        <v>6.73</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="147">
@@ -6509,49 +6509,49 @@
         <v>201</v>
       </c>
       <c r="B147" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D147" t="n">
         <v>5.7</v>
       </c>
-      <c r="C147" s="1" t="n">
+      <c r="E147" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D147" t="n">
+      <c r="F147" t="n">
         <v>6</v>
       </c>
-      <c r="E147" s="1" t="n">
+      <c r="G147" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F147" t="n">
+      <c r="H147" t="n">
         <v>6.2</v>
       </c>
-      <c r="G147" s="1" t="n">
+      <c r="I147" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H147" t="n">
+      <c r="J147" t="n">
         <v>6.9</v>
       </c>
-      <c r="I147" s="1" t="n">
+      <c r="K147" s="1" t="n">
         <v>45949</v>
       </c>
-      <c r="J147" t="n">
+      <c r="L147" t="n">
         <v>7.5</v>
       </c>
-      <c r="K147" s="1" t="n">
+      <c r="M147" s="1" t="n">
         <v>45934</v>
       </c>
-      <c r="L147" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M147" s="1" t="n">
+      <c r="N147" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O147" s="1" t="n">
         <v>45928</v>
       </c>
-      <c r="N147" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O147" s="1" t="n">
-        <v>45920</v>
-      </c>
       <c r="P147" t="n">
-        <v>6.51</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="148">
@@ -8135,49 +8135,49 @@
         <v>247</v>
       </c>
       <c r="B187" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D187" t="n">
         <v>5.8</v>
       </c>
-      <c r="C187" s="1" t="n">
+      <c r="E187" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D187" t="n">
+      <c r="F187" t="n">
         <v>8.1</v>
       </c>
-      <c r="E187" s="1" t="n">
+      <c r="G187" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F187" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G187" s="1" t="n">
+      <c r="H187" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I187" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="H187" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I187" s="1" t="n">
+      <c r="J187" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K187" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="J187" t="n">
+      <c r="L187" t="n">
         <v>7</v>
       </c>
-      <c r="K187" s="1" t="n">
+      <c r="M187" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="L187" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M187" s="1" t="n">
+      <c r="N187" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O187" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N187" t="n">
-        <v>8</v>
-      </c>
-      <c r="O187" s="1" t="n">
-        <v>45989</v>
-      </c>
       <c r="P187" t="n">
-        <v>6.97</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="188">
@@ -8285,49 +8285,49 @@
         <v>255</v>
       </c>
       <c r="B191" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C191" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D191" t="n">
         <v>6.4</v>
       </c>
-      <c r="C191" s="1" t="n">
+      <c r="E191" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="D191" t="n">
+      <c r="F191" t="n">
         <v>7.2</v>
       </c>
-      <c r="E191" s="1" t="n">
+      <c r="G191" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="F191" t="n">
+      <c r="H191" t="n">
         <v>7.9</v>
       </c>
-      <c r="G191" s="1" t="n">
+      <c r="I191" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="H191" t="n">
+      <c r="J191" t="n">
         <v>7.1</v>
       </c>
-      <c r="I191" s="1" t="n">
+      <c r="K191" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="J191" t="n">
+      <c r="L191" t="n">
         <v>7.2</v>
       </c>
-      <c r="K191" s="1" t="n">
+      <c r="M191" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L191" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M191" s="1" t="n">
+      <c r="N191" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O191" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N191" t="n">
-        <v>6</v>
-      </c>
-      <c r="O191" s="1" t="n">
-        <v>45921</v>
-      </c>
       <c r="P191" t="n">
-        <v>6.91</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="192">
@@ -8385,49 +8385,49 @@
         <v>258</v>
       </c>
       <c r="B193" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D193" t="n">
         <v>6.3</v>
       </c>
-      <c r="C193" s="1" t="n">
+      <c r="E193" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="D193" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E193" s="1" t="n">
+      <c r="F193" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G193" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="F193" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G193" s="1" t="n">
+      <c r="H193" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I193" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H193" t="n">
+      <c r="J193" t="n">
         <v>7</v>
       </c>
-      <c r="I193" s="1" t="n">
+      <c r="K193" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="J193" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K193" s="1" t="n">
+      <c r="L193" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M193" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="L193" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M193" s="1" t="n">
+      <c r="N193" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O193" s="1" t="n">
         <v>45929</v>
       </c>
-      <c r="N193" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O193" s="1" t="n">
-        <v>45886</v>
-      </c>
       <c r="P193" t="n">
-        <v>6.6</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="194">
@@ -8435,49 +8435,49 @@
         <v>259</v>
       </c>
       <c r="B194" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C194" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D194" t="n">
         <v>7.4</v>
       </c>
-      <c r="C194" s="1" t="n">
+      <c r="E194" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D194" t="n">
+      <c r="F194" t="n">
         <v>6.2</v>
       </c>
-      <c r="E194" s="1" t="n">
+      <c r="G194" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="F194" t="n">
+      <c r="H194" t="n">
         <v>6.3</v>
       </c>
-      <c r="G194" s="1" t="n">
+      <c r="I194" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="H194" t="n">
+      <c r="J194" t="n">
         <v>7.6</v>
       </c>
-      <c r="I194" s="1" t="n">
+      <c r="K194" s="1" t="n">
         <v>45950</v>
-      </c>
-      <c r="J194" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K194" s="1" t="n">
-        <v>45935</v>
       </c>
       <c r="L194" t="n">
         <v>6.8</v>
       </c>
       <c r="M194" s="1" t="n">
+        <v>45935</v>
+      </c>
+      <c r="N194" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O194" s="1" t="n">
         <v>45928</v>
       </c>
-      <c r="N194" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O194" s="1" t="n">
-        <v>45921</v>
-      </c>
       <c r="P194" t="n">
-        <v>6.96</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="195">
@@ -8705,46 +8705,46 @@
         <v>273</v>
       </c>
       <c r="B200" t="n">
+        <v>7</v>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D200" t="n">
         <v>6.2</v>
       </c>
-      <c r="C200" s="1" t="n">
+      <c r="E200" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D200" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E200" s="1" t="n">
+      <c r="F200" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G200" s="1" t="n">
         <v>46065</v>
-      </c>
-      <c r="F200" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G200" s="1" t="n">
-        <v>46061</v>
       </c>
       <c r="H200" t="n">
         <v>7.1</v>
       </c>
       <c r="I200" s="1" t="n">
+        <v>46061</v>
+      </c>
+      <c r="J200" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K200" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J200" t="n">
+      <c r="L200" t="n">
         <v>6.2</v>
       </c>
-      <c r="K200" s="1" t="n">
+      <c r="M200" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="L200" t="n">
+      <c r="N200" t="n">
         <v>4.5</v>
       </c>
-      <c r="M200" s="1" t="n">
+      <c r="O200" s="1" t="n">
         <v>46005</v>
-      </c>
-      <c r="N200" t="n">
-        <v>7</v>
-      </c>
-      <c r="O200" s="1" t="n">
-        <v>45998</v>
       </c>
       <c r="P200" t="n">
         <v>6.4</v>
@@ -9139,49 +9139,49 @@
         <v>282</v>
       </c>
       <c r="B209" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C209" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D209" t="n">
         <v>7.2</v>
       </c>
-      <c r="C209" s="1" t="n">
+      <c r="E209" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D209" t="n">
+      <c r="F209" t="n">
         <v>7</v>
       </c>
-      <c r="E209" s="1" t="n">
+      <c r="G209" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F209" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G209" s="1" t="n">
+      <c r="H209" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I209" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H209" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I209" s="1" t="n">
+      <c r="J209" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K209" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="J209" t="n">
+      <c r="L209" t="n">
         <v>6.8</v>
       </c>
-      <c r="K209" s="1" t="n">
+      <c r="M209" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="L209" t="n">
+      <c r="N209" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="M209" s="1" t="n">
+      <c r="O209" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="N209" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O209" s="1" t="n">
-        <v>45998</v>
-      </c>
       <c r="P209" t="n">
-        <v>7.13</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="210">
@@ -9285,49 +9285,49 @@
         <v>286</v>
       </c>
       <c r="B212" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C212" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D212" t="n">
         <v>7.4</v>
       </c>
-      <c r="C212" s="1" t="n">
+      <c r="E212" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D212" t="n">
+      <c r="F212" t="n">
         <v>6.2</v>
       </c>
-      <c r="E212" s="1" t="n">
+      <c r="G212" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F212" t="n">
+      <c r="H212" t="n">
         <v>7.8</v>
       </c>
-      <c r="G212" s="1" t="n">
+      <c r="I212" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H212" t="n">
+      <c r="J212" t="n">
         <v>7.4</v>
       </c>
-      <c r="I212" s="1" t="n">
+      <c r="K212" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="J212" t="n">
+      <c r="L212" t="n">
         <v>7.7</v>
       </c>
-      <c r="K212" s="1" t="n">
+      <c r="M212" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="L212" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M212" s="1" t="n">
+      <c r="N212" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O212" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="N212" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O212" s="1" t="n">
-        <v>45990</v>
-      </c>
       <c r="P212" t="n">
-        <v>7.1</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="213">
@@ -9435,49 +9435,49 @@
         <v>289</v>
       </c>
       <c r="B215" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D215" t="n">
         <v>6.8</v>
       </c>
-      <c r="C215" s="1" t="n">
+      <c r="E215" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D215" t="n">
+      <c r="F215" t="n">
         <v>6.3</v>
       </c>
-      <c r="E215" s="1" t="n">
+      <c r="G215" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F215" t="n">
+      <c r="H215" t="n">
         <v>7.2</v>
       </c>
-      <c r="G215" s="1" t="n">
+      <c r="I215" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H215" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I215" s="1" t="n">
+      <c r="J215" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K215" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="J215" t="n">
+      <c r="L215" t="n">
         <v>7</v>
       </c>
-      <c r="K215" s="1" t="n">
+      <c r="M215" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="L215" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M215" s="1" t="n">
+      <c r="N215" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O215" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="N215" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O215" s="1" t="n">
-        <v>45984</v>
-      </c>
       <c r="P215" t="n">
-        <v>6.81</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="216">
@@ -9485,49 +9485,49 @@
         <v>290</v>
       </c>
       <c r="B216" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="C216" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D216" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E216" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D216" t="n">
+      <c r="F216" t="n">
         <v>7.9</v>
       </c>
-      <c r="E216" s="1" t="n">
+      <c r="G216" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="F216" t="n">
+      <c r="H216" t="n">
         <v>7.8</v>
       </c>
-      <c r="G216" s="1" t="n">
+      <c r="I216" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="H216" t="n">
+      <c r="J216" t="n">
         <v>7.3</v>
       </c>
-      <c r="I216" s="1" t="n">
+      <c r="K216" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="J216" t="n">
+      <c r="L216" t="n">
         <v>6.2</v>
       </c>
-      <c r="K216" s="1" t="n">
+      <c r="M216" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="L216" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M216" s="1" t="n">
+      <c r="N216" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O216" s="1" t="n">
         <v>45964</v>
       </c>
-      <c r="N216" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O216" s="1" t="n">
-        <v>45955</v>
-      </c>
       <c r="P216" t="n">
-        <v>7.06</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="217">
@@ -9723,49 +9723,49 @@
         <v>295</v>
       </c>
       <c r="B221" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D221" t="n">
         <v>7.3</v>
       </c>
-      <c r="C221" s="1" t="n">
+      <c r="E221" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="D221" t="n">
+      <c r="F221" t="n">
         <v>6.8</v>
       </c>
-      <c r="E221" s="1" t="n">
+      <c r="G221" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="F221" t="n">
+      <c r="H221" t="n">
         <v>7.3</v>
       </c>
-      <c r="G221" s="1" t="n">
+      <c r="I221" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="H221" t="n">
+      <c r="J221" t="n">
         <v>7.5</v>
       </c>
-      <c r="I221" s="1" t="n">
+      <c r="K221" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J221" t="n">
+      <c r="L221" t="n">
         <v>7.9</v>
       </c>
-      <c r="K221" s="1" t="n">
+      <c r="M221" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L221" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M221" s="1" t="n">
+      <c r="N221" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O221" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="N221" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O221" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P221" t="n">
-        <v>7.09</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="222">
@@ -10011,49 +10011,49 @@
         <v>302</v>
       </c>
       <c r="B227" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C227" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D227" t="n">
         <v>7.6</v>
       </c>
-      <c r="C227" s="1" t="n">
+      <c r="E227" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D227" t="n">
+      <c r="F227" t="n">
         <v>7</v>
       </c>
-      <c r="E227" s="1" t="n">
+      <c r="G227" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F227" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G227" s="1" t="n">
+      <c r="H227" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I227" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H227" t="n">
+      <c r="J227" t="n">
         <v>5.5</v>
       </c>
-      <c r="I227" s="1" t="n">
+      <c r="K227" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="J227" t="n">
+      <c r="L227" t="n">
         <v>6.3</v>
       </c>
-      <c r="K227" s="1" t="n">
+      <c r="M227" s="1" t="n">
         <v>45928</v>
-      </c>
-      <c r="L227" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M227" s="1" t="n">
-        <v>45919</v>
       </c>
       <c r="N227" t="n">
         <v>5.4</v>
       </c>
       <c r="O227" s="1" t="n">
-        <v>45914</v>
+        <v>45919</v>
       </c>
       <c r="P227" t="n">
-        <v>6.27</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="228">
@@ -10061,49 +10061,49 @@
         <v>303</v>
       </c>
       <c r="B228" t="n">
+        <v>7</v>
+      </c>
+      <c r="C228" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D228" t="n">
         <v>6.9</v>
       </c>
-      <c r="C228" s="1" t="n">
+      <c r="E228" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D228" t="n">
+      <c r="F228" t="n">
         <v>6.8</v>
       </c>
-      <c r="E228" s="1" t="n">
+      <c r="G228" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F228" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G228" s="1" t="n">
+      <c r="H228" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I228" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="H228" t="n">
+      <c r="J228" t="n">
         <v>7.1</v>
       </c>
-      <c r="I228" s="1" t="n">
+      <c r="K228" s="1" t="n">
         <v>45994</v>
       </c>
-      <c r="J228" t="n">
+      <c r="L228" t="n">
         <v>7.2</v>
       </c>
-      <c r="K228" s="1" t="n">
+      <c r="M228" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L228" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M228" s="1" t="n">
+      <c r="N228" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O228" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N228" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O228" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P228" t="n">
-        <v>6.81</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="229">
@@ -10111,49 +10111,49 @@
         <v>305</v>
       </c>
       <c r="B229" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C229" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D229" t="n">
         <v>7</v>
       </c>
-      <c r="C229" s="1" t="n">
+      <c r="E229" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D229" t="n">
+      <c r="F229" t="n">
         <v>5.9</v>
       </c>
-      <c r="E229" s="1" t="n">
+      <c r="G229" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F229" t="n">
+      <c r="H229" t="n">
         <v>7</v>
       </c>
-      <c r="G229" s="1" t="n">
+      <c r="I229" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H229" t="n">
+      <c r="J229" t="n">
         <v>6.4</v>
       </c>
-      <c r="I229" s="1" t="n">
+      <c r="K229" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="J229" t="n">
+      <c r="L229" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K229" s="1" t="n">
+      <c r="M229" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L229" t="n">
+      <c r="N229" t="n">
         <v>7</v>
       </c>
-      <c r="M229" s="1" t="n">
+      <c r="O229" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N229" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O229" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P229" t="n">
-        <v>7.03</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="230">
@@ -10311,49 +10311,49 @@
         <v>309</v>
       </c>
       <c r="B233" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C233" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D233" t="n">
         <v>5.2</v>
       </c>
-      <c r="C233" s="1" t="n">
+      <c r="E233" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D233" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E233" s="1" t="n">
+      <c r="F233" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G233" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F233" t="n">
+      <c r="H233" t="n">
         <v>6.3</v>
       </c>
-      <c r="G233" s="1" t="n">
+      <c r="I233" s="1" t="n">
         <v>46005</v>
-      </c>
-      <c r="H233" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I233" s="1" t="n">
-        <v>45990</v>
       </c>
       <c r="J233" t="n">
         <v>6.4</v>
       </c>
       <c r="K233" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="L233" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M233" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="L233" t="n">
+      <c r="N233" t="n">
         <v>7.2</v>
       </c>
-      <c r="M233" s="1" t="n">
+      <c r="O233" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N233" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O233" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P233" t="n">
-        <v>6.43</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="234">
@@ -10361,49 +10361,49 @@
         <v>310</v>
       </c>
       <c r="B234" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C234" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D234" t="n">
         <v>7.1</v>
       </c>
-      <c r="C234" s="1" t="n">
+      <c r="E234" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D234" t="n">
+      <c r="F234" t="n">
         <v>7.7</v>
       </c>
-      <c r="E234" s="1" t="n">
+      <c r="G234" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F234" t="n">
+      <c r="H234" t="n">
         <v>6.4</v>
       </c>
-      <c r="G234" s="1" t="n">
+      <c r="I234" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H234" t="n">
+      <c r="J234" t="n">
         <v>6.2</v>
       </c>
-      <c r="I234" s="1" t="n">
+      <c r="K234" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J234" t="n">
+      <c r="L234" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K234" s="1" t="n">
+      <c r="M234" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L234" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M234" s="1" t="n">
+      <c r="N234" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O234" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N234" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O234" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P234" t="n">
-        <v>7.1</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="235">
@@ -10411,49 +10411,49 @@
         <v>311</v>
       </c>
       <c r="B235" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C235" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D235" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E235" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F235" t="n">
         <v>7</v>
       </c>
-      <c r="C235" s="1" t="n">
+      <c r="G235" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="D235" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E235" s="1" t="n">
+      <c r="H235" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I235" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="F235" t="n">
+      <c r="J235" t="n">
         <v>6.9</v>
       </c>
-      <c r="G235" s="1" t="n">
+      <c r="K235" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="H235" t="n">
+      <c r="L235" t="n">
         <v>7.1</v>
       </c>
-      <c r="I235" s="1" t="n">
+      <c r="M235" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="J235" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K235" s="1" t="n">
+      <c r="N235" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O235" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="L235" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M235" s="1" t="n">
-        <v>45963</v>
-      </c>
-      <c r="N235" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O235" s="1" t="n">
-        <v>45956</v>
-      </c>
       <c r="P235" t="n">
-        <v>6.94</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="236">
@@ -10461,49 +10461,49 @@
         <v>312</v>
       </c>
       <c r="B236" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C236" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D236" t="n">
         <v>7.2</v>
       </c>
-      <c r="C236" s="1" t="n">
+      <c r="E236" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D236" t="n">
+      <c r="F236" t="n">
         <v>6.3</v>
       </c>
-      <c r="E236" s="1" t="n">
+      <c r="G236" s="1" t="n">
         <v>46061</v>
-      </c>
-      <c r="F236" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G236" s="1" t="n">
-        <v>46053</v>
       </c>
       <c r="H236" t="n">
         <v>7.1</v>
       </c>
       <c r="I236" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="J236" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K236" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="J236" t="n">
+      <c r="L236" t="n">
         <v>7.7</v>
       </c>
-      <c r="K236" s="1" t="n">
+      <c r="M236" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="L236" t="n">
+      <c r="N236" t="n">
         <v>6.4</v>
       </c>
-      <c r="M236" s="1" t="n">
+      <c r="O236" s="1" t="n">
         <v>46033</v>
       </c>
-      <c r="N236" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O236" s="1" t="n">
-        <v>46011</v>
-      </c>
       <c r="P236" t="n">
-        <v>6.94</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="237">
@@ -10611,49 +10611,49 @@
         <v>315</v>
       </c>
       <c r="B239" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C239" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D239" t="n">
         <v>7.4</v>
       </c>
-      <c r="C239" s="1" t="n">
+      <c r="E239" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D239" t="n">
+      <c r="F239" t="n">
         <v>8.1</v>
       </c>
-      <c r="E239" s="1" t="n">
+      <c r="G239" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F239" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G239" s="1" t="n">
+      <c r="H239" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I239" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H239" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I239" s="1" t="n">
+      <c r="J239" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K239" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="J239" t="n">
+      <c r="L239" t="n">
         <v>6.8</v>
       </c>
-      <c r="K239" s="1" t="n">
+      <c r="M239" s="1" t="n">
         <v>46043</v>
       </c>
-      <c r="L239" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M239" s="1" t="n">
+      <c r="N239" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O239" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="N239" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O239" s="1" t="n">
-        <v>46032</v>
-      </c>
       <c r="P239" t="n">
-        <v>6.96</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="240">
@@ -10711,49 +10711,49 @@
         <v>317</v>
       </c>
       <c r="B241" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C241" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D241" t="n">
         <v>6.1</v>
       </c>
-      <c r="C241" s="1" t="n">
+      <c r="E241" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="D241" t="n">
+      <c r="F241" t="n">
         <v>6.4</v>
       </c>
-      <c r="E241" s="1" t="n">
+      <c r="G241" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="F241" t="n">
+      <c r="H241" t="n">
         <v>6.1</v>
       </c>
-      <c r="G241" s="1" t="n">
+      <c r="I241" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="H241" t="n">
+      <c r="J241" t="n">
         <v>6.3</v>
       </c>
-      <c r="I241" s="1" t="n">
+      <c r="K241" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="J241" t="n">
+      <c r="L241" t="n">
         <v>7.1</v>
       </c>
-      <c r="K241" s="1" t="n">
+      <c r="M241" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="L241" t="n">
+      <c r="N241" t="n">
         <v>6.4</v>
       </c>
-      <c r="M241" s="1" t="n">
+      <c r="O241" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N241" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O241" s="1" t="n">
-        <v>45962</v>
-      </c>
       <c r="P241" t="n">
-        <v>6.39</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="242">
@@ -10761,49 +10761,49 @@
         <v>318</v>
       </c>
       <c r="B242" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C242" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="D242" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E242" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F242" t="n">
         <v>7</v>
       </c>
-      <c r="C242" s="1" t="n">
+      <c r="G242" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="D242" t="n">
+      <c r="H242" t="n">
         <v>6.8</v>
       </c>
-      <c r="E242" s="1" t="n">
+      <c r="I242" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="F242" t="n">
+      <c r="J242" t="n">
         <v>6.4</v>
       </c>
-      <c r="G242" s="1" t="n">
+      <c r="K242" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H242" t="n">
+      <c r="L242" t="n">
         <v>7.1</v>
       </c>
-      <c r="I242" s="1" t="n">
+      <c r="M242" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="J242" t="n">
+      <c r="N242" t="n">
         <v>6.9</v>
       </c>
-      <c r="K242" s="1" t="n">
+      <c r="O242" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L242" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M242" s="1" t="n">
-        <v>45956</v>
-      </c>
-      <c r="N242" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O242" s="1" t="n">
-        <v>45950</v>
-      </c>
       <c r="P242" t="n">
-        <v>6.76</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="243">
@@ -11245,49 +11245,49 @@
         <v>330</v>
       </c>
       <c r="B253" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C253" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D253" t="n">
         <v>7.9</v>
       </c>
-      <c r="C253" s="1" t="n">
+      <c r="E253" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="D253" t="n">
+      <c r="F253" t="n">
         <v>7</v>
       </c>
-      <c r="E253" s="1" t="n">
+      <c r="G253" s="1" t="n">
         <v>46058</v>
       </c>
-      <c r="F253" t="n">
+      <c r="H253" t="n">
         <v>6.9</v>
       </c>
-      <c r="G253" s="1" t="n">
+      <c r="I253" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H253" t="n">
+      <c r="J253" t="n">
         <v>6.4</v>
       </c>
-      <c r="I253" s="1" t="n">
+      <c r="K253" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J253" t="n">
+      <c r="L253" t="n">
         <v>6.8</v>
       </c>
-      <c r="K253" s="1" t="n">
+      <c r="M253" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L253" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M253" s="1" t="n">
+      <c r="N253" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O253" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="N253" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O253" s="1" t="n">
-        <v>45948</v>
-      </c>
       <c r="P253" t="n">
-        <v>6.89</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="254">
@@ -11445,49 +11445,49 @@
         <v>336</v>
       </c>
       <c r="B257" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C257" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D257" t="n">
         <v>6.9</v>
       </c>
-      <c r="C257" s="1" t="n">
+      <c r="E257" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D257" t="n">
+      <c r="F257" t="n">
         <v>6.1</v>
       </c>
-      <c r="E257" s="1" t="n">
+      <c r="G257" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F257" t="n">
+      <c r="H257" t="n">
         <v>7.4</v>
       </c>
-      <c r="G257" s="1" t="n">
+      <c r="I257" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H257" t="n">
+      <c r="J257" t="n">
         <v>6.8</v>
       </c>
-      <c r="I257" s="1" t="n">
+      <c r="K257" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J257" t="n">
+      <c r="L257" t="n">
         <v>6.2</v>
       </c>
-      <c r="K257" s="1" t="n">
+      <c r="M257" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L257" t="n">
+      <c r="N257" t="n">
         <v>6.9</v>
       </c>
-      <c r="M257" s="1" t="n">
+      <c r="O257" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="N257" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O257" s="1" t="n">
-        <v>45948</v>
-      </c>
       <c r="P257" t="n">
-        <v>6.71</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="258">
@@ -11495,49 +11495,49 @@
         <v>337</v>
       </c>
       <c r="B258" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C258" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D258" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E258" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D258" t="n">
+      <c r="F258" t="n">
         <v>7.5</v>
       </c>
-      <c r="E258" s="1" t="n">
+      <c r="G258" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F258" t="n">
+      <c r="H258" t="n">
         <v>6.9</v>
       </c>
-      <c r="G258" s="1" t="n">
+      <c r="I258" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H258" t="n">
+      <c r="J258" t="n">
         <v>7.1</v>
       </c>
-      <c r="I258" s="1" t="n">
+      <c r="K258" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J258" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K258" s="1" t="n">
+      <c r="L258" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M258" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L258" t="n">
+      <c r="N258" t="n">
         <v>7.1</v>
       </c>
-      <c r="M258" s="1" t="n">
+      <c r="O258" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N258" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O258" s="1" t="n">
-        <v>45934</v>
-      </c>
       <c r="P258" t="n">
-        <v>6.9</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="259">
@@ -11575,25 +11575,29 @@
         <v>339</v>
       </c>
       <c r="B260" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C260" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D260" t="n">
         <v>7</v>
       </c>
-      <c r="C260" s="1" t="n">
+      <c r="E260" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D260" t="n">
+      <c r="F260" t="n">
         <v>6.9</v>
       </c>
-      <c r="E260" s="1" t="n">
+      <c r="G260" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="F260" t="n">
+      <c r="H260" t="n">
         <v>6</v>
       </c>
-      <c r="G260" s="1" t="n">
+      <c r="I260" s="1" t="n">
         <v>45899</v>
       </c>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr"/>
@@ -11601,7 +11605,7 @@
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr"/>
       <c r="P260" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="261">
@@ -12259,49 +12263,49 @@
         <v>353</v>
       </c>
       <c r="B274" t="n">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="C274" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D274" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E274" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D274" t="n">
+      <c r="F274" t="n">
         <v>6.8</v>
       </c>
-      <c r="E274" s="1" t="n">
+      <c r="G274" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="F274" t="n">
+      <c r="H274" t="n">
         <v>8.1</v>
       </c>
-      <c r="G274" s="1" t="n">
+      <c r="I274" s="1" t="n">
         <v>46058</v>
       </c>
-      <c r="H274" t="n">
+      <c r="J274" t="n">
         <v>6.1</v>
       </c>
-      <c r="I274" s="1" t="n">
+      <c r="K274" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J274" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K274" s="1" t="n">
+      <c r="L274" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M274" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="L274" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M274" s="1" t="n">
+      <c r="N274" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O274" s="1" t="n">
         <v>46041</v>
       </c>
-      <c r="N274" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="O274" s="1" t="n">
-        <v>46013</v>
-      </c>
       <c r="P274" t="n">
-        <v>7.11</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="275">
@@ -12385,25 +12389,29 @@
         <v>356</v>
       </c>
       <c r="B277" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="C277" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="D277" t="n">
         <v>6.9</v>
       </c>
-      <c r="C277" s="1" t="n">
+      <c r="E277" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="D277" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E277" s="1" t="n">
+      <c r="F277" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G277" s="1" t="n">
         <v>45920</v>
       </c>
-      <c r="F277" t="n">
+      <c r="H277" t="n">
         <v>7.1</v>
       </c>
-      <c r="G277" s="1" t="n">
+      <c r="I277" s="1" t="n">
         <v>45911</v>
       </c>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
@@ -12411,7 +12419,7 @@
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="n">
-        <v>6.9</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="278">
@@ -12419,49 +12427,49 @@
         <v>357</v>
       </c>
       <c r="B278" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C278" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D278" t="n">
         <v>6.4</v>
       </c>
-      <c r="C278" s="1" t="n">
+      <c r="E278" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D278" t="n">
+      <c r="F278" t="n">
         <v>7</v>
       </c>
-      <c r="E278" s="1" t="n">
+      <c r="G278" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F278" t="n">
+      <c r="H278" t="n">
         <v>7.4</v>
       </c>
-      <c r="G278" s="1" t="n">
+      <c r="I278" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H278" t="n">
+      <c r="J278" t="n">
         <v>6.9</v>
       </c>
-      <c r="I278" s="1" t="n">
+      <c r="K278" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="J278" t="n">
+      <c r="L278" t="n">
         <v>7.8</v>
       </c>
-      <c r="K278" s="1" t="n">
+      <c r="M278" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="L278" t="n">
+      <c r="N278" t="n">
         <v>6.2</v>
       </c>
-      <c r="M278" s="1" t="n">
+      <c r="O278" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N278" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O278" s="1" t="n">
-        <v>45990</v>
-      </c>
       <c r="P278" t="n">
-        <v>7.01</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="279">
@@ -12572,46 +12580,46 @@
         <v>7.2</v>
       </c>
       <c r="C281" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="D281" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E281" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="D281" t="n">
+      <c r="F281" t="n">
         <v>6.8</v>
       </c>
-      <c r="E281" s="1" t="n">
+      <c r="G281" s="1" t="n">
         <v>46058</v>
       </c>
-      <c r="F281" t="n">
+      <c r="H281" t="n">
         <v>6.9</v>
       </c>
-      <c r="G281" s="1" t="n">
+      <c r="I281" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="H281" t="n">
+      <c r="J281" t="n">
         <v>6.8</v>
       </c>
-      <c r="I281" s="1" t="n">
+      <c r="K281" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="J281" t="n">
+      <c r="L281" t="n">
         <v>7.5</v>
       </c>
-      <c r="K281" s="1" t="n">
+      <c r="M281" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="L281" t="n">
+      <c r="N281" t="n">
         <v>6.2</v>
       </c>
-      <c r="M281" s="1" t="n">
+      <c r="O281" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N281" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O281" s="1" t="n">
-        <v>45962</v>
-      </c>
       <c r="P281" t="n">
-        <v>6.86</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="282">
@@ -12903,49 +12911,49 @@
         <v>369</v>
       </c>
       <c r="B288" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C288" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D288" t="n">
         <v>6.9</v>
       </c>
-      <c r="C288" s="1" t="n">
+      <c r="E288" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D288" t="n">
+      <c r="F288" t="n">
         <v>6.8</v>
       </c>
-      <c r="E288" s="1" t="n">
+      <c r="G288" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="F288" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G288" s="1" t="n">
+      <c r="H288" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I288" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="H288" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I288" s="1" t="n">
+      <c r="J288" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K288" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J288" t="n">
+      <c r="L288" t="n">
         <v>6.2</v>
       </c>
-      <c r="K288" s="1" t="n">
+      <c r="M288" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L288" t="n">
+      <c r="N288" t="n">
         <v>7.5</v>
       </c>
-      <c r="M288" s="1" t="n">
+      <c r="O288" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N288" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O288" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P288" t="n">
-        <v>6.79</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="289">
@@ -12953,49 +12961,49 @@
         <v>370</v>
       </c>
       <c r="B289" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="C289" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D289" t="n">
         <v>7.6</v>
       </c>
-      <c r="C289" s="1" t="n">
+      <c r="E289" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D289" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E289" s="1" t="n">
+      <c r="F289" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G289" s="1" t="n">
         <v>46060</v>
-      </c>
-      <c r="F289" t="n">
-        <v>6</v>
-      </c>
-      <c r="G289" s="1" t="n">
-        <v>46054</v>
       </c>
       <c r="H289" t="n">
         <v>6</v>
       </c>
       <c r="I289" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="J289" t="n">
+        <v>6</v>
+      </c>
+      <c r="K289" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="J289" t="n">
+      <c r="L289" t="n">
         <v>7.8</v>
       </c>
-      <c r="K289" s="1" t="n">
+      <c r="M289" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="L289" t="n">
+      <c r="N289" t="n">
         <v>7.1</v>
       </c>
-      <c r="M289" s="1" t="n">
+      <c r="O289" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="N289" t="n">
-        <v>7</v>
-      </c>
-      <c r="O289" s="1" t="n">
-        <v>45899</v>
-      </c>
       <c r="P289" t="n">
-        <v>6.87</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="290">
@@ -13103,49 +13111,49 @@
         <v>373</v>
       </c>
       <c r="B292" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C292" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D292" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E292" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F292" t="n">
         <v>7.2</v>
       </c>
-      <c r="C292" s="1" t="n">
+      <c r="G292" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="D292" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E292" s="1" t="n">
+      <c r="H292" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I292" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="F292" t="n">
+      <c r="J292" t="n">
         <v>6</v>
       </c>
-      <c r="G292" s="1" t="n">
+      <c r="K292" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H292" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I292" s="1" t="n">
+      <c r="L292" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M292" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="J292" t="n">
+      <c r="N292" t="n">
         <v>6.1</v>
       </c>
-      <c r="K292" s="1" t="n">
+      <c r="O292" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="L292" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M292" s="1" t="n">
-        <v>46011</v>
-      </c>
-      <c r="N292" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O292" s="1" t="n">
-        <v>46006</v>
-      </c>
       <c r="P292" t="n">
-        <v>6.57</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="293">
@@ -13253,46 +13261,46 @@
         <v>376</v>
       </c>
       <c r="B295" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C295" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="D295" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E295" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F295" t="n">
         <v>7.8</v>
       </c>
-      <c r="C295" s="1" t="n">
+      <c r="G295" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="D295" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E295" s="1" t="n">
+      <c r="H295" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I295" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="F295" t="n">
+      <c r="J295" t="n">
         <v>6.3</v>
       </c>
-      <c r="G295" s="1" t="n">
+      <c r="K295" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="H295" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I295" s="1" t="n">
+      <c r="L295" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M295" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="J295" t="n">
+      <c r="N295" t="n">
         <v>7.5</v>
       </c>
-      <c r="K295" s="1" t="n">
+      <c r="O295" s="1" t="n">
         <v>45970</v>
-      </c>
-      <c r="L295" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M295" s="1" t="n">
-        <v>45963</v>
-      </c>
-      <c r="N295" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O295" s="1" t="n">
-        <v>45956</v>
       </c>
       <c r="P295" t="n">
         <v>6.89</v>
@@ -13453,45 +13461,49 @@
         <v>380</v>
       </c>
       <c r="B299" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46061</v>
+        <v>46075</v>
       </c>
       <c r="D299" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>45982</v>
+        <v>46069</v>
       </c>
       <c r="F299" t="n">
         <v>6.4</v>
       </c>
       <c r="G299" s="1" t="n">
+        <v>46061</v>
+      </c>
+      <c r="H299" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I299" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="J299" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K299" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="H299" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I299" s="1" t="n">
+      <c r="L299" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M299" s="1" t="n">
         <v>45921</v>
       </c>
-      <c r="J299" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K299" s="1" t="n">
+      <c r="N299" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O299" s="1" t="n">
         <v>45886</v>
       </c>
-      <c r="L299" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M299" s="1" t="n">
-        <v>45872</v>
-      </c>
-      <c r="N299" t="inlineStr"/>
-      <c r="O299" t="inlineStr"/>
       <c r="P299" t="n">
-        <v>6.5</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="300">
@@ -13949,49 +13961,49 @@
         <v>391</v>
       </c>
       <c r="B310" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="C310" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D310" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E310" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="D310" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E310" s="1" t="n">
+      <c r="F310" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G310" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="F310" t="n">
+      <c r="H310" t="n">
         <v>6.2</v>
       </c>
-      <c r="G310" s="1" t="n">
+      <c r="I310" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="H310" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I310" s="1" t="n">
+      <c r="J310" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K310" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="J310" t="n">
+      <c r="L310" t="n">
         <v>5.9</v>
       </c>
-      <c r="K310" s="1" t="n">
+      <c r="M310" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="L310" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M310" s="1" t="n">
+      <c r="N310" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O310" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N310" t="n">
-        <v>6</v>
-      </c>
-      <c r="O310" s="1" t="n">
-        <v>45990</v>
-      </c>
       <c r="P310" t="n">
-        <v>6.36</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="311">
@@ -14735,49 +14747,49 @@
         <v>409</v>
       </c>
       <c r="B328" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C328" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D328" t="n">
         <v>6.9</v>
       </c>
-      <c r="C328" s="1" t="n">
+      <c r="E328" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D328" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E328" s="1" t="n">
+      <c r="F328" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G328" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F328" t="n">
+      <c r="H328" t="n">
         <v>6.2</v>
       </c>
-      <c r="G328" s="1" t="n">
+      <c r="I328" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H328" t="n">
+      <c r="J328" t="n">
         <v>8.6</v>
       </c>
-      <c r="I328" s="1" t="n">
+      <c r="K328" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="J328" t="n">
+      <c r="L328" t="n">
         <v>7</v>
       </c>
-      <c r="K328" s="1" t="n">
+      <c r="M328" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="L328" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M328" s="1" t="n">
+      <c r="N328" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O328" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="N328" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O328" s="1" t="n">
-        <v>45997</v>
-      </c>
       <c r="P328" t="n">
-        <v>6.99</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="329">
@@ -15081,49 +15093,49 @@
         <v>416</v>
       </c>
       <c r="B335" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C335" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D335" t="n">
         <v>6.3</v>
       </c>
-      <c r="C335" s="1" t="n">
+      <c r="E335" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D335" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E335" s="1" t="n">
+      <c r="F335" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G335" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F335" t="n">
+      <c r="H335" t="n">
         <v>8</v>
       </c>
-      <c r="G335" s="1" t="n">
+      <c r="I335" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H335" t="n">
+      <c r="J335" t="n">
         <v>5.7</v>
       </c>
-      <c r="I335" s="1" t="n">
+      <c r="K335" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J335" t="n">
+      <c r="L335" t="n">
         <v>9</v>
       </c>
-      <c r="K335" s="1" t="n">
+      <c r="M335" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L335" t="n">
+      <c r="N335" t="n">
         <v>6.3</v>
       </c>
-      <c r="M335" s="1" t="n">
+      <c r="O335" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N335" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O335" s="1" t="n">
-        <v>45954</v>
-      </c>
       <c r="P335" t="n">
-        <v>6.96</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="336">
@@ -15181,49 +15193,49 @@
         <v>418</v>
       </c>
       <c r="B337" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C337" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D337" t="n">
         <v>8.6</v>
       </c>
-      <c r="C337" s="1" t="n">
+      <c r="E337" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D337" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E337" s="1" t="n">
+      <c r="F337" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G337" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F337" t="n">
+      <c r="H337" t="n">
         <v>8.1</v>
       </c>
-      <c r="G337" s="1" t="n">
+      <c r="I337" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="H337" t="n">
+      <c r="J337" t="n">
         <v>7.3</v>
       </c>
-      <c r="I337" s="1" t="n">
+      <c r="K337" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="J337" t="n">
+      <c r="L337" t="n">
         <v>7.7</v>
       </c>
-      <c r="K337" s="1" t="n">
+      <c r="M337" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="L337" t="n">
+      <c r="N337" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M337" s="1" t="n">
+      <c r="O337" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="N337" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O337" s="1" t="n">
-        <v>46001</v>
-      </c>
       <c r="P337" t="n">
-        <v>7.59</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="338">
@@ -15631,49 +15643,49 @@
         <v>428</v>
       </c>
       <c r="B347" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C347" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D347" t="n">
         <v>8.5</v>
       </c>
-      <c r="C347" s="1" t="n">
+      <c r="E347" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D347" t="n">
+      <c r="F347" t="n">
         <v>7.1</v>
       </c>
-      <c r="E347" s="1" t="n">
+      <c r="G347" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F347" t="n">
+      <c r="H347" t="n">
         <v>7.4</v>
       </c>
-      <c r="G347" s="1" t="n">
+      <c r="I347" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H347" t="n">
+      <c r="J347" t="n">
         <v>6.1</v>
       </c>
-      <c r="I347" s="1" t="n">
+      <c r="K347" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J347" t="n">
+      <c r="L347" t="n">
         <v>8.1</v>
       </c>
-      <c r="K347" s="1" t="n">
+      <c r="M347" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L347" t="n">
+      <c r="N347" t="n">
         <v>6.4</v>
       </c>
-      <c r="M347" s="1" t="n">
+      <c r="O347" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N347" t="n">
-        <v>8</v>
-      </c>
-      <c r="O347" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P347" t="n">
-        <v>7.37</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="348">
@@ -15681,49 +15693,49 @@
         <v>429</v>
       </c>
       <c r="B348" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C348" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D348" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="C348" s="1" t="n">
+      <c r="E348" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D348" t="n">
+      <c r="F348" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E348" s="1" t="n">
+      <c r="G348" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F348" t="n">
+      <c r="H348" t="n">
         <v>7</v>
       </c>
-      <c r="G348" s="1" t="n">
+      <c r="I348" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H348" t="n">
+      <c r="J348" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I348" s="1" t="n">
+      <c r="K348" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="J348" t="n">
+      <c r="L348" t="n">
         <v>7.7</v>
       </c>
-      <c r="K348" s="1" t="n">
+      <c r="M348" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="L348" t="n">
+      <c r="N348" t="n">
         <v>7.1</v>
       </c>
-      <c r="M348" s="1" t="n">
+      <c r="O348" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="N348" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O348" s="1" t="n">
-        <v>45991</v>
-      </c>
       <c r="P348" t="n">
-        <v>7.79</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="349">
@@ -16061,49 +16073,49 @@
         <v>437</v>
       </c>
       <c r="B356" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C356" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D356" t="n">
         <v>9</v>
       </c>
-      <c r="C356" s="1" t="n">
+      <c r="E356" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D356" t="n">
+      <c r="F356" t="n">
         <v>6.9</v>
       </c>
-      <c r="E356" s="1" t="n">
+      <c r="G356" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F356" t="n">
+      <c r="H356" t="n">
         <v>7</v>
       </c>
-      <c r="G356" s="1" t="n">
+      <c r="I356" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H356" t="n">
+      <c r="J356" t="n">
         <v>7.4</v>
       </c>
-      <c r="I356" s="1" t="n">
+      <c r="K356" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="J356" t="n">
+      <c r="L356" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K356" s="1" t="n">
+      <c r="M356" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="L356" t="n">
+      <c r="N356" t="n">
         <v>7.5</v>
       </c>
-      <c r="M356" s="1" t="n">
+      <c r="O356" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="N356" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O356" s="1" t="n">
-        <v>46010</v>
-      </c>
       <c r="P356" t="n">
-        <v>7.54</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="357">
@@ -16153,49 +16165,49 @@
         <v>439</v>
       </c>
       <c r="B358" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C358" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D358" t="n">
         <v>7.4</v>
       </c>
-      <c r="C358" s="1" t="n">
+      <c r="E358" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D358" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E358" s="1" t="n">
+      <c r="F358" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G358" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F358" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G358" s="1" t="n">
+      <c r="H358" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I358" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H358" t="n">
+      <c r="J358" t="n">
         <v>7.1</v>
       </c>
-      <c r="I358" s="1" t="n">
+      <c r="K358" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J358" t="n">
+      <c r="L358" t="n">
         <v>7.4</v>
       </c>
-      <c r="K358" s="1" t="n">
+      <c r="M358" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L358" t="n">
+      <c r="N358" t="n">
         <v>6.8</v>
       </c>
-      <c r="M358" s="1" t="n">
+      <c r="O358" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="N358" t="n">
-        <v>7</v>
-      </c>
-      <c r="O358" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P358" t="n">
-        <v>7</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="359">
@@ -16651,49 +16663,49 @@
         <v>452</v>
       </c>
       <c r="B370" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C370" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D370" t="n">
         <v>7.3</v>
       </c>
-      <c r="C370" s="1" t="n">
+      <c r="E370" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D370" t="n">
+      <c r="F370" t="n">
         <v>6.1</v>
       </c>
-      <c r="E370" s="1" t="n">
+      <c r="G370" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="F370" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G370" s="1" t="n">
+      <c r="H370" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I370" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="H370" t="n">
+      <c r="J370" t="n">
         <v>7.5</v>
       </c>
-      <c r="I370" s="1" t="n">
+      <c r="K370" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="J370" t="n">
+      <c r="L370" t="n">
         <v>7</v>
       </c>
-      <c r="K370" s="1" t="n">
+      <c r="M370" s="1" t="n">
         <v>45949</v>
       </c>
-      <c r="L370" t="n">
+      <c r="N370" t="n">
         <v>6.4</v>
       </c>
-      <c r="M370" s="1" t="n">
+      <c r="O370" s="1" t="n">
         <v>45935</v>
       </c>
-      <c r="N370" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O370" s="1" t="n">
-        <v>45928</v>
-      </c>
       <c r="P370" t="n">
-        <v>6.81</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="371">
@@ -16701,49 +16713,49 @@
         <v>453</v>
       </c>
       <c r="B371" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="C371" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D371" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E371" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D371" t="n">
+      <c r="F371" t="n">
         <v>7</v>
       </c>
-      <c r="E371" s="1" t="n">
+      <c r="G371" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F371" t="n">
+      <c r="H371" t="n">
         <v>6.4</v>
       </c>
-      <c r="G371" s="1" t="n">
+      <c r="I371" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H371" t="n">
+      <c r="J371" t="n">
         <v>6.9</v>
       </c>
-      <c r="I371" s="1" t="n">
+      <c r="K371" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J371" t="n">
+      <c r="L371" t="n">
         <v>7.1</v>
       </c>
-      <c r="K371" s="1" t="n">
+      <c r="M371" s="1" t="n">
         <v>45985</v>
       </c>
-      <c r="L371" t="n">
+      <c r="N371" t="n">
         <v>6.4</v>
       </c>
-      <c r="M371" s="1" t="n">
+      <c r="O371" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N371" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O371" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P371" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="372">
@@ -16904,46 +16916,46 @@
         <v>6.6</v>
       </c>
       <c r="C375" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D375" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E375" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D375" t="n">
+      <c r="F375" t="n">
         <v>7.5</v>
       </c>
-      <c r="E375" s="1" t="n">
+      <c r="G375" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="F375" t="n">
+      <c r="H375" t="n">
         <v>7.3</v>
       </c>
-      <c r="G375" s="1" t="n">
+      <c r="I375" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="H375" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I375" s="1" t="n">
+      <c r="J375" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K375" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="J375" t="n">
+      <c r="L375" t="n">
         <v>7.1</v>
       </c>
-      <c r="K375" s="1" t="n">
+      <c r="M375" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="L375" t="n">
+      <c r="N375" t="n">
         <v>7.5</v>
       </c>
-      <c r="M375" s="1" t="n">
+      <c r="O375" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="N375" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O375" s="1" t="n">
-        <v>45956</v>
-      </c>
       <c r="P375" t="n">
-        <v>6.99</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="376">
@@ -16951,49 +16963,49 @@
         <v>458</v>
       </c>
       <c r="B376" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C376" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D376" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E376" s="1" t="n">
+        <v>46068</v>
+      </c>
+      <c r="F376" t="n">
         <v>6.4</v>
       </c>
-      <c r="C376" s="1" t="n">
+      <c r="G376" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="D376" t="n">
+      <c r="H376" t="n">
         <v>6.2</v>
       </c>
-      <c r="E376" s="1" t="n">
+      <c r="I376" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="F376" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G376" s="1" t="n">
+      <c r="J376" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K376" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="H376" t="n">
+      <c r="L376" t="n">
         <v>7</v>
       </c>
-      <c r="I376" s="1" t="n">
+      <c r="M376" s="1" t="n">
         <v>45959</v>
       </c>
-      <c r="J376" t="n">
+      <c r="N376" t="n">
         <v>7.1</v>
       </c>
-      <c r="K376" s="1" t="n">
+      <c r="O376" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="L376" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M376" s="1" t="n">
-        <v>45949</v>
-      </c>
-      <c r="N376" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O376" s="1" t="n">
-        <v>45934</v>
-      </c>
       <c r="P376" t="n">
-        <v>6.64</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="377">
@@ -17280,34 +17292,38 @@
         <v>6.5</v>
       </c>
       <c r="C383" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D383" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E383" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="D383" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E383" s="1" t="n">
+      <c r="F383" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G383" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="F383" t="n">
+      <c r="H383" t="n">
         <v>6.8</v>
       </c>
-      <c r="G383" s="1" t="n">
+      <c r="I383" s="1" t="n">
         <v>45879</v>
       </c>
-      <c r="H383" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I383" s="1" t="n">
+      <c r="J383" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K383" s="1" t="n">
         <v>45871</v>
       </c>
-      <c r="J383" t="inlineStr"/>
-      <c r="K383" t="inlineStr"/>
       <c r="L383" t="inlineStr"/>
       <c r="M383" t="inlineStr"/>
       <c r="N383" t="inlineStr"/>
       <c r="O383" t="inlineStr"/>
       <c r="P383" t="n">
-        <v>6.65</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="384">
@@ -17318,46 +17334,46 @@
         <v>6.5</v>
       </c>
       <c r="C384" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D384" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E384" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F384" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G384" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="D384" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E384" s="1" t="n">
+      <c r="H384" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I384" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="F384" t="n">
+      <c r="J384" t="n">
         <v>6.8</v>
       </c>
-      <c r="G384" s="1" t="n">
+      <c r="K384" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H384" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I384" s="1" t="n">
+      <c r="L384" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M384" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="J384" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K384" s="1" t="n">
+      <c r="N384" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O384" s="1" t="n">
         <v>45893</v>
       </c>
-      <c r="L384" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M384" s="1" t="n">
-        <v>45878</v>
-      </c>
-      <c r="N384" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O384" s="1" t="n">
-        <v>45872</v>
-      </c>
       <c r="P384" t="n">
-        <v>6.59</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="385">
@@ -17365,49 +17381,49 @@
         <v>467</v>
       </c>
       <c r="B385" t="n">
+        <v>7</v>
+      </c>
+      <c r="C385" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D385" t="n">
         <v>8.5</v>
       </c>
-      <c r="C385" s="1" t="n">
+      <c r="E385" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D385" t="n">
+      <c r="F385" t="n">
         <v>7.7</v>
       </c>
-      <c r="E385" s="1" t="n">
+      <c r="G385" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F385" t="n">
+      <c r="H385" t="n">
         <v>7.3</v>
       </c>
-      <c r="G385" s="1" t="n">
+      <c r="I385" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H385" t="n">
+      <c r="J385" t="n">
         <v>7.1</v>
       </c>
-      <c r="I385" s="1" t="n">
+      <c r="K385" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J385" t="n">
+      <c r="L385" t="n">
         <v>8</v>
       </c>
-      <c r="K385" s="1" t="n">
+      <c r="M385" s="1" t="n">
         <v>45993</v>
       </c>
-      <c r="L385" t="n">
+      <c r="N385" t="n">
         <v>7.5</v>
       </c>
-      <c r="M385" s="1" t="n">
+      <c r="O385" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="N385" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O385" s="1" t="n">
-        <v>45984</v>
-      </c>
       <c r="P385" t="n">
-        <v>7.71</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="386">
@@ -17415,49 +17431,49 @@
         <v>468</v>
       </c>
       <c r="B386" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="C386" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D386" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E386" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D386" t="n">
+      <c r="F386" t="n">
         <v>6.2</v>
       </c>
-      <c r="E386" s="1" t="n">
+      <c r="G386" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F386" t="n">
+      <c r="H386" t="n">
         <v>6.1</v>
       </c>
-      <c r="G386" s="1" t="n">
+      <c r="I386" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H386" t="n">
+      <c r="J386" t="n">
         <v>6.3</v>
       </c>
-      <c r="I386" s="1" t="n">
+      <c r="K386" s="1" t="n">
         <v>45994</v>
       </c>
-      <c r="J386" t="n">
+      <c r="L386" t="n">
         <v>6.2</v>
       </c>
-      <c r="K386" s="1" t="n">
+      <c r="M386" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="L386" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M386" s="1" t="n">
+      <c r="N386" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O386" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N386" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O386" s="1" t="n">
-        <v>45961</v>
-      </c>
       <c r="P386" t="n">
-        <v>6.43</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="387">
@@ -17465,46 +17481,46 @@
         <v>469</v>
       </c>
       <c r="B387" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C387" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="D387" t="n">
         <v>6.9</v>
       </c>
-      <c r="C387" s="1" t="n">
+      <c r="E387" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="D387" t="n">
+      <c r="F387" t="n">
         <v>6</v>
       </c>
-      <c r="E387" s="1" t="n">
+      <c r="G387" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="F387" t="n">
+      <c r="H387" t="n">
         <v>6.4</v>
       </c>
-      <c r="G387" s="1" t="n">
+      <c r="I387" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="H387" t="n">
+      <c r="J387" t="n">
         <v>7.1</v>
       </c>
-      <c r="I387" s="1" t="n">
+      <c r="K387" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="J387" t="n">
+      <c r="L387" t="n">
         <v>7.2</v>
       </c>
-      <c r="K387" s="1" t="n">
+      <c r="M387" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="L387" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M387" s="1" t="n">
+      <c r="N387" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O387" s="1" t="n">
         <v>45961</v>
-      </c>
-      <c r="N387" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O387" s="1" t="n">
-        <v>45955</v>
       </c>
       <c r="P387" t="n">
         <v>6.71</v>
@@ -17518,46 +17534,46 @@
         <v>6.3</v>
       </c>
       <c r="C388" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D388" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E388" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D388" t="n">
+      <c r="F388" t="n">
         <v>6.2</v>
       </c>
-      <c r="E388" s="1" t="n">
+      <c r="G388" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="F388" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G388" s="1" t="n">
+      <c r="H388" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I388" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="H388" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I388" s="1" t="n">
+      <c r="J388" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K388" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="J388" t="n">
+      <c r="L388" t="n">
         <v>6.4</v>
       </c>
-      <c r="K388" s="1" t="n">
+      <c r="M388" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="L388" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M388" s="1" t="n">
+      <c r="N388" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O388" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="N388" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O388" s="1" t="n">
-        <v>45933</v>
-      </c>
       <c r="P388" t="n">
-        <v>6.46</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="389">
@@ -17565,49 +17581,49 @@
         <v>471</v>
       </c>
       <c r="B389" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46067</v>
+        <v>46074</v>
       </c>
       <c r="D389" t="n">
         <v>6.8</v>
       </c>
       <c r="E389" s="1" t="n">
+        <v>46067</v>
+      </c>
+      <c r="F389" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G389" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F389" t="n">
+      <c r="H389" t="n">
         <v>7</v>
       </c>
-      <c r="G389" s="1" t="n">
+      <c r="I389" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="H389" t="n">
+      <c r="J389" t="n">
         <v>6</v>
       </c>
-      <c r="I389" s="1" t="n">
+      <c r="K389" s="1" t="n">
         <v>45995</v>
       </c>
-      <c r="J389" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K389" s="1" t="n">
+      <c r="L389" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M389" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L389" t="n">
+      <c r="N389" t="n">
         <v>6.1</v>
       </c>
-      <c r="M389" s="1" t="n">
+      <c r="O389" s="1" t="n">
         <v>45985</v>
       </c>
-      <c r="N389" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O389" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P389" t="n">
-        <v>6.59</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="390">
@@ -17813,49 +17829,49 @@
         <v>479</v>
       </c>
       <c r="B397" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C397" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D397" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E397" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="D397" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E397" s="1" t="n">
+      <c r="F397" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G397" s="1" t="n">
         <v>46000</v>
       </c>
-      <c r="F397" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G397" s="1" t="n">
+      <c r="H397" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I397" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="H397" t="n">
+      <c r="J397" t="n">
         <v>6.2</v>
       </c>
-      <c r="I397" s="1" t="n">
+      <c r="K397" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="J397" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K397" s="1" t="n">
+      <c r="L397" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M397" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L397" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M397" s="1" t="n">
+      <c r="N397" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O397" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="N397" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O397" s="1" t="n">
-        <v>45950</v>
-      </c>
       <c r="P397" t="n">
-        <v>6.49</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="398">
@@ -17863,49 +17879,49 @@
         <v>480</v>
       </c>
       <c r="B398" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C398" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D398" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E398" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="D398" t="n">
+      <c r="F398" t="n">
         <v>6.8</v>
       </c>
-      <c r="E398" s="1" t="n">
+      <c r="G398" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="F398" t="n">
+      <c r="H398" t="n">
         <v>6.4</v>
       </c>
-      <c r="G398" s="1" t="n">
+      <c r="I398" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="H398" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I398" s="1" t="n">
+      <c r="J398" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K398" s="1" t="n">
         <v>45964</v>
-      </c>
-      <c r="J398" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K398" s="1" t="n">
-        <v>45957</v>
       </c>
       <c r="L398" t="n">
         <v>6.4</v>
       </c>
       <c r="M398" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="N398" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O398" s="1" t="n">
         <v>45934</v>
       </c>
-      <c r="N398" t="n">
-        <v>7</v>
-      </c>
-      <c r="O398" s="1" t="n">
-        <v>45925</v>
-      </c>
       <c r="P398" t="n">
-        <v>6.6</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="399">
@@ -18053,49 +18069,49 @@
         <v>485</v>
       </c>
       <c r="B403" t="n">
-        <v>7.9</v>
+        <v>6.7</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>46068</v>
+        <v>46074</v>
       </c>
       <c r="D403" t="n">
         <v>7.9</v>
       </c>
       <c r="E403" s="1" t="n">
+        <v>46068</v>
+      </c>
+      <c r="F403" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G403" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="F403" t="n">
+      <c r="H403" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G403" s="1" t="n">
+      <c r="I403" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="H403" t="n">
+      <c r="J403" t="n">
         <v>7.9</v>
       </c>
-      <c r="I403" s="1" t="n">
+      <c r="K403" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J403" t="n">
+      <c r="L403" t="n">
         <v>6.8</v>
       </c>
-      <c r="K403" s="1" t="n">
+      <c r="M403" s="1" t="n">
         <v>45985</v>
       </c>
-      <c r="L403" t="n">
+      <c r="N403" t="n">
         <v>7</v>
       </c>
-      <c r="M403" s="1" t="n">
+      <c r="O403" s="1" t="n">
         <v>45957</v>
       </c>
-      <c r="N403" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O403" s="1" t="n">
-        <v>45949</v>
-      </c>
       <c r="P403" t="n">
-        <v>7.47</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="404">
@@ -18103,49 +18119,49 @@
         <v>486</v>
       </c>
       <c r="B404" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="C404" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D404" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E404" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="D404" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E404" s="1" t="n">
+      <c r="F404" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G404" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="F404" t="n">
+      <c r="H404" t="n">
         <v>6.2</v>
       </c>
-      <c r="G404" s="1" t="n">
+      <c r="I404" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H404" t="n">
+      <c r="J404" t="n">
         <v>6.1</v>
       </c>
-      <c r="I404" s="1" t="n">
+      <c r="K404" s="1" t="n">
         <v>45949</v>
       </c>
-      <c r="J404" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K404" s="1" t="n">
+      <c r="L404" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M404" s="1" t="n">
         <v>45928</v>
       </c>
-      <c r="L404" t="n">
+      <c r="N404" t="n">
         <v>6.4</v>
       </c>
-      <c r="M404" s="1" t="n">
+      <c r="O404" s="1" t="n">
         <v>45921</v>
       </c>
-      <c r="N404" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O404" s="1" t="n">
-        <v>45915</v>
-      </c>
       <c r="P404" t="n">
-        <v>6.43</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="405">
@@ -18153,49 +18169,49 @@
         <v>487</v>
       </c>
       <c r="B405" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C405" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D405" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E405" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D405" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E405" s="1" t="n">
+      <c r="F405" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G405" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="F405" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G405" s="1" t="n">
+      <c r="H405" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I405" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H405" t="n">
+      <c r="J405" t="n">
         <v>6.3</v>
       </c>
-      <c r="I405" s="1" t="n">
+      <c r="K405" s="1" t="n">
         <v>45935</v>
       </c>
-      <c r="J405" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K405" s="1" t="n">
+      <c r="L405" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M405" s="1" t="n">
         <v>45928</v>
       </c>
-      <c r="L405" t="n">
+      <c r="N405" t="n">
         <v>6.8</v>
       </c>
-      <c r="M405" s="1" t="n">
+      <c r="O405" s="1" t="n">
         <v>45921</v>
       </c>
-      <c r="N405" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O405" s="1" t="n">
-        <v>45915</v>
-      </c>
       <c r="P405" t="n">
-        <v>6.54</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="406">
@@ -18249,46 +18265,46 @@
         <v>489</v>
       </c>
       <c r="B407" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C407" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D407" t="n">
         <v>6.2</v>
       </c>
-      <c r="C407" s="1" t="n">
+      <c r="E407" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="D407" t="n">
+      <c r="F407" t="n">
         <v>6.4</v>
       </c>
-      <c r="E407" s="1" t="n">
+      <c r="G407" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="F407" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G407" s="1" t="n">
+      <c r="H407" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I407" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="H407" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I407" s="1" t="n">
+      <c r="J407" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K407" s="1" t="n">
         <v>45985</v>
       </c>
-      <c r="J407" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K407" s="1" t="n">
+      <c r="L407" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M407" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="L407" t="n">
+      <c r="N407" t="n">
         <v>6.2</v>
       </c>
-      <c r="M407" s="1" t="n">
+      <c r="O407" s="1" t="n">
         <v>45963</v>
-      </c>
-      <c r="N407" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O407" s="1" t="n">
-        <v>45929</v>
       </c>
       <c r="P407" t="n">
         <v>6.49</v>
@@ -18299,49 +18315,49 @@
         <v>490</v>
       </c>
       <c r="B408" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C408" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D408" t="n">
         <v>6.3</v>
       </c>
-      <c r="C408" s="1" t="n">
+      <c r="E408" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="D408" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E408" s="1" t="n">
+      <c r="F408" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G408" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="F408" t="n">
+      <c r="H408" t="n">
         <v>6</v>
       </c>
-      <c r="G408" s="1" t="n">
+      <c r="I408" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="H408" t="n">
+      <c r="J408" t="n">
         <v>7.5</v>
       </c>
-      <c r="I408" s="1" t="n">
+      <c r="K408" s="1" t="n">
         <v>45949</v>
       </c>
-      <c r="J408" t="n">
+      <c r="L408" t="n">
         <v>7.2</v>
       </c>
-      <c r="K408" s="1" t="n">
+      <c r="M408" s="1" t="n">
         <v>45935</v>
       </c>
-      <c r="L408" t="n">
+      <c r="N408" t="n">
         <v>7.1</v>
       </c>
-      <c r="M408" s="1" t="n">
+      <c r="O408" s="1" t="n">
         <v>45928</v>
       </c>
-      <c r="N408" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O408" s="1" t="n">
-        <v>45922</v>
-      </c>
       <c r="P408" t="n">
-        <v>6.76</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="409">
@@ -19205,49 +19221,49 @@
         <v>510</v>
       </c>
       <c r="B428" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>46066</v>
+        <v>46074</v>
       </c>
       <c r="D428" t="n">
         <v>6.4</v>
       </c>
       <c r="E428" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="F428" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G428" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F428" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G428" s="1" t="n">
+      <c r="H428" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I428" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="H428" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I428" s="1" t="n">
+      <c r="J428" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K428" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="J428" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K428" s="1" t="n">
+      <c r="L428" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M428" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="L428" t="n">
+      <c r="N428" t="n">
         <v>6.1</v>
       </c>
-      <c r="M428" s="1" t="n">
+      <c r="O428" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N428" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O428" s="1" t="n">
-        <v>45984</v>
-      </c>
       <c r="P428" t="n">
-        <v>6.51</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="429">
@@ -19312,46 +19328,46 @@
         <v>6.3</v>
       </c>
       <c r="C431" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D431" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E431" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D431" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E431" s="1" t="n">
+      <c r="F431" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G431" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="F431" t="n">
+      <c r="H431" t="n">
         <v>6.9</v>
       </c>
-      <c r="G431" s="1" t="n">
+      <c r="I431" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="H431" t="n">
+      <c r="J431" t="n">
         <v>6.8</v>
       </c>
-      <c r="I431" s="1" t="n">
+      <c r="K431" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J431" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K431" s="1" t="n">
+      <c r="L431" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M431" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="L431" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M431" s="1" t="n">
+      <c r="N431" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O431" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="N431" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O431" s="1" t="n">
-        <v>45927</v>
-      </c>
       <c r="P431" t="n">
-        <v>6.63</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="432">
@@ -19359,46 +19375,46 @@
         <v>514</v>
       </c>
       <c r="B432" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C432" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D432" t="n">
         <v>6.3</v>
       </c>
-      <c r="C432" s="1" t="n">
+      <c r="E432" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D432" t="n">
+      <c r="F432" t="n">
         <v>6.8</v>
       </c>
-      <c r="E432" s="1" t="n">
+      <c r="G432" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F432" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G432" s="1" t="n">
+      <c r="H432" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I432" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H432" t="n">
+      <c r="J432" t="n">
         <v>6.4</v>
       </c>
-      <c r="I432" s="1" t="n">
+      <c r="K432" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="J432" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K432" s="1" t="n">
+      <c r="L432" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M432" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="L432" t="n">
+      <c r="N432" t="n">
         <v>7.3</v>
       </c>
-      <c r="M432" s="1" t="n">
+      <c r="O432" s="1" t="n">
         <v>45996</v>
-      </c>
-      <c r="N432" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O432" s="1" t="n">
-        <v>45992</v>
       </c>
       <c r="P432" t="n">
         <v>6.66</v>
@@ -20636,46 +20652,46 @@
         <v>7.1</v>
       </c>
       <c r="C461" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D461" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E461" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D461" t="n">
+      <c r="F461" t="n">
         <v>6.9</v>
       </c>
-      <c r="E461" s="1" t="n">
+      <c r="G461" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F461" t="n">
+      <c r="H461" t="n">
         <v>7.2</v>
       </c>
-      <c r="G461" s="1" t="n">
+      <c r="I461" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H461" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I461" s="1" t="n">
+      <c r="J461" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K461" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="J461" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K461" s="1" t="n">
+      <c r="L461" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M461" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L461" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M461" s="1" t="n">
+      <c r="N461" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O461" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="N461" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O461" s="1" t="n">
-        <v>45950</v>
-      </c>
       <c r="P461" t="n">
-        <v>6.81</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="462">
@@ -20683,49 +20699,49 @@
         <v>544</v>
       </c>
       <c r="B462" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C462" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D462" t="n">
         <v>6.8</v>
       </c>
-      <c r="C462" s="1" t="n">
+      <c r="E462" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D462" t="n">
+      <c r="F462" t="n">
         <v>8.4</v>
       </c>
-      <c r="E462" s="1" t="n">
+      <c r="G462" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F462" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G462" s="1" t="n">
+      <c r="H462" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I462" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H462" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I462" s="1" t="n">
+      <c r="J462" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K462" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J462" t="n">
+      <c r="L462" t="n">
         <v>7.3</v>
       </c>
-      <c r="K462" s="1" t="n">
+      <c r="M462" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L462" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M462" s="1" t="n">
+      <c r="N462" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O462" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N462" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O462" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P462" t="n">
-        <v>7.07</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="463">
@@ -20733,49 +20749,49 @@
         <v>545</v>
       </c>
       <c r="B463" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C463" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D463" t="n">
         <v>5.9</v>
       </c>
-      <c r="C463" s="1" t="n">
+      <c r="E463" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D463" t="n">
+      <c r="F463" t="n">
         <v>7.1</v>
       </c>
-      <c r="E463" s="1" t="n">
+      <c r="G463" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F463" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G463" s="1" t="n">
+      <c r="H463" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I463" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="H463" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I463" s="1" t="n">
+      <c r="J463" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K463" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="J463" t="n">
+      <c r="L463" t="n">
         <v>7.3</v>
       </c>
-      <c r="K463" s="1" t="n">
+      <c r="M463" s="1" t="n">
         <v>45934</v>
       </c>
-      <c r="L463" t="n">
+      <c r="N463" t="n">
         <v>5.9</v>
       </c>
-      <c r="M463" s="1" t="n">
+      <c r="O463" s="1" t="n">
         <v>45928</v>
       </c>
-      <c r="N463" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O463" s="1" t="n">
-        <v>45920</v>
-      </c>
       <c r="P463" t="n">
-        <v>6.73</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="464">
@@ -21031,49 +21047,49 @@
         <v>552</v>
       </c>
       <c r="B470" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C470" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D470" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E470" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F470" t="n">
         <v>6</v>
       </c>
-      <c r="C470" s="1" t="n">
+      <c r="G470" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="D470" t="n">
+      <c r="H470" t="n">
         <v>6.4</v>
       </c>
-      <c r="E470" s="1" t="n">
+      <c r="I470" s="1" t="n">
         <v>46057</v>
       </c>
-      <c r="F470" t="n">
+      <c r="J470" t="n">
         <v>7.2</v>
       </c>
-      <c r="G470" s="1" t="n">
+      <c r="K470" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="H470" t="n">
+      <c r="L470" t="n">
         <v>6.8</v>
       </c>
-      <c r="I470" s="1" t="n">
+      <c r="M470" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="J470" t="n">
+      <c r="N470" t="n">
         <v>7.1</v>
       </c>
-      <c r="K470" s="1" t="n">
+      <c r="O470" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="L470" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M470" s="1" t="n">
-        <v>46011</v>
-      </c>
-      <c r="N470" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O470" s="1" t="n">
-        <v>46005</v>
-      </c>
       <c r="P470" t="n">
-        <v>6.96</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="471">
@@ -21119,49 +21135,49 @@
         <v>554</v>
       </c>
       <c r="B472" t="n">
+        <v>8</v>
+      </c>
+      <c r="C472" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D472" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E472" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F472" t="n">
         <v>7.7</v>
       </c>
-      <c r="C472" s="1" t="n">
+      <c r="G472" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="D472" t="n">
+      <c r="H472" t="n">
         <v>6.1</v>
       </c>
-      <c r="E472" s="1" t="n">
+      <c r="I472" s="1" t="n">
         <v>46057</v>
       </c>
-      <c r="F472" t="n">
+      <c r="J472" t="n">
         <v>6.9</v>
       </c>
-      <c r="G472" s="1" t="n">
+      <c r="K472" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="H472" t="n">
+      <c r="L472" t="n">
         <v>7.7</v>
       </c>
-      <c r="I472" s="1" t="n">
+      <c r="M472" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="J472" t="n">
+      <c r="N472" t="n">
         <v>6.1</v>
       </c>
-      <c r="K472" s="1" t="n">
+      <c r="O472" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="L472" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="M472" s="1" t="n">
-        <v>46010</v>
-      </c>
-      <c r="N472" t="n">
+      <c r="P472" t="n">
         <v>7.2</v>
-      </c>
-      <c r="O472" s="1" t="n">
-        <v>46003</v>
-      </c>
-      <c r="P472" t="n">
-        <v>6.84</v>
       </c>
     </row>
     <row r="473">
@@ -21369,49 +21385,49 @@
         <v>559</v>
       </c>
       <c r="B477" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C477" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="D477" t="n">
         <v>7.4</v>
       </c>
-      <c r="C477" s="1" t="n">
+      <c r="E477" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="D477" t="n">
+      <c r="F477" t="n">
         <v>9.1</v>
       </c>
-      <c r="E477" s="1" t="n">
+      <c r="G477" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="F477" t="n">
+      <c r="H477" t="n">
         <v>7</v>
       </c>
-      <c r="G477" s="1" t="n">
+      <c r="I477" s="1" t="n">
         <v>45990</v>
-      </c>
-      <c r="H477" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I477" s="1" t="n">
-        <v>45983</v>
       </c>
       <c r="J477" t="n">
         <v>7.2</v>
       </c>
       <c r="K477" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="L477" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M477" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L477" t="n">
+      <c r="N477" t="n">
         <v>6.4</v>
       </c>
-      <c r="M477" s="1" t="n">
+      <c r="O477" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N477" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O477" s="1" t="n">
-        <v>45948</v>
-      </c>
       <c r="P477" t="n">
-        <v>7.23</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="478">
@@ -21549,49 +21565,49 @@
         <v>563</v>
       </c>
       <c r="B481" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C481" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D481" t="n">
         <v>7</v>
       </c>
-      <c r="C481" s="1" t="n">
+      <c r="E481" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D481" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E481" s="1" t="n">
+      <c r="F481" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G481" s="1" t="n">
         <v>46060</v>
-      </c>
-      <c r="F481" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="G481" s="1" t="n">
-        <v>46004</v>
       </c>
       <c r="H481" t="n">
         <v>6.8</v>
       </c>
       <c r="I481" s="1" t="n">
+        <v>46004</v>
+      </c>
+      <c r="J481" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K481" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J481" t="n">
+      <c r="L481" t="n">
         <v>6.9</v>
       </c>
-      <c r="K481" s="1" t="n">
+      <c r="M481" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L481" t="n">
+      <c r="N481" t="n">
         <v>6.3</v>
       </c>
-      <c r="M481" s="1" t="n">
+      <c r="O481" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="N481" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O481" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P481" t="n">
-        <v>6.81</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="482">
@@ -21649,49 +21665,49 @@
         <v>565</v>
       </c>
       <c r="B483" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="C483" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D483" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E483" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="D483" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E483" s="1" t="n">
+      <c r="F483" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G483" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="F483" t="n">
+      <c r="H483" t="n">
         <v>6</v>
       </c>
-      <c r="G483" s="1" t="n">
+      <c r="I483" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="H483" t="n">
+      <c r="J483" t="n">
         <v>6.4</v>
       </c>
-      <c r="I483" s="1" t="n">
+      <c r="K483" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="J483" t="n">
+      <c r="L483" t="n">
         <v>6.8</v>
       </c>
-      <c r="K483" s="1" t="n">
+      <c r="M483" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L483" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M483" s="1" t="n">
+      <c r="N483" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O483" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N483" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O483" s="1" t="n">
-        <v>45962</v>
-      </c>
       <c r="P483" t="n">
-        <v>6.56</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="484">
@@ -22725,49 +22741,49 @@
         <v>589</v>
       </c>
       <c r="B506" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C506" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D506" t="n">
         <v>6.9</v>
       </c>
-      <c r="C506" s="1" t="n">
+      <c r="E506" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D506" t="n">
+      <c r="F506" t="n">
         <v>7.2</v>
       </c>
-      <c r="E506" s="1" t="n">
+      <c r="G506" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F506" t="n">
+      <c r="H506" t="n">
         <v>6.8</v>
       </c>
-      <c r="G506" s="1" t="n">
+      <c r="I506" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="H506" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I506" s="1" t="n">
+      <c r="J506" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K506" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="J506" t="n">
+      <c r="L506" t="n">
         <v>7.7</v>
       </c>
-      <c r="K506" s="1" t="n">
+      <c r="M506" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="L506" t="n">
+      <c r="N506" t="n">
         <v>6.4</v>
       </c>
-      <c r="M506" s="1" t="n">
+      <c r="O506" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="N506" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O506" s="1" t="n">
-        <v>45998</v>
-      </c>
       <c r="P506" t="n">
-        <v>6.91</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="507">
@@ -22775,49 +22791,49 @@
         <v>590</v>
       </c>
       <c r="B507" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C507" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D507" t="n">
         <v>6.4</v>
       </c>
-      <c r="C507" s="1" t="n">
+      <c r="E507" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="D507" t="n">
+      <c r="F507" t="n">
         <v>7.2</v>
       </c>
-      <c r="E507" s="1" t="n">
+      <c r="G507" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="F507" t="n">
+      <c r="H507" t="n">
         <v>7.1</v>
       </c>
-      <c r="G507" s="1" t="n">
+      <c r="I507" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="H507" t="n">
+      <c r="J507" t="n">
         <v>6.2</v>
       </c>
-      <c r="I507" s="1" t="n">
+      <c r="K507" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="J507" t="n">
+      <c r="L507" t="n">
         <v>7.6</v>
       </c>
-      <c r="K507" s="1" t="n">
+      <c r="M507" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="L507" t="n">
+      <c r="N507" t="n">
         <v>7.3</v>
       </c>
-      <c r="M507" s="1" t="n">
+      <c r="O507" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N507" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O507" s="1" t="n">
-        <v>45949</v>
-      </c>
       <c r="P507" t="n">
-        <v>6.94</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="508">
@@ -22928,46 +22944,46 @@
         <v>6.9</v>
       </c>
       <c r="C510" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D510" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E510" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D510" t="n">
+      <c r="F510" t="n">
         <v>6.4</v>
       </c>
-      <c r="E510" s="1" t="n">
+      <c r="G510" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F510" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G510" s="1" t="n">
+      <c r="H510" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I510" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H510" t="n">
+      <c r="J510" t="n">
         <v>7.8</v>
       </c>
-      <c r="I510" s="1" t="n">
+      <c r="K510" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J510" t="n">
+      <c r="L510" t="n">
         <v>8.4</v>
       </c>
-      <c r="K510" s="1" t="n">
+      <c r="M510" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L510" t="n">
+      <c r="N510" t="n">
         <v>6</v>
       </c>
-      <c r="M510" s="1" t="n">
+      <c r="O510" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N510" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O510" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P510" t="n">
-        <v>7.09</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="511">
@@ -23125,49 +23141,49 @@
         <v>597</v>
       </c>
       <c r="B514" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C514" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D514" t="n">
         <v>6.4</v>
       </c>
-      <c r="C514" s="1" t="n">
+      <c r="E514" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D514" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E514" s="1" t="n">
+      <c r="F514" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G514" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F514" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G514" s="1" t="n">
+      <c r="H514" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I514" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="H514" t="n">
+      <c r="J514" t="n">
         <v>7.5</v>
       </c>
-      <c r="I514" s="1" t="n">
+      <c r="K514" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="J514" t="n">
+      <c r="L514" t="n">
         <v>7</v>
       </c>
-      <c r="K514" s="1" t="n">
+      <c r="M514" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="L514" t="n">
+      <c r="N514" t="n">
         <v>6.2</v>
       </c>
-      <c r="M514" s="1" t="n">
+      <c r="O514" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N514" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O514" s="1" t="n">
-        <v>45964</v>
-      </c>
       <c r="P514" t="n">
-        <v>6.87</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="515">
@@ -23175,49 +23191,49 @@
         <v>598</v>
       </c>
       <c r="B515" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C515" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="D515" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E515" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F515" t="n">
         <v>6.9</v>
       </c>
-      <c r="C515" s="1" t="n">
+      <c r="G515" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="D515" t="n">
+      <c r="H515" t="n">
         <v>7.2</v>
       </c>
-      <c r="E515" s="1" t="n">
+      <c r="I515" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="F515" t="n">
+      <c r="J515" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G515" s="1" t="n">
+      <c r="K515" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H515" t="n">
+      <c r="L515" t="n">
         <v>7.7</v>
       </c>
-      <c r="I515" s="1" t="n">
+      <c r="M515" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="J515" t="n">
+      <c r="N515" t="n">
         <v>6.4</v>
       </c>
-      <c r="K515" s="1" t="n">
+      <c r="O515" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L515" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M515" s="1" t="n">
-        <v>45984</v>
-      </c>
-      <c r="N515" t="n">
-        <v>7</v>
-      </c>
-      <c r="O515" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P515" t="n">
-        <v>7.27</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="516">
@@ -23325,49 +23341,49 @@
         <v>601</v>
       </c>
       <c r="B518" t="n">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>46068</v>
+        <v>46074</v>
       </c>
       <c r="D518" t="n">
         <v>7.2</v>
       </c>
       <c r="E518" s="1" t="n">
+        <v>46068</v>
+      </c>
+      <c r="F518" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G518" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F518" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G518" s="1" t="n">
+      <c r="H518" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I518" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H518" t="n">
+      <c r="J518" t="n">
         <v>6</v>
       </c>
-      <c r="I518" s="1" t="n">
+      <c r="K518" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="J518" t="n">
+      <c r="L518" t="n">
         <v>6.1</v>
       </c>
-      <c r="K518" s="1" t="n">
+      <c r="M518" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="L518" t="n">
+      <c r="N518" t="n">
         <v>6.9</v>
       </c>
-      <c r="M518" s="1" t="n">
+      <c r="O518" s="1" t="n">
         <v>45995</v>
       </c>
-      <c r="N518" t="n">
-        <v>7</v>
-      </c>
-      <c r="O518" s="1" t="n">
-        <v>45991</v>
-      </c>
       <c r="P518" t="n">
-        <v>6.73</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="519">
@@ -23609,49 +23625,49 @@
         <v>607</v>
       </c>
       <c r="B524" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C524" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D524" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E524" s="1" t="n">
+        <v>46067</v>
+      </c>
+      <c r="F524" t="n">
         <v>7</v>
       </c>
-      <c r="C524" s="1" t="n">
+      <c r="G524" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="D524" t="n">
+      <c r="H524" t="n">
         <v>7.2</v>
       </c>
-      <c r="E524" s="1" t="n">
+      <c r="I524" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="F524" t="n">
+      <c r="J524" t="n">
         <v>7.3</v>
       </c>
-      <c r="G524" s="1" t="n">
+      <c r="K524" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="H524" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I524" s="1" t="n">
+      <c r="L524" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M524" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="J524" t="n">
+      <c r="N524" t="n">
         <v>7.4</v>
       </c>
-      <c r="K524" s="1" t="n">
+      <c r="O524" s="1" t="n">
         <v>46036</v>
       </c>
-      <c r="L524" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M524" s="1" t="n">
-        <v>46015</v>
-      </c>
-      <c r="N524" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O524" s="1" t="n">
-        <v>46011</v>
-      </c>
       <c r="P524" t="n">
-        <v>6.96</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="525">
@@ -23709,49 +23725,49 @@
         <v>609</v>
       </c>
       <c r="B526" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C526" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D526" t="n">
         <v>6.4</v>
       </c>
-      <c r="C526" s="1" t="n">
+      <c r="E526" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D526" t="n">
+      <c r="F526" t="n">
         <v>6.8</v>
       </c>
-      <c r="E526" s="1" t="n">
+      <c r="G526" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="F526" t="n">
+      <c r="H526" t="n">
         <v>5.9</v>
       </c>
-      <c r="G526" s="1" t="n">
+      <c r="I526" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="H526" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I526" s="1" t="n">
+      <c r="J526" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K526" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="J526" t="n">
+      <c r="L526" t="n">
         <v>7.3</v>
       </c>
-      <c r="K526" s="1" t="n">
+      <c r="M526" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="L526" t="n">
+      <c r="N526" t="n">
         <v>6.1</v>
       </c>
-      <c r="M526" s="1" t="n">
+      <c r="O526" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="N526" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O526" s="1" t="n">
-        <v>45948</v>
-      </c>
       <c r="P526" t="n">
-        <v>6.54</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="527">
@@ -23809,49 +23825,49 @@
         <v>611</v>
       </c>
       <c r="B528" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C528" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D528" t="n">
         <v>7.2</v>
       </c>
-      <c r="C528" s="1" t="n">
+      <c r="E528" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D528" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E528" s="1" t="n">
+      <c r="F528" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G528" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F528" t="n">
+      <c r="H528" t="n">
         <v>7.2</v>
       </c>
-      <c r="G528" s="1" t="n">
+      <c r="I528" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H528" t="n">
+      <c r="J528" t="n">
         <v>7</v>
       </c>
-      <c r="I528" s="1" t="n">
+      <c r="K528" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="J528" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K528" s="1" t="n">
+      <c r="L528" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M528" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="L528" t="n">
+      <c r="N528" t="n">
         <v>7.2</v>
       </c>
-      <c r="M528" s="1" t="n">
+      <c r="O528" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="N528" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O528" s="1" t="n">
-        <v>45996</v>
-      </c>
       <c r="P528" t="n">
-        <v>7.09</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="529">
@@ -24109,49 +24125,49 @@
         <v>617</v>
       </c>
       <c r="B534" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C534" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="D534" t="n">
         <v>6</v>
       </c>
-      <c r="C534" s="1" t="n">
+      <c r="E534" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="D534" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E534" s="1" t="n">
+      <c r="F534" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G534" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="F534" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G534" s="1" t="n">
+      <c r="H534" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I534" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="H534" t="n">
+      <c r="J534" t="n">
         <v>6.4</v>
       </c>
-      <c r="I534" s="1" t="n">
+      <c r="K534" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="J534" t="n">
+      <c r="L534" t="n">
         <v>7</v>
       </c>
-      <c r="K534" s="1" t="n">
+      <c r="M534" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="L534" t="n">
+      <c r="N534" t="n">
         <v>6.4</v>
       </c>
-      <c r="M534" s="1" t="n">
+      <c r="O534" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="N534" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O534" s="1" t="n">
-        <v>45996</v>
-      </c>
       <c r="P534" t="n">
-        <v>6.51</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="535">
@@ -24159,49 +24175,49 @@
         <v>618</v>
       </c>
       <c r="B535" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C535" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D535" t="n">
         <v>6.8</v>
       </c>
-      <c r="C535" s="1" t="n">
+      <c r="E535" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D535" t="n">
+      <c r="F535" t="n">
         <v>7.2</v>
       </c>
-      <c r="E535" s="1" t="n">
+      <c r="G535" s="1" t="n">
         <v>46055</v>
       </c>
-      <c r="F535" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G535" s="1" t="n">
+      <c r="H535" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I535" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="H535" t="n">
+      <c r="J535" t="n">
         <v>6.1</v>
       </c>
-      <c r="I535" s="1" t="n">
+      <c r="K535" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="J535" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K535" s="1" t="n">
+      <c r="L535" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M535" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="L535" t="n">
+      <c r="N535" t="n">
         <v>7.3</v>
       </c>
-      <c r="M535" s="1" t="n">
+      <c r="O535" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="N535" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O535" s="1" t="n">
-        <v>46003</v>
-      </c>
       <c r="P535" t="n">
-        <v>6.7</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="536">
@@ -24209,49 +24225,49 @@
         <v>619</v>
       </c>
       <c r="B536" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C536" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D536" t="n">
         <v>7.4</v>
       </c>
-      <c r="C536" s="1" t="n">
+      <c r="E536" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="D536" t="n">
+      <c r="F536" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="E536" s="1" t="n">
+      <c r="G536" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="F536" t="n">
+      <c r="H536" t="n">
         <v>7.1</v>
       </c>
-      <c r="G536" s="1" t="n">
+      <c r="I536" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="H536" t="n">
+      <c r="J536" t="n">
         <v>7.7</v>
       </c>
-      <c r="I536" s="1" t="n">
+      <c r="K536" s="1" t="n">
         <v>45986</v>
       </c>
-      <c r="J536" t="n">
+      <c r="L536" t="n">
         <v>7.6</v>
       </c>
-      <c r="K536" s="1" t="n">
+      <c r="M536" s="1" t="n">
         <v>45961</v>
       </c>
-      <c r="L536" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M536" s="1" t="n">
+      <c r="N536" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O536" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N536" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O536" s="1" t="n">
-        <v>45947</v>
-      </c>
       <c r="P536" t="n">
-        <v>7.4</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="537">
@@ -24359,49 +24375,49 @@
         <v>622</v>
       </c>
       <c r="B539" t="n">
+        <v>7</v>
+      </c>
+      <c r="C539" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D539" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E539" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="F539" t="n">
         <v>7.3</v>
       </c>
-      <c r="C539" s="1" t="n">
+      <c r="G539" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="D539" t="n">
+      <c r="H539" t="n">
         <v>6.9</v>
       </c>
-      <c r="E539" s="1" t="n">
+      <c r="I539" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="F539" t="n">
+      <c r="J539" t="n">
         <v>6.9</v>
       </c>
-      <c r="G539" s="1" t="n">
+      <c r="K539" s="1" t="n">
         <v>45990</v>
-      </c>
-      <c r="H539" t="n">
-        <v>7</v>
-      </c>
-      <c r="I539" s="1" t="n">
-        <v>45984</v>
-      </c>
-      <c r="J539" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K539" s="1" t="n">
-        <v>45976</v>
       </c>
       <c r="L539" t="n">
         <v>7</v>
       </c>
       <c r="M539" s="1" t="n">
-        <v>45970</v>
+        <v>45984</v>
       </c>
       <c r="N539" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="O539" s="1" t="n">
-        <v>45964</v>
+        <v>45976</v>
       </c>
       <c r="P539" t="n">
-        <v>6.81</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="540">
@@ -24459,49 +24475,49 @@
         <v>624</v>
       </c>
       <c r="B541" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C541" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="D541" t="n">
         <v>7.7</v>
       </c>
-      <c r="C541" s="1" t="n">
+      <c r="E541" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="D541" t="n">
+      <c r="F541" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="E541" s="1" t="n">
+      <c r="G541" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="F541" t="n">
+      <c r="H541" t="n">
         <v>7.9</v>
       </c>
-      <c r="G541" s="1" t="n">
+      <c r="I541" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="H541" t="n">
+      <c r="J541" t="n">
         <v>6.9</v>
       </c>
-      <c r="I541" s="1" t="n">
+      <c r="K541" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="J541" t="n">
+      <c r="L541" t="n">
         <v>7.1</v>
       </c>
-      <c r="K541" s="1" t="n">
+      <c r="M541" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="L541" t="n">
+      <c r="N541" t="n">
         <v>5.6</v>
       </c>
-      <c r="M541" s="1" t="n">
+      <c r="O541" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="N541" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O541" s="1" t="n">
-        <v>45984</v>
-      </c>
       <c r="P541" t="n">
-        <v>7.34</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="542">
@@ -24559,49 +24575,49 @@
         <v>626</v>
       </c>
       <c r="B543" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C543" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="D543" t="n">
         <v>6.8</v>
       </c>
-      <c r="C543" s="1" t="n">
+      <c r="E543" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D543" t="n">
+      <c r="F543" t="n">
         <v>7.4</v>
       </c>
-      <c r="E543" s="1" t="n">
+      <c r="G543" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F543" t="n">
+      <c r="H543" t="n">
         <v>7.6</v>
       </c>
-      <c r="G543" s="1" t="n">
+      <c r="I543" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H543" t="n">
+      <c r="J543" t="n">
         <v>8.1</v>
       </c>
-      <c r="I543" s="1" t="n">
+      <c r="K543" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="J543" t="n">
+      <c r="L543" t="n">
         <v>6.1</v>
       </c>
-      <c r="K543" s="1" t="n">
+      <c r="M543" s="1" t="n">
         <v>45994</v>
       </c>
-      <c r="L543" t="n">
+      <c r="N543" t="n">
         <v>7.8</v>
       </c>
-      <c r="M543" s="1" t="n">
+      <c r="O543" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="N543" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O543" s="1" t="n">
-        <v>45983</v>
-      </c>
       <c r="P543" t="n">
-        <v>7.2</v>
+        <v>7.47</v>
       </c>
     </row>
   </sheetData>

--- a/players_ratings.xlsx
+++ b/players_ratings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P482"/>
+  <dimension ref="A1:P492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,49 +507,49 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D2" t="n">
         <v>7.3</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="E2" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>7.6</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="G2" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G2" s="1" t="n">
+      <c r="H2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>6.3</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="K2" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="J2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K2" s="1" t="n">
+      <c r="L2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M2" s="1" t="n">
         <v>45936</v>
       </c>
-      <c r="L2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M2" s="1" t="n">
+      <c r="N2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O2" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="N2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>45920</v>
-      </c>
       <c r="P2" t="n">
-        <v>6.77</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="3">
@@ -607,49 +607,49 @@
         <v>15</v>
       </c>
       <c r="B4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D4" t="n">
         <v>7.2</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="E4" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>6.3</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="G4" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>8.6</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>6.1</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>6.3</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="M4" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>6.8</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="O4" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="N4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P4" t="n">
-        <v>6.9</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="5">
@@ -829,49 +829,49 @@
         <v>27</v>
       </c>
       <c r="B9" t="n">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="C9" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E9" s="1" t="n">
+      <c r="F9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="I9" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="H9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I9" s="1" t="n">
+      <c r="J9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K9" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="J9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K9" s="1" t="n">
+      <c r="L9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M9" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="L9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M9" s="1" t="n">
+      <c r="N9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O9" s="1" t="n">
         <v>45949</v>
       </c>
-      <c r="N9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O9" s="1" t="n">
-        <v>45936</v>
-      </c>
       <c r="P9" t="n">
-        <v>6.77</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="10">
@@ -949,49 +949,49 @@
         <v>30</v>
       </c>
       <c r="B12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D12" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="E12" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="G12" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G12" s="1" t="n">
+      <c r="H12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>7.4</v>
       </c>
-      <c r="I12" s="1" t="n">
+      <c r="K12" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="J12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K12" s="1" t="n">
+      <c r="L12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M12" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>6.9</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="O12" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N12" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P12" t="n">
-        <v>7.46</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="13">
@@ -999,49 +999,49 @@
         <v>34</v>
       </c>
       <c r="B13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D13" t="n">
         <v>6.8</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="E13" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>6.3</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="G13" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>8.1</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="I13" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>7.6</v>
       </c>
-      <c r="I13" s="1" t="n">
+      <c r="K13" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>7</v>
       </c>
-      <c r="K13" s="1" t="n">
+      <c r="M13" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>7.8</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="O13" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="N13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P13" t="n">
-        <v>7.11</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="14">
@@ -1049,49 +1049,49 @@
         <v>36</v>
       </c>
       <c r="B14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D14" t="n">
         <v>8.4</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="E14" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>7.4</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="G14" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G14" s="1" t="n">
+      <c r="H14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I14" s="1" t="n">
+      <c r="J14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K14" s="1" t="n">
         <v>45991</v>
-      </c>
-      <c r="J14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>45970</v>
       </c>
       <c r="L14" t="n">
         <v>6.4</v>
       </c>
       <c r="M14" s="1" t="n">
+        <v>45970</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O14" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="N14" t="n">
-        <v>7</v>
-      </c>
-      <c r="O14" s="1" t="n">
-        <v>45949</v>
-      </c>
       <c r="P14" t="n">
-        <v>6.96</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="15">
@@ -1099,49 +1099,49 @@
         <v>38</v>
       </c>
       <c r="B15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D15" t="n">
         <v>6.9</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="E15" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>8.1</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="G15" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="I15" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="H15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I15" s="1" t="n">
+      <c r="J15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K15" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>6</v>
       </c>
-      <c r="K15" s="1" t="n">
+      <c r="M15" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>6.2</v>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="O15" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="N15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>45932</v>
-      </c>
       <c r="P15" t="n">
-        <v>6.74</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="16">
@@ -1175,19 +1175,23 @@
         <v>41</v>
       </c>
       <c r="B17" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C17" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E17" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>6.3</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="G17" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -1205,49 +1209,49 @@
         <v>43</v>
       </c>
       <c r="B18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D18" t="n">
         <v>7.7</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="E18" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>6</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="G18" s="1" t="n">
         <v>45981</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>7.4</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="I18" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>6.4</v>
       </c>
-      <c r="I18" s="1" t="n">
+      <c r="K18" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="J18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K18" s="1" t="n">
+      <c r="L18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M18" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>7.6</v>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="O18" s="1" t="n">
         <v>45946</v>
       </c>
-      <c r="N18" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O18" s="1" t="n">
-        <v>45933</v>
-      </c>
       <c r="P18" t="n">
-        <v>6.84</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="19">
@@ -1495,13 +1499,17 @@
         <v>55</v>
       </c>
       <c r="B25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D25" t="n">
         <v>7</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="E25" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1513,7 +1521,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="26">
@@ -1893,49 +1901,49 @@
         <v>75</v>
       </c>
       <c r="B34" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D34" t="n">
         <v>6.2</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="E34" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>6.4</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="G34" s="1" t="n">
         <v>46055</v>
       </c>
-      <c r="F34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G34" s="1" t="n">
+      <c r="H34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I34" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="H34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I34" s="1" t="n">
+      <c r="J34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K34" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="J34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K34" s="1" t="n">
+      <c r="L34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M34" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>6.3</v>
       </c>
-      <c r="M34" s="1" t="n">
+      <c r="O34" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="N34" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O34" s="1" t="n">
-        <v>45976</v>
-      </c>
       <c r="P34" t="n">
-        <v>6.49</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="35">
@@ -1943,49 +1951,49 @@
         <v>80</v>
       </c>
       <c r="B35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D35" t="n">
         <v>6.2</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="E35" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>6.8</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="G35" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F35" t="n">
+      <c r="H35" t="n">
         <v>7.3</v>
       </c>
-      <c r="G35" s="1" t="n">
+      <c r="I35" s="1" t="n">
         <v>46060</v>
-      </c>
-      <c r="H35" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I35" s="1" t="n">
-        <v>46054</v>
       </c>
       <c r="J35" t="n">
         <v>6.8</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46047</v>
+        <v>46054</v>
       </c>
       <c r="L35" t="n">
         <v>6.8</v>
       </c>
       <c r="M35" s="1" t="n">
+        <v>46047</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O35" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="N35" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O35" s="1" t="n">
-        <v>46012</v>
-      </c>
       <c r="P35" t="n">
-        <v>6.99</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="36">
@@ -2933,49 +2941,49 @@
         <v>124</v>
       </c>
       <c r="B59" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D59" t="n">
         <v>6.8</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="E59" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D59" t="n">
+      <c r="F59" t="n">
         <v>5.9</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="G59" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F59" t="n">
+      <c r="H59" t="n">
         <v>6.4</v>
       </c>
-      <c r="G59" s="1" t="n">
+      <c r="I59" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="H59" t="n">
+      <c r="J59" t="n">
         <v>7</v>
       </c>
-      <c r="I59" s="1" t="n">
+      <c r="K59" s="1" t="n">
         <v>45992</v>
-      </c>
-      <c r="J59" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K59" s="1" t="n">
-        <v>45983</v>
       </c>
       <c r="L59" t="n">
         <v>7.1</v>
       </c>
       <c r="M59" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="N59" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O59" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N59" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O59" s="1" t="n">
-        <v>45956</v>
-      </c>
       <c r="P59" t="n">
-        <v>6.8</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="60">
@@ -3003,49 +3011,49 @@
         <v>132</v>
       </c>
       <c r="B61" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="C61" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E61" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D61" t="n">
+      <c r="F61" t="n">
         <v>6.4</v>
       </c>
-      <c r="E61" s="1" t="n">
+      <c r="G61" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F61" t="n">
+      <c r="H61" t="n">
         <v>7</v>
       </c>
-      <c r="G61" s="1" t="n">
+      <c r="I61" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="H61" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I61" s="1" t="n">
+      <c r="J61" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K61" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="J61" t="n">
+      <c r="L61" t="n">
         <v>7.5</v>
       </c>
-      <c r="K61" s="1" t="n">
+      <c r="M61" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="L61" t="n">
+      <c r="N61" t="n">
         <v>7.7</v>
       </c>
-      <c r="M61" s="1" t="n">
+      <c r="O61" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="N61" t="n">
-        <v>7</v>
-      </c>
-      <c r="O61" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P61" t="n">
-        <v>6.97</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="62">
@@ -3156,46 +3164,46 @@
         <v>6.8</v>
       </c>
       <c r="C64" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D64" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E64" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D64" t="n">
+      <c r="F64" t="n">
         <v>6.9</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="G64" s="1" t="n">
         <v>45991</v>
-      </c>
-      <c r="F64" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>45969</v>
       </c>
       <c r="H64" t="n">
         <v>6.8</v>
       </c>
       <c r="I64" s="1" t="n">
+        <v>45969</v>
+      </c>
+      <c r="J64" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K64" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="J64" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K64" s="1" t="n">
+      <c r="L64" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M64" s="1" t="n">
         <v>45950</v>
       </c>
-      <c r="L64" t="n">
+      <c r="N64" t="n">
         <v>7.3</v>
       </c>
-      <c r="M64" s="1" t="n">
+      <c r="O64" s="1" t="n">
         <v>45935</v>
       </c>
-      <c r="N64" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O64" s="1" t="n">
-        <v>45932</v>
-      </c>
       <c r="P64" t="n">
-        <v>6.91</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="65">
@@ -3223,46 +3231,46 @@
         <v>143</v>
       </c>
       <c r="B66" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D66" t="n">
         <v>6.3</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="E66" s="1" t="n">
         <v>46076</v>
       </c>
-      <c r="D66" t="n">
+      <c r="F66" t="n">
         <v>7</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="G66" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F66" t="n">
+      <c r="H66" t="n">
         <v>6</v>
       </c>
-      <c r="G66" s="1" t="n">
+      <c r="I66" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H66" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I66" s="1" t="n">
+      <c r="J66" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K66" s="1" t="n">
         <v>46057</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>5.7</v>
       </c>
-      <c r="K66" s="1" t="n">
+      <c r="M66" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="L66" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M66" s="1" t="n">
+      <c r="N66" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O66" s="1" t="n">
         <v>46045</v>
-      </c>
-      <c r="N66" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O66" s="1" t="n">
-        <v>46039</v>
       </c>
       <c r="P66" t="n">
         <v>6.37</v>
@@ -3323,49 +3331,49 @@
         <v>145</v>
       </c>
       <c r="B68" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C68" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D68" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E68" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D68" t="n">
+      <c r="F68" t="n">
         <v>6.8</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="G68" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="F68" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G68" s="1" t="n">
+      <c r="H68" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I68" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="H68" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I68" s="1" t="n">
+      <c r="J68" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K68" s="1" t="n">
         <v>46057</v>
       </c>
-      <c r="J68" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K68" s="1" t="n">
+      <c r="L68" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M68" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="L68" t="n">
+      <c r="N68" t="n">
         <v>6.3</v>
       </c>
-      <c r="M68" s="1" t="n">
+      <c r="O68" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="N68" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O68" s="1" t="n">
-        <v>46005</v>
-      </c>
       <c r="P68" t="n">
-        <v>6.79</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="69">
@@ -3373,46 +3381,46 @@
         <v>146</v>
       </c>
       <c r="B69" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D69" t="n">
         <v>7.7</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="E69" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D69" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E69" s="1" t="n">
+      <c r="F69" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G69" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F69" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G69" s="1" t="n">
+      <c r="H69" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I69" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H69" t="n">
+      <c r="J69" t="n">
         <v>6</v>
       </c>
-      <c r="I69" s="1" t="n">
+      <c r="K69" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>7.1</v>
       </c>
-      <c r="K69" s="1" t="n">
+      <c r="M69" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L69" t="n">
+      <c r="N69" t="n">
         <v>7.3</v>
       </c>
-      <c r="M69" s="1" t="n">
+      <c r="O69" s="1" t="n">
         <v>46038</v>
-      </c>
-      <c r="N69" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O69" s="1" t="n">
-        <v>46011</v>
       </c>
       <c r="P69" t="n">
         <v>6.89</v>
@@ -3423,49 +3431,49 @@
         <v>147</v>
       </c>
       <c r="B70" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C70" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E70" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D70" t="n">
+      <c r="F70" t="n">
         <v>6.2</v>
       </c>
-      <c r="E70" s="1" t="n">
+      <c r="G70" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F70" t="n">
+      <c r="H70" t="n">
         <v>7.1</v>
       </c>
-      <c r="G70" s="1" t="n">
+      <c r="I70" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H70" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I70" s="1" t="n">
+      <c r="J70" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K70" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="J70" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K70" s="1" t="n">
+      <c r="L70" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M70" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L70" t="n">
+      <c r="N70" t="n">
         <v>6.2</v>
       </c>
-      <c r="M70" s="1" t="n">
+      <c r="O70" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="N70" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O70" s="1" t="n">
-        <v>46038</v>
-      </c>
       <c r="P70" t="n">
-        <v>6.71</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="71">
@@ -3493,49 +3501,49 @@
         <v>149</v>
       </c>
       <c r="B72" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="C72" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D72" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E72" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="D72" t="n">
+      <c r="F72" t="n">
         <v>7.1</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="G72" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="F72" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G72" s="1" t="n">
+      <c r="H72" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I72" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="H72" t="n">
+      <c r="J72" t="n">
         <v>7.2</v>
       </c>
-      <c r="I72" s="1" t="n">
+      <c r="K72" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>6.2</v>
       </c>
-      <c r="K72" s="1" t="n">
+      <c r="M72" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L72" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M72" s="1" t="n">
+      <c r="N72" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O72" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="N72" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O72" s="1" t="n">
-        <v>45947</v>
-      </c>
       <c r="P72" t="n">
-        <v>6.67</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="73">
@@ -3543,49 +3551,49 @@
         <v>150</v>
       </c>
       <c r="B73" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D73" t="n">
         <v>7.1</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="E73" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="D73" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E73" s="1" t="n">
+      <c r="F73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G73" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="F73" t="n">
+      <c r="H73" t="n">
         <v>7.9</v>
       </c>
-      <c r="G73" s="1" t="n">
+      <c r="I73" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="H73" t="n">
+      <c r="J73" t="n">
         <v>8</v>
       </c>
-      <c r="I73" s="1" t="n">
+      <c r="K73" s="1" t="n">
         <v>45951</v>
       </c>
-      <c r="J73" t="n">
+      <c r="L73" t="n">
         <v>6.9</v>
       </c>
-      <c r="K73" s="1" t="n">
+      <c r="M73" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="L73" t="n">
+      <c r="N73" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="M73" s="1" t="n">
+      <c r="O73" s="1" t="n">
         <v>45933</v>
       </c>
-      <c r="N73" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O73" s="1" t="n">
-        <v>45927</v>
-      </c>
       <c r="P73" t="n">
-        <v>7.34</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="74">
@@ -3793,49 +3801,49 @@
         <v>167</v>
       </c>
       <c r="B78" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="C78" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D78" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E78" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D78" t="n">
+      <c r="F78" t="n">
         <v>8.1</v>
       </c>
-      <c r="E78" s="1" t="n">
+      <c r="G78" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F78" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G78" s="1" t="n">
+      <c r="H78" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I78" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H78" t="n">
+      <c r="J78" t="n">
         <v>7.1</v>
       </c>
-      <c r="I78" s="1" t="n">
+      <c r="K78" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="K78" s="1" t="n">
+      <c r="M78" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L78" t="n">
+      <c r="N78" t="n">
         <v>7.8</v>
       </c>
-      <c r="M78" s="1" t="n">
+      <c r="O78" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="N78" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O78" s="1" t="n">
-        <v>45983</v>
-      </c>
       <c r="P78" t="n">
-        <v>7.43</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="79">
@@ -3965,19 +3973,23 @@
         <v>173</v>
       </c>
       <c r="B82" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D82" t="n">
         <v>6.3</v>
       </c>
-      <c r="C82" s="1" t="n">
+      <c r="E82" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D82" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E82" s="1" t="n">
+      <c r="F82" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G82" s="1" t="n">
         <v>46058</v>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
@@ -3987,7 +3999,7 @@
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
-        <v>6.4</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="83">
@@ -4175,49 +4187,49 @@
         <v>181</v>
       </c>
       <c r="B87" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="C87" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D87" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E87" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D87" t="n">
+      <c r="F87" t="n">
         <v>6.9</v>
       </c>
-      <c r="E87" s="1" t="n">
+      <c r="G87" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="F87" t="n">
+      <c r="H87" t="n">
         <v>7.1</v>
       </c>
-      <c r="G87" s="1" t="n">
+      <c r="I87" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H87" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I87" s="1" t="n">
+      <c r="J87" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K87" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="J87" t="n">
+      <c r="L87" t="n">
         <v>7</v>
       </c>
-      <c r="K87" s="1" t="n">
+      <c r="M87" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L87" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M87" s="1" t="n">
+      <c r="N87" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O87" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N87" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O87" s="1" t="n">
-        <v>45991</v>
-      </c>
       <c r="P87" t="n">
-        <v>6.81</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="88">
@@ -4355,49 +4367,49 @@
         <v>186</v>
       </c>
       <c r="B91" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="C91" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D91" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E91" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D91" t="n">
+      <c r="F91" t="n">
         <v>6.2</v>
       </c>
-      <c r="E91" s="1" t="n">
+      <c r="G91" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F91" t="n">
+      <c r="H91" t="n">
         <v>7.2</v>
       </c>
-      <c r="G91" s="1" t="n">
+      <c r="I91" s="1" t="n">
         <v>46051</v>
       </c>
-      <c r="H91" t="n">
+      <c r="J91" t="n">
         <v>6</v>
       </c>
-      <c r="I91" s="1" t="n">
+      <c r="K91" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="J91" t="n">
+      <c r="L91" t="n">
         <v>6.8</v>
       </c>
-      <c r="K91" s="1" t="n">
+      <c r="M91" s="1" t="n">
         <v>46028</v>
       </c>
-      <c r="L91" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M91" s="1" t="n">
+      <c r="N91" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O91" s="1" t="n">
         <v>46024</v>
       </c>
-      <c r="N91" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O91" s="1" t="n">
-        <v>46020</v>
-      </c>
       <c r="P91" t="n">
-        <v>6.79</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="92">
@@ -4525,37 +4537,41 @@
         <v>192</v>
       </c>
       <c r="B95" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="C95" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D95" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E95" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D95" t="n">
+      <c r="F95" t="n">
         <v>6.9</v>
       </c>
-      <c r="E95" s="1" t="n">
+      <c r="G95" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F95" t="n">
+      <c r="H95" t="n">
         <v>5.8</v>
       </c>
-      <c r="G95" s="1" t="n">
+      <c r="I95" s="1" t="n">
         <v>46064</v>
       </c>
-      <c r="H95" t="n">
+      <c r="J95" t="n">
         <v>6.2</v>
       </c>
-      <c r="I95" s="1" t="n">
+      <c r="K95" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="n">
-        <v>6.38</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="96">
@@ -4563,25 +4579,29 @@
         <v>193</v>
       </c>
       <c r="B96" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C96" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D96" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E96" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D96" t="n">
+      <c r="F96" t="n">
         <v>6.9</v>
       </c>
-      <c r="E96" s="1" t="n">
+      <c r="G96" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F96" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G96" s="1" t="n">
+      <c r="H96" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I96" s="1" t="n">
         <v>45900</v>
       </c>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
@@ -4589,7 +4609,7 @@
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="n">
-        <v>6.67</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="97">
@@ -4647,49 +4667,49 @@
         <v>195</v>
       </c>
       <c r="B98" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D98" t="n">
         <v>6.1</v>
       </c>
-      <c r="C98" s="1" t="n">
+      <c r="E98" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D98" t="n">
+      <c r="F98" t="n">
         <v>7.7</v>
       </c>
-      <c r="E98" s="1" t="n">
+      <c r="G98" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F98" t="n">
+      <c r="H98" t="n">
         <v>5.8</v>
       </c>
-      <c r="G98" s="1" t="n">
+      <c r="I98" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H98" t="n">
+      <c r="J98" t="n">
         <v>6.4</v>
       </c>
-      <c r="I98" s="1" t="n">
+      <c r="K98" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="J98" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K98" s="1" t="n">
+      <c r="L98" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M98" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="L98" t="n">
+      <c r="N98" t="n">
         <v>7.1</v>
       </c>
-      <c r="M98" s="1" t="n">
+      <c r="O98" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="N98" t="n">
-        <v>7</v>
-      </c>
-      <c r="O98" s="1" t="n">
-        <v>45999</v>
-      </c>
       <c r="P98" t="n">
-        <v>6.69</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="99">
@@ -4747,49 +4767,49 @@
         <v>198</v>
       </c>
       <c r="B100" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C100" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D100" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E100" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D100" t="n">
+      <c r="F100" t="n">
         <v>6.4</v>
       </c>
-      <c r="E100" s="1" t="n">
+      <c r="G100" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="F100" t="n">
+      <c r="H100" t="n">
         <v>7</v>
       </c>
-      <c r="G100" s="1" t="n">
+      <c r="I100" s="1" t="n">
         <v>46013</v>
       </c>
-      <c r="H100" t="n">
+      <c r="J100" t="n">
         <v>6.9</v>
       </c>
-      <c r="I100" s="1" t="n">
+      <c r="K100" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="J100" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K100" s="1" t="n">
+      <c r="L100" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M100" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L100" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M100" s="1" t="n">
+      <c r="N100" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O100" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="N100" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O100" s="1" t="n">
-        <v>45954</v>
-      </c>
       <c r="P100" t="n">
-        <v>6.67</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="101">
@@ -4797,49 +4817,49 @@
         <v>200</v>
       </c>
       <c r="B101" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D101" t="n">
         <v>6.9</v>
       </c>
-      <c r="C101" s="1" t="n">
+      <c r="E101" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D101" t="n">
+      <c r="F101" t="n">
         <v>7.9</v>
       </c>
-      <c r="E101" s="1" t="n">
+      <c r="G101" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F101" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G101" s="1" t="n">
+      <c r="H101" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I101" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H101" t="n">
+      <c r="J101" t="n">
         <v>6.3</v>
       </c>
-      <c r="I101" s="1" t="n">
+      <c r="K101" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="J101" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K101" s="1" t="n">
+      <c r="L101" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M101" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L101" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M101" s="1" t="n">
+      <c r="N101" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O101" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N101" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O101" s="1" t="n">
-        <v>45948</v>
-      </c>
       <c r="P101" t="n">
-        <v>6.79</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="102">
@@ -4847,49 +4867,49 @@
         <v>201</v>
       </c>
       <c r="B102" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D102" t="n">
         <v>5.9</v>
       </c>
-      <c r="C102" s="1" t="n">
+      <c r="E102" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D102" t="n">
+      <c r="F102" t="n">
         <v>5.7</v>
       </c>
-      <c r="E102" s="1" t="n">
+      <c r="G102" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F102" t="n">
+      <c r="H102" t="n">
         <v>6</v>
       </c>
-      <c r="G102" s="1" t="n">
+      <c r="I102" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H102" t="n">
+      <c r="J102" t="n">
         <v>6.2</v>
       </c>
-      <c r="I102" s="1" t="n">
+      <c r="K102" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J102" t="n">
+      <c r="L102" t="n">
         <v>6.9</v>
       </c>
-      <c r="K102" s="1" t="n">
+      <c r="M102" s="1" t="n">
         <v>45949</v>
       </c>
-      <c r="L102" t="n">
+      <c r="N102" t="n">
         <v>7.5</v>
       </c>
-      <c r="M102" s="1" t="n">
+      <c r="O102" s="1" t="n">
         <v>45934</v>
       </c>
-      <c r="N102" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O102" s="1" t="n">
-        <v>45928</v>
-      </c>
       <c r="P102" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="103">
@@ -5299,37 +5319,41 @@
         <v>217</v>
       </c>
       <c r="B113" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D113" t="n">
         <v>5.6</v>
       </c>
-      <c r="C113" s="1" t="n">
+      <c r="E113" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D113" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E113" s="1" t="n">
+      <c r="F113" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G113" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F113" t="n">
+      <c r="H113" t="n">
         <v>6</v>
       </c>
-      <c r="G113" s="1" t="n">
+      <c r="I113" s="1" t="n">
         <v>46065</v>
       </c>
-      <c r="H113" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I113" s="1" t="n">
+      <c r="J113" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K113" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
-        <v>6.22</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="114">
@@ -6201,49 +6225,49 @@
         <v>247</v>
       </c>
       <c r="B136" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D136" t="n">
         <v>7.1</v>
       </c>
-      <c r="C136" s="1" t="n">
+      <c r="E136" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D136" t="n">
+      <c r="F136" t="n">
         <v>5.8</v>
       </c>
-      <c r="E136" s="1" t="n">
+      <c r="G136" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F136" t="n">
+      <c r="H136" t="n">
         <v>8.1</v>
       </c>
-      <c r="G136" s="1" t="n">
+      <c r="I136" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H136" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I136" s="1" t="n">
+      <c r="J136" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K136" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="J136" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K136" s="1" t="n">
+      <c r="L136" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M136" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="L136" t="n">
+      <c r="N136" t="n">
         <v>7</v>
       </c>
-      <c r="M136" s="1" t="n">
+      <c r="O136" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="N136" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O136" s="1" t="n">
-        <v>45998</v>
-      </c>
       <c r="P136" t="n">
-        <v>6.84</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="137">
@@ -6251,49 +6275,49 @@
         <v>248</v>
       </c>
       <c r="B137" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D137" t="n">
         <v>6.9</v>
       </c>
-      <c r="C137" s="1" t="n">
+      <c r="E137" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D137" t="n">
+      <c r="F137" t="n">
         <v>7.7</v>
       </c>
-      <c r="E137" s="1" t="n">
+      <c r="G137" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F137" t="n">
+      <c r="H137" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G137" s="1" t="n">
+      <c r="I137" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H137" t="n">
+      <c r="J137" t="n">
         <v>7.2</v>
       </c>
-      <c r="I137" s="1" t="n">
+      <c r="K137" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J137" t="n">
+      <c r="L137" t="n">
         <v>7.7</v>
       </c>
-      <c r="K137" s="1" t="n">
+      <c r="M137" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="L137" t="n">
+      <c r="N137" t="n">
         <v>6.8</v>
       </c>
-      <c r="M137" s="1" t="n">
+      <c r="O137" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="N137" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O137" s="1" t="n">
-        <v>46017</v>
-      </c>
       <c r="P137" t="n">
-        <v>7.46</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="138">
@@ -6351,49 +6375,49 @@
         <v>255</v>
       </c>
       <c r="B139" t="n">
+        <v>7</v>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D139" t="n">
         <v>6.1</v>
       </c>
-      <c r="C139" s="1" t="n">
+      <c r="E139" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D139" t="n">
+      <c r="F139" t="n">
         <v>6.4</v>
       </c>
-      <c r="E139" s="1" t="n">
+      <c r="G139" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="F139" t="n">
+      <c r="H139" t="n">
         <v>7.2</v>
       </c>
-      <c r="G139" s="1" t="n">
+      <c r="I139" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H139" t="n">
+      <c r="J139" t="n">
         <v>7.9</v>
       </c>
-      <c r="I139" s="1" t="n">
+      <c r="K139" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J139" t="n">
+      <c r="L139" t="n">
         <v>7.1</v>
       </c>
-      <c r="K139" s="1" t="n">
+      <c r="M139" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L139" t="n">
+      <c r="N139" t="n">
         <v>7.2</v>
       </c>
-      <c r="M139" s="1" t="n">
+      <c r="O139" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="N139" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O139" s="1" t="n">
-        <v>45955</v>
-      </c>
       <c r="P139" t="n">
-        <v>6.93</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="140">
@@ -6501,49 +6525,49 @@
         <v>259</v>
       </c>
       <c r="B142" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="C142" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D142" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E142" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D142" t="n">
+      <c r="F142" t="n">
         <v>7.4</v>
       </c>
-      <c r="E142" s="1" t="n">
+      <c r="G142" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="F142" t="n">
+      <c r="H142" t="n">
         <v>6.2</v>
       </c>
-      <c r="G142" s="1" t="n">
+      <c r="I142" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="H142" t="n">
+      <c r="J142" t="n">
         <v>6.3</v>
       </c>
-      <c r="I142" s="1" t="n">
+      <c r="K142" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="J142" t="n">
+      <c r="L142" t="n">
         <v>7.6</v>
       </c>
-      <c r="K142" s="1" t="n">
+      <c r="M142" s="1" t="n">
         <v>45950</v>
-      </c>
-      <c r="L142" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M142" s="1" t="n">
-        <v>45935</v>
       </c>
       <c r="N142" t="n">
         <v>6.8</v>
       </c>
       <c r="O142" s="1" t="n">
-        <v>45928</v>
+        <v>45935</v>
       </c>
       <c r="P142" t="n">
-        <v>6.8</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="143">
@@ -6771,49 +6795,49 @@
         <v>273</v>
       </c>
       <c r="B148" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D148" t="n">
         <v>7</v>
       </c>
-      <c r="C148" s="1" t="n">
+      <c r="E148" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D148" t="n">
+      <c r="F148" t="n">
         <v>6.2</v>
       </c>
-      <c r="E148" s="1" t="n">
+      <c r="G148" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F148" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G148" s="1" t="n">
+      <c r="H148" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I148" s="1" t="n">
         <v>46065</v>
-      </c>
-      <c r="H148" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I148" s="1" t="n">
-        <v>46061</v>
       </c>
       <c r="J148" t="n">
         <v>7.1</v>
       </c>
       <c r="K148" s="1" t="n">
+        <v>46061</v>
+      </c>
+      <c r="L148" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M148" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L148" t="n">
+      <c r="N148" t="n">
         <v>6.2</v>
       </c>
-      <c r="M148" s="1" t="n">
+      <c r="O148" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="N148" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O148" s="1" t="n">
-        <v>46005</v>
-      </c>
       <c r="P148" t="n">
-        <v>6.4</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="149">
@@ -6917,49 +6941,49 @@
         <v>276</v>
       </c>
       <c r="B151" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D151" t="n">
         <v>5.6</v>
       </c>
-      <c r="C151" s="1" t="n">
+      <c r="E151" s="1" t="n">
         <v>45921</v>
       </c>
-      <c r="D151" t="n">
+      <c r="F151" t="n">
         <v>7.5</v>
       </c>
-      <c r="E151" s="1" t="n">
+      <c r="G151" s="1" t="n">
         <v>45913</v>
       </c>
-      <c r="F151" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G151" s="1" t="n">
+      <c r="H151" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I151" s="1" t="n">
         <v>45901</v>
       </c>
-      <c r="H151" t="n">
+      <c r="J151" t="n">
         <v>7.9</v>
       </c>
-      <c r="I151" s="1" t="n">
+      <c r="K151" s="1" t="n">
         <v>45892</v>
       </c>
-      <c r="J151" t="n">
+      <c r="L151" t="n">
         <v>6.2</v>
       </c>
-      <c r="K151" s="1" t="n">
+      <c r="M151" s="1" t="n">
         <v>45888</v>
-      </c>
-      <c r="L151" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M151" s="1" t="n">
-        <v>45885</v>
       </c>
       <c r="N151" t="n">
         <v>7.1</v>
       </c>
       <c r="O151" s="1" t="n">
-        <v>45879</v>
+        <v>45885</v>
       </c>
       <c r="P151" t="n">
-        <v>6.86</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="152">
@@ -7108,22 +7132,26 @@
         <v>6.4</v>
       </c>
       <c r="C155" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D155" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E155" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D155" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E155" s="1" t="n">
+      <c r="F155" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G155" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F155" t="n">
+      <c r="H155" t="n">
         <v>6.2</v>
       </c>
-      <c r="G155" s="1" t="n">
+      <c r="I155" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
@@ -7131,7 +7159,7 @@
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="n">
-        <v>6.37</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="156">
@@ -7139,49 +7167,49 @@
         <v>281</v>
       </c>
       <c r="B156" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D156" t="n">
         <v>6.3</v>
       </c>
-      <c r="C156" s="1" t="n">
+      <c r="E156" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="D156" t="n">
+      <c r="F156" t="n">
         <v>8.1</v>
       </c>
-      <c r="E156" s="1" t="n">
+      <c r="G156" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="F156" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G156" s="1" t="n">
+      <c r="H156" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I156" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="H156" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I156" s="1" t="n">
+      <c r="J156" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K156" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="J156" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K156" s="1" t="n">
+      <c r="L156" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M156" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="L156" t="n">
+      <c r="N156" t="n">
         <v>6.9</v>
       </c>
-      <c r="M156" s="1" t="n">
+      <c r="O156" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="N156" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O156" s="1" t="n">
-        <v>46007</v>
-      </c>
       <c r="P156" t="n">
-        <v>6.84</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="157">
@@ -7189,49 +7217,49 @@
         <v>282</v>
       </c>
       <c r="B157" t="n">
+        <v>7</v>
+      </c>
+      <c r="C157" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D157" t="n">
         <v>7.1</v>
       </c>
-      <c r="C157" s="1" t="n">
+      <c r="E157" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D157" t="n">
+      <c r="F157" t="n">
         <v>7.2</v>
       </c>
-      <c r="E157" s="1" t="n">
+      <c r="G157" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F157" t="n">
+      <c r="H157" t="n">
         <v>7</v>
       </c>
-      <c r="G157" s="1" t="n">
+      <c r="I157" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H157" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I157" s="1" t="n">
+      <c r="J157" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K157" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J157" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K157" s="1" t="n">
+      <c r="L157" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M157" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="L157" t="n">
+      <c r="N157" t="n">
         <v>6.8</v>
       </c>
-      <c r="M157" s="1" t="n">
+      <c r="O157" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="N157" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="O157" s="1" t="n">
-        <v>46004</v>
-      </c>
       <c r="P157" t="n">
-        <v>7.17</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="158">
@@ -7335,49 +7363,49 @@
         <v>286</v>
       </c>
       <c r="B160" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D160" t="n">
         <v>6.9</v>
       </c>
-      <c r="C160" s="1" t="n">
+      <c r="E160" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D160" t="n">
+      <c r="F160" t="n">
         <v>7.4</v>
       </c>
-      <c r="E160" s="1" t="n">
+      <c r="G160" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F160" t="n">
+      <c r="H160" t="n">
         <v>6.2</v>
       </c>
-      <c r="G160" s="1" t="n">
+      <c r="I160" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H160" t="n">
+      <c r="J160" t="n">
         <v>7.8</v>
       </c>
-      <c r="I160" s="1" t="n">
+      <c r="K160" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J160" t="n">
+      <c r="L160" t="n">
         <v>7.4</v>
       </c>
-      <c r="K160" s="1" t="n">
+      <c r="M160" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="L160" t="n">
+      <c r="N160" t="n">
         <v>7.7</v>
       </c>
-      <c r="M160" s="1" t="n">
+      <c r="O160" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="N160" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O160" s="1" t="n">
-        <v>45999</v>
-      </c>
       <c r="P160" t="n">
-        <v>7.14</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="161">
@@ -7435,49 +7463,49 @@
         <v>288</v>
       </c>
       <c r="B162" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D162" t="n">
         <v>6.1</v>
       </c>
-      <c r="C162" s="1" t="n">
+      <c r="E162" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="D162" t="n">
+      <c r="F162" t="n">
         <v>6.3</v>
       </c>
-      <c r="E162" s="1" t="n">
+      <c r="G162" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="F162" t="n">
+      <c r="H162" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G162" s="1" t="n">
+      <c r="I162" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H162" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I162" s="1" t="n">
+      <c r="J162" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K162" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="J162" t="n">
+      <c r="L162" t="n">
         <v>7.6</v>
       </c>
-      <c r="K162" s="1" t="n">
+      <c r="M162" s="1" t="n">
         <v>45961</v>
       </c>
-      <c r="L162" t="n">
+      <c r="N162" t="n">
         <v>7.4</v>
       </c>
-      <c r="M162" s="1" t="n">
+      <c r="O162" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N162" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O162" s="1" t="n">
-        <v>45948</v>
-      </c>
       <c r="P162" t="n">
-        <v>6.97</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="163">
@@ -7485,49 +7513,49 @@
         <v>289</v>
       </c>
       <c r="B163" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C163" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D163" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E163" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D163" t="n">
+      <c r="F163" t="n">
         <v>6.8</v>
       </c>
-      <c r="E163" s="1" t="n">
+      <c r="G163" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F163" t="n">
+      <c r="H163" t="n">
         <v>6.3</v>
       </c>
-      <c r="G163" s="1" t="n">
+      <c r="I163" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H163" t="n">
+      <c r="J163" t="n">
         <v>7.2</v>
       </c>
-      <c r="I163" s="1" t="n">
+      <c r="K163" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J163" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K163" s="1" t="n">
+      <c r="L163" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M163" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="L163" t="n">
+      <c r="N163" t="n">
         <v>7</v>
       </c>
-      <c r="M163" s="1" t="n">
+      <c r="O163" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N163" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O163" s="1" t="n">
-        <v>45990</v>
-      </c>
       <c r="P163" t="n">
-        <v>6.71</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="164">
@@ -7535,49 +7563,49 @@
         <v>290</v>
       </c>
       <c r="B164" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D164" t="n">
         <v>6.1</v>
       </c>
-      <c r="C164" s="1" t="n">
+      <c r="E164" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D164" t="n">
+      <c r="F164" t="n">
         <v>6.3</v>
       </c>
-      <c r="E164" s="1" t="n">
+      <c r="G164" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F164" t="n">
+      <c r="H164" t="n">
         <v>7.9</v>
       </c>
-      <c r="G164" s="1" t="n">
+      <c r="I164" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="H164" t="n">
+      <c r="J164" t="n">
         <v>7.8</v>
       </c>
-      <c r="I164" s="1" t="n">
+      <c r="K164" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J164" t="n">
+      <c r="L164" t="n">
         <v>7.3</v>
       </c>
-      <c r="K164" s="1" t="n">
+      <c r="M164" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="L164" t="n">
+      <c r="N164" t="n">
         <v>6.2</v>
       </c>
-      <c r="M164" s="1" t="n">
+      <c r="O164" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N164" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O164" s="1" t="n">
-        <v>45964</v>
-      </c>
       <c r="P164" t="n">
-        <v>6.9</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="165">
@@ -7708,34 +7736,38 @@
         <v>6.5</v>
       </c>
       <c r="C168" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D168" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E168" s="1" t="n">
         <v>45987</v>
       </c>
-      <c r="D168" t="n">
+      <c r="F168" t="n">
         <v>5.9</v>
       </c>
-      <c r="E168" s="1" t="n">
+      <c r="G168" s="1" t="n">
         <v>45900</v>
       </c>
-      <c r="F168" t="n">
+      <c r="H168" t="n">
         <v>6.8</v>
       </c>
-      <c r="G168" s="1" t="n">
+      <c r="I168" s="1" t="n">
         <v>45879</v>
       </c>
-      <c r="H168" t="n">
+      <c r="J168" t="n">
         <v>6.3</v>
       </c>
-      <c r="I168" s="1" t="n">
+      <c r="K168" s="1" t="n">
         <v>45872</v>
       </c>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="n">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="169">
@@ -7743,49 +7775,49 @@
         <v>295</v>
       </c>
       <c r="B169" t="n">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="C169" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D169" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E169" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D169" t="n">
+      <c r="F169" t="n">
         <v>7.3</v>
       </c>
-      <c r="E169" s="1" t="n">
+      <c r="G169" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F169" t="n">
+      <c r="H169" t="n">
         <v>6.8</v>
       </c>
-      <c r="G169" s="1" t="n">
+      <c r="I169" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H169" t="n">
+      <c r="J169" t="n">
         <v>7.3</v>
       </c>
-      <c r="I169" s="1" t="n">
+      <c r="K169" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="J169" t="n">
+      <c r="L169" t="n">
         <v>7.5</v>
       </c>
-      <c r="K169" s="1" t="n">
+      <c r="M169" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="L169" t="n">
+      <c r="N169" t="n">
         <v>7.9</v>
       </c>
-      <c r="M169" s="1" t="n">
+      <c r="O169" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="N169" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O169" s="1" t="n">
-        <v>45984</v>
-      </c>
       <c r="P169" t="n">
-        <v>7.13</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="170">
@@ -7951,49 +7983,49 @@
         <v>302</v>
       </c>
       <c r="B174" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C174" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D174" t="n">
         <v>6.4</v>
       </c>
-      <c r="C174" s="1" t="n">
+      <c r="E174" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D174" t="n">
+      <c r="F174" t="n">
         <v>7.6</v>
       </c>
-      <c r="E174" s="1" t="n">
+      <c r="G174" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F174" t="n">
+      <c r="H174" t="n">
         <v>7</v>
       </c>
-      <c r="G174" s="1" t="n">
+      <c r="I174" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H174" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I174" s="1" t="n">
+      <c r="J174" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K174" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J174" t="n">
+      <c r="L174" t="n">
         <v>5.5</v>
       </c>
-      <c r="K174" s="1" t="n">
+      <c r="M174" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="L174" t="n">
+      <c r="N174" t="n">
         <v>6.3</v>
       </c>
-      <c r="M174" s="1" t="n">
+      <c r="O174" s="1" t="n">
         <v>45928</v>
       </c>
-      <c r="N174" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O174" s="1" t="n">
-        <v>45919</v>
-      </c>
       <c r="P174" t="n">
-        <v>6.41</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="175">
@@ -8001,49 +8033,49 @@
         <v>303</v>
       </c>
       <c r="B175" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C175" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D175" t="n">
         <v>7</v>
       </c>
-      <c r="C175" s="1" t="n">
+      <c r="E175" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D175" t="n">
+      <c r="F175" t="n">
         <v>6.9</v>
       </c>
-      <c r="E175" s="1" t="n">
+      <c r="G175" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F175" t="n">
+      <c r="H175" t="n">
         <v>6.8</v>
       </c>
-      <c r="G175" s="1" t="n">
+      <c r="I175" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H175" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I175" s="1" t="n">
+      <c r="J175" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K175" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="J175" t="n">
+      <c r="L175" t="n">
         <v>7.1</v>
       </c>
-      <c r="K175" s="1" t="n">
+      <c r="M175" s="1" t="n">
         <v>45994</v>
       </c>
-      <c r="L175" t="n">
+      <c r="N175" t="n">
         <v>7.2</v>
       </c>
-      <c r="M175" s="1" t="n">
+      <c r="O175" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="N175" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O175" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P175" t="n">
-        <v>6.89</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="176">
@@ -8051,49 +8083,49 @@
         <v>305</v>
       </c>
       <c r="B176" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C176" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D176" t="n">
         <v>7.4</v>
       </c>
-      <c r="C176" s="1" t="n">
+      <c r="E176" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D176" t="n">
+      <c r="F176" t="n">
         <v>7</v>
       </c>
-      <c r="E176" s="1" t="n">
+      <c r="G176" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F176" t="n">
+      <c r="H176" t="n">
         <v>5.9</v>
       </c>
-      <c r="G176" s="1" t="n">
+      <c r="I176" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H176" t="n">
+      <c r="J176" t="n">
         <v>7</v>
       </c>
-      <c r="I176" s="1" t="n">
+      <c r="K176" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J176" t="n">
+      <c r="L176" t="n">
         <v>6.4</v>
       </c>
-      <c r="K176" s="1" t="n">
+      <c r="M176" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="L176" t="n">
+      <c r="N176" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="M176" s="1" t="n">
+      <c r="O176" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="N176" t="n">
-        <v>7</v>
-      </c>
-      <c r="O176" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P176" t="n">
-        <v>7.13</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="177">
@@ -8101,49 +8133,49 @@
         <v>306</v>
       </c>
       <c r="B177" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C177" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D177" t="n">
         <v>6.9</v>
       </c>
-      <c r="C177" s="1" t="n">
+      <c r="E177" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="D177" t="n">
+      <c r="F177" t="n">
         <v>6.3</v>
       </c>
-      <c r="E177" s="1" t="n">
+      <c r="G177" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="F177" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G177" s="1" t="n">
+      <c r="H177" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I177" s="1" t="n">
         <v>45953</v>
       </c>
-      <c r="H177" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I177" s="1" t="n">
+      <c r="J177" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K177" s="1" t="n">
         <v>45932</v>
-      </c>
-      <c r="J177" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K177" s="1" t="n">
-        <v>45927</v>
       </c>
       <c r="L177" t="n">
         <v>6.9</v>
       </c>
       <c r="M177" s="1" t="n">
+        <v>45927</v>
+      </c>
+      <c r="N177" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O177" s="1" t="n">
         <v>45921</v>
       </c>
-      <c r="N177" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O177" s="1" t="n">
-        <v>45913</v>
-      </c>
       <c r="P177" t="n">
-        <v>6.66</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="178">
@@ -8151,49 +8183,49 @@
         <v>307</v>
       </c>
       <c r="B178" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C178" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D178" t="n">
         <v>6.3</v>
       </c>
-      <c r="C178" s="1" t="n">
+      <c r="E178" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="D178" t="n">
+      <c r="F178" t="n">
         <v>7</v>
       </c>
-      <c r="E178" s="1" t="n">
+      <c r="G178" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="F178" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G178" s="1" t="n">
+      <c r="H178" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I178" s="1" t="n">
         <v>45961</v>
       </c>
-      <c r="H178" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I178" s="1" t="n">
+      <c r="J178" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K178" s="1" t="n">
         <v>45953</v>
       </c>
-      <c r="J178" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K178" s="1" t="n">
+      <c r="L178" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M178" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="L178" t="n">
+      <c r="N178" t="n">
         <v>5.6</v>
       </c>
-      <c r="M178" s="1" t="n">
+      <c r="O178" s="1" t="n">
         <v>45932</v>
       </c>
-      <c r="N178" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O178" s="1" t="n">
-        <v>45927</v>
-      </c>
       <c r="P178" t="n">
-        <v>6.59</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="179">
@@ -8201,49 +8233,49 @@
         <v>309</v>
       </c>
       <c r="B179" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="C179" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D179" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E179" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D179" t="n">
+      <c r="F179" t="n">
         <v>5.2</v>
       </c>
-      <c r="E179" s="1" t="n">
+      <c r="G179" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F179" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G179" s="1" t="n">
+      <c r="H179" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I179" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H179" t="n">
+      <c r="J179" t="n">
         <v>6.3</v>
       </c>
-      <c r="I179" s="1" t="n">
+      <c r="K179" s="1" t="n">
         <v>46005</v>
-      </c>
-      <c r="J179" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K179" s="1" t="n">
-        <v>45990</v>
       </c>
       <c r="L179" t="n">
         <v>6.4</v>
       </c>
       <c r="M179" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="N179" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O179" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="N179" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O179" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P179" t="n">
-        <v>6.37</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="180">
@@ -8251,49 +8283,49 @@
         <v>310</v>
       </c>
       <c r="B180" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C180" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D180" t="n">
         <v>6.9</v>
       </c>
-      <c r="C180" s="1" t="n">
+      <c r="E180" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D180" t="n">
+      <c r="F180" t="n">
         <v>7.1</v>
       </c>
-      <c r="E180" s="1" t="n">
+      <c r="G180" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F180" t="n">
+      <c r="H180" t="n">
         <v>7.7</v>
       </c>
-      <c r="G180" s="1" t="n">
+      <c r="I180" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H180" t="n">
+      <c r="J180" t="n">
         <v>6.4</v>
       </c>
-      <c r="I180" s="1" t="n">
+      <c r="K180" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J180" t="n">
+      <c r="L180" t="n">
         <v>6.2</v>
       </c>
-      <c r="K180" s="1" t="n">
+      <c r="M180" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L180" t="n">
+      <c r="N180" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="M180" s="1" t="n">
+      <c r="O180" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="N180" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O180" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P180" t="n">
-        <v>7.03</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="181">
@@ -8304,46 +8336,46 @@
         <v>6.8</v>
       </c>
       <c r="C181" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D181" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E181" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D181" t="n">
+      <c r="F181" t="n">
         <v>7.4</v>
       </c>
-      <c r="E181" s="1" t="n">
+      <c r="G181" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="F181" t="n">
+      <c r="H181" t="n">
         <v>7</v>
       </c>
-      <c r="G181" s="1" t="n">
+      <c r="I181" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H181" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I181" s="1" t="n">
+      <c r="J181" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K181" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J181" t="n">
+      <c r="L181" t="n">
         <v>6.9</v>
       </c>
-      <c r="K181" s="1" t="n">
+      <c r="M181" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L181" t="n">
+      <c r="N181" t="n">
         <v>7.1</v>
       </c>
-      <c r="M181" s="1" t="n">
+      <c r="O181" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="N181" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O181" s="1" t="n">
-        <v>45968</v>
-      </c>
       <c r="P181" t="n">
-        <v>6.9</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="182">
@@ -8351,49 +8383,49 @@
         <v>312</v>
       </c>
       <c r="B182" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="C182" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D182" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E182" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D182" t="n">
+      <c r="F182" t="n">
         <v>7.2</v>
       </c>
-      <c r="E182" s="1" t="n">
+      <c r="G182" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F182" t="n">
+      <c r="H182" t="n">
         <v>6.3</v>
       </c>
-      <c r="G182" s="1" t="n">
+      <c r="I182" s="1" t="n">
         <v>46061</v>
-      </c>
-      <c r="H182" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I182" s="1" t="n">
-        <v>46053</v>
       </c>
       <c r="J182" t="n">
         <v>7.1</v>
       </c>
       <c r="K182" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="L182" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M182" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="L182" t="n">
+      <c r="N182" t="n">
         <v>7.7</v>
       </c>
-      <c r="M182" s="1" t="n">
+      <c r="O182" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="N182" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O182" s="1" t="n">
-        <v>46033</v>
-      </c>
       <c r="P182" t="n">
-        <v>6.91</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="183">
@@ -8471,49 +8503,49 @@
         <v>315</v>
       </c>
       <c r="B185" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C185" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D185" t="n">
         <v>6.9</v>
       </c>
-      <c r="C185" s="1" t="n">
+      <c r="E185" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D185" t="n">
+      <c r="F185" t="n">
         <v>7.4</v>
       </c>
-      <c r="E185" s="1" t="n">
+      <c r="G185" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F185" t="n">
+      <c r="H185" t="n">
         <v>8.1</v>
       </c>
-      <c r="G185" s="1" t="n">
+      <c r="I185" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H185" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I185" s="1" t="n">
+      <c r="J185" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K185" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J185" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K185" s="1" t="n">
+      <c r="L185" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M185" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="L185" t="n">
+      <c r="N185" t="n">
         <v>6.8</v>
       </c>
-      <c r="M185" s="1" t="n">
+      <c r="O185" s="1" t="n">
         <v>46043</v>
       </c>
-      <c r="N185" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O185" s="1" t="n">
-        <v>46039</v>
-      </c>
       <c r="P185" t="n">
-        <v>7.01</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="186">
@@ -8521,13 +8553,17 @@
         <v>316</v>
       </c>
       <c r="B186" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C186" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D186" t="n">
         <v>7.6</v>
       </c>
-      <c r="C186" s="1" t="n">
+      <c r="E186" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
@@ -8539,7 +8575,7 @@
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="n">
-        <v>7.6</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="187">
@@ -8547,49 +8583,49 @@
         <v>317</v>
       </c>
       <c r="B187" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D187" t="n">
         <v>6.9</v>
       </c>
-      <c r="C187" s="1" t="n">
+      <c r="E187" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D187" t="n">
+      <c r="F187" t="n">
         <v>6.1</v>
       </c>
-      <c r="E187" s="1" t="n">
+      <c r="G187" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F187" t="n">
+      <c r="H187" t="n">
         <v>6.4</v>
       </c>
-      <c r="G187" s="1" t="n">
+      <c r="I187" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="H187" t="n">
+      <c r="J187" t="n">
         <v>6.1</v>
       </c>
-      <c r="I187" s="1" t="n">
+      <c r="K187" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="J187" t="n">
+      <c r="L187" t="n">
         <v>6.3</v>
       </c>
-      <c r="K187" s="1" t="n">
+      <c r="M187" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="L187" t="n">
+      <c r="N187" t="n">
         <v>7.1</v>
       </c>
-      <c r="M187" s="1" t="n">
+      <c r="O187" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="N187" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O187" s="1" t="n">
-        <v>45998</v>
-      </c>
       <c r="P187" t="n">
-        <v>6.47</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="188">
@@ -8597,49 +8633,49 @@
         <v>318</v>
       </c>
       <c r="B188" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="C188" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D188" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E188" s="1" t="n">
         <v>46076</v>
       </c>
-      <c r="D188" t="n">
+      <c r="F188" t="n">
         <v>7.5</v>
       </c>
-      <c r="E188" s="1" t="n">
+      <c r="G188" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="F188" t="n">
+      <c r="H188" t="n">
         <v>7</v>
       </c>
-      <c r="G188" s="1" t="n">
+      <c r="I188" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H188" t="n">
+      <c r="J188" t="n">
         <v>6.8</v>
       </c>
-      <c r="I188" s="1" t="n">
+      <c r="K188" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J188" t="n">
+      <c r="L188" t="n">
         <v>6.4</v>
       </c>
-      <c r="K188" s="1" t="n">
+      <c r="M188" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L188" t="n">
+      <c r="N188" t="n">
         <v>7.1</v>
       </c>
-      <c r="M188" s="1" t="n">
+      <c r="O188" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N188" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O188" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P188" t="n">
-        <v>6.91</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="189">
@@ -8647,25 +8683,29 @@
         <v>319</v>
       </c>
       <c r="B189" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D189" t="n">
         <v>7.3</v>
       </c>
-      <c r="C189" s="1" t="n">
+      <c r="E189" s="1" t="n">
         <v>46076</v>
       </c>
-      <c r="D189" t="n">
+      <c r="F189" t="n">
         <v>6.9</v>
       </c>
-      <c r="E189" s="1" t="n">
+      <c r="G189" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F189" t="n">
+      <c r="H189" t="n">
         <v>7.3</v>
       </c>
-      <c r="G189" s="1" t="n">
+      <c r="I189" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
@@ -8673,7 +8713,7 @@
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="n">
-        <v>7.17</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="190">
@@ -9063,49 +9103,49 @@
         <v>330</v>
       </c>
       <c r="B199" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D199" t="n">
         <v>7.4</v>
       </c>
-      <c r="C199" s="1" t="n">
+      <c r="E199" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D199" t="n">
+      <c r="F199" t="n">
         <v>7.9</v>
       </c>
-      <c r="E199" s="1" t="n">
+      <c r="G199" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F199" t="n">
+      <c r="H199" t="n">
         <v>7</v>
       </c>
-      <c r="G199" s="1" t="n">
+      <c r="I199" s="1" t="n">
         <v>46058</v>
       </c>
-      <c r="H199" t="n">
+      <c r="J199" t="n">
         <v>6.9</v>
       </c>
-      <c r="I199" s="1" t="n">
+      <c r="K199" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J199" t="n">
+      <c r="L199" t="n">
         <v>6.4</v>
       </c>
-      <c r="K199" s="1" t="n">
+      <c r="M199" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="L199" t="n">
+      <c r="N199" t="n">
         <v>6.8</v>
       </c>
-      <c r="M199" s="1" t="n">
+      <c r="O199" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="N199" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O199" s="1" t="n">
-        <v>45984</v>
-      </c>
       <c r="P199" t="n">
-        <v>7.01</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200">
@@ -9163,49 +9203,49 @@
         <v>335</v>
       </c>
       <c r="B201" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D201" t="n">
         <v>6.4</v>
       </c>
-      <c r="C201" s="1" t="n">
+      <c r="E201" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="D201" t="n">
+      <c r="F201" t="n">
         <v>6.3</v>
       </c>
-      <c r="E201" s="1" t="n">
+      <c r="G201" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="F201" t="n">
+      <c r="H201" t="n">
         <v>6.8</v>
       </c>
-      <c r="G201" s="1" t="n">
+      <c r="I201" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="H201" t="n">
+      <c r="J201" t="n">
         <v>7.1</v>
       </c>
-      <c r="I201" s="1" t="n">
+      <c r="K201" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="J201" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K201" s="1" t="n">
+      <c r="L201" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M201" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="L201" t="n">
+      <c r="N201" t="n">
         <v>6.3</v>
       </c>
-      <c r="M201" s="1" t="n">
+      <c r="O201" s="1" t="n">
         <v>45921</v>
       </c>
-      <c r="N201" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O201" s="1" t="n">
-        <v>45913</v>
-      </c>
       <c r="P201" t="n">
-        <v>6.59</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="202">
@@ -9263,49 +9303,49 @@
         <v>337</v>
       </c>
       <c r="B203" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C203" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D203" t="n">
         <v>6.8</v>
       </c>
-      <c r="C203" s="1" t="n">
+      <c r="E203" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D203" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E203" s="1" t="n">
+      <c r="F203" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G203" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F203" t="n">
+      <c r="H203" t="n">
         <v>7.5</v>
       </c>
-      <c r="G203" s="1" t="n">
+      <c r="I203" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H203" t="n">
+      <c r="J203" t="n">
         <v>6.9</v>
       </c>
-      <c r="I203" s="1" t="n">
+      <c r="K203" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="J203" t="n">
+      <c r="L203" t="n">
         <v>7.1</v>
       </c>
-      <c r="K203" s="1" t="n">
+      <c r="M203" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="L203" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M203" s="1" t="n">
+      <c r="N203" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O203" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="N203" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O203" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P203" t="n">
-        <v>6.93</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="204">
@@ -9381,49 +9421,49 @@
         <v>340</v>
       </c>
       <c r="B206" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C206" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D206" t="n">
         <v>7</v>
       </c>
-      <c r="C206" s="1" t="n">
+      <c r="E206" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="D206" t="n">
+      <c r="F206" t="n">
         <v>7.7</v>
       </c>
-      <c r="E206" s="1" t="n">
+      <c r="G206" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="F206" t="n">
+      <c r="H206" t="n">
         <v>7.1</v>
       </c>
-      <c r="G206" s="1" t="n">
+      <c r="I206" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="H206" t="n">
+      <c r="J206" t="n">
         <v>7.3</v>
       </c>
-      <c r="I206" s="1" t="n">
+      <c r="K206" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="J206" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K206" s="1" t="n">
+      <c r="L206" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M206" s="1" t="n">
         <v>46036</v>
       </c>
-      <c r="L206" t="n">
+      <c r="N206" t="n">
         <v>6.8</v>
       </c>
-      <c r="M206" s="1" t="n">
+      <c r="O206" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="N206" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O206" s="1" t="n">
-        <v>46005</v>
-      </c>
       <c r="P206" t="n">
-        <v>7.13</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="207">
@@ -9481,49 +9521,49 @@
         <v>342</v>
       </c>
       <c r="B208" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C208" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D208" t="n">
         <v>7.1</v>
       </c>
-      <c r="C208" s="1" t="n">
+      <c r="E208" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="D208" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E208" s="1" t="n">
+      <c r="F208" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G208" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="F208" t="n">
+      <c r="H208" t="n">
         <v>7</v>
       </c>
-      <c r="G208" s="1" t="n">
+      <c r="I208" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="H208" t="n">
+      <c r="J208" t="n">
         <v>7.1</v>
       </c>
-      <c r="I208" s="1" t="n">
+      <c r="K208" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="J208" t="n">
+      <c r="L208" t="n">
         <v>6.9</v>
       </c>
-      <c r="K208" s="1" t="n">
+      <c r="M208" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="L208" t="n">
+      <c r="N208" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="M208" s="1" t="n">
+      <c r="O208" s="1" t="n">
         <v>45949</v>
       </c>
-      <c r="N208" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O208" s="1" t="n">
-        <v>45934</v>
-      </c>
       <c r="P208" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="209">
@@ -10001,49 +10041,49 @@
         <v>353</v>
       </c>
       <c r="B219" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C219" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D219" t="n">
         <v>7.9</v>
       </c>
-      <c r="C219" s="1" t="n">
+      <c r="E219" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D219" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E219" s="1" t="n">
+      <c r="F219" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G219" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F219" t="n">
+      <c r="H219" t="n">
         <v>6.8</v>
       </c>
-      <c r="G219" s="1" t="n">
+      <c r="I219" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="H219" t="n">
+      <c r="J219" t="n">
         <v>8.1</v>
       </c>
-      <c r="I219" s="1" t="n">
+      <c r="K219" s="1" t="n">
         <v>46058</v>
       </c>
-      <c r="J219" t="n">
+      <c r="L219" t="n">
         <v>6.1</v>
       </c>
-      <c r="K219" s="1" t="n">
+      <c r="M219" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="L219" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M219" s="1" t="n">
+      <c r="N219" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O219" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="N219" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O219" s="1" t="n">
-        <v>46041</v>
-      </c>
       <c r="P219" t="n">
-        <v>6.97</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="220">
@@ -10077,37 +10117,41 @@
         <v>356</v>
       </c>
       <c r="B221" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D221" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="C221" s="1" t="n">
+      <c r="E221" s="1" t="n">
         <v>46072</v>
       </c>
-      <c r="D221" t="n">
+      <c r="F221" t="n">
         <v>6.9</v>
       </c>
-      <c r="E221" s="1" t="n">
+      <c r="G221" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="F221" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G221" s="1" t="n">
+      <c r="H221" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I221" s="1" t="n">
         <v>45920</v>
       </c>
-      <c r="H221" t="n">
+      <c r="J221" t="n">
         <v>7.1</v>
       </c>
-      <c r="I221" s="1" t="n">
+      <c r="K221" s="1" t="n">
         <v>45911</v>
       </c>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="n">
-        <v>7.22</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="222">
@@ -10115,49 +10159,49 @@
         <v>357</v>
       </c>
       <c r="B222" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C222" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D222" t="n">
         <v>7.1</v>
       </c>
-      <c r="C222" s="1" t="n">
+      <c r="E222" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D222" t="n">
+      <c r="F222" t="n">
         <v>6.4</v>
       </c>
-      <c r="E222" s="1" t="n">
+      <c r="G222" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F222" t="n">
+      <c r="H222" t="n">
         <v>7</v>
       </c>
-      <c r="G222" s="1" t="n">
+      <c r="I222" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H222" t="n">
+      <c r="J222" t="n">
         <v>7.4</v>
       </c>
-      <c r="I222" s="1" t="n">
+      <c r="K222" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J222" t="n">
+      <c r="L222" t="n">
         <v>6.9</v>
       </c>
-      <c r="K222" s="1" t="n">
+      <c r="M222" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="L222" t="n">
+      <c r="N222" t="n">
         <v>7.8</v>
       </c>
-      <c r="M222" s="1" t="n">
+      <c r="O222" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="N222" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O222" s="1" t="n">
-        <v>45998</v>
-      </c>
       <c r="P222" t="n">
-        <v>6.97</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="223">
@@ -10335,25 +10379,29 @@
         <v>365</v>
       </c>
       <c r="B227" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="C227" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D227" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E227" s="1" t="n">
         <v>45884</v>
       </c>
-      <c r="D227" t="n">
+      <c r="F227" t="n">
         <v>7</v>
       </c>
-      <c r="E227" s="1" t="n">
+      <c r="G227" s="1" t="n">
         <v>45879</v>
       </c>
-      <c r="F227" t="n">
+      <c r="H227" t="n">
         <v>7.1</v>
       </c>
-      <c r="G227" s="1" t="n">
+      <c r="I227" s="1" t="n">
         <v>45873</v>
       </c>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
@@ -10361,7 +10409,7 @@
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="n">
-        <v>6.9</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="228">
@@ -10469,49 +10517,49 @@
         <v>369</v>
       </c>
       <c r="B230" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C230" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D230" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E230" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D230" t="n">
+      <c r="F230" t="n">
         <v>6.9</v>
       </c>
-      <c r="E230" s="1" t="n">
+      <c r="G230" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F230" t="n">
+      <c r="H230" t="n">
         <v>6.8</v>
       </c>
-      <c r="G230" s="1" t="n">
+      <c r="I230" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="H230" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I230" s="1" t="n">
+      <c r="J230" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K230" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="J230" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K230" s="1" t="n">
+      <c r="L230" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M230" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L230" t="n">
+      <c r="N230" t="n">
         <v>6.2</v>
       </c>
-      <c r="M230" s="1" t="n">
+      <c r="O230" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="N230" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O230" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P230" t="n">
-        <v>6.77</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="231">
@@ -10519,49 +10567,49 @@
         <v>370</v>
       </c>
       <c r="B231" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C231" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D231" t="n">
         <v>5.8</v>
       </c>
-      <c r="C231" s="1" t="n">
+      <c r="E231" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D231" t="n">
+      <c r="F231" t="n">
         <v>7.6</v>
       </c>
-      <c r="E231" s="1" t="n">
+      <c r="G231" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F231" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G231" s="1" t="n">
+      <c r="H231" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I231" s="1" t="n">
         <v>46060</v>
-      </c>
-      <c r="H231" t="n">
-        <v>6</v>
-      </c>
-      <c r="I231" s="1" t="n">
-        <v>46054</v>
       </c>
       <c r="J231" t="n">
         <v>6</v>
       </c>
       <c r="K231" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="L231" t="n">
+        <v>6</v>
+      </c>
+      <c r="M231" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="L231" t="n">
+      <c r="N231" t="n">
         <v>7.8</v>
       </c>
-      <c r="M231" s="1" t="n">
+      <c r="O231" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N231" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O231" s="1" t="n">
-        <v>45927</v>
-      </c>
       <c r="P231" t="n">
-        <v>6.7</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="232">
@@ -10569,49 +10617,49 @@
         <v>371</v>
       </c>
       <c r="B232" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="C232" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D232" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E232" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="D232" t="n">
+      <c r="F232" t="n">
         <v>6.4</v>
       </c>
-      <c r="E232" s="1" t="n">
+      <c r="G232" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="F232" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G232" s="1" t="n">
+      <c r="H232" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I232" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="H232" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I232" s="1" t="n">
+      <c r="J232" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K232" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="J232" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K232" s="1" t="n">
+      <c r="L232" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M232" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="L232" t="n">
+      <c r="N232" t="n">
         <v>6.3</v>
       </c>
-      <c r="M232" s="1" t="n">
+      <c r="O232" s="1" t="n">
         <v>45935</v>
       </c>
-      <c r="N232" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O232" s="1" t="n">
-        <v>45928</v>
-      </c>
       <c r="P232" t="n">
-        <v>6.49</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="233">
@@ -10792,46 +10840,46 @@
         <v>6.5</v>
       </c>
       <c r="C237" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D237" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E237" s="1" t="n">
         <v>46076</v>
       </c>
-      <c r="D237" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E237" s="1" t="n">
+      <c r="F237" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G237" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="F237" t="n">
+      <c r="H237" t="n">
         <v>7.8</v>
       </c>
-      <c r="G237" s="1" t="n">
+      <c r="I237" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H237" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I237" s="1" t="n">
+      <c r="J237" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K237" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J237" t="n">
+      <c r="L237" t="n">
         <v>6.3</v>
       </c>
-      <c r="K237" s="1" t="n">
+      <c r="M237" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="L237" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M237" s="1" t="n">
+      <c r="N237" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O237" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="N237" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O237" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P237" t="n">
-        <v>6.89</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="238">
@@ -11409,45 +11457,49 @@
         <v>395</v>
       </c>
       <c r="B254" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C254" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D254" t="n">
         <v>7.6</v>
       </c>
-      <c r="C254" s="1" t="n">
+      <c r="E254" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D254" t="n">
+      <c r="F254" t="n">
         <v>6.4</v>
       </c>
-      <c r="E254" s="1" t="n">
+      <c r="G254" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F254" t="n">
+      <c r="H254" t="n">
         <v>6.8</v>
       </c>
-      <c r="G254" s="1" t="n">
+      <c r="I254" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="H254" t="n">
+      <c r="J254" t="n">
         <v>6.2</v>
       </c>
-      <c r="I254" s="1" t="n">
+      <c r="K254" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J254" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K254" s="1" t="n">
+      <c r="L254" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M254" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="L254" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M254" s="1" t="n">
+      <c r="N254" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O254" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="N254" t="inlineStr"/>
-      <c r="O254" t="inlineStr"/>
       <c r="P254" t="n">
-        <v>6.72</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="255">
@@ -11961,49 +12013,49 @@
         <v>409</v>
       </c>
       <c r="B268" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="C268" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D268" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E268" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D268" t="n">
+      <c r="F268" t="n">
         <v>6.9</v>
       </c>
-      <c r="E268" s="1" t="n">
+      <c r="G268" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F268" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G268" s="1" t="n">
+      <c r="H268" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I268" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H268" t="n">
+      <c r="J268" t="n">
         <v>6.2</v>
       </c>
-      <c r="I268" s="1" t="n">
+      <c r="K268" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J268" t="n">
+      <c r="L268" t="n">
         <v>8.6</v>
       </c>
-      <c r="K268" s="1" t="n">
+      <c r="M268" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="L268" t="n">
+      <c r="N268" t="n">
         <v>7</v>
       </c>
-      <c r="M268" s="1" t="n">
+      <c r="O268" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="N268" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O268" s="1" t="n">
-        <v>46005</v>
-      </c>
       <c r="P268" t="n">
-        <v>6.91</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="269">
@@ -12307,46 +12359,46 @@
         <v>416</v>
       </c>
       <c r="B275" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C275" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D275" t="n">
         <v>7.6</v>
       </c>
-      <c r="C275" s="1" t="n">
+      <c r="E275" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D275" t="n">
+      <c r="F275" t="n">
         <v>6.3</v>
       </c>
-      <c r="E275" s="1" t="n">
+      <c r="G275" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F275" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G275" s="1" t="n">
+      <c r="H275" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I275" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H275" t="n">
+      <c r="J275" t="n">
         <v>8</v>
       </c>
-      <c r="I275" s="1" t="n">
+      <c r="K275" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J275" t="n">
+      <c r="L275" t="n">
         <v>5.7</v>
       </c>
-      <c r="K275" s="1" t="n">
+      <c r="M275" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L275" t="n">
+      <c r="N275" t="n">
         <v>9</v>
       </c>
-      <c r="M275" s="1" t="n">
+      <c r="O275" s="1" t="n">
         <v>45984</v>
-      </c>
-      <c r="N275" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O275" s="1" t="n">
-        <v>45970</v>
       </c>
       <c r="P275" t="n">
         <v>7.07</v>
@@ -12407,49 +12459,49 @@
         <v>418</v>
       </c>
       <c r="B277" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C277" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D277" t="n">
         <v>6.8</v>
       </c>
-      <c r="C277" s="1" t="n">
+      <c r="E277" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D277" t="n">
+      <c r="F277" t="n">
         <v>8.6</v>
       </c>
-      <c r="E277" s="1" t="n">
+      <c r="G277" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F277" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G277" s="1" t="n">
+      <c r="H277" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I277" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H277" t="n">
+      <c r="J277" t="n">
         <v>8.1</v>
       </c>
-      <c r="I277" s="1" t="n">
+      <c r="K277" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="J277" t="n">
+      <c r="L277" t="n">
         <v>7.3</v>
       </c>
-      <c r="K277" s="1" t="n">
+      <c r="M277" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="L277" t="n">
+      <c r="N277" t="n">
         <v>7.7</v>
       </c>
-      <c r="M277" s="1" t="n">
+      <c r="O277" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="N277" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O277" s="1" t="n">
-        <v>46004</v>
-      </c>
       <c r="P277" t="n">
-        <v>7.63</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="278">
@@ -12827,49 +12879,49 @@
         <v>428</v>
       </c>
       <c r="B287" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="C287" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D287" t="n">
         <v>6.2</v>
       </c>
-      <c r="C287" s="1" t="n">
+      <c r="E287" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D287" t="n">
+      <c r="F287" t="n">
         <v>8.5</v>
       </c>
-      <c r="E287" s="1" t="n">
+      <c r="G287" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F287" t="n">
+      <c r="H287" t="n">
         <v>7.1</v>
       </c>
-      <c r="G287" s="1" t="n">
+      <c r="I287" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H287" t="n">
+      <c r="J287" t="n">
         <v>7.4</v>
       </c>
-      <c r="I287" s="1" t="n">
+      <c r="K287" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J287" t="n">
+      <c r="L287" t="n">
         <v>6.1</v>
       </c>
-      <c r="K287" s="1" t="n">
+      <c r="M287" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L287" t="n">
+      <c r="N287" t="n">
         <v>8.1</v>
       </c>
-      <c r="M287" s="1" t="n">
+      <c r="O287" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="N287" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O287" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P287" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="288">
@@ -13249,49 +13301,49 @@
         <v>439</v>
       </c>
       <c r="B296" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C296" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D296" t="n">
         <v>8.5</v>
       </c>
-      <c r="C296" s="1" t="n">
+      <c r="E296" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D296" t="n">
+      <c r="F296" t="n">
         <v>7.4</v>
       </c>
-      <c r="E296" s="1" t="n">
+      <c r="G296" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F296" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G296" s="1" t="n">
+      <c r="H296" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I296" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H296" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I296" s="1" t="n">
+      <c r="J296" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K296" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="J296" t="n">
+      <c r="L296" t="n">
         <v>7.1</v>
       </c>
-      <c r="K296" s="1" t="n">
+      <c r="M296" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="L296" t="n">
+      <c r="N296" t="n">
         <v>7.4</v>
       </c>
-      <c r="M296" s="1" t="n">
+      <c r="O296" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="N296" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O296" s="1" t="n">
-        <v>45984</v>
-      </c>
       <c r="P296" t="n">
-        <v>7.21</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="297">
@@ -13697,49 +13749,49 @@
         <v>452</v>
       </c>
       <c r="B307" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C307" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D307" t="n">
         <v>5.3</v>
       </c>
-      <c r="C307" s="1" t="n">
+      <c r="E307" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D307" t="n">
+      <c r="F307" t="n">
         <v>7.3</v>
       </c>
-      <c r="E307" s="1" t="n">
+      <c r="G307" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F307" t="n">
+      <c r="H307" t="n">
         <v>6.1</v>
       </c>
-      <c r="G307" s="1" t="n">
+      <c r="I307" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H307" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I307" s="1" t="n">
+      <c r="J307" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K307" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="J307" t="n">
+      <c r="L307" t="n">
         <v>7.5</v>
       </c>
-      <c r="K307" s="1" t="n">
+      <c r="M307" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="L307" t="n">
+      <c r="N307" t="n">
         <v>7</v>
       </c>
-      <c r="M307" s="1" t="n">
+      <c r="O307" s="1" t="n">
         <v>45949</v>
       </c>
-      <c r="N307" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O307" s="1" t="n">
-        <v>45935</v>
-      </c>
       <c r="P307" t="n">
-        <v>6.61</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="308">
@@ -13747,49 +13799,49 @@
         <v>453</v>
       </c>
       <c r="B308" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C308" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D308" t="n">
         <v>6.4</v>
       </c>
-      <c r="C308" s="1" t="n">
+      <c r="E308" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D308" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E308" s="1" t="n">
+      <c r="F308" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G308" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F308" t="n">
+      <c r="H308" t="n">
         <v>7</v>
       </c>
-      <c r="G308" s="1" t="n">
+      <c r="I308" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H308" t="n">
+      <c r="J308" t="n">
         <v>6.4</v>
       </c>
-      <c r="I308" s="1" t="n">
+      <c r="K308" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J308" t="n">
+      <c r="L308" t="n">
         <v>6.9</v>
       </c>
-      <c r="K308" s="1" t="n">
+      <c r="M308" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L308" t="n">
+      <c r="N308" t="n">
         <v>7.1</v>
       </c>
-      <c r="M308" s="1" t="n">
+      <c r="O308" s="1" t="n">
         <v>45985</v>
       </c>
-      <c r="N308" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O308" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P308" t="n">
-        <v>6.7</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="309">
@@ -13997,49 +14049,49 @@
         <v>459</v>
       </c>
       <c r="B313" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C313" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D313" t="n">
         <v>7.3</v>
       </c>
-      <c r="C313" s="1" t="n">
+      <c r="E313" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="D313" t="n">
+      <c r="F313" t="n">
         <v>6.8</v>
       </c>
-      <c r="E313" s="1" t="n">
+      <c r="G313" s="1" t="n">
         <v>45994</v>
       </c>
-      <c r="F313" t="n">
+      <c r="H313" t="n">
         <v>7.1</v>
       </c>
-      <c r="G313" s="1" t="n">
+      <c r="I313" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="H313" t="n">
+      <c r="J313" t="n">
         <v>6.4</v>
       </c>
-      <c r="I313" s="1" t="n">
+      <c r="K313" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="J313" t="n">
+      <c r="L313" t="n">
         <v>6</v>
       </c>
-      <c r="K313" s="1" t="n">
+      <c r="M313" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="L313" t="n">
+      <c r="N313" t="n">
         <v>6.9</v>
       </c>
-      <c r="M313" s="1" t="n">
+      <c r="O313" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="N313" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O313" s="1" t="n">
-        <v>45959</v>
-      </c>
       <c r="P313" t="n">
-        <v>6.69</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="314">
@@ -14368,46 +14420,46 @@
         <v>7</v>
       </c>
       <c r="C321" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D321" t="n">
+        <v>7</v>
+      </c>
+      <c r="E321" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D321" t="n">
+      <c r="F321" t="n">
         <v>8.5</v>
       </c>
-      <c r="E321" s="1" t="n">
+      <c r="G321" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F321" t="n">
+      <c r="H321" t="n">
         <v>7.7</v>
       </c>
-      <c r="G321" s="1" t="n">
+      <c r="I321" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H321" t="n">
+      <c r="J321" t="n">
         <v>7.3</v>
       </c>
-      <c r="I321" s="1" t="n">
+      <c r="K321" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="J321" t="n">
+      <c r="L321" t="n">
         <v>7.1</v>
       </c>
-      <c r="K321" s="1" t="n">
+      <c r="M321" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="L321" t="n">
+      <c r="N321" t="n">
         <v>8</v>
       </c>
-      <c r="M321" s="1" t="n">
+      <c r="O321" s="1" t="n">
         <v>45993</v>
       </c>
-      <c r="N321" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O321" s="1" t="n">
-        <v>45990</v>
-      </c>
       <c r="P321" t="n">
-        <v>7.59</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="322">
@@ -14565,49 +14617,49 @@
         <v>471</v>
       </c>
       <c r="B325" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C325" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D325" t="n">
         <v>5.7</v>
       </c>
-      <c r="C325" s="1" t="n">
+      <c r="E325" s="1" t="n">
         <v>46074</v>
-      </c>
-      <c r="D325" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E325" s="1" t="n">
-        <v>46067</v>
       </c>
       <c r="F325" t="n">
         <v>6.8</v>
       </c>
       <c r="G325" s="1" t="n">
+        <v>46067</v>
+      </c>
+      <c r="H325" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I325" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H325" t="n">
+      <c r="J325" t="n">
         <v>7</v>
       </c>
-      <c r="I325" s="1" t="n">
+      <c r="K325" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="J325" t="n">
+      <c r="L325" t="n">
         <v>6</v>
       </c>
-      <c r="K325" s="1" t="n">
+      <c r="M325" s="1" t="n">
         <v>45995</v>
       </c>
-      <c r="L325" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M325" s="1" t="n">
+      <c r="N325" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O325" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="N325" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O325" s="1" t="n">
-        <v>45985</v>
-      </c>
       <c r="P325" t="n">
-        <v>6.41</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="326">
@@ -14986,16 +15038,20 @@
         <v>6.3</v>
       </c>
       <c r="C337" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D337" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E337" s="1" t="n">
         <v>46076</v>
       </c>
-      <c r="D337" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E337" s="1" t="n">
+      <c r="F337" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G337" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F337" t="inlineStr"/>
-      <c r="G337" t="inlineStr"/>
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr"/>
@@ -15005,7 +15061,7 @@
       <c r="N337" t="inlineStr"/>
       <c r="O337" t="inlineStr"/>
       <c r="P337" t="n">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="338">
@@ -15016,46 +15072,46 @@
         <v>6.8</v>
       </c>
       <c r="C338" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D338" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E338" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="D338" t="n">
+      <c r="F338" t="n">
         <v>7.2</v>
       </c>
-      <c r="E338" s="1" t="n">
+      <c r="G338" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="F338" t="n">
+      <c r="H338" t="n">
         <v>6.8</v>
       </c>
-      <c r="G338" s="1" t="n">
+      <c r="I338" s="1" t="n">
         <v>45971</v>
       </c>
-      <c r="H338" t="n">
+      <c r="J338" t="n">
         <v>7.2</v>
       </c>
-      <c r="I338" s="1" t="n">
+      <c r="K338" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="J338" t="n">
+      <c r="L338" t="n">
         <v>7.1</v>
       </c>
-      <c r="K338" s="1" t="n">
+      <c r="M338" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="L338" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M338" s="1" t="n">
+      <c r="N338" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O338" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="N338" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O338" s="1" t="n">
-        <v>45934</v>
-      </c>
       <c r="P338" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="339">
@@ -15063,49 +15119,49 @@
         <v>485</v>
       </c>
       <c r="B339" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="C339" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D339" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E339" s="1" t="n">
         <v>46074</v>
-      </c>
-      <c r="D339" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E339" s="1" t="n">
-        <v>46068</v>
       </c>
       <c r="F339" t="n">
         <v>7.9</v>
       </c>
       <c r="G339" s="1" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H339" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I339" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="H339" t="n">
+      <c r="J339" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I339" s="1" t="n">
+      <c r="K339" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="J339" t="n">
+      <c r="L339" t="n">
         <v>7.9</v>
       </c>
-      <c r="K339" s="1" t="n">
+      <c r="M339" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L339" t="n">
+      <c r="N339" t="n">
         <v>6.8</v>
       </c>
-      <c r="M339" s="1" t="n">
+      <c r="O339" s="1" t="n">
         <v>45985</v>
       </c>
-      <c r="N339" t="n">
-        <v>7</v>
-      </c>
-      <c r="O339" s="1" t="n">
-        <v>45957</v>
-      </c>
       <c r="P339" t="n">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="340">
@@ -15113,49 +15169,49 @@
         <v>486</v>
       </c>
       <c r="B340" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C340" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D340" t="n">
         <v>7.4</v>
       </c>
-      <c r="C340" s="1" t="n">
+      <c r="E340" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D340" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E340" s="1" t="n">
+      <c r="F340" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G340" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="F340" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G340" s="1" t="n">
+      <c r="H340" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I340" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="H340" t="n">
+      <c r="J340" t="n">
         <v>6.2</v>
       </c>
-      <c r="I340" s="1" t="n">
+      <c r="K340" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="J340" t="n">
+      <c r="L340" t="n">
         <v>6.1</v>
       </c>
-      <c r="K340" s="1" t="n">
+      <c r="M340" s="1" t="n">
         <v>45949</v>
       </c>
-      <c r="L340" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M340" s="1" t="n">
+      <c r="N340" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O340" s="1" t="n">
         <v>45928</v>
       </c>
-      <c r="N340" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O340" s="1" t="n">
-        <v>45921</v>
-      </c>
       <c r="P340" t="n">
-        <v>6.56</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="341">
@@ -15163,49 +15219,49 @@
         <v>487</v>
       </c>
       <c r="B341" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C341" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D341" t="n">
         <v>6.3</v>
       </c>
-      <c r="C341" s="1" t="n">
+      <c r="E341" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D341" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E341" s="1" t="n">
+      <c r="F341" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G341" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F341" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G341" s="1" t="n">
+      <c r="H341" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I341" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="H341" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I341" s="1" t="n">
+      <c r="J341" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K341" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="J341" t="n">
+      <c r="L341" t="n">
         <v>6.3</v>
       </c>
-      <c r="K341" s="1" t="n">
+      <c r="M341" s="1" t="n">
         <v>45935</v>
       </c>
-      <c r="L341" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M341" s="1" t="n">
+      <c r="N341" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O341" s="1" t="n">
         <v>45928</v>
       </c>
-      <c r="N341" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O341" s="1" t="n">
-        <v>45921</v>
-      </c>
       <c r="P341" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="342">
@@ -15409,49 +15465,49 @@
         <v>492</v>
       </c>
       <c r="B346" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C346" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D346" t="n">
         <v>7.1</v>
       </c>
-      <c r="C346" s="1" t="n">
+      <c r="E346" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="D346" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E346" s="1" t="n">
+      <c r="F346" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G346" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="F346" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G346" s="1" t="n">
+      <c r="H346" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I346" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="H346" t="n">
+      <c r="J346" t="n">
         <v>7</v>
       </c>
-      <c r="I346" s="1" t="n">
+      <c r="K346" s="1" t="n">
         <v>45961</v>
       </c>
-      <c r="J346" t="n">
+      <c r="L346" t="n">
         <v>3.3</v>
       </c>
-      <c r="K346" s="1" t="n">
+      <c r="M346" s="1" t="n">
         <v>45933</v>
       </c>
-      <c r="L346" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M346" s="1" t="n">
+      <c r="N346" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O346" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="N346" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O346" s="1" t="n">
-        <v>45920</v>
-      </c>
       <c r="P346" t="n">
-        <v>6.36</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="347">
@@ -15509,49 +15565,49 @@
         <v>494</v>
       </c>
       <c r="B348" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="C348" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D348" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E348" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D348" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E348" s="1" t="n">
+      <c r="F348" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G348" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="F348" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G348" s="1" t="n">
+      <c r="H348" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I348" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="H348" t="n">
+      <c r="J348" t="n">
         <v>6.4</v>
       </c>
-      <c r="I348" s="1" t="n">
+      <c r="K348" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="J348" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K348" s="1" t="n">
+      <c r="L348" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M348" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="L348" t="n">
+      <c r="N348" t="n">
         <v>7.1</v>
       </c>
-      <c r="M348" s="1" t="n">
+      <c r="O348" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="N348" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O348" s="1" t="n">
-        <v>45920</v>
-      </c>
       <c r="P348" t="n">
-        <v>6.56</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="349">
@@ -15985,46 +16041,46 @@
         <v>507</v>
       </c>
       <c r="B360" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C360" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D360" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E360" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D360" t="n">
+      <c r="F360" t="n">
         <v>6.4</v>
       </c>
-      <c r="E360" s="1" t="n">
+      <c r="G360" s="1" t="n">
         <v>46055</v>
       </c>
-      <c r="F360" t="n">
+      <c r="H360" t="n">
         <v>5.7</v>
       </c>
-      <c r="G360" s="1" t="n">
+      <c r="I360" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="H360" t="n">
+      <c r="J360" t="n">
         <v>5.9</v>
       </c>
-      <c r="I360" s="1" t="n">
+      <c r="K360" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J360" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K360" s="1" t="n">
+      <c r="L360" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M360" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="L360" t="n">
+      <c r="N360" t="n">
         <v>6.4</v>
       </c>
-      <c r="M360" s="1" t="n">
+      <c r="O360" s="1" t="n">
         <v>45922</v>
-      </c>
-      <c r="N360" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O360" s="1" t="n">
-        <v>45913</v>
       </c>
       <c r="P360" t="n">
         <v>6.3</v>
@@ -16135,49 +16191,49 @@
         <v>510</v>
       </c>
       <c r="B363" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C363" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D363" t="n">
         <v>7.5</v>
       </c>
-      <c r="C363" s="1" t="n">
+      <c r="E363" s="1" t="n">
         <v>46074</v>
-      </c>
-      <c r="D363" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E363" s="1" t="n">
-        <v>46066</v>
       </c>
       <c r="F363" t="n">
         <v>6.4</v>
       </c>
       <c r="G363" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="H363" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I363" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H363" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I363" s="1" t="n">
+      <c r="J363" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K363" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="J363" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K363" s="1" t="n">
+      <c r="L363" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M363" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="L363" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M363" s="1" t="n">
+      <c r="N363" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O363" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="N363" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O363" s="1" t="n">
-        <v>45998</v>
-      </c>
       <c r="P363" t="n">
-        <v>6.61</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="364">
@@ -16289,49 +16345,49 @@
         <v>514</v>
       </c>
       <c r="B367" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="C367" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D367" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E367" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D367" t="n">
+      <c r="F367" t="n">
         <v>6.3</v>
       </c>
-      <c r="E367" s="1" t="n">
+      <c r="G367" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F367" t="n">
+      <c r="H367" t="n">
         <v>6.8</v>
       </c>
-      <c r="G367" s="1" t="n">
+      <c r="I367" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H367" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I367" s="1" t="n">
+      <c r="J367" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K367" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J367" t="n">
+      <c r="L367" t="n">
         <v>6.4</v>
       </c>
-      <c r="K367" s="1" t="n">
+      <c r="M367" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="L367" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M367" s="1" t="n">
+      <c r="N367" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O367" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="N367" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O367" s="1" t="n">
-        <v>45996</v>
-      </c>
       <c r="P367" t="n">
-        <v>6.66</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="368">
@@ -16467,49 +16523,49 @@
         <v>520</v>
       </c>
       <c r="B373" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C373" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D373" t="n">
         <v>5.6</v>
       </c>
-      <c r="C373" s="1" t="n">
+      <c r="E373" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="D373" t="n">
+      <c r="F373" t="n">
         <v>8</v>
       </c>
-      <c r="E373" s="1" t="n">
+      <c r="G373" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F373" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G373" s="1" t="n">
+      <c r="H373" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I373" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H373" t="n">
+      <c r="J373" t="n">
         <v>8</v>
       </c>
-      <c r="I373" s="1" t="n">
+      <c r="K373" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="J373" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K373" s="1" t="n">
+      <c r="L373" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M373" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="L373" t="n">
+      <c r="N373" t="n">
         <v>6.8</v>
       </c>
-      <c r="M373" s="1" t="n">
+      <c r="O373" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="N373" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O373" s="1" t="n">
-        <v>45989</v>
-      </c>
       <c r="P373" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="374">
@@ -17483,49 +17539,49 @@
         <v>543</v>
       </c>
       <c r="B395" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46073</v>
+        <v>46082</v>
       </c>
       <c r="D395" t="n">
         <v>7.1</v>
       </c>
       <c r="E395" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="F395" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G395" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F395" t="n">
+      <c r="H395" t="n">
         <v>6.9</v>
       </c>
-      <c r="G395" s="1" t="n">
+      <c r="I395" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H395" t="n">
+      <c r="J395" t="n">
         <v>7.2</v>
       </c>
-      <c r="I395" s="1" t="n">
+      <c r="K395" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="J395" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K395" s="1" t="n">
+      <c r="L395" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M395" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="L395" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M395" s="1" t="n">
+      <c r="N395" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O395" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="N395" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O395" s="1" t="n">
-        <v>45956</v>
-      </c>
       <c r="P395" t="n">
-        <v>6.89</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="396">
@@ -17533,49 +17589,49 @@
         <v>544</v>
       </c>
       <c r="B396" t="n">
+        <v>7</v>
+      </c>
+      <c r="C396" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D396" t="n">
         <v>6.4</v>
       </c>
-      <c r="C396" s="1" t="n">
+      <c r="E396" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D396" t="n">
+      <c r="F396" t="n">
         <v>6.8</v>
       </c>
-      <c r="E396" s="1" t="n">
+      <c r="G396" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F396" t="n">
+      <c r="H396" t="n">
         <v>8.4</v>
       </c>
-      <c r="G396" s="1" t="n">
+      <c r="I396" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H396" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I396" s="1" t="n">
+      <c r="J396" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K396" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J396" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K396" s="1" t="n">
+      <c r="L396" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M396" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L396" t="n">
+      <c r="N396" t="n">
         <v>7.3</v>
       </c>
-      <c r="M396" s="1" t="n">
+      <c r="O396" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="N396" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O396" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P396" t="n">
-        <v>6.93</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="397">
@@ -17633,45 +17689,49 @@
         <v>546</v>
       </c>
       <c r="B398" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C398" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D398" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E398" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="F398" t="n">
         <v>7.6</v>
       </c>
-      <c r="C398" s="1" t="n">
+      <c r="G398" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="D398" t="n">
+      <c r="H398" t="n">
         <v>7.2</v>
       </c>
-      <c r="E398" s="1" t="n">
+      <c r="I398" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="F398" t="n">
+      <c r="J398" t="n">
         <v>7</v>
       </c>
-      <c r="G398" s="1" t="n">
+      <c r="K398" s="1" t="n">
         <v>45920</v>
       </c>
-      <c r="H398" t="n">
+      <c r="L398" t="n">
         <v>7.3</v>
       </c>
-      <c r="I398" s="1" t="n">
+      <c r="M398" s="1" t="n">
         <v>45893</v>
       </c>
-      <c r="J398" t="n">
+      <c r="N398" t="n">
         <v>6.4</v>
       </c>
-      <c r="K398" s="1" t="n">
+      <c r="O398" s="1" t="n">
         <v>45885</v>
       </c>
-      <c r="L398" t="n">
-        <v>3</v>
-      </c>
-      <c r="M398" s="1" t="n">
-        <v>45871</v>
-      </c>
-      <c r="N398" t="inlineStr"/>
-      <c r="O398" t="inlineStr"/>
       <c r="P398" t="n">
-        <v>6.42</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="399">
@@ -17709,49 +17769,49 @@
         <v>548</v>
       </c>
       <c r="B400" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="C400" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="D400" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E400" s="1" t="n">
         <v>45926</v>
       </c>
-      <c r="D400" t="n">
+      <c r="F400" t="n">
         <v>6.3</v>
       </c>
-      <c r="E400" s="1" t="n">
+      <c r="G400" s="1" t="n">
         <v>45913</v>
       </c>
-      <c r="F400" t="n">
+      <c r="H400" t="n">
         <v>7</v>
       </c>
-      <c r="G400" s="1" t="n">
+      <c r="I400" s="1" t="n">
         <v>45898</v>
       </c>
-      <c r="H400" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I400" s="1" t="n">
+      <c r="J400" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K400" s="1" t="n">
         <v>45891</v>
       </c>
-      <c r="J400" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K400" s="1" t="n">
+      <c r="L400" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M400" s="1" t="n">
         <v>45885</v>
       </c>
-      <c r="L400" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M400" s="1" t="n">
+      <c r="N400" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O400" s="1" t="n">
         <v>45879</v>
       </c>
-      <c r="N400" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O400" s="1" t="n">
-        <v>45870</v>
-      </c>
       <c r="P400" t="n">
-        <v>6.6</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="401">
@@ -17762,34 +17822,38 @@
         <v>6.7</v>
       </c>
       <c r="C401" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D401" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E401" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="D401" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E401" s="1" t="n">
+      <c r="F401" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G401" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="F401" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G401" s="1" t="n">
+      <c r="H401" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I401" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="H401" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I401" s="1" t="n">
+      <c r="J401" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K401" s="1" t="n">
         <v>45892</v>
       </c>
-      <c r="J401" t="n">
+      <c r="L401" t="n">
         <v>7.2</v>
       </c>
-      <c r="K401" s="1" t="n">
+      <c r="M401" s="1" t="n">
         <v>45877</v>
       </c>
-      <c r="L401" t="inlineStr"/>
-      <c r="M401" t="inlineStr"/>
       <c r="N401" t="inlineStr"/>
       <c r="O401" t="inlineStr"/>
       <c r="P401" t="n">
@@ -17843,37 +17907,41 @@
         <v>551</v>
       </c>
       <c r="B403" t="n">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="C403" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D403" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E403" s="1" t="n">
         <v>45912</v>
       </c>
-      <c r="D403" t="n">
+      <c r="F403" t="n">
         <v>6.3</v>
       </c>
-      <c r="E403" s="1" t="n">
+      <c r="G403" s="1" t="n">
         <v>45898</v>
       </c>
-      <c r="F403" t="n">
+      <c r="H403" t="n">
         <v>7</v>
       </c>
-      <c r="G403" s="1" t="n">
+      <c r="I403" s="1" t="n">
         <v>45892</v>
       </c>
-      <c r="H403" t="n">
+      <c r="J403" t="n">
         <v>7.1</v>
       </c>
-      <c r="I403" s="1" t="n">
+      <c r="K403" s="1" t="n">
         <v>45877</v>
       </c>
-      <c r="J403" t="inlineStr"/>
-      <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr"/>
       <c r="M403" t="inlineStr"/>
       <c r="N403" t="inlineStr"/>
       <c r="O403" t="inlineStr"/>
       <c r="P403" t="n">
-        <v>6.75</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="404">
@@ -17881,46 +17949,46 @@
         <v>552</v>
       </c>
       <c r="B404" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C404" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D404" t="n">
         <v>6.9</v>
       </c>
-      <c r="C404" s="1" t="n">
+      <c r="E404" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D404" t="n">
+      <c r="F404" t="n">
         <v>7.8</v>
       </c>
-      <c r="E404" s="1" t="n">
+      <c r="G404" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="F404" t="n">
+      <c r="H404" t="n">
         <v>6</v>
       </c>
-      <c r="G404" s="1" t="n">
+      <c r="I404" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="H404" t="n">
+      <c r="J404" t="n">
         <v>6.4</v>
       </c>
-      <c r="I404" s="1" t="n">
+      <c r="K404" s="1" t="n">
         <v>46057</v>
       </c>
-      <c r="J404" t="n">
+      <c r="L404" t="n">
         <v>7.2</v>
       </c>
-      <c r="K404" s="1" t="n">
+      <c r="M404" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="L404" t="n">
+      <c r="N404" t="n">
         <v>6.8</v>
       </c>
-      <c r="M404" s="1" t="n">
+      <c r="O404" s="1" t="n">
         <v>46045</v>
-      </c>
-      <c r="N404" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O404" s="1" t="n">
-        <v>46040</v>
       </c>
       <c r="P404" t="n">
         <v>6.89</v>
@@ -17931,37 +17999,41 @@
         <v>553</v>
       </c>
       <c r="B405" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="C405" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D405" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E405" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D405" t="n">
+      <c r="F405" t="n">
         <v>6.3</v>
       </c>
-      <c r="E405" s="1" t="n">
+      <c r="G405" s="1" t="n">
         <v>45929</v>
       </c>
-      <c r="F405" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G405" s="1" t="n">
+      <c r="H405" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I405" s="1" t="n">
         <v>45912</v>
       </c>
-      <c r="H405" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I405" s="1" t="n">
+      <c r="J405" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K405" s="1" t="n">
         <v>45899</v>
       </c>
-      <c r="J405" t="inlineStr"/>
-      <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr"/>
       <c r="M405" t="inlineStr"/>
       <c r="N405" t="inlineStr"/>
       <c r="O405" t="inlineStr"/>
       <c r="P405" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="406">
@@ -17969,49 +18041,49 @@
         <v>554</v>
       </c>
       <c r="B406" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C406" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D406" t="n">
         <v>8</v>
       </c>
-      <c r="C406" s="1" t="n">
+      <c r="E406" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D406" t="n">
+      <c r="F406" t="n">
         <v>7.9</v>
       </c>
-      <c r="E406" s="1" t="n">
+      <c r="G406" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="F406" t="n">
+      <c r="H406" t="n">
         <v>7.7</v>
       </c>
-      <c r="G406" s="1" t="n">
+      <c r="I406" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H406" t="n">
+      <c r="J406" t="n">
         <v>6.1</v>
       </c>
-      <c r="I406" s="1" t="n">
+      <c r="K406" s="1" t="n">
         <v>46057</v>
       </c>
-      <c r="J406" t="n">
+      <c r="L406" t="n">
         <v>6.9</v>
       </c>
-      <c r="K406" s="1" t="n">
+      <c r="M406" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="L406" t="n">
+      <c r="N406" t="n">
         <v>7.7</v>
       </c>
-      <c r="M406" s="1" t="n">
+      <c r="O406" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="N406" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O406" s="1" t="n">
-        <v>46040</v>
-      </c>
       <c r="P406" t="n">
-        <v>7.2</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="407">
@@ -18019,49 +18091,49 @@
         <v>555</v>
       </c>
       <c r="B407" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C407" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D407" t="n">
         <v>7</v>
       </c>
-      <c r="C407" s="1" t="n">
+      <c r="E407" s="1" t="n">
         <v>45957</v>
       </c>
-      <c r="D407" t="n">
+      <c r="F407" t="n">
         <v>7.2</v>
       </c>
-      <c r="E407" s="1" t="n">
+      <c r="G407" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="F407" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G407" s="1" t="n">
+      <c r="H407" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I407" s="1" t="n">
         <v>45936</v>
       </c>
-      <c r="H407" t="n">
+      <c r="J407" t="n">
         <v>6.2</v>
       </c>
-      <c r="I407" s="1" t="n">
+      <c r="K407" s="1" t="n">
         <v>45929</v>
       </c>
-      <c r="J407" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K407" s="1" t="n">
+      <c r="L407" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M407" s="1" t="n">
         <v>45919</v>
       </c>
-      <c r="L407" t="n">
+      <c r="N407" t="n">
         <v>7.1</v>
       </c>
-      <c r="M407" s="1" t="n">
+      <c r="O407" s="1" t="n">
         <v>45914</v>
       </c>
-      <c r="N407" t="n">
-        <v>6</v>
-      </c>
-      <c r="O407" s="1" t="n">
-        <v>45900</v>
-      </c>
       <c r="P407" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="408">
@@ -18119,49 +18191,49 @@
         <v>557</v>
       </c>
       <c r="B409" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C409" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D409" t="n">
         <v>7.9</v>
       </c>
-      <c r="C409" s="1" t="n">
+      <c r="E409" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="D409" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E409" s="1" t="n">
+      <c r="F409" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G409" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="F409" t="n">
+      <c r="H409" t="n">
         <v>6.9</v>
       </c>
-      <c r="G409" s="1" t="n">
+      <c r="I409" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="H409" t="n">
+      <c r="J409" t="n">
         <v>7.7</v>
       </c>
-      <c r="I409" s="1" t="n">
+      <c r="K409" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="J409" t="n">
+      <c r="L409" t="n">
         <v>6.3</v>
       </c>
-      <c r="K409" s="1" t="n">
+      <c r="M409" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="L409" t="n">
+      <c r="N409" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M409" s="1" t="n">
+      <c r="O409" s="1" t="n">
         <v>45965</v>
       </c>
-      <c r="N409" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O409" s="1" t="n">
-        <v>45955</v>
-      </c>
       <c r="P409" t="n">
-        <v>7.13</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="410">
@@ -18169,49 +18241,49 @@
         <v>558</v>
       </c>
       <c r="B410" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C410" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D410" t="n">
         <v>7.4</v>
       </c>
-      <c r="C410" s="1" t="n">
+      <c r="E410" s="1" t="n">
         <v>46074</v>
-      </c>
-      <c r="D410" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E410" s="1" t="n">
-        <v>46004</v>
       </c>
       <c r="F410" t="n">
         <v>6.9</v>
       </c>
       <c r="G410" s="1" t="n">
+        <v>46004</v>
+      </c>
+      <c r="H410" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I410" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="H410" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I410" s="1" t="n">
+      <c r="J410" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K410" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="J410" t="n">
+      <c r="L410" t="n">
         <v>6.2</v>
       </c>
-      <c r="K410" s="1" t="n">
+      <c r="M410" s="1" t="n">
         <v>45986</v>
       </c>
-      <c r="L410" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M410" s="1" t="n">
+      <c r="N410" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O410" s="1" t="n">
         <v>45972</v>
       </c>
-      <c r="N410" t="n">
-        <v>6</v>
-      </c>
-      <c r="O410" s="1" t="n">
-        <v>45962</v>
-      </c>
       <c r="P410" t="n">
-        <v>6.63</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="411">
@@ -18222,46 +18294,46 @@
         <v>7.2</v>
       </c>
       <c r="C411" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="D411" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E411" s="1" t="n">
         <v>46072</v>
       </c>
-      <c r="D411" t="n">
+      <c r="F411" t="n">
         <v>7.4</v>
       </c>
-      <c r="E411" s="1" t="n">
+      <c r="G411" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="F411" t="n">
+      <c r="H411" t="n">
         <v>9.1</v>
       </c>
-      <c r="G411" s="1" t="n">
+      <c r="I411" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="H411" t="n">
+      <c r="J411" t="n">
         <v>7</v>
       </c>
-      <c r="I411" s="1" t="n">
+      <c r="K411" s="1" t="n">
         <v>45990</v>
-      </c>
-      <c r="J411" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K411" s="1" t="n">
-        <v>45983</v>
       </c>
       <c r="L411" t="n">
         <v>7.2</v>
       </c>
       <c r="M411" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="N411" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O411" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="N411" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O411" s="1" t="n">
-        <v>45955</v>
-      </c>
       <c r="P411" t="n">
-        <v>7.36</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="412">
@@ -18269,46 +18341,46 @@
         <v>560</v>
       </c>
       <c r="B412" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C412" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D412" t="n">
         <v>6.2</v>
       </c>
-      <c r="C412" s="1" t="n">
+      <c r="E412" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D412" t="n">
+      <c r="F412" t="n">
         <v>6.9</v>
       </c>
-      <c r="E412" s="1" t="n">
+      <c r="G412" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F412" t="n">
+      <c r="H412" t="n">
         <v>7</v>
       </c>
-      <c r="G412" s="1" t="n">
+      <c r="I412" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H412" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I412" s="1" t="n">
+      <c r="J412" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K412" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J412" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K412" s="1" t="n">
+      <c r="L412" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M412" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L412" t="n">
+      <c r="N412" t="n">
         <v>6.4</v>
       </c>
-      <c r="M412" s="1" t="n">
+      <c r="O412" s="1" t="n">
         <v>45984</v>
-      </c>
-      <c r="N412" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O412" s="1" t="n">
-        <v>45969</v>
       </c>
       <c r="P412" t="n">
         <v>6.63</v>
@@ -18469,49 +18541,49 @@
         <v>565</v>
       </c>
       <c r="B417" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C417" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D417" t="n">
         <v>7.6</v>
       </c>
-      <c r="C417" s="1" t="n">
+      <c r="E417" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D417" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E417" s="1" t="n">
+      <c r="F417" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G417" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F417" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G417" s="1" t="n">
+      <c r="H417" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I417" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H417" t="n">
+      <c r="J417" t="n">
         <v>6</v>
       </c>
-      <c r="I417" s="1" t="n">
+      <c r="K417" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="J417" t="n">
+      <c r="L417" t="n">
         <v>6.4</v>
       </c>
-      <c r="K417" s="1" t="n">
+      <c r="M417" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L417" t="n">
+      <c r="N417" t="n">
         <v>6.8</v>
       </c>
-      <c r="M417" s="1" t="n">
+      <c r="O417" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="N417" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O417" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P417" t="n">
-        <v>6.67</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="418">
@@ -18557,49 +18629,49 @@
         <v>567</v>
       </c>
       <c r="B419" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C419" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D419" t="n">
         <v>6.3</v>
       </c>
-      <c r="C419" s="1" t="n">
+      <c r="E419" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D419" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E419" s="1" t="n">
+      <c r="F419" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G419" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F419" t="n">
+      <c r="H419" t="n">
         <v>7.2</v>
       </c>
-      <c r="G419" s="1" t="n">
+      <c r="I419" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="H419" t="n">
+      <c r="J419" t="n">
         <v>7</v>
       </c>
-      <c r="I419" s="1" t="n">
+      <c r="K419" s="1" t="n">
         <v>45990</v>
-      </c>
-      <c r="J419" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K419" s="1" t="n">
-        <v>45984</v>
       </c>
       <c r="L419" t="n">
         <v>6.9</v>
       </c>
       <c r="M419" s="1" t="n">
+        <v>45984</v>
+      </c>
+      <c r="N419" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O419" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="N419" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O419" s="1" t="n">
-        <v>45964</v>
-      </c>
       <c r="P419" t="n">
-        <v>6.8</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="420">
@@ -18915,46 +18987,46 @@
         <v>577</v>
       </c>
       <c r="B427" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C427" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D427" t="n">
         <v>5.9</v>
       </c>
-      <c r="C427" s="1" t="n">
+      <c r="E427" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D427" t="n">
+      <c r="F427" t="n">
         <v>5.7</v>
       </c>
-      <c r="E427" s="1" t="n">
+      <c r="G427" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="F427" t="n">
+      <c r="H427" t="n">
         <v>6.3</v>
       </c>
-      <c r="G427" s="1" t="n">
+      <c r="I427" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H427" t="n">
+      <c r="J427" t="n">
         <v>7.4</v>
       </c>
-      <c r="I427" s="1" t="n">
+      <c r="K427" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="J427" t="n">
+      <c r="L427" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K427" s="1" t="n">
+      <c r="M427" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="L427" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M427" s="1" t="n">
+      <c r="N427" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O427" s="1" t="n">
         <v>46004</v>
-      </c>
-      <c r="N427" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O427" s="1" t="n">
-        <v>45999</v>
       </c>
       <c r="P427" t="n">
         <v>6.66</v>
@@ -19018,46 +19090,46 @@
         <v>6.2</v>
       </c>
       <c r="C429" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D429" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E429" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D429" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E429" s="1" t="n">
+      <c r="F429" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G429" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F429" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G429" s="1" t="n">
+      <c r="H429" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I429" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H429" t="n">
+      <c r="J429" t="n">
         <v>7</v>
       </c>
-      <c r="I429" s="1" t="n">
+      <c r="K429" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="J429" t="n">
+      <c r="L429" t="n">
         <v>6.3</v>
       </c>
-      <c r="K429" s="1" t="n">
+      <c r="M429" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L429" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M429" s="1" t="n">
+      <c r="N429" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O429" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N429" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O429" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P429" t="n">
-        <v>6.49</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="430">
@@ -19353,49 +19425,49 @@
         <v>587</v>
       </c>
       <c r="B436" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C436" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D436" t="n">
         <v>7.5</v>
       </c>
-      <c r="C436" s="1" t="n">
+      <c r="E436" s="1" t="n">
         <v>46052</v>
-      </c>
-      <c r="D436" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E436" s="1" t="n">
-        <v>46010</v>
       </c>
       <c r="F436" t="n">
         <v>6.4</v>
       </c>
       <c r="G436" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="H436" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I436" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="H436" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I436" s="1" t="n">
+      <c r="J436" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K436" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J436" t="n">
+      <c r="L436" t="n">
         <v>6.9</v>
       </c>
-      <c r="K436" s="1" t="n">
+      <c r="M436" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="L436" t="n">
+      <c r="N436" t="n">
         <v>6.8</v>
       </c>
-      <c r="M436" s="1" t="n">
+      <c r="O436" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="N436" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O436" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P436" t="n">
-        <v>6.71</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="437">
@@ -19403,49 +19475,49 @@
         <v>588</v>
       </c>
       <c r="B437" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C437" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D437" t="n">
         <v>5.6</v>
       </c>
-      <c r="C437" s="1" t="n">
+      <c r="E437" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="D437" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E437" s="1" t="n">
+      <c r="F437" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G437" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="F437" t="n">
+      <c r="H437" t="n">
         <v>6</v>
       </c>
-      <c r="G437" s="1" t="n">
+      <c r="I437" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="H437" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I437" s="1" t="n">
+      <c r="J437" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K437" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="J437" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K437" s="1" t="n">
+      <c r="L437" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M437" s="1" t="n">
         <v>46001</v>
       </c>
-      <c r="L437" t="n">
+      <c r="N437" t="n">
         <v>6.4</v>
       </c>
-      <c r="M437" s="1" t="n">
+      <c r="O437" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="N437" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O437" s="1" t="n">
-        <v>45989</v>
-      </c>
       <c r="P437" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="438">
@@ -19503,49 +19575,49 @@
         <v>590</v>
       </c>
       <c r="B439" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C439" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D439" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E439" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D439" t="n">
+      <c r="F439" t="n">
         <v>6.4</v>
       </c>
-      <c r="E439" s="1" t="n">
+      <c r="G439" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="F439" t="n">
+      <c r="H439" t="n">
         <v>7.2</v>
       </c>
-      <c r="G439" s="1" t="n">
+      <c r="I439" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="H439" t="n">
+      <c r="J439" t="n">
         <v>7.1</v>
       </c>
-      <c r="I439" s="1" t="n">
+      <c r="K439" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="J439" t="n">
+      <c r="L439" t="n">
         <v>6.2</v>
       </c>
-      <c r="K439" s="1" t="n">
+      <c r="M439" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="L439" t="n">
+      <c r="N439" t="n">
         <v>7.6</v>
       </c>
-      <c r="M439" s="1" t="n">
+      <c r="O439" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N439" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O439" s="1" t="n">
-        <v>45955</v>
-      </c>
       <c r="P439" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="440">
@@ -19653,49 +19725,49 @@
         <v>593</v>
       </c>
       <c r="B442" t="n">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>46073</v>
+        <v>46082</v>
       </c>
       <c r="D442" t="n">
         <v>6.9</v>
       </c>
       <c r="E442" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="F442" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G442" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F442" t="n">
+      <c r="H442" t="n">
         <v>6.4</v>
       </c>
-      <c r="G442" s="1" t="n">
+      <c r="I442" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H442" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I442" s="1" t="n">
+      <c r="J442" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K442" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J442" t="n">
+      <c r="L442" t="n">
         <v>7.8</v>
       </c>
-      <c r="K442" s="1" t="n">
+      <c r="M442" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L442" t="n">
+      <c r="N442" t="n">
         <v>8.4</v>
       </c>
-      <c r="M442" s="1" t="n">
+      <c r="O442" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="N442" t="n">
-        <v>6</v>
-      </c>
-      <c r="O442" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P442" t="n">
-        <v>7.01</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="443">
@@ -19853,49 +19925,49 @@
         <v>597</v>
       </c>
       <c r="B446" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C446" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D446" t="n">
         <v>7.7</v>
       </c>
-      <c r="C446" s="1" t="n">
+      <c r="E446" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D446" t="n">
+      <c r="F446" t="n">
         <v>6.4</v>
       </c>
-      <c r="E446" s="1" t="n">
+      <c r="G446" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F446" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G446" s="1" t="n">
+      <c r="H446" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I446" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H446" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I446" s="1" t="n">
+      <c r="J446" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K446" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="J446" t="n">
+      <c r="L446" t="n">
         <v>7.5</v>
       </c>
-      <c r="K446" s="1" t="n">
+      <c r="M446" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="L446" t="n">
+      <c r="N446" t="n">
         <v>7</v>
       </c>
-      <c r="M446" s="1" t="n">
+      <c r="O446" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="N446" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O446" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P446" t="n">
-        <v>6.86</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="447">
@@ -19903,49 +19975,49 @@
         <v>598</v>
       </c>
       <c r="B447" t="n">
+        <v>7</v>
+      </c>
+      <c r="C447" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D447" t="n">
         <v>7.8</v>
       </c>
-      <c r="C447" s="1" t="n">
+      <c r="E447" s="1" t="n">
         <v>46076</v>
       </c>
-      <c r="D447" t="n">
+      <c r="F447" t="n">
         <v>6.8</v>
       </c>
-      <c r="E447" s="1" t="n">
+      <c r="G447" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="F447" t="n">
+      <c r="H447" t="n">
         <v>6.9</v>
       </c>
-      <c r="G447" s="1" t="n">
+      <c r="I447" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H447" t="n">
+      <c r="J447" t="n">
         <v>7.2</v>
       </c>
-      <c r="I447" s="1" t="n">
+      <c r="K447" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="J447" t="n">
+      <c r="L447" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K447" s="1" t="n">
+      <c r="M447" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="L447" t="n">
+      <c r="N447" t="n">
         <v>7.7</v>
       </c>
-      <c r="M447" s="1" t="n">
+      <c r="O447" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="N447" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O447" s="1" t="n">
-        <v>45990</v>
-      </c>
       <c r="P447" t="n">
-        <v>7.29</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="448">
@@ -20073,13 +20145,17 @@
         <v>602</v>
       </c>
       <c r="B451" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C451" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D451" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E451" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="D451" t="inlineStr"/>
-      <c r="E451" t="inlineStr"/>
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr"/>
@@ -20091,7 +20167,7 @@
       <c r="N451" t="inlineStr"/>
       <c r="O451" t="inlineStr"/>
       <c r="P451" t="n">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="452">
@@ -20099,49 +20175,49 @@
         <v>603</v>
       </c>
       <c r="B452" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C452" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D452" t="n">
         <v>7</v>
       </c>
-      <c r="C452" s="1" t="n">
+      <c r="E452" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D452" t="n">
+      <c r="F452" t="n">
         <v>7.1</v>
       </c>
-      <c r="E452" s="1" t="n">
+      <c r="G452" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F452" t="n">
+      <c r="H452" t="n">
         <v>7.4</v>
       </c>
-      <c r="G452" s="1" t="n">
+      <c r="I452" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="H452" t="n">
+      <c r="J452" t="n">
         <v>7</v>
       </c>
-      <c r="I452" s="1" t="n">
+      <c r="K452" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J452" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K452" s="1" t="n">
+      <c r="L452" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M452" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="L452" t="n">
+      <c r="N452" t="n">
         <v>7.2</v>
       </c>
-      <c r="M452" s="1" t="n">
+      <c r="O452" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N452" t="n">
-        <v>6</v>
-      </c>
-      <c r="O452" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P452" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
     </row>
     <row r="453">
@@ -20283,49 +20359,49 @@
         <v>607</v>
       </c>
       <c r="B456" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C456" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D456" t="n">
         <v>6.8</v>
       </c>
-      <c r="C456" s="1" t="n">
+      <c r="E456" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D456" t="n">
+      <c r="F456" t="n">
         <v>7.9</v>
       </c>
-      <c r="E456" s="1" t="n">
+      <c r="G456" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F456" t="n">
+      <c r="H456" t="n">
         <v>7</v>
       </c>
-      <c r="G456" s="1" t="n">
+      <c r="I456" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H456" t="n">
+      <c r="J456" t="n">
         <v>7.2</v>
       </c>
-      <c r="I456" s="1" t="n">
+      <c r="K456" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J456" t="n">
+      <c r="L456" t="n">
         <v>7.3</v>
       </c>
-      <c r="K456" s="1" t="n">
+      <c r="M456" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="L456" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M456" s="1" t="n">
+      <c r="N456" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O456" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="N456" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O456" s="1" t="n">
-        <v>46036</v>
-      </c>
       <c r="P456" t="n">
-        <v>7.17</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="457">
@@ -20383,49 +20459,49 @@
         <v>609</v>
       </c>
       <c r="B458" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C458" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D458" t="n">
         <v>7.6</v>
       </c>
-      <c r="C458" s="1" t="n">
+      <c r="E458" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D458" t="n">
+      <c r="F458" t="n">
         <v>6.4</v>
       </c>
-      <c r="E458" s="1" t="n">
+      <c r="G458" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="F458" t="n">
+      <c r="H458" t="n">
         <v>6.8</v>
       </c>
-      <c r="G458" s="1" t="n">
+      <c r="I458" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="H458" t="n">
+      <c r="J458" t="n">
         <v>5.9</v>
       </c>
-      <c r="I458" s="1" t="n">
+      <c r="K458" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="J458" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K458" s="1" t="n">
+      <c r="L458" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M458" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="L458" t="n">
+      <c r="N458" t="n">
         <v>7.3</v>
       </c>
-      <c r="M458" s="1" t="n">
+      <c r="O458" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="N458" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O458" s="1" t="n">
-        <v>45956</v>
-      </c>
       <c r="P458" t="n">
-        <v>6.67</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="459">
@@ -20453,49 +20529,49 @@
         <v>611</v>
       </c>
       <c r="B460" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C460" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D460" t="n">
         <v>7.4</v>
       </c>
-      <c r="C460" s="1" t="n">
+      <c r="E460" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D460" t="n">
+      <c r="F460" t="n">
         <v>7.2</v>
       </c>
-      <c r="E460" s="1" t="n">
+      <c r="G460" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F460" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G460" s="1" t="n">
+      <c r="H460" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I460" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H460" t="n">
+      <c r="J460" t="n">
         <v>7.2</v>
       </c>
-      <c r="I460" s="1" t="n">
+      <c r="K460" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J460" t="n">
+      <c r="L460" t="n">
         <v>7</v>
       </c>
-      <c r="K460" s="1" t="n">
+      <c r="M460" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="L460" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M460" s="1" t="n">
+      <c r="N460" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O460" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="N460" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O460" s="1" t="n">
-        <v>46004</v>
-      </c>
       <c r="P460" t="n">
-        <v>7.03</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="461">
@@ -20703,46 +20779,46 @@
         <v>617</v>
       </c>
       <c r="B465" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C465" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D465" t="n">
         <v>6.8</v>
       </c>
-      <c r="C465" s="1" t="n">
+      <c r="E465" s="1" t="n">
         <v>46076</v>
       </c>
-      <c r="D465" t="n">
+      <c r="F465" t="n">
         <v>6</v>
       </c>
-      <c r="E465" s="1" t="n">
+      <c r="G465" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F465" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G465" s="1" t="n">
+      <c r="H465" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I465" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="H465" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I465" s="1" t="n">
+      <c r="J465" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K465" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="J465" t="n">
+      <c r="L465" t="n">
         <v>6.4</v>
       </c>
-      <c r="K465" s="1" t="n">
+      <c r="M465" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="L465" t="n">
+      <c r="N465" t="n">
         <v>7</v>
       </c>
-      <c r="M465" s="1" t="n">
+      <c r="O465" s="1" t="n">
         <v>46012</v>
-      </c>
-      <c r="N465" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O465" s="1" t="n">
-        <v>46003</v>
       </c>
       <c r="P465" t="n">
         <v>6.54</v>
@@ -20753,49 +20829,49 @@
         <v>618</v>
       </c>
       <c r="B466" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C466" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D466" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E466" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D466" t="n">
+      <c r="F466" t="n">
         <v>6.8</v>
       </c>
-      <c r="E466" s="1" t="n">
+      <c r="G466" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F466" t="n">
+      <c r="H466" t="n">
         <v>7.2</v>
       </c>
-      <c r="G466" s="1" t="n">
+      <c r="I466" s="1" t="n">
         <v>46055</v>
       </c>
-      <c r="H466" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I466" s="1" t="n">
+      <c r="J466" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K466" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="J466" t="n">
+      <c r="L466" t="n">
         <v>6.1</v>
       </c>
-      <c r="K466" s="1" t="n">
+      <c r="M466" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="L466" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M466" s="1" t="n">
+      <c r="N466" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O466" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="N466" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O466" s="1" t="n">
-        <v>46011</v>
-      </c>
       <c r="P466" t="n">
-        <v>6.73</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="467">
@@ -20803,49 +20879,49 @@
         <v>619</v>
       </c>
       <c r="B467" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C467" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D467" t="n">
         <v>7.2</v>
       </c>
-      <c r="C467" s="1" t="n">
+      <c r="E467" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D467" t="n">
+      <c r="F467" t="n">
         <v>7.4</v>
       </c>
-      <c r="E467" s="1" t="n">
+      <c r="G467" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="F467" t="n">
+      <c r="H467" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G467" s="1" t="n">
+      <c r="I467" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H467" t="n">
+      <c r="J467" t="n">
         <v>7.1</v>
       </c>
-      <c r="I467" s="1" t="n">
+      <c r="K467" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="J467" t="n">
+      <c r="L467" t="n">
         <v>7.7</v>
       </c>
-      <c r="K467" s="1" t="n">
+      <c r="M467" s="1" t="n">
         <v>45986</v>
       </c>
-      <c r="L467" t="n">
+      <c r="N467" t="n">
         <v>7.6</v>
       </c>
-      <c r="M467" s="1" t="n">
+      <c r="O467" s="1" t="n">
         <v>45961</v>
       </c>
-      <c r="N467" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O467" s="1" t="n">
-        <v>45955</v>
-      </c>
       <c r="P467" t="n">
-        <v>7.4</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="468">
@@ -20853,49 +20929,49 @@
         <v>620</v>
       </c>
       <c r="B468" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C468" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D468" t="n">
         <v>7.1</v>
       </c>
-      <c r="C468" s="1" t="n">
+      <c r="E468" s="1" t="n">
         <v>46077</v>
       </c>
-      <c r="D468" t="n">
+      <c r="F468" t="n">
         <v>7.9</v>
       </c>
-      <c r="E468" s="1" t="n">
+      <c r="G468" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="F468" t="n">
+      <c r="H468" t="n">
         <v>7.1</v>
       </c>
-      <c r="G468" s="1" t="n">
+      <c r="I468" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H468" t="n">
+      <c r="J468" t="n">
         <v>7.6</v>
       </c>
-      <c r="I468" s="1" t="n">
+      <c r="K468" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="J468" t="n">
+      <c r="L468" t="n">
         <v>7</v>
       </c>
-      <c r="K468" s="1" t="n">
+      <c r="M468" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="L468" t="n">
+      <c r="N468" t="n">
         <v>7.5</v>
       </c>
-      <c r="M468" s="1" t="n">
+      <c r="O468" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N468" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O468" s="1" t="n">
-        <v>45962</v>
-      </c>
       <c r="P468" t="n">
-        <v>7.37</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="469">
@@ -20903,37 +20979,41 @@
         <v>621</v>
       </c>
       <c r="B469" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="C469" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D469" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E469" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D469" t="n">
+      <c r="F469" t="n">
         <v>6.3</v>
       </c>
-      <c r="E469" s="1" t="n">
+      <c r="G469" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F469" t="n">
+      <c r="H469" t="n">
         <v>6.1</v>
       </c>
-      <c r="G469" s="1" t="n">
+      <c r="I469" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H469" t="n">
+      <c r="J469" t="n">
         <v>7.8</v>
       </c>
-      <c r="I469" s="1" t="n">
+      <c r="K469" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J469" t="inlineStr"/>
-      <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr"/>
       <c r="M469" t="inlineStr"/>
       <c r="N469" t="inlineStr"/>
       <c r="O469" t="inlineStr"/>
       <c r="P469" t="n">
-        <v>6.7</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="470">
@@ -21041,49 +21121,49 @@
         <v>624</v>
       </c>
       <c r="B472" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C472" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D472" t="n">
         <v>6.9</v>
       </c>
-      <c r="C472" s="1" t="n">
+      <c r="E472" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="D472" t="n">
+      <c r="F472" t="n">
         <v>7.7</v>
       </c>
-      <c r="E472" s="1" t="n">
+      <c r="G472" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F472" t="n">
+      <c r="H472" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G472" s="1" t="n">
+      <c r="I472" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H472" t="n">
+      <c r="J472" t="n">
         <v>7.9</v>
       </c>
-      <c r="I472" s="1" t="n">
+      <c r="K472" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="J472" t="n">
+      <c r="L472" t="n">
         <v>6.9</v>
       </c>
-      <c r="K472" s="1" t="n">
+      <c r="M472" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="L472" t="n">
+      <c r="N472" t="n">
         <v>7.1</v>
       </c>
-      <c r="M472" s="1" t="n">
+      <c r="O472" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="N472" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O472" s="1" t="n">
-        <v>45990</v>
-      </c>
       <c r="P472" t="n">
-        <v>7.2</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="473">
@@ -21141,49 +21221,49 @@
         <v>626</v>
       </c>
       <c r="B474" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C474" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D474" t="n">
         <v>8.5</v>
       </c>
-      <c r="C474" s="1" t="n">
+      <c r="E474" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D474" t="n">
+      <c r="F474" t="n">
         <v>6.8</v>
       </c>
-      <c r="E474" s="1" t="n">
+      <c r="G474" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F474" t="n">
+      <c r="H474" t="n">
         <v>7.4</v>
       </c>
-      <c r="G474" s="1" t="n">
+      <c r="I474" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H474" t="n">
+      <c r="J474" t="n">
         <v>7.6</v>
       </c>
-      <c r="I474" s="1" t="n">
+      <c r="K474" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="J474" t="n">
+      <c r="L474" t="n">
         <v>8.1</v>
       </c>
-      <c r="K474" s="1" t="n">
+      <c r="M474" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="L474" t="n">
+      <c r="N474" t="n">
         <v>6.1</v>
       </c>
-      <c r="M474" s="1" t="n">
+      <c r="O474" s="1" t="n">
         <v>45994</v>
       </c>
-      <c r="N474" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O474" s="1" t="n">
-        <v>45991</v>
-      </c>
       <c r="P474" t="n">
-        <v>7.47</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="475">
@@ -21191,19 +21271,23 @@
         <v>627</v>
       </c>
       <c r="B475" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C475" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D475" t="n">
         <v>7.1</v>
       </c>
-      <c r="C475" s="1" t="n">
+      <c r="E475" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D475" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E475" s="1" t="n">
+      <c r="F475" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G475" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F475" t="inlineStr"/>
-      <c r="G475" t="inlineStr"/>
       <c r="H475" t="inlineStr"/>
       <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr"/>
@@ -21213,7 +21297,7 @@
       <c r="N475" t="inlineStr"/>
       <c r="O475" t="inlineStr"/>
       <c r="P475" t="n">
-        <v>6.85</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="476">
@@ -21271,37 +21355,41 @@
         <v>629</v>
       </c>
       <c r="B477" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C477" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D477" t="n">
         <v>6.9</v>
       </c>
-      <c r="C477" s="1" t="n">
+      <c r="E477" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D477" t="n">
+      <c r="F477" t="n">
         <v>6.4</v>
       </c>
-      <c r="E477" s="1" t="n">
+      <c r="G477" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F477" t="n">
+      <c r="H477" t="n">
         <v>8.6</v>
       </c>
-      <c r="G477" s="1" t="n">
+      <c r="I477" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H477" t="n">
+      <c r="J477" t="n">
         <v>6.8</v>
       </c>
-      <c r="I477" s="1" t="n">
+      <c r="K477" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J477" t="inlineStr"/>
-      <c r="K477" t="inlineStr"/>
       <c r="L477" t="inlineStr"/>
       <c r="M477" t="inlineStr"/>
       <c r="N477" t="inlineStr"/>
       <c r="O477" t="inlineStr"/>
       <c r="P477" t="n">
-        <v>7.18</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="478">
@@ -21343,49 +21431,49 @@
         <v>631</v>
       </c>
       <c r="B479" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="C479" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D479" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E479" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D479" t="n">
+      <c r="F479" t="n">
         <v>7</v>
       </c>
-      <c r="E479" s="1" t="n">
+      <c r="G479" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F479" t="n">
+      <c r="H479" t="n">
         <v>6.8</v>
       </c>
-      <c r="G479" s="1" t="n">
+      <c r="I479" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H479" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I479" s="1" t="n">
+      <c r="J479" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K479" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="J479" t="n">
+      <c r="L479" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="K479" s="1" t="n">
+      <c r="M479" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L479" t="n">
+      <c r="N479" t="n">
         <v>7</v>
       </c>
-      <c r="M479" s="1" t="n">
+      <c r="O479" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="N479" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O479" s="1" t="n">
-        <v>45991</v>
-      </c>
       <c r="P479" t="n">
-        <v>7.1</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="480">
@@ -21493,31 +21581,35 @@
         <v>634</v>
       </c>
       <c r="B482" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C482" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D482" t="n">
         <v>6.4</v>
       </c>
-      <c r="C482" s="1" t="n">
+      <c r="E482" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D482" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E482" s="1" t="n">
+      <c r="F482" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G482" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F482" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G482" s="1" t="n">
+      <c r="H482" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I482" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="H482" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I482" s="1" t="n">
+      <c r="J482" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K482" s="1" t="n">
         <v>45865</v>
       </c>
-      <c r="J482" t="inlineStr"/>
-      <c r="K482" t="inlineStr"/>
       <c r="L482" t="inlineStr"/>
       <c r="M482" t="inlineStr"/>
       <c r="N482" t="inlineStr"/>
@@ -21526,6 +21618,506 @@
         <v>6.58</v>
       </c>
     </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>635</v>
+      </c>
+      <c r="B483" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C483" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="D483" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E483" s="1" t="n">
+        <v>45997</v>
+      </c>
+      <c r="F483" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G483" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="H483" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I483" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="J483" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K483" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="L483" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M483" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="N483" t="n">
+        <v>7</v>
+      </c>
+      <c r="O483" s="1" t="n">
+        <v>45948</v>
+      </c>
+      <c r="P483" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>636</v>
+      </c>
+      <c r="B484" t="n">
+        <v>8</v>
+      </c>
+      <c r="C484" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="D484" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E484" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="F484" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G484" s="1" t="n">
+        <v>45970</v>
+      </c>
+      <c r="H484" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I484" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="J484" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K484" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="L484" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M484" s="1" t="n">
+        <v>45956</v>
+      </c>
+      <c r="N484" t="n">
+        <v>7</v>
+      </c>
+      <c r="O484" s="1" t="n">
+        <v>45935</v>
+      </c>
+      <c r="P484" t="n">
+        <v>7.16</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>637</v>
+      </c>
+      <c r="B485" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C485" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D485" t="n">
+        <v>7</v>
+      </c>
+      <c r="E485" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="F485" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G485" s="1" t="n">
+        <v>46067</v>
+      </c>
+      <c r="H485" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I485" s="1" t="n">
+        <v>46060</v>
+      </c>
+      <c r="J485" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K485" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="L485" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M485" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="N485" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O485" s="1" t="n">
+        <v>45935</v>
+      </c>
+      <c r="P485" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>638</v>
+      </c>
+      <c r="B486" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C486" s="1" t="n">
+        <v>46067</v>
+      </c>
+      <c r="D486" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E486" s="1" t="n">
+        <v>45997</v>
+      </c>
+      <c r="F486" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G486" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="H486" t="n">
+        <v>7</v>
+      </c>
+      <c r="I486" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="J486" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K486" s="1" t="n">
+        <v>45963</v>
+      </c>
+      <c r="L486" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M486" s="1" t="n">
+        <v>45956</v>
+      </c>
+      <c r="N486" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O486" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="P486" t="n">
+        <v>7.17</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>639</v>
+      </c>
+      <c r="B487" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C487" s="1" t="n">
+        <v>45970</v>
+      </c>
+      <c r="D487" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E487" s="1" t="n">
+        <v>45963</v>
+      </c>
+      <c r="F487" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G487" s="1" t="n">
+        <v>45955</v>
+      </c>
+      <c r="H487" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I487" s="1" t="n">
+        <v>45948</v>
+      </c>
+      <c r="J487" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K487" s="1" t="n">
+        <v>45935</v>
+      </c>
+      <c r="L487" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M487" s="1" t="n">
+        <v>45929</v>
+      </c>
+      <c r="N487" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O487" s="1" t="n">
+        <v>45921</v>
+      </c>
+      <c r="P487" t="n">
+        <v>6.74</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>640</v>
+      </c>
+      <c r="B488" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C488" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="D488" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E488" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="F488" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G488" s="1" t="n">
+        <v>45997</v>
+      </c>
+      <c r="H488" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I488" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="J488" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K488" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="L488" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M488" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="N488" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O488" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="P488" t="n">
+        <v>7.56</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>641</v>
+      </c>
+      <c r="B489" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C489" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="D489" t="n">
+        <v>7</v>
+      </c>
+      <c r="E489" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="F489" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G489" s="1" t="n">
+        <v>45997</v>
+      </c>
+      <c r="H489" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I489" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="J489" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K489" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="L489" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M489" s="1" t="n">
+        <v>45969</v>
+      </c>
+      <c r="N489" t="n">
+        <v>7</v>
+      </c>
+      <c r="O489" s="1" t="n">
+        <v>45963</v>
+      </c>
+      <c r="P489" t="n">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>642</v>
+      </c>
+      <c r="B490" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C490" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D490" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E490" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="F490" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G490" s="1" t="n">
+        <v>46061</v>
+      </c>
+      <c r="H490" t="n">
+        <v>7</v>
+      </c>
+      <c r="I490" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="J490" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K490" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="L490" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M490" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="N490" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O490" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="P490" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>643</v>
+      </c>
+      <c r="B491" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C491" s="1" t="n">
+        <v>45969</v>
+      </c>
+      <c r="D491" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E491" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="F491" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G491" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="H491" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="I491" s="1" t="n">
+        <v>45948</v>
+      </c>
+      <c r="J491" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K491" s="1" t="n">
+        <v>45934</v>
+      </c>
+      <c r="L491" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M491" s="1" t="n">
+        <v>45928</v>
+      </c>
+      <c r="N491" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="O491" s="1" t="n">
+        <v>45925</v>
+      </c>
+      <c r="P491" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>644</v>
+      </c>
+      <c r="B492" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C492" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D492" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E492" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="F492" t="n">
+        <v>7</v>
+      </c>
+      <c r="G492" s="1" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H492" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I492" s="1" t="n">
+        <v>46060</v>
+      </c>
+      <c r="J492" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K492" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="L492" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M492" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="N492" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O492" s="1" t="n">
+        <v>45983</v>
+      </c>
+      <c r="P492" t="n">
+        <v>6.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/players_ratings.xlsx
+++ b/players_ratings.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P492"/>
+  <dimension ref="A1:P494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,49 +507,49 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="C2" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>7.3</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="G2" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>7.6</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="I2" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I2" s="1" t="n">
+      <c r="J2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K2" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>6.3</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="M2" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="L2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M2" s="1" t="n">
+      <c r="N2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O2" s="1" t="n">
         <v>45936</v>
       </c>
-      <c r="N2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>45927</v>
-      </c>
       <c r="P2" t="n">
-        <v>6.81</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="3">
@@ -607,49 +607,49 @@
         <v>15</v>
       </c>
       <c r="B4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D4" t="n">
         <v>6.4</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="E4" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>7.2</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="G4" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>6.3</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>8.6</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>6.1</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="M4" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>6.3</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="O4" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>6.8</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>45983</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6.81</v>
       </c>
     </row>
     <row r="5">
@@ -657,49 +657,49 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C5" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="D5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>6.4</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="I5" s="1" t="n">
         <v>45935</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>7.1</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <v>45898</v>
       </c>
-      <c r="J5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>45893</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>45887</v>
       </c>
       <c r="N5" t="n">
         <v>6.8</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>45871</v>
+        <v>45887</v>
       </c>
       <c r="P5" t="n">
-        <v>6.7</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="6">
@@ -899,49 +899,49 @@
         <v>29</v>
       </c>
       <c r="B11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D11" t="n">
         <v>7.4</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="E11" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>7</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="G11" s="1" t="n">
         <v>45976</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>7.9</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="I11" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="H11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I11" s="1" t="n">
+      <c r="J11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K11" s="1" t="n">
         <v>45966</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>7.2</v>
       </c>
-      <c r="K11" s="1" t="n">
+      <c r="M11" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>6.9</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="O11" s="1" t="n">
         <v>45949</v>
       </c>
-      <c r="N11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>45942</v>
-      </c>
       <c r="P11" t="n">
-        <v>7.2</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="12">
@@ -1099,49 +1099,49 @@
         <v>38</v>
       </c>
       <c r="B15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D15" t="n">
         <v>6.4</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="E15" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>6.9</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="G15" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>8.1</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="I15" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>7</v>
       </c>
-      <c r="I15" s="1" t="n">
+      <c r="K15" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="J15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K15" s="1" t="n">
+      <c r="L15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M15" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="O15" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O15" s="1" t="n">
-        <v>45947</v>
-      </c>
       <c r="P15" t="n">
-        <v>6.73</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="16">
@@ -1212,46 +1212,46 @@
         <v>6.5</v>
       </c>
       <c r="C18" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E18" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>7.7</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="G18" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>6</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="I18" s="1" t="n">
         <v>45981</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>7.4</v>
       </c>
-      <c r="I18" s="1" t="n">
+      <c r="K18" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>6.4</v>
       </c>
-      <c r="K18" s="1" t="n">
+      <c r="M18" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M18" s="1" t="n">
+      <c r="N18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O18" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O18" s="1" t="n">
-        <v>45946</v>
-      </c>
       <c r="P18" t="n">
-        <v>6.87</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="19">
@@ -1309,49 +1309,49 @@
         <v>46</v>
       </c>
       <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D20" t="n">
         <v>6.8</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="E20" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>6.3</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="G20" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G20" s="1" t="n">
+      <c r="H20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I20" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>7.4</v>
       </c>
-      <c r="I20" s="1" t="n">
+      <c r="K20" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="J20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K20" s="1" t="n">
+      <c r="L20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M20" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="L20" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M20" s="1" t="n">
+      <c r="N20" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O20" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N20" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O20" s="1" t="n">
-        <v>45994</v>
-      </c>
       <c r="P20" t="n">
-        <v>6.9</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="21">
@@ -1499,19 +1499,23 @@
         <v>55</v>
       </c>
       <c r="B25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D25" t="n">
         <v>6.4</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="E25" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>7</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="G25" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -1521,7 +1525,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>6.7</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="26">
@@ -1901,49 +1905,49 @@
         <v>75</v>
       </c>
       <c r="B34" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C34" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G34" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D34" t="n">
+      <c r="H34" t="n">
         <v>6.2</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="I34" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="F34" t="n">
+      <c r="J34" t="n">
         <v>6.4</v>
       </c>
-      <c r="G34" s="1" t="n">
+      <c r="K34" s="1" t="n">
         <v>46055</v>
       </c>
-      <c r="H34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I34" s="1" t="n">
+      <c r="L34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M34" s="1" t="n">
         <v>46038</v>
       </c>
-      <c r="J34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K34" s="1" t="n">
+      <c r="N34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O34" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="L34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M34" s="1" t="n">
-        <v>45996</v>
-      </c>
-      <c r="N34" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O34" s="1" t="n">
-        <v>45982</v>
-      </c>
       <c r="P34" t="n">
-        <v>6.47</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="35">
@@ -1951,49 +1955,49 @@
         <v>80</v>
       </c>
       <c r="B35" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D35" t="n">
         <v>6.8</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="E35" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>6.2</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="G35" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="F35" t="n">
+      <c r="H35" t="n">
         <v>6.8</v>
       </c>
-      <c r="G35" s="1" t="n">
+      <c r="I35" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>7.3</v>
       </c>
-      <c r="I35" s="1" t="n">
+      <c r="K35" s="1" t="n">
         <v>46060</v>
-      </c>
-      <c r="J35" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K35" s="1" t="n">
-        <v>46054</v>
       </c>
       <c r="L35" t="n">
         <v>6.8</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>46047</v>
+        <v>46054</v>
       </c>
       <c r="N35" t="n">
         <v>6.8</v>
       </c>
       <c r="O35" s="1" t="n">
-        <v>46039</v>
+        <v>46047</v>
       </c>
       <c r="P35" t="n">
-        <v>6.79</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="36">
@@ -2941,49 +2945,49 @@
         <v>124</v>
       </c>
       <c r="B59" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D59" t="n">
         <v>7.4</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="E59" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D59" t="n">
+      <c r="F59" t="n">
         <v>6.8</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="G59" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F59" t="n">
+      <c r="H59" t="n">
         <v>5.9</v>
       </c>
-      <c r="G59" s="1" t="n">
+      <c r="I59" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H59" t="n">
+      <c r="J59" t="n">
         <v>6.4</v>
       </c>
-      <c r="I59" s="1" t="n">
+      <c r="K59" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="J59" t="n">
+      <c r="L59" t="n">
         <v>7</v>
       </c>
-      <c r="K59" s="1" t="n">
+      <c r="M59" s="1" t="n">
         <v>45992</v>
-      </c>
-      <c r="L59" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M59" s="1" t="n">
-        <v>45983</v>
       </c>
       <c r="N59" t="n">
         <v>7.1</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>45969</v>
+        <v>45983</v>
       </c>
       <c r="P59" t="n">
-        <v>6.81</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="60">
@@ -3011,49 +3015,49 @@
         <v>132</v>
       </c>
       <c r="B61" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D61" t="n">
         <v>8</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="E61" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D61" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E61" s="1" t="n">
+      <c r="F61" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G61" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F61" t="n">
+      <c r="H61" t="n">
         <v>6.4</v>
       </c>
-      <c r="G61" s="1" t="n">
+      <c r="I61" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H61" t="n">
+      <c r="J61" t="n">
         <v>7</v>
       </c>
-      <c r="I61" s="1" t="n">
+      <c r="K61" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="J61" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K61" s="1" t="n">
+      <c r="L61" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M61" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="L61" t="n">
+      <c r="N61" t="n">
         <v>7.5</v>
       </c>
-      <c r="M61" s="1" t="n">
+      <c r="O61" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="N61" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O61" s="1" t="n">
-        <v>45983</v>
-      </c>
       <c r="P61" t="n">
-        <v>7.11</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="62">
@@ -3061,49 +3065,49 @@
         <v>133</v>
       </c>
       <c r="B62" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46073</v>
+        <v>46088</v>
       </c>
       <c r="D62" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46068</v>
+        <v>46083</v>
       </c>
       <c r="F62" t="n">
         <v>7.3</v>
       </c>
       <c r="G62" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="H62" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I62" s="1" t="n">
+        <v>46068</v>
+      </c>
+      <c r="J62" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K62" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H62" t="n">
+      <c r="L62" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I62" s="1" t="n">
+      <c r="M62" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="J62" t="n">
+      <c r="N62" t="n">
         <v>6.1</v>
       </c>
-      <c r="K62" s="1" t="n">
+      <c r="O62" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L62" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="M62" s="1" t="n">
-        <v>45983</v>
-      </c>
-      <c r="N62" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O62" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P62" t="n">
-        <v>7.27</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="63">
@@ -3281,49 +3285,49 @@
         <v>144</v>
       </c>
       <c r="B67" t="n">
+        <v>7</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D67" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="F67" t="n">
         <v>7.5</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="G67" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D67" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E67" s="1" t="n">
+      <c r="H67" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I67" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="F67" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G67" s="1" t="n">
+      <c r="J67" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K67" s="1" t="n">
         <v>45972</v>
       </c>
-      <c r="H67" t="n">
+      <c r="L67" t="n">
         <v>7.1</v>
       </c>
-      <c r="I67" s="1" t="n">
+      <c r="M67" s="1" t="n">
         <v>45962</v>
-      </c>
-      <c r="J67" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K67" s="1" t="n">
-        <v>45955</v>
-      </c>
-      <c r="L67" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M67" s="1" t="n">
-        <v>45948</v>
       </c>
       <c r="N67" t="n">
         <v>6.4</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>45923</v>
+        <v>45955</v>
       </c>
       <c r="P67" t="n">
-        <v>6.71</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="68">
@@ -3381,46 +3385,46 @@
         <v>146</v>
       </c>
       <c r="B69" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D69" t="n">
         <v>6.8</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="E69" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D69" t="n">
+      <c r="F69" t="n">
         <v>7.7</v>
       </c>
-      <c r="E69" s="1" t="n">
+      <c r="G69" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F69" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G69" s="1" t="n">
+      <c r="H69" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I69" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="H69" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I69" s="1" t="n">
+      <c r="J69" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K69" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>6</v>
       </c>
-      <c r="K69" s="1" t="n">
+      <c r="M69" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="L69" t="n">
+      <c r="N69" t="n">
         <v>7.1</v>
       </c>
-      <c r="M69" s="1" t="n">
+      <c r="O69" s="1" t="n">
         <v>46053</v>
-      </c>
-      <c r="N69" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O69" s="1" t="n">
-        <v>46038</v>
       </c>
       <c r="P69" t="n">
         <v>6.89</v>
@@ -3431,49 +3435,49 @@
         <v>147</v>
       </c>
       <c r="B70" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="C70" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E70" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D70" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E70" s="1" t="n">
+      <c r="F70" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G70" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F70" t="n">
+      <c r="H70" t="n">
         <v>6.2</v>
       </c>
-      <c r="G70" s="1" t="n">
+      <c r="I70" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="H70" t="n">
+      <c r="J70" t="n">
         <v>7.1</v>
       </c>
-      <c r="I70" s="1" t="n">
+      <c r="K70" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="J70" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K70" s="1" t="n">
+      <c r="L70" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M70" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="L70" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M70" s="1" t="n">
+      <c r="N70" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O70" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="N70" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O70" s="1" t="n">
-        <v>46045</v>
-      </c>
       <c r="P70" t="n">
-        <v>6.56</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="71">
@@ -3501,49 +3505,49 @@
         <v>149</v>
       </c>
       <c r="B72" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D72" t="n">
         <v>6.9</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="E72" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D72" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E72" s="1" t="n">
+      <c r="F72" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G72" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="F72" t="n">
+      <c r="H72" t="n">
         <v>7.1</v>
       </c>
-      <c r="G72" s="1" t="n">
+      <c r="I72" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="H72" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I72" s="1" t="n">
+      <c r="J72" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K72" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>7.2</v>
       </c>
-      <c r="K72" s="1" t="n">
+      <c r="M72" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="L72" t="n">
+      <c r="N72" t="n">
         <v>6.2</v>
       </c>
-      <c r="M72" s="1" t="n">
+      <c r="O72" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="N72" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O72" s="1" t="n">
-        <v>45954</v>
-      </c>
       <c r="P72" t="n">
-        <v>6.71</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="73">
@@ -3551,49 +3555,49 @@
         <v>150</v>
       </c>
       <c r="B73" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D73" t="n">
         <v>7.3</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="E73" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D73" t="n">
+      <c r="F73" t="n">
         <v>7.1</v>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="G73" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="F73" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G73" s="1" t="n">
+      <c r="H73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I73" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="H73" t="n">
+      <c r="J73" t="n">
         <v>7.9</v>
       </c>
-      <c r="I73" s="1" t="n">
+      <c r="K73" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="J73" t="n">
+      <c r="L73" t="n">
         <v>8</v>
       </c>
-      <c r="K73" s="1" t="n">
+      <c r="M73" s="1" t="n">
         <v>45951</v>
       </c>
-      <c r="L73" t="n">
+      <c r="N73" t="n">
         <v>6.9</v>
       </c>
-      <c r="M73" s="1" t="n">
+      <c r="O73" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="N73" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="O73" s="1" t="n">
-        <v>45933</v>
-      </c>
       <c r="P73" t="n">
-        <v>7.43</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="74">
@@ -3651,49 +3655,49 @@
         <v>164</v>
       </c>
       <c r="B75" t="n">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C75" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E75" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="D75" t="n">
+      <c r="F75" t="n">
         <v>7.4</v>
       </c>
-      <c r="E75" s="1" t="n">
+      <c r="G75" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="F75" t="n">
+      <c r="H75" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G75" s="1" t="n">
+      <c r="I75" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="H75" t="n">
+      <c r="J75" t="n">
         <v>7.4</v>
       </c>
-      <c r="I75" s="1" t="n">
+      <c r="K75" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="J75" t="n">
+      <c r="L75" t="n">
         <v>6.4</v>
       </c>
-      <c r="K75" s="1" t="n">
+      <c r="M75" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="L75" t="n">
+      <c r="N75" t="n">
         <v>7.2</v>
       </c>
-      <c r="M75" s="1" t="n">
+      <c r="O75" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="N75" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O75" s="1" t="n">
-        <v>45941</v>
-      </c>
       <c r="P75" t="n">
-        <v>7.21</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="76">
@@ -3701,46 +3705,46 @@
         <v>165</v>
       </c>
       <c r="B76" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D76" t="n">
         <v>6.9</v>
       </c>
-      <c r="C76" s="1" t="n">
+      <c r="E76" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="D76" t="n">
+      <c r="F76" t="n">
         <v>7.3</v>
       </c>
-      <c r="E76" s="1" t="n">
+      <c r="G76" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="F76" t="n">
+      <c r="H76" t="n">
         <v>6.9</v>
       </c>
-      <c r="G76" s="1" t="n">
+      <c r="I76" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H76" t="n">
+      <c r="J76" t="n">
         <v>7.2</v>
       </c>
-      <c r="I76" s="1" t="n">
+      <c r="K76" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
         <v>6.3</v>
       </c>
-      <c r="K76" s="1" t="n">
+      <c r="M76" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L76" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M76" s="1" t="n">
+      <c r="N76" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O76" s="1" t="n">
         <v>45984</v>
-      </c>
-      <c r="N76" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O76" s="1" t="n">
-        <v>45968</v>
       </c>
       <c r="P76" t="n">
         <v>6.81</v>
@@ -3801,49 +3805,49 @@
         <v>167</v>
       </c>
       <c r="B78" t="n">
+        <v>7</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D78" t="n">
         <v>7.5</v>
       </c>
-      <c r="C78" s="1" t="n">
+      <c r="E78" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D78" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E78" s="1" t="n">
+      <c r="F78" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G78" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F78" t="n">
+      <c r="H78" t="n">
         <v>8.1</v>
       </c>
-      <c r="G78" s="1" t="n">
+      <c r="I78" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H78" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I78" s="1" t="n">
+      <c r="J78" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K78" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>7.1</v>
       </c>
-      <c r="K78" s="1" t="n">
+      <c r="M78" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="L78" t="n">
+      <c r="N78" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M78" s="1" t="n">
+      <c r="O78" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="N78" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O78" s="1" t="n">
-        <v>45996</v>
-      </c>
       <c r="P78" t="n">
-        <v>7.49</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="79">
@@ -3881,49 +3885,49 @@
         <v>170</v>
       </c>
       <c r="B80" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D80" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="C80" s="1" t="n">
+      <c r="E80" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="D80" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E80" s="1" t="n">
+      <c r="F80" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G80" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="F80" t="n">
+      <c r="H80" t="n">
         <v>6.9</v>
       </c>
-      <c r="G80" s="1" t="n">
+      <c r="I80" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="H80" t="n">
+      <c r="J80" t="n">
         <v>7.4</v>
       </c>
-      <c r="I80" s="1" t="n">
+      <c r="K80" s="1" t="n">
         <v>45963</v>
-      </c>
-      <c r="J80" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K80" s="1" t="n">
-        <v>45955</v>
       </c>
       <c r="L80" t="n">
         <v>6.4</v>
       </c>
       <c r="M80" s="1" t="n">
+        <v>45955</v>
+      </c>
+      <c r="N80" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O80" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="N80" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O80" s="1" t="n">
-        <v>45941</v>
-      </c>
       <c r="P80" t="n">
-        <v>7.17</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="81">
@@ -4141,45 +4145,49 @@
         <v>178</v>
       </c>
       <c r="B86" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D86" t="n">
         <v>7.1</v>
       </c>
-      <c r="C86" s="1" t="n">
+      <c r="E86" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="D86" t="n">
+      <c r="F86" t="n">
         <v>6.1</v>
       </c>
-      <c r="E86" s="1" t="n">
+      <c r="G86" s="1" t="n">
         <v>45976</v>
       </c>
-      <c r="F86" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G86" s="1" t="n">
+      <c r="H86" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I86" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="H86" t="n">
+      <c r="J86" t="n">
         <v>6.3</v>
       </c>
-      <c r="I86" s="1" t="n">
+      <c r="K86" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="J86" t="n">
+      <c r="L86" t="n">
         <v>6.9</v>
       </c>
-      <c r="K86" s="1" t="n">
+      <c r="M86" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="L86" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M86" s="1" t="n">
+      <c r="N86" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O86" s="1" t="n">
         <v>45877</v>
       </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>6.6</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="87">
@@ -4237,49 +4245,49 @@
         <v>182</v>
       </c>
       <c r="B88" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D88" t="n">
         <v>7.2</v>
       </c>
-      <c r="C88" s="1" t="n">
+      <c r="E88" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="D88" t="n">
+      <c r="F88" t="n">
         <v>6</v>
       </c>
-      <c r="E88" s="1" t="n">
+      <c r="G88" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="F88" t="n">
+      <c r="H88" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G88" s="1" t="n">
+      <c r="I88" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="H88" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I88" s="1" t="n">
+      <c r="J88" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K88" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="J88" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K88" s="1" t="n">
+      <c r="L88" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M88" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="L88" t="n">
+      <c r="N88" t="n">
         <v>7.5</v>
       </c>
-      <c r="M88" s="1" t="n">
+      <c r="O88" s="1" t="n">
         <v>45941</v>
       </c>
-      <c r="N88" t="n">
-        <v>9</v>
-      </c>
-      <c r="O88" s="1" t="n">
-        <v>45934</v>
-      </c>
       <c r="P88" t="n">
-        <v>7.31</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="89">
@@ -4287,19 +4295,23 @@
         <v>184</v>
       </c>
       <c r="B89" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="C89" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D89" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E89" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D89" t="n">
+      <c r="F89" t="n">
         <v>6.9</v>
       </c>
-      <c r="E89" s="1" t="n">
+      <c r="G89" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
@@ -4309,7 +4321,7 @@
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="90">
@@ -4367,49 +4379,49 @@
         <v>186</v>
       </c>
       <c r="B91" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D91" t="n">
         <v>7.2</v>
       </c>
-      <c r="C91" s="1" t="n">
+      <c r="E91" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D91" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E91" s="1" t="n">
+      <c r="F91" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G91" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F91" t="n">
+      <c r="H91" t="n">
         <v>6.2</v>
       </c>
-      <c r="G91" s="1" t="n">
+      <c r="I91" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H91" t="n">
+      <c r="J91" t="n">
         <v>7.2</v>
       </c>
-      <c r="I91" s="1" t="n">
+      <c r="K91" s="1" t="n">
         <v>46051</v>
       </c>
-      <c r="J91" t="n">
+      <c r="L91" t="n">
         <v>6</v>
       </c>
-      <c r="K91" s="1" t="n">
+      <c r="M91" s="1" t="n">
         <v>46040</v>
       </c>
-      <c r="L91" t="n">
+      <c r="N91" t="n">
         <v>6.8</v>
       </c>
-      <c r="M91" s="1" t="n">
+      <c r="O91" s="1" t="n">
         <v>46028</v>
       </c>
-      <c r="N91" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O91" s="1" t="n">
-        <v>46024</v>
-      </c>
       <c r="P91" t="n">
-        <v>6.66</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="92">
@@ -4537,41 +4549,49 @@
         <v>192</v>
       </c>
       <c r="B95" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D95" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="F95" t="n">
         <v>7.1</v>
       </c>
-      <c r="C95" s="1" t="n">
+      <c r="G95" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D95" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E95" s="1" t="n">
+      <c r="H95" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I95" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F95" t="n">
+      <c r="J95" t="n">
         <v>6.9</v>
       </c>
-      <c r="G95" s="1" t="n">
+      <c r="K95" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H95" t="n">
+      <c r="L95" t="n">
         <v>5.8</v>
       </c>
-      <c r="I95" s="1" t="n">
+      <c r="M95" s="1" t="n">
         <v>46064</v>
       </c>
-      <c r="J95" t="n">
+      <c r="N95" t="n">
         <v>6.2</v>
       </c>
-      <c r="K95" s="1" t="n">
+      <c r="O95" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
       <c r="P95" t="n">
-        <v>6.52</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="96">
@@ -4579,37 +4599,41 @@
         <v>193</v>
       </c>
       <c r="B96" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C96" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D96" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E96" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D96" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E96" s="1" t="n">
+      <c r="F96" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G96" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F96" t="n">
+      <c r="H96" t="n">
         <v>6.9</v>
       </c>
-      <c r="G96" s="1" t="n">
+      <c r="I96" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H96" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I96" s="1" t="n">
+      <c r="J96" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K96" s="1" t="n">
         <v>45900</v>
       </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="n">
-        <v>6.65</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="97">
@@ -4667,49 +4691,49 @@
         <v>195</v>
       </c>
       <c r="B98" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D98" t="n">
         <v>8.4</v>
       </c>
-      <c r="C98" s="1" t="n">
+      <c r="E98" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D98" t="n">
+      <c r="F98" t="n">
         <v>6.1</v>
       </c>
-      <c r="E98" s="1" t="n">
+      <c r="G98" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F98" t="n">
+      <c r="H98" t="n">
         <v>7.7</v>
       </c>
-      <c r="G98" s="1" t="n">
+      <c r="I98" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H98" t="n">
+      <c r="J98" t="n">
         <v>5.8</v>
       </c>
-      <c r="I98" s="1" t="n">
+      <c r="K98" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J98" t="n">
+      <c r="L98" t="n">
         <v>6.4</v>
       </c>
-      <c r="K98" s="1" t="n">
+      <c r="M98" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="L98" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M98" s="1" t="n">
+      <c r="N98" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O98" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="N98" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O98" s="1" t="n">
-        <v>46004</v>
-      </c>
       <c r="P98" t="n">
-        <v>6.89</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="99">
@@ -4770,46 +4794,46 @@
         <v>6.6</v>
       </c>
       <c r="C100" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D100" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E100" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D100" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E100" s="1" t="n">
+      <c r="F100" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G100" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F100" t="n">
+      <c r="H100" t="n">
         <v>6.4</v>
       </c>
-      <c r="G100" s="1" t="n">
+      <c r="I100" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="H100" t="n">
+      <c r="J100" t="n">
         <v>7</v>
       </c>
-      <c r="I100" s="1" t="n">
+      <c r="K100" s="1" t="n">
         <v>46013</v>
       </c>
-      <c r="J100" t="n">
+      <c r="L100" t="n">
         <v>6.9</v>
       </c>
-      <c r="K100" s="1" t="n">
+      <c r="M100" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="L100" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M100" s="1" t="n">
+      <c r="N100" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O100" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="N100" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O100" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P100" t="n">
-        <v>6.63</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="101">
@@ -4817,49 +4841,49 @@
         <v>200</v>
       </c>
       <c r="B101" t="n">
+        <v>7</v>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D101" t="n">
         <v>5.9</v>
       </c>
-      <c r="C101" s="1" t="n">
+      <c r="E101" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D101" t="n">
+      <c r="F101" t="n">
         <v>6.9</v>
       </c>
-      <c r="E101" s="1" t="n">
+      <c r="G101" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F101" t="n">
+      <c r="H101" t="n">
         <v>7.9</v>
       </c>
-      <c r="G101" s="1" t="n">
+      <c r="I101" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H101" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I101" s="1" t="n">
+      <c r="J101" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K101" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J101" t="n">
+      <c r="L101" t="n">
         <v>6.3</v>
       </c>
-      <c r="K101" s="1" t="n">
+      <c r="M101" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L101" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M101" s="1" t="n">
+      <c r="N101" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O101" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="N101" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O101" s="1" t="n">
-        <v>45955</v>
-      </c>
       <c r="P101" t="n">
-        <v>6.66</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="102">
@@ -4917,19 +4941,23 @@
         <v>202</v>
       </c>
       <c r="B103" t="n">
+        <v>7</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D103" t="n">
         <v>7.2</v>
       </c>
-      <c r="C103" s="1" t="n">
+      <c r="E103" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D103" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E103" s="1" t="n">
+      <c r="F103" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G103" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
@@ -4939,7 +4967,7 @@
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>6.9</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="104">
@@ -6225,49 +6253,49 @@
         <v>247</v>
       </c>
       <c r="B136" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D136" t="n">
         <v>6.8</v>
       </c>
-      <c r="C136" s="1" t="n">
+      <c r="E136" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D136" t="n">
+      <c r="F136" t="n">
         <v>7.1</v>
       </c>
-      <c r="E136" s="1" t="n">
+      <c r="G136" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="F136" t="n">
+      <c r="H136" t="n">
         <v>5.8</v>
       </c>
-      <c r="G136" s="1" t="n">
+      <c r="I136" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="H136" t="n">
+      <c r="J136" t="n">
         <v>8.1</v>
       </c>
-      <c r="I136" s="1" t="n">
+      <c r="K136" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J136" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K136" s="1" t="n">
+      <c r="L136" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M136" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="L136" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M136" s="1" t="n">
+      <c r="N136" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O136" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="N136" t="n">
-        <v>7</v>
-      </c>
-      <c r="O136" s="1" t="n">
-        <v>46003</v>
-      </c>
       <c r="P136" t="n">
-        <v>6.86</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="137">
@@ -6275,46 +6303,46 @@
         <v>248</v>
       </c>
       <c r="B137" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D137" t="n">
         <v>6.3</v>
       </c>
-      <c r="C137" s="1" t="n">
+      <c r="E137" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D137" t="n">
+      <c r="F137" t="n">
         <v>6.9</v>
       </c>
-      <c r="E137" s="1" t="n">
+      <c r="G137" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F137" t="n">
+      <c r="H137" t="n">
         <v>7.7</v>
       </c>
-      <c r="G137" s="1" t="n">
+      <c r="I137" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H137" t="n">
+      <c r="J137" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I137" s="1" t="n">
+      <c r="K137" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="J137" t="n">
+      <c r="L137" t="n">
         <v>7.2</v>
       </c>
-      <c r="K137" s="1" t="n">
+      <c r="M137" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="L137" t="n">
+      <c r="N137" t="n">
         <v>7.7</v>
       </c>
-      <c r="M137" s="1" t="n">
+      <c r="O137" s="1" t="n">
         <v>46046</v>
-      </c>
-      <c r="N137" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O137" s="1" t="n">
-        <v>46039</v>
       </c>
       <c r="P137" t="n">
         <v>7.26</v>
@@ -6795,46 +6823,46 @@
         <v>273</v>
       </c>
       <c r="B148" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D148" t="n">
         <v>6.4</v>
       </c>
-      <c r="C148" s="1" t="n">
+      <c r="E148" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="F148" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G148" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D148" t="n">
+      <c r="H148" t="n">
         <v>7</v>
       </c>
-      <c r="E148" s="1" t="n">
+      <c r="I148" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F148" t="n">
+      <c r="J148" t="n">
         <v>6.2</v>
       </c>
-      <c r="G148" s="1" t="n">
+      <c r="K148" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H148" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I148" s="1" t="n">
+      <c r="L148" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M148" s="1" t="n">
         <v>46065</v>
       </c>
-      <c r="J148" t="n">
+      <c r="N148" t="n">
         <v>7.1</v>
       </c>
-      <c r="K148" s="1" t="n">
+      <c r="O148" s="1" t="n">
         <v>46061</v>
-      </c>
-      <c r="L148" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M148" s="1" t="n">
-        <v>46053</v>
-      </c>
-      <c r="N148" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O148" s="1" t="n">
-        <v>46046</v>
       </c>
       <c r="P148" t="n">
         <v>6.67</v>
@@ -6941,49 +6969,49 @@
         <v>276</v>
       </c>
       <c r="B151" t="n">
+        <v>7</v>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D151" t="n">
         <v>6.3</v>
       </c>
-      <c r="C151" s="1" t="n">
+      <c r="E151" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D151" t="n">
+      <c r="F151" t="n">
         <v>5.6</v>
       </c>
-      <c r="E151" s="1" t="n">
+      <c r="G151" s="1" t="n">
         <v>45921</v>
       </c>
-      <c r="F151" t="n">
+      <c r="H151" t="n">
         <v>7.5</v>
       </c>
-      <c r="G151" s="1" t="n">
+      <c r="I151" s="1" t="n">
         <v>45913</v>
       </c>
-      <c r="H151" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I151" s="1" t="n">
+      <c r="J151" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K151" s="1" t="n">
         <v>45901</v>
       </c>
-      <c r="J151" t="n">
+      <c r="L151" t="n">
         <v>7.9</v>
       </c>
-      <c r="K151" s="1" t="n">
+      <c r="M151" s="1" t="n">
         <v>45892</v>
       </c>
-      <c r="L151" t="n">
+      <c r="N151" t="n">
         <v>6.2</v>
       </c>
-      <c r="M151" s="1" t="n">
+      <c r="O151" s="1" t="n">
         <v>45888</v>
       </c>
-      <c r="N151" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O151" s="1" t="n">
-        <v>45885</v>
-      </c>
       <c r="P151" t="n">
-        <v>6.74</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="152">
@@ -7129,37 +7157,41 @@
         <v>280</v>
       </c>
       <c r="B155" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46080</v>
+        <v>46087</v>
       </c>
       <c r="D155" t="n">
         <v>6.4</v>
       </c>
       <c r="E155" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="F155" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G155" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F155" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G155" s="1" t="n">
+      <c r="H155" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I155" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H155" t="n">
+      <c r="J155" t="n">
         <v>6.2</v>
       </c>
-      <c r="I155" s="1" t="n">
+      <c r="K155" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="n">
-        <v>6.38</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="156">
@@ -7167,49 +7199,49 @@
         <v>281</v>
       </c>
       <c r="B156" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C156" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D156" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E156" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D156" t="n">
+      <c r="F156" t="n">
         <v>6.3</v>
       </c>
-      <c r="E156" s="1" t="n">
+      <c r="G156" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="F156" t="n">
+      <c r="H156" t="n">
         <v>8.1</v>
       </c>
-      <c r="G156" s="1" t="n">
+      <c r="I156" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="H156" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I156" s="1" t="n">
+      <c r="J156" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K156" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="J156" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K156" s="1" t="n">
+      <c r="L156" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M156" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="L156" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M156" s="1" t="n">
+      <c r="N156" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O156" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="N156" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O156" s="1" t="n">
-        <v>46011</v>
-      </c>
       <c r="P156" t="n">
-        <v>6.83</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="157">
@@ -7220,46 +7252,46 @@
         <v>7</v>
       </c>
       <c r="C157" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D157" t="n">
+        <v>7</v>
+      </c>
+      <c r="E157" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D157" t="n">
+      <c r="F157" t="n">
         <v>7.1</v>
       </c>
-      <c r="E157" s="1" t="n">
+      <c r="G157" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F157" t="n">
+      <c r="H157" t="n">
         <v>7.2</v>
       </c>
-      <c r="G157" s="1" t="n">
+      <c r="I157" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H157" t="n">
+      <c r="J157" t="n">
         <v>7</v>
       </c>
-      <c r="I157" s="1" t="n">
+      <c r="K157" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J157" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K157" s="1" t="n">
+      <c r="L157" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M157" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L157" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M157" s="1" t="n">
+      <c r="N157" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O157" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="N157" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O157" s="1" t="n">
-        <v>46011</v>
-      </c>
       <c r="P157" t="n">
-        <v>6.93</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="158">
@@ -7363,49 +7395,49 @@
         <v>286</v>
       </c>
       <c r="B160" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D160" t="n">
         <v>7.4</v>
       </c>
-      <c r="C160" s="1" t="n">
+      <c r="E160" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D160" t="n">
+      <c r="F160" t="n">
         <v>6.9</v>
       </c>
-      <c r="E160" s="1" t="n">
+      <c r="G160" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F160" t="n">
+      <c r="H160" t="n">
         <v>7.4</v>
       </c>
-      <c r="G160" s="1" t="n">
+      <c r="I160" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H160" t="n">
+      <c r="J160" t="n">
         <v>6.2</v>
       </c>
-      <c r="I160" s="1" t="n">
+      <c r="K160" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="J160" t="n">
+      <c r="L160" t="n">
         <v>7.8</v>
       </c>
-      <c r="K160" s="1" t="n">
+      <c r="M160" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L160" t="n">
+      <c r="N160" t="n">
         <v>7.4</v>
       </c>
-      <c r="M160" s="1" t="n">
+      <c r="O160" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="N160" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O160" s="1" t="n">
-        <v>46005</v>
-      </c>
       <c r="P160" t="n">
-        <v>7.26</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="161">
@@ -7463,49 +7495,49 @@
         <v>288</v>
       </c>
       <c r="B162" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="C162" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D162" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E162" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D162" t="n">
+      <c r="F162" t="n">
         <v>6.1</v>
       </c>
-      <c r="E162" s="1" t="n">
+      <c r="G162" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F162" t="n">
+      <c r="H162" t="n">
         <v>6.3</v>
       </c>
-      <c r="G162" s="1" t="n">
+      <c r="I162" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="H162" t="n">
+      <c r="J162" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I162" s="1" t="n">
+      <c r="K162" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="J162" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K162" s="1" t="n">
+      <c r="L162" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M162" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="L162" t="n">
+      <c r="N162" t="n">
         <v>7.6</v>
       </c>
-      <c r="M162" s="1" t="n">
+      <c r="O162" s="1" t="n">
         <v>45961</v>
       </c>
-      <c r="N162" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O162" s="1" t="n">
-        <v>45955</v>
-      </c>
       <c r="P162" t="n">
-        <v>6.99</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="163">
@@ -7516,46 +7548,46 @@
         <v>6.4</v>
       </c>
       <c r="C163" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D163" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E163" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D163" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E163" s="1" t="n">
+      <c r="F163" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G163" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F163" t="n">
+      <c r="H163" t="n">
         <v>6.8</v>
       </c>
-      <c r="G163" s="1" t="n">
+      <c r="I163" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H163" t="n">
+      <c r="J163" t="n">
         <v>6.3</v>
       </c>
-      <c r="I163" s="1" t="n">
+      <c r="K163" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J163" t="n">
+      <c r="L163" t="n">
         <v>7.2</v>
       </c>
-      <c r="K163" s="1" t="n">
+      <c r="M163" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="L163" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M163" s="1" t="n">
+      <c r="N163" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O163" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="N163" t="n">
-        <v>7</v>
-      </c>
-      <c r="O163" s="1" t="n">
-        <v>45998</v>
-      </c>
       <c r="P163" t="n">
-        <v>6.67</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="164">
@@ -7736,38 +7768,42 @@
         <v>6.5</v>
       </c>
       <c r="C168" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D168" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E168" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D168" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E168" s="1" t="n">
+      <c r="F168" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G168" s="1" t="n">
         <v>45987</v>
       </c>
-      <c r="F168" t="n">
+      <c r="H168" t="n">
         <v>5.9</v>
       </c>
-      <c r="G168" s="1" t="n">
+      <c r="I168" s="1" t="n">
         <v>45900</v>
       </c>
-      <c r="H168" t="n">
+      <c r="J168" t="n">
         <v>6.8</v>
       </c>
-      <c r="I168" s="1" t="n">
+      <c r="K168" s="1" t="n">
         <v>45879</v>
       </c>
-      <c r="J168" t="n">
+      <c r="L168" t="n">
         <v>6.3</v>
       </c>
-      <c r="K168" s="1" t="n">
+      <c r="M168" s="1" t="n">
         <v>45872</v>
       </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="n">
-        <v>6.4</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="169">
@@ -7775,49 +7811,49 @@
         <v>295</v>
       </c>
       <c r="B169" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C169" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D169" t="n">
         <v>7.9</v>
       </c>
-      <c r="C169" s="1" t="n">
+      <c r="E169" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D169" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E169" s="1" t="n">
+      <c r="F169" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G169" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F169" t="n">
+      <c r="H169" t="n">
         <v>7.3</v>
       </c>
-      <c r="G169" s="1" t="n">
+      <c r="I169" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H169" t="n">
+      <c r="J169" t="n">
         <v>6.8</v>
       </c>
-      <c r="I169" s="1" t="n">
+      <c r="K169" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J169" t="n">
+      <c r="L169" t="n">
         <v>7.3</v>
       </c>
-      <c r="K169" s="1" t="n">
+      <c r="M169" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="L169" t="n">
+      <c r="N169" t="n">
         <v>7.5</v>
       </c>
-      <c r="M169" s="1" t="n">
+      <c r="O169" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N169" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O169" s="1" t="n">
-        <v>45990</v>
-      </c>
       <c r="P169" t="n">
-        <v>7.33</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="170">
@@ -7875,49 +7911,49 @@
         <v>298</v>
       </c>
       <c r="B171" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C171" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D171" t="n">
         <v>6.9</v>
       </c>
-      <c r="C171" s="1" t="n">
+      <c r="E171" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D171" t="n">
+      <c r="F171" t="n">
         <v>6.3</v>
       </c>
-      <c r="E171" s="1" t="n">
+      <c r="G171" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="F171" t="n">
+      <c r="H171" t="n">
         <v>6</v>
       </c>
-      <c r="G171" s="1" t="n">
+      <c r="I171" s="1" t="n">
         <v>45994</v>
       </c>
-      <c r="H171" t="n">
+      <c r="J171" t="n">
         <v>6.1</v>
       </c>
-      <c r="I171" s="1" t="n">
+      <c r="K171" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J171" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K171" s="1" t="n">
+      <c r="L171" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M171" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="L171" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M171" s="1" t="n">
+      <c r="N171" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O171" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="N171" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O171" s="1" t="n">
-        <v>45962</v>
-      </c>
       <c r="P171" t="n">
-        <v>6.43</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="172">
@@ -7983,46 +8019,46 @@
         <v>302</v>
       </c>
       <c r="B174" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C174" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D174" t="n">
         <v>7.2</v>
       </c>
-      <c r="C174" s="1" t="n">
+      <c r="E174" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D174" t="n">
+      <c r="F174" t="n">
         <v>6.4</v>
       </c>
-      <c r="E174" s="1" t="n">
+      <c r="G174" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F174" t="n">
+      <c r="H174" t="n">
         <v>7.6</v>
       </c>
-      <c r="G174" s="1" t="n">
+      <c r="I174" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H174" t="n">
+      <c r="J174" t="n">
         <v>7</v>
       </c>
-      <c r="I174" s="1" t="n">
+      <c r="K174" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="J174" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K174" s="1" t="n">
+      <c r="L174" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M174" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L174" t="n">
+      <c r="N174" t="n">
         <v>5.5</v>
       </c>
-      <c r="M174" s="1" t="n">
+      <c r="O174" s="1" t="n">
         <v>45954</v>
-      </c>
-      <c r="N174" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O174" s="1" t="n">
-        <v>45928</v>
       </c>
       <c r="P174" t="n">
         <v>6.67</v>
@@ -8033,49 +8069,49 @@
         <v>303</v>
       </c>
       <c r="B175" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46081</v>
+        <v>46089</v>
       </c>
       <c r="D175" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46074</v>
+        <v>46085</v>
       </c>
       <c r="F175" t="n">
         <v>6.9</v>
       </c>
       <c r="G175" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="H175" t="n">
+        <v>7</v>
+      </c>
+      <c r="I175" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="J175" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K175" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H175" t="n">
+      <c r="L175" t="n">
         <v>6.8</v>
       </c>
-      <c r="I175" s="1" t="n">
+      <c r="M175" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="J175" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K175" s="1" t="n">
+      <c r="N175" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O175" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="L175" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M175" s="1" t="n">
-        <v>45994</v>
-      </c>
-      <c r="N175" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O175" s="1" t="n">
-        <v>45990</v>
-      </c>
       <c r="P175" t="n">
-        <v>6.91</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="176">
@@ -8133,49 +8169,49 @@
         <v>306</v>
       </c>
       <c r="B177" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="C177" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D177" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E177" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D177" t="n">
+      <c r="F177" t="n">
         <v>6.9</v>
       </c>
-      <c r="E177" s="1" t="n">
+      <c r="G177" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="F177" t="n">
+      <c r="H177" t="n">
         <v>6.3</v>
       </c>
-      <c r="G177" s="1" t="n">
+      <c r="I177" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H177" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I177" s="1" t="n">
+      <c r="J177" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K177" s="1" t="n">
         <v>45953</v>
       </c>
-      <c r="J177" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K177" s="1" t="n">
+      <c r="L177" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M177" s="1" t="n">
         <v>45932</v>
-      </c>
-      <c r="L177" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M177" s="1" t="n">
-        <v>45927</v>
       </c>
       <c r="N177" t="n">
         <v>6.9</v>
       </c>
       <c r="O177" s="1" t="n">
-        <v>45921</v>
+        <v>45927</v>
       </c>
       <c r="P177" t="n">
-        <v>6.69</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="178">
@@ -8186,46 +8222,46 @@
         <v>6.5</v>
       </c>
       <c r="C178" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D178" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E178" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D178" t="n">
+      <c r="F178" t="n">
         <v>6.3</v>
       </c>
-      <c r="E178" s="1" t="n">
+      <c r="G178" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="F178" t="n">
+      <c r="H178" t="n">
         <v>7</v>
       </c>
-      <c r="G178" s="1" t="n">
+      <c r="I178" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="H178" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I178" s="1" t="n">
+      <c r="J178" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K178" s="1" t="n">
         <v>45961</v>
       </c>
-      <c r="J178" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K178" s="1" t="n">
+      <c r="L178" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M178" s="1" t="n">
         <v>45953</v>
       </c>
-      <c r="L178" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M178" s="1" t="n">
+      <c r="N178" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O178" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="N178" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O178" s="1" t="n">
-        <v>45932</v>
-      </c>
       <c r="P178" t="n">
-        <v>6.49</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="179">
@@ -8233,49 +8269,49 @@
         <v>309</v>
       </c>
       <c r="B179" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C179" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D179" t="n">
         <v>8</v>
       </c>
-      <c r="C179" s="1" t="n">
+      <c r="E179" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D179" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E179" s="1" t="n">
+      <c r="F179" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G179" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F179" t="n">
+      <c r="H179" t="n">
         <v>5.2</v>
       </c>
-      <c r="G179" s="1" t="n">
+      <c r="I179" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H179" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I179" s="1" t="n">
+      <c r="J179" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K179" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="J179" t="n">
+      <c r="L179" t="n">
         <v>6.3</v>
       </c>
-      <c r="K179" s="1" t="n">
+      <c r="M179" s="1" t="n">
         <v>46005</v>
-      </c>
-      <c r="L179" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M179" s="1" t="n">
-        <v>45990</v>
       </c>
       <c r="N179" t="n">
         <v>6.4</v>
       </c>
       <c r="O179" s="1" t="n">
-        <v>45983</v>
+        <v>45990</v>
       </c>
       <c r="P179" t="n">
-        <v>6.49</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="180">
@@ -8503,49 +8539,49 @@
         <v>315</v>
       </c>
       <c r="B185" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C185" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D185" t="n">
         <v>7.7</v>
       </c>
-      <c r="C185" s="1" t="n">
+      <c r="E185" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D185" t="n">
+      <c r="F185" t="n">
         <v>6.9</v>
       </c>
-      <c r="E185" s="1" t="n">
+      <c r="G185" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="F185" t="n">
+      <c r="H185" t="n">
         <v>7.4</v>
       </c>
-      <c r="G185" s="1" t="n">
+      <c r="I185" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H185" t="n">
+      <c r="J185" t="n">
         <v>8.1</v>
       </c>
-      <c r="I185" s="1" t="n">
+      <c r="K185" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="J185" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K185" s="1" t="n">
+      <c r="L185" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M185" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="L185" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M185" s="1" t="n">
+      <c r="N185" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O185" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="N185" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O185" s="1" t="n">
-        <v>46043</v>
-      </c>
       <c r="P185" t="n">
-        <v>7.17</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="186">
@@ -8583,49 +8619,49 @@
         <v>317</v>
       </c>
       <c r="B187" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C187" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D187" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E187" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D187" t="n">
+      <c r="F187" t="n">
         <v>6.9</v>
       </c>
-      <c r="E187" s="1" t="n">
+      <c r="G187" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F187" t="n">
+      <c r="H187" t="n">
         <v>6.1</v>
       </c>
-      <c r="G187" s="1" t="n">
+      <c r="I187" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H187" t="n">
+      <c r="J187" t="n">
         <v>6.4</v>
       </c>
-      <c r="I187" s="1" t="n">
+      <c r="K187" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="J187" t="n">
+      <c r="L187" t="n">
         <v>6.1</v>
       </c>
-      <c r="K187" s="1" t="n">
+      <c r="M187" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="L187" t="n">
+      <c r="N187" t="n">
         <v>6.3</v>
       </c>
-      <c r="M187" s="1" t="n">
+      <c r="O187" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="N187" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O187" s="1" t="n">
-        <v>46010</v>
-      </c>
       <c r="P187" t="n">
-        <v>6.5</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="188">
@@ -8683,37 +8719,41 @@
         <v>319</v>
       </c>
       <c r="B189" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D189" t="n">
         <v>7.6</v>
       </c>
-      <c r="C189" s="1" t="n">
+      <c r="E189" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D189" t="n">
+      <c r="F189" t="n">
         <v>7.3</v>
       </c>
-      <c r="E189" s="1" t="n">
+      <c r="G189" s="1" t="n">
         <v>46076</v>
       </c>
-      <c r="F189" t="n">
+      <c r="H189" t="n">
         <v>6.9</v>
       </c>
-      <c r="G189" s="1" t="n">
+      <c r="I189" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="H189" t="n">
+      <c r="J189" t="n">
         <v>7.3</v>
       </c>
-      <c r="I189" s="1" t="n">
+      <c r="K189" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="n">
-        <v>7.28</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="190">
@@ -8817,49 +8857,49 @@
         <v>322</v>
       </c>
       <c r="B192" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C192" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D192" t="n">
         <v>6.2</v>
       </c>
-      <c r="C192" s="1" t="n">
+      <c r="E192" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="D192" t="n">
+      <c r="F192" t="n">
         <v>8.5</v>
       </c>
-      <c r="E192" s="1" t="n">
+      <c r="G192" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="F192" t="n">
+      <c r="H192" t="n">
         <v>6.2</v>
       </c>
-      <c r="G192" s="1" t="n">
+      <c r="I192" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="H192" t="n">
+      <c r="J192" t="n">
         <v>7</v>
       </c>
-      <c r="I192" s="1" t="n">
+      <c r="K192" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="J192" t="n">
+      <c r="L192" t="n">
         <v>7.1</v>
       </c>
-      <c r="K192" s="1" t="n">
+      <c r="M192" s="1" t="n">
         <v>45940</v>
       </c>
-      <c r="L192" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M192" s="1" t="n">
+      <c r="N192" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O192" s="1" t="n">
         <v>45933</v>
       </c>
-      <c r="N192" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O192" s="1" t="n">
-        <v>45884</v>
-      </c>
       <c r="P192" t="n">
-        <v>7.13</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="193">
@@ -9206,43 +9246,43 @@
         <v>6.3</v>
       </c>
       <c r="C201" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D201" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E201" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D201" t="n">
+      <c r="F201" t="n">
         <v>6.4</v>
       </c>
-      <c r="E201" s="1" t="n">
+      <c r="G201" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="F201" t="n">
+      <c r="H201" t="n">
         <v>6.3</v>
       </c>
-      <c r="G201" s="1" t="n">
+      <c r="I201" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="H201" t="n">
+      <c r="J201" t="n">
         <v>6.8</v>
       </c>
-      <c r="I201" s="1" t="n">
+      <c r="K201" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="J201" t="n">
+      <c r="L201" t="n">
         <v>7.1</v>
       </c>
-      <c r="K201" s="1" t="n">
+      <c r="M201" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="L201" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M201" s="1" t="n">
+      <c r="N201" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O201" s="1" t="n">
         <v>45962</v>
-      </c>
-      <c r="N201" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O201" s="1" t="n">
-        <v>45921</v>
       </c>
       <c r="P201" t="n">
         <v>6.53</v>
@@ -9253,49 +9293,49 @@
         <v>336</v>
       </c>
       <c r="B202" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C202" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D202" t="n">
         <v>6.8</v>
       </c>
-      <c r="C202" s="1" t="n">
+      <c r="E202" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D202" t="n">
+      <c r="F202" t="n">
         <v>6.9</v>
       </c>
-      <c r="E202" s="1" t="n">
+      <c r="G202" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F202" t="n">
+      <c r="H202" t="n">
         <v>6.1</v>
       </c>
-      <c r="G202" s="1" t="n">
+      <c r="I202" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H202" t="n">
+      <c r="J202" t="n">
         <v>7.4</v>
       </c>
-      <c r="I202" s="1" t="n">
+      <c r="K202" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="J202" t="n">
+      <c r="L202" t="n">
         <v>6.8</v>
       </c>
-      <c r="K202" s="1" t="n">
+      <c r="M202" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="L202" t="n">
+      <c r="N202" t="n">
         <v>6.2</v>
       </c>
-      <c r="M202" s="1" t="n">
+      <c r="O202" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="N202" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O202" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P202" t="n">
-        <v>6.73</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="203">
@@ -9303,49 +9343,49 @@
         <v>337</v>
       </c>
       <c r="B203" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C203" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D203" t="n">
         <v>6.9</v>
       </c>
-      <c r="C203" s="1" t="n">
+      <c r="E203" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D203" t="n">
+      <c r="F203" t="n">
         <v>6.8</v>
       </c>
-      <c r="E203" s="1" t="n">
+      <c r="G203" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F203" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G203" s="1" t="n">
+      <c r="H203" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I203" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H203" t="n">
+      <c r="J203" t="n">
         <v>7.5</v>
       </c>
-      <c r="I203" s="1" t="n">
+      <c r="K203" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J203" t="n">
+      <c r="L203" t="n">
         <v>6.9</v>
       </c>
-      <c r="K203" s="1" t="n">
+      <c r="M203" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="L203" t="n">
+      <c r="N203" t="n">
         <v>7.1</v>
       </c>
-      <c r="M203" s="1" t="n">
+      <c r="O203" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N203" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O203" s="1" t="n">
-        <v>45990</v>
-      </c>
       <c r="P203" t="n">
-        <v>6.9</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="204">
@@ -9383,31 +9423,35 @@
         <v>339</v>
       </c>
       <c r="B205" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D205" t="n">
         <v>6.8</v>
       </c>
-      <c r="C205" s="1" t="n">
+      <c r="E205" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D205" t="n">
+      <c r="F205" t="n">
         <v>7</v>
       </c>
-      <c r="E205" s="1" t="n">
+      <c r="G205" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F205" t="n">
+      <c r="H205" t="n">
         <v>6.9</v>
       </c>
-      <c r="G205" s="1" t="n">
+      <c r="I205" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="H205" t="n">
+      <c r="J205" t="n">
         <v>6</v>
       </c>
-      <c r="I205" s="1" t="n">
+      <c r="K205" s="1" t="n">
         <v>45899</v>
       </c>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
@@ -9521,49 +9565,49 @@
         <v>342</v>
       </c>
       <c r="B208" t="n">
-        <v>6.6</v>
+        <v>8.9</v>
       </c>
       <c r="C208" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D208" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E208" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D208" t="n">
+      <c r="F208" t="n">
         <v>7.1</v>
       </c>
-      <c r="E208" s="1" t="n">
+      <c r="G208" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="F208" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G208" s="1" t="n">
+      <c r="H208" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I208" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H208" t="n">
+      <c r="J208" t="n">
         <v>7</v>
       </c>
-      <c r="I208" s="1" t="n">
+      <c r="K208" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="J208" t="n">
+      <c r="L208" t="n">
         <v>7.1</v>
       </c>
-      <c r="K208" s="1" t="n">
+      <c r="M208" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="L208" t="n">
+      <c r="N208" t="n">
         <v>6.9</v>
       </c>
-      <c r="M208" s="1" t="n">
+      <c r="O208" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N208" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="O208" s="1" t="n">
-        <v>45949</v>
-      </c>
       <c r="P208" t="n">
-        <v>7.13</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="209">
@@ -9971,49 +10015,49 @@
         <v>351</v>
       </c>
       <c r="B217" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C217" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D217" t="n">
         <v>5.8</v>
       </c>
-      <c r="C217" s="1" t="n">
+      <c r="E217" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="D217" t="n">
+      <c r="F217" t="n">
         <v>6.8</v>
       </c>
-      <c r="E217" s="1" t="n">
+      <c r="G217" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="F217" t="n">
+      <c r="H217" t="n">
         <v>7.3</v>
       </c>
-      <c r="G217" s="1" t="n">
+      <c r="I217" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H217" t="n">
+      <c r="J217" t="n">
         <v>6.3</v>
       </c>
-      <c r="I217" s="1" t="n">
+      <c r="K217" s="1" t="n">
         <v>45970</v>
       </c>
-      <c r="J217" t="n">
+      <c r="L217" t="n">
         <v>6.8</v>
       </c>
-      <c r="K217" s="1" t="n">
+      <c r="M217" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="L217" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M217" s="1" t="n">
+      <c r="N217" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O217" s="1" t="n">
         <v>45949</v>
       </c>
-      <c r="N217" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O217" s="1" t="n">
-        <v>45935</v>
-      </c>
       <c r="P217" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="218">
@@ -10041,49 +10085,49 @@
         <v>353</v>
       </c>
       <c r="B219" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="C219" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D219" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E219" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D219" t="n">
+      <c r="F219" t="n">
         <v>7.9</v>
       </c>
-      <c r="E219" s="1" t="n">
+      <c r="G219" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F219" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G219" s="1" t="n">
+      <c r="H219" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I219" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H219" t="n">
+      <c r="J219" t="n">
         <v>6.8</v>
       </c>
-      <c r="I219" s="1" t="n">
+      <c r="K219" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="J219" t="n">
+      <c r="L219" t="n">
         <v>8.1</v>
       </c>
-      <c r="K219" s="1" t="n">
+      <c r="M219" s="1" t="n">
         <v>46058</v>
       </c>
-      <c r="L219" t="n">
+      <c r="N219" t="n">
         <v>6.1</v>
       </c>
-      <c r="M219" s="1" t="n">
+      <c r="O219" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="N219" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O219" s="1" t="n">
-        <v>46046</v>
-      </c>
       <c r="P219" t="n">
-        <v>6.99</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="220">
@@ -10117,41 +10161,45 @@
         <v>356</v>
       </c>
       <c r="B221" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D221" t="n">
         <v>6.8</v>
       </c>
-      <c r="C221" s="1" t="n">
+      <c r="E221" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D221" t="n">
+      <c r="F221" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="E221" s="1" t="n">
+      <c r="G221" s="1" t="n">
         <v>46072</v>
       </c>
-      <c r="F221" t="n">
+      <c r="H221" t="n">
         <v>6.9</v>
       </c>
-      <c r="G221" s="1" t="n">
+      <c r="I221" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H221" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I221" s="1" t="n">
+      <c r="J221" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K221" s="1" t="n">
         <v>45920</v>
       </c>
-      <c r="J221" t="n">
+      <c r="L221" t="n">
         <v>7.1</v>
       </c>
-      <c r="K221" s="1" t="n">
+      <c r="M221" s="1" t="n">
         <v>45911</v>
       </c>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="n">
-        <v>7.14</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="222">
@@ -10159,49 +10207,49 @@
         <v>357</v>
       </c>
       <c r="B222" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C222" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D222" t="n">
         <v>7.5</v>
       </c>
-      <c r="C222" s="1" t="n">
+      <c r="E222" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D222" t="n">
+      <c r="F222" t="n">
         <v>7.1</v>
       </c>
-      <c r="E222" s="1" t="n">
+      <c r="G222" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F222" t="n">
+      <c r="H222" t="n">
         <v>6.4</v>
       </c>
-      <c r="G222" s="1" t="n">
+      <c r="I222" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H222" t="n">
+      <c r="J222" t="n">
         <v>7</v>
       </c>
-      <c r="I222" s="1" t="n">
+      <c r="K222" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="J222" t="n">
+      <c r="L222" t="n">
         <v>7.4</v>
       </c>
-      <c r="K222" s="1" t="n">
+      <c r="M222" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L222" t="n">
+      <c r="N222" t="n">
         <v>6.9</v>
       </c>
-      <c r="M222" s="1" t="n">
+      <c r="O222" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="N222" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O222" s="1" t="n">
-        <v>46004</v>
-      </c>
       <c r="P222" t="n">
-        <v>7.16</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="223">
@@ -10259,49 +10307,49 @@
         <v>360</v>
       </c>
       <c r="B224" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C224" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D224" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E224" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="F224" t="n">
         <v>7.2</v>
       </c>
-      <c r="C224" s="1" t="n">
+      <c r="G224" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="D224" t="n">
+      <c r="H224" t="n">
         <v>7.2</v>
       </c>
-      <c r="E224" s="1" t="n">
+      <c r="I224" s="1" t="n">
         <v>46061</v>
-      </c>
-      <c r="F224" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="G224" s="1" t="n">
-        <v>46058</v>
-      </c>
-      <c r="H224" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I224" s="1" t="n">
-        <v>46052</v>
       </c>
       <c r="J224" t="n">
         <v>6.8</v>
       </c>
       <c r="K224" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="L224" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M224" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="N224" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O224" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="L224" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M224" s="1" t="n">
-        <v>45989</v>
-      </c>
-      <c r="N224" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O224" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P224" t="n">
-        <v>6.94</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="225">
@@ -10379,37 +10427,41 @@
         <v>365</v>
       </c>
       <c r="B227" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C227" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D227" t="n">
         <v>7</v>
       </c>
-      <c r="C227" s="1" t="n">
+      <c r="E227" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D227" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E227" s="1" t="n">
+      <c r="F227" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G227" s="1" t="n">
         <v>45884</v>
       </c>
-      <c r="F227" t="n">
+      <c r="H227" t="n">
         <v>7</v>
       </c>
-      <c r="G227" s="1" t="n">
+      <c r="I227" s="1" t="n">
         <v>45879</v>
       </c>
-      <c r="H227" t="n">
+      <c r="J227" t="n">
         <v>7.1</v>
       </c>
-      <c r="I227" s="1" t="n">
+      <c r="K227" s="1" t="n">
         <v>45873</v>
       </c>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="n">
-        <v>6.93</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="228">
@@ -10567,49 +10619,49 @@
         <v>370</v>
       </c>
       <c r="B231" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C231" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D231" t="n">
         <v>6.3</v>
       </c>
-      <c r="C231" s="1" t="n">
+      <c r="E231" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D231" t="n">
+      <c r="F231" t="n">
         <v>5.8</v>
       </c>
-      <c r="E231" s="1" t="n">
+      <c r="G231" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F231" t="n">
+      <c r="H231" t="n">
         <v>7.6</v>
       </c>
-      <c r="G231" s="1" t="n">
+      <c r="I231" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H231" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I231" s="1" t="n">
+      <c r="J231" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K231" s="1" t="n">
         <v>46060</v>
-      </c>
-      <c r="J231" t="n">
-        <v>6</v>
-      </c>
-      <c r="K231" s="1" t="n">
-        <v>46054</v>
       </c>
       <c r="L231" t="n">
         <v>6</v>
       </c>
       <c r="M231" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="N231" t="n">
+        <v>6</v>
+      </c>
+      <c r="O231" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N231" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O231" s="1" t="n">
-        <v>45955</v>
-      </c>
       <c r="P231" t="n">
-        <v>6.59</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="232">
@@ -10717,49 +10769,49 @@
         <v>373</v>
       </c>
       <c r="B234" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C234" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D234" t="n">
+        <v>7</v>
+      </c>
+      <c r="E234" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="F234" t="n">
         <v>6.2</v>
       </c>
-      <c r="C234" s="1" t="n">
+      <c r="G234" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D234" t="n">
+      <c r="H234" t="n">
         <v>6.8</v>
       </c>
-      <c r="E234" s="1" t="n">
+      <c r="I234" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="F234" t="n">
+      <c r="J234" t="n">
         <v>7.2</v>
       </c>
-      <c r="G234" s="1" t="n">
+      <c r="K234" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H234" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I234" s="1" t="n">
+      <c r="L234" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M234" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="J234" t="n">
+      <c r="N234" t="n">
         <v>6</v>
       </c>
-      <c r="K234" s="1" t="n">
+      <c r="O234" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L234" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M234" s="1" t="n">
-        <v>46046</v>
-      </c>
-      <c r="N234" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O234" s="1" t="n">
-        <v>46039</v>
-      </c>
       <c r="P234" t="n">
-        <v>6.49</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="235">
@@ -11197,19 +11249,23 @@
         <v>386</v>
       </c>
       <c r="B246" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C246" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D246" t="n">
         <v>6.8</v>
       </c>
-      <c r="C246" s="1" t="n">
+      <c r="E246" s="1" t="n">
         <v>45900</v>
       </c>
-      <c r="D246" t="n">
+      <c r="F246" t="n">
         <v>6.4</v>
       </c>
-      <c r="E246" s="1" t="n">
+      <c r="G246" s="1" t="n">
         <v>45879</v>
       </c>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
@@ -11219,7 +11275,7 @@
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="n">
-        <v>6.6</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="247">
@@ -11457,49 +11513,49 @@
         <v>395</v>
       </c>
       <c r="B254" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="C254" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D254" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E254" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D254" t="n">
+      <c r="F254" t="n">
         <v>7.6</v>
       </c>
-      <c r="E254" s="1" t="n">
+      <c r="G254" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F254" t="n">
+      <c r="H254" t="n">
         <v>6.4</v>
       </c>
-      <c r="G254" s="1" t="n">
+      <c r="I254" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H254" t="n">
+      <c r="J254" t="n">
         <v>6.8</v>
       </c>
-      <c r="I254" s="1" t="n">
+      <c r="K254" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="J254" t="n">
+      <c r="L254" t="n">
         <v>6.2</v>
       </c>
-      <c r="K254" s="1" t="n">
+      <c r="M254" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="L254" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M254" s="1" t="n">
+      <c r="N254" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O254" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="N254" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O254" s="1" t="n">
-        <v>46039</v>
-      </c>
       <c r="P254" t="n">
-        <v>6.7</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="255">
@@ -11843,49 +11899,49 @@
         <v>405</v>
       </c>
       <c r="B264" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C264" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D264" t="n">
         <v>6.1</v>
       </c>
-      <c r="C264" s="1" t="n">
+      <c r="E264" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="D264" t="n">
+      <c r="F264" t="n">
         <v>7.3</v>
       </c>
-      <c r="E264" s="1" t="n">
+      <c r="G264" s="1" t="n">
         <v>45993</v>
       </c>
-      <c r="F264" t="n">
+      <c r="H264" t="n">
         <v>6.4</v>
       </c>
-      <c r="G264" s="1" t="n">
+      <c r="I264" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="H264" t="n">
+      <c r="J264" t="n">
         <v>6.3</v>
       </c>
-      <c r="I264" s="1" t="n">
+      <c r="K264" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="J264" t="n">
+      <c r="L264" t="n">
         <v>7.2</v>
       </c>
-      <c r="K264" s="1" t="n">
+      <c r="M264" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="L264" t="n">
+      <c r="N264" t="n">
         <v>7.4</v>
       </c>
-      <c r="M264" s="1" t="n">
+      <c r="O264" s="1" t="n">
         <v>45928</v>
       </c>
-      <c r="N264" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O264" s="1" t="n">
-        <v>45920</v>
-      </c>
       <c r="P264" t="n">
-        <v>6.79</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="265">
@@ -12016,46 +12072,46 @@
         <v>6.4</v>
       </c>
       <c r="C268" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D268" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E268" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D268" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E268" s="1" t="n">
+      <c r="F268" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G268" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F268" t="n">
+      <c r="H268" t="n">
         <v>6.9</v>
       </c>
-      <c r="G268" s="1" t="n">
+      <c r="I268" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H268" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I268" s="1" t="n">
+      <c r="J268" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K268" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J268" t="n">
+      <c r="L268" t="n">
         <v>6.2</v>
       </c>
-      <c r="K268" s="1" t="n">
+      <c r="M268" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="L268" t="n">
+      <c r="N268" t="n">
         <v>8.6</v>
       </c>
-      <c r="M268" s="1" t="n">
+      <c r="O268" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="N268" t="n">
-        <v>7</v>
-      </c>
-      <c r="O268" s="1" t="n">
-        <v>46011</v>
-      </c>
       <c r="P268" t="n">
-        <v>6.9</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="269">
@@ -12409,49 +12465,49 @@
         <v>417</v>
       </c>
       <c r="B276" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C276" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D276" t="n">
         <v>6.3</v>
       </c>
-      <c r="C276" s="1" t="n">
+      <c r="E276" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="D276" t="n">
+      <c r="F276" t="n">
         <v>5.9</v>
       </c>
-      <c r="E276" s="1" t="n">
+      <c r="G276" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="F276" t="n">
+      <c r="H276" t="n">
         <v>8.1</v>
       </c>
-      <c r="G276" s="1" t="n">
+      <c r="I276" s="1" t="n">
         <v>46045</v>
       </c>
-      <c r="H276" t="n">
+      <c r="J276" t="n">
         <v>8.4</v>
       </c>
-      <c r="I276" s="1" t="n">
+      <c r="K276" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="J276" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K276" s="1" t="n">
+      <c r="L276" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M276" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="L276" t="n">
+      <c r="N276" t="n">
         <v>7.2</v>
       </c>
-      <c r="M276" s="1" t="n">
+      <c r="O276" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="N276" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O276" s="1" t="n">
-        <v>45983</v>
-      </c>
       <c r="P276" t="n">
-        <v>6.96</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="277">
@@ -12459,49 +12515,49 @@
         <v>418</v>
       </c>
       <c r="B277" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C277" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D277" t="n">
         <v>7.3</v>
       </c>
-      <c r="C277" s="1" t="n">
+      <c r="E277" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D277" t="n">
+      <c r="F277" t="n">
         <v>6.8</v>
       </c>
-      <c r="E277" s="1" t="n">
+      <c r="G277" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F277" t="n">
+      <c r="H277" t="n">
         <v>8.6</v>
       </c>
-      <c r="G277" s="1" t="n">
+      <c r="I277" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="H277" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I277" s="1" t="n">
+      <c r="J277" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K277" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="J277" t="n">
+      <c r="L277" t="n">
         <v>8.1</v>
       </c>
-      <c r="K277" s="1" t="n">
+      <c r="M277" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="L277" t="n">
+      <c r="N277" t="n">
         <v>7.3</v>
       </c>
-      <c r="M277" s="1" t="n">
+      <c r="O277" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="N277" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O277" s="1" t="n">
-        <v>46010</v>
-      </c>
       <c r="P277" t="n">
-        <v>7.5</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="278">
@@ -12509,49 +12565,49 @@
         <v>419</v>
       </c>
       <c r="B278" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C278" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D278" t="n">
         <v>6.4</v>
       </c>
-      <c r="C278" s="1" t="n">
+      <c r="E278" s="1" t="n">
         <v>45926</v>
       </c>
-      <c r="D278" t="n">
+      <c r="F278" t="n">
         <v>7.1</v>
       </c>
-      <c r="E278" s="1" t="n">
+      <c r="G278" s="1" t="n">
         <v>45919</v>
       </c>
-      <c r="F278" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G278" s="1" t="n">
+      <c r="H278" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I278" s="1" t="n">
         <v>45914</v>
-      </c>
-      <c r="H278" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I278" s="1" t="n">
-        <v>45898</v>
       </c>
       <c r="J278" t="n">
         <v>6.8</v>
       </c>
       <c r="K278" s="1" t="n">
-        <v>45891</v>
+        <v>45898</v>
       </c>
       <c r="L278" t="n">
         <v>6.8</v>
       </c>
       <c r="M278" s="1" t="n">
+        <v>45891</v>
+      </c>
+      <c r="N278" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O278" s="1" t="n">
         <v>45878</v>
       </c>
-      <c r="N278" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O278" s="1" t="n">
-        <v>45871</v>
-      </c>
       <c r="P278" t="n">
-        <v>6.76</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="279">
@@ -12559,49 +12615,49 @@
         <v>420</v>
       </c>
       <c r="B279" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="C279" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D279" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E279" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="D279" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E279" s="1" t="n">
+      <c r="F279" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G279" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="F279" t="n">
+      <c r="H279" t="n">
         <v>8</v>
       </c>
-      <c r="G279" s="1" t="n">
+      <c r="I279" s="1" t="n">
         <v>45969</v>
-      </c>
-      <c r="H279" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I279" s="1" t="n">
-        <v>45964</v>
       </c>
       <c r="J279" t="n">
         <v>7.3</v>
       </c>
       <c r="K279" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="L279" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M279" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="L279" t="n">
+      <c r="N279" t="n">
         <v>7.2</v>
       </c>
-      <c r="M279" s="1" t="n">
+      <c r="O279" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="N279" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O279" s="1" t="n">
-        <v>45933</v>
-      </c>
       <c r="P279" t="n">
-        <v>7.2</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="280">
@@ -12609,49 +12665,49 @@
         <v>421</v>
       </c>
       <c r="B280" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C280" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D280" t="n">
         <v>8.4</v>
       </c>
-      <c r="C280" s="1" t="n">
+      <c r="E280" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="D280" t="n">
+      <c r="F280" t="n">
         <v>9.6</v>
       </c>
-      <c r="E280" s="1" t="n">
+      <c r="G280" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="F280" t="n">
+      <c r="H280" t="n">
         <v>6.9</v>
       </c>
-      <c r="G280" s="1" t="n">
+      <c r="I280" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H280" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I280" s="1" t="n">
+      <c r="J280" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K280" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="J280" t="n">
+      <c r="L280" t="n">
         <v>7.1</v>
       </c>
-      <c r="K280" s="1" t="n">
+      <c r="M280" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L280" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M280" s="1" t="n">
+      <c r="N280" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O280" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N280" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O280" s="1" t="n">
-        <v>45949</v>
-      </c>
       <c r="P280" t="n">
-        <v>7.41</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="281">
@@ -12701,46 +12757,46 @@
         <v>423</v>
       </c>
       <c r="B282" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C282" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D282" t="n">
         <v>7.2</v>
       </c>
-      <c r="C282" s="1" t="n">
+      <c r="E282" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="D282" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E282" s="1" t="n">
+      <c r="F282" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G282" s="1" t="n">
         <v>45986</v>
       </c>
-      <c r="F282" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G282" s="1" t="n">
+      <c r="H282" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I282" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="H282" t="n">
+      <c r="J282" t="n">
         <v>7</v>
       </c>
-      <c r="I282" s="1" t="n">
+      <c r="K282" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="J282" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K282" s="1" t="n">
+      <c r="L282" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M282" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="L282" t="n">
+      <c r="N282" t="n">
         <v>6.1</v>
       </c>
-      <c r="M282" s="1" t="n">
+      <c r="O282" s="1" t="n">
         <v>45949</v>
-      </c>
-      <c r="N282" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O282" s="1" t="n">
-        <v>45935</v>
       </c>
       <c r="P282" t="n">
         <v>6.69</v>
@@ -12929,49 +12985,49 @@
         <v>429</v>
       </c>
       <c r="B288" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="C288" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D288" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E288" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D288" t="n">
+      <c r="F288" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="E288" s="1" t="n">
+      <c r="G288" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F288" t="n">
+      <c r="H288" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G288" s="1" t="n">
+      <c r="I288" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H288" t="n">
+      <c r="J288" t="n">
         <v>7</v>
       </c>
-      <c r="I288" s="1" t="n">
+      <c r="K288" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J288" t="n">
+      <c r="L288" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K288" s="1" t="n">
+      <c r="M288" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="L288" t="n">
+      <c r="N288" t="n">
         <v>7.7</v>
       </c>
-      <c r="M288" s="1" t="n">
+      <c r="O288" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="N288" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O288" s="1" t="n">
-        <v>45999</v>
-      </c>
       <c r="P288" t="n">
-        <v>7.66</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="289">
@@ -13209,49 +13265,49 @@
         <v>437</v>
       </c>
       <c r="B294" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C294" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D294" t="n">
         <v>7.1</v>
       </c>
-      <c r="C294" s="1" t="n">
+      <c r="E294" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D294" t="n">
+      <c r="F294" t="n">
         <v>9</v>
       </c>
-      <c r="E294" s="1" t="n">
+      <c r="G294" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F294" t="n">
+      <c r="H294" t="n">
         <v>6.9</v>
       </c>
-      <c r="G294" s="1" t="n">
+      <c r="I294" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H294" t="n">
+      <c r="J294" t="n">
         <v>7</v>
       </c>
-      <c r="I294" s="1" t="n">
+      <c r="K294" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J294" t="n">
+      <c r="L294" t="n">
         <v>7.4</v>
       </c>
-      <c r="K294" s="1" t="n">
+      <c r="M294" s="1" t="n">
         <v>46049</v>
       </c>
-      <c r="L294" t="n">
+      <c r="N294" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M294" s="1" t="n">
+      <c r="O294" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="N294" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O294" s="1" t="n">
-        <v>46038</v>
-      </c>
       <c r="P294" t="n">
-        <v>7.59</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="295">
@@ -13301,49 +13357,49 @@
         <v>439</v>
       </c>
       <c r="B296" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C296" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D296" t="n">
         <v>6.9</v>
       </c>
-      <c r="C296" s="1" t="n">
+      <c r="E296" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D296" t="n">
+      <c r="F296" t="n">
         <v>8.5</v>
       </c>
-      <c r="E296" s="1" t="n">
+      <c r="G296" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F296" t="n">
+      <c r="H296" t="n">
         <v>7.4</v>
       </c>
-      <c r="G296" s="1" t="n">
+      <c r="I296" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H296" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I296" s="1" t="n">
+      <c r="J296" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K296" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J296" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K296" s="1" t="n">
+      <c r="L296" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M296" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="L296" t="n">
+      <c r="N296" t="n">
         <v>7.1</v>
       </c>
-      <c r="M296" s="1" t="n">
+      <c r="O296" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N296" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O296" s="1" t="n">
-        <v>45990</v>
-      </c>
       <c r="P296" t="n">
-        <v>7.23</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="297">
@@ -13949,49 +14005,49 @@
         <v>457</v>
       </c>
       <c r="B311" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="C311" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D311" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E311" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D311" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E311" s="1" t="n">
+      <c r="F311" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G311" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F311" t="n">
+      <c r="H311" t="n">
         <v>7.5</v>
       </c>
-      <c r="G311" s="1" t="n">
+      <c r="I311" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="H311" t="n">
+      <c r="J311" t="n">
         <v>7.3</v>
       </c>
-      <c r="I311" s="1" t="n">
+      <c r="K311" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="J311" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K311" s="1" t="n">
+      <c r="L311" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M311" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="L311" t="n">
+      <c r="N311" t="n">
         <v>7.1</v>
       </c>
-      <c r="M311" s="1" t="n">
+      <c r="O311" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="N311" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O311" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P311" t="n">
-        <v>7.03</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="312">
@@ -14049,7 +14105,7 @@
         <v>459</v>
       </c>
       <c r="B313" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="C313" s="1" t="n">
         <v>46081</v>
@@ -14091,7 +14147,7 @@
         <v>45965</v>
       </c>
       <c r="P313" t="n">
-        <v>6.73</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="314">
@@ -14225,49 +14281,49 @@
         <v>463</v>
       </c>
       <c r="B317" t="n">
+        <v>7</v>
+      </c>
+      <c r="C317" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D317" t="n">
         <v>6.4</v>
       </c>
-      <c r="C317" s="1" t="n">
+      <c r="E317" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="D317" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E317" s="1" t="n">
+      <c r="F317" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G317" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="F317" t="n">
+      <c r="H317" t="n">
         <v>7.3</v>
       </c>
-      <c r="G317" s="1" t="n">
+      <c r="I317" s="1" t="n">
         <v>45984</v>
-      </c>
-      <c r="H317" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="I317" s="1" t="n">
-        <v>45969</v>
       </c>
       <c r="J317" t="n">
         <v>6.3</v>
       </c>
       <c r="K317" s="1" t="n">
+        <v>45969</v>
+      </c>
+      <c r="L317" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M317" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L317" t="n">
+      <c r="N317" t="n">
         <v>6.2</v>
       </c>
-      <c r="M317" s="1" t="n">
+      <c r="O317" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N317" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O317" s="1" t="n">
-        <v>45934</v>
-      </c>
       <c r="P317" t="n">
-        <v>6.51</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="318">
@@ -14328,38 +14384,46 @@
         <v>6.5</v>
       </c>
       <c r="C319" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D319" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E319" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="F319" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G319" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D319" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E319" s="1" t="n">
+      <c r="H319" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I319" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="F319" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G319" s="1" t="n">
+      <c r="J319" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K319" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="H319" t="n">
+      <c r="L319" t="n">
         <v>6.8</v>
       </c>
-      <c r="I319" s="1" t="n">
+      <c r="M319" s="1" t="n">
         <v>45879</v>
       </c>
-      <c r="J319" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K319" s="1" t="n">
+      <c r="N319" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O319" s="1" t="n">
         <v>45871</v>
       </c>
-      <c r="L319" t="inlineStr"/>
-      <c r="M319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
-      <c r="O319" t="inlineStr"/>
       <c r="P319" t="n">
-        <v>6.62</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="320">
@@ -14417,49 +14481,49 @@
         <v>467</v>
       </c>
       <c r="B321" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46081</v>
+        <v>46087</v>
       </c>
       <c r="D321" t="n">
         <v>7</v>
       </c>
       <c r="E321" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="F321" t="n">
+        <v>7</v>
+      </c>
+      <c r="G321" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F321" t="n">
+      <c r="H321" t="n">
         <v>8.5</v>
       </c>
-      <c r="G321" s="1" t="n">
+      <c r="I321" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H321" t="n">
+      <c r="J321" t="n">
         <v>7.7</v>
       </c>
-      <c r="I321" s="1" t="n">
+      <c r="K321" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J321" t="n">
+      <c r="L321" t="n">
         <v>7.3</v>
       </c>
-      <c r="K321" s="1" t="n">
+      <c r="M321" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="L321" t="n">
+      <c r="N321" t="n">
         <v>7.1</v>
       </c>
-      <c r="M321" s="1" t="n">
+      <c r="O321" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N321" t="n">
-        <v>8</v>
-      </c>
-      <c r="O321" s="1" t="n">
-        <v>45993</v>
-      </c>
       <c r="P321" t="n">
-        <v>7.51</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="322">
@@ -14467,49 +14531,49 @@
         <v>468</v>
       </c>
       <c r="B322" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C322" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D322" t="n">
         <v>6.2</v>
       </c>
-      <c r="C322" s="1" t="n">
+      <c r="E322" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D322" t="n">
+      <c r="F322" t="n">
         <v>6.8</v>
       </c>
-      <c r="E322" s="1" t="n">
+      <c r="G322" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F322" t="n">
+      <c r="H322" t="n">
         <v>6.2</v>
       </c>
-      <c r="G322" s="1" t="n">
+      <c r="I322" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H322" t="n">
+      <c r="J322" t="n">
         <v>6.1</v>
       </c>
-      <c r="I322" s="1" t="n">
+      <c r="K322" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="J322" t="n">
+      <c r="L322" t="n">
         <v>6.3</v>
       </c>
-      <c r="K322" s="1" t="n">
+      <c r="M322" s="1" t="n">
         <v>45994</v>
       </c>
-      <c r="L322" t="n">
+      <c r="N322" t="n">
         <v>6.2</v>
       </c>
-      <c r="M322" s="1" t="n">
+      <c r="O322" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="N322" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O322" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P322" t="n">
-        <v>6.36</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="323">
@@ -14517,49 +14581,49 @@
         <v>469</v>
       </c>
       <c r="B323" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C323" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D323" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E323" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="D323" t="n">
+      <c r="F323" t="n">
         <v>6.9</v>
       </c>
-      <c r="E323" s="1" t="n">
+      <c r="G323" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F323" t="n">
+      <c r="H323" t="n">
         <v>6</v>
       </c>
-      <c r="G323" s="1" t="n">
+      <c r="I323" s="1" t="n">
         <v>46005</v>
       </c>
-      <c r="H323" t="n">
+      <c r="J323" t="n">
         <v>6.4</v>
       </c>
-      <c r="I323" s="1" t="n">
+      <c r="K323" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="J323" t="n">
+      <c r="L323" t="n">
         <v>7.1</v>
       </c>
-      <c r="K323" s="1" t="n">
+      <c r="M323" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L323" t="n">
+      <c r="N323" t="n">
         <v>7.2</v>
       </c>
-      <c r="M323" s="1" t="n">
+      <c r="O323" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="N323" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O323" s="1" t="n">
-        <v>45961</v>
-      </c>
       <c r="P323" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="324">
@@ -14567,49 +14631,49 @@
         <v>470</v>
       </c>
       <c r="B324" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46074</v>
+        <v>46086</v>
       </c>
       <c r="D324" t="n">
         <v>6.3</v>
       </c>
       <c r="E324" s="1" t="n">
+        <v>46074</v>
+      </c>
+      <c r="F324" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G324" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F324" t="n">
+      <c r="H324" t="n">
         <v>6.2</v>
       </c>
-      <c r="G324" s="1" t="n">
+      <c r="I324" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="H324" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I324" s="1" t="n">
+      <c r="J324" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K324" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="J324" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K324" s="1" t="n">
+      <c r="L324" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M324" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L324" t="n">
+      <c r="N324" t="n">
         <v>6.4</v>
       </c>
-      <c r="M324" s="1" t="n">
+      <c r="O324" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="N324" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O324" s="1" t="n">
-        <v>45947</v>
-      </c>
       <c r="P324" t="n">
-        <v>6.41</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="325">
@@ -14617,49 +14681,49 @@
         <v>471</v>
       </c>
       <c r="B325" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="C325" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D325" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E325" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="F325" t="n">
         <v>6.9</v>
       </c>
-      <c r="C325" s="1" t="n">
+      <c r="G325" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D325" t="n">
+      <c r="H325" t="n">
         <v>5.7</v>
       </c>
-      <c r="E325" s="1" t="n">
+      <c r="I325" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F325" t="n">
+      <c r="J325" t="n">
         <v>6.8</v>
       </c>
-      <c r="G325" s="1" t="n">
+      <c r="K325" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H325" t="n">
+      <c r="L325" t="n">
         <v>6.8</v>
       </c>
-      <c r="I325" s="1" t="n">
+      <c r="M325" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="J325" t="n">
+      <c r="N325" t="n">
         <v>7</v>
       </c>
-      <c r="K325" s="1" t="n">
+      <c r="O325" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="L325" t="n">
-        <v>6</v>
-      </c>
-      <c r="M325" s="1" t="n">
-        <v>45995</v>
-      </c>
-      <c r="N325" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O325" s="1" t="n">
-        <v>45991</v>
-      </c>
       <c r="P325" t="n">
-        <v>6.53</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="326">
@@ -14865,49 +14929,49 @@
         <v>479</v>
       </c>
       <c r="B333" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C333" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D333" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E333" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D333" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E333" s="1" t="n">
+      <c r="F333" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G333" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="F333" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G333" s="1" t="n">
+      <c r="H333" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I333" s="1" t="n">
         <v>46000</v>
       </c>
-      <c r="H333" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I333" s="1" t="n">
+      <c r="J333" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K333" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="J333" t="n">
+      <c r="L333" t="n">
         <v>6.2</v>
       </c>
-      <c r="K333" s="1" t="n">
+      <c r="M333" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L333" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M333" s="1" t="n">
+      <c r="N333" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O333" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="N333" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O333" s="1" t="n">
-        <v>45954</v>
-      </c>
       <c r="P333" t="n">
-        <v>6.53</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="334">
@@ -14915,49 +14979,49 @@
         <v>480</v>
       </c>
       <c r="B334" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C334" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D334" t="n">
+        <v>7</v>
+      </c>
+      <c r="E334" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="F334" t="n">
         <v>6.4</v>
       </c>
-      <c r="C334" s="1" t="n">
+      <c r="G334" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D334" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E334" s="1" t="n">
+      <c r="H334" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I334" s="1" t="n">
         <v>45999</v>
       </c>
-      <c r="F334" t="n">
+      <c r="J334" t="n">
         <v>6.8</v>
       </c>
-      <c r="G334" s="1" t="n">
+      <c r="K334" s="1" t="n">
         <v>45983</v>
-      </c>
-      <c r="H334" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I334" s="1" t="n">
-        <v>45970</v>
-      </c>
-      <c r="J334" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K334" s="1" t="n">
-        <v>45964</v>
       </c>
       <c r="L334" t="n">
         <v>6.4</v>
       </c>
       <c r="M334" s="1" t="n">
-        <v>45957</v>
+        <v>45970</v>
       </c>
       <c r="N334" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="O334" s="1" t="n">
-        <v>45934</v>
+        <v>45964</v>
       </c>
       <c r="P334" t="n">
-        <v>6.51</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="335">
@@ -15069,49 +15133,49 @@
         <v>484</v>
       </c>
       <c r="B338" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46081</v>
+        <v>46088</v>
       </c>
       <c r="D338" t="n">
         <v>6.8</v>
       </c>
       <c r="E338" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="F338" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G338" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="F338" t="n">
+      <c r="H338" t="n">
         <v>7.2</v>
       </c>
-      <c r="G338" s="1" t="n">
+      <c r="I338" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="H338" t="n">
+      <c r="J338" t="n">
         <v>6.8</v>
       </c>
-      <c r="I338" s="1" t="n">
+      <c r="K338" s="1" t="n">
         <v>45971</v>
       </c>
-      <c r="J338" t="n">
+      <c r="L338" t="n">
         <v>7.2</v>
       </c>
-      <c r="K338" s="1" t="n">
+      <c r="M338" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="L338" t="n">
+      <c r="N338" t="n">
         <v>7.1</v>
       </c>
-      <c r="M338" s="1" t="n">
+      <c r="O338" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="N338" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O338" s="1" t="n">
-        <v>45948</v>
-      </c>
       <c r="P338" t="n">
-        <v>6.91</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="339">
@@ -15565,49 +15629,49 @@
         <v>494</v>
       </c>
       <c r="B348" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C348" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D348" t="n">
         <v>6.3</v>
       </c>
-      <c r="C348" s="1" t="n">
+      <c r="E348" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D348" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E348" s="1" t="n">
+      <c r="F348" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G348" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="F348" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G348" s="1" t="n">
+      <c r="H348" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I348" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H348" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I348" s="1" t="n">
+      <c r="J348" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K348" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="J348" t="n">
+      <c r="L348" t="n">
         <v>6.4</v>
       </c>
-      <c r="K348" s="1" t="n">
+      <c r="M348" s="1" t="n">
         <v>45962</v>
       </c>
-      <c r="L348" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M348" s="1" t="n">
+      <c r="N348" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O348" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="N348" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O348" s="1" t="n">
-        <v>45927</v>
-      </c>
       <c r="P348" t="n">
-        <v>6.66</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="349">
@@ -16044,46 +16108,46 @@
         <v>6.5</v>
       </c>
       <c r="C360" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D360" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E360" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D360" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E360" s="1" t="n">
+      <c r="F360" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G360" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F360" t="n">
+      <c r="H360" t="n">
         <v>6.4</v>
       </c>
-      <c r="G360" s="1" t="n">
+      <c r="I360" s="1" t="n">
         <v>46055</v>
       </c>
-      <c r="H360" t="n">
+      <c r="J360" t="n">
         <v>5.7</v>
       </c>
-      <c r="I360" s="1" t="n">
+      <c r="K360" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="J360" t="n">
+      <c r="L360" t="n">
         <v>5.9</v>
       </c>
-      <c r="K360" s="1" t="n">
+      <c r="M360" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L360" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M360" s="1" t="n">
+      <c r="N360" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O360" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="N360" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O360" s="1" t="n">
-        <v>45922</v>
-      </c>
       <c r="P360" t="n">
-        <v>6.3</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="361">
@@ -16191,49 +16255,49 @@
         <v>510</v>
       </c>
       <c r="B363" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C363" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D363" t="n">
         <v>6.8</v>
       </c>
-      <c r="C363" s="1" t="n">
+      <c r="E363" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D363" t="n">
+      <c r="F363" t="n">
         <v>7.5</v>
       </c>
-      <c r="E363" s="1" t="n">
+      <c r="G363" s="1" t="n">
         <v>46074</v>
-      </c>
-      <c r="F363" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G363" s="1" t="n">
-        <v>46066</v>
       </c>
       <c r="H363" t="n">
         <v>6.4</v>
       </c>
       <c r="I363" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="J363" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K363" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="J363" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K363" s="1" t="n">
+      <c r="L363" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M363" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="L363" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M363" s="1" t="n">
+      <c r="N363" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O363" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="N363" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O363" s="1" t="n">
-        <v>46011</v>
-      </c>
       <c r="P363" t="n">
-        <v>6.71</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="364">
@@ -16345,46 +16409,46 @@
         <v>514</v>
       </c>
       <c r="B367" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C367" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D367" t="n">
         <v>6.4</v>
       </c>
-      <c r="C367" s="1" t="n">
+      <c r="E367" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D367" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E367" s="1" t="n">
+      <c r="F367" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G367" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F367" t="n">
+      <c r="H367" t="n">
         <v>6.3</v>
       </c>
-      <c r="G367" s="1" t="n">
+      <c r="I367" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H367" t="n">
+      <c r="J367" t="n">
         <v>6.8</v>
       </c>
-      <c r="I367" s="1" t="n">
+      <c r="K367" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="J367" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K367" s="1" t="n">
+      <c r="L367" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M367" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L367" t="n">
+      <c r="N367" t="n">
         <v>6.4</v>
       </c>
-      <c r="M367" s="1" t="n">
+      <c r="O367" s="1" t="n">
         <v>46048</v>
-      </c>
-      <c r="N367" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O367" s="1" t="n">
-        <v>46012</v>
       </c>
       <c r="P367" t="n">
         <v>6.53</v>
@@ -16523,49 +16587,49 @@
         <v>520</v>
       </c>
       <c r="B373" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C373" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D373" t="n">
         <v>8.1</v>
       </c>
-      <c r="C373" s="1" t="n">
+      <c r="E373" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D373" t="n">
+      <c r="F373" t="n">
         <v>5.6</v>
       </c>
-      <c r="E373" s="1" t="n">
+      <c r="G373" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F373" t="n">
+      <c r="H373" t="n">
         <v>8</v>
       </c>
-      <c r="G373" s="1" t="n">
+      <c r="I373" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H373" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I373" s="1" t="n">
+      <c r="J373" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K373" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J373" t="n">
+      <c r="L373" t="n">
         <v>8</v>
       </c>
-      <c r="K373" s="1" t="n">
+      <c r="M373" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="L373" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M373" s="1" t="n">
+      <c r="N373" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O373" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="N373" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O373" s="1" t="n">
-        <v>46005</v>
-      </c>
       <c r="P373" t="n">
-        <v>7.1</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="374">
@@ -17419,49 +17483,49 @@
         <v>540</v>
       </c>
       <c r="B392" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="C392" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D392" t="n">
+        <v>7</v>
+      </c>
+      <c r="E392" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="F392" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G392" s="1" t="n">
         <v>46077</v>
       </c>
-      <c r="D392" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E392" s="1" t="n">
+      <c r="H392" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I392" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="F392" t="n">
+      <c r="J392" t="n">
         <v>7.2</v>
       </c>
-      <c r="G392" s="1" t="n">
+      <c r="K392" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="H392" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I392" s="1" t="n">
+      <c r="L392" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M392" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="J392" t="n">
+      <c r="N392" t="n">
         <v>6.9</v>
       </c>
-      <c r="K392" s="1" t="n">
+      <c r="O392" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L392" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M392" s="1" t="n">
-        <v>45956</v>
-      </c>
-      <c r="N392" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O392" s="1" t="n">
-        <v>45951</v>
-      </c>
       <c r="P392" t="n">
-        <v>6.67</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="393">
@@ -17539,7 +17603,7 @@
         <v>543</v>
       </c>
       <c r="B395" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="C395" s="1" t="n">
         <v>46082</v>
@@ -17581,7 +17645,7 @@
         <v>45963</v>
       </c>
       <c r="P395" t="n">
-        <v>6.94</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="396">
@@ -17689,49 +17753,49 @@
         <v>546</v>
       </c>
       <c r="B398" t="n">
+        <v>7</v>
+      </c>
+      <c r="C398" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D398" t="n">
         <v>7.3</v>
       </c>
-      <c r="C398" s="1" t="n">
+      <c r="E398" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D398" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E398" s="1" t="n">
+      <c r="F398" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G398" s="1" t="n">
         <v>46077</v>
       </c>
-      <c r="F398" t="n">
+      <c r="H398" t="n">
         <v>7.6</v>
       </c>
-      <c r="G398" s="1" t="n">
+      <c r="I398" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="H398" t="n">
+      <c r="J398" t="n">
         <v>7.2</v>
       </c>
-      <c r="I398" s="1" t="n">
+      <c r="K398" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="J398" t="n">
+      <c r="L398" t="n">
         <v>7</v>
       </c>
-      <c r="K398" s="1" t="n">
+      <c r="M398" s="1" t="n">
         <v>45920</v>
       </c>
-      <c r="L398" t="n">
+      <c r="N398" t="n">
         <v>7.3</v>
       </c>
-      <c r="M398" s="1" t="n">
+      <c r="O398" s="1" t="n">
         <v>45893</v>
       </c>
-      <c r="N398" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O398" s="1" t="n">
-        <v>45885</v>
-      </c>
       <c r="P398" t="n">
-        <v>7.07</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="399">
@@ -17819,45 +17883,49 @@
         <v>549</v>
       </c>
       <c r="B401" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="C401" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D401" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E401" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D401" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E401" s="1" t="n">
+      <c r="F401" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G401" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="F401" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G401" s="1" t="n">
+      <c r="H401" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I401" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="H401" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I401" s="1" t="n">
+      <c r="J401" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K401" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="J401" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K401" s="1" t="n">
+      <c r="L401" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M401" s="1" t="n">
         <v>45892</v>
       </c>
-      <c r="L401" t="n">
+      <c r="N401" t="n">
         <v>7.2</v>
       </c>
-      <c r="M401" s="1" t="n">
+      <c r="O401" s="1" t="n">
         <v>45877</v>
       </c>
-      <c r="N401" t="inlineStr"/>
-      <c r="O401" t="inlineStr"/>
       <c r="P401" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="402">
@@ -17865,41 +17933,45 @@
         <v>550</v>
       </c>
       <c r="B402" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C402" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D402" t="n">
         <v>6.3</v>
       </c>
-      <c r="C402" s="1" t="n">
+      <c r="E402" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="D402" t="n">
+      <c r="F402" t="n">
         <v>6.8</v>
       </c>
-      <c r="E402" s="1" t="n">
+      <c r="G402" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="F402" t="n">
+      <c r="H402" t="n">
         <v>6.4</v>
       </c>
-      <c r="G402" s="1" t="n">
+      <c r="I402" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="H402" t="n">
+      <c r="J402" t="n">
         <v>6.3</v>
       </c>
-      <c r="I402" s="1" t="n">
+      <c r="K402" s="1" t="n">
         <v>45954</v>
       </c>
-      <c r="J402" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K402" s="1" t="n">
+      <c r="L402" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M402" s="1" t="n">
         <v>45947</v>
       </c>
-      <c r="L402" t="inlineStr"/>
-      <c r="M402" t="inlineStr"/>
       <c r="N402" t="inlineStr"/>
       <c r="O402" t="inlineStr"/>
       <c r="P402" t="n">
-        <v>6.46</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="403">
@@ -17907,41 +17979,45 @@
         <v>551</v>
       </c>
       <c r="B403" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C403" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D403" t="n">
         <v>7.9</v>
       </c>
-      <c r="C403" s="1" t="n">
+      <c r="E403" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D403" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E403" s="1" t="n">
+      <c r="F403" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G403" s="1" t="n">
         <v>45912</v>
       </c>
-      <c r="F403" t="n">
+      <c r="H403" t="n">
         <v>6.3</v>
       </c>
-      <c r="G403" s="1" t="n">
+      <c r="I403" s="1" t="n">
         <v>45898</v>
       </c>
-      <c r="H403" t="n">
+      <c r="J403" t="n">
         <v>7</v>
       </c>
-      <c r="I403" s="1" t="n">
+      <c r="K403" s="1" t="n">
         <v>45892</v>
       </c>
-      <c r="J403" t="n">
+      <c r="L403" t="n">
         <v>7.1</v>
       </c>
-      <c r="K403" s="1" t="n">
+      <c r="M403" s="1" t="n">
         <v>45877</v>
       </c>
-      <c r="L403" t="inlineStr"/>
-      <c r="M403" t="inlineStr"/>
       <c r="N403" t="inlineStr"/>
       <c r="O403" t="inlineStr"/>
       <c r="P403" t="n">
-        <v>6.98</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="404">
@@ -18091,49 +18167,49 @@
         <v>555</v>
       </c>
       <c r="B407" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C407" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D407" t="n">
         <v>6.9</v>
       </c>
-      <c r="C407" s="1" t="n">
+      <c r="E407" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D407" t="n">
+      <c r="F407" t="n">
         <v>7</v>
       </c>
-      <c r="E407" s="1" t="n">
+      <c r="G407" s="1" t="n">
         <v>45957</v>
       </c>
-      <c r="F407" t="n">
+      <c r="H407" t="n">
         <v>7.2</v>
       </c>
-      <c r="G407" s="1" t="n">
+      <c r="I407" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="H407" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I407" s="1" t="n">
+      <c r="J407" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K407" s="1" t="n">
         <v>45936</v>
       </c>
-      <c r="J407" t="n">
+      <c r="L407" t="n">
         <v>6.2</v>
       </c>
-      <c r="K407" s="1" t="n">
+      <c r="M407" s="1" t="n">
         <v>45929</v>
       </c>
-      <c r="L407" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M407" s="1" t="n">
+      <c r="N407" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O407" s="1" t="n">
         <v>45919</v>
       </c>
-      <c r="N407" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O407" s="1" t="n">
-        <v>45914</v>
-      </c>
       <c r="P407" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="408">
@@ -18144,43 +18220,43 @@
         <v>6.5</v>
       </c>
       <c r="C408" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D408" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E408" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="D408" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E408" s="1" t="n">
+      <c r="F408" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G408" s="1" t="n">
         <v>46006</v>
       </c>
-      <c r="F408" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G408" s="1" t="n">
+      <c r="H408" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I408" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="H408" t="n">
+      <c r="J408" t="n">
         <v>6.4</v>
       </c>
-      <c r="I408" s="1" t="n">
+      <c r="K408" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="J408" t="n">
+      <c r="L408" t="n">
         <v>6.8</v>
       </c>
-      <c r="K408" s="1" t="n">
+      <c r="M408" s="1" t="n">
         <v>45984</v>
       </c>
-      <c r="L408" t="n">
+      <c r="N408" t="n">
         <v>6.3</v>
       </c>
-      <c r="M408" s="1" t="n">
+      <c r="O408" s="1" t="n">
         <v>45928</v>
-      </c>
-      <c r="N408" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O408" s="1" t="n">
-        <v>45914</v>
       </c>
       <c r="P408" t="n">
         <v>6.54</v>
@@ -18191,49 +18267,49 @@
         <v>557</v>
       </c>
       <c r="B409" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="C409" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D409" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E409" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D409" t="n">
+      <c r="F409" t="n">
         <v>7.9</v>
       </c>
-      <c r="E409" s="1" t="n">
+      <c r="G409" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="F409" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G409" s="1" t="n">
+      <c r="H409" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I409" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="H409" t="n">
+      <c r="J409" t="n">
         <v>6.9</v>
       </c>
-      <c r="I409" s="1" t="n">
+      <c r="K409" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="J409" t="n">
+      <c r="L409" t="n">
         <v>7.7</v>
       </c>
-      <c r="K409" s="1" t="n">
+      <c r="M409" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="L409" t="n">
+      <c r="N409" t="n">
         <v>6.3</v>
       </c>
-      <c r="M409" s="1" t="n">
+      <c r="O409" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N409" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O409" s="1" t="n">
-        <v>45965</v>
-      </c>
       <c r="P409" t="n">
-        <v>7.16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="410">
@@ -18291,49 +18367,49 @@
         <v>559</v>
       </c>
       <c r="B411" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>46079</v>
+        <v>46088</v>
       </c>
       <c r="D411" t="n">
         <v>7.2</v>
       </c>
       <c r="E411" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="F411" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G411" s="1" t="n">
         <v>46072</v>
       </c>
-      <c r="F411" t="n">
+      <c r="H411" t="n">
         <v>7.4</v>
       </c>
-      <c r="G411" s="1" t="n">
+      <c r="I411" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H411" t="n">
+      <c r="J411" t="n">
         <v>9.1</v>
       </c>
-      <c r="I411" s="1" t="n">
+      <c r="K411" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="J411" t="n">
+      <c r="L411" t="n">
         <v>7</v>
       </c>
-      <c r="K411" s="1" t="n">
+      <c r="M411" s="1" t="n">
         <v>45990</v>
-      </c>
-      <c r="L411" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="M411" s="1" t="n">
-        <v>45983</v>
       </c>
       <c r="N411" t="n">
         <v>7.2</v>
       </c>
       <c r="O411" s="1" t="n">
-        <v>45963</v>
+        <v>45983</v>
       </c>
       <c r="P411" t="n">
-        <v>7.47</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="412">
@@ -18471,49 +18547,49 @@
         <v>563</v>
       </c>
       <c r="B415" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C415" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D415" t="n">
         <v>7.8</v>
       </c>
-      <c r="C415" s="1" t="n">
+      <c r="E415" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="D415" t="n">
+      <c r="F415" t="n">
         <v>7</v>
       </c>
-      <c r="E415" s="1" t="n">
+      <c r="G415" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F415" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G415" s="1" t="n">
+      <c r="H415" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I415" s="1" t="n">
         <v>46060</v>
-      </c>
-      <c r="H415" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I415" s="1" t="n">
-        <v>46004</v>
       </c>
       <c r="J415" t="n">
         <v>6.8</v>
       </c>
       <c r="K415" s="1" t="n">
+        <v>46004</v>
+      </c>
+      <c r="L415" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M415" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="L415" t="n">
+      <c r="N415" t="n">
         <v>6.9</v>
       </c>
-      <c r="M415" s="1" t="n">
+      <c r="O415" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="N415" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O415" s="1" t="n">
-        <v>45983</v>
-      </c>
       <c r="P415" t="n">
-        <v>6.9</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="416">
@@ -18629,49 +18705,49 @@
         <v>567</v>
       </c>
       <c r="B419" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C419" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D419" t="n">
         <v>6.8</v>
       </c>
-      <c r="C419" s="1" t="n">
+      <c r="E419" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D419" t="n">
+      <c r="F419" t="n">
         <v>6.3</v>
       </c>
-      <c r="E419" s="1" t="n">
+      <c r="G419" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F419" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G419" s="1" t="n">
+      <c r="H419" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I419" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H419" t="n">
+      <c r="J419" t="n">
         <v>7.2</v>
       </c>
-      <c r="I419" s="1" t="n">
+      <c r="K419" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="J419" t="n">
+      <c r="L419" t="n">
         <v>7</v>
       </c>
-      <c r="K419" s="1" t="n">
+      <c r="M419" s="1" t="n">
         <v>45990</v>
-      </c>
-      <c r="L419" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M419" s="1" t="n">
-        <v>45984</v>
       </c>
       <c r="N419" t="n">
         <v>6.9</v>
       </c>
       <c r="O419" s="1" t="n">
-        <v>45968</v>
+        <v>45984</v>
       </c>
       <c r="P419" t="n">
-        <v>6.83</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="420">
@@ -18795,46 +18871,46 @@
         <v>573</v>
       </c>
       <c r="B423" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C423" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D423" t="n">
         <v>6.1</v>
       </c>
-      <c r="C423" s="1" t="n">
+      <c r="E423" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="D423" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E423" s="1" t="n">
+      <c r="F423" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G423" s="1" t="n">
         <v>45975</v>
       </c>
-      <c r="F423" t="n">
+      <c r="H423" t="n">
         <v>6.4</v>
       </c>
-      <c r="G423" s="1" t="n">
+      <c r="I423" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="H423" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I423" s="1" t="n">
+      <c r="J423" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K423" s="1" t="n">
         <v>45966</v>
       </c>
-      <c r="J423" t="n">
+      <c r="L423" t="n">
         <v>7</v>
       </c>
-      <c r="K423" s="1" t="n">
+      <c r="M423" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="L423" t="n">
+      <c r="N423" t="n">
         <v>6.8</v>
       </c>
-      <c r="M423" s="1" t="n">
+      <c r="O423" s="1" t="n">
         <v>45948</v>
-      </c>
-      <c r="N423" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O423" s="1" t="n">
-        <v>45940</v>
       </c>
       <c r="P423" t="n">
         <v>6.54</v>
@@ -18845,49 +18921,49 @@
         <v>574</v>
       </c>
       <c r="B424" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C424" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D424" t="n">
         <v>7.3</v>
       </c>
-      <c r="C424" s="1" t="n">
+      <c r="E424" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="D424" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E424" s="1" t="n">
+      <c r="F424" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G424" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="F424" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G424" s="1" t="n">
+      <c r="H424" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I424" s="1" t="n">
         <v>45960</v>
       </c>
-      <c r="H424" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I424" s="1" t="n">
+      <c r="J424" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K424" s="1" t="n">
         <v>45955</v>
       </c>
-      <c r="J424" t="n">
+      <c r="L424" t="n">
         <v>6.9</v>
       </c>
-      <c r="K424" s="1" t="n">
+      <c r="M424" s="1" t="n">
         <v>45948</v>
       </c>
-      <c r="L424" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M424" s="1" t="n">
+      <c r="N424" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O424" s="1" t="n">
         <v>45933</v>
       </c>
-      <c r="N424" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O424" s="1" t="n">
-        <v>45928</v>
-      </c>
       <c r="P424" t="n">
-        <v>6.73</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="425">
@@ -18987,49 +19063,49 @@
         <v>577</v>
       </c>
       <c r="B427" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C427" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D427" t="n">
         <v>6.4</v>
       </c>
-      <c r="C427" s="1" t="n">
+      <c r="E427" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D427" t="n">
+      <c r="F427" t="n">
         <v>5.9</v>
       </c>
-      <c r="E427" s="1" t="n">
+      <c r="G427" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="F427" t="n">
+      <c r="H427" t="n">
         <v>5.7</v>
       </c>
-      <c r="G427" s="1" t="n">
+      <c r="I427" s="1" t="n">
         <v>46062</v>
       </c>
-      <c r="H427" t="n">
+      <c r="J427" t="n">
         <v>6.3</v>
       </c>
-      <c r="I427" s="1" t="n">
+      <c r="K427" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J427" t="n">
+      <c r="L427" t="n">
         <v>7.4</v>
       </c>
-      <c r="K427" s="1" t="n">
+      <c r="M427" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="L427" t="n">
+      <c r="N427" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M427" s="1" t="n">
+      <c r="O427" s="1" t="n">
         <v>46008</v>
       </c>
-      <c r="N427" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O427" s="1" t="n">
-        <v>46004</v>
-      </c>
       <c r="P427" t="n">
-        <v>6.66</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="428">
@@ -19087,49 +19163,49 @@
         <v>579</v>
       </c>
       <c r="B429" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>46081</v>
+        <v>46088</v>
       </c>
       <c r="D429" t="n">
         <v>6.2</v>
       </c>
       <c r="E429" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="F429" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G429" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F429" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G429" s="1" t="n">
+      <c r="H429" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I429" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H429" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I429" s="1" t="n">
+      <c r="J429" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K429" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J429" t="n">
+      <c r="L429" t="n">
         <v>7</v>
       </c>
-      <c r="K429" s="1" t="n">
+      <c r="M429" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="L429" t="n">
+      <c r="N429" t="n">
         <v>6.3</v>
       </c>
-      <c r="M429" s="1" t="n">
+      <c r="O429" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="N429" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O429" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P429" t="n">
-        <v>6.46</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="430">
@@ -19428,46 +19504,46 @@
         <v>6.6</v>
       </c>
       <c r="C436" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D436" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E436" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D436" t="n">
+      <c r="F436" t="n">
         <v>7.5</v>
       </c>
-      <c r="E436" s="1" t="n">
+      <c r="G436" s="1" t="n">
         <v>46052</v>
-      </c>
-      <c r="F436" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G436" s="1" t="n">
-        <v>46010</v>
       </c>
       <c r="H436" t="n">
         <v>6.4</v>
       </c>
       <c r="I436" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="J436" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K436" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="J436" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K436" s="1" t="n">
+      <c r="L436" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M436" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="L436" t="n">
+      <c r="N436" t="n">
         <v>6.9</v>
       </c>
-      <c r="M436" s="1" t="n">
+      <c r="O436" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="N436" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O436" s="1" t="n">
-        <v>45983</v>
-      </c>
       <c r="P436" t="n">
-        <v>6.73</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="437">
@@ -19525,49 +19601,49 @@
         <v>589</v>
       </c>
       <c r="B438" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C438" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D438" t="n">
         <v>7.1</v>
       </c>
-      <c r="C438" s="1" t="n">
+      <c r="E438" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D438" t="n">
+      <c r="F438" t="n">
         <v>6.9</v>
       </c>
-      <c r="E438" s="1" t="n">
+      <c r="G438" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="F438" t="n">
+      <c r="H438" t="n">
         <v>7.2</v>
       </c>
-      <c r="G438" s="1" t="n">
+      <c r="I438" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H438" t="n">
+      <c r="J438" t="n">
         <v>6.8</v>
       </c>
-      <c r="I438" s="1" t="n">
+      <c r="K438" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="J438" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K438" s="1" t="n">
+      <c r="L438" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M438" s="1" t="n">
         <v>46047</v>
       </c>
-      <c r="L438" t="n">
+      <c r="N438" t="n">
         <v>7.7</v>
       </c>
-      <c r="M438" s="1" t="n">
+      <c r="O438" s="1" t="n">
         <v>46012</v>
       </c>
-      <c r="N438" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O438" s="1" t="n">
-        <v>46004</v>
-      </c>
       <c r="P438" t="n">
-        <v>6.94</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="439">
@@ -19578,46 +19654,46 @@
         <v>6.6</v>
       </c>
       <c r="C439" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D439" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E439" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D439" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E439" s="1" t="n">
+      <c r="F439" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G439" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F439" t="n">
+      <c r="H439" t="n">
         <v>6.4</v>
       </c>
-      <c r="G439" s="1" t="n">
+      <c r="I439" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H439" t="n">
+      <c r="J439" t="n">
         <v>7.2</v>
       </c>
-      <c r="I439" s="1" t="n">
+      <c r="K439" s="1" t="n">
         <v>45996</v>
       </c>
-      <c r="J439" t="n">
+      <c r="L439" t="n">
         <v>7.1</v>
       </c>
-      <c r="K439" s="1" t="n">
+      <c r="M439" s="1" t="n">
         <v>45990</v>
       </c>
-      <c r="L439" t="n">
+      <c r="N439" t="n">
         <v>6.2</v>
       </c>
-      <c r="M439" s="1" t="n">
+      <c r="O439" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="N439" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O439" s="1" t="n">
-        <v>45969</v>
-      </c>
       <c r="P439" t="n">
-        <v>6.8</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="440">
@@ -19925,49 +20001,49 @@
         <v>597</v>
       </c>
       <c r="B446" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="C446" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D446" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E446" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D446" t="n">
+      <c r="F446" t="n">
         <v>7.7</v>
       </c>
-      <c r="E446" s="1" t="n">
+      <c r="G446" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F446" t="n">
+      <c r="H446" t="n">
         <v>6.4</v>
       </c>
-      <c r="G446" s="1" t="n">
+      <c r="I446" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H446" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I446" s="1" t="n">
+      <c r="J446" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K446" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J446" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K446" s="1" t="n">
+      <c r="L446" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M446" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="L446" t="n">
+      <c r="N446" t="n">
         <v>7.5</v>
       </c>
-      <c r="M446" s="1" t="n">
+      <c r="O446" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="N446" t="n">
-        <v>7</v>
-      </c>
-      <c r="O446" s="1" t="n">
-        <v>45982</v>
-      </c>
       <c r="P446" t="n">
-        <v>6.93</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="447">
@@ -19975,49 +20051,49 @@
         <v>598</v>
       </c>
       <c r="B447" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C447" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D447" t="n">
         <v>7</v>
       </c>
-      <c r="C447" s="1" t="n">
+      <c r="E447" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D447" t="n">
+      <c r="F447" t="n">
         <v>7.8</v>
       </c>
-      <c r="E447" s="1" t="n">
+      <c r="G447" s="1" t="n">
         <v>46076</v>
       </c>
-      <c r="F447" t="n">
+      <c r="H447" t="n">
         <v>6.8</v>
       </c>
-      <c r="G447" s="1" t="n">
+      <c r="I447" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="H447" t="n">
+      <c r="J447" t="n">
         <v>6.9</v>
       </c>
-      <c r="I447" s="1" t="n">
+      <c r="K447" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J447" t="n">
+      <c r="L447" t="n">
         <v>7.2</v>
       </c>
-      <c r="K447" s="1" t="n">
+      <c r="M447" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="L447" t="n">
+      <c r="N447" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M447" s="1" t="n">
+      <c r="O447" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="N447" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O447" s="1" t="n">
-        <v>45997</v>
-      </c>
       <c r="P447" t="n">
-        <v>7.37</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="448">
@@ -20095,49 +20171,49 @@
         <v>601</v>
       </c>
       <c r="B450" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C450" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D450" t="n">
         <v>6.1</v>
       </c>
-      <c r="C450" s="1" t="n">
+      <c r="E450" s="1" t="n">
         <v>46074</v>
-      </c>
-      <c r="D450" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E450" s="1" t="n">
-        <v>46068</v>
       </c>
       <c r="F450" t="n">
         <v>7.2</v>
       </c>
       <c r="G450" s="1" t="n">
+        <v>46068</v>
+      </c>
+      <c r="H450" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I450" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="H450" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I450" s="1" t="n">
+      <c r="J450" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K450" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="J450" t="n">
+      <c r="L450" t="n">
         <v>6</v>
       </c>
-      <c r="K450" s="1" t="n">
+      <c r="M450" s="1" t="n">
         <v>46046</v>
       </c>
-      <c r="L450" t="n">
+      <c r="N450" t="n">
         <v>6.1</v>
       </c>
-      <c r="M450" s="1" t="n">
+      <c r="O450" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="N450" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O450" s="1" t="n">
-        <v>45995</v>
-      </c>
       <c r="P450" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="451">
@@ -20145,19 +20221,23 @@
         <v>602</v>
       </c>
       <c r="B451" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="C451" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D451" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E451" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D451" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E451" s="1" t="n">
+      <c r="F451" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G451" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="F451" t="inlineStr"/>
-      <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr"/>
       <c r="I451" t="inlineStr"/>
       <c r="J451" t="inlineStr"/>
@@ -20167,7 +20247,7 @@
       <c r="N451" t="inlineStr"/>
       <c r="O451" t="inlineStr"/>
       <c r="P451" t="n">
-        <v>6.65</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="452">
@@ -20175,49 +20255,49 @@
         <v>603</v>
       </c>
       <c r="B452" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="C452" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D452" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E452" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D452" t="n">
+      <c r="F452" t="n">
         <v>7</v>
       </c>
-      <c r="E452" s="1" t="n">
+      <c r="G452" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F452" t="n">
+      <c r="H452" t="n">
         <v>7.1</v>
       </c>
-      <c r="G452" s="1" t="n">
+      <c r="I452" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H452" t="n">
+      <c r="J452" t="n">
         <v>7.4</v>
       </c>
-      <c r="I452" s="1" t="n">
+      <c r="K452" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="J452" t="n">
+      <c r="L452" t="n">
         <v>7</v>
       </c>
-      <c r="K452" s="1" t="n">
+      <c r="M452" s="1" t="n">
         <v>45991</v>
       </c>
-      <c r="L452" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M452" s="1" t="n">
+      <c r="N452" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O452" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="N452" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O452" s="1" t="n">
-        <v>45970</v>
-      </c>
       <c r="P452" t="n">
-        <v>7</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="453">
@@ -20459,49 +20539,49 @@
         <v>609</v>
       </c>
       <c r="B458" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C458" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D458" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E458" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D458" t="n">
+      <c r="F458" t="n">
         <v>7.6</v>
       </c>
-      <c r="E458" s="1" t="n">
+      <c r="G458" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F458" t="n">
+      <c r="H458" t="n">
         <v>6.4</v>
       </c>
-      <c r="G458" s="1" t="n">
+      <c r="I458" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="H458" t="n">
+      <c r="J458" t="n">
         <v>6.8</v>
       </c>
-      <c r="I458" s="1" t="n">
+      <c r="K458" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="J458" t="n">
+      <c r="L458" t="n">
         <v>5.9</v>
       </c>
-      <c r="K458" s="1" t="n">
+      <c r="M458" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="L458" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M458" s="1" t="n">
+      <c r="N458" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O458" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="N458" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O458" s="1" t="n">
-        <v>45962</v>
-      </c>
       <c r="P458" t="n">
-        <v>6.76</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="459">
@@ -20529,49 +20609,49 @@
         <v>611</v>
       </c>
       <c r="B460" t="n">
+        <v>7</v>
+      </c>
+      <c r="C460" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D460" t="n">
         <v>6.3</v>
       </c>
-      <c r="C460" s="1" t="n">
+      <c r="E460" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D460" t="n">
+      <c r="F460" t="n">
         <v>7.4</v>
       </c>
-      <c r="E460" s="1" t="n">
+      <c r="G460" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F460" t="n">
+      <c r="H460" t="n">
         <v>7.2</v>
       </c>
-      <c r="G460" s="1" t="n">
+      <c r="I460" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H460" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I460" s="1" t="n">
+      <c r="J460" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K460" s="1" t="n">
         <v>46059</v>
       </c>
-      <c r="J460" t="n">
+      <c r="L460" t="n">
         <v>7.2</v>
       </c>
-      <c r="K460" s="1" t="n">
+      <c r="M460" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L460" t="n">
+      <c r="N460" t="n">
         <v>7</v>
       </c>
-      <c r="M460" s="1" t="n">
+      <c r="O460" s="1" t="n">
         <v>46048</v>
       </c>
-      <c r="N460" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O460" s="1" t="n">
-        <v>46012</v>
-      </c>
       <c r="P460" t="n">
-        <v>6.9</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="461">
@@ -20829,49 +20909,49 @@
         <v>618</v>
       </c>
       <c r="B466" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="C466" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D466" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E466" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="F466" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G466" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D466" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E466" s="1" t="n">
+      <c r="H466" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I466" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F466" t="n">
+      <c r="J466" t="n">
         <v>6.8</v>
       </c>
-      <c r="G466" s="1" t="n">
+      <c r="K466" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="H466" t="n">
+      <c r="L466" t="n">
         <v>7.2</v>
       </c>
-      <c r="I466" s="1" t="n">
+      <c r="M466" s="1" t="n">
         <v>46055</v>
       </c>
-      <c r="J466" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K466" s="1" t="n">
+      <c r="N466" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O466" s="1" t="n">
         <v>46052</v>
       </c>
-      <c r="L466" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M466" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="N466" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O466" s="1" t="n">
-        <v>46040</v>
-      </c>
       <c r="P466" t="n">
-        <v>6.63</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="467">
@@ -20879,49 +20959,49 @@
         <v>619</v>
       </c>
       <c r="B467" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="C467" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D467" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E467" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D467" t="n">
+      <c r="F467" t="n">
         <v>7.2</v>
       </c>
-      <c r="E467" s="1" t="n">
+      <c r="G467" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F467" t="n">
+      <c r="H467" t="n">
         <v>7.4</v>
       </c>
-      <c r="G467" s="1" t="n">
+      <c r="I467" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="H467" t="n">
+      <c r="J467" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I467" s="1" t="n">
+      <c r="K467" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="J467" t="n">
+      <c r="L467" t="n">
         <v>7.1</v>
       </c>
-      <c r="K467" s="1" t="n">
+      <c r="M467" s="1" t="n">
         <v>45992</v>
       </c>
-      <c r="L467" t="n">
+      <c r="N467" t="n">
         <v>7.7</v>
       </c>
-      <c r="M467" s="1" t="n">
+      <c r="O467" s="1" t="n">
         <v>45986</v>
       </c>
-      <c r="N467" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O467" s="1" t="n">
-        <v>45961</v>
-      </c>
       <c r="P467" t="n">
-        <v>7.39</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="468">
@@ -20979,41 +21059,45 @@
         <v>621</v>
       </c>
       <c r="B469" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C469" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D469" t="n">
         <v>6.4</v>
       </c>
-      <c r="C469" s="1" t="n">
+      <c r="E469" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D469" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E469" s="1" t="n">
+      <c r="F469" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G469" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F469" t="n">
+      <c r="H469" t="n">
         <v>6.3</v>
       </c>
-      <c r="G469" s="1" t="n">
+      <c r="I469" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H469" t="n">
+      <c r="J469" t="n">
         <v>6.1</v>
       </c>
-      <c r="I469" s="1" t="n">
+      <c r="K469" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J469" t="n">
+      <c r="L469" t="n">
         <v>7.8</v>
       </c>
-      <c r="K469" s="1" t="n">
+      <c r="M469" s="1" t="n">
         <v>46054</v>
       </c>
-      <c r="L469" t="inlineStr"/>
-      <c r="M469" t="inlineStr"/>
       <c r="N469" t="inlineStr"/>
       <c r="O469" t="inlineStr"/>
       <c r="P469" t="n">
-        <v>6.64</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="470">
@@ -21121,49 +21205,49 @@
         <v>624</v>
       </c>
       <c r="B472" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C472" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D472" t="n">
         <v>7.6</v>
       </c>
-      <c r="C472" s="1" t="n">
+      <c r="E472" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D472" t="n">
+      <c r="F472" t="n">
         <v>6.9</v>
       </c>
-      <c r="E472" s="1" t="n">
+      <c r="G472" s="1" t="n">
         <v>46069</v>
       </c>
-      <c r="F472" t="n">
+      <c r="H472" t="n">
         <v>7.7</v>
       </c>
-      <c r="G472" s="1" t="n">
+      <c r="I472" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="H472" t="n">
+      <c r="J472" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I472" s="1" t="n">
+      <c r="K472" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="J472" t="n">
+      <c r="L472" t="n">
         <v>7.9</v>
       </c>
-      <c r="K472" s="1" t="n">
+      <c r="M472" s="1" t="n">
         <v>46011</v>
       </c>
-      <c r="L472" t="n">
+      <c r="N472" t="n">
         <v>6.9</v>
       </c>
-      <c r="M472" s="1" t="n">
+      <c r="O472" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="N472" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O472" s="1" t="n">
-        <v>45997</v>
-      </c>
       <c r="P472" t="n">
-        <v>7.49</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="473">
@@ -21221,49 +21305,49 @@
         <v>626</v>
       </c>
       <c r="B474" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C474" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D474" t="n">
         <v>7.9</v>
       </c>
-      <c r="C474" s="1" t="n">
+      <c r="E474" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D474" t="n">
+      <c r="F474" t="n">
         <v>8.5</v>
       </c>
-      <c r="E474" s="1" t="n">
+      <c r="G474" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F474" t="n">
+      <c r="H474" t="n">
         <v>6.8</v>
       </c>
-      <c r="G474" s="1" t="n">
+      <c r="I474" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H474" t="n">
+      <c r="J474" t="n">
         <v>7.4</v>
       </c>
-      <c r="I474" s="1" t="n">
+      <c r="K474" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J474" t="n">
+      <c r="L474" t="n">
         <v>7.6</v>
       </c>
-      <c r="K474" s="1" t="n">
+      <c r="M474" s="1" t="n">
         <v>46004</v>
       </c>
-      <c r="L474" t="n">
+      <c r="N474" t="n">
         <v>8.1</v>
       </c>
-      <c r="M474" s="1" t="n">
+      <c r="O474" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="N474" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O474" s="1" t="n">
-        <v>45994</v>
-      </c>
       <c r="P474" t="n">
-        <v>7.49</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="475">
@@ -21271,25 +21355,29 @@
         <v>627</v>
       </c>
       <c r="B475" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C475" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="D475" t="n">
         <v>7.8</v>
       </c>
-      <c r="C475" s="1" t="n">
+      <c r="E475" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D475" t="n">
+      <c r="F475" t="n">
         <v>7.1</v>
       </c>
-      <c r="E475" s="1" t="n">
+      <c r="G475" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F475" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G475" s="1" t="n">
+      <c r="H475" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I475" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H475" t="inlineStr"/>
-      <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr"/>
@@ -21297,7 +21385,7 @@
       <c r="N475" t="inlineStr"/>
       <c r="O475" t="inlineStr"/>
       <c r="P475" t="n">
-        <v>7.17</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="476">
@@ -21355,41 +21443,45 @@
         <v>629</v>
       </c>
       <c r="B477" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C477" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D477" t="n">
         <v>7.3</v>
       </c>
-      <c r="C477" s="1" t="n">
+      <c r="E477" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D477" t="n">
+      <c r="F477" t="n">
         <v>6.9</v>
       </c>
-      <c r="E477" s="1" t="n">
+      <c r="G477" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F477" t="n">
+      <c r="H477" t="n">
         <v>6.4</v>
       </c>
-      <c r="G477" s="1" t="n">
+      <c r="I477" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H477" t="n">
+      <c r="J477" t="n">
         <v>8.6</v>
       </c>
-      <c r="I477" s="1" t="n">
+      <c r="K477" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="J477" t="n">
+      <c r="L477" t="n">
         <v>6.8</v>
       </c>
-      <c r="K477" s="1" t="n">
+      <c r="M477" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="L477" t="inlineStr"/>
-      <c r="M477" t="inlineStr"/>
       <c r="N477" t="inlineStr"/>
       <c r="O477" t="inlineStr"/>
       <c r="P477" t="n">
-        <v>7.2</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="478">
@@ -21397,25 +21489,29 @@
         <v>630</v>
       </c>
       <c r="B478" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C478" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D478" t="n">
         <v>6.1</v>
       </c>
-      <c r="C478" s="1" t="n">
+      <c r="E478" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="D478" t="n">
+      <c r="F478" t="n">
         <v>7.5</v>
       </c>
-      <c r="E478" s="1" t="n">
+      <c r="G478" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="F478" t="n">
+      <c r="H478" t="n">
         <v>7.3</v>
       </c>
-      <c r="G478" s="1" t="n">
+      <c r="I478" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="H478" t="inlineStr"/>
-      <c r="I478" t="inlineStr"/>
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr"/>
       <c r="L478" t="inlineStr"/>
@@ -21423,7 +21519,7 @@
       <c r="N478" t="inlineStr"/>
       <c r="O478" t="inlineStr"/>
       <c r="P478" t="n">
-        <v>6.97</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="479">
@@ -21431,46 +21527,46 @@
         <v>631</v>
       </c>
       <c r="B479" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="C479" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D479" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E479" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="D479" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E479" s="1" t="n">
+      <c r="F479" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G479" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F479" t="n">
+      <c r="H479" t="n">
         <v>7</v>
       </c>
-      <c r="G479" s="1" t="n">
+      <c r="I479" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H479" t="n">
+      <c r="J479" t="n">
         <v>6.8</v>
       </c>
-      <c r="I479" s="1" t="n">
+      <c r="K479" s="1" t="n">
         <v>46061</v>
       </c>
-      <c r="J479" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K479" s="1" t="n">
+      <c r="L479" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M479" s="1" t="n">
         <v>46056</v>
       </c>
-      <c r="L479" t="n">
+      <c r="N479" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M479" s="1" t="n">
+      <c r="O479" s="1" t="n">
         <v>46053</v>
-      </c>
-      <c r="N479" t="n">
-        <v>7</v>
-      </c>
-      <c r="O479" s="1" t="n">
-        <v>45996</v>
       </c>
       <c r="P479" t="n">
         <v>7.19</v>
@@ -21623,46 +21719,46 @@
         <v>635</v>
       </c>
       <c r="B483" t="n">
+        <v>7</v>
+      </c>
+      <c r="C483" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D483" t="n">
         <v>7.3</v>
       </c>
-      <c r="C483" s="1" t="n">
+      <c r="E483" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="D483" t="n">
+      <c r="F483" t="n">
         <v>7.1</v>
       </c>
-      <c r="E483" s="1" t="n">
+      <c r="G483" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="F483" t="n">
+      <c r="H483" t="n">
         <v>7.5</v>
       </c>
-      <c r="G483" s="1" t="n">
+      <c r="I483" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="H483" t="n">
+      <c r="J483" t="n">
         <v>6.9</v>
       </c>
-      <c r="I483" s="1" t="n">
+      <c r="K483" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="J483" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K483" s="1" t="n">
+      <c r="L483" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M483" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="L483" t="n">
+      <c r="N483" t="n">
         <v>7.2</v>
       </c>
-      <c r="M483" s="1" t="n">
+      <c r="O483" s="1" t="n">
         <v>45954</v>
-      </c>
-      <c r="N483" t="n">
-        <v>7</v>
-      </c>
-      <c r="O483" s="1" t="n">
-        <v>45948</v>
       </c>
       <c r="P483" t="n">
         <v>7.1</v>
@@ -21723,49 +21819,49 @@
         <v>637</v>
       </c>
       <c r="B485" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C485" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D485" t="n">
         <v>6.3</v>
       </c>
-      <c r="C485" s="1" t="n">
+      <c r="E485" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D485" t="n">
+      <c r="F485" t="n">
         <v>7</v>
       </c>
-      <c r="E485" s="1" t="n">
+      <c r="G485" s="1" t="n">
         <v>46074</v>
       </c>
-      <c r="F485" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G485" s="1" t="n">
+      <c r="H485" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I485" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="H485" t="n">
+      <c r="J485" t="n">
         <v>7.3</v>
       </c>
-      <c r="I485" s="1" t="n">
+      <c r="K485" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J485" t="n">
+      <c r="L485" t="n">
         <v>6.4</v>
       </c>
-      <c r="K485" s="1" t="n">
+      <c r="M485" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="L485" t="n">
+      <c r="N485" t="n">
         <v>6.8</v>
       </c>
-      <c r="M485" s="1" t="n">
+      <c r="O485" s="1" t="n">
         <v>45982</v>
       </c>
-      <c r="N485" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O485" s="1" t="n">
-        <v>45935</v>
-      </c>
       <c r="P485" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="486">
@@ -21773,49 +21869,49 @@
         <v>638</v>
       </c>
       <c r="B486" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C486" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D486" t="n">
         <v>6.4</v>
       </c>
-      <c r="C486" s="1" t="n">
+      <c r="E486" s="1" t="n">
         <v>46067</v>
       </c>
-      <c r="D486" t="n">
+      <c r="F486" t="n">
         <v>7.8</v>
       </c>
-      <c r="E486" s="1" t="n">
+      <c r="G486" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="F486" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G486" s="1" t="n">
+      <c r="H486" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I486" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="H486" t="n">
+      <c r="J486" t="n">
         <v>7</v>
       </c>
-      <c r="I486" s="1" t="n">
+      <c r="K486" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="J486" t="n">
+      <c r="L486" t="n">
         <v>7.2</v>
       </c>
-      <c r="K486" s="1" t="n">
+      <c r="M486" s="1" t="n">
         <v>45963</v>
       </c>
-      <c r="L486" t="n">
+      <c r="N486" t="n">
         <v>7.8</v>
       </c>
-      <c r="M486" s="1" t="n">
+      <c r="O486" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="N486" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O486" s="1" t="n">
-        <v>45947</v>
-      </c>
       <c r="P486" t="n">
-        <v>7.17</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="487">
@@ -21873,49 +21969,49 @@
         <v>640</v>
       </c>
       <c r="B488" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C488" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D488" t="n">
         <v>7.8</v>
       </c>
-      <c r="C488" s="1" t="n">
+      <c r="E488" s="1" t="n">
         <v>46080</v>
       </c>
-      <c r="D488" t="n">
+      <c r="F488" t="n">
         <v>6.9</v>
       </c>
-      <c r="E488" s="1" t="n">
+      <c r="G488" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="F488" t="n">
+      <c r="H488" t="n">
         <v>7.8</v>
       </c>
-      <c r="G488" s="1" t="n">
+      <c r="I488" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="H488" t="n">
+      <c r="J488" t="n">
         <v>8.6</v>
       </c>
-      <c r="I488" s="1" t="n">
+      <c r="K488" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="J488" t="n">
+      <c r="L488" t="n">
         <v>7.4</v>
       </c>
-      <c r="K488" s="1" t="n">
+      <c r="M488" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="L488" t="n">
+      <c r="N488" t="n">
         <v>7.7</v>
       </c>
-      <c r="M488" s="1" t="n">
+      <c r="O488" s="1" t="n">
         <v>45968</v>
       </c>
-      <c r="N488" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O488" s="1" t="n">
-        <v>45962</v>
-      </c>
       <c r="P488" t="n">
-        <v>7.56</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="489">
@@ -21923,49 +22019,49 @@
         <v>641</v>
       </c>
       <c r="B489" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="C489" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="D489" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E489" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="D489" t="n">
+      <c r="F489" t="n">
         <v>7</v>
       </c>
-      <c r="E489" s="1" t="n">
+      <c r="G489" s="1" t="n">
         <v>46003</v>
       </c>
-      <c r="F489" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G489" s="1" t="n">
+      <c r="H489" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I489" s="1" t="n">
         <v>45997</v>
       </c>
-      <c r="H489" t="n">
+      <c r="J489" t="n">
         <v>6.4</v>
       </c>
-      <c r="I489" s="1" t="n">
+      <c r="K489" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="J489" t="n">
+      <c r="L489" t="n">
         <v>6.8</v>
       </c>
-      <c r="K489" s="1" t="n">
+      <c r="M489" s="1" t="n">
         <v>45983</v>
       </c>
-      <c r="L489" t="n">
+      <c r="N489" t="n">
         <v>7.2</v>
       </c>
-      <c r="M489" s="1" t="n">
+      <c r="O489" s="1" t="n">
         <v>45969</v>
       </c>
-      <c r="N489" t="n">
-        <v>7</v>
-      </c>
-      <c r="O489" s="1" t="n">
-        <v>45963</v>
-      </c>
       <c r="P489" t="n">
-        <v>6.81</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="490">
@@ -22076,46 +22172,116 @@
         <v>6.6</v>
       </c>
       <c r="C492" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="D492" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E492" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="D492" t="n">
+      <c r="F492" t="n">
         <v>6.4</v>
       </c>
-      <c r="E492" s="1" t="n">
+      <c r="G492" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="F492" t="n">
+      <c r="H492" t="n">
         <v>7</v>
       </c>
-      <c r="G492" s="1" t="n">
+      <c r="I492" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="H492" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I492" s="1" t="n">
+      <c r="J492" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K492" s="1" t="n">
         <v>46060</v>
       </c>
-      <c r="J492" t="n">
+      <c r="L492" t="n">
         <v>7.2</v>
       </c>
-      <c r="K492" s="1" t="n">
+      <c r="M492" s="1" t="n">
         <v>45998</v>
       </c>
-      <c r="L492" t="n">
+      <c r="N492" t="n">
         <v>7.4</v>
       </c>
-      <c r="M492" s="1" t="n">
+      <c r="O492" s="1" t="n">
         <v>45989</v>
-      </c>
-      <c r="N492" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O492" s="1" t="n">
-        <v>45983</v>
       </c>
       <c r="P492" t="n">
         <v>6.83</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>645</v>
+      </c>
+      <c r="B493" t="inlineStr"/>
+      <c r="C493" t="inlineStr"/>
+      <c r="D493" t="inlineStr"/>
+      <c r="E493" t="inlineStr"/>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr"/>
+      <c r="H493" t="inlineStr"/>
+      <c r="I493" t="inlineStr"/>
+      <c r="J493" t="inlineStr"/>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr"/>
+      <c r="N493" t="inlineStr"/>
+      <c r="O493" t="inlineStr"/>
+      <c r="P493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>646</v>
+      </c>
+      <c r="B494" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="C494" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D494" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E494" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="F494" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G494" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="H494" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I494" s="1" t="n">
+        <v>46067</v>
+      </c>
+      <c r="J494" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K494" s="1" t="n">
+        <v>46005</v>
+      </c>
+      <c r="L494" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M494" s="1" t="n">
+        <v>45998</v>
+      </c>
+      <c r="N494" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O494" s="1" t="n">
+        <v>45990</v>
+      </c>
+      <c r="P494" t="n">
+        <v>7.16</v>
       </c>
     </row>
   </sheetData>

--- a/players_ratings.xlsx
+++ b/players_ratings.xlsx
@@ -519,49 +519,49 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="D2" t="n">
         <v>7.1</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="E2" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="D2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E2" s="2" t="n">
+      <c r="F2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>7.3</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="K2" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>7.6</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M2" s="2" t="n">
+      <c r="N2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="N2" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>45954</v>
-      </c>
       <c r="P2" t="n">
-        <v>6.87</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="3">
@@ -841,49 +841,49 @@
         <v>27</v>
       </c>
       <c r="B9" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="C9" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>7.2</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>6.2</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>7.7</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K9" s="2" t="n">
+      <c r="L9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="L9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M9" s="2" t="n">
+      <c r="N9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O9" s="2" t="n">
         <v>45982</v>
       </c>
-      <c r="N9" t="n">
-        <v>8</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>45969</v>
-      </c>
       <c r="P9" t="n">
-        <v>6.99</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="10">
@@ -1111,49 +1111,49 @@
         <v>38</v>
       </c>
       <c r="B15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D15" t="n">
         <v>6.9</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="E15" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>6.8</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>6.3</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="I15" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>6.4</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="K15" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>6.9</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="M15" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>8.1</v>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="O15" s="2" t="n">
         <v>45983</v>
       </c>
-      <c r="N15" t="n">
-        <v>7</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>45970</v>
-      </c>
       <c r="P15" t="n">
-        <v>6.91</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="16">
@@ -1187,41 +1187,45 @@
         <v>41</v>
       </c>
       <c r="B17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D17" t="n">
         <v>7.1</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E17" s="2" t="n">
+      <c r="F17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
         <v>6.4</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="I17" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I17" s="2" t="n">
+      <c r="J17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K17" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>6.3</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="M17" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>6.58</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="18">
@@ -1229,49 +1233,49 @@
         <v>43</v>
       </c>
       <c r="B18" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="C18" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>6.3</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="H18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I18" s="2" t="n">
+      <c r="J18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K18" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>7.7</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>6</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="O18" s="2" t="n">
         <v>45981</v>
       </c>
-      <c r="N18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>45968</v>
-      </c>
       <c r="P18" t="n">
-        <v>6.73</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="19">
@@ -1875,46 +1879,46 @@
         <v>69</v>
       </c>
       <c r="B33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D33" t="n">
         <v>7</v>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="E33" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D33" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E33" s="2" t="n">
+      <c r="F33" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G33" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>6.3</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="I33" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>7.1</v>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="K33" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>6.4</v>
       </c>
-      <c r="K33" s="2" t="n">
+      <c r="M33" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="L33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M33" s="2" t="n">
+      <c r="N33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O33" s="2" t="n">
         <v>45969</v>
-      </c>
-      <c r="N33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v>45956</v>
       </c>
       <c r="P33" t="n">
         <v>6.64</v>
@@ -1925,46 +1929,46 @@
         <v>75</v>
       </c>
       <c r="B34" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C34" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E34" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>6.4</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G34" s="2" t="n">
+      <c r="H34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I34" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I34" s="2" t="n">
+      <c r="J34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K34" s="2" t="n">
         <v>46084</v>
       </c>
-      <c r="J34" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K34" s="2" t="n">
+      <c r="L34" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>6.2</v>
       </c>
-      <c r="M34" s="2" t="n">
+      <c r="O34" s="2" t="n">
         <v>46069</v>
-      </c>
-      <c r="N34" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O34" s="2" t="n">
-        <v>46055</v>
       </c>
       <c r="P34" t="n">
         <v>6.47</v>
@@ -1975,49 +1979,49 @@
         <v>80</v>
       </c>
       <c r="B35" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="C35" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D35" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E35" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>7.1</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F35" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G35" s="2" t="n">
+      <c r="H35" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I35" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>6.8</v>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="K35" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>6.2</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="M35" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>6.8</v>
       </c>
-      <c r="M35" s="2" t="n">
+      <c r="O35" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N35" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O35" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P35" t="n">
-        <v>6.8</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="36">
@@ -2773,49 +2777,49 @@
         <v>133</v>
       </c>
       <c r="B62" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C62" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D62" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E62" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
         <v>7.4</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F62" t="n">
+      <c r="H62" t="n">
         <v>6.2</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="I62" s="2" t="n">
         <v>46083</v>
       </c>
-      <c r="H62" t="n">
+      <c r="J62" t="n">
         <v>7.3</v>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="K62" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>6.9</v>
       </c>
-      <c r="K62" s="2" t="n">
+      <c r="M62" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L62" t="n">
+      <c r="N62" t="n">
         <v>7.3</v>
       </c>
-      <c r="M62" s="2" t="n">
+      <c r="O62" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N62" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O62" s="2" t="n">
-        <v>45997</v>
-      </c>
       <c r="P62" t="n">
-        <v>7.04</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="63">
@@ -2993,49 +2997,49 @@
         <v>144</v>
       </c>
       <c r="B67" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D67" t="n">
         <v>7.5</v>
       </c>
-      <c r="C67" s="2" t="n">
+      <c r="E67" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D67" t="n">
+      <c r="F67" t="n">
         <v>7</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F67" t="n">
+      <c r="H67" t="n">
         <v>8.1</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="I67" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H67" t="n">
+      <c r="J67" t="n">
         <v>7.5</v>
       </c>
-      <c r="I67" s="2" t="n">
+      <c r="K67" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J67" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K67" s="2" t="n">
+      <c r="L67" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M67" s="2" t="n">
         <v>45996</v>
       </c>
-      <c r="L67" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M67" s="2" t="n">
+      <c r="N67" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O67" s="2" t="n">
         <v>45972</v>
       </c>
-      <c r="N67" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O67" s="2" t="n">
-        <v>45962</v>
-      </c>
       <c r="P67" t="n">
-        <v>7.19</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="68">
@@ -3093,49 +3097,49 @@
         <v>146</v>
       </c>
       <c r="B69" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D69" t="n">
         <v>6.8</v>
       </c>
-      <c r="C69" s="2" t="n">
+      <c r="E69" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D69" t="n">
+      <c r="F69" t="n">
         <v>7.1</v>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F69" t="n">
+      <c r="H69" t="n">
         <v>7.3</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="I69" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H69" t="n">
+      <c r="J69" t="n">
         <v>6.8</v>
       </c>
-      <c r="I69" s="2" t="n">
+      <c r="K69" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>7.7</v>
       </c>
-      <c r="K69" s="2" t="n">
+      <c r="M69" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L69" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M69" s="2" t="n">
+      <c r="N69" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O69" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="N69" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O69" s="2" t="n">
-        <v>46059</v>
-      </c>
       <c r="P69" t="n">
-        <v>7</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="70">
@@ -3143,49 +3147,49 @@
         <v>147</v>
       </c>
       <c r="B70" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="C70" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E70" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="D70" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E70" s="2" t="n">
+      <c r="F70" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G70" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F70" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G70" s="2" t="n">
+      <c r="H70" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I70" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H70" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I70" s="2" t="n">
+      <c r="J70" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K70" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>6.2</v>
       </c>
-      <c r="K70" s="2" t="n">
+      <c r="M70" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="L70" t="n">
+      <c r="N70" t="n">
         <v>7.1</v>
       </c>
-      <c r="M70" s="2" t="n">
+      <c r="O70" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="N70" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O70" s="2" t="n">
-        <v>46056</v>
-      </c>
       <c r="P70" t="n">
-        <v>6.63</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="71">
@@ -3213,46 +3217,46 @@
         <v>149</v>
       </c>
       <c r="B72" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C72" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D72" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E72" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D72" t="n">
+      <c r="F72" t="n">
         <v>6.3</v>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F72" t="n">
+      <c r="H72" t="n">
         <v>7.1</v>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="I72" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H72" t="n">
+      <c r="J72" t="n">
         <v>6.9</v>
       </c>
-      <c r="I72" s="2" t="n">
+      <c r="K72" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J72" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K72" s="2" t="n">
+      <c r="L72" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M72" s="2" t="n">
         <v>45998</v>
       </c>
-      <c r="L72" t="n">
+      <c r="N72" t="n">
         <v>7.1</v>
       </c>
-      <c r="M72" s="2" t="n">
+      <c r="O72" s="2" t="n">
         <v>45989</v>
-      </c>
-      <c r="N72" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O72" s="2" t="n">
-        <v>45983</v>
       </c>
       <c r="P72" t="n">
         <v>6.71</v>
@@ -3363,49 +3367,49 @@
         <v>164</v>
       </c>
       <c r="B75" t="n">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="H75" t="n">
         <v>5.9</v>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="I75" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="D75" t="n">
+      <c r="J75" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="K75" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="F75" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G75" s="2" t="n">
+      <c r="L75" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M75" s="2" t="n">
         <v>45982</v>
       </c>
-      <c r="H75" t="n">
+      <c r="N75" t="n">
         <v>7.4</v>
       </c>
-      <c r="I75" s="2" t="n">
+      <c r="O75" s="2" t="n">
         <v>45975</v>
       </c>
-      <c r="J75" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="K75" s="2" t="n">
-        <v>45970</v>
-      </c>
-      <c r="L75" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="M75" s="2" t="n">
-        <v>45963</v>
-      </c>
-      <c r="N75" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O75" s="2" t="n">
-        <v>45954</v>
-      </c>
       <c r="P75" t="n">
-        <v>7.29</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="76">
@@ -3563,19 +3567,23 @@
         <v>169</v>
       </c>
       <c r="B79" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="C79" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D79" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E79" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="D79" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E79" s="2" t="n">
+      <c r="F79" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G79" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
@@ -3585,7 +3593,7 @@
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
-        <v>6.65</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="80">
@@ -3593,49 +3601,49 @@
         <v>170</v>
       </c>
       <c r="B80" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D80" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="F80" t="n">
         <v>7.3</v>
       </c>
-      <c r="C80" s="2" t="n">
+      <c r="G80" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="D80" t="n">
+      <c r="H80" t="n">
         <v>7.1</v>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="I80" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="F80" t="n">
+      <c r="J80" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="K80" s="2" t="n">
         <v>45982</v>
       </c>
-      <c r="H80" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I80" s="2" t="n">
+      <c r="L80" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M80" s="2" t="n">
         <v>45975</v>
       </c>
-      <c r="J80" t="n">
+      <c r="N80" t="n">
         <v>6.9</v>
       </c>
-      <c r="K80" s="2" t="n">
+      <c r="O80" s="2" t="n">
         <v>45970</v>
       </c>
-      <c r="L80" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>45963</v>
-      </c>
-      <c r="N80" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O80" s="2" t="n">
-        <v>45955</v>
-      </c>
       <c r="P80" t="n">
-        <v>7.26</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="81">
@@ -3685,41 +3693,45 @@
         <v>173</v>
       </c>
       <c r="B82" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D82" t="n">
         <v>7.1</v>
       </c>
-      <c r="C82" s="2" t="n">
+      <c r="E82" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D82" t="n">
+      <c r="F82" t="n">
         <v>7.3</v>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="G82" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F82" t="n">
+      <c r="H82" t="n">
         <v>6.8</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="I82" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H82" t="n">
+      <c r="J82" t="n">
         <v>6.3</v>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="K82" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J82" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K82" s="2" t="n">
+      <c r="L82" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M82" s="2" t="n">
         <v>46058</v>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
-        <v>6.8</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="83">
@@ -3861,49 +3873,49 @@
         <v>178</v>
       </c>
       <c r="B86" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="D86" t="n">
         <v>6.1</v>
       </c>
-      <c r="C86" s="2" t="n">
+      <c r="E86" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="D86" t="n">
+      <c r="F86" t="n">
         <v>7.1</v>
       </c>
-      <c r="E86" s="2" t="n">
+      <c r="G86" s="2" t="n">
         <v>45982</v>
       </c>
-      <c r="F86" t="n">
+      <c r="H86" t="n">
         <v>6.1</v>
       </c>
-      <c r="G86" s="2" t="n">
+      <c r="I86" s="2" t="n">
         <v>45976</v>
       </c>
-      <c r="H86" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I86" s="2" t="n">
+      <c r="J86" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K86" s="2" t="n">
         <v>45970</v>
       </c>
-      <c r="J86" t="n">
+      <c r="L86" t="n">
         <v>6.3</v>
       </c>
-      <c r="K86" s="2" t="n">
+      <c r="M86" s="2" t="n">
         <v>45955</v>
       </c>
-      <c r="L86" t="n">
+      <c r="N86" t="n">
         <v>6.9</v>
       </c>
-      <c r="M86" s="2" t="n">
+      <c r="O86" s="2" t="n">
         <v>45948</v>
       </c>
-      <c r="N86" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O86" s="2" t="n">
-        <v>45877</v>
-      </c>
       <c r="P86" t="n">
-        <v>6.53</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="87">
@@ -3911,49 +3923,49 @@
         <v>181</v>
       </c>
       <c r="B87" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D87" t="n">
         <v>7</v>
       </c>
-      <c r="C87" s="2" t="n">
+      <c r="E87" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="D87" t="n">
+      <c r="F87" t="n">
         <v>6.4</v>
       </c>
-      <c r="E87" s="2" t="n">
+      <c r="G87" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="F87" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G87" s="2" t="n">
+      <c r="H87" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I87" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="H87" t="n">
+      <c r="J87" t="n">
         <v>6.9</v>
       </c>
-      <c r="I87" s="2" t="n">
+      <c r="K87" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="J87" t="n">
+      <c r="L87" t="n">
         <v>7.1</v>
       </c>
-      <c r="K87" s="2" t="n">
+      <c r="M87" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="L87" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M87" s="2" t="n">
+      <c r="N87" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O87" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="N87" t="n">
-        <v>7</v>
-      </c>
-      <c r="O87" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P87" t="n">
-        <v>6.8</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="88">
@@ -3961,49 +3973,49 @@
         <v>182</v>
       </c>
       <c r="B88" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D88" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="F88" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="H88" t="n">
         <v>6.1</v>
       </c>
-      <c r="C88" s="2" t="n">
+      <c r="I88" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="D88" t="n">
+      <c r="J88" t="n">
         <v>7.6</v>
       </c>
-      <c r="E88" s="2" t="n">
+      <c r="K88" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="F88" t="n">
+      <c r="L88" t="n">
         <v>7.2</v>
       </c>
-      <c r="G88" s="2" t="n">
+      <c r="M88" s="2" t="n">
         <v>45982</v>
       </c>
-      <c r="H88" t="n">
+      <c r="N88" t="n">
         <v>6</v>
       </c>
-      <c r="I88" s="2" t="n">
+      <c r="O88" s="2" t="n">
         <v>45970</v>
       </c>
-      <c r="J88" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>45963</v>
-      </c>
-      <c r="L88" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M88" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="N88" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O88" s="2" t="n">
-        <v>45947</v>
-      </c>
       <c r="P88" t="n">
-        <v>6.91</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="89">
@@ -4014,22 +4026,26 @@
         <v>6.9</v>
       </c>
       <c r="C89" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D89" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E89" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="D89" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E89" s="2" t="n">
+      <c r="F89" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G89" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="F89" t="n">
+      <c r="H89" t="n">
         <v>6.9</v>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="I89" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -4037,7 +4053,7 @@
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="n">
-        <v>6.8</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="90">
@@ -4095,49 +4111,49 @@
         <v>186</v>
       </c>
       <c r="B91" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D91" t="n">
         <v>6.9</v>
       </c>
-      <c r="C91" s="2" t="n">
+      <c r="E91" s="2" t="n">
         <v>46099</v>
       </c>
-      <c r="D91" t="n">
+      <c r="F91" t="n">
         <v>7.5</v>
       </c>
-      <c r="E91" s="2" t="n">
+      <c r="G91" s="2" t="n">
         <v>46093</v>
       </c>
-      <c r="F91" t="n">
+      <c r="H91" t="n">
         <v>7.6</v>
       </c>
-      <c r="G91" s="2" t="n">
+      <c r="I91" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H91" t="n">
+      <c r="J91" t="n">
         <v>7.2</v>
       </c>
-      <c r="I91" s="2" t="n">
+      <c r="K91" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J91" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K91" s="2" t="n">
+      <c r="L91" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M91" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L91" t="n">
+      <c r="N91" t="n">
         <v>6.2</v>
       </c>
-      <c r="M91" s="2" t="n">
+      <c r="O91" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N91" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O91" s="2" t="n">
-        <v>46051</v>
-      </c>
       <c r="P91" t="n">
-        <v>7.04</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="92">
@@ -4215,49 +4231,49 @@
         <v>191</v>
       </c>
       <c r="B94" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="D94" t="n">
         <v>5.9</v>
       </c>
-      <c r="C94" s="2" t="n">
+      <c r="E94" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="D94" t="n">
+      <c r="F94" t="n">
         <v>7</v>
       </c>
-      <c r="E94" s="2" t="n">
+      <c r="G94" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="F94" t="n">
+      <c r="H94" t="n">
         <v>8</v>
       </c>
-      <c r="G94" s="2" t="n">
+      <c r="I94" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="H94" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I94" s="2" t="n">
+      <c r="J94" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K94" s="2" t="n">
         <v>46005</v>
       </c>
-      <c r="J94" t="n">
+      <c r="L94" t="n">
         <v>6.2</v>
       </c>
-      <c r="K94" s="2" t="n">
+      <c r="M94" s="2" t="n">
         <v>45997</v>
       </c>
-      <c r="L94" t="n">
+      <c r="N94" t="n">
         <v>7.2</v>
       </c>
-      <c r="M94" s="2" t="n">
+      <c r="O94" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="N94" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O94" s="2" t="n">
-        <v>45978</v>
-      </c>
       <c r="P94" t="n">
-        <v>6.96</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="95">
@@ -4265,49 +4281,49 @@
         <v>192</v>
       </c>
       <c r="B95" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D95" t="n">
         <v>6.3</v>
       </c>
-      <c r="C95" s="2" t="n">
+      <c r="E95" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="D95" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E95" s="2" t="n">
+      <c r="F95" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G95" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="F95" t="n">
+      <c r="H95" t="n">
         <v>7.1</v>
       </c>
-      <c r="G95" s="2" t="n">
+      <c r="I95" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H95" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I95" s="2" t="n">
+      <c r="J95" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K95" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J95" t="n">
+      <c r="L95" t="n">
         <v>6.9</v>
       </c>
-      <c r="K95" s="2" t="n">
+      <c r="M95" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L95" t="n">
+      <c r="N95" t="n">
         <v>5.8</v>
       </c>
-      <c r="M95" s="2" t="n">
+      <c r="O95" s="2" t="n">
         <v>46064</v>
       </c>
-      <c r="N95" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O95" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P95" t="n">
-        <v>6.51</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="96">
@@ -4407,49 +4423,49 @@
         <v>195</v>
       </c>
       <c r="B98" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D98" t="n">
         <v>7.9</v>
       </c>
-      <c r="C98" s="2" t="n">
+      <c r="E98" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D98" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E98" s="2" t="n">
+      <c r="F98" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G98" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F98" t="n">
+      <c r="H98" t="n">
         <v>6.2</v>
       </c>
-      <c r="G98" s="2" t="n">
+      <c r="I98" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H98" t="n">
+      <c r="J98" t="n">
         <v>8.4</v>
       </c>
-      <c r="I98" s="2" t="n">
+      <c r="K98" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J98" t="n">
+      <c r="L98" t="n">
         <v>6.1</v>
       </c>
-      <c r="K98" s="2" t="n">
+      <c r="M98" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L98" t="n">
+      <c r="N98" t="n">
         <v>7.7</v>
       </c>
-      <c r="M98" s="2" t="n">
+      <c r="O98" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N98" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O98" s="2" t="n">
-        <v>46054</v>
-      </c>
       <c r="P98" t="n">
-        <v>6.97</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="99">
@@ -4557,49 +4573,49 @@
         <v>200</v>
       </c>
       <c r="B101" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D101" t="n">
         <v>6.3</v>
       </c>
-      <c r="C101" s="2" t="n">
+      <c r="E101" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D101" t="n">
+      <c r="F101" t="n">
         <v>6.8</v>
       </c>
-      <c r="E101" s="2" t="n">
+      <c r="G101" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F101" t="n">
+      <c r="H101" t="n">
         <v>7</v>
       </c>
-      <c r="G101" s="2" t="n">
+      <c r="I101" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H101" t="n">
+      <c r="J101" t="n">
         <v>5.9</v>
       </c>
-      <c r="I101" s="2" t="n">
+      <c r="K101" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J101" t="n">
+      <c r="L101" t="n">
         <v>6.9</v>
       </c>
-      <c r="K101" s="2" t="n">
+      <c r="M101" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L101" t="n">
+      <c r="N101" t="n">
         <v>7.9</v>
       </c>
-      <c r="M101" s="2" t="n">
+      <c r="O101" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="N101" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O101" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P101" t="n">
-        <v>6.76</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="102">
@@ -4607,49 +4623,49 @@
         <v>201</v>
       </c>
       <c r="B102" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D102" t="n">
         <v>7.3</v>
       </c>
-      <c r="C102" s="2" t="n">
+      <c r="E102" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="D102" t="n">
+      <c r="F102" t="n">
         <v>5.9</v>
       </c>
-      <c r="E102" s="2" t="n">
+      <c r="G102" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="F102" t="n">
+      <c r="H102" t="n">
         <v>5.7</v>
       </c>
-      <c r="G102" s="2" t="n">
+      <c r="I102" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="H102" t="n">
+      <c r="J102" t="n">
         <v>6</v>
       </c>
-      <c r="I102" s="2" t="n">
+      <c r="K102" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="J102" t="n">
+      <c r="L102" t="n">
         <v>6.2</v>
       </c>
-      <c r="K102" s="2" t="n">
+      <c r="M102" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="L102" t="n">
+      <c r="N102" t="n">
         <v>6.9</v>
       </c>
-      <c r="M102" s="2" t="n">
+      <c r="O102" s="2" t="n">
         <v>45949</v>
       </c>
-      <c r="N102" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O102" s="2" t="n">
-        <v>45934</v>
-      </c>
       <c r="P102" t="n">
-        <v>6.5</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="103">
@@ -4657,37 +4673,49 @@
         <v>202</v>
       </c>
       <c r="B103" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="D103" t="n">
         <v>6.4</v>
       </c>
-      <c r="C103" s="2" t="n">
+      <c r="E103" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="F103" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="H103" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I103" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="D103" t="n">
+      <c r="J103" t="n">
         <v>7</v>
       </c>
-      <c r="E103" s="2" t="n">
+      <c r="K103" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="F103" t="n">
+      <c r="L103" t="n">
         <v>7.2</v>
       </c>
-      <c r="G103" s="2" t="n">
+      <c r="M103" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="H103" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I103" s="2" t="n">
+      <c r="N103" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O103" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>6.8</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="104">
@@ -5067,41 +5095,45 @@
         <v>217</v>
       </c>
       <c r="B113" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D113" t="n">
         <v>7.1</v>
       </c>
-      <c r="C113" s="2" t="n">
+      <c r="E113" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="D113" t="n">
+      <c r="F113" t="n">
         <v>5.6</v>
       </c>
-      <c r="E113" s="2" t="n">
+      <c r="G113" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="F113" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G113" s="2" t="n">
+      <c r="H113" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I113" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="H113" t="n">
+      <c r="J113" t="n">
         <v>6</v>
       </c>
-      <c r="I113" s="2" t="n">
+      <c r="K113" s="2" t="n">
         <v>46065</v>
       </c>
-      <c r="J113" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K113" s="2" t="n">
+      <c r="L113" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M113" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
-        <v>6.4</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="114">
@@ -5943,49 +5975,49 @@
         <v>247</v>
       </c>
       <c r="B136" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D136" t="n">
         <v>7.3</v>
       </c>
-      <c r="C136" s="2" t="n">
+      <c r="E136" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D136" t="n">
+      <c r="F136" t="n">
         <v>7.7</v>
       </c>
-      <c r="E136" s="2" t="n">
+      <c r="G136" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F136" t="n">
+      <c r="H136" t="n">
         <v>7.5</v>
       </c>
-      <c r="G136" s="2" t="n">
+      <c r="I136" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="H136" t="n">
+      <c r="J136" t="n">
         <v>6.8</v>
       </c>
-      <c r="I136" s="2" t="n">
+      <c r="K136" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J136" t="n">
+      <c r="L136" t="n">
         <v>7.1</v>
       </c>
-      <c r="K136" s="2" t="n">
+      <c r="M136" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="L136" t="n">
+      <c r="N136" t="n">
         <v>5.8</v>
       </c>
-      <c r="M136" s="2" t="n">
+      <c r="O136" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="N136" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O136" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P136" t="n">
-        <v>7.19</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="137">
@@ -5993,49 +6025,49 @@
         <v>248</v>
       </c>
       <c r="B137" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D137" t="n">
         <v>7.3</v>
       </c>
-      <c r="C137" s="2" t="n">
+      <c r="E137" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D137" t="n">
+      <c r="F137" t="n">
         <v>6.9</v>
       </c>
-      <c r="E137" s="2" t="n">
+      <c r="G137" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F137" t="n">
+      <c r="H137" t="n">
         <v>6.8</v>
       </c>
-      <c r="G137" s="2" t="n">
+      <c r="I137" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H137" t="n">
+      <c r="J137" t="n">
         <v>6.3</v>
       </c>
-      <c r="I137" s="2" t="n">
+      <c r="K137" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J137" t="n">
+      <c r="L137" t="n">
         <v>6.9</v>
       </c>
-      <c r="K137" s="2" t="n">
+      <c r="M137" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L137" t="n">
+      <c r="N137" t="n">
         <v>7.7</v>
       </c>
-      <c r="M137" s="2" t="n">
+      <c r="O137" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N137" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O137" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="P137" t="n">
-        <v>7.16</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="138">
@@ -6093,49 +6125,49 @@
         <v>255</v>
       </c>
       <c r="B139" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D139" t="n">
         <v>8.1</v>
       </c>
-      <c r="C139" s="2" t="n">
+      <c r="E139" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D139" t="n">
+      <c r="F139" t="n">
         <v>6.1</v>
       </c>
-      <c r="E139" s="2" t="n">
+      <c r="G139" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="F139" t="n">
+      <c r="H139" t="n">
         <v>7</v>
       </c>
-      <c r="G139" s="2" t="n">
+      <c r="I139" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H139" t="n">
+      <c r="J139" t="n">
         <v>6.1</v>
       </c>
-      <c r="I139" s="2" t="n">
+      <c r="K139" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="J139" t="n">
+      <c r="L139" t="n">
         <v>6.4</v>
       </c>
-      <c r="K139" s="2" t="n">
+      <c r="M139" s="2" t="n">
         <v>46005</v>
       </c>
-      <c r="L139" t="n">
+      <c r="N139" t="n">
         <v>7.2</v>
       </c>
-      <c r="M139" s="2" t="n">
+      <c r="O139" s="2" t="n">
         <v>45998</v>
       </c>
-      <c r="N139" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O139" s="2" t="n">
-        <v>45991</v>
-      </c>
       <c r="P139" t="n">
-        <v>6.97</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="140">
@@ -6243,49 +6275,49 @@
         <v>259</v>
       </c>
       <c r="B142" t="n">
+        <v>7</v>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D142" t="n">
         <v>8.4</v>
       </c>
-      <c r="C142" s="2" t="n">
+      <c r="E142" s="2" t="n">
         <v>46100</v>
       </c>
-      <c r="D142" t="n">
+      <c r="F142" t="n">
         <v>6.4</v>
       </c>
-      <c r="E142" s="2" t="n">
+      <c r="G142" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F142" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G142" s="2" t="n">
+      <c r="H142" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I142" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="H142" t="n">
+      <c r="J142" t="n">
         <v>7.4</v>
       </c>
-      <c r="I142" s="2" t="n">
+      <c r="K142" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J142" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K142" s="2" t="n">
+      <c r="L142" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M142" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L142" t="n">
+      <c r="N142" t="n">
         <v>7.4</v>
       </c>
-      <c r="M142" s="2" t="n">
+      <c r="O142" s="2" t="n">
         <v>46003</v>
       </c>
-      <c r="N142" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O142" s="2" t="n">
-        <v>45991</v>
-      </c>
       <c r="P142" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="143">
@@ -6293,49 +6325,49 @@
         <v>260</v>
       </c>
       <c r="B143" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D143" t="n">
         <v>6.2</v>
       </c>
-      <c r="C143" s="2" t="n">
+      <c r="E143" s="2" t="n">
         <v>46100</v>
       </c>
-      <c r="D143" t="n">
+      <c r="F143" t="n">
         <v>6.4</v>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="G143" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F143" t="n">
+      <c r="H143" t="n">
         <v>6.8</v>
       </c>
-      <c r="G143" s="2" t="n">
+      <c r="I143" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="H143" t="n">
+      <c r="J143" t="n">
         <v>7.2</v>
       </c>
-      <c r="I143" s="2" t="n">
+      <c r="K143" s="2" t="n">
         <v>46003</v>
       </c>
-      <c r="J143" t="n">
+      <c r="L143" t="n">
         <v>6</v>
       </c>
-      <c r="K143" s="2" t="n">
+      <c r="M143" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="L143" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M143" s="2" t="n">
+      <c r="N143" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O143" s="2" t="n">
         <v>45983</v>
       </c>
-      <c r="N143" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O143" s="2" t="n">
-        <v>45969</v>
-      </c>
       <c r="P143" t="n">
-        <v>6.6</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="144">
@@ -6513,49 +6545,49 @@
         <v>273</v>
       </c>
       <c r="B148" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D148" t="n">
         <v>6.8</v>
       </c>
-      <c r="C148" s="2" t="n">
+      <c r="E148" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D148" t="n">
+      <c r="F148" t="n">
         <v>6.3</v>
       </c>
-      <c r="E148" s="2" t="n">
+      <c r="G148" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F148" t="n">
+      <c r="H148" t="n">
         <v>6.9</v>
       </c>
-      <c r="G148" s="2" t="n">
+      <c r="I148" s="2" t="n">
         <v>46089</v>
-      </c>
-      <c r="H148" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>46085</v>
       </c>
       <c r="J148" t="n">
         <v>6.4</v>
       </c>
       <c r="K148" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="L148" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M148" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="L148" t="n">
+      <c r="N148" t="n">
         <v>7</v>
       </c>
-      <c r="M148" s="2" t="n">
+      <c r="O148" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="N148" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O148" s="2" t="n">
-        <v>46068</v>
-      </c>
       <c r="P148" t="n">
-        <v>6.57</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="149">
@@ -6943,49 +6975,49 @@
         <v>282</v>
       </c>
       <c r="B157" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D157" t="n">
         <v>7.8</v>
       </c>
-      <c r="C157" s="2" t="n">
+      <c r="E157" s="2" t="n">
         <v>46103</v>
-      </c>
-      <c r="D157" t="n">
-        <v>7</v>
-      </c>
-      <c r="E157" s="2" t="n">
-        <v>46088</v>
       </c>
       <c r="F157" t="n">
         <v>7</v>
       </c>
       <c r="G157" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="H157" t="n">
+        <v>7</v>
+      </c>
+      <c r="I157" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H157" t="n">
+      <c r="J157" t="n">
         <v>7.1</v>
       </c>
-      <c r="I157" s="2" t="n">
+      <c r="K157" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J157" t="n">
+      <c r="L157" t="n">
         <v>7.2</v>
       </c>
-      <c r="K157" s="2" t="n">
+      <c r="M157" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L157" t="n">
+      <c r="N157" t="n">
         <v>7</v>
       </c>
-      <c r="M157" s="2" t="n">
+      <c r="O157" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N157" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O157" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P157" t="n">
-        <v>7.11</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="158">
@@ -7089,49 +7121,49 @@
         <v>286</v>
       </c>
       <c r="B160" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D160" t="n">
         <v>6.4</v>
       </c>
-      <c r="C160" s="2" t="n">
+      <c r="E160" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D160" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E160" s="2" t="n">
+      <c r="F160" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G160" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F160" t="n">
+      <c r="H160" t="n">
         <v>6.1</v>
       </c>
-      <c r="G160" s="2" t="n">
+      <c r="I160" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H160" t="n">
+      <c r="J160" t="n">
         <v>7.4</v>
       </c>
-      <c r="I160" s="2" t="n">
+      <c r="K160" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J160" t="n">
+      <c r="L160" t="n">
         <v>6.9</v>
       </c>
-      <c r="K160" s="2" t="n">
+      <c r="M160" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L160" t="n">
+      <c r="N160" t="n">
         <v>7.4</v>
       </c>
-      <c r="M160" s="2" t="n">
+      <c r="O160" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N160" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O160" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="P160" t="n">
-        <v>6.73</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="161">
@@ -7239,49 +7271,49 @@
         <v>289</v>
       </c>
       <c r="B163" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D163" t="n">
         <v>8.1</v>
       </c>
-      <c r="C163" s="2" t="n">
+      <c r="E163" s="2" t="n">
         <v>46096</v>
-      </c>
-      <c r="D163" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E163" s="2" t="n">
-        <v>46089</v>
       </c>
       <c r="F163" t="n">
         <v>6.4</v>
       </c>
       <c r="G163" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="H163" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I163" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H163" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I163" s="2" t="n">
+      <c r="J163" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K163" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J163" t="n">
+      <c r="L163" t="n">
         <v>6.8</v>
       </c>
-      <c r="K163" s="2" t="n">
+      <c r="M163" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L163" t="n">
+      <c r="N163" t="n">
         <v>6.3</v>
       </c>
-      <c r="M163" s="2" t="n">
+      <c r="O163" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N163" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O163" s="2" t="n">
-        <v>46054</v>
-      </c>
       <c r="P163" t="n">
-        <v>6.81</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="164">
@@ -7289,49 +7321,49 @@
         <v>290</v>
       </c>
       <c r="B164" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="C164" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D164" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E164" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D164" t="n">
+      <c r="F164" t="n">
         <v>6.8</v>
       </c>
-      <c r="E164" s="2" t="n">
+      <c r="G164" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F164" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G164" s="2" t="n">
+      <c r="H164" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I164" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H164" t="n">
+      <c r="J164" t="n">
         <v>6.1</v>
       </c>
-      <c r="I164" s="2" t="n">
+      <c r="K164" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J164" t="n">
+      <c r="L164" t="n">
         <v>6.3</v>
       </c>
-      <c r="K164" s="2" t="n">
+      <c r="M164" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L164" t="n">
+      <c r="N164" t="n">
         <v>7.9</v>
       </c>
-      <c r="M164" s="2" t="n">
+      <c r="O164" s="2" t="n">
         <v>45999</v>
       </c>
-      <c r="N164" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O164" s="2" t="n">
-        <v>45991</v>
-      </c>
       <c r="P164" t="n">
-        <v>6.84</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="165">
@@ -7511,49 +7543,49 @@
         <v>295</v>
       </c>
       <c r="B169" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D169" t="n">
         <v>7.6</v>
       </c>
-      <c r="C169" s="2" t="n">
+      <c r="E169" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="D169" t="n">
+      <c r="F169" t="n">
         <v>7.1</v>
       </c>
-      <c r="E169" s="2" t="n">
+      <c r="G169" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F169" t="n">
+      <c r="H169" t="n">
         <v>7.9</v>
       </c>
-      <c r="G169" s="2" t="n">
+      <c r="I169" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H169" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I169" s="2" t="n">
+      <c r="J169" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K169" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J169" t="n">
+      <c r="L169" t="n">
         <v>7.3</v>
       </c>
-      <c r="K169" s="2" t="n">
+      <c r="M169" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="L169" t="n">
+      <c r="N169" t="n">
         <v>6.8</v>
       </c>
-      <c r="M169" s="2" t="n">
+      <c r="O169" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="N169" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O169" s="2" t="n">
-        <v>46005</v>
-      </c>
       <c r="P169" t="n">
-        <v>7.23</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="170">
@@ -7561,49 +7593,49 @@
         <v>296</v>
       </c>
       <c r="B170" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D170" t="n">
         <v>6.8</v>
       </c>
-      <c r="C170" s="2" t="n">
+      <c r="E170" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D170" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E170" s="2" t="n">
+      <c r="F170" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G170" s="2" t="n">
         <v>46098</v>
       </c>
-      <c r="F170" t="n">
+      <c r="H170" t="n">
         <v>6.4</v>
       </c>
-      <c r="G170" s="2" t="n">
+      <c r="I170" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H170" t="n">
+      <c r="J170" t="n">
         <v>7.5</v>
       </c>
-      <c r="I170" s="2" t="n">
+      <c r="K170" s="2" t="n">
         <v>45933</v>
       </c>
-      <c r="J170" t="n">
+      <c r="L170" t="n">
         <v>6.3</v>
       </c>
-      <c r="K170" s="2" t="n">
+      <c r="M170" s="2" t="n">
         <v>45929</v>
       </c>
-      <c r="L170" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M170" s="2" t="n">
+      <c r="N170" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O170" s="2" t="n">
         <v>45926</v>
       </c>
-      <c r="N170" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O170" s="2" t="n">
-        <v>45919</v>
-      </c>
       <c r="P170" t="n">
-        <v>6.63</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="171">
@@ -7719,49 +7751,49 @@
         <v>302</v>
       </c>
       <c r="B174" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D174" t="n">
         <v>6.2</v>
       </c>
-      <c r="C174" s="2" t="n">
+      <c r="E174" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D174" t="n">
+      <c r="F174" t="n">
         <v>6.1</v>
       </c>
-      <c r="E174" s="2" t="n">
+      <c r="G174" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="F174" t="n">
+      <c r="H174" t="n">
         <v>6.3</v>
       </c>
-      <c r="G174" s="2" t="n">
+      <c r="I174" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H174" t="n">
+      <c r="J174" t="n">
         <v>7.2</v>
       </c>
-      <c r="I174" s="2" t="n">
+      <c r="K174" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J174" t="n">
+      <c r="L174" t="n">
         <v>6.4</v>
       </c>
-      <c r="K174" s="2" t="n">
+      <c r="M174" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L174" t="n">
+      <c r="N174" t="n">
         <v>7.6</v>
       </c>
-      <c r="M174" s="2" t="n">
+      <c r="O174" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N174" t="n">
-        <v>7</v>
-      </c>
-      <c r="O174" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="P174" t="n">
-        <v>6.69</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="175">
@@ -7919,46 +7951,46 @@
         <v>307</v>
       </c>
       <c r="B178" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D178" t="n">
         <v>7.2</v>
       </c>
-      <c r="C178" s="2" t="n">
+      <c r="E178" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D178" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E178" s="2" t="n">
+      <c r="F178" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G178" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F178" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G178" s="2" t="n">
+      <c r="H178" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I178" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H178" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I178" s="2" t="n">
+      <c r="J178" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K178" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J178" t="n">
+      <c r="L178" t="n">
         <v>6.3</v>
       </c>
-      <c r="K178" s="2" t="n">
+      <c r="M178" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="L178" t="n">
+      <c r="N178" t="n">
         <v>7</v>
       </c>
-      <c r="M178" s="2" t="n">
+      <c r="O178" s="2" t="n">
         <v>45968</v>
-      </c>
-      <c r="N178" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O178" s="2" t="n">
-        <v>45961</v>
       </c>
       <c r="P178" t="n">
         <v>6.69</v>
@@ -7969,46 +8001,46 @@
         <v>309</v>
       </c>
       <c r="B179" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C179" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D179" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E179" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D179" t="n">
+      <c r="F179" t="n">
         <v>7.2</v>
       </c>
-      <c r="E179" s="2" t="n">
+      <c r="G179" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F179" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G179" s="2" t="n">
+      <c r="H179" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I179" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H179" t="n">
+      <c r="J179" t="n">
         <v>8</v>
       </c>
-      <c r="I179" s="2" t="n">
+      <c r="K179" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J179" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K179" s="2" t="n">
+      <c r="L179" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M179" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L179" t="n">
+      <c r="N179" t="n">
         <v>5.2</v>
       </c>
-      <c r="M179" s="2" t="n">
+      <c r="O179" s="2" t="n">
         <v>46068</v>
-      </c>
-      <c r="N179" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O179" s="2" t="n">
-        <v>46061</v>
       </c>
       <c r="P179" t="n">
         <v>6.7</v>
@@ -8069,49 +8101,49 @@
         <v>311</v>
       </c>
       <c r="B181" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="C181" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D181" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E181" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D181" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E181" s="2" t="n">
+      <c r="F181" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G181" s="2" t="n">
         <v>46097</v>
-      </c>
-      <c r="F181" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="G181" s="2" t="n">
-        <v>46082</v>
       </c>
       <c r="H181" t="n">
         <v>6.8</v>
       </c>
       <c r="I181" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="J181" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K181" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J181" t="n">
+      <c r="L181" t="n">
         <v>7.4</v>
       </c>
-      <c r="K181" s="2" t="n">
+      <c r="M181" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="L181" t="n">
+      <c r="N181" t="n">
         <v>7</v>
       </c>
-      <c r="M181" s="2" t="n">
+      <c r="O181" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="N181" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O181" s="2" t="n">
-        <v>45998</v>
-      </c>
       <c r="P181" t="n">
-        <v>6.8</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="182">
@@ -8249,49 +8281,49 @@
         <v>315</v>
       </c>
       <c r="B185" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D185" t="n">
         <v>6.8</v>
       </c>
-      <c r="C185" s="2" t="n">
+      <c r="E185" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D185" t="n">
+      <c r="F185" t="n">
         <v>6.2</v>
       </c>
-      <c r="E185" s="2" t="n">
+      <c r="G185" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F185" t="n">
+      <c r="H185" t="n">
         <v>7.9</v>
       </c>
-      <c r="G185" s="2" t="n">
+      <c r="I185" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H185" t="n">
+      <c r="J185" t="n">
         <v>7.7</v>
       </c>
-      <c r="I185" s="2" t="n">
+      <c r="K185" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J185" t="n">
+      <c r="L185" t="n">
         <v>6.9</v>
       </c>
-      <c r="K185" s="2" t="n">
+      <c r="M185" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="L185" t="n">
+      <c r="N185" t="n">
         <v>7.4</v>
       </c>
-      <c r="M185" s="2" t="n">
+      <c r="O185" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N185" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O185" s="2" t="n">
-        <v>46059</v>
-      </c>
       <c r="P185" t="n">
-        <v>7.29</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="186">
@@ -8387,49 +8419,49 @@
         <v>318</v>
       </c>
       <c r="B188" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C188" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D188" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E188" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D188" t="n">
+      <c r="F188" t="n">
         <v>7.4</v>
       </c>
-      <c r="E188" s="2" t="n">
+      <c r="G188" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F188" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G188" s="2" t="n">
+      <c r="H188" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I188" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H188" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I188" s="2" t="n">
+      <c r="J188" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K188" s="2" t="n">
         <v>46076</v>
       </c>
-      <c r="J188" t="n">
+      <c r="L188" t="n">
         <v>7.5</v>
       </c>
-      <c r="K188" s="2" t="n">
+      <c r="M188" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="L188" t="n">
+      <c r="N188" t="n">
         <v>7</v>
       </c>
-      <c r="M188" s="2" t="n">
+      <c r="O188" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="N188" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O188" s="2" t="n">
-        <v>45998</v>
-      </c>
       <c r="P188" t="n">
-        <v>6.94</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="189">
@@ -8583,49 +8615,49 @@
         <v>322</v>
       </c>
       <c r="B192" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="D192" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="F192" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="H192" t="n">
         <v>7.1</v>
       </c>
-      <c r="C192" s="2" t="n">
+      <c r="I192" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="D192" t="n">
+      <c r="J192" t="n">
         <v>6.3</v>
       </c>
-      <c r="E192" s="2" t="n">
+      <c r="K192" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="F192" t="n">
+      <c r="L192" t="n">
         <v>6.2</v>
       </c>
-      <c r="G192" s="2" t="n">
+      <c r="M192" s="2" t="n">
         <v>45975</v>
       </c>
-      <c r="H192" t="n">
+      <c r="N192" t="n">
         <v>8.5</v>
       </c>
-      <c r="I192" s="2" t="n">
+      <c r="O192" s="2" t="n">
         <v>45968</v>
       </c>
-      <c r="J192" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K192" s="2" t="n">
-        <v>45963</v>
-      </c>
-      <c r="L192" t="n">
-        <v>7</v>
-      </c>
-      <c r="M192" s="2" t="n">
-        <v>45954</v>
-      </c>
-      <c r="N192" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O192" s="2" t="n">
-        <v>45940</v>
-      </c>
       <c r="P192" t="n">
-        <v>6.91</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="193">
@@ -8763,45 +8795,49 @@
         <v>326</v>
       </c>
       <c r="B196" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="C196" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D196" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E196" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="D196" t="n">
+      <c r="F196" t="n">
         <v>6.4</v>
       </c>
-      <c r="E196" s="2" t="n">
+      <c r="G196" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="F196" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G196" s="2" t="n">
+      <c r="H196" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I196" s="2" t="n">
         <v>45878</v>
       </c>
-      <c r="H196" t="n">
+      <c r="J196" t="n">
         <v>7.8</v>
       </c>
-      <c r="I196" s="2" t="n">
+      <c r="K196" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="J196" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K196" s="2" t="n">
+      <c r="L196" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M196" s="2" t="n">
         <v>45864</v>
       </c>
-      <c r="L196" t="n">
+      <c r="N196" t="n">
         <v>7.3</v>
       </c>
-      <c r="M196" s="2" t="n">
+      <c r="O196" s="2" t="n">
         <v>45856</v>
       </c>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
       <c r="P196" t="n">
-        <v>6.9</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="197">
@@ -8879,49 +8915,49 @@
         <v>330</v>
       </c>
       <c r="B199" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C199" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D199" t="n">
         <v>7.3</v>
       </c>
-      <c r="C199" s="2" t="n">
+      <c r="E199" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D199" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E199" s="2" t="n">
+      <c r="F199" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G199" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F199" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G199" s="2" t="n">
+      <c r="H199" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I199" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H199" t="n">
+      <c r="J199" t="n">
         <v>7.4</v>
       </c>
-      <c r="I199" s="2" t="n">
+      <c r="K199" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J199" t="n">
+      <c r="L199" t="n">
         <v>7.9</v>
       </c>
-      <c r="K199" s="2" t="n">
+      <c r="M199" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L199" t="n">
+      <c r="N199" t="n">
         <v>7</v>
       </c>
-      <c r="M199" s="2" t="n">
+      <c r="O199" s="2" t="n">
         <v>46058</v>
       </c>
-      <c r="N199" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O199" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P199" t="n">
-        <v>7.1</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="200">
@@ -8979,49 +9015,49 @@
         <v>335</v>
       </c>
       <c r="B201" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="C201" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D201" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E201" s="2" t="n">
         <v>46095</v>
-      </c>
-      <c r="D201" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E201" s="2" t="n">
-        <v>46089</v>
       </c>
       <c r="F201" t="n">
         <v>6.3</v>
       </c>
       <c r="G201" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="H201" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I201" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H201" t="n">
+      <c r="J201" t="n">
         <v>6.4</v>
       </c>
-      <c r="I201" s="2" t="n">
+      <c r="K201" s="2" t="n">
         <v>45998</v>
       </c>
-      <c r="J201" t="n">
+      <c r="L201" t="n">
         <v>6.3</v>
       </c>
-      <c r="K201" s="2" t="n">
+      <c r="M201" s="2" t="n">
         <v>45990</v>
       </c>
-      <c r="L201" t="n">
+      <c r="N201" t="n">
         <v>6.8</v>
       </c>
-      <c r="M201" s="2" t="n">
+      <c r="O201" s="2" t="n">
         <v>45983</v>
       </c>
-      <c r="N201" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O201" s="2" t="n">
-        <v>45969</v>
-      </c>
       <c r="P201" t="n">
-        <v>6.54</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="202">
@@ -9029,49 +9065,49 @@
         <v>336</v>
       </c>
       <c r="B202" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C202" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D202" t="n">
         <v>6.4</v>
       </c>
-      <c r="C202" s="2" t="n">
+      <c r="E202" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D202" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E202" s="2" t="n">
+      <c r="F202" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G202" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F202" t="n">
+      <c r="H202" t="n">
         <v>6.3</v>
       </c>
-      <c r="G202" s="2" t="n">
+      <c r="I202" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H202" t="n">
+      <c r="J202" t="n">
         <v>6.8</v>
       </c>
-      <c r="I202" s="2" t="n">
+      <c r="K202" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J202" t="n">
+      <c r="L202" t="n">
         <v>6.9</v>
       </c>
-      <c r="K202" s="2" t="n">
+      <c r="M202" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L202" t="n">
+      <c r="N202" t="n">
         <v>6.1</v>
       </c>
-      <c r="M202" s="2" t="n">
+      <c r="O202" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N202" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O202" s="2" t="n">
-        <v>46004</v>
-      </c>
       <c r="P202" t="n">
-        <v>6.66</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="203">
@@ -9079,49 +9115,49 @@
         <v>337</v>
       </c>
       <c r="B203" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D203" t="n">
         <v>7.7</v>
       </c>
-      <c r="C203" s="2" t="n">
+      <c r="E203" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D203" t="n">
+      <c r="F203" t="n">
         <v>6.8</v>
       </c>
-      <c r="E203" s="2" t="n">
+      <c r="G203" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F203" t="n">
+      <c r="H203" t="n">
         <v>6.1</v>
       </c>
-      <c r="G203" s="2" t="n">
+      <c r="I203" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H203" t="n">
+      <c r="J203" t="n">
         <v>6.9</v>
       </c>
-      <c r="I203" s="2" t="n">
+      <c r="K203" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J203" t="n">
+      <c r="L203" t="n">
         <v>6.8</v>
       </c>
-      <c r="K203" s="2" t="n">
+      <c r="M203" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L203" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M203" s="2" t="n">
+      <c r="N203" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O203" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N203" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O203" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P203" t="n">
-        <v>6.9</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="204">
@@ -9159,45 +9195,49 @@
         <v>339</v>
       </c>
       <c r="B205" t="n">
+        <v>6</v>
+      </c>
+      <c r="C205" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D205" t="n">
         <v>6.8</v>
       </c>
-      <c r="C205" s="2" t="n">
+      <c r="E205" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="D205" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E205" s="2" t="n">
+      <c r="F205" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G205" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F205" t="n">
+      <c r="H205" t="n">
         <v>6.8</v>
       </c>
-      <c r="G205" s="2" t="n">
+      <c r="I205" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="H205" t="n">
+      <c r="J205" t="n">
         <v>7</v>
       </c>
-      <c r="I205" s="2" t="n">
+      <c r="K205" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="J205" t="n">
+      <c r="L205" t="n">
         <v>6.9</v>
       </c>
-      <c r="K205" s="2" t="n">
+      <c r="M205" s="2" t="n">
         <v>45996</v>
       </c>
-      <c r="L205" t="n">
+      <c r="N205" t="n">
         <v>6</v>
       </c>
-      <c r="M205" s="2" t="n">
+      <c r="O205" s="2" t="n">
         <v>45899</v>
       </c>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
       <c r="P205" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="206">
@@ -10017,49 +10057,49 @@
         <v>360</v>
       </c>
       <c r="B224" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C224" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="D224" t="n">
         <v>6.3</v>
       </c>
-      <c r="C224" s="2" t="n">
+      <c r="E224" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="D224" t="n">
+      <c r="F224" t="n">
         <v>6.9</v>
       </c>
-      <c r="E224" s="2" t="n">
+      <c r="G224" s="2" t="n">
         <v>46086</v>
-      </c>
-      <c r="F224" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G224" s="2" t="n">
-        <v>46069</v>
       </c>
       <c r="H224" t="n">
         <v>7.2</v>
       </c>
       <c r="I224" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="J224" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K224" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="J224" t="n">
+      <c r="L224" t="n">
         <v>6.8</v>
       </c>
-      <c r="K224" s="2" t="n">
+      <c r="M224" s="2" t="n">
         <v>46058</v>
       </c>
-      <c r="L224" t="n">
+      <c r="N224" t="n">
         <v>6.9</v>
       </c>
-      <c r="M224" s="2" t="n">
+      <c r="O224" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="N224" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O224" s="2" t="n">
-        <v>45997</v>
-      </c>
       <c r="P224" t="n">
-        <v>6.87</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="225">
@@ -10339,49 +10379,49 @@
         <v>370</v>
       </c>
       <c r="B231" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C231" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D231" t="n">
         <v>6.8</v>
       </c>
-      <c r="C231" s="2" t="n">
+      <c r="E231" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D231" t="n">
+      <c r="F231" t="n">
         <v>7.5</v>
       </c>
-      <c r="E231" s="2" t="n">
+      <c r="G231" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F231" t="n">
+      <c r="H231" t="n">
         <v>6.8</v>
       </c>
-      <c r="G231" s="2" t="n">
+      <c r="I231" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H231" t="n">
+      <c r="J231" t="n">
         <v>6.3</v>
       </c>
-      <c r="I231" s="2" t="n">
+      <c r="K231" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J231" t="n">
+      <c r="L231" t="n">
         <v>5.8</v>
       </c>
-      <c r="K231" s="2" t="n">
+      <c r="M231" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L231" t="n">
+      <c r="N231" t="n">
         <v>7.6</v>
       </c>
-      <c r="M231" s="2" t="n">
+      <c r="O231" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N231" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O231" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P231" t="n">
-        <v>6.77</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="232">
@@ -10489,49 +10529,49 @@
         <v>373</v>
       </c>
       <c r="B234" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C234" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D234" t="n">
         <v>5.8</v>
       </c>
-      <c r="C234" s="2" t="n">
+      <c r="E234" s="2" t="n">
         <v>46104</v>
       </c>
-      <c r="D234" t="n">
+      <c r="F234" t="n">
         <v>7.1</v>
       </c>
-      <c r="E234" s="2" t="n">
+      <c r="G234" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="F234" t="n">
+      <c r="H234" t="n">
         <v>7.4</v>
       </c>
-      <c r="G234" s="2" t="n">
+      <c r="I234" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H234" t="n">
+      <c r="J234" t="n">
         <v>7</v>
       </c>
-      <c r="I234" s="2" t="n">
+      <c r="K234" s="2" t="n">
         <v>46083</v>
       </c>
-      <c r="J234" t="n">
+      <c r="L234" t="n">
         <v>6.2</v>
       </c>
-      <c r="K234" s="2" t="n">
+      <c r="M234" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L234" t="n">
+      <c r="N234" t="n">
         <v>6.8</v>
       </c>
-      <c r="M234" s="2" t="n">
+      <c r="O234" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="N234" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O234" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P234" t="n">
-        <v>6.79</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="235">
@@ -10585,49 +10625,49 @@
         <v>376</v>
       </c>
       <c r="B237" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C237" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D237" t="n">
         <v>6.8</v>
       </c>
-      <c r="C237" s="2" t="n">
+      <c r="E237" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D237" t="n">
+      <c r="F237" t="n">
         <v>7.4</v>
       </c>
-      <c r="E237" s="2" t="n">
+      <c r="G237" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F237" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G237" s="2" t="n">
+      <c r="H237" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I237" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H237" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I237" s="2" t="n">
+      <c r="J237" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K237" s="2" t="n">
         <v>46076</v>
       </c>
-      <c r="J237" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K237" s="2" t="n">
+      <c r="L237" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M237" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="L237" t="n">
+      <c r="N237" t="n">
         <v>7.8</v>
       </c>
-      <c r="M237" s="2" t="n">
+      <c r="O237" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="N237" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O237" s="2" t="n">
-        <v>45998</v>
-      </c>
       <c r="P237" t="n">
-        <v>6.91</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="238">
@@ -10725,49 +10765,49 @@
         <v>380</v>
       </c>
       <c r="B241" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C241" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D241" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E241" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="D241" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E241" s="2" t="n">
+      <c r="F241" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G241" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="F241" t="n">
+      <c r="H241" t="n">
         <v>6.4</v>
       </c>
-      <c r="G241" s="2" t="n">
+      <c r="I241" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="H241" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I241" s="2" t="n">
+      <c r="J241" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K241" s="2" t="n">
         <v>45982</v>
       </c>
-      <c r="J241" t="n">
+      <c r="L241" t="n">
         <v>6.4</v>
       </c>
-      <c r="K241" s="2" t="n">
+      <c r="M241" s="2" t="n">
         <v>45963</v>
       </c>
-      <c r="L241" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M241" s="2" t="n">
+      <c r="N241" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O241" s="2" t="n">
         <v>45921</v>
       </c>
-      <c r="N241" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O241" s="2" t="n">
-        <v>45886</v>
-      </c>
       <c r="P241" t="n">
-        <v>6.51</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="242">
@@ -11143,19 +11183,23 @@
         <v>393</v>
       </c>
       <c r="B252" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C252" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D252" t="n">
         <v>7.3</v>
       </c>
-      <c r="C252" s="2" t="n">
+      <c r="E252" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="D252" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E252" s="2" t="n">
+      <c r="F252" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G252" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
@@ -11165,7 +11209,7 @@
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr"/>
       <c r="P252" t="n">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="253">
@@ -11223,49 +11267,49 @@
         <v>395</v>
       </c>
       <c r="B254" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C254" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D254" t="n">
         <v>6.8</v>
       </c>
-      <c r="C254" s="2" t="n">
+      <c r="E254" s="2" t="n">
         <v>46098</v>
       </c>
-      <c r="D254" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E254" s="2" t="n">
+      <c r="F254" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G254" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F254" t="n">
+      <c r="H254" t="n">
         <v>6.3</v>
       </c>
-      <c r="G254" s="2" t="n">
+      <c r="I254" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H254" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I254" s="2" t="n">
+      <c r="J254" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K254" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J254" t="n">
+      <c r="L254" t="n">
         <v>7.6</v>
       </c>
-      <c r="K254" s="2" t="n">
+      <c r="M254" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L254" t="n">
+      <c r="N254" t="n">
         <v>6.4</v>
       </c>
-      <c r="M254" s="2" t="n">
+      <c r="O254" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="N254" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O254" s="2" t="n">
-        <v>46062</v>
-      </c>
       <c r="P254" t="n">
-        <v>6.71</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="255">
@@ -11579,49 +11623,49 @@
         <v>405</v>
       </c>
       <c r="B264" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C264" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D264" t="n">
         <v>6.8</v>
       </c>
-      <c r="C264" s="2" t="n">
+      <c r="E264" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D264" t="n">
+      <c r="F264" t="n">
         <v>7.2</v>
       </c>
-      <c r="E264" s="2" t="n">
+      <c r="G264" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="F264" t="n">
+      <c r="H264" t="n">
         <v>7.1</v>
       </c>
-      <c r="G264" s="2" t="n">
+      <c r="I264" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H264" t="n">
+      <c r="J264" t="n">
         <v>6.1</v>
       </c>
-      <c r="I264" s="2" t="n">
+      <c r="K264" s="2" t="n">
         <v>45997</v>
       </c>
-      <c r="J264" t="n">
+      <c r="L264" t="n">
         <v>7.3</v>
       </c>
-      <c r="K264" s="2" t="n">
+      <c r="M264" s="2" t="n">
         <v>45993</v>
       </c>
-      <c r="L264" t="n">
+      <c r="N264" t="n">
         <v>6.4</v>
       </c>
-      <c r="M264" s="2" t="n">
+      <c r="O264" s="2" t="n">
         <v>45983</v>
       </c>
-      <c r="N264" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O264" s="2" t="n">
-        <v>45962</v>
-      </c>
       <c r="P264" t="n">
-        <v>6.74</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="265">
@@ -11749,49 +11793,49 @@
         <v>409</v>
       </c>
       <c r="B268" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="C268" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D268" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E268" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D268" t="n">
+      <c r="F268" t="n">
         <v>6.8</v>
       </c>
-      <c r="E268" s="2" t="n">
+      <c r="G268" s="2" t="n">
         <v>46095</v>
-      </c>
-      <c r="F268" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G268" s="2" t="n">
-        <v>46088</v>
       </c>
       <c r="H268" t="n">
         <v>6.4</v>
       </c>
       <c r="I268" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="J268" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K268" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J268" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K268" s="2" t="n">
+      <c r="L268" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M268" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L268" t="n">
+      <c r="N268" t="n">
         <v>6.9</v>
       </c>
-      <c r="M268" s="2" t="n">
+      <c r="O268" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N268" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O268" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P268" t="n">
-        <v>6.63</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="269">
@@ -12115,49 +12159,49 @@
         <v>417</v>
       </c>
       <c r="B276" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C276" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D276" t="n">
         <v>8</v>
       </c>
-      <c r="C276" s="2" t="n">
+      <c r="E276" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D276" t="n">
+      <c r="F276" t="n">
         <v>7.1</v>
       </c>
-      <c r="E276" s="2" t="n">
+      <c r="G276" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F276" t="n">
+      <c r="H276" t="n">
         <v>6.9</v>
       </c>
-      <c r="G276" s="2" t="n">
+      <c r="I276" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="H276" t="n">
+      <c r="J276" t="n">
         <v>6.3</v>
       </c>
-      <c r="I276" s="2" t="n">
+      <c r="K276" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="J276" t="n">
+      <c r="L276" t="n">
         <v>5.9</v>
       </c>
-      <c r="K276" s="2" t="n">
+      <c r="M276" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="L276" t="n">
+      <c r="N276" t="n">
         <v>8.1</v>
       </c>
-      <c r="M276" s="2" t="n">
+      <c r="O276" s="2" t="n">
         <v>46045</v>
       </c>
-      <c r="N276" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O276" s="2" t="n">
-        <v>46010</v>
-      </c>
       <c r="P276" t="n">
-        <v>7.24</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="277">
@@ -12165,49 +12209,49 @@
         <v>418</v>
       </c>
       <c r="B277" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C277" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D277" t="n">
         <v>6.3</v>
       </c>
-      <c r="C277" s="2" t="n">
+      <c r="E277" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D277" t="n">
+      <c r="F277" t="n">
         <v>7.2</v>
       </c>
-      <c r="E277" s="2" t="n">
+      <c r="G277" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F277" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G277" s="2" t="n">
+      <c r="H277" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I277" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H277" t="n">
+      <c r="J277" t="n">
         <v>7.3</v>
       </c>
-      <c r="I277" s="2" t="n">
+      <c r="K277" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J277" t="n">
+      <c r="L277" t="n">
         <v>6.8</v>
       </c>
-      <c r="K277" s="2" t="n">
+      <c r="M277" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L277" t="n">
+      <c r="N277" t="n">
         <v>8.6</v>
       </c>
-      <c r="M277" s="2" t="n">
+      <c r="O277" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="N277" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O277" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="P277" t="n">
-        <v>7.07</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="278">
@@ -12215,49 +12259,49 @@
         <v>419</v>
       </c>
       <c r="B278" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C278" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D278" t="n">
         <v>6.4</v>
       </c>
-      <c r="C278" s="2" t="n">
+      <c r="E278" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D278" t="n">
+      <c r="F278" t="n">
         <v>7.5</v>
       </c>
-      <c r="E278" s="2" t="n">
+      <c r="G278" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F278" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G278" s="2" t="n">
+      <c r="H278" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I278" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H278" t="n">
+      <c r="J278" t="n">
         <v>6.4</v>
       </c>
-      <c r="I278" s="2" t="n">
+      <c r="K278" s="2" t="n">
         <v>45926</v>
       </c>
-      <c r="J278" t="n">
+      <c r="L278" t="n">
         <v>7.1</v>
       </c>
-      <c r="K278" s="2" t="n">
+      <c r="M278" s="2" t="n">
         <v>45919</v>
       </c>
-      <c r="L278" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M278" s="2" t="n">
+      <c r="N278" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O278" s="2" t="n">
         <v>45914</v>
       </c>
-      <c r="N278" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O278" s="2" t="n">
-        <v>45898</v>
-      </c>
       <c r="P278" t="n">
-        <v>6.79</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="279">
@@ -12318,46 +12362,46 @@
         <v>7.2</v>
       </c>
       <c r="C280" s="2" t="n">
-        <v>46101</v>
+        <v>46117</v>
       </c>
       <c r="D280" t="n">
         <v>7.2</v>
       </c>
       <c r="E280" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="F280" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G280" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F280" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G280" s="2" t="n">
+      <c r="H280" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I280" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H280" t="n">
+      <c r="J280" t="n">
         <v>8.4</v>
       </c>
-      <c r="I280" s="2" t="n">
+      <c r="K280" s="2" t="n">
         <v>45997</v>
       </c>
-      <c r="J280" t="n">
+      <c r="L280" t="n">
         <v>9.6</v>
       </c>
-      <c r="K280" s="2" t="n">
+      <c r="M280" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="L280" t="n">
+      <c r="N280" t="n">
         <v>6.9</v>
       </c>
-      <c r="M280" s="2" t="n">
+      <c r="O280" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="N280" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O280" s="2" t="n">
-        <v>45969</v>
-      </c>
       <c r="P280" t="n">
-        <v>7.53</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="281">
@@ -12605,49 +12649,49 @@
         <v>429</v>
       </c>
       <c r="B288" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C288" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D288" t="n">
         <v>7.8</v>
       </c>
-      <c r="C288" s="2" t="n">
+      <c r="E288" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D288" t="n">
+      <c r="F288" t="n">
         <v>6.9</v>
       </c>
-      <c r="E288" s="2" t="n">
+      <c r="G288" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F288" t="n">
+      <c r="H288" t="n">
         <v>7.4</v>
       </c>
-      <c r="G288" s="2" t="n">
+      <c r="I288" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H288" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I288" s="2" t="n">
+      <c r="J288" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K288" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J288" t="n">
+      <c r="L288" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K288" s="2" t="n">
+      <c r="M288" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L288" t="n">
+      <c r="N288" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M288" s="2" t="n">
+      <c r="O288" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N288" t="n">
-        <v>7</v>
-      </c>
-      <c r="O288" s="2" t="n">
-        <v>46054</v>
-      </c>
       <c r="P288" t="n">
-        <v>7.51</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="289">
@@ -12855,49 +12899,49 @@
         <v>437</v>
       </c>
       <c r="B294" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C294" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D294" t="n">
         <v>6.9</v>
       </c>
-      <c r="C294" s="2" t="n">
+      <c r="E294" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="D294" t="n">
+      <c r="F294" t="n">
         <v>6.3</v>
       </c>
-      <c r="E294" s="2" t="n">
+      <c r="G294" s="2" t="n">
         <v>46092</v>
       </c>
-      <c r="F294" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G294" s="2" t="n">
+      <c r="H294" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I294" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H294" t="n">
+      <c r="J294" t="n">
         <v>7.1</v>
       </c>
-      <c r="I294" s="2" t="n">
+      <c r="K294" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J294" t="n">
+      <c r="L294" t="n">
         <v>9</v>
       </c>
-      <c r="K294" s="2" t="n">
+      <c r="M294" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L294" t="n">
+      <c r="N294" t="n">
         <v>6.9</v>
       </c>
-      <c r="M294" s="2" t="n">
+      <c r="O294" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="N294" t="n">
-        <v>7</v>
-      </c>
-      <c r="O294" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P294" t="n">
-        <v>7.1</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="295">
@@ -12947,49 +12991,49 @@
         <v>439</v>
       </c>
       <c r="B296" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="C296" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D296" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E296" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D296" t="n">
+      <c r="F296" t="n">
         <v>7.6</v>
       </c>
-      <c r="E296" s="2" t="n">
+      <c r="G296" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F296" t="n">
+      <c r="H296" t="n">
         <v>6.9</v>
       </c>
-      <c r="G296" s="2" t="n">
+      <c r="I296" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H296" t="n">
+      <c r="J296" t="n">
         <v>8.5</v>
       </c>
-      <c r="I296" s="2" t="n">
+      <c r="K296" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J296" t="n">
+      <c r="L296" t="n">
         <v>7.4</v>
       </c>
-      <c r="K296" s="2" t="n">
+      <c r="M296" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L296" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M296" s="2" t="n">
+      <c r="N296" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O296" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N296" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O296" s="2" t="n">
-        <v>46004</v>
-      </c>
       <c r="P296" t="n">
-        <v>7.19</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="297">
@@ -13854,46 +13898,46 @@
         <v>6.4</v>
       </c>
       <c r="C317" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D317" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E317" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D317" t="n">
+      <c r="F317" t="n">
         <v>5.9</v>
       </c>
-      <c r="E317" s="2" t="n">
+      <c r="G317" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F317" t="n">
+      <c r="H317" t="n">
         <v>7</v>
       </c>
-      <c r="G317" s="2" t="n">
+      <c r="I317" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H317" t="n">
+      <c r="J317" t="n">
         <v>6.4</v>
       </c>
-      <c r="I317" s="2" t="n">
+      <c r="K317" s="2" t="n">
         <v>45997</v>
       </c>
-      <c r="J317" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K317" s="2" t="n">
+      <c r="L317" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M317" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="L317" t="n">
+      <c r="N317" t="n">
         <v>7.3</v>
       </c>
-      <c r="M317" s="2" t="n">
+      <c r="O317" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="N317" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O317" s="2" t="n">
-        <v>45969</v>
-      </c>
       <c r="P317" t="n">
-        <v>6.56</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="318">
@@ -14001,7 +14045,7 @@
         <v>466</v>
       </c>
       <c r="B320" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="C320" s="2" t="n">
         <v>46103</v>
@@ -14043,7 +14087,7 @@
         <v>46004</v>
       </c>
       <c r="P320" t="n">
-        <v>6.63</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="321">
@@ -14051,49 +14095,49 @@
         <v>467</v>
       </c>
       <c r="B321" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C321" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D321" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E321" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="F321" t="n">
         <v>7.5</v>
       </c>
-      <c r="C321" s="2" t="n">
+      <c r="G321" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="D321" t="n">
+      <c r="H321" t="n">
         <v>7</v>
       </c>
-      <c r="E321" s="2" t="n">
+      <c r="I321" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="F321" t="n">
+      <c r="J321" t="n">
         <v>7</v>
       </c>
-      <c r="G321" s="2" t="n">
+      <c r="K321" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="H321" t="n">
+      <c r="L321" t="n">
         <v>8.5</v>
       </c>
-      <c r="I321" s="2" t="n">
+      <c r="M321" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="J321" t="n">
+      <c r="N321" t="n">
         <v>7.7</v>
       </c>
-      <c r="K321" s="2" t="n">
+      <c r="O321" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="L321" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="M321" s="2" t="n">
-        <v>46004</v>
-      </c>
-      <c r="N321" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O321" s="2" t="n">
-        <v>45998</v>
-      </c>
       <c r="P321" t="n">
-        <v>7.44</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="322">
@@ -14101,49 +14145,49 @@
         <v>468</v>
       </c>
       <c r="B322" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="C322" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D322" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E322" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="D322" t="n">
+      <c r="F322" t="n">
         <v>6.2</v>
       </c>
-      <c r="E322" s="2" t="n">
+      <c r="G322" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="F322" t="n">
+      <c r="H322" t="n">
         <v>6.8</v>
       </c>
-      <c r="G322" s="2" t="n">
+      <c r="I322" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="H322" t="n">
+      <c r="J322" t="n">
         <v>6.2</v>
       </c>
-      <c r="I322" s="2" t="n">
+      <c r="K322" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="J322" t="n">
+      <c r="L322" t="n">
         <v>6.1</v>
       </c>
-      <c r="K322" s="2" t="n">
+      <c r="M322" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="L322" t="n">
+      <c r="N322" t="n">
         <v>6.3</v>
       </c>
-      <c r="M322" s="2" t="n">
+      <c r="O322" s="2" t="n">
         <v>45994</v>
       </c>
-      <c r="N322" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O322" s="2" t="n">
-        <v>45982</v>
-      </c>
       <c r="P322" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="323">
@@ -14669,49 +14713,49 @@
         <v>483</v>
       </c>
       <c r="B337" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="C337" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D337" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E337" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D337" t="n">
+      <c r="F337" t="n">
         <v>6.4</v>
       </c>
-      <c r="E337" s="2" t="n">
+      <c r="G337" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="F337" t="n">
+      <c r="H337" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G337" s="2" t="n">
+      <c r="I337" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H337" t="n">
+      <c r="J337" t="n">
         <v>7.4</v>
       </c>
-      <c r="I337" s="2" t="n">
+      <c r="K337" s="2" t="n">
         <v>46090</v>
-      </c>
-      <c r="J337" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K337" s="2" t="n">
-        <v>46080</v>
       </c>
       <c r="L337" t="n">
         <v>6.3</v>
       </c>
       <c r="M337" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="N337" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O337" s="2" t="n">
         <v>46076</v>
       </c>
-      <c r="N337" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O337" s="2" t="n">
-        <v>46066</v>
-      </c>
       <c r="P337" t="n">
-        <v>6.83</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="338">
@@ -14719,49 +14763,49 @@
         <v>484</v>
       </c>
       <c r="B338" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C338" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D338" t="n">
         <v>7</v>
       </c>
-      <c r="C338" s="2" t="n">
+      <c r="E338" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D338" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E338" s="2" t="n">
+      <c r="F338" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G338" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F338" t="n">
+      <c r="H338" t="n">
         <v>6.9</v>
       </c>
-      <c r="G338" s="2" t="n">
+      <c r="I338" s="2" t="n">
         <v>46088</v>
-      </c>
-      <c r="H338" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I338" s="2" t="n">
-        <v>46081</v>
       </c>
       <c r="J338" t="n">
         <v>6.8</v>
       </c>
       <c r="K338" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="L338" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M338" s="2" t="n">
         <v>45990</v>
       </c>
-      <c r="L338" t="n">
+      <c r="N338" t="n">
         <v>7.2</v>
       </c>
-      <c r="M338" s="2" t="n">
+      <c r="O338" s="2" t="n">
         <v>45983</v>
       </c>
-      <c r="N338" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O338" s="2" t="n">
-        <v>45971</v>
-      </c>
       <c r="P338" t="n">
-        <v>6.87</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="339">
@@ -15115,49 +15159,49 @@
         <v>492</v>
       </c>
       <c r="B346" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C346" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D346" t="n">
         <v>5.8</v>
       </c>
-      <c r="C346" s="2" t="n">
+      <c r="E346" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D346" t="n">
+      <c r="F346" t="n">
         <v>6.9</v>
       </c>
-      <c r="E346" s="2" t="n">
+      <c r="G346" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F346" t="n">
+      <c r="H346" t="n">
         <v>6</v>
       </c>
-      <c r="G346" s="2" t="n">
+      <c r="I346" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="H346" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I346" s="2" t="n">
+      <c r="J346" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K346" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J346" t="n">
+      <c r="L346" t="n">
         <v>7.1</v>
       </c>
-      <c r="K346" s="2" t="n">
+      <c r="M346" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="L346" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M346" s="2" t="n">
+      <c r="N346" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O346" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="N346" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O346" s="2" t="n">
-        <v>45968</v>
-      </c>
       <c r="P346" t="n">
-        <v>6.53</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="347">
@@ -15215,49 +15259,49 @@
         <v>494</v>
       </c>
       <c r="B348" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C348" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D348" t="n">
         <v>7.2</v>
       </c>
-      <c r="C348" s="2" t="n">
+      <c r="E348" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D348" t="n">
+      <c r="F348" t="n">
         <v>7</v>
       </c>
-      <c r="E348" s="2" t="n">
+      <c r="G348" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F348" t="n">
+      <c r="H348" t="n">
         <v>7.5</v>
       </c>
-      <c r="G348" s="2" t="n">
+      <c r="I348" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H348" t="n">
+      <c r="J348" t="n">
         <v>6.3</v>
       </c>
-      <c r="I348" s="2" t="n">
+      <c r="K348" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J348" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K348" s="2" t="n">
+      <c r="L348" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M348" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="L348" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M348" s="2" t="n">
+      <c r="N348" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O348" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="N348" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O348" s="2" t="n">
-        <v>45968</v>
-      </c>
       <c r="P348" t="n">
-        <v>6.87</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="349">
@@ -16173,49 +16217,49 @@
         <v>520</v>
       </c>
       <c r="B373" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="C373" s="2" t="n">
-        <v>46103</v>
+        <v>46117</v>
       </c>
       <c r="D373" t="n">
         <v>6.8</v>
       </c>
       <c r="E373" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="F373" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G373" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F373" t="n">
+      <c r="H373" t="n">
         <v>7.2</v>
       </c>
-      <c r="G373" s="2" t="n">
+      <c r="I373" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H373" t="n">
+      <c r="J373" t="n">
         <v>8.1</v>
       </c>
-      <c r="I373" s="2" t="n">
+      <c r="K373" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J373" t="n">
+      <c r="L373" t="n">
         <v>5.6</v>
       </c>
-      <c r="K373" s="2" t="n">
+      <c r="M373" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="L373" t="n">
+      <c r="N373" t="n">
         <v>8</v>
       </c>
-      <c r="M373" s="2" t="n">
+      <c r="O373" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N373" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O373" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P373" t="n">
-        <v>7.03</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="374">
@@ -16873,49 +16917,49 @@
         <v>545</v>
       </c>
       <c r="B397" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C397" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D397" t="n">
         <v>6.2</v>
       </c>
-      <c r="C397" s="2" t="n">
+      <c r="E397" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="D397" t="n">
+      <c r="F397" t="n">
         <v>5.9</v>
       </c>
-      <c r="E397" s="2" t="n">
+      <c r="G397" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="F397" t="n">
+      <c r="H397" t="n">
         <v>7.1</v>
       </c>
-      <c r="G397" s="2" t="n">
+      <c r="I397" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="H397" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I397" s="2" t="n">
+      <c r="J397" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K397" s="2" t="n">
         <v>46005</v>
       </c>
-      <c r="J397" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K397" s="2" t="n">
+      <c r="L397" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M397" s="2" t="n">
         <v>45948</v>
       </c>
-      <c r="L397" t="n">
+      <c r="N397" t="n">
         <v>7.3</v>
       </c>
-      <c r="M397" s="2" t="n">
+      <c r="O397" s="2" t="n">
         <v>45934</v>
       </c>
-      <c r="N397" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O397" s="2" t="n">
-        <v>45928</v>
-      </c>
       <c r="P397" t="n">
-        <v>6.53</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="398">
@@ -17003,49 +17047,49 @@
         <v>548</v>
       </c>
       <c r="B400" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="C400" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D400" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E400" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D400" t="n">
+      <c r="F400" t="n">
         <v>6.9</v>
       </c>
-      <c r="E400" s="2" t="n">
+      <c r="G400" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F400" t="n">
+      <c r="H400" t="n">
         <v>6.2</v>
       </c>
-      <c r="G400" s="2" t="n">
+      <c r="I400" s="2" t="n">
         <v>46077</v>
       </c>
-      <c r="H400" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I400" s="2" t="n">
+      <c r="J400" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K400" s="2" t="n">
         <v>45926</v>
       </c>
-      <c r="J400" t="n">
+      <c r="L400" t="n">
         <v>6.3</v>
       </c>
-      <c r="K400" s="2" t="n">
+      <c r="M400" s="2" t="n">
         <v>45913</v>
       </c>
-      <c r="L400" t="n">
+      <c r="N400" t="n">
         <v>7</v>
       </c>
-      <c r="M400" s="2" t="n">
+      <c r="O400" s="2" t="n">
         <v>45898</v>
       </c>
-      <c r="N400" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O400" s="2" t="n">
-        <v>45891</v>
-      </c>
       <c r="P400" t="n">
-        <v>6.59</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="401">
@@ -17053,49 +17097,49 @@
         <v>549</v>
       </c>
       <c r="B401" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C401" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D401" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E401" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D401" t="n">
+      <c r="F401" t="n">
         <v>6.4</v>
       </c>
-      <c r="E401" s="2" t="n">
+      <c r="G401" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F401" t="n">
+      <c r="H401" t="n">
         <v>6.8</v>
       </c>
-      <c r="G401" s="2" t="n">
+      <c r="I401" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H401" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I401" s="2" t="n">
+      <c r="J401" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K401" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J401" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K401" s="2" t="n">
+      <c r="L401" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M401" s="2" t="n">
         <v>45998</v>
       </c>
-      <c r="L401" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M401" s="2" t="n">
+      <c r="N401" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O401" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="N401" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O401" s="2" t="n">
-        <v>45983</v>
-      </c>
       <c r="P401" t="n">
-        <v>6.63</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="402">
@@ -17153,49 +17197,49 @@
         <v>551</v>
       </c>
       <c r="B403" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="C403" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D403" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E403" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D403" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E403" s="2" t="n">
+      <c r="F403" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G403" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F403" t="n">
+      <c r="H403" t="n">
         <v>7.3</v>
       </c>
-      <c r="G403" s="2" t="n">
+      <c r="I403" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H403" t="n">
+      <c r="J403" t="n">
         <v>7.9</v>
       </c>
-      <c r="I403" s="2" t="n">
+      <c r="K403" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J403" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K403" s="2" t="n">
+      <c r="L403" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M403" s="2" t="n">
         <v>45912</v>
       </c>
-      <c r="L403" t="n">
+      <c r="N403" t="n">
         <v>6.3</v>
       </c>
-      <c r="M403" s="2" t="n">
+      <c r="O403" s="2" t="n">
         <v>45898</v>
       </c>
-      <c r="N403" t="n">
-        <v>7</v>
-      </c>
-      <c r="O403" s="2" t="n">
-        <v>45892</v>
-      </c>
       <c r="P403" t="n">
-        <v>6.93</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="404">
@@ -17203,49 +17247,49 @@
         <v>552</v>
       </c>
       <c r="B404" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D404" t="n">
         <v>6.4</v>
       </c>
-      <c r="C404" s="2" t="n">
+      <c r="E404" s="2" t="n">
         <v>46100</v>
       </c>
-      <c r="D404" t="n">
+      <c r="F404" t="n">
         <v>6.1</v>
       </c>
-      <c r="E404" s="2" t="n">
+      <c r="G404" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F404" t="n">
+      <c r="H404" t="n">
         <v>6.3</v>
       </c>
-      <c r="G404" s="2" t="n">
+      <c r="I404" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="H404" t="n">
+      <c r="J404" t="n">
         <v>7.1</v>
       </c>
-      <c r="I404" s="2" t="n">
+      <c r="K404" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J404" t="n">
+      <c r="L404" t="n">
         <v>6.9</v>
       </c>
-      <c r="K404" s="2" t="n">
+      <c r="M404" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L404" t="n">
+      <c r="N404" t="n">
         <v>7.8</v>
       </c>
-      <c r="M404" s="2" t="n">
+      <c r="O404" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="N404" t="n">
-        <v>6</v>
-      </c>
-      <c r="O404" s="2" t="n">
-        <v>46062</v>
-      </c>
       <c r="P404" t="n">
-        <v>6.66</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="405">
@@ -17449,49 +17493,49 @@
         <v>557</v>
       </c>
       <c r="B409" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C409" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D409" t="n">
+        <v>8</v>
+      </c>
+      <c r="E409" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="F409" t="n">
         <v>7.1</v>
       </c>
-      <c r="C409" s="2" t="n">
+      <c r="G409" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D409" t="n">
+      <c r="H409" t="n">
         <v>7.1</v>
       </c>
-      <c r="E409" s="2" t="n">
+      <c r="I409" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="F409" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G409" s="2" t="n">
+      <c r="J409" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K409" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H409" t="n">
+      <c r="L409" t="n">
         <v>7.9</v>
       </c>
-      <c r="I409" s="2" t="n">
+      <c r="M409" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="J409" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K409" s="2" t="n">
+      <c r="N409" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O409" s="2" t="n">
         <v>45997</v>
       </c>
-      <c r="L409" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M409" s="2" t="n">
-        <v>45990</v>
-      </c>
-      <c r="N409" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O409" s="2" t="n">
-        <v>45983</v>
-      </c>
       <c r="P409" t="n">
-        <v>7.11</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="410">
@@ -17549,49 +17593,49 @@
         <v>559</v>
       </c>
       <c r="B411" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C411" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="D411" t="n">
         <v>6.8</v>
       </c>
-      <c r="C411" s="2" t="n">
+      <c r="E411" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D411" t="n">
+      <c r="F411" t="n">
         <v>6.4</v>
       </c>
-      <c r="E411" s="2" t="n">
+      <c r="G411" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F411" t="n">
+      <c r="H411" t="n">
         <v>6.3</v>
       </c>
-      <c r="G411" s="2" t="n">
+      <c r="I411" s="2" t="n">
         <v>46088</v>
-      </c>
-      <c r="H411" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I411" s="2" t="n">
-        <v>46079</v>
       </c>
       <c r="J411" t="n">
         <v>7.2</v>
       </c>
       <c r="K411" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="L411" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M411" s="2" t="n">
         <v>46072</v>
       </c>
-      <c r="L411" t="n">
+      <c r="N411" t="n">
         <v>7.4</v>
       </c>
-      <c r="M411" s="2" t="n">
+      <c r="O411" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="N411" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="O411" s="2" t="n">
-        <v>45997</v>
-      </c>
       <c r="P411" t="n">
-        <v>7.2</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="412">
@@ -17649,41 +17693,45 @@
         <v>561</v>
       </c>
       <c r="B413" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="C413" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D413" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E413" s="2" t="n">
         <v>45914</v>
       </c>
-      <c r="D413" t="n">
+      <c r="F413" t="n">
         <v>6.8</v>
       </c>
-      <c r="E413" s="2" t="n">
+      <c r="G413" s="2" t="n">
         <v>45892</v>
       </c>
-      <c r="F413" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G413" s="2" t="n">
+      <c r="H413" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I413" s="2" t="n">
         <v>45885</v>
       </c>
-      <c r="H413" t="n">
+      <c r="J413" t="n">
         <v>7.8</v>
       </c>
-      <c r="I413" s="2" t="n">
+      <c r="K413" s="2" t="n">
         <v>45878</v>
       </c>
-      <c r="J413" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K413" s="2" t="n">
+      <c r="L413" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M413" s="2" t="n">
         <v>45864</v>
       </c>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
       <c r="N413" t="inlineStr"/>
       <c r="O413" t="inlineStr"/>
       <c r="P413" t="n">
-        <v>6.88</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="414">
@@ -18053,49 +18101,49 @@
         <v>573</v>
       </c>
       <c r="B423" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C423" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D423" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E423" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="F423" t="n">
         <v>5.6</v>
       </c>
-      <c r="C423" s="2" t="n">
+      <c r="G423" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="D423" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E423" s="2" t="n">
+      <c r="H423" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I423" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="F423" t="n">
+      <c r="J423" t="n">
         <v>6.1</v>
       </c>
-      <c r="G423" s="2" t="n">
+      <c r="K423" s="2" t="n">
         <v>45982</v>
       </c>
-      <c r="H423" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I423" s="2" t="n">
+      <c r="L423" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M423" s="2" t="n">
         <v>45975</v>
       </c>
-      <c r="J423" t="n">
+      <c r="N423" t="n">
         <v>6.4</v>
       </c>
-      <c r="K423" s="2" t="n">
+      <c r="O423" s="2" t="n">
         <v>45969</v>
       </c>
-      <c r="L423" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M423" s="2" t="n">
-        <v>45966</v>
-      </c>
-      <c r="N423" t="n">
-        <v>7</v>
-      </c>
-      <c r="O423" s="2" t="n">
-        <v>45956</v>
-      </c>
       <c r="P423" t="n">
-        <v>6.37</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="424">
@@ -18103,49 +18151,49 @@
         <v>574</v>
       </c>
       <c r="B424" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C424" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="D424" t="n">
+        <v>7</v>
+      </c>
+      <c r="E424" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="F424" t="n">
         <v>6.4</v>
       </c>
-      <c r="C424" s="2" t="n">
+      <c r="G424" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="D424" t="n">
+      <c r="H424" t="n">
         <v>7.5</v>
       </c>
-      <c r="E424" s="2" t="n">
+      <c r="I424" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="F424" t="n">
+      <c r="J424" t="n">
         <v>7.3</v>
       </c>
-      <c r="G424" s="2" t="n">
+      <c r="K424" s="2" t="n">
         <v>45983</v>
       </c>
-      <c r="H424" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I424" s="2" t="n">
+      <c r="L424" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M424" s="2" t="n">
         <v>45969</v>
       </c>
-      <c r="J424" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K424" s="2" t="n">
+      <c r="N424" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O424" s="2" t="n">
         <v>45960</v>
       </c>
-      <c r="L424" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M424" s="2" t="n">
-        <v>45955</v>
-      </c>
-      <c r="N424" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O424" s="2" t="n">
-        <v>45948</v>
-      </c>
       <c r="P424" t="n">
-        <v>6.84</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="425">
@@ -18249,49 +18297,49 @@
         <v>577</v>
       </c>
       <c r="B427" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C427" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D427" t="n">
         <v>7</v>
       </c>
-      <c r="C427" s="2" t="n">
+      <c r="E427" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D427" t="n">
+      <c r="F427" t="n">
         <v>6.3</v>
       </c>
-      <c r="E427" s="2" t="n">
+      <c r="G427" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F427" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G427" s="2" t="n">
+      <c r="H427" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I427" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H427" t="n">
+      <c r="J427" t="n">
         <v>6.4</v>
       </c>
-      <c r="I427" s="2" t="n">
+      <c r="K427" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J427" t="n">
+      <c r="L427" t="n">
         <v>5.9</v>
       </c>
-      <c r="K427" s="2" t="n">
+      <c r="M427" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L427" t="n">
+      <c r="N427" t="n">
         <v>5.7</v>
       </c>
-      <c r="M427" s="2" t="n">
+      <c r="O427" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="N427" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O427" s="2" t="n">
-        <v>46054</v>
-      </c>
       <c r="P427" t="n">
-        <v>6.31</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="428">
@@ -18299,49 +18347,49 @@
         <v>578</v>
       </c>
       <c r="B428" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C428" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D428" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="C428" s="2" t="n">
+      <c r="E428" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D428" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E428" s="2" t="n">
+      <c r="F428" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G428" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F428" t="n">
+      <c r="H428" t="n">
         <v>6.3</v>
       </c>
-      <c r="G428" s="2" t="n">
+      <c r="I428" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="H428" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I428" s="2" t="n">
+      <c r="J428" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K428" s="2" t="n">
         <v>45969</v>
       </c>
-      <c r="J428" t="n">
+      <c r="L428" t="n">
         <v>6.2</v>
       </c>
-      <c r="K428" s="2" t="n">
+      <c r="M428" s="2" t="n">
         <v>45954</v>
       </c>
-      <c r="L428" t="n">
+      <c r="N428" t="n">
         <v>7.8</v>
       </c>
-      <c r="M428" s="2" t="n">
+      <c r="O428" s="2" t="n">
         <v>45949</v>
       </c>
-      <c r="N428" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O428" s="2" t="n">
-        <v>45934</v>
-      </c>
       <c r="P428" t="n">
-        <v>6.87</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="429">
@@ -18399,49 +18447,49 @@
         <v>580</v>
       </c>
       <c r="B430" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C430" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D430" t="n">
         <v>5.9</v>
       </c>
-      <c r="C430" s="2" t="n">
+      <c r="E430" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D430" t="n">
+      <c r="F430" t="n">
         <v>7</v>
       </c>
-      <c r="E430" s="2" t="n">
+      <c r="G430" s="2" t="n">
         <v>46006</v>
       </c>
-      <c r="F430" t="n">
+      <c r="H430" t="n">
         <v>6.1</v>
       </c>
-      <c r="G430" s="2" t="n">
+      <c r="I430" s="2" t="n">
         <v>45999</v>
       </c>
-      <c r="H430" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I430" s="2" t="n">
+      <c r="J430" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K430" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="J430" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K430" s="2" t="n">
+      <c r="L430" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M430" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="L430" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M430" s="2" t="n">
+      <c r="N430" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O430" s="2" t="n">
         <v>45970</v>
       </c>
-      <c r="N430" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O430" s="2" t="n">
-        <v>45934</v>
-      </c>
       <c r="P430" t="n">
-        <v>6.51</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="431">
@@ -18687,49 +18735,49 @@
         <v>587</v>
       </c>
       <c r="B436" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="C436" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D436" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E436" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D436" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E436" s="2" t="n">
+      <c r="F436" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G436" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="F436" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G436" s="2" t="n">
+      <c r="H436" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I436" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="H436" t="n">
+      <c r="J436" t="n">
         <v>7.5</v>
       </c>
-      <c r="I436" s="2" t="n">
+      <c r="K436" s="2" t="n">
         <v>46052</v>
-      </c>
-      <c r="J436" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K436" s="2" t="n">
-        <v>46010</v>
       </c>
       <c r="L436" t="n">
         <v>6.4</v>
       </c>
       <c r="M436" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="N436" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O436" s="2" t="n">
         <v>46003</v>
       </c>
-      <c r="N436" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O436" s="2" t="n">
-        <v>45998</v>
-      </c>
       <c r="P436" t="n">
-        <v>6.66</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="437">
@@ -18737,49 +18785,49 @@
         <v>588</v>
       </c>
       <c r="B437" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C437" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D437" t="n">
         <v>5.6</v>
       </c>
-      <c r="C437" s="2" t="n">
+      <c r="E437" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D437" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E437" s="2" t="n">
+      <c r="F437" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G437" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F437" t="n">
+      <c r="H437" t="n">
         <v>7.1</v>
       </c>
-      <c r="G437" s="2" t="n">
+      <c r="I437" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H437" t="n">
+      <c r="J437" t="n">
         <v>5.6</v>
       </c>
-      <c r="I437" s="2" t="n">
+      <c r="K437" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="J437" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K437" s="2" t="n">
+      <c r="L437" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M437" s="2" t="n">
         <v>46047</v>
       </c>
-      <c r="L437" t="n">
+      <c r="N437" t="n">
         <v>6</v>
       </c>
-      <c r="M437" s="2" t="n">
+      <c r="O437" s="2" t="n">
         <v>46010</v>
       </c>
-      <c r="N437" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O437" s="2" t="n">
-        <v>46005</v>
-      </c>
       <c r="P437" t="n">
-        <v>6.29</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="438">
@@ -18887,49 +18935,49 @@
         <v>591</v>
       </c>
       <c r="B440" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C440" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D440" t="n">
         <v>7.1</v>
       </c>
-      <c r="C440" s="2" t="n">
+      <c r="E440" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D440" t="n">
+      <c r="F440" t="n">
         <v>7</v>
       </c>
-      <c r="E440" s="2" t="n">
+      <c r="G440" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="F440" t="n">
+      <c r="H440" t="n">
         <v>7.1</v>
       </c>
-      <c r="G440" s="2" t="n">
+      <c r="I440" s="2" t="n">
         <v>45983</v>
       </c>
-      <c r="H440" t="n">
+      <c r="J440" t="n">
         <v>6.8</v>
       </c>
-      <c r="I440" s="2" t="n">
+      <c r="K440" s="2" t="n">
         <v>45969</v>
       </c>
-      <c r="J440" t="n">
+      <c r="L440" t="n">
         <v>7.2</v>
       </c>
-      <c r="K440" s="2" t="n">
+      <c r="M440" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="L440" t="n">
+      <c r="N440" t="n">
         <v>7.4</v>
       </c>
-      <c r="M440" s="2" t="n">
+      <c r="O440" s="2" t="n">
         <v>45956</v>
       </c>
-      <c r="N440" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O440" s="2" t="n">
-        <v>45948</v>
-      </c>
       <c r="P440" t="n">
-        <v>7.06</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="441">
@@ -19240,46 +19288,46 @@
         <v>7.5</v>
       </c>
       <c r="C447" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D447" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E447" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D447" t="n">
+      <c r="F447" t="n">
         <v>8</v>
       </c>
-      <c r="E447" s="2" t="n">
+      <c r="G447" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F447" t="n">
+      <c r="H447" t="n">
         <v>6.9</v>
       </c>
-      <c r="G447" s="2" t="n">
+      <c r="I447" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H447" t="n">
+      <c r="J447" t="n">
         <v>7</v>
       </c>
-      <c r="I447" s="2" t="n">
+      <c r="K447" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J447" t="n">
+      <c r="L447" t="n">
         <v>7.8</v>
       </c>
-      <c r="K447" s="2" t="n">
+      <c r="M447" s="2" t="n">
         <v>46076</v>
       </c>
-      <c r="L447" t="n">
+      <c r="N447" t="n">
         <v>6.8</v>
       </c>
-      <c r="M447" s="2" t="n">
+      <c r="O447" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="N447" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O447" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P447" t="n">
-        <v>7.27</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="448">
@@ -19363,49 +19411,49 @@
         <v>601</v>
       </c>
       <c r="B450" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C450" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D450" t="n">
         <v>6.9</v>
       </c>
-      <c r="C450" s="2" t="n">
+      <c r="E450" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D450" t="n">
+      <c r="F450" t="n">
         <v>7</v>
       </c>
-      <c r="E450" s="2" t="n">
+      <c r="G450" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F450" t="n">
+      <c r="H450" t="n">
         <v>7.6</v>
       </c>
-      <c r="G450" s="2" t="n">
+      <c r="I450" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="H450" t="n">
+      <c r="J450" t="n">
         <v>6.1</v>
       </c>
-      <c r="I450" s="2" t="n">
+      <c r="K450" s="2" t="n">
         <v>46074</v>
-      </c>
-      <c r="J450" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K450" s="2" t="n">
-        <v>46068</v>
       </c>
       <c r="L450" t="n">
         <v>7.2</v>
       </c>
       <c r="M450" s="2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="N450" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O450" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="N450" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O450" s="2" t="n">
-        <v>46054</v>
-      </c>
       <c r="P450" t="n">
-        <v>6.96</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="451">
@@ -19413,31 +19461,35 @@
         <v>602</v>
       </c>
       <c r="B451" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C451" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D451" t="n">
         <v>6.4</v>
       </c>
-      <c r="C451" s="2" t="n">
+      <c r="E451" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="D451" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E451" s="2" t="n">
+      <c r="F451" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G451" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F451" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G451" s="2" t="n">
+      <c r="H451" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I451" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H451" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I451" s="2" t="n">
+      <c r="J451" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K451" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="J451" t="inlineStr"/>
-      <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr"/>
       <c r="M451" t="inlineStr"/>
       <c r="N451" t="inlineStr"/>
@@ -19721,49 +19773,49 @@
         <v>609</v>
       </c>
       <c r="B458" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C458" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D458" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E458" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D458" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E458" s="2" t="n">
+      <c r="F458" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G458" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F458" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G458" s="2" t="n">
+      <c r="H458" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I458" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="H458" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I458" s="2" t="n">
+      <c r="J458" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K458" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J458" t="n">
+      <c r="L458" t="n">
         <v>7.6</v>
       </c>
-      <c r="K458" s="2" t="n">
+      <c r="M458" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L458" t="n">
+      <c r="N458" t="n">
         <v>6.4</v>
       </c>
-      <c r="M458" s="2" t="n">
+      <c r="O458" s="2" t="n">
         <v>46003</v>
       </c>
-      <c r="N458" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O458" s="2" t="n">
-        <v>45997</v>
-      </c>
       <c r="P458" t="n">
-        <v>6.76</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="459">
@@ -19791,49 +19843,49 @@
         <v>611</v>
       </c>
       <c r="B460" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C460" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D460" t="n">
         <v>7.2</v>
       </c>
-      <c r="C460" s="2" t="n">
+      <c r="E460" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D460" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E460" s="2" t="n">
+      <c r="F460" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G460" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F460" t="n">
+      <c r="H460" t="n">
         <v>7</v>
       </c>
-      <c r="G460" s="2" t="n">
+      <c r="I460" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H460" t="n">
+      <c r="J460" t="n">
         <v>6.3</v>
       </c>
-      <c r="I460" s="2" t="n">
+      <c r="K460" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J460" t="n">
+      <c r="L460" t="n">
         <v>7.4</v>
       </c>
-      <c r="K460" s="2" t="n">
+      <c r="M460" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L460" t="n">
+      <c r="N460" t="n">
         <v>7.2</v>
       </c>
-      <c r="M460" s="2" t="n">
+      <c r="O460" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="N460" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O460" s="2" t="n">
-        <v>46059</v>
-      </c>
       <c r="P460" t="n">
-        <v>6.91</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="461">
@@ -20091,49 +20143,49 @@
         <v>618</v>
       </c>
       <c r="B466" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C466" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D466" t="n">
         <v>8</v>
       </c>
-      <c r="C466" s="2" t="n">
+      <c r="E466" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D466" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E466" s="2" t="n">
+      <c r="F466" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G466" s="2" t="n">
         <v>46098</v>
       </c>
-      <c r="F466" t="n">
+      <c r="H466" t="n">
         <v>7</v>
       </c>
-      <c r="G466" s="2" t="n">
+      <c r="I466" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H466" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I466" s="2" t="n">
+      <c r="J466" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K466" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="J466" t="n">
+      <c r="L466" t="n">
         <v>5.8</v>
       </c>
-      <c r="K466" s="2" t="n">
+      <c r="M466" s="2" t="n">
         <v>46084</v>
       </c>
-      <c r="L466" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M466" s="2" t="n">
+      <c r="N466" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O466" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="N466" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O466" s="2" t="n">
-        <v>46074</v>
-      </c>
       <c r="P466" t="n">
-        <v>6.73</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="467">
@@ -20141,49 +20193,49 @@
         <v>619</v>
       </c>
       <c r="B467" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C467" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D467" t="n">
         <v>6.9</v>
       </c>
-      <c r="C467" s="2" t="n">
+      <c r="E467" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D467" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E467" s="2" t="n">
+      <c r="F467" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G467" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F467" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G467" s="2" t="n">
+      <c r="H467" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I467" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H467" t="n">
+      <c r="J467" t="n">
         <v>7.2</v>
       </c>
-      <c r="I467" s="2" t="n">
+      <c r="K467" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J467" t="n">
+      <c r="L467" t="n">
         <v>7.4</v>
       </c>
-      <c r="K467" s="2" t="n">
+      <c r="M467" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="L467" t="n">
+      <c r="N467" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M467" s="2" t="n">
+      <c r="O467" s="2" t="n">
         <v>45998</v>
       </c>
-      <c r="N467" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O467" s="2" t="n">
-        <v>45992</v>
-      </c>
       <c r="P467" t="n">
-        <v>7.14</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="468">
@@ -20191,49 +20243,49 @@
         <v>620</v>
       </c>
       <c r="B468" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C468" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D468" t="n">
         <v>7.3</v>
       </c>
-      <c r="C468" s="2" t="n">
+      <c r="E468" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D468" t="n">
+      <c r="F468" t="n">
         <v>7</v>
       </c>
-      <c r="E468" s="2" t="n">
+      <c r="G468" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F468" t="n">
+      <c r="H468" t="n">
         <v>6.2</v>
       </c>
-      <c r="G468" s="2" t="n">
+      <c r="I468" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H468" t="n">
+      <c r="J468" t="n">
         <v>6.4</v>
       </c>
-      <c r="I468" s="2" t="n">
+      <c r="K468" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J468" t="n">
+      <c r="L468" t="n">
         <v>7.1</v>
       </c>
-      <c r="K468" s="2" t="n">
+      <c r="M468" s="2" t="n">
         <v>46077</v>
       </c>
-      <c r="L468" t="n">
+      <c r="N468" t="n">
         <v>7.9</v>
       </c>
-      <c r="M468" s="2" t="n">
+      <c r="O468" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="N468" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O468" s="2" t="n">
-        <v>45998</v>
-      </c>
       <c r="P468" t="n">
-        <v>7</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="469">
@@ -20241,49 +20293,49 @@
         <v>621</v>
       </c>
       <c r="B469" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C469" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D469" t="n">
         <v>7.7</v>
       </c>
-      <c r="C469" s="2" t="n">
+      <c r="E469" s="2" t="n">
         <v>46096</v>
-      </c>
-      <c r="D469" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E469" s="2" t="n">
-        <v>46088</v>
       </c>
       <c r="F469" t="n">
         <v>6.4</v>
       </c>
       <c r="G469" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="H469" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I469" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H469" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I469" s="2" t="n">
+      <c r="J469" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K469" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J469" t="n">
+      <c r="L469" t="n">
         <v>6.3</v>
       </c>
-      <c r="K469" s="2" t="n">
+      <c r="M469" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L469" t="n">
+      <c r="N469" t="n">
         <v>6.1</v>
       </c>
-      <c r="M469" s="2" t="n">
+      <c r="O469" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N469" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O469" s="2" t="n">
-        <v>46054</v>
-      </c>
       <c r="P469" t="n">
-        <v>6.76</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="470">
@@ -20391,149 +20443,119 @@
         <v>624</v>
       </c>
       <c r="B472" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C472" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D472" t="n">
         <v>7.7</v>
       </c>
-      <c r="C472" s="2" t="n">
+      <c r="E472" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D472" t="n">
+      <c r="F472" t="n">
         <v>7</v>
       </c>
-      <c r="E472" s="2" t="n">
+      <c r="G472" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F472" t="n">
+      <c r="H472" t="n">
         <v>6.9</v>
       </c>
-      <c r="G472" s="2" t="n">
+      <c r="I472" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H472" t="n">
+      <c r="J472" t="n">
         <v>7.6</v>
       </c>
-      <c r="I472" s="2" t="n">
+      <c r="K472" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J472" t="n">
+      <c r="L472" t="n">
         <v>6.9</v>
       </c>
-      <c r="K472" s="2" t="n">
+      <c r="M472" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="L472" t="n">
+      <c r="N472" t="n">
         <v>7.7</v>
       </c>
-      <c r="M472" s="2" t="n">
+      <c r="O472" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N472" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="O472" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P472" t="n">
-        <v>7.44</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
         <v>625</v>
       </c>
-      <c r="B473" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="C473" s="2" t="n">
-        <v>45970</v>
-      </c>
-      <c r="D473" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E473" s="2" t="n">
-        <v>45963</v>
-      </c>
-      <c r="F473" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G473" s="2" t="n">
-        <v>45955</v>
-      </c>
-      <c r="H473" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I473" s="2" t="n">
-        <v>45948</v>
-      </c>
-      <c r="J473" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="K473" s="2" t="n">
-        <v>45935</v>
-      </c>
-      <c r="L473" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M473" s="2" t="n">
-        <v>45929</v>
-      </c>
-      <c r="N473" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O473" s="2" t="n">
-        <v>45915</v>
-      </c>
-      <c r="P473" t="n">
-        <v>7.31</v>
-      </c>
+      <c r="B473" t="inlineStr"/>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr"/>
+      <c r="E473" t="inlineStr"/>
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr"/>
+      <c r="I473" t="inlineStr"/>
+      <c r="J473" t="inlineStr"/>
+      <c r="K473" t="inlineStr"/>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr"/>
+      <c r="N473" t="inlineStr"/>
+      <c r="O473" t="inlineStr"/>
+      <c r="P473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
         <v>626</v>
       </c>
       <c r="B474" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="C474" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D474" t="n">
         <v>7.1</v>
       </c>
-      <c r="C474" s="2" t="n">
+      <c r="E474" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D474" t="n">
+      <c r="F474" t="n">
         <v>6.4</v>
       </c>
-      <c r="E474" s="2" t="n">
+      <c r="G474" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F474" t="n">
+      <c r="H474" t="n">
         <v>7.9</v>
       </c>
-      <c r="G474" s="2" t="n">
+      <c r="I474" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H474" t="n">
+      <c r="J474" t="n">
         <v>8.5</v>
       </c>
-      <c r="I474" s="2" t="n">
+      <c r="K474" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J474" t="n">
+      <c r="L474" t="n">
         <v>6.8</v>
       </c>
-      <c r="K474" s="2" t="n">
+      <c r="M474" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L474" t="n">
+      <c r="N474" t="n">
         <v>7.4</v>
       </c>
-      <c r="M474" s="2" t="n">
+      <c r="O474" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N474" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O474" s="2" t="n">
-        <v>46004</v>
-      </c>
       <c r="P474" t="n">
-        <v>7.39</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="475">
@@ -20641,49 +20663,49 @@
         <v>629</v>
       </c>
       <c r="B477" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="C477" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D477" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E477" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D477" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E477" s="2" t="n">
+      <c r="F477" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G477" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F477" t="n">
+      <c r="H477" t="n">
         <v>6.4</v>
       </c>
-      <c r="G477" s="2" t="n">
+      <c r="I477" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H477" t="n">
+      <c r="J477" t="n">
         <v>7.3</v>
       </c>
-      <c r="I477" s="2" t="n">
+      <c r="K477" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J477" t="n">
+      <c r="L477" t="n">
         <v>6.9</v>
       </c>
-      <c r="K477" s="2" t="n">
+      <c r="M477" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L477" t="n">
+      <c r="N477" t="n">
         <v>6.4</v>
       </c>
-      <c r="M477" s="2" t="n">
+      <c r="O477" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N477" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O477" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="P477" t="n">
-        <v>6.96</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="478">
@@ -20783,49 +20805,49 @@
         <v>632</v>
       </c>
       <c r="B480" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C480" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D480" t="n">
         <v>5.9</v>
       </c>
-      <c r="C480" s="2" t="n">
+      <c r="E480" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D480" t="n">
+      <c r="F480" t="n">
         <v>7</v>
       </c>
-      <c r="E480" s="2" t="n">
+      <c r="G480" s="2" t="n">
         <v>46006</v>
       </c>
-      <c r="F480" t="n">
+      <c r="H480" t="n">
         <v>6.1</v>
       </c>
-      <c r="G480" s="2" t="n">
+      <c r="I480" s="2" t="n">
         <v>45999</v>
       </c>
-      <c r="H480" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I480" s="2" t="n">
+      <c r="J480" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K480" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="J480" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K480" s="2" t="n">
+      <c r="L480" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M480" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="L480" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M480" s="2" t="n">
+      <c r="N480" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O480" s="2" t="n">
         <v>45970</v>
       </c>
-      <c r="N480" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O480" s="2" t="n">
-        <v>45934</v>
-      </c>
       <c r="P480" t="n">
-        <v>6.51</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="481">
@@ -21205,49 +21227,49 @@
         <v>641</v>
       </c>
       <c r="B489" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C489" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D489" t="n">
         <v>6.3</v>
       </c>
-      <c r="C489" s="2" t="n">
+      <c r="E489" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D489" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E489" s="2" t="n">
+      <c r="F489" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G489" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="F489" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G489" s="2" t="n">
+      <c r="H489" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I489" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="H489" t="n">
+      <c r="J489" t="n">
         <v>7</v>
       </c>
-      <c r="I489" s="2" t="n">
+      <c r="K489" s="2" t="n">
         <v>46003</v>
       </c>
-      <c r="J489" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K489" s="2" t="n">
+      <c r="L489" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M489" s="2" t="n">
         <v>45997</v>
       </c>
-      <c r="L489" t="n">
+      <c r="N489" t="n">
         <v>6.4</v>
       </c>
-      <c r="M489" s="2" t="n">
+      <c r="O489" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="N489" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O489" s="2" t="n">
-        <v>45983</v>
-      </c>
       <c r="P489" t="n">
-        <v>6.61</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="490">
@@ -21255,49 +21277,49 @@
         <v>642</v>
       </c>
       <c r="B490" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C490" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D490" t="n">
         <v>7.3</v>
       </c>
-      <c r="C490" s="2" t="n">
+      <c r="E490" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D490" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E490" s="2" t="n">
+      <c r="F490" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G490" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F490" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G490" s="2" t="n">
+      <c r="H490" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I490" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H490" t="n">
+      <c r="J490" t="n">
         <v>7.4</v>
       </c>
-      <c r="I490" s="2" t="n">
+      <c r="K490" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J490" t="n">
+      <c r="L490" t="n">
         <v>7.9</v>
       </c>
-      <c r="K490" s="2" t="n">
+      <c r="M490" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L490" t="n">
+      <c r="N490" t="n">
         <v>7</v>
       </c>
-      <c r="M490" s="2" t="n">
+      <c r="O490" s="2" t="n">
         <v>46058</v>
       </c>
-      <c r="N490" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O490" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P490" t="n">
-        <v>7.1</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="491">
@@ -21425,49 +21447,49 @@
         <v>646</v>
       </c>
       <c r="B494" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C494" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D494" t="n">
         <v>6.4</v>
       </c>
-      <c r="C494" s="2" t="n">
+      <c r="E494" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D494" t="n">
+      <c r="F494" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="E494" s="2" t="n">
+      <c r="G494" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F494" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G494" s="2" t="n">
+      <c r="H494" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I494" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H494" t="n">
+      <c r="J494" t="n">
         <v>7.6</v>
       </c>
-      <c r="I494" s="2" t="n">
+      <c r="K494" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="J494" t="n">
+      <c r="L494" t="n">
         <v>7.3</v>
       </c>
-      <c r="K494" s="2" t="n">
+      <c r="M494" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L494" t="n">
+      <c r="N494" t="n">
         <v>7.2</v>
       </c>
-      <c r="M494" s="2" t="n">
+      <c r="O494" s="2" t="n">
         <v>46005</v>
       </c>
-      <c r="N494" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O494" s="2" t="n">
-        <v>45998</v>
-      </c>
       <c r="P494" t="n">
-        <v>7.11</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="495">
@@ -21545,19 +21567,23 @@
         <v>649</v>
       </c>
       <c r="B497" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C497" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D497" t="n">
         <v>7.3</v>
       </c>
-      <c r="C497" s="2" t="n">
+      <c r="E497" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D497" t="n">
+      <c r="F497" t="n">
         <v>8.1</v>
       </c>
-      <c r="E497" s="2" t="n">
+      <c r="G497" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F497" t="inlineStr"/>
-      <c r="G497" t="inlineStr"/>
       <c r="H497" t="inlineStr"/>
       <c r="I497" t="inlineStr"/>
       <c r="J497" t="inlineStr"/>
@@ -21567,7 +21593,7 @@
       <c r="N497" t="inlineStr"/>
       <c r="O497" t="inlineStr"/>
       <c r="P497" t="n">
-        <v>7.7</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="498">
@@ -21605,49 +21631,49 @@
         <v>651</v>
       </c>
       <c r="B499" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C499" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D499" t="n">
         <v>7.3</v>
       </c>
-      <c r="C499" s="2" t="n">
+      <c r="E499" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D499" t="n">
+      <c r="F499" t="n">
         <v>6.8</v>
       </c>
-      <c r="E499" s="2" t="n">
+      <c r="G499" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F499" t="n">
+      <c r="H499" t="n">
         <v>7</v>
       </c>
-      <c r="G499" s="2" t="n">
+      <c r="I499" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H499" t="n">
+      <c r="J499" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I499" s="2" t="n">
+      <c r="K499" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J499" t="n">
+      <c r="L499" t="n">
         <v>7.5</v>
       </c>
-      <c r="K499" s="2" t="n">
+      <c r="M499" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="L499" t="n">
+      <c r="N499" t="n">
         <v>9</v>
       </c>
-      <c r="M499" s="2" t="n">
+      <c r="O499" s="2" t="n">
         <v>45997</v>
       </c>
-      <c r="N499" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O499" s="2" t="n">
-        <v>45991</v>
-      </c>
       <c r="P499" t="n">
-        <v>7.63</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="500">
@@ -21655,25 +21681,29 @@
         <v>652</v>
       </c>
       <c r="B500" t="n">
+        <v>7</v>
+      </c>
+      <c r="C500" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D500" t="n">
         <v>6.8</v>
       </c>
-      <c r="C500" s="2" t="n">
+      <c r="E500" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D500" t="n">
+      <c r="F500" t="n">
         <v>7.3</v>
       </c>
-      <c r="E500" s="2" t="n">
+      <c r="G500" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F500" t="n">
+      <c r="H500" t="n">
         <v>7</v>
       </c>
-      <c r="G500" s="2" t="n">
+      <c r="I500" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="H500" t="inlineStr"/>
-      <c r="I500" t="inlineStr"/>
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr"/>
       <c r="L500" t="inlineStr"/>
@@ -21681,7 +21711,7 @@
       <c r="N500" t="inlineStr"/>
       <c r="O500" t="inlineStr"/>
       <c r="P500" t="n">
-        <v>7.03</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="501">
@@ -21739,25 +21769,29 @@
         <v>654</v>
       </c>
       <c r="B502" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C502" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D502" t="n">
         <v>7.9</v>
       </c>
-      <c r="C502" s="2" t="n">
+      <c r="E502" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="D502" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E502" s="2" t="n">
+      <c r="F502" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G502" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="F502" t="n">
+      <c r="H502" t="n">
         <v>7.3</v>
       </c>
-      <c r="G502" s="2" t="n">
+      <c r="I502" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="H502" t="inlineStr"/>
-      <c r="I502" t="inlineStr"/>
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr"/>
       <c r="L502" t="inlineStr"/>
@@ -21765,7 +21799,7 @@
       <c r="N502" t="inlineStr"/>
       <c r="O502" t="inlineStr"/>
       <c r="P502" t="n">
-        <v>7.23</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="503">
@@ -21773,49 +21807,49 @@
         <v>655</v>
       </c>
       <c r="B503" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C503" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D503" t="n">
         <v>6.9</v>
       </c>
-      <c r="C503" s="2" t="n">
+      <c r="E503" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D503" t="n">
+      <c r="F503" t="n">
         <v>7.3</v>
       </c>
-      <c r="E503" s="2" t="n">
+      <c r="G503" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F503" t="n">
+      <c r="H503" t="n">
         <v>6.8</v>
       </c>
-      <c r="G503" s="2" t="n">
+      <c r="I503" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H503" t="n">
+      <c r="J503" t="n">
         <v>7.9</v>
       </c>
-      <c r="I503" s="2" t="n">
+      <c r="K503" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J503" t="n">
+      <c r="L503" t="n">
         <v>7.3</v>
       </c>
-      <c r="K503" s="2" t="n">
+      <c r="M503" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L503" t="n">
+      <c r="N503" t="n">
         <v>7.5</v>
       </c>
-      <c r="M503" s="2" t="n">
+      <c r="O503" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N503" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O503" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P503" t="n">
-        <v>7.21</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="504">
@@ -21853,49 +21887,49 @@
         <v>657</v>
       </c>
       <c r="B505" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C505" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D505" t="n">
         <v>7.3</v>
       </c>
-      <c r="C505" s="2" t="n">
+      <c r="E505" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D505" t="n">
+      <c r="F505" t="n">
         <v>7.4</v>
       </c>
-      <c r="E505" s="2" t="n">
+      <c r="G505" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F505" t="n">
+      <c r="H505" t="n">
         <v>7.3</v>
       </c>
-      <c r="G505" s="2" t="n">
+      <c r="I505" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H505" t="n">
+      <c r="J505" t="n">
         <v>6.4</v>
       </c>
-      <c r="I505" s="2" t="n">
+      <c r="K505" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J505" t="n">
+      <c r="L505" t="n">
         <v>6.3</v>
       </c>
-      <c r="K505" s="2" t="n">
+      <c r="M505" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L505" t="n">
+      <c r="N505" t="n">
         <v>6.2</v>
       </c>
-      <c r="M505" s="2" t="n">
+      <c r="O505" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N505" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O505" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="P505" t="n">
-        <v>6.79</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="506">
@@ -21903,49 +21937,49 @@
         <v>658</v>
       </c>
       <c r="B506" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C506" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D506" t="n">
         <v>7.1</v>
       </c>
-      <c r="C506" s="2" t="n">
+      <c r="E506" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="D506" t="n">
+      <c r="F506" t="n">
         <v>7.6</v>
       </c>
-      <c r="E506" s="2" t="n">
+      <c r="G506" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="F506" t="n">
+      <c r="H506" t="n">
         <v>7.2</v>
       </c>
-      <c r="G506" s="2" t="n">
+      <c r="I506" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="H506" t="n">
+      <c r="J506" t="n">
         <v>7.4</v>
       </c>
-      <c r="I506" s="2" t="n">
+      <c r="K506" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="J506" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K506" s="2" t="n">
+      <c r="L506" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M506" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="L506" t="n">
+      <c r="N506" t="n">
         <v>6.1</v>
       </c>
-      <c r="M506" s="2" t="n">
+      <c r="O506" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="N506" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O506" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P506" t="n">
-        <v>6.93</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="507">
@@ -21953,46 +21987,46 @@
         <v>659</v>
       </c>
       <c r="B507" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C507" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="D507" t="n">
         <v>7.1</v>
       </c>
-      <c r="C507" s="2" t="n">
+      <c r="E507" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D507" t="n">
+      <c r="F507" t="n">
         <v>6.3</v>
       </c>
-      <c r="E507" s="2" t="n">
+      <c r="G507" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F507" t="n">
+      <c r="H507" t="n">
         <v>7</v>
       </c>
-      <c r="G507" s="2" t="n">
+      <c r="I507" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H507" t="n">
+      <c r="J507" t="n">
         <v>7.3</v>
       </c>
-      <c r="I507" s="2" t="n">
+      <c r="K507" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="J507" t="n">
+      <c r="L507" t="n">
         <v>6.9</v>
       </c>
-      <c r="K507" s="2" t="n">
+      <c r="M507" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L507" t="n">
+      <c r="N507" t="n">
         <v>7.9</v>
       </c>
-      <c r="M507" s="2" t="n">
+      <c r="O507" s="2" t="n">
         <v>46060</v>
-      </c>
-      <c r="N507" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O507" s="2" t="n">
-        <v>46005</v>
       </c>
       <c r="P507" t="n">
         <v>7.04</v>

--- a/players_ratings.xlsx
+++ b/players_ratings.xlsx
@@ -519,49 +519,49 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D2" t="n">
         <v>7.3</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="E2" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>7.1</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>7.3</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>7.6</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="N2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>46059</v>
-      </c>
       <c r="P2" t="n">
-        <v>7.01</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="3">
@@ -619,49 +619,49 @@
         <v>15</v>
       </c>
       <c r="B4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D4" t="n">
         <v>6.4</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>7.1</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F4" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I4" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>6.4</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>7.2</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="M4" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>6.3</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="N4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P4" t="n">
-        <v>6.96</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="5">
@@ -961,49 +961,49 @@
         <v>30</v>
       </c>
       <c r="B12" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>46103</v>
+        <v>46118</v>
       </c>
       <c r="D12" t="n">
         <v>6.8</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>46096</v>
+        <v>46103</v>
       </c>
       <c r="F12" t="n">
         <v>6.8</v>
       </c>
       <c r="G12" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I12" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="K12" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="M12" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M12" s="2" t="n">
+      <c r="N12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O12" s="2" t="n">
         <v>45998</v>
       </c>
-      <c r="N12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>45989</v>
-      </c>
       <c r="P12" t="n">
-        <v>7.33</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="13">
@@ -1011,49 +1011,49 @@
         <v>34</v>
       </c>
       <c r="B13" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="C13" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>6.2</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="G13" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>7.1</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>6.8</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="K13" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>6.3</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="M13" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>8.1</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="O13" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="N13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>45999</v>
-      </c>
       <c r="P13" t="n">
-        <v>6.97</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="14">
@@ -1061,49 +1061,49 @@
         <v>36</v>
       </c>
       <c r="B14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D14" t="n">
         <v>6.3</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="E14" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>7.5</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>8.4</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="K14" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>7.4</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="M14" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="L14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M14" s="2" t="n">
+      <c r="N14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O14" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="N14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>45991</v>
-      </c>
       <c r="P14" t="n">
-        <v>7.04</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="15">
@@ -1929,49 +1929,49 @@
         <v>75</v>
       </c>
       <c r="B34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D34" t="n">
         <v>6.4</v>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="E34" s="2" t="n">
         <v>46105</v>
       </c>
-      <c r="D34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E34" s="2" t="n">
+      <c r="F34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G34" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>6.4</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="I34" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I34" s="2" t="n">
+      <c r="J34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K34" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K34" s="2" t="n">
+      <c r="L34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>46084</v>
       </c>
-      <c r="L34" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M34" s="2" t="n">
+      <c r="N34" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O34" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="N34" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O34" s="2" t="n">
-        <v>46069</v>
-      </c>
       <c r="P34" t="n">
-        <v>6.47</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="35">
@@ -2475,13 +2475,17 @@
         <v>110</v>
       </c>
       <c r="B52" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D52" t="n">
         <v>6</v>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="E52" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
@@ -2493,7 +2497,7 @@
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="53">
@@ -2660,46 +2664,46 @@
         <v>7.2</v>
       </c>
       <c r="C59" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D59" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E59" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D59" t="n">
+      <c r="F59" t="n">
         <v>6.9</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F59" t="n">
+      <c r="H59" t="n">
         <v>6.8</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="I59" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H59" t="n">
+      <c r="J59" t="n">
         <v>7.4</v>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="K59" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J59" t="n">
+      <c r="L59" t="n">
         <v>6.8</v>
       </c>
-      <c r="K59" s="2" t="n">
+      <c r="M59" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L59" t="n">
+      <c r="N59" t="n">
         <v>5.9</v>
       </c>
-      <c r="M59" s="2" t="n">
+      <c r="O59" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="N59" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O59" s="2" t="n">
-        <v>45999</v>
-      </c>
       <c r="P59" t="n">
-        <v>6.77</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="60">
@@ -2727,46 +2731,46 @@
         <v>132</v>
       </c>
       <c r="B61" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D61" t="n">
         <v>7.3</v>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="E61" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D61" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E61" s="2" t="n">
+      <c r="F61" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G61" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F61" t="n">
+      <c r="H61" t="n">
         <v>7</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="I61" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H61" t="n">
+      <c r="J61" t="n">
         <v>8</v>
       </c>
-      <c r="I61" s="2" t="n">
+      <c r="K61" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J61" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K61" s="2" t="n">
+      <c r="L61" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M61" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L61" t="n">
+      <c r="N61" t="n">
         <v>6.4</v>
       </c>
-      <c r="M61" s="2" t="n">
+      <c r="O61" s="2" t="n">
         <v>46068</v>
-      </c>
-      <c r="N61" t="n">
-        <v>7</v>
-      </c>
-      <c r="O61" s="2" t="n">
-        <v>46062</v>
       </c>
       <c r="P61" t="n">
         <v>7</v>
@@ -2827,49 +2831,49 @@
         <v>135</v>
       </c>
       <c r="B63" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D63" t="n">
         <v>7.3</v>
       </c>
-      <c r="C63" s="2" t="n">
+      <c r="E63" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D63" t="n">
+      <c r="F63" t="n">
         <v>6.9</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F63" t="n">
+      <c r="H63" t="n">
         <v>7.8</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="I63" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="H63" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I63" s="2" t="n">
+      <c r="J63" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K63" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>7.5</v>
       </c>
-      <c r="K63" s="2" t="n">
+      <c r="M63" s="2" t="n">
         <v>45998</v>
       </c>
-      <c r="L63" t="n">
+      <c r="N63" t="n">
         <v>8.1</v>
       </c>
-      <c r="M63" s="2" t="n">
+      <c r="O63" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="N63" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O63" s="2" t="n">
-        <v>45984</v>
-      </c>
       <c r="P63" t="n">
-        <v>7.43</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="64">
@@ -2877,49 +2881,49 @@
         <v>138</v>
       </c>
       <c r="B64" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>46082</v>
+        <v>46118</v>
       </c>
       <c r="D64" t="n">
         <v>6.8</v>
       </c>
       <c r="E64" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G64" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="F64" t="n">
+      <c r="H64" t="n">
         <v>6.9</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="I64" s="2" t="n">
         <v>45991</v>
-      </c>
-      <c r="H64" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>45969</v>
       </c>
       <c r="J64" t="n">
         <v>6.8</v>
       </c>
       <c r="K64" s="2" t="n">
+        <v>45969</v>
+      </c>
+      <c r="L64" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M64" s="2" t="n">
         <v>45956</v>
       </c>
-      <c r="L64" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M64" s="2" t="n">
+      <c r="N64" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O64" s="2" t="n">
         <v>45950</v>
       </c>
-      <c r="N64" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O64" s="2" t="n">
-        <v>45935</v>
-      </c>
       <c r="P64" t="n">
-        <v>6.87</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="65">
@@ -3217,49 +3221,49 @@
         <v>149</v>
       </c>
       <c r="B72" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="C72" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D72" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E72" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="D72" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E72" s="2" t="n">
+      <c r="F72" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G72" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F72" t="n">
+      <c r="H72" t="n">
         <v>6.3</v>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="I72" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H72" t="n">
+      <c r="J72" t="n">
         <v>7.1</v>
       </c>
-      <c r="I72" s="2" t="n">
+      <c r="K72" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>6.9</v>
       </c>
-      <c r="K72" s="2" t="n">
+      <c r="M72" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="L72" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M72" s="2" t="n">
+      <c r="N72" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O72" s="2" t="n">
         <v>45998</v>
       </c>
-      <c r="N72" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O72" s="2" t="n">
-        <v>45989</v>
-      </c>
       <c r="P72" t="n">
-        <v>6.71</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="73">
@@ -3267,49 +3271,49 @@
         <v>150</v>
       </c>
       <c r="B73" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C73" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E73" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D73" t="n">
+      <c r="F73" t="n">
         <v>7.6</v>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="F73" t="n">
+      <c r="H73" t="n">
         <v>7.1</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="I73" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H73" t="n">
+      <c r="J73" t="n">
         <v>7.3</v>
       </c>
-      <c r="I73" s="2" t="n">
+      <c r="K73" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J73" t="n">
+      <c r="L73" t="n">
         <v>7.1</v>
       </c>
-      <c r="K73" s="2" t="n">
+      <c r="M73" s="2" t="n">
         <v>45970</v>
       </c>
-      <c r="L73" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M73" s="2" t="n">
+      <c r="N73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O73" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="N73" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O73" s="2" t="n">
-        <v>45956</v>
-      </c>
       <c r="P73" t="n">
-        <v>7.14</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="74">
@@ -3417,49 +3421,49 @@
         <v>165</v>
       </c>
       <c r="B76" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="C76" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D76" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E76" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D76" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E76" s="2" t="n">
+      <c r="F76" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G76" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F76" t="n">
+      <c r="H76" t="n">
         <v>6.9</v>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="I76" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="H76" t="n">
+      <c r="J76" t="n">
         <v>7.3</v>
       </c>
-      <c r="I76" s="2" t="n">
+      <c r="K76" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
         <v>6.9</v>
       </c>
-      <c r="K76" s="2" t="n">
+      <c r="M76" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="L76" t="n">
+      <c r="N76" t="n">
         <v>7.2</v>
       </c>
-      <c r="M76" s="2" t="n">
+      <c r="O76" s="2" t="n">
         <v>45997</v>
       </c>
-      <c r="N76" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O76" s="2" t="n">
-        <v>45990</v>
-      </c>
       <c r="P76" t="n">
-        <v>6.81</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="77">
@@ -3517,49 +3521,49 @@
         <v>167</v>
       </c>
       <c r="B78" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D78" t="n">
         <v>7</v>
       </c>
-      <c r="C78" s="2" t="n">
+      <c r="E78" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="D78" t="n">
+      <c r="F78" t="n">
         <v>7.5</v>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="F78" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G78" s="2" t="n">
+      <c r="H78" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I78" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="H78" t="n">
+      <c r="J78" t="n">
         <v>8.1</v>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="K78" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="J78" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K78" s="2" t="n">
+      <c r="L78" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M78" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L78" t="n">
+      <c r="N78" t="n">
         <v>7.1</v>
       </c>
-      <c r="M78" s="2" t="n">
+      <c r="O78" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="N78" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O78" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P78" t="n">
-        <v>7.37</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="79">
@@ -3693,45 +3697,49 @@
         <v>173</v>
       </c>
       <c r="B82" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D82" t="n">
         <v>6.9</v>
       </c>
-      <c r="C82" s="2" t="n">
+      <c r="E82" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D82" t="n">
+      <c r="F82" t="n">
         <v>7.1</v>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="G82" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F82" t="n">
+      <c r="H82" t="n">
         <v>7.3</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="I82" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H82" t="n">
+      <c r="J82" t="n">
         <v>6.8</v>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="K82" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J82" t="n">
+      <c r="L82" t="n">
         <v>6.3</v>
       </c>
-      <c r="K82" s="2" t="n">
+      <c r="M82" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L82" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M82" s="2" t="n">
+      <c r="N82" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O82" s="2" t="n">
         <v>46058</v>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
-        <v>6.82</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="83">
@@ -3789,49 +3797,49 @@
         <v>175</v>
       </c>
       <c r="B84" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D84" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="C84" s="2" t="n">
+      <c r="E84" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="D84" t="n">
+      <c r="F84" t="n">
         <v>6</v>
       </c>
-      <c r="E84" s="2" t="n">
+      <c r="G84" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="F84" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G84" s="2" t="n">
+      <c r="H84" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I84" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="H84" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I84" s="2" t="n">
+      <c r="J84" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K84" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="J84" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K84" s="2" t="n">
+      <c r="L84" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M84" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="L84" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M84" s="2" t="n">
+      <c r="N84" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O84" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="N84" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O84" s="2" t="n">
-        <v>45991</v>
-      </c>
       <c r="P84" t="n">
-        <v>6.97</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="85">
@@ -3923,49 +3931,49 @@
         <v>181</v>
       </c>
       <c r="B87" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D87" t="n">
         <v>6.9</v>
       </c>
-      <c r="C87" s="2" t="n">
+      <c r="E87" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D87" t="n">
+      <c r="F87" t="n">
         <v>7</v>
       </c>
-      <c r="E87" s="2" t="n">
+      <c r="G87" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="F87" t="n">
+      <c r="H87" t="n">
         <v>6.4</v>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="I87" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H87" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I87" s="2" t="n">
+      <c r="J87" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K87" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J87" t="n">
+      <c r="L87" t="n">
         <v>6.9</v>
       </c>
-      <c r="K87" s="2" t="n">
+      <c r="M87" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
         <v>7.1</v>
       </c>
-      <c r="M87" s="2" t="n">
+      <c r="O87" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N87" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O87" s="2" t="n">
-        <v>46056</v>
-      </c>
       <c r="P87" t="n">
-        <v>6.79</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="88">
@@ -6495,49 +6503,49 @@
         <v>267</v>
       </c>
       <c r="B147" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C147" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D147" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E147" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="D147" t="n">
+      <c r="F147" t="n">
         <v>6.4</v>
       </c>
-      <c r="E147" s="2" t="n">
+      <c r="G147" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="F147" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G147" s="2" t="n">
+      <c r="H147" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I147" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="H147" t="n">
+      <c r="J147" t="n">
         <v>6.1</v>
       </c>
-      <c r="I147" s="2" t="n">
+      <c r="K147" s="2" t="n">
         <v>46046</v>
       </c>
-      <c r="J147" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K147" s="2" t="n">
+      <c r="L147" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M147" s="2" t="n">
         <v>46038</v>
       </c>
-      <c r="L147" t="n">
+      <c r="N147" t="n">
         <v>7.2</v>
       </c>
-      <c r="M147" s="2" t="n">
+      <c r="O147" s="2" t="n">
         <v>46018</v>
       </c>
-      <c r="N147" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O147" s="2" t="n">
-        <v>46011</v>
-      </c>
       <c r="P147" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="148">
@@ -7221,49 +7229,49 @@
         <v>288</v>
       </c>
       <c r="B162" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D162" t="n">
         <v>9</v>
       </c>
-      <c r="C162" s="2" t="n">
+      <c r="E162" s="2" t="n">
         <v>46103</v>
-      </c>
-      <c r="D162" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E162" s="2" t="n">
-        <v>46097</v>
       </c>
       <c r="F162" t="n">
         <v>6.4</v>
       </c>
       <c r="G162" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="H162" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I162" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H162" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I162" s="2" t="n">
+      <c r="J162" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K162" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J162" t="n">
+      <c r="L162" t="n">
         <v>6.1</v>
       </c>
-      <c r="K162" s="2" t="n">
+      <c r="M162" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="L162" t="n">
+      <c r="N162" t="n">
         <v>6.3</v>
       </c>
-      <c r="M162" s="2" t="n">
+      <c r="O162" s="2" t="n">
         <v>45990</v>
       </c>
-      <c r="N162" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O162" s="2" t="n">
-        <v>45984</v>
-      </c>
       <c r="P162" t="n">
-        <v>7.01</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="163">
@@ -7371,41 +7379,45 @@
         <v>291</v>
       </c>
       <c r="B165" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D165" t="n">
         <v>6.4</v>
       </c>
-      <c r="C165" s="2" t="n">
+      <c r="E165" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D165" t="n">
+      <c r="F165" t="n">
         <v>7</v>
       </c>
-      <c r="E165" s="2" t="n">
+      <c r="G165" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="F165" t="n">
+      <c r="H165" t="n">
         <v>6.2</v>
       </c>
-      <c r="G165" s="2" t="n">
+      <c r="I165" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H165" t="n">
+      <c r="J165" t="n">
         <v>6.3</v>
       </c>
-      <c r="I165" s="2" t="n">
+      <c r="K165" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J165" t="n">
+      <c r="L165" t="n">
         <v>6.4</v>
       </c>
-      <c r="K165" s="2" t="n">
+      <c r="M165" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="n">
-        <v>6.46</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="166">
@@ -7413,19 +7425,23 @@
         <v>292</v>
       </c>
       <c r="B166" t="n">
+        <v>7</v>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D166" t="n">
         <v>7.4</v>
       </c>
-      <c r="C166" s="2" t="n">
+      <c r="E166" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D166" t="n">
+      <c r="F166" t="n">
         <v>6.8</v>
       </c>
-      <c r="E166" s="2" t="n">
+      <c r="G166" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
@@ -7435,7 +7451,7 @@
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="n">
-        <v>7.1</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="167">
@@ -7593,49 +7609,49 @@
         <v>296</v>
       </c>
       <c r="B170" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="C170" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D170" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E170" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="D170" t="n">
+      <c r="F170" t="n">
         <v>6.8</v>
       </c>
-      <c r="E170" s="2" t="n">
+      <c r="G170" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F170" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G170" s="2" t="n">
+      <c r="H170" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I170" s="2" t="n">
         <v>46098</v>
       </c>
-      <c r="H170" t="n">
+      <c r="J170" t="n">
         <v>6.4</v>
       </c>
-      <c r="I170" s="2" t="n">
+      <c r="K170" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="J170" t="n">
+      <c r="L170" t="n">
         <v>7.5</v>
       </c>
-      <c r="K170" s="2" t="n">
+      <c r="M170" s="2" t="n">
         <v>45933</v>
       </c>
-      <c r="L170" t="n">
+      <c r="N170" t="n">
         <v>6.3</v>
       </c>
-      <c r="M170" s="2" t="n">
+      <c r="O170" s="2" t="n">
         <v>45929</v>
       </c>
-      <c r="N170" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O170" s="2" t="n">
-        <v>45926</v>
-      </c>
       <c r="P170" t="n">
-        <v>6.69</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="171">
@@ -7851,49 +7867,49 @@
         <v>305</v>
       </c>
       <c r="B176" t="n">
+        <v>8</v>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D176" t="n">
         <v>7.3</v>
       </c>
-      <c r="C176" s="2" t="n">
+      <c r="E176" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D176" t="n">
+      <c r="F176" t="n">
         <v>7.4</v>
       </c>
-      <c r="E176" s="2" t="n">
+      <c r="G176" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F176" t="n">
+      <c r="H176" t="n">
         <v>8.1</v>
       </c>
-      <c r="G176" s="2" t="n">
+      <c r="I176" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H176" t="n">
+      <c r="J176" t="n">
         <v>7.4</v>
       </c>
-      <c r="I176" s="2" t="n">
+      <c r="K176" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J176" t="n">
+      <c r="L176" t="n">
         <v>7</v>
       </c>
-      <c r="K176" s="2" t="n">
+      <c r="M176" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L176" t="n">
+      <c r="N176" t="n">
         <v>5.9</v>
       </c>
-      <c r="M176" s="2" t="n">
+      <c r="O176" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="N176" t="n">
-        <v>7</v>
-      </c>
-      <c r="O176" s="2" t="n">
-        <v>45998</v>
-      </c>
       <c r="P176" t="n">
-        <v>7.16</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="177">
@@ -7901,49 +7917,49 @@
         <v>306</v>
       </c>
       <c r="B177" t="n">
+        <v>7</v>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D177" t="n">
         <v>6.3</v>
       </c>
-      <c r="C177" s="2" t="n">
+      <c r="E177" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D177" t="n">
+      <c r="F177" t="n">
         <v>6.8</v>
       </c>
-      <c r="E177" s="2" t="n">
+      <c r="G177" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F177" t="n">
+      <c r="H177" t="n">
         <v>6.4</v>
       </c>
-      <c r="G177" s="2" t="n">
+      <c r="I177" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="H177" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I177" s="2" t="n">
+      <c r="J177" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K177" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J177" t="n">
+      <c r="L177" t="n">
         <v>6.9</v>
       </c>
-      <c r="K177" s="2" t="n">
+      <c r="M177" s="2" t="n">
         <v>45990</v>
       </c>
-      <c r="L177" t="n">
+      <c r="N177" t="n">
         <v>6.3</v>
       </c>
-      <c r="M177" s="2" t="n">
+      <c r="O177" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="N177" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O177" s="2" t="n">
-        <v>45953</v>
-      </c>
       <c r="P177" t="n">
-        <v>6.57</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="178">
@@ -8201,19 +8217,23 @@
         <v>313</v>
       </c>
       <c r="B183" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D183" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="C183" s="2" t="n">
+      <c r="E183" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D183" t="n">
+      <c r="F183" t="n">
         <v>6.2</v>
       </c>
-      <c r="E183" s="2" t="n">
+      <c r="G183" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
@@ -8223,7 +8243,7 @@
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="n">
-        <v>7.2</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="184">
@@ -8331,31 +8351,35 @@
         <v>316</v>
       </c>
       <c r="B186" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="C186" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D186" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E186" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D186" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E186" s="2" t="n">
+      <c r="F186" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G186" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F186" t="n">
+      <c r="H186" t="n">
         <v>6.9</v>
       </c>
-      <c r="G186" s="2" t="n">
+      <c r="I186" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H186" t="n">
+      <c r="J186" t="n">
         <v>7.6</v>
       </c>
-      <c r="I186" s="2" t="n">
+      <c r="K186" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
@@ -8915,49 +8939,49 @@
         <v>330</v>
       </c>
       <c r="B199" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C199" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D199" t="n">
         <v>7.2</v>
       </c>
-      <c r="C199" s="2" t="n">
+      <c r="E199" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D199" t="n">
+      <c r="F199" t="n">
         <v>7.3</v>
       </c>
-      <c r="E199" s="2" t="n">
+      <c r="G199" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F199" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G199" s="2" t="n">
+      <c r="H199" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I199" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H199" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I199" s="2" t="n">
+      <c r="J199" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K199" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J199" t="n">
+      <c r="L199" t="n">
         <v>7.4</v>
       </c>
-      <c r="K199" s="2" t="n">
+      <c r="M199" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L199" t="n">
+      <c r="N199" t="n">
         <v>7.9</v>
       </c>
-      <c r="M199" s="2" t="n">
+      <c r="O199" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="N199" t="n">
-        <v>7</v>
-      </c>
-      <c r="O199" s="2" t="n">
-        <v>46058</v>
-      </c>
       <c r="P199" t="n">
-        <v>7.14</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="200">
@@ -9245,49 +9269,49 @@
         <v>340</v>
       </c>
       <c r="B206" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C206" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D206" t="n">
         <v>7.7</v>
       </c>
-      <c r="C206" s="2" t="n">
+      <c r="E206" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D206" t="n">
+      <c r="F206" t="n">
         <v>6.8</v>
       </c>
-      <c r="E206" s="2" t="n">
+      <c r="G206" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F206" t="n">
+      <c r="H206" t="n">
         <v>7.1</v>
       </c>
-      <c r="G206" s="2" t="n">
+      <c r="I206" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H206" t="n">
+      <c r="J206" t="n">
         <v>6.3</v>
       </c>
-      <c r="I206" s="2" t="n">
+      <c r="K206" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J206" t="n">
+      <c r="L206" t="n">
         <v>7</v>
       </c>
-      <c r="K206" s="2" t="n">
+      <c r="M206" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="L206" t="n">
+      <c r="N206" t="n">
         <v>7.7</v>
       </c>
-      <c r="M206" s="2" t="n">
+      <c r="O206" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="N206" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O206" s="2" t="n">
-        <v>46046</v>
-      </c>
       <c r="P206" t="n">
-        <v>7.1</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="207">
@@ -9315,49 +9339,49 @@
         <v>342</v>
       </c>
       <c r="B208" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C208" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D208" t="n">
         <v>7.9</v>
       </c>
-      <c r="C208" s="2" t="n">
+      <c r="E208" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D208" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E208" s="2" t="n">
+      <c r="F208" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G208" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F208" t="n">
+      <c r="H208" t="n">
         <v>8.9</v>
       </c>
-      <c r="G208" s="2" t="n">
+      <c r="I208" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="H208" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I208" s="2" t="n">
+      <c r="J208" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K208" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J208" t="n">
+      <c r="L208" t="n">
         <v>7.1</v>
       </c>
-      <c r="K208" s="2" t="n">
+      <c r="M208" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="L208" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M208" s="2" t="n">
+      <c r="N208" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O208" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="N208" t="n">
-        <v>7</v>
-      </c>
-      <c r="O208" s="2" t="n">
-        <v>45968</v>
-      </c>
       <c r="P208" t="n">
-        <v>7.23</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="209">
@@ -9835,49 +9859,49 @@
         <v>353</v>
       </c>
       <c r="B219" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C219" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D219" t="n">
         <v>6.4</v>
       </c>
-      <c r="C219" s="2" t="n">
+      <c r="E219" s="2" t="n">
         <v>46100</v>
       </c>
-      <c r="D219" t="n">
+      <c r="F219" t="n">
         <v>7.1</v>
       </c>
-      <c r="E219" s="2" t="n">
+      <c r="G219" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F219" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G219" s="2" t="n">
+      <c r="H219" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I219" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H219" t="n">
+      <c r="J219" t="n">
         <v>7.9</v>
       </c>
-      <c r="I219" s="2" t="n">
+      <c r="K219" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J219" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K219" s="2" t="n">
+      <c r="L219" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M219" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L219" t="n">
+      <c r="N219" t="n">
         <v>6.8</v>
       </c>
-      <c r="M219" s="2" t="n">
+      <c r="O219" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="N219" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O219" s="2" t="n">
-        <v>46058</v>
-      </c>
       <c r="P219" t="n">
-        <v>7.09</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="220">
@@ -10329,49 +10353,49 @@
         <v>369</v>
       </c>
       <c r="B230" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C230" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D230" t="n">
         <v>7.2</v>
       </c>
-      <c r="C230" s="2" t="n">
+      <c r="E230" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D230" t="n">
+      <c r="F230" t="n">
         <v>7.8</v>
       </c>
-      <c r="E230" s="2" t="n">
+      <c r="G230" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="F230" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G230" s="2" t="n">
+      <c r="H230" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I230" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H230" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I230" s="2" t="n">
+      <c r="J230" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K230" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="J230" t="n">
+      <c r="L230" t="n">
         <v>6.9</v>
       </c>
-      <c r="K230" s="2" t="n">
+      <c r="M230" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="L230" t="n">
+      <c r="N230" t="n">
         <v>6.8</v>
       </c>
-      <c r="M230" s="2" t="n">
+      <c r="O230" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="N230" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O230" s="2" t="n">
-        <v>45999</v>
-      </c>
       <c r="P230" t="n">
-        <v>6.94</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="231">
@@ -10579,13 +10603,17 @@
         <v>374</v>
       </c>
       <c r="B235" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C235" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D235" t="n">
         <v>6.1</v>
       </c>
-      <c r="C235" s="2" t="n">
+      <c r="E235" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
@@ -10597,7 +10625,7 @@
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="n">
-        <v>6.1</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="236">
@@ -12162,46 +12190,46 @@
         <v>6.5</v>
       </c>
       <c r="C276" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D276" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E276" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="D276" t="n">
+      <c r="F276" t="n">
         <v>8</v>
       </c>
-      <c r="E276" s="2" t="n">
+      <c r="G276" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F276" t="n">
+      <c r="H276" t="n">
         <v>7.1</v>
       </c>
-      <c r="G276" s="2" t="n">
+      <c r="I276" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H276" t="n">
+      <c r="J276" t="n">
         <v>6.9</v>
       </c>
-      <c r="I276" s="2" t="n">
+      <c r="K276" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="J276" t="n">
+      <c r="L276" t="n">
         <v>6.3</v>
       </c>
-      <c r="K276" s="2" t="n">
+      <c r="M276" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="L276" t="n">
+      <c r="N276" t="n">
         <v>5.9</v>
       </c>
-      <c r="M276" s="2" t="n">
+      <c r="O276" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="N276" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O276" s="2" t="n">
-        <v>46045</v>
-      </c>
       <c r="P276" t="n">
-        <v>6.97</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="277">
@@ -12309,49 +12337,49 @@
         <v>420</v>
       </c>
       <c r="B279" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C279" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D279" t="n">
         <v>6.4</v>
       </c>
-      <c r="C279" s="2" t="n">
+      <c r="E279" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D279" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E279" s="2" t="n">
+      <c r="F279" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G279" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F279" t="n">
+      <c r="H279" t="n">
         <v>7.3</v>
       </c>
-      <c r="G279" s="2" t="n">
+      <c r="I279" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H279" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I279" s="2" t="n">
+      <c r="J279" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K279" s="2" t="n">
         <v>45990</v>
       </c>
-      <c r="J279" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K279" s="2" t="n">
+      <c r="L279" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M279" s="2" t="n">
         <v>45983</v>
       </c>
-      <c r="L279" t="n">
+      <c r="N279" t="n">
         <v>8</v>
       </c>
-      <c r="M279" s="2" t="n">
+      <c r="O279" s="2" t="n">
         <v>45969</v>
       </c>
-      <c r="N279" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O279" s="2" t="n">
-        <v>45964</v>
-      </c>
       <c r="P279" t="n">
-        <v>6.97</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="280">
@@ -13419,49 +13447,49 @@
         <v>452</v>
       </c>
       <c r="B307" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="C307" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D307" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E307" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D307" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E307" s="2" t="n">
+      <c r="F307" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G307" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F307" t="n">
+      <c r="H307" t="n">
         <v>7.9</v>
       </c>
-      <c r="G307" s="2" t="n">
+      <c r="I307" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H307" t="n">
+      <c r="J307" t="n">
         <v>5.3</v>
       </c>
-      <c r="I307" s="2" t="n">
+      <c r="K307" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J307" t="n">
+      <c r="L307" t="n">
         <v>7.3</v>
       </c>
-      <c r="K307" s="2" t="n">
+      <c r="M307" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L307" t="n">
+      <c r="N307" t="n">
         <v>6.1</v>
       </c>
-      <c r="M307" s="2" t="n">
+      <c r="O307" s="2" t="n">
         <v>45998</v>
       </c>
-      <c r="N307" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O307" s="2" t="n">
-        <v>45989</v>
-      </c>
       <c r="P307" t="n">
-        <v>6.67</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="308">
@@ -13469,49 +13497,49 @@
         <v>453</v>
       </c>
       <c r="B308" t="n">
+        <v>6</v>
+      </c>
+      <c r="C308" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D308" t="n">
         <v>6.2</v>
       </c>
-      <c r="C308" s="2" t="n">
+      <c r="E308" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D308" t="n">
+      <c r="F308" t="n">
         <v>7.2</v>
       </c>
-      <c r="E308" s="2" t="n">
+      <c r="G308" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F308" t="n">
+      <c r="H308" t="n">
         <v>6.8</v>
       </c>
-      <c r="G308" s="2" t="n">
+      <c r="I308" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H308" t="n">
+      <c r="J308" t="n">
         <v>6.4</v>
       </c>
-      <c r="I308" s="2" t="n">
+      <c r="K308" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J308" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K308" s="2" t="n">
+      <c r="L308" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M308" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="L308" t="n">
+      <c r="N308" t="n">
         <v>7</v>
       </c>
-      <c r="M308" s="2" t="n">
+      <c r="O308" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="N308" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O308" s="2" t="n">
-        <v>45998</v>
-      </c>
       <c r="P308" t="n">
-        <v>6.67</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="309">
@@ -13619,49 +13647,49 @@
         <v>457</v>
       </c>
       <c r="B311" t="n">
+        <v>7</v>
+      </c>
+      <c r="C311" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D311" t="n">
         <v>6</v>
       </c>
-      <c r="C311" s="2" t="n">
+      <c r="E311" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="D311" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E311" s="2" t="n">
+      <c r="F311" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G311" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="F311" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G311" s="2" t="n">
+      <c r="H311" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I311" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="H311" t="n">
+      <c r="J311" t="n">
         <v>7.5</v>
       </c>
-      <c r="I311" s="2" t="n">
+      <c r="K311" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="J311" t="n">
+      <c r="L311" t="n">
         <v>7.3</v>
       </c>
-      <c r="K311" s="2" t="n">
+      <c r="M311" s="2" t="n">
         <v>45999</v>
       </c>
-      <c r="L311" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M311" s="2" t="n">
+      <c r="N311" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O311" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="N311" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O311" s="2" t="n">
-        <v>45983</v>
-      </c>
       <c r="P311" t="n">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="312">
@@ -13998,46 +14026,46 @@
         <v>6.6</v>
       </c>
       <c r="C319" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D319" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E319" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D319" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E319" s="2" t="n">
+      <c r="F319" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G319" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F319" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G319" s="2" t="n">
+      <c r="H319" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I319" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H319" t="n">
+      <c r="J319" t="n">
         <v>6.4</v>
       </c>
-      <c r="I319" s="2" t="n">
+      <c r="K319" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J319" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K319" s="2" t="n">
+      <c r="L319" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M319" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L319" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M319" s="2" t="n">
+      <c r="N319" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O319" s="2" t="n">
         <v>45999</v>
       </c>
-      <c r="N319" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O319" s="2" t="n">
-        <v>45962</v>
-      </c>
       <c r="P319" t="n">
-        <v>6.53</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="320">
@@ -14045,49 +14073,49 @@
         <v>466</v>
       </c>
       <c r="B320" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C320" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D320" t="n">
         <v>7</v>
       </c>
-      <c r="C320" s="2" t="n">
+      <c r="E320" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D320" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E320" s="2" t="n">
+      <c r="F320" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G320" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F320" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G320" s="2" t="n">
+      <c r="H320" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I320" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="H320" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I320" s="2" t="n">
+      <c r="J320" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K320" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="J320" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K320" s="2" t="n">
+      <c r="L320" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M320" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L320" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M320" s="2" t="n">
+      <c r="N320" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O320" s="2" t="n">
         <v>46008</v>
       </c>
-      <c r="N320" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O320" s="2" t="n">
-        <v>46004</v>
-      </c>
       <c r="P320" t="n">
-        <v>6.64</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="321">
@@ -14195,49 +14223,49 @@
         <v>469</v>
       </c>
       <c r="B323" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C323" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="D323" t="n">
         <v>6.8</v>
       </c>
-      <c r="C323" s="2" t="n">
+      <c r="E323" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D323" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E323" s="2" t="n">
+      <c r="F323" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G323" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F323" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G323" s="2" t="n">
+      <c r="H323" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I323" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="H323" t="n">
+      <c r="J323" t="n">
         <v>6.9</v>
       </c>
-      <c r="I323" s="2" t="n">
+      <c r="K323" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="J323" t="n">
+      <c r="L323" t="n">
         <v>6</v>
       </c>
-      <c r="K323" s="2" t="n">
+      <c r="M323" s="2" t="n">
         <v>46005</v>
       </c>
-      <c r="L323" t="n">
+      <c r="N323" t="n">
         <v>6.4</v>
       </c>
-      <c r="M323" s="2" t="n">
+      <c r="O323" s="2" t="n">
         <v>45999</v>
       </c>
-      <c r="N323" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O323" s="2" t="n">
-        <v>45990</v>
-      </c>
       <c r="P323" t="n">
-        <v>6.64</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="324">
@@ -14295,49 +14323,49 @@
         <v>471</v>
       </c>
       <c r="B325" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="C325" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D325" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E325" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D325" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E325" s="2" t="n">
+      <c r="F325" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G325" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F325" t="n">
+      <c r="H325" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G325" s="2" t="n">
+      <c r="I325" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="H325" t="n">
+      <c r="J325" t="n">
         <v>7.8</v>
       </c>
-      <c r="I325" s="2" t="n">
+      <c r="K325" s="2" t="n">
         <v>46084</v>
       </c>
-      <c r="J325" t="n">
+      <c r="L325" t="n">
         <v>6.9</v>
       </c>
-      <c r="K325" s="2" t="n">
+      <c r="M325" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="L325" t="n">
+      <c r="N325" t="n">
         <v>5.7</v>
       </c>
-      <c r="M325" s="2" t="n">
+      <c r="O325" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N325" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O325" s="2" t="n">
-        <v>46067</v>
-      </c>
       <c r="P325" t="n">
-        <v>7.06</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="326">
@@ -14713,49 +14741,49 @@
         <v>483</v>
       </c>
       <c r="B337" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C337" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D337" t="n">
         <v>7.2</v>
       </c>
-      <c r="C337" s="2" t="n">
+      <c r="E337" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="D337" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E337" s="2" t="n">
+      <c r="F337" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G337" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F337" t="n">
+      <c r="H337" t="n">
         <v>6.4</v>
       </c>
-      <c r="G337" s="2" t="n">
+      <c r="I337" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="H337" t="n">
+      <c r="J337" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I337" s="2" t="n">
+      <c r="K337" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="J337" t="n">
+      <c r="L337" t="n">
         <v>7.4</v>
       </c>
-      <c r="K337" s="2" t="n">
+      <c r="M337" s="2" t="n">
         <v>46090</v>
-      </c>
-      <c r="L337" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M337" s="2" t="n">
-        <v>46080</v>
       </c>
       <c r="N337" t="n">
         <v>6.3</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>46076</v>
+        <v>46080</v>
       </c>
       <c r="P337" t="n">
-        <v>6.91</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="338">
@@ -14813,49 +14841,49 @@
         <v>485</v>
       </c>
       <c r="B339" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C339" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D339" t="n">
         <v>7.3</v>
       </c>
-      <c r="C339" s="2" t="n">
+      <c r="E339" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D339" t="n">
+      <c r="F339" t="n">
         <v>7.6</v>
       </c>
-      <c r="E339" s="2" t="n">
+      <c r="G339" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F339" t="n">
+      <c r="H339" t="n">
         <v>7.2</v>
       </c>
-      <c r="G339" s="2" t="n">
+      <c r="I339" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H339" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I339" s="2" t="n">
+      <c r="J339" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K339" s="2" t="n">
         <v>46074</v>
-      </c>
-      <c r="J339" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K339" s="2" t="n">
-        <v>46068</v>
       </c>
       <c r="L339" t="n">
         <v>7.9</v>
       </c>
       <c r="M339" s="2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="N339" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O339" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="N339" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="O339" s="2" t="n">
-        <v>45996</v>
-      </c>
       <c r="P339" t="n">
-        <v>7.56</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="340">
@@ -14866,46 +14894,46 @@
         <v>6.6</v>
       </c>
       <c r="C340" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D340" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E340" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D340" t="n">
+      <c r="F340" t="n">
         <v>6.3</v>
       </c>
-      <c r="E340" s="2" t="n">
+      <c r="G340" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="F340" t="n">
+      <c r="H340" t="n">
         <v>7.4</v>
       </c>
-      <c r="G340" s="2" t="n">
+      <c r="I340" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="H340" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I340" s="2" t="n">
+      <c r="J340" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K340" s="2" t="n">
         <v>45999</v>
       </c>
-      <c r="J340" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K340" s="2" t="n">
+      <c r="L340" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M340" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="L340" t="n">
+      <c r="N340" t="n">
         <v>6.2</v>
       </c>
-      <c r="M340" s="2" t="n">
+      <c r="O340" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="N340" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O340" s="2" t="n">
-        <v>45949</v>
-      </c>
       <c r="P340" t="n">
-        <v>6.54</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="341">
@@ -14913,49 +14941,49 @@
         <v>487</v>
       </c>
       <c r="B341" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C341" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D341" t="n">
         <v>6.8</v>
       </c>
-      <c r="C341" s="2" t="n">
+      <c r="E341" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="D341" t="n">
+      <c r="F341" t="n">
         <v>6.1</v>
       </c>
-      <c r="E341" s="2" t="n">
+      <c r="G341" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="F341" t="n">
+      <c r="H341" t="n">
         <v>6.3</v>
       </c>
-      <c r="G341" s="2" t="n">
+      <c r="I341" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="H341" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I341" s="2" t="n">
+      <c r="J341" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K341" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="J341" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K341" s="2" t="n">
+      <c r="L341" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M341" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="L341" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M341" s="2" t="n">
+      <c r="N341" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O341" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="N341" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O341" s="2" t="n">
-        <v>45935</v>
-      </c>
       <c r="P341" t="n">
-        <v>6.43</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="342">
@@ -14963,45 +14991,49 @@
         <v>488</v>
       </c>
       <c r="B342" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C342" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D342" t="n">
         <v>6.4</v>
       </c>
-      <c r="C342" s="2" t="n">
+      <c r="E342" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="D342" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E342" s="2" t="n">
+      <c r="F342" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G342" s="2" t="n">
         <v>45963</v>
       </c>
-      <c r="F342" t="n">
+      <c r="H342" t="n">
         <v>7.2</v>
       </c>
-      <c r="G342" s="2" t="n">
+      <c r="I342" s="2" t="n">
         <v>45956</v>
       </c>
-      <c r="H342" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I342" s="2" t="n">
+      <c r="J342" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K342" s="2" t="n">
         <v>45949</v>
       </c>
-      <c r="J342" t="n">
+      <c r="L342" t="n">
         <v>6.4</v>
       </c>
-      <c r="K342" s="2" t="n">
+      <c r="M342" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="L342" t="n">
+      <c r="N342" t="n">
         <v>6.9</v>
       </c>
-      <c r="M342" s="2" t="n">
+      <c r="O342" s="2" t="n">
         <v>45898</v>
       </c>
-      <c r="N342" t="inlineStr"/>
-      <c r="O342" t="inlineStr"/>
       <c r="P342" t="n">
-        <v>6.7</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="343">
@@ -15735,49 +15767,49 @@
         <v>507</v>
       </c>
       <c r="B360" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C360" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="D360" t="n">
         <v>6.3</v>
       </c>
-      <c r="C360" s="2" t="n">
+      <c r="E360" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D360" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E360" s="2" t="n">
+      <c r="F360" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G360" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F360" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G360" s="2" t="n">
+      <c r="H360" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I360" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H360" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I360" s="2" t="n">
+      <c r="J360" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K360" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J360" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K360" s="2" t="n">
+      <c r="L360" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M360" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L360" t="n">
+      <c r="N360" t="n">
         <v>6.4</v>
       </c>
-      <c r="M360" s="2" t="n">
+      <c r="O360" s="2" t="n">
         <v>46055</v>
       </c>
-      <c r="N360" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O360" s="2" t="n">
-        <v>46046</v>
-      </c>
       <c r="P360" t="n">
-        <v>6.39</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="361">
@@ -15885,49 +15917,49 @@
         <v>510</v>
       </c>
       <c r="B363" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C363" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="D363" t="n">
         <v>6.4</v>
       </c>
-      <c r="C363" s="2" t="n">
+      <c r="E363" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D363" t="n">
+      <c r="F363" t="n">
         <v>6.1</v>
       </c>
-      <c r="E363" s="2" t="n">
+      <c r="G363" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F363" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G363" s="2" t="n">
+      <c r="H363" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I363" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H363" t="n">
+      <c r="J363" t="n">
         <v>6.8</v>
       </c>
-      <c r="I363" s="2" t="n">
+      <c r="K363" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J363" t="n">
+      <c r="L363" t="n">
         <v>7.5</v>
       </c>
-      <c r="K363" s="2" t="n">
+      <c r="M363" s="2" t="n">
         <v>46074</v>
-      </c>
-      <c r="L363" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M363" s="2" t="n">
-        <v>46066</v>
       </c>
       <c r="N363" t="n">
         <v>6.4</v>
       </c>
       <c r="O363" s="2" t="n">
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="P363" t="n">
-        <v>6.61</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="364">
@@ -16387,19 +16419,23 @@
         <v>525</v>
       </c>
       <c r="B378" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C378" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D378" t="n">
         <v>7.1</v>
       </c>
-      <c r="C378" s="2" t="n">
+      <c r="E378" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D378" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E378" s="2" t="n">
+      <c r="F378" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G378" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F378" t="inlineStr"/>
-      <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr"/>
@@ -16409,7 +16445,7 @@
       <c r="N378" t="inlineStr"/>
       <c r="O378" t="inlineStr"/>
       <c r="P378" t="n">
-        <v>6.85</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="379">
@@ -16417,19 +16453,23 @@
         <v>526</v>
       </c>
       <c r="B379" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C379" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D379" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="C379" s="2" t="n">
+      <c r="E379" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D379" t="n">
+      <c r="F379" t="n">
         <v>6</v>
       </c>
-      <c r="E379" s="2" t="n">
+      <c r="G379" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr"/>
       <c r="J379" t="inlineStr"/>
@@ -16439,7 +16479,7 @@
       <c r="N379" t="inlineStr"/>
       <c r="O379" t="inlineStr"/>
       <c r="P379" t="n">
-        <v>7.15</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="380">
@@ -16817,49 +16857,49 @@
         <v>543</v>
       </c>
       <c r="B395" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="C395" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D395" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E395" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D395" t="n">
+      <c r="F395" t="n">
         <v>6.9</v>
       </c>
-      <c r="E395" s="2" t="n">
+      <c r="G395" s="2" t="n">
         <v>46082</v>
-      </c>
-      <c r="F395" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G395" s="2" t="n">
-        <v>46073</v>
       </c>
       <c r="H395" t="n">
         <v>7.1</v>
       </c>
       <c r="I395" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="J395" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K395" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="J395" t="n">
+      <c r="L395" t="n">
         <v>6.9</v>
       </c>
-      <c r="K395" s="2" t="n">
+      <c r="M395" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="L395" t="n">
+      <c r="N395" t="n">
         <v>7.2</v>
       </c>
-      <c r="M395" s="2" t="n">
+      <c r="O395" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="N395" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O395" s="2" t="n">
-        <v>45969</v>
-      </c>
       <c r="P395" t="n">
-        <v>6.94</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="396">
@@ -16867,49 +16907,49 @@
         <v>544</v>
       </c>
       <c r="B396" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="C396" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D396" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E396" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D396" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E396" s="2" t="n">
+      <c r="F396" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G396" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F396" t="n">
+      <c r="H396" t="n">
         <v>7</v>
       </c>
-      <c r="G396" s="2" t="n">
+      <c r="I396" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H396" t="n">
+      <c r="J396" t="n">
         <v>6.4</v>
       </c>
-      <c r="I396" s="2" t="n">
+      <c r="K396" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="J396" t="n">
+      <c r="L396" t="n">
         <v>6.8</v>
       </c>
-      <c r="K396" s="2" t="n">
+      <c r="M396" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L396" t="n">
+      <c r="N396" t="n">
         <v>8.4</v>
       </c>
-      <c r="M396" s="2" t="n">
+      <c r="O396" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="N396" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O396" s="2" t="n">
-        <v>45998</v>
-      </c>
       <c r="P396" t="n">
-        <v>6.91</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="397">
@@ -16967,49 +17007,49 @@
         <v>546</v>
       </c>
       <c r="B398" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C398" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D398" t="n">
         <v>7</v>
       </c>
-      <c r="C398" s="2" t="n">
+      <c r="E398" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="D398" t="n">
+      <c r="F398" t="n">
         <v>7.3</v>
       </c>
-      <c r="E398" s="2" t="n">
+      <c r="G398" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="F398" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G398" s="2" t="n">
+      <c r="H398" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I398" s="2" t="n">
         <v>46077</v>
       </c>
-      <c r="H398" t="n">
+      <c r="J398" t="n">
         <v>7.6</v>
       </c>
-      <c r="I398" s="2" t="n">
+      <c r="K398" s="2" t="n">
         <v>45947</v>
       </c>
-      <c r="J398" t="n">
+      <c r="L398" t="n">
         <v>7.2</v>
       </c>
-      <c r="K398" s="2" t="n">
+      <c r="M398" s="2" t="n">
         <v>45927</v>
       </c>
-      <c r="L398" t="n">
+      <c r="N398" t="n">
         <v>7</v>
       </c>
-      <c r="M398" s="2" t="n">
+      <c r="O398" s="2" t="n">
         <v>45920</v>
       </c>
-      <c r="N398" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O398" s="2" t="n">
-        <v>45893</v>
-      </c>
       <c r="P398" t="n">
-        <v>7.16</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="399">
@@ -17097,49 +17137,49 @@
         <v>549</v>
       </c>
       <c r="B401" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="C401" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D401" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E401" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="D401" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E401" s="2" t="n">
+      <c r="F401" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G401" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F401" t="n">
+      <c r="H401" t="n">
         <v>6.4</v>
       </c>
-      <c r="G401" s="2" t="n">
+      <c r="I401" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H401" t="n">
+      <c r="J401" t="n">
         <v>6.8</v>
       </c>
-      <c r="I401" s="2" t="n">
+      <c r="K401" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J401" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K401" s="2" t="n">
+      <c r="L401" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M401" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="L401" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M401" s="2" t="n">
+      <c r="N401" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O401" s="2" t="n">
         <v>45998</v>
       </c>
-      <c r="N401" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O401" s="2" t="n">
-        <v>45989</v>
-      </c>
       <c r="P401" t="n">
-        <v>6.64</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="402">
@@ -17147,46 +17187,46 @@
         <v>550</v>
       </c>
       <c r="B402" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C402" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D402" t="n">
         <v>6.9</v>
       </c>
-      <c r="C402" s="2" t="n">
+      <c r="E402" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D402" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E402" s="2" t="n">
+      <c r="F402" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G402" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F402" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G402" s="2" t="n">
+      <c r="H402" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I402" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H402" t="n">
+      <c r="J402" t="n">
         <v>6.3</v>
       </c>
-      <c r="I402" s="2" t="n">
+      <c r="K402" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="J402" t="n">
+      <c r="L402" t="n">
         <v>6.8</v>
       </c>
-      <c r="K402" s="2" t="n">
+      <c r="M402" s="2" t="n">
         <v>45983</v>
       </c>
-      <c r="L402" t="n">
+      <c r="N402" t="n">
         <v>6.4</v>
       </c>
-      <c r="M402" s="2" t="n">
+      <c r="O402" s="2" t="n">
         <v>45963</v>
-      </c>
-      <c r="N402" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O402" s="2" t="n">
-        <v>45954</v>
       </c>
       <c r="P402" t="n">
         <v>6.54</v>
@@ -17197,46 +17237,46 @@
         <v>551</v>
       </c>
       <c r="B403" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C403" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D403" t="n">
         <v>6.9</v>
       </c>
-      <c r="C403" s="2" t="n">
+      <c r="E403" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="D403" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E403" s="2" t="n">
+      <c r="F403" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G403" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F403" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G403" s="2" t="n">
+      <c r="H403" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I403" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H403" t="n">
+      <c r="J403" t="n">
         <v>7.3</v>
       </c>
-      <c r="I403" s="2" t="n">
+      <c r="K403" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J403" t="n">
+      <c r="L403" t="n">
         <v>7.9</v>
       </c>
-      <c r="K403" s="2" t="n">
+      <c r="M403" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="L403" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M403" s="2" t="n">
+      <c r="N403" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O403" s="2" t="n">
         <v>45912</v>
-      </c>
-      <c r="N403" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O403" s="2" t="n">
-        <v>45898</v>
       </c>
       <c r="P403" t="n">
         <v>6.91</v>
@@ -17343,49 +17383,49 @@
         <v>554</v>
       </c>
       <c r="B406" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C406" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D406" t="n">
         <v>7.6</v>
       </c>
-      <c r="C406" s="2" t="n">
+      <c r="E406" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D406" t="n">
+      <c r="F406" t="n">
         <v>7.2</v>
       </c>
-      <c r="E406" s="2" t="n">
+      <c r="G406" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="F406" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G406" s="2" t="n">
+      <c r="H406" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I406" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="H406" t="n">
+      <c r="J406" t="n">
         <v>6.4</v>
       </c>
-      <c r="I406" s="2" t="n">
+      <c r="K406" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J406" t="n">
+      <c r="L406" t="n">
         <v>8</v>
       </c>
-      <c r="K406" s="2" t="n">
+      <c r="M406" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L406" t="n">
+      <c r="N406" t="n">
         <v>7.9</v>
       </c>
-      <c r="M406" s="2" t="n">
+      <c r="O406" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="N406" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O406" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P406" t="n">
-        <v>7.34</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="407">
@@ -17847,49 +17887,49 @@
         <v>565</v>
       </c>
       <c r="B417" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="C417" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D417" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E417" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D417" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E417" s="2" t="n">
+      <c r="F417" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G417" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F417" t="n">
+      <c r="H417" t="n">
         <v>7.1</v>
       </c>
-      <c r="G417" s="2" t="n">
+      <c r="I417" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H417" t="n">
+      <c r="J417" t="n">
         <v>7.6</v>
       </c>
-      <c r="I417" s="2" t="n">
+      <c r="K417" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J417" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K417" s="2" t="n">
+      <c r="L417" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M417" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L417" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M417" s="2" t="n">
+      <c r="N417" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O417" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="N417" t="n">
-        <v>6</v>
-      </c>
-      <c r="O417" s="2" t="n">
-        <v>45997</v>
-      </c>
       <c r="P417" t="n">
-        <v>6.71</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="418">
@@ -17935,49 +17975,49 @@
         <v>567</v>
       </c>
       <c r="B419" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="C419" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D419" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E419" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D419" t="n">
+      <c r="F419" t="n">
         <v>7.1</v>
       </c>
-      <c r="E419" s="2" t="n">
+      <c r="G419" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F419" t="n">
+      <c r="H419" t="n">
         <v>6.8</v>
       </c>
-      <c r="G419" s="2" t="n">
+      <c r="I419" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H419" t="n">
+      <c r="J419" t="n">
         <v>6.3</v>
       </c>
-      <c r="I419" s="2" t="n">
+      <c r="K419" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="J419" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K419" s="2" t="n">
+      <c r="L419" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M419" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L419" t="n">
+      <c r="N419" t="n">
         <v>7.2</v>
       </c>
-      <c r="M419" s="2" t="n">
+      <c r="O419" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="N419" t="n">
-        <v>7</v>
-      </c>
-      <c r="O419" s="2" t="n">
-        <v>45990</v>
-      </c>
       <c r="P419" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="420">
@@ -18835,49 +18875,49 @@
         <v>589</v>
       </c>
       <c r="B438" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="C438" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D438" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E438" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="D438" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E438" s="2" t="n">
+      <c r="F438" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G438" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F438" t="n">
+      <c r="H438" t="n">
         <v>7.1</v>
       </c>
-      <c r="G438" s="2" t="n">
+      <c r="I438" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="H438" t="n">
+      <c r="J438" t="n">
         <v>6.9</v>
       </c>
-      <c r="I438" s="2" t="n">
+      <c r="K438" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="J438" t="n">
+      <c r="L438" t="n">
         <v>7.2</v>
       </c>
-      <c r="K438" s="2" t="n">
+      <c r="M438" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="L438" t="n">
+      <c r="N438" t="n">
         <v>6.8</v>
       </c>
-      <c r="M438" s="2" t="n">
+      <c r="O438" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="N438" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O438" s="2" t="n">
-        <v>46047</v>
-      </c>
       <c r="P438" t="n">
-        <v>6.81</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="439">
@@ -19035,49 +19075,49 @@
         <v>593</v>
       </c>
       <c r="B442" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="C442" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D442" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E442" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D442" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E442" s="2" t="n">
+      <c r="F442" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G442" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F442" t="n">
+      <c r="H442" t="n">
         <v>6.1</v>
       </c>
-      <c r="G442" s="2" t="n">
+      <c r="I442" s="2" t="n">
         <v>46082</v>
-      </c>
-      <c r="H442" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I442" s="2" t="n">
-        <v>46073</v>
       </c>
       <c r="J442" t="n">
         <v>6.9</v>
       </c>
       <c r="K442" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="L442" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M442" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L442" t="n">
+      <c r="N442" t="n">
         <v>6.4</v>
       </c>
-      <c r="M442" s="2" t="n">
+      <c r="O442" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="N442" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O442" s="2" t="n">
-        <v>45998</v>
-      </c>
       <c r="P442" t="n">
-        <v>6.59</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="443">
@@ -19673,49 +19713,49 @@
         <v>607</v>
       </c>
       <c r="B456" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="C456" s="2" t="n">
-        <v>46102</v>
+        <v>46116</v>
       </c>
       <c r="D456" t="n">
         <v>6.8</v>
       </c>
       <c r="E456" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="F456" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G456" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F456" t="n">
+      <c r="H456" t="n">
         <v>7.3</v>
       </c>
-      <c r="G456" s="2" t="n">
+      <c r="I456" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H456" t="n">
+      <c r="J456" t="n">
         <v>6.8</v>
       </c>
-      <c r="I456" s="2" t="n">
+      <c r="K456" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="J456" t="n">
+      <c r="L456" t="n">
         <v>7.9</v>
       </c>
-      <c r="K456" s="2" t="n">
+      <c r="M456" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L456" t="n">
+      <c r="N456" t="n">
         <v>7</v>
       </c>
-      <c r="M456" s="2" t="n">
+      <c r="O456" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="N456" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O456" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P456" t="n">
-        <v>7.11</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="457">
@@ -19773,49 +19813,49 @@
         <v>609</v>
       </c>
       <c r="B458" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C458" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D458" t="n">
         <v>6.4</v>
       </c>
-      <c r="C458" s="2" t="n">
+      <c r="E458" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="D458" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E458" s="2" t="n">
+      <c r="F458" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G458" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="F458" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G458" s="2" t="n">
+      <c r="H458" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I458" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H458" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I458" s="2" t="n">
+      <c r="J458" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K458" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="J458" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K458" s="2" t="n">
+      <c r="L458" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M458" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="L458" t="n">
+      <c r="N458" t="n">
         <v>7.6</v>
       </c>
-      <c r="M458" s="2" t="n">
+      <c r="O458" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="N458" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O458" s="2" t="n">
-        <v>46003</v>
-      </c>
       <c r="P458" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="459">
@@ -19943,49 +19983,49 @@
         <v>613</v>
       </c>
       <c r="B462" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C462" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="D462" t="n">
         <v>6.9</v>
       </c>
-      <c r="C462" s="2" t="n">
+      <c r="E462" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D462" t="n">
+      <c r="F462" t="n">
         <v>7.7</v>
       </c>
-      <c r="E462" s="2" t="n">
+      <c r="G462" s="2" t="n">
         <v>46095</v>
-      </c>
-      <c r="F462" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G462" s="2" t="n">
-        <v>46089</v>
       </c>
       <c r="H462" t="n">
         <v>6.3</v>
       </c>
       <c r="I462" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="J462" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K462" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="J462" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K462" s="2" t="n">
+      <c r="L462" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M462" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L462" t="n">
+      <c r="N462" t="n">
         <v>6.4</v>
       </c>
-      <c r="M462" s="2" t="n">
+      <c r="O462" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="N462" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O462" s="2" t="n">
-        <v>45991</v>
-      </c>
       <c r="P462" t="n">
-        <v>6.81</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="463">
@@ -20093,49 +20133,49 @@
         <v>617</v>
       </c>
       <c r="B465" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C465" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D465" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E465" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D465" t="n">
+      <c r="F465" t="n">
         <v>7.5</v>
       </c>
-      <c r="E465" s="2" t="n">
+      <c r="G465" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="F465" t="n">
+      <c r="H465" t="n">
         <v>7.3</v>
       </c>
-      <c r="G465" s="2" t="n">
+      <c r="I465" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H465" t="n">
+      <c r="J465" t="n">
         <v>6.4</v>
       </c>
-      <c r="I465" s="2" t="n">
+      <c r="K465" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="J465" t="n">
+      <c r="L465" t="n">
         <v>6.8</v>
       </c>
-      <c r="K465" s="2" t="n">
+      <c r="M465" s="2" t="n">
         <v>46076</v>
       </c>
-      <c r="L465" t="n">
+      <c r="N465" t="n">
         <v>6</v>
       </c>
-      <c r="M465" s="2" t="n">
+      <c r="O465" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="N465" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O465" s="2" t="n">
-        <v>46048</v>
-      </c>
       <c r="P465" t="n">
-        <v>6.76</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="466">
@@ -20143,49 +20183,49 @@
         <v>618</v>
       </c>
       <c r="B466" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C466" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D466" t="n">
         <v>6.8</v>
       </c>
-      <c r="C466" s="2" t="n">
+      <c r="E466" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="D466" t="n">
+      <c r="F466" t="n">
         <v>8</v>
       </c>
-      <c r="E466" s="2" t="n">
+      <c r="G466" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F466" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G466" s="2" t="n">
+      <c r="H466" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I466" s="2" t="n">
         <v>46098</v>
       </c>
-      <c r="H466" t="n">
+      <c r="J466" t="n">
         <v>7</v>
       </c>
-      <c r="I466" s="2" t="n">
+      <c r="K466" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="J466" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K466" s="2" t="n">
+      <c r="L466" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M466" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="L466" t="n">
+      <c r="N466" t="n">
         <v>5.8</v>
       </c>
-      <c r="M466" s="2" t="n">
+      <c r="O466" s="2" t="n">
         <v>46084</v>
       </c>
-      <c r="N466" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O466" s="2" t="n">
-        <v>46080</v>
-      </c>
       <c r="P466" t="n">
-        <v>6.77</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="467">
@@ -20755,49 +20795,49 @@
         <v>631</v>
       </c>
       <c r="B479" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C479" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D479" t="n">
         <v>7.1</v>
       </c>
-      <c r="C479" s="2" t="n">
+      <c r="E479" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="D479" t="n">
+      <c r="F479" t="n">
         <v>7.3</v>
       </c>
-      <c r="E479" s="2" t="n">
+      <c r="G479" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="F479" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G479" s="2" t="n">
+      <c r="H479" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I479" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="H479" t="n">
+      <c r="J479" t="n">
         <v>7</v>
       </c>
-      <c r="I479" s="2" t="n">
+      <c r="K479" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="J479" t="n">
+      <c r="L479" t="n">
         <v>6.8</v>
       </c>
-      <c r="K479" s="2" t="n">
+      <c r="M479" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L479" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M479" s="2" t="n">
+      <c r="N479" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O479" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="N479" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O479" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P479" t="n">
-        <v>7.19</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="480">
@@ -21227,49 +21267,49 @@
         <v>641</v>
       </c>
       <c r="B489" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="C489" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D489" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E489" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="D489" t="n">
+      <c r="F489" t="n">
         <v>6.3</v>
       </c>
-      <c r="E489" s="2" t="n">
+      <c r="G489" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F489" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G489" s="2" t="n">
+      <c r="H489" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I489" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="H489" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I489" s="2" t="n">
+      <c r="J489" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K489" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="J489" t="n">
+      <c r="L489" t="n">
         <v>7</v>
       </c>
-      <c r="K489" s="2" t="n">
+      <c r="M489" s="2" t="n">
         <v>46003</v>
       </c>
-      <c r="L489" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M489" s="2" t="n">
+      <c r="N489" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O489" s="2" t="n">
         <v>45997</v>
       </c>
-      <c r="N489" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O489" s="2" t="n">
-        <v>45989</v>
-      </c>
       <c r="P489" t="n">
-        <v>6.59</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="490">
@@ -21277,49 +21317,49 @@
         <v>642</v>
       </c>
       <c r="B490" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C490" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D490" t="n">
         <v>7.2</v>
       </c>
-      <c r="C490" s="2" t="n">
+      <c r="E490" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D490" t="n">
+      <c r="F490" t="n">
         <v>7.3</v>
       </c>
-      <c r="E490" s="2" t="n">
+      <c r="G490" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F490" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G490" s="2" t="n">
+      <c r="H490" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I490" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H490" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I490" s="2" t="n">
+      <c r="J490" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K490" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J490" t="n">
+      <c r="L490" t="n">
         <v>7.4</v>
       </c>
-      <c r="K490" s="2" t="n">
+      <c r="M490" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L490" t="n">
+      <c r="N490" t="n">
         <v>7.9</v>
       </c>
-      <c r="M490" s="2" t="n">
+      <c r="O490" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="N490" t="n">
-        <v>7</v>
-      </c>
-      <c r="O490" s="2" t="n">
-        <v>46058</v>
-      </c>
       <c r="P490" t="n">
-        <v>7.14</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="491">
@@ -21517,49 +21557,49 @@
         <v>648</v>
       </c>
       <c r="B496" t="n">
+        <v>6</v>
+      </c>
+      <c r="C496" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="D496" t="n">
         <v>6.3</v>
       </c>
-      <c r="C496" s="2" t="n">
+      <c r="E496" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D496" t="n">
+      <c r="F496" t="n">
         <v>6.9</v>
       </c>
-      <c r="E496" s="2" t="n">
+      <c r="G496" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F496" t="n">
+      <c r="H496" t="n">
         <v>7</v>
       </c>
-      <c r="G496" s="2" t="n">
+      <c r="I496" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H496" t="n">
+      <c r="J496" t="n">
         <v>6.2</v>
       </c>
-      <c r="I496" s="2" t="n">
+      <c r="K496" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="J496" t="n">
+      <c r="L496" t="n">
         <v>6.9</v>
       </c>
-      <c r="K496" s="2" t="n">
+      <c r="M496" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="L496" t="n">
+      <c r="N496" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="M496" s="2" t="n">
+      <c r="O496" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="N496" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O496" s="2" t="n">
-        <v>46067</v>
-      </c>
       <c r="P496" t="n">
-        <v>7.34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="497">
@@ -21937,49 +21977,49 @@
         <v>658</v>
       </c>
       <c r="B506" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C506" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="D506" t="n">
         <v>7.3</v>
       </c>
-      <c r="C506" s="2" t="n">
+      <c r="E506" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D506" t="n">
+      <c r="F506" t="n">
         <v>7.1</v>
       </c>
-      <c r="E506" s="2" t="n">
+      <c r="G506" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="F506" t="n">
+      <c r="H506" t="n">
         <v>7.6</v>
       </c>
-      <c r="G506" s="2" t="n">
+      <c r="I506" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H506" t="n">
+      <c r="J506" t="n">
         <v>7.2</v>
       </c>
-      <c r="I506" s="2" t="n">
+      <c r="K506" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J506" t="n">
+      <c r="L506" t="n">
         <v>7.4</v>
       </c>
-      <c r="K506" s="2" t="n">
+      <c r="M506" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="L506" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M506" s="2" t="n">
+      <c r="N506" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O506" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N506" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O506" s="2" t="n">
-        <v>46056</v>
-      </c>
       <c r="P506" t="n">
-        <v>7.04</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="507">

--- a/players_ratings.xlsx
+++ b/players_ratings.xlsx
@@ -619,49 +619,49 @@
         <v>15</v>
       </c>
       <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D4" t="n">
         <v>7.8</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>6.4</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>7.1</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="H4" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I4" s="2" t="n">
+      <c r="J4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>6.4</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="M4" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>7.2</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="N4" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>46068</v>
-      </c>
       <c r="P4" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="5">
@@ -1011,49 +1011,49 @@
         <v>34</v>
       </c>
       <c r="B13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D13" t="n">
         <v>6.2</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="E13" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="D13" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E13" s="2" t="n">
+      <c r="F13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>6.2</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>7.1</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="K13" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>6.8</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="M13" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>6.3</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="O13" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="N13" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>46062</v>
-      </c>
       <c r="P13" t="n">
-        <v>6.77</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="14">
@@ -3121,49 +3121,49 @@
         <v>146</v>
       </c>
       <c r="B69" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="C69" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D69" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E69" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D69" t="n">
+      <c r="F69" t="n">
         <v>6.8</v>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F69" t="n">
+      <c r="H69" t="n">
         <v>7.1</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="I69" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H69" t="n">
+      <c r="J69" t="n">
         <v>7.3</v>
       </c>
-      <c r="I69" s="2" t="n">
+      <c r="K69" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>6.8</v>
       </c>
-      <c r="K69" s="2" t="n">
+      <c r="M69" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="L69" t="n">
+      <c r="N69" t="n">
         <v>7.7</v>
       </c>
-      <c r="M69" s="2" t="n">
+      <c r="O69" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="N69" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O69" s="2" t="n">
-        <v>46066</v>
-      </c>
       <c r="P69" t="n">
-        <v>6.97</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="70">
@@ -3171,49 +3171,49 @@
         <v>147</v>
       </c>
       <c r="B70" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D70" t="n">
         <v>6.8</v>
       </c>
-      <c r="C70" s="2" t="n">
+      <c r="E70" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D70" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E70" s="2" t="n">
+      <c r="F70" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G70" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="F70" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G70" s="2" t="n">
+      <c r="H70" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I70" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H70" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I70" s="2" t="n">
+      <c r="J70" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K70" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J70" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K70" s="2" t="n">
+      <c r="L70" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M70" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L70" t="n">
+      <c r="N70" t="n">
         <v>6.2</v>
       </c>
-      <c r="M70" s="2" t="n">
+      <c r="O70" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="N70" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O70" s="2" t="n">
-        <v>46059</v>
-      </c>
       <c r="P70" t="n">
-        <v>6.64</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="71">
@@ -3291,49 +3291,49 @@
         <v>150</v>
       </c>
       <c r="B73" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="F73" t="n">
         <v>6.8</v>
       </c>
-      <c r="C73" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D73" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E73" s="2" t="n">
+      <c r="H73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I73" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F73" t="n">
+      <c r="J73" t="n">
         <v>7.6</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="K73" s="2" t="n">
         <v>46097</v>
-      </c>
-      <c r="H73" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>46089</v>
-      </c>
-      <c r="J73" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="K73" s="2" t="n">
-        <v>46081</v>
       </c>
       <c r="L73" t="n">
         <v>7.1</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>45970</v>
+        <v>46089</v>
       </c>
       <c r="N73" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="O73" s="2" t="n">
-        <v>45962</v>
+        <v>46081</v>
       </c>
       <c r="P73" t="n">
-        <v>6.99</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="74">
@@ -3441,49 +3441,49 @@
         <v>165</v>
       </c>
       <c r="B76" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D76" t="n">
         <v>6.8</v>
       </c>
-      <c r="C76" s="2" t="n">
+      <c r="E76" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D76" t="n">
+      <c r="F76" t="n">
         <v>6.9</v>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="G76" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F76" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G76" s="2" t="n">
+      <c r="H76" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I76" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H76" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I76" s="2" t="n">
+      <c r="J76" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K76" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
         <v>6.9</v>
       </c>
-      <c r="K76" s="2" t="n">
+      <c r="M76" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L76" t="n">
+      <c r="N76" t="n">
         <v>7.3</v>
       </c>
-      <c r="M76" s="2" t="n">
+      <c r="O76" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="N76" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O76" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P76" t="n">
-        <v>6.84</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="77">
@@ -3541,49 +3541,49 @@
         <v>167</v>
       </c>
       <c r="B78" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="D78" t="n">
         <v>7.8</v>
       </c>
-      <c r="C78" s="2" t="n">
+      <c r="E78" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="D78" t="n">
+      <c r="F78" t="n">
         <v>6.8</v>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="F78" t="n">
+      <c r="H78" t="n">
         <v>6.9</v>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="I78" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="H78" t="n">
+      <c r="J78" t="n">
         <v>7</v>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="K78" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>7.5</v>
       </c>
-      <c r="K78" s="2" t="n">
+      <c r="M78" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="L78" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M78" s="2" t="n">
+      <c r="N78" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O78" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N78" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O78" s="2" t="n">
-        <v>46068</v>
-      </c>
       <c r="P78" t="n">
-        <v>7.24</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="79">
@@ -3721,49 +3721,49 @@
         <v>173</v>
       </c>
       <c r="B82" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D82" t="n">
         <v>7.3</v>
       </c>
-      <c r="C82" s="2" t="n">
+      <c r="E82" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D82" t="n">
+      <c r="F82" t="n">
         <v>6.9</v>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="G82" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F82" t="n">
+      <c r="H82" t="n">
         <v>7.1</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="I82" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H82" t="n">
+      <c r="J82" t="n">
         <v>7.3</v>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="K82" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J82" t="n">
+      <c r="L82" t="n">
         <v>6.8</v>
       </c>
-      <c r="K82" s="2" t="n">
+      <c r="M82" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="L82" t="n">
+      <c r="N82" t="n">
         <v>6.3</v>
       </c>
-      <c r="M82" s="2" t="n">
+      <c r="O82" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N82" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O82" s="2" t="n">
-        <v>46058</v>
-      </c>
       <c r="P82" t="n">
-        <v>6.89</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="83">
@@ -3821,49 +3821,49 @@
         <v>175</v>
       </c>
       <c r="B84" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="C84" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D84" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E84" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D84" t="n">
+      <c r="F84" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E84" s="2" t="n">
+      <c r="G84" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="F84" t="n">
+      <c r="H84" t="n">
         <v>6</v>
       </c>
-      <c r="G84" s="2" t="n">
+      <c r="I84" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="H84" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I84" s="2" t="n">
+      <c r="J84" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K84" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="J84" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K84" s="2" t="n">
+      <c r="L84" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M84" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="L84" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M84" s="2" t="n">
+      <c r="N84" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O84" s="2" t="n">
         <v>46056</v>
       </c>
-      <c r="N84" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O84" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P84" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="85">
@@ -3955,46 +3955,46 @@
         <v>181</v>
       </c>
       <c r="B87" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D87" t="n">
         <v>7.4</v>
       </c>
-      <c r="C87" s="2" t="n">
+      <c r="E87" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D87" t="n">
+      <c r="F87" t="n">
         <v>6.9</v>
       </c>
-      <c r="E87" s="2" t="n">
+      <c r="G87" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F87" t="n">
+      <c r="H87" t="n">
         <v>7</v>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="I87" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="H87" t="n">
+      <c r="J87" t="n">
         <v>6.4</v>
       </c>
-      <c r="I87" s="2" t="n">
+      <c r="K87" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J87" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K87" s="2" t="n">
+      <c r="L87" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M87" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
         <v>6.9</v>
       </c>
-      <c r="M87" s="2" t="n">
+      <c r="O87" s="2" t="n">
         <v>46069</v>
-      </c>
-      <c r="N87" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O87" s="2" t="n">
-        <v>46060</v>
       </c>
       <c r="P87" t="n">
         <v>6.91</v>
@@ -7065,45 +7065,49 @@
         <v>283</v>
       </c>
       <c r="B158" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="C158" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D158" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E158" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="D158" t="n">
+      <c r="F158" t="n">
         <v>6.3</v>
       </c>
-      <c r="E158" s="2" t="n">
+      <c r="G158" s="2" t="n">
         <v>45886</v>
       </c>
-      <c r="F158" t="n">
+      <c r="H158" t="n">
         <v>7</v>
       </c>
-      <c r="G158" s="2" t="n">
+      <c r="I158" s="2" t="n">
         <v>45880</v>
       </c>
-      <c r="H158" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I158" s="2" t="n">
+      <c r="J158" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K158" s="2" t="n">
         <v>45863</v>
       </c>
-      <c r="J158" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K158" s="2" t="n">
+      <c r="L158" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M158" s="2" t="n">
         <v>45858</v>
       </c>
-      <c r="L158" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M158" s="2" t="n">
+      <c r="N158" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O158" s="2" t="n">
         <v>45849</v>
       </c>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
       <c r="P158" t="n">
-        <v>6.63</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="159">
@@ -7411,49 +7415,49 @@
         <v>291</v>
       </c>
       <c r="B165" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D165" t="n">
         <v>7.9</v>
       </c>
-      <c r="C165" s="2" t="n">
+      <c r="E165" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="D165" t="n">
+      <c r="F165" t="n">
         <v>6.8</v>
       </c>
-      <c r="E165" s="2" t="n">
+      <c r="G165" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F165" t="n">
+      <c r="H165" t="n">
         <v>6.4</v>
       </c>
-      <c r="G165" s="2" t="n">
+      <c r="I165" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H165" t="n">
+      <c r="J165" t="n">
         <v>7</v>
       </c>
-      <c r="I165" s="2" t="n">
+      <c r="K165" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="J165" t="n">
+      <c r="L165" t="n">
         <v>6.2</v>
       </c>
-      <c r="K165" s="2" t="n">
+      <c r="M165" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="L165" t="n">
+      <c r="N165" t="n">
         <v>6.3</v>
       </c>
-      <c r="M165" s="2" t="n">
+      <c r="O165" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N165" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O165" s="2" t="n">
-        <v>46068</v>
-      </c>
       <c r="P165" t="n">
-        <v>6.71</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="166">
@@ -7461,37 +7465,41 @@
         <v>292</v>
       </c>
       <c r="B166" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D166" t="n">
         <v>7.6</v>
       </c>
-      <c r="C166" s="2" t="n">
+      <c r="E166" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="D166" t="n">
+      <c r="F166" t="n">
         <v>7</v>
       </c>
-      <c r="E166" s="2" t="n">
+      <c r="G166" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="F166" t="n">
+      <c r="H166" t="n">
         <v>7.4</v>
       </c>
-      <c r="G166" s="2" t="n">
+      <c r="I166" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="H166" t="n">
+      <c r="J166" t="n">
         <v>6.8</v>
       </c>
-      <c r="I166" s="2" t="n">
+      <c r="K166" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="n">
-        <v>7.2</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="167">
@@ -7860,46 +7868,46 @@
         <v>6.5</v>
       </c>
       <c r="C175" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D175" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E175" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D175" t="n">
+      <c r="F175" t="n">
         <v>7.1</v>
       </c>
-      <c r="E175" s="2" t="n">
+      <c r="G175" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F175" t="n">
+      <c r="H175" t="n">
         <v>7.3</v>
       </c>
-      <c r="G175" s="2" t="n">
+      <c r="I175" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="H175" t="n">
+      <c r="J175" t="n">
         <v>6.9</v>
       </c>
-      <c r="I175" s="2" t="n">
+      <c r="K175" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J175" t="n">
+      <c r="L175" t="n">
         <v>7</v>
       </c>
-      <c r="K175" s="2" t="n">
+      <c r="M175" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L175" t="n">
+      <c r="N175" t="n">
         <v>6.9</v>
       </c>
-      <c r="M175" s="2" t="n">
+      <c r="O175" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N175" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O175" s="2" t="n">
-        <v>46059</v>
-      </c>
       <c r="P175" t="n">
-        <v>6.93</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="176">
@@ -8687,49 +8695,49 @@
         <v>322</v>
       </c>
       <c r="B192" t="n">
+        <v>8</v>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D192" t="n">
         <v>6.9</v>
       </c>
-      <c r="C192" s="2" t="n">
+      <c r="E192" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="D192" t="n">
+      <c r="F192" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="E192" s="2" t="n">
+      <c r="G192" s="2" t="n">
         <v>46114</v>
-      </c>
-      <c r="F192" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G192" s="2" t="n">
-        <v>46108</v>
       </c>
       <c r="H192" t="n">
         <v>7.3</v>
       </c>
       <c r="I192" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="J192" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K192" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="J192" t="n">
+      <c r="L192" t="n">
         <v>7.1</v>
       </c>
-      <c r="K192" s="2" t="n">
+      <c r="M192" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="L192" t="n">
+      <c r="N192" t="n">
         <v>6.3</v>
       </c>
-      <c r="M192" s="2" t="n">
+      <c r="O192" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="N192" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O192" s="2" t="n">
-        <v>45975</v>
-      </c>
       <c r="P192" t="n">
-        <v>7.06</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="193">
@@ -8987,49 +8995,49 @@
         <v>330</v>
       </c>
       <c r="B199" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C199" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D199" t="n">
         <v>6.8</v>
       </c>
-      <c r="C199" s="2" t="n">
+      <c r="E199" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D199" t="n">
+      <c r="F199" t="n">
         <v>7.2</v>
       </c>
-      <c r="E199" s="2" t="n">
+      <c r="G199" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F199" t="n">
+      <c r="H199" t="n">
         <v>7.3</v>
       </c>
-      <c r="G199" s="2" t="n">
+      <c r="I199" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H199" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I199" s="2" t="n">
+      <c r="J199" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K199" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J199" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K199" s="2" t="n">
+      <c r="L199" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M199" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="L199" t="n">
+      <c r="N199" t="n">
         <v>7.4</v>
       </c>
-      <c r="M199" s="2" t="n">
+      <c r="O199" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N199" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O199" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="P199" t="n">
-        <v>7.11</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="200">
@@ -9317,49 +9325,49 @@
         <v>340</v>
       </c>
       <c r="B206" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="C206" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D206" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E206" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D206" t="n">
+      <c r="F206" t="n">
         <v>7.7</v>
       </c>
-      <c r="E206" s="2" t="n">
+      <c r="G206" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F206" t="n">
+      <c r="H206" t="n">
         <v>6.8</v>
       </c>
-      <c r="G206" s="2" t="n">
+      <c r="I206" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H206" t="n">
+      <c r="J206" t="n">
         <v>7.1</v>
       </c>
-      <c r="I206" s="2" t="n">
+      <c r="K206" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J206" t="n">
+      <c r="L206" t="n">
         <v>6.3</v>
       </c>
-      <c r="K206" s="2" t="n">
+      <c r="M206" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="L206" t="n">
+      <c r="N206" t="n">
         <v>7</v>
       </c>
-      <c r="M206" s="2" t="n">
+      <c r="O206" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="N206" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O206" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P206" t="n">
-        <v>7.03</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="207">
@@ -9907,49 +9915,49 @@
         <v>353</v>
       </c>
       <c r="B219" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="C219" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D219" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E219" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="D219" t="n">
+      <c r="F219" t="n">
         <v>6.4</v>
       </c>
-      <c r="E219" s="2" t="n">
+      <c r="G219" s="2" t="n">
         <v>46100</v>
       </c>
-      <c r="F219" t="n">
+      <c r="H219" t="n">
         <v>7.1</v>
       </c>
-      <c r="G219" s="2" t="n">
+      <c r="I219" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H219" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I219" s="2" t="n">
+      <c r="J219" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K219" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J219" t="n">
+      <c r="L219" t="n">
         <v>7.9</v>
       </c>
-      <c r="K219" s="2" t="n">
+      <c r="M219" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L219" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M219" s="2" t="n">
+      <c r="N219" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O219" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="N219" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O219" s="2" t="n">
-        <v>46062</v>
-      </c>
       <c r="P219" t="n">
-        <v>6.87</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="220">
@@ -10132,43 +10140,43 @@
         <v>6.9</v>
       </c>
       <c r="C224" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D224" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E224" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="D224" t="n">
+      <c r="F224" t="n">
         <v>6.3</v>
       </c>
-      <c r="E224" s="2" t="n">
+      <c r="G224" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F224" t="n">
+      <c r="H224" t="n">
         <v>6.9</v>
       </c>
-      <c r="G224" s="2" t="n">
+      <c r="I224" s="2" t="n">
         <v>46086</v>
-      </c>
-      <c r="H224" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I224" s="2" t="n">
-        <v>46069</v>
       </c>
       <c r="J224" t="n">
         <v>7.2</v>
       </c>
       <c r="K224" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="L224" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M224" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L224" t="n">
+      <c r="N224" t="n">
         <v>6.8</v>
       </c>
-      <c r="M224" s="2" t="n">
+      <c r="O224" s="2" t="n">
         <v>46058</v>
-      </c>
-      <c r="N224" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O224" s="2" t="n">
-        <v>46052</v>
       </c>
       <c r="P224" t="n">
         <v>6.89</v>
@@ -10401,49 +10409,49 @@
         <v>369</v>
       </c>
       <c r="B230" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="C230" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D230" t="n">
         <v>6.8</v>
       </c>
-      <c r="C230" s="2" t="n">
+      <c r="E230" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="D230" t="n">
+      <c r="F230" t="n">
         <v>7.2</v>
       </c>
-      <c r="E230" s="2" t="n">
+      <c r="G230" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F230" t="n">
+      <c r="H230" t="n">
         <v>7.8</v>
       </c>
-      <c r="G230" s="2" t="n">
+      <c r="I230" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="H230" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I230" s="2" t="n">
+      <c r="J230" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K230" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J230" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K230" s="2" t="n">
+      <c r="L230" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M230" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="L230" t="n">
+      <c r="N230" t="n">
         <v>6.9</v>
       </c>
-      <c r="M230" s="2" t="n">
+      <c r="O230" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="N230" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O230" s="2" t="n">
-        <v>46062</v>
-      </c>
       <c r="P230" t="n">
-        <v>6.97</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="231">
@@ -10795,46 +10803,46 @@
         <v>379</v>
       </c>
       <c r="B240" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C240" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D240" t="n">
         <v>6.9</v>
       </c>
-      <c r="C240" s="2" t="n">
+      <c r="E240" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="D240" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E240" s="2" t="n">
+      <c r="F240" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G240" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="F240" t="n">
+      <c r="H240" t="n">
         <v>6.4</v>
       </c>
-      <c r="G240" s="2" t="n">
+      <c r="I240" s="2" t="n">
         <v>46058</v>
       </c>
-      <c r="H240" t="n">
+      <c r="J240" t="n">
         <v>6.8</v>
       </c>
-      <c r="I240" s="2" t="n">
+      <c r="K240" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="J240" t="n">
+      <c r="L240" t="n">
         <v>7.7</v>
       </c>
-      <c r="K240" s="2" t="n">
+      <c r="M240" s="2" t="n">
         <v>46041</v>
       </c>
-      <c r="L240" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M240" s="2" t="n">
+      <c r="N240" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O240" s="2" t="n">
         <v>46013</v>
-      </c>
-      <c r="N240" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O240" s="2" t="n">
-        <v>45998</v>
       </c>
       <c r="P240" t="n">
         <v>6.8</v>
@@ -11351,49 +11359,49 @@
         <v>395</v>
       </c>
       <c r="B254" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="C254" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D254" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E254" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D254" t="n">
+      <c r="F254" t="n">
         <v>6.8</v>
       </c>
-      <c r="E254" s="2" t="n">
+      <c r="G254" s="2" t="n">
         <v>46098</v>
       </c>
-      <c r="F254" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G254" s="2" t="n">
+      <c r="H254" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I254" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H254" t="n">
+      <c r="J254" t="n">
         <v>6.3</v>
       </c>
-      <c r="I254" s="2" t="n">
+      <c r="K254" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J254" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K254" s="2" t="n">
+      <c r="L254" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M254" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="L254" t="n">
+      <c r="N254" t="n">
         <v>7.6</v>
       </c>
-      <c r="M254" s="2" t="n">
+      <c r="O254" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="N254" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O254" s="2" t="n">
-        <v>46068</v>
-      </c>
       <c r="P254" t="n">
-        <v>6.67</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="255">
@@ -12343,49 +12351,49 @@
         <v>419</v>
       </c>
       <c r="B278" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C278" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="D278" t="n">
         <v>6.3</v>
       </c>
-      <c r="C278" s="2" t="n">
+      <c r="E278" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="D278" t="n">
+      <c r="F278" t="n">
         <v>6.4</v>
       </c>
-      <c r="E278" s="2" t="n">
+      <c r="G278" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F278" t="n">
+      <c r="H278" t="n">
         <v>7.5</v>
       </c>
-      <c r="G278" s="2" t="n">
+      <c r="I278" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="H278" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I278" s="2" t="n">
+      <c r="J278" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K278" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J278" t="n">
+      <c r="L278" t="n">
         <v>6.4</v>
       </c>
-      <c r="K278" s="2" t="n">
+      <c r="M278" s="2" t="n">
         <v>45926</v>
       </c>
-      <c r="L278" t="n">
+      <c r="N278" t="n">
         <v>7.1</v>
       </c>
-      <c r="M278" s="2" t="n">
+      <c r="O278" s="2" t="n">
         <v>45919</v>
       </c>
-      <c r="N278" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O278" s="2" t="n">
-        <v>45914</v>
-      </c>
       <c r="P278" t="n">
-        <v>6.71</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="279">
@@ -12443,49 +12451,49 @@
         <v>421</v>
       </c>
       <c r="B280" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="C280" s="2" t="n">
-        <v>46117</v>
+        <v>46124</v>
       </c>
       <c r="D280" t="n">
         <v>7.2</v>
       </c>
       <c r="E280" s="2" t="n">
-        <v>46101</v>
+        <v>46117</v>
       </c>
       <c r="F280" t="n">
         <v>7.2</v>
       </c>
       <c r="G280" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="H280" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I280" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="H280" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I280" s="2" t="n">
+      <c r="J280" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K280" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J280" t="n">
+      <c r="L280" t="n">
         <v>8.4</v>
       </c>
-      <c r="K280" s="2" t="n">
+      <c r="M280" s="2" t="n">
         <v>45997</v>
       </c>
-      <c r="L280" t="n">
+      <c r="N280" t="n">
         <v>9.6</v>
       </c>
-      <c r="M280" s="2" t="n">
+      <c r="O280" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="N280" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O280" s="2" t="n">
-        <v>45984</v>
-      </c>
       <c r="P280" t="n">
-        <v>7.6</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="281">
@@ -13757,49 +13765,49 @@
         <v>458</v>
       </c>
       <c r="B312" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C312" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D312" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E312" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D312" t="n">
+      <c r="F312" t="n">
         <v>6.4</v>
       </c>
-      <c r="E312" s="2" t="n">
+      <c r="G312" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F312" t="n">
+      <c r="H312" t="n">
         <v>6.8</v>
       </c>
-      <c r="G312" s="2" t="n">
+      <c r="I312" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H312" t="n">
+      <c r="J312" t="n">
         <v>6.3</v>
       </c>
-      <c r="I312" s="2" t="n">
+      <c r="K312" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J312" t="n">
+      <c r="L312" t="n">
         <v>7.2</v>
       </c>
-      <c r="K312" s="2" t="n">
+      <c r="M312" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L312" t="n">
+      <c r="N312" t="n">
         <v>6.4</v>
       </c>
-      <c r="M312" s="2" t="n">
+      <c r="O312" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="N312" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O312" s="2" t="n">
-        <v>46053</v>
-      </c>
       <c r="P312" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="313">
@@ -13807,49 +13815,49 @@
         <v>459</v>
       </c>
       <c r="B313" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C313" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D313" t="n">
         <v>6.9</v>
       </c>
-      <c r="C313" s="2" t="n">
+      <c r="E313" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D313" t="n">
+      <c r="F313" t="n">
         <v>7.2</v>
       </c>
-      <c r="E313" s="2" t="n">
+      <c r="G313" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F313" t="n">
+      <c r="H313" t="n">
         <v>8</v>
       </c>
-      <c r="G313" s="2" t="n">
+      <c r="I313" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="H313" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I313" s="2" t="n">
+      <c r="J313" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K313" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J313" t="n">
+      <c r="L313" t="n">
         <v>7.3</v>
       </c>
-      <c r="K313" s="2" t="n">
+      <c r="M313" s="2" t="n">
         <v>45998</v>
       </c>
-      <c r="L313" t="n">
+      <c r="N313" t="n">
         <v>6.8</v>
       </c>
-      <c r="M313" s="2" t="n">
+      <c r="O313" s="2" t="n">
         <v>45994</v>
       </c>
-      <c r="N313" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O313" s="2" t="n">
-        <v>45989</v>
-      </c>
       <c r="P313" t="n">
-        <v>7.14</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="314">
@@ -14684,46 +14692,46 @@
         <v>6.6</v>
       </c>
       <c r="C334" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D334" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E334" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="D334" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E334" s="2" t="n">
+      <c r="F334" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G334" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F334" t="n">
+      <c r="H334" t="n">
         <v>7</v>
       </c>
-      <c r="G334" s="2" t="n">
+      <c r="I334" s="2" t="n">
         <v>46086</v>
       </c>
-      <c r="H334" t="n">
+      <c r="J334" t="n">
         <v>6.4</v>
       </c>
-      <c r="I334" s="2" t="n">
+      <c r="K334" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="J334" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K334" s="2" t="n">
+      <c r="L334" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M334" s="2" t="n">
         <v>45999</v>
       </c>
-      <c r="L334" t="n">
+      <c r="N334" t="n">
         <v>6.8</v>
       </c>
-      <c r="M334" s="2" t="n">
+      <c r="O334" s="2" t="n">
         <v>45983</v>
       </c>
-      <c r="N334" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O334" s="2" t="n">
-        <v>45970</v>
-      </c>
       <c r="P334" t="n">
-        <v>6.6</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="335">
@@ -14801,49 +14809,49 @@
         <v>483</v>
       </c>
       <c r="B337" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C337" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D337" t="n">
         <v>5.4</v>
       </c>
-      <c r="C337" s="2" t="n">
+      <c r="E337" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="D337" t="n">
+      <c r="F337" t="n">
         <v>7.2</v>
       </c>
-      <c r="E337" s="2" t="n">
+      <c r="G337" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="F337" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G337" s="2" t="n">
+      <c r="H337" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I337" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="H337" t="n">
+      <c r="J337" t="n">
         <v>6.4</v>
       </c>
-      <c r="I337" s="2" t="n">
+      <c r="K337" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="J337" t="n">
+      <c r="L337" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K337" s="2" t="n">
+      <c r="M337" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="L337" t="n">
+      <c r="N337" t="n">
         <v>7.4</v>
       </c>
-      <c r="M337" s="2" t="n">
+      <c r="O337" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="N337" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O337" s="2" t="n">
-        <v>46080</v>
-      </c>
       <c r="P337" t="n">
-        <v>6.79</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="338">
@@ -14951,49 +14959,49 @@
         <v>486</v>
       </c>
       <c r="B340" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="C340" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D340" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E340" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="D340" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E340" s="2" t="n">
+      <c r="F340" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G340" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="F340" t="n">
+      <c r="H340" t="n">
         <v>6.3</v>
       </c>
-      <c r="G340" s="2" t="n">
+      <c r="I340" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H340" t="n">
+      <c r="J340" t="n">
         <v>7.4</v>
       </c>
-      <c r="I340" s="2" t="n">
+      <c r="K340" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="J340" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K340" s="2" t="n">
+      <c r="L340" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M340" s="2" t="n">
         <v>45999</v>
       </c>
-      <c r="L340" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M340" s="2" t="n">
+      <c r="N340" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O340" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="N340" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O340" s="2" t="n">
-        <v>45984</v>
-      </c>
       <c r="P340" t="n">
-        <v>6.61</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="341">
@@ -15001,49 +15009,49 @@
         <v>487</v>
       </c>
       <c r="B341" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="C341" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D341" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E341" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="D341" t="n">
+      <c r="F341" t="n">
         <v>6.8</v>
       </c>
-      <c r="E341" s="2" t="n">
+      <c r="G341" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="F341" t="n">
+      <c r="H341" t="n">
         <v>6.1</v>
       </c>
-      <c r="G341" s="2" t="n">
+      <c r="I341" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H341" t="n">
+      <c r="J341" t="n">
         <v>6.3</v>
       </c>
-      <c r="I341" s="2" t="n">
+      <c r="K341" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="J341" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K341" s="2" t="n">
+      <c r="L341" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M341" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="L341" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M341" s="2" t="n">
+      <c r="N341" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O341" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="N341" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O341" s="2" t="n">
-        <v>45984</v>
-      </c>
       <c r="P341" t="n">
-        <v>6.46</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="342">
@@ -15051,49 +15059,49 @@
         <v>488</v>
       </c>
       <c r="B342" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="C342" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D342" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E342" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="D342" t="n">
+      <c r="F342" t="n">
         <v>6.4</v>
       </c>
-      <c r="E342" s="2" t="n">
+      <c r="G342" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="F342" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G342" s="2" t="n">
+      <c r="H342" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I342" s="2" t="n">
         <v>45963</v>
       </c>
-      <c r="H342" t="n">
+      <c r="J342" t="n">
         <v>7.2</v>
       </c>
-      <c r="I342" s="2" t="n">
+      <c r="K342" s="2" t="n">
         <v>45956</v>
       </c>
-      <c r="J342" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K342" s="2" t="n">
+      <c r="L342" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M342" s="2" t="n">
         <v>45949</v>
       </c>
-      <c r="L342" t="n">
+      <c r="N342" t="n">
         <v>6.4</v>
       </c>
-      <c r="M342" s="2" t="n">
+      <c r="O342" s="2" t="n">
         <v>45928</v>
       </c>
-      <c r="N342" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O342" s="2" t="n">
-        <v>45898</v>
-      </c>
       <c r="P342" t="n">
-        <v>6.69</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="343">
@@ -15827,49 +15835,49 @@
         <v>507</v>
       </c>
       <c r="B360" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C360" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D360" t="n">
         <v>6.8</v>
       </c>
-      <c r="C360" s="2" t="n">
+      <c r="E360" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="D360" t="n">
+      <c r="F360" t="n">
         <v>6.3</v>
       </c>
-      <c r="E360" s="2" t="n">
+      <c r="G360" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F360" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G360" s="2" t="n">
+      <c r="H360" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I360" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H360" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I360" s="2" t="n">
+      <c r="J360" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K360" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J360" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K360" s="2" t="n">
+      <c r="L360" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M360" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="L360" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M360" s="2" t="n">
+      <c r="N360" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O360" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="N360" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O360" s="2" t="n">
-        <v>46055</v>
-      </c>
       <c r="P360" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="361">
@@ -16309,49 +16317,49 @@
         <v>520</v>
       </c>
       <c r="B373" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C373" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D373" t="n">
         <v>7.1</v>
       </c>
-      <c r="C373" s="2" t="n">
+      <c r="E373" s="2" t="n">
         <v>46117</v>
-      </c>
-      <c r="D373" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E373" s="2" t="n">
-        <v>46103</v>
       </c>
       <c r="F373" t="n">
         <v>6.8</v>
       </c>
       <c r="G373" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="H373" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I373" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H373" t="n">
+      <c r="J373" t="n">
         <v>7.2</v>
       </c>
-      <c r="I373" s="2" t="n">
+      <c r="K373" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J373" t="n">
+      <c r="L373" t="n">
         <v>8.1</v>
       </c>
-      <c r="K373" s="2" t="n">
+      <c r="M373" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="L373" t="n">
+      <c r="N373" t="n">
         <v>5.6</v>
       </c>
-      <c r="M373" s="2" t="n">
+      <c r="O373" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="N373" t="n">
-        <v>8</v>
-      </c>
-      <c r="O373" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P373" t="n">
-        <v>7.09</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="374">
@@ -16359,49 +16367,49 @@
         <v>521</v>
       </c>
       <c r="B374" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="C374" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="D374" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E374" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="D374" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E374" s="2" t="n">
+      <c r="F374" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G374" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="F374" t="n">
+      <c r="H374" t="n">
         <v>6.9</v>
       </c>
-      <c r="G374" s="2" t="n">
+      <c r="I374" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="H374" t="n">
+      <c r="J374" t="n">
         <v>6.2</v>
       </c>
-      <c r="I374" s="2" t="n">
+      <c r="K374" s="2" t="n">
         <v>46011</v>
       </c>
-      <c r="J374" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K374" s="2" t="n">
+      <c r="L374" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M374" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="L374" t="n">
+      <c r="N374" t="n">
         <v>6.3</v>
       </c>
-      <c r="M374" s="2" t="n">
+      <c r="O374" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="N374" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O374" s="2" t="n">
-        <v>45983</v>
-      </c>
       <c r="P374" t="n">
-        <v>6.51</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="375">
@@ -16487,37 +16495,41 @@
         <v>525</v>
       </c>
       <c r="B378" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C378" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D378" t="n">
         <v>7.6</v>
       </c>
-      <c r="C378" s="2" t="n">
+      <c r="E378" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="D378" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E378" s="2" t="n">
+      <c r="F378" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G378" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="F378" t="n">
+      <c r="H378" t="n">
         <v>7.1</v>
       </c>
-      <c r="G378" s="2" t="n">
+      <c r="I378" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="H378" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I378" s="2" t="n">
+      <c r="J378" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K378" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="J378" t="inlineStr"/>
-      <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr"/>
       <c r="M378" t="inlineStr"/>
       <c r="N378" t="inlineStr"/>
       <c r="O378" t="inlineStr"/>
       <c r="P378" t="n">
-        <v>6.95</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="379">
@@ -16817,49 +16829,49 @@
         <v>540</v>
       </c>
       <c r="B392" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C392" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="D392" t="n">
         <v>6.8</v>
       </c>
-      <c r="C392" s="2" t="n">
+      <c r="E392" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D392" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E392" s="2" t="n">
+      <c r="F392" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G392" s="2" t="n">
         <v>46099</v>
       </c>
-      <c r="F392" t="n">
+      <c r="H392" t="n">
         <v>7.2</v>
       </c>
-      <c r="G392" s="2" t="n">
+      <c r="I392" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H392" t="n">
+      <c r="J392" t="n">
         <v>8.6</v>
       </c>
-      <c r="I392" s="2" t="n">
+      <c r="K392" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="J392" t="n">
+      <c r="L392" t="n">
         <v>7</v>
       </c>
-      <c r="K392" s="2" t="n">
+      <c r="M392" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="L392" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M392" s="2" t="n">
+      <c r="N392" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O392" s="2" t="n">
         <v>46077</v>
       </c>
-      <c r="N392" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O392" s="2" t="n">
-        <v>45991</v>
-      </c>
       <c r="P392" t="n">
-        <v>7.04</v>
+        <v>7</v>
       </c>
     </row>
     <row r="393">
@@ -17613,49 +17625,49 @@
         <v>557</v>
       </c>
       <c r="B409" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C409" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D409" t="n">
         <v>7.6</v>
       </c>
-      <c r="C409" s="2" t="n">
+      <c r="E409" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="D409" t="n">
+      <c r="F409" t="n">
         <v>6.4</v>
       </c>
-      <c r="E409" s="2" t="n">
+      <c r="G409" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="F409" t="n">
+      <c r="H409" t="n">
         <v>8</v>
       </c>
-      <c r="G409" s="2" t="n">
+      <c r="I409" s="2" t="n">
         <v>46103</v>
-      </c>
-      <c r="H409" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I409" s="2" t="n">
-        <v>46095</v>
       </c>
       <c r="J409" t="n">
         <v>7.1</v>
       </c>
       <c r="K409" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="L409" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M409" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="L409" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M409" s="2" t="n">
+      <c r="N409" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O409" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="N409" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O409" s="2" t="n">
-        <v>46004</v>
-      </c>
       <c r="P409" t="n">
-        <v>7.24</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="410">
@@ -17663,49 +17675,49 @@
         <v>558</v>
       </c>
       <c r="B410" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C410" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="D410" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E410" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F410" t="n">
         <v>6.4</v>
       </c>
-      <c r="C410" s="2" t="n">
+      <c r="G410" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="D410" t="n">
+      <c r="H410" t="n">
         <v>7.1</v>
       </c>
-      <c r="E410" s="2" t="n">
+      <c r="I410" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="F410" t="n">
+      <c r="J410" t="n">
         <v>7.4</v>
       </c>
-      <c r="G410" s="2" t="n">
+      <c r="K410" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="H410" t="n">
+      <c r="L410" t="n">
         <v>6.9</v>
       </c>
-      <c r="I410" s="2" t="n">
+      <c r="M410" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="J410" t="n">
+      <c r="N410" t="n">
         <v>6.9</v>
       </c>
-      <c r="K410" s="2" t="n">
+      <c r="O410" s="2" t="n">
         <v>45996</v>
       </c>
-      <c r="L410" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M410" s="2" t="n">
-        <v>45990</v>
-      </c>
-      <c r="N410" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O410" s="2" t="n">
-        <v>45986</v>
-      </c>
       <c r="P410" t="n">
-        <v>6.77</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="411">
@@ -17967,49 +17979,49 @@
         <v>565</v>
       </c>
       <c r="B417" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C417" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="D417" t="n">
         <v>6.4</v>
       </c>
-      <c r="C417" s="2" t="n">
+      <c r="E417" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D417" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E417" s="2" t="n">
+      <c r="F417" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G417" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F417" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G417" s="2" t="n">
+      <c r="H417" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I417" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H417" t="n">
+      <c r="J417" t="n">
         <v>7.1</v>
       </c>
-      <c r="I417" s="2" t="n">
+      <c r="K417" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J417" t="n">
+      <c r="L417" t="n">
         <v>7.6</v>
       </c>
-      <c r="K417" s="2" t="n">
+      <c r="M417" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L417" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M417" s="2" t="n">
+      <c r="N417" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O417" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="N417" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O417" s="2" t="n">
-        <v>46054</v>
-      </c>
       <c r="P417" t="n">
-        <v>6.77</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="418">
@@ -18055,49 +18067,49 @@
         <v>567</v>
       </c>
       <c r="B419" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C419" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D419" t="n">
         <v>6.8</v>
       </c>
-      <c r="C419" s="2" t="n">
+      <c r="E419" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D419" t="n">
+      <c r="F419" t="n">
         <v>7.8</v>
       </c>
-      <c r="E419" s="2" t="n">
+      <c r="G419" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F419" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G419" s="2" t="n">
+      <c r="H419" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I419" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H419" t="n">
+      <c r="J419" t="n">
         <v>7.1</v>
       </c>
-      <c r="I419" s="2" t="n">
+      <c r="K419" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="J419" t="n">
+      <c r="L419" t="n">
         <v>6.8</v>
       </c>
-      <c r="K419" s="2" t="n">
+      <c r="M419" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="L419" t="n">
+      <c r="N419" t="n">
         <v>6.3</v>
       </c>
-      <c r="M419" s="2" t="n">
+      <c r="O419" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N419" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O419" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="P419" t="n">
-        <v>6.89</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="420">
@@ -19055,49 +19067,49 @@
         <v>591</v>
       </c>
       <c r="B440" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C440" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D440" t="n">
         <v>7.2</v>
       </c>
-      <c r="C440" s="2" t="n">
+      <c r="E440" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="D440" t="n">
+      <c r="F440" t="n">
         <v>6.9</v>
       </c>
-      <c r="E440" s="2" t="n">
+      <c r="G440" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="F440" t="n">
+      <c r="H440" t="n">
         <v>7.1</v>
       </c>
-      <c r="G440" s="2" t="n">
+      <c r="I440" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="H440" t="n">
+      <c r="J440" t="n">
         <v>7</v>
       </c>
-      <c r="I440" s="2" t="n">
+      <c r="K440" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="J440" t="n">
+      <c r="L440" t="n">
         <v>7.1</v>
       </c>
-      <c r="K440" s="2" t="n">
+      <c r="M440" s="2" t="n">
         <v>45983</v>
       </c>
-      <c r="L440" t="n">
+      <c r="N440" t="n">
         <v>6.8</v>
       </c>
-      <c r="M440" s="2" t="n">
+      <c r="O440" s="2" t="n">
         <v>45969</v>
       </c>
-      <c r="N440" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O440" s="2" t="n">
-        <v>45962</v>
-      </c>
       <c r="P440" t="n">
-        <v>7.04</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="441">
@@ -19531,49 +19543,49 @@
         <v>601</v>
       </c>
       <c r="B450" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C450" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D450" t="n">
         <v>6.8</v>
       </c>
-      <c r="C450" s="2" t="n">
+      <c r="E450" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D450" t="n">
+      <c r="F450" t="n">
         <v>6.9</v>
       </c>
-      <c r="E450" s="2" t="n">
+      <c r="G450" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="F450" t="n">
+      <c r="H450" t="n">
         <v>7</v>
       </c>
-      <c r="G450" s="2" t="n">
+      <c r="I450" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H450" t="n">
+      <c r="J450" t="n">
         <v>7.6</v>
       </c>
-      <c r="I450" s="2" t="n">
+      <c r="K450" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="J450" t="n">
+      <c r="L450" t="n">
         <v>6.1</v>
       </c>
-      <c r="K450" s="2" t="n">
+      <c r="M450" s="2" t="n">
         <v>46074</v>
-      </c>
-      <c r="L450" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="M450" s="2" t="n">
-        <v>46068</v>
       </c>
       <c r="N450" t="n">
         <v>7.2</v>
       </c>
       <c r="O450" s="2" t="n">
-        <v>46059</v>
+        <v>46068</v>
       </c>
       <c r="P450" t="n">
-        <v>6.97</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="451">
@@ -19793,49 +19805,49 @@
         <v>607</v>
       </c>
       <c r="B456" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C456" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D456" t="n">
         <v>6.2</v>
       </c>
-      <c r="C456" s="2" t="n">
+      <c r="E456" s="2" t="n">
         <v>46116</v>
-      </c>
-      <c r="D456" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E456" s="2" t="n">
-        <v>46102</v>
       </c>
       <c r="F456" t="n">
         <v>6.8</v>
       </c>
       <c r="G456" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="H456" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I456" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H456" t="n">
+      <c r="J456" t="n">
         <v>7.3</v>
       </c>
-      <c r="I456" s="2" t="n">
+      <c r="K456" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J456" t="n">
+      <c r="L456" t="n">
         <v>6.8</v>
       </c>
-      <c r="K456" s="2" t="n">
+      <c r="M456" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L456" t="n">
+      <c r="N456" t="n">
         <v>7.9</v>
       </c>
-      <c r="M456" s="2" t="n">
+      <c r="O456" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N456" t="n">
-        <v>7</v>
-      </c>
-      <c r="O456" s="2" t="n">
-        <v>46059</v>
-      </c>
       <c r="P456" t="n">
-        <v>6.97</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="457">
@@ -20063,49 +20075,49 @@
         <v>613</v>
       </c>
       <c r="B462" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C462" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D462" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E462" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="D462" t="n">
+      <c r="F462" t="n">
         <v>6.9</v>
       </c>
-      <c r="E462" s="2" t="n">
+      <c r="G462" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="F462" t="n">
+      <c r="H462" t="n">
         <v>7.7</v>
       </c>
-      <c r="G462" s="2" t="n">
+      <c r="I462" s="2" t="n">
         <v>46095</v>
-      </c>
-      <c r="H462" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="I462" s="2" t="n">
-        <v>46089</v>
       </c>
       <c r="J462" t="n">
         <v>6.3</v>
       </c>
       <c r="K462" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="L462" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M462" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L462" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M462" s="2" t="n">
+      <c r="N462" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O462" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="N462" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O462" s="2" t="n">
-        <v>46054</v>
-      </c>
       <c r="P462" t="n">
-        <v>6.69</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="463">
@@ -20316,46 +20328,46 @@
         <v>7.1</v>
       </c>
       <c r="C467" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="D467" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E467" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D467" t="n">
+      <c r="F467" t="n">
         <v>7.3</v>
       </c>
-      <c r="E467" s="2" t="n">
+      <c r="G467" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F467" t="n">
+      <c r="H467" t="n">
         <v>6.9</v>
       </c>
-      <c r="G467" s="2" t="n">
+      <c r="I467" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H467" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I467" s="2" t="n">
+      <c r="J467" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K467" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="J467" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K467" s="2" t="n">
+      <c r="L467" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M467" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="L467" t="n">
+      <c r="N467" t="n">
         <v>7.2</v>
       </c>
-      <c r="M467" s="2" t="n">
+      <c r="O467" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N467" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O467" s="2" t="n">
-        <v>46004</v>
-      </c>
       <c r="P467" t="n">
-        <v>7.01</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="468">
@@ -20363,49 +20375,49 @@
         <v>620</v>
       </c>
       <c r="B468" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="C468" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="D468" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E468" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="D468" t="n">
+      <c r="F468" t="n">
         <v>6.8</v>
       </c>
-      <c r="E468" s="2" t="n">
+      <c r="G468" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="F468" t="n">
+      <c r="H468" t="n">
         <v>7.3</v>
       </c>
-      <c r="G468" s="2" t="n">
+      <c r="I468" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="H468" t="n">
+      <c r="J468" t="n">
         <v>7</v>
       </c>
-      <c r="I468" s="2" t="n">
+      <c r="K468" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="J468" t="n">
+      <c r="L468" t="n">
         <v>6.2</v>
       </c>
-      <c r="K468" s="2" t="n">
+      <c r="M468" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="L468" t="n">
+      <c r="N468" t="n">
         <v>6.4</v>
       </c>
-      <c r="M468" s="2" t="n">
+      <c r="O468" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="N468" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O468" s="2" t="n">
-        <v>46077</v>
-      </c>
       <c r="P468" t="n">
-        <v>6.77</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="469">
@@ -20875,49 +20887,49 @@
         <v>631</v>
       </c>
       <c r="B479" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C479" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="D479" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="C479" s="2" t="n">
+      <c r="E479" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="D479" t="n">
+      <c r="F479" t="n">
         <v>7.2</v>
       </c>
-      <c r="E479" s="2" t="n">
+      <c r="G479" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="F479" t="n">
+      <c r="H479" t="n">
         <v>7.4</v>
       </c>
-      <c r="G479" s="2" t="n">
+      <c r="I479" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="H479" t="n">
+      <c r="J479" t="n">
         <v>7.1</v>
       </c>
-      <c r="I479" s="2" t="n">
+      <c r="K479" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J479" t="n">
+      <c r="L479" t="n">
         <v>7.3</v>
       </c>
-      <c r="K479" s="2" t="n">
+      <c r="M479" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="L479" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M479" s="2" t="n">
+      <c r="N479" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O479" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N479" t="n">
-        <v>7</v>
-      </c>
-      <c r="O479" s="2" t="n">
-        <v>46068</v>
-      </c>
       <c r="P479" t="n">
-        <v>7.29</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="480">
@@ -21397,49 +21409,49 @@
         <v>642</v>
       </c>
       <c r="B490" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C490" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D490" t="n">
         <v>6.8</v>
       </c>
-      <c r="C490" s="2" t="n">
+      <c r="E490" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D490" t="n">
+      <c r="F490" t="n">
         <v>7.2</v>
       </c>
-      <c r="E490" s="2" t="n">
+      <c r="G490" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F490" t="n">
+      <c r="H490" t="n">
         <v>7.3</v>
       </c>
-      <c r="G490" s="2" t="n">
+      <c r="I490" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H490" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I490" s="2" t="n">
+      <c r="J490" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K490" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J490" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K490" s="2" t="n">
+      <c r="L490" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M490" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="L490" t="n">
+      <c r="N490" t="n">
         <v>7.4</v>
       </c>
-      <c r="M490" s="2" t="n">
+      <c r="O490" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N490" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O490" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="P490" t="n">
-        <v>7.11</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="491">
@@ -21767,49 +21779,49 @@
         <v>651</v>
       </c>
       <c r="B499" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="C499" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="D499" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E499" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="D499" t="n">
+      <c r="F499" t="n">
         <v>7.3</v>
       </c>
-      <c r="E499" s="2" t="n">
+      <c r="G499" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="F499" t="n">
+      <c r="H499" t="n">
         <v>6.8</v>
       </c>
-      <c r="G499" s="2" t="n">
+      <c r="I499" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H499" t="n">
+      <c r="J499" t="n">
         <v>7</v>
       </c>
-      <c r="I499" s="2" t="n">
+      <c r="K499" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J499" t="n">
+      <c r="L499" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K499" s="2" t="n">
+      <c r="M499" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L499" t="n">
+      <c r="N499" t="n">
         <v>7.5</v>
       </c>
-      <c r="M499" s="2" t="n">
+      <c r="O499" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="N499" t="n">
-        <v>9</v>
-      </c>
-      <c r="O499" s="2" t="n">
-        <v>45997</v>
-      </c>
       <c r="P499" t="n">
-        <v>7.49</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="500">
@@ -21817,41 +21829,45 @@
         <v>652</v>
       </c>
       <c r="B500" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C500" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D500" t="n">
         <v>7.1</v>
       </c>
-      <c r="C500" s="2" t="n">
+      <c r="E500" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="D500" t="n">
+      <c r="F500" t="n">
         <v>7.2</v>
       </c>
-      <c r="E500" s="2" t="n">
+      <c r="G500" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="F500" t="n">
+      <c r="H500" t="n">
         <v>6.8</v>
       </c>
-      <c r="G500" s="2" t="n">
+      <c r="I500" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="H500" t="n">
+      <c r="J500" t="n">
         <v>7.3</v>
       </c>
-      <c r="I500" s="2" t="n">
+      <c r="K500" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="J500" t="n">
+      <c r="L500" t="n">
         <v>7</v>
       </c>
-      <c r="K500" s="2" t="n">
+      <c r="M500" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="L500" t="inlineStr"/>
-      <c r="M500" t="inlineStr"/>
       <c r="N500" t="inlineStr"/>
       <c r="O500" t="inlineStr"/>
       <c r="P500" t="n">
-        <v>7.08</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="501">
@@ -22081,49 +22097,49 @@
         <v>658</v>
       </c>
       <c r="B506" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C506" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D506" t="n">
         <v>6.9</v>
       </c>
-      <c r="C506" s="2" t="n">
+      <c r="E506" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="D506" t="n">
+      <c r="F506" t="n">
         <v>7.3</v>
       </c>
-      <c r="E506" s="2" t="n">
+      <c r="G506" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F506" t="n">
+      <c r="H506" t="n">
         <v>7.1</v>
       </c>
-      <c r="G506" s="2" t="n">
+      <c r="I506" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="H506" t="n">
+      <c r="J506" t="n">
         <v>7.6</v>
       </c>
-      <c r="I506" s="2" t="n">
+      <c r="K506" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J506" t="n">
+      <c r="L506" t="n">
         <v>7.2</v>
       </c>
-      <c r="K506" s="2" t="n">
+      <c r="M506" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L506" t="n">
+      <c r="N506" t="n">
         <v>7.4</v>
       </c>
-      <c r="M506" s="2" t="n">
+      <c r="O506" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="N506" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O506" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P506" t="n">
-        <v>7.16</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="507">

--- a/players_ratings.xlsx
+++ b/players_ratings.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P509"/>
+  <dimension ref="A1:P515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B2" t="n">
@@ -565,7 +565,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B3" t="n">
@@ -615,7 +615,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B4" t="n">
@@ -665,7 +665,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B5" t="n">
@@ -715,7 +715,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B6" t="n">
@@ -761,7 +761,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B7" t="n">
@@ -811,7 +811,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B8" t="n">
@@ -841,57 +841,57 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
         <v>27</v>
       </c>
       <c r="B9" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="C9" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>7.9</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>6.3</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I9" s="2" t="n">
+      <c r="J9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>7.2</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="M9" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>6.2</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="N9" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>46080</v>
-      </c>
       <c r="P9" t="n">
-        <v>6.93</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
         <v>28</v>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -911,7 +911,7 @@
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="1" t="n">
         <v>29</v>
       </c>
       <c r="B11" t="n">
@@ -961,7 +961,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="1" t="n">
         <v>30</v>
       </c>
       <c r="B12" t="n">
@@ -1011,7 +1011,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="1" t="n">
         <v>34</v>
       </c>
       <c r="B13" t="n">
@@ -1061,7 +1061,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="1" t="n">
         <v>36</v>
       </c>
       <c r="B14" t="n">
@@ -1111,7 +1111,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="1" t="n">
         <v>38</v>
       </c>
       <c r="B15" t="n">
@@ -1161,7 +1161,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="1" t="n">
         <v>39</v>
       </c>
       <c r="B16" t="n">
@@ -1187,7 +1187,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="1" t="n">
         <v>41</v>
       </c>
       <c r="B17" t="n">
@@ -1237,7 +1237,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="1" t="n">
         <v>43</v>
       </c>
       <c r="B18" t="n">
@@ -1287,7 +1287,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="1" t="n">
         <v>44</v>
       </c>
       <c r="B19" t="n">
@@ -1337,7 +1337,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="1" t="n">
         <v>46</v>
       </c>
       <c r="B20" t="n">
@@ -1387,7 +1387,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="1" t="n">
         <v>47</v>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
       <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="1" t="n">
         <v>49</v>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
       <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="1" t="n">
         <v>51</v>
       </c>
       <c r="B23" t="n">
@@ -1477,7 +1477,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="1" t="n">
         <v>53</v>
       </c>
       <c r="B24" t="n">
@@ -1527,7 +1527,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="1" t="n">
         <v>55</v>
       </c>
       <c r="B25" t="n">
@@ -1561,7 +1561,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="1" t="n">
         <v>56</v>
       </c>
       <c r="B26" t="n">
@@ -1599,7 +1599,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="1" t="n">
         <v>57</v>
       </c>
       <c r="B27" t="n">
@@ -1649,7 +1649,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="1" t="n">
         <v>59</v>
       </c>
       <c r="B28" t="n">
@@ -1683,7 +1683,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="1" t="n">
         <v>62</v>
       </c>
       <c r="B29" t="n">
@@ -1733,7 +1733,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="1" t="n">
         <v>65</v>
       </c>
       <c r="B30" t="n">
@@ -1783,7 +1783,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="1" t="n">
         <v>66</v>
       </c>
       <c r="B31" t="n">
@@ -1833,7 +1833,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="1" t="n">
         <v>67</v>
       </c>
       <c r="B32" t="n">
@@ -1883,7 +1883,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="1" t="n">
         <v>69</v>
       </c>
       <c r="B33" t="n">
@@ -1933,7 +1933,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="1" t="n">
         <v>75</v>
       </c>
       <c r="B34" t="n">
@@ -1983,7 +1983,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" s="1" t="n">
         <v>80</v>
       </c>
       <c r="B35" t="n">
@@ -2033,7 +2033,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="1" t="n">
         <v>81</v>
       </c>
       <c r="B36" t="n">
@@ -2075,7 +2075,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="1" t="n">
         <v>83</v>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2095,7 +2095,7 @@
       <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="1" t="n">
         <v>85</v>
       </c>
       <c r="B38" t="n">
@@ -2125,7 +2125,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="1" t="n">
         <v>91</v>
       </c>
       <c r="B39" t="n">
@@ -2175,7 +2175,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="1" t="n">
         <v>94</v>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="1" t="n">
         <v>95</v>
       </c>
       <c r="B41" t="n">
@@ -2245,7 +2245,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="1" t="n">
         <v>96</v>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
       <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="1" t="n">
         <v>98</v>
       </c>
       <c r="B43" t="n">
@@ -2315,7 +2315,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="1" t="n">
         <v>99</v>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="1" t="n">
         <v>100</v>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2355,7 +2355,7 @@
       <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="1" t="n">
         <v>101</v>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2375,7 +2375,7 @@
       <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="1" t="n">
         <v>102</v>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
       <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="1" t="n">
         <v>103</v>
       </c>
       <c r="B48" t="n">
@@ -2429,7 +2429,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="1" t="n">
         <v>104</v>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2449,7 +2449,7 @@
       <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="1" t="n">
         <v>106</v>
       </c>
       <c r="B50" t="n">
@@ -2475,7 +2475,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="1" t="n">
         <v>107</v>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2495,7 +2495,7 @@
       <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" s="1" t="n">
         <v>110</v>
       </c>
       <c r="B52" t="n">
@@ -2533,7 +2533,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" s="1" t="n">
         <v>111</v>
       </c>
       <c r="B53" t="n">
@@ -2559,7 +2559,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" s="1" t="n">
         <v>117</v>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
       <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="1" t="n">
         <v>118</v>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2599,7 +2599,7 @@
       <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" s="1" t="n">
         <v>119</v>
       </c>
       <c r="B56" t="n">
@@ -2649,7 +2649,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="1" t="n">
         <v>121</v>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2669,7 +2669,7 @@
       <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" s="1" t="n">
         <v>122</v>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2689,7 +2689,7 @@
       <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="1" t="n">
         <v>124</v>
       </c>
       <c r="B59" t="n">
@@ -2739,7 +2739,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" s="1" t="n">
         <v>126</v>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2759,7 +2759,7 @@
       <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" s="1" t="n">
         <v>132</v>
       </c>
       <c r="B61" t="n">
@@ -2809,7 +2809,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" s="1" t="n">
         <v>133</v>
       </c>
       <c r="B62" t="n">
@@ -2859,7 +2859,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" s="1" t="n">
         <v>135</v>
       </c>
       <c r="B63" t="n">
@@ -2909,7 +2909,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" s="1" t="n">
         <v>138</v>
       </c>
       <c r="B64" t="n">
@@ -2959,7 +2959,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" s="1" t="n">
         <v>141</v>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2979,7 +2979,7 @@
       <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="1" t="n">
         <v>143</v>
       </c>
       <c r="B66" t="n">
@@ -3029,7 +3029,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="1" t="n">
         <v>144</v>
       </c>
       <c r="B67" t="n">
@@ -3079,7 +3079,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="1" t="n">
         <v>145</v>
       </c>
       <c r="B68" t="n">
@@ -3129,7 +3129,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="1" t="n">
         <v>146</v>
       </c>
       <c r="B69" t="n">
@@ -3179,7 +3179,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" s="1" t="n">
         <v>147</v>
       </c>
       <c r="B70" t="n">
@@ -3229,7 +3229,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="1" t="n">
         <v>148</v>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3249,7 +3249,7 @@
       <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" s="1" t="n">
         <v>149</v>
       </c>
       <c r="B72" t="n">
@@ -3299,7 +3299,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" s="1" t="n">
         <v>150</v>
       </c>
       <c r="B73" t="n">
@@ -3349,7 +3349,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" s="1" t="n">
         <v>155</v>
       </c>
       <c r="B74" t="n">
@@ -3399,7 +3399,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="1" t="n">
         <v>164</v>
       </c>
       <c r="B75" t="n">
@@ -3449,7 +3449,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76" s="1" t="n">
         <v>165</v>
       </c>
       <c r="B76" t="n">
@@ -3499,7 +3499,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" s="1" t="n">
         <v>166</v>
       </c>
       <c r="B77" t="n">
@@ -3549,7 +3549,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78" s="1" t="n">
         <v>167</v>
       </c>
       <c r="B78" t="n">
@@ -3599,7 +3599,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79" s="1" t="n">
         <v>169</v>
       </c>
       <c r="B79" t="n">
@@ -3641,7 +3641,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80" s="1" t="n">
         <v>170</v>
       </c>
       <c r="B80" t="n">
@@ -3691,7 +3691,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" s="1" t="n">
         <v>171</v>
       </c>
       <c r="B81" t="n">
@@ -3733,7 +3733,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
+      <c r="A82" s="1" t="n">
         <v>173</v>
       </c>
       <c r="B82" t="n">
@@ -3783,7 +3783,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83" s="1" t="n">
         <v>174</v>
       </c>
       <c r="B83" t="n">
@@ -3833,57 +3833,57 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84" s="1" t="n">
         <v>175</v>
       </c>
       <c r="B84" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>46127</v>
+        <v>46131</v>
       </c>
       <c r="D84" t="n">
         <v>6.8</v>
       </c>
       <c r="E84" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="F84" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G84" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F84" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G84" s="2" t="n">
+      <c r="H84" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I84" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H84" t="n">
+      <c r="J84" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I84" s="2" t="n">
+      <c r="K84" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="J84" t="n">
+      <c r="L84" t="n">
         <v>6</v>
       </c>
-      <c r="K84" s="2" t="n">
+      <c r="M84" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L84" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M84" s="2" t="n">
+      <c r="N84" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O84" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="N84" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O84" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="P84" t="n">
-        <v>6.91</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85" s="1" t="n">
         <v>176</v>
       </c>
       <c r="B85" t="n">
@@ -3917,7 +3917,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
+      <c r="A86" s="1" t="n">
         <v>178</v>
       </c>
       <c r="B86" t="n">
@@ -3967,57 +3967,57 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" s="1" t="n">
         <v>181</v>
       </c>
       <c r="B87" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>46127</v>
+        <v>46131</v>
       </c>
       <c r="D87" t="n">
         <v>7.1</v>
       </c>
       <c r="E87" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="F87" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G87" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F87" t="n">
+      <c r="H87" t="n">
         <v>7.4</v>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="I87" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H87" t="n">
+      <c r="J87" t="n">
         <v>6.9</v>
       </c>
-      <c r="I87" s="2" t="n">
+      <c r="K87" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J87" t="n">
+      <c r="L87" t="n">
         <v>7</v>
       </c>
-      <c r="K87" s="2" t="n">
+      <c r="M87" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
         <v>6.4</v>
       </c>
-      <c r="M87" s="2" t="n">
+      <c r="O87" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="N87" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O87" s="2" t="n">
-        <v>46075</v>
-      </c>
       <c r="P87" t="n">
-        <v>6.94</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88" s="1" t="n">
         <v>182</v>
       </c>
       <c r="B88" t="n">
@@ -4067,7 +4067,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89" s="1" t="n">
         <v>184</v>
       </c>
       <c r="B89" t="n">
@@ -4105,7 +4105,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
+      <c r="A90" s="1" t="n">
         <v>185</v>
       </c>
       <c r="B90" t="n">
@@ -4155,7 +4155,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
+      <c r="A91" s="1" t="n">
         <v>186</v>
       </c>
       <c r="B91" t="n">
@@ -4205,7 +4205,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
+      <c r="A92" s="1" t="n">
         <v>188</v>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -4225,7 +4225,7 @@
       <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="n">
+      <c r="A93" s="1" t="n">
         <v>189</v>
       </c>
       <c r="B93" t="n">
@@ -4275,7 +4275,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
+      <c r="A94" s="1" t="n">
         <v>191</v>
       </c>
       <c r="B94" t="n">
@@ -4325,7 +4325,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
+      <c r="A95" s="1" t="n">
         <v>192</v>
       </c>
       <c r="B95" t="n">
@@ -4375,7 +4375,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
+      <c r="A96" s="1" t="n">
         <v>193</v>
       </c>
       <c r="B96" t="n">
@@ -4417,7 +4417,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" s="1" t="n">
         <v>194</v>
       </c>
       <c r="B97" t="n">
@@ -4467,7 +4467,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
+      <c r="A98" s="1" t="n">
         <v>195</v>
       </c>
       <c r="B98" t="n">
@@ -4517,7 +4517,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99" s="1" t="n">
         <v>196</v>
       </c>
       <c r="B99" t="n">
@@ -4567,7 +4567,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
+      <c r="A100" s="1" t="n">
         <v>198</v>
       </c>
       <c r="B100" t="n">
@@ -4617,7 +4617,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
+      <c r="A101" s="1" t="n">
         <v>200</v>
       </c>
       <c r="B101" t="n">
@@ -4667,7 +4667,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
+      <c r="A102" s="1" t="n">
         <v>201</v>
       </c>
       <c r="B102" t="n">
@@ -4717,7 +4717,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
+      <c r="A103" s="1" t="n">
         <v>202</v>
       </c>
       <c r="B103" t="n">
@@ -4767,7 +4767,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
+      <c r="A104" s="1" t="n">
         <v>206</v>
       </c>
       <c r="B104" t="n">
@@ -4817,7 +4817,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
+      <c r="A105" s="1" t="n">
         <v>207</v>
       </c>
       <c r="B105" t="n">
@@ -4843,7 +4843,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
+      <c r="A106" s="1" t="n">
         <v>208</v>
       </c>
       <c r="B106" t="n">
@@ -4893,7 +4893,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
+      <c r="A107" s="1" t="n">
         <v>210</v>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4913,7 +4913,7 @@
       <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="n">
+      <c r="A108" s="1" t="n">
         <v>211</v>
       </c>
       <c r="B108" t="n">
@@ -4963,7 +4963,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
+      <c r="A109" s="1" t="n">
         <v>212</v>
       </c>
       <c r="B109" t="n">
@@ -5013,7 +5013,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
+      <c r="A110" s="1" t="n">
         <v>213</v>
       </c>
       <c r="B110" t="n">
@@ -5039,7 +5039,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
+      <c r="A111" s="1" t="n">
         <v>214</v>
       </c>
       <c r="B111" t="n">
@@ -5089,7 +5089,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
+      <c r="A112" s="1" t="n">
         <v>216</v>
       </c>
       <c r="B112" t="n">
@@ -5139,7 +5139,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
+      <c r="A113" s="1" t="n">
         <v>217</v>
       </c>
       <c r="B113" t="n">
@@ -5189,7 +5189,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
+      <c r="A114" s="1" t="n">
         <v>218</v>
       </c>
       <c r="B114" t="n">
@@ -5239,7 +5239,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="n">
+      <c r="A115" s="1" t="n">
         <v>219</v>
       </c>
       <c r="B115" t="n">
@@ -5289,7 +5289,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
+      <c r="A116" s="1" t="n">
         <v>220</v>
       </c>
       <c r="B116" t="n">
@@ -5315,7 +5315,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
+      <c r="A117" s="1" t="n">
         <v>221</v>
       </c>
       <c r="B117" t="n">
@@ -5365,7 +5365,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
+      <c r="A118" s="1" t="n">
         <v>222</v>
       </c>
       <c r="B118" t="n">
@@ -5415,7 +5415,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
+      <c r="A119" s="1" t="n">
         <v>223</v>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -5435,7 +5435,7 @@
       <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="n">
+      <c r="A120" s="1" t="n">
         <v>224</v>
       </c>
       <c r="B120" t="n">
@@ -5485,7 +5485,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
+      <c r="A121" s="1" t="n">
         <v>226</v>
       </c>
       <c r="B121" t="n">
@@ -5535,7 +5535,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
+      <c r="A122" s="1" t="n">
         <v>227</v>
       </c>
       <c r="B122" t="n">
@@ -5585,7 +5585,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
+      <c r="A123" s="1" t="n">
         <v>228</v>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5605,7 +5605,7 @@
       <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="n">
+      <c r="A124" s="1" t="n">
         <v>229</v>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5625,7 +5625,7 @@
       <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="n">
+      <c r="A125" s="1" t="n">
         <v>230</v>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5645,7 +5645,7 @@
       <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="n">
+      <c r="A126" s="1" t="n">
         <v>232</v>
       </c>
       <c r="B126" t="n">
@@ -5695,7 +5695,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="n">
+      <c r="A127" s="1" t="n">
         <v>234</v>
       </c>
       <c r="B127" t="n">
@@ -5721,7 +5721,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
+      <c r="A128" s="1" t="n">
         <v>236</v>
       </c>
       <c r="B128" t="n">
@@ -5771,7 +5771,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
+      <c r="A129" s="1" t="n">
         <v>237</v>
       </c>
       <c r="B129" t="n">
@@ -5821,7 +5821,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
+      <c r="A130" s="1" t="n">
         <v>238</v>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
       <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="n">
+      <c r="A131" s="1" t="n">
         <v>239</v>
       </c>
       <c r="B131" t="n">
@@ -5879,7 +5879,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
+      <c r="A132" s="1" t="n">
         <v>241</v>
       </c>
       <c r="B132" t="n">
@@ -5913,7 +5913,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="n">
+      <c r="A133" s="1" t="n">
         <v>243</v>
       </c>
       <c r="B133" t="n">
@@ -5939,7 +5939,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
+      <c r="A134" s="1" t="n">
         <v>244</v>
       </c>
       <c r="B134" t="n">
@@ -5989,7 +5989,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
+      <c r="A135" s="1" t="n">
         <v>245</v>
       </c>
       <c r="B135" t="n">
@@ -6023,7 +6023,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
+      <c r="A136" s="1" t="n">
         <v>247</v>
       </c>
       <c r="B136" t="n">
@@ -6073,7 +6073,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
+      <c r="A137" s="1" t="n">
         <v>248</v>
       </c>
       <c r="B137" t="n">
@@ -6123,7 +6123,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
+      <c r="A138" s="1" t="n">
         <v>252</v>
       </c>
       <c r="B138" t="n">
@@ -6173,11 +6173,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139" s="1" t="n">
         <v>255</v>
       </c>
       <c r="B139" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="C139" s="2" t="n">
         <v>46131</v>
@@ -6219,11 +6219,11 @@
         <v>46005</v>
       </c>
       <c r="P139" t="n">
-        <v>6.57</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
+      <c r="A140" s="1" t="n">
         <v>256</v>
       </c>
       <c r="B140" t="n">
@@ -6273,7 +6273,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
+      <c r="A141" s="1" t="n">
         <v>258</v>
       </c>
       <c r="B141" t="n">
@@ -6323,7 +6323,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="n">
+      <c r="A142" s="1" t="n">
         <v>259</v>
       </c>
       <c r="B142" t="n">
@@ -6373,7 +6373,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="n">
+      <c r="A143" s="1" t="n">
         <v>260</v>
       </c>
       <c r="B143" t="n">
@@ -6423,7 +6423,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="n">
+      <c r="A144" s="1" t="n">
         <v>261</v>
       </c>
       <c r="B144" t="n">
@@ -6473,7 +6473,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="n">
+      <c r="A145" s="1" t="n">
         <v>263</v>
       </c>
       <c r="B145" t="n">
@@ -6523,7 +6523,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="n">
+      <c r="A146" s="1" t="n">
         <v>265</v>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -6543,7 +6543,7 @@
       <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="n">
+      <c r="A147" s="1" t="n">
         <v>267</v>
       </c>
       <c r="B147" t="n">
@@ -6593,7 +6593,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="n">
+      <c r="A148" s="1" t="n">
         <v>273</v>
       </c>
       <c r="B148" t="n">
@@ -6643,7 +6643,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="n">
+      <c r="A149" s="1" t="n">
         <v>274</v>
       </c>
       <c r="B149" t="n">
@@ -6689,7 +6689,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="n">
+      <c r="A150" s="1" t="n">
         <v>275</v>
       </c>
       <c r="B150" t="n">
@@ -6739,7 +6739,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="n">
+      <c r="A151" s="1" t="n">
         <v>276</v>
       </c>
       <c r="B151" t="n">
@@ -6789,7 +6789,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="n">
+      <c r="A152" s="1" t="n">
         <v>277</v>
       </c>
       <c r="B152" t="n">
@@ -6827,7 +6827,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="n">
+      <c r="A153" s="1" t="n">
         <v>278</v>
       </c>
       <c r="B153" t="n">
@@ -6877,7 +6877,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="n">
+      <c r="A154" s="1" t="n">
         <v>279</v>
       </c>
       <c r="B154" t="n">
@@ -6927,7 +6927,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="n">
+      <c r="A155" s="1" t="n">
         <v>280</v>
       </c>
       <c r="B155" t="n">
@@ -6977,7 +6977,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="n">
+      <c r="A156" s="1" t="n">
         <v>281</v>
       </c>
       <c r="B156" t="n">
@@ -7027,7 +7027,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="n">
+      <c r="A157" s="1" t="n">
         <v>282</v>
       </c>
       <c r="B157" t="n">
@@ -7077,7 +7077,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="n">
+      <c r="A158" s="1" t="n">
         <v>283</v>
       </c>
       <c r="B158" t="n">
@@ -7127,7 +7127,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="n">
+      <c r="A159" s="1" t="n">
         <v>285</v>
       </c>
       <c r="B159" t="n">
@@ -7177,7 +7177,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="n">
+      <c r="A160" s="1" t="n">
         <v>286</v>
       </c>
       <c r="B160" t="n">
@@ -7227,7 +7227,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="n">
+      <c r="A161" s="1" t="n">
         <v>287</v>
       </c>
       <c r="B161" t="n">
@@ -7277,7 +7277,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="n">
+      <c r="A162" s="1" t="n">
         <v>288</v>
       </c>
       <c r="B162" t="n">
@@ -7327,7 +7327,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="n">
+      <c r="A163" s="1" t="n">
         <v>289</v>
       </c>
       <c r="B163" t="n">
@@ -7377,7 +7377,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="n">
+      <c r="A164" s="1" t="n">
         <v>290</v>
       </c>
       <c r="B164" t="n">
@@ -7427,7 +7427,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="n">
+      <c r="A165" s="1" t="n">
         <v>291</v>
       </c>
       <c r="B165" t="n">
@@ -7477,7 +7477,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="n">
+      <c r="A166" s="1" t="n">
         <v>292</v>
       </c>
       <c r="B166" t="n">
@@ -7523,7 +7523,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="n">
+      <c r="A167" s="1" t="n">
         <v>293</v>
       </c>
       <c r="B167" t="n">
@@ -7573,7 +7573,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="n">
+      <c r="A168" s="1" t="n">
         <v>294</v>
       </c>
       <c r="B168" t="n">
@@ -7623,7 +7623,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="n">
+      <c r="A169" s="1" t="n">
         <v>295</v>
       </c>
       <c r="B169" t="n">
@@ -7673,7 +7673,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="n">
+      <c r="A170" s="1" t="n">
         <v>296</v>
       </c>
       <c r="B170" t="n">
@@ -7723,7 +7723,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="n">
+      <c r="A171" s="1" t="n">
         <v>298</v>
       </c>
       <c r="B171" t="n">
@@ -7773,7 +7773,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="n">
+      <c r="A172" s="1" t="n">
         <v>300</v>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -7793,7 +7793,7 @@
       <c r="P172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" t="n">
+      <c r="A173" s="1" t="n">
         <v>301</v>
       </c>
       <c r="B173" t="n">
@@ -7831,7 +7831,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="n">
+      <c r="A174" s="1" t="n">
         <v>302</v>
       </c>
       <c r="B174" t="n">
@@ -7881,7 +7881,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="n">
+      <c r="A175" s="1" t="n">
         <v>303</v>
       </c>
       <c r="B175" t="n">
@@ -7931,7 +7931,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="n">
+      <c r="A176" s="1" t="n">
         <v>305</v>
       </c>
       <c r="B176" t="n">
@@ -7981,7 +7981,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="n">
+      <c r="A177" s="1" t="n">
         <v>306</v>
       </c>
       <c r="B177" t="n">
@@ -8031,107 +8031,107 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="n">
+      <c r="A178" s="1" t="n">
         <v>307</v>
       </c>
       <c r="B178" t="n">
+        <v>6</v>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D178" t="n">
         <v>6.9</v>
       </c>
-      <c r="C178" s="2" t="n">
+      <c r="E178" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="D178" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E178" s="2" t="n">
+      <c r="F178" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G178" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="F178" t="n">
+      <c r="H178" t="n">
         <v>7.2</v>
       </c>
-      <c r="G178" s="2" t="n">
+      <c r="I178" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="H178" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I178" s="2" t="n">
+      <c r="J178" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K178" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="J178" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K178" s="2" t="n">
+      <c r="L178" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M178" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="L178" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M178" s="2" t="n">
+      <c r="N178" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O178" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="N178" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O178" s="2" t="n">
-        <v>45984</v>
-      </c>
       <c r="P178" t="n">
-        <v>6.67</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="n">
+      <c r="A179" s="1" t="n">
         <v>309</v>
       </c>
       <c r="B179" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D179" t="n">
         <v>6.8</v>
       </c>
-      <c r="C179" s="2" t="n">
+      <c r="E179" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="D179" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E179" s="2" t="n">
+      <c r="F179" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G179" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="F179" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G179" s="2" t="n">
+      <c r="H179" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I179" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="H179" t="n">
+      <c r="J179" t="n">
         <v>7.2</v>
       </c>
-      <c r="I179" s="2" t="n">
+      <c r="K179" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="J179" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K179" s="2" t="n">
+      <c r="L179" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M179" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="L179" t="n">
+      <c r="N179" t="n">
         <v>8</v>
       </c>
-      <c r="M179" s="2" t="n">
+      <c r="O179" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="N179" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O179" s="2" t="n">
-        <v>46074</v>
-      </c>
       <c r="P179" t="n">
-        <v>6.93</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="n">
+      <c r="A180" s="1" t="n">
         <v>310</v>
       </c>
       <c r="B180" t="n">
@@ -8181,7 +8181,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="n">
+      <c r="A181" s="1" t="n">
         <v>311</v>
       </c>
       <c r="B181" t="n">
@@ -8231,7 +8231,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="n">
+      <c r="A182" s="1" t="n">
         <v>312</v>
       </c>
       <c r="B182" t="n">
@@ -8281,7 +8281,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="n">
+      <c r="A183" s="1" t="n">
         <v>313</v>
       </c>
       <c r="B183" t="n">
@@ -8323,7 +8323,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="n">
+      <c r="A184" s="1" t="n">
         <v>314</v>
       </c>
       <c r="B184" t="n">
@@ -8373,7 +8373,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="n">
+      <c r="A185" s="1" t="n">
         <v>315</v>
       </c>
       <c r="B185" t="n">
@@ -8423,7 +8423,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="n">
+      <c r="A186" s="1" t="n">
         <v>316</v>
       </c>
       <c r="B186" t="n">
@@ -8469,7 +8469,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="n">
+      <c r="A187" s="1" t="n">
         <v>317</v>
       </c>
       <c r="B187" t="n">
@@ -8519,7 +8519,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="n">
+      <c r="A188" s="1" t="n">
         <v>318</v>
       </c>
       <c r="B188" t="n">
@@ -8569,7 +8569,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="n">
+      <c r="A189" s="1" t="n">
         <v>319</v>
       </c>
       <c r="B189" t="n">
@@ -8619,7 +8619,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="n">
+      <c r="A190" s="1" t="n">
         <v>320</v>
       </c>
       <c r="B190" t="n">
@@ -8665,7 +8665,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="n">
+      <c r="A191" s="1" t="n">
         <v>321</v>
       </c>
       <c r="B191" t="n">
@@ -8715,7 +8715,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="n">
+      <c r="A192" s="1" t="n">
         <v>322</v>
       </c>
       <c r="B192" t="n">
@@ -8765,7 +8765,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="n">
+      <c r="A193" s="1" t="n">
         <v>323</v>
       </c>
       <c r="B193" t="n">
@@ -8815,7 +8815,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="n">
+      <c r="A194" s="1" t="n">
         <v>324</v>
       </c>
       <c r="B194" t="n">
@@ -8865,7 +8865,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="n">
+      <c r="A195" s="1" t="n">
         <v>325</v>
       </c>
       <c r="B195" t="n">
@@ -8895,7 +8895,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="n">
+      <c r="A196" s="1" t="n">
         <v>326</v>
       </c>
       <c r="B196" t="n">
@@ -8945,7 +8945,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="n">
+      <c r="A197" s="1" t="n">
         <v>327</v>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -8965,7 +8965,7 @@
       <c r="P197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" t="n">
+      <c r="A198" s="1" t="n">
         <v>328</v>
       </c>
       <c r="B198" t="n">
@@ -9015,7 +9015,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="n">
+      <c r="A199" s="1" t="n">
         <v>330</v>
       </c>
       <c r="B199" t="n">
@@ -9065,7 +9065,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="n">
+      <c r="A200" s="1" t="n">
         <v>333</v>
       </c>
       <c r="B200" t="n">
@@ -9115,7 +9115,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="n">
+      <c r="A201" s="1" t="n">
         <v>335</v>
       </c>
       <c r="B201" t="n">
@@ -9165,7 +9165,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="n">
+      <c r="A202" s="1" t="n">
         <v>336</v>
       </c>
       <c r="B202" t="n">
@@ -9215,7 +9215,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="n">
+      <c r="A203" s="1" t="n">
         <v>337</v>
       </c>
       <c r="B203" t="n">
@@ -9265,7 +9265,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="n">
+      <c r="A204" s="1" t="n">
         <v>338</v>
       </c>
       <c r="B204" t="n">
@@ -9295,7 +9295,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="n">
+      <c r="A205" s="1" t="n">
         <v>339</v>
       </c>
       <c r="B205" t="n">
@@ -9345,7 +9345,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="n">
+      <c r="A206" s="1" t="n">
         <v>340</v>
       </c>
       <c r="B206" t="n">
@@ -9395,7 +9395,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="n">
+      <c r="A207" s="1" t="n">
         <v>341</v>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -9415,7 +9415,7 @@
       <c r="P207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" t="n">
+      <c r="A208" s="1" t="n">
         <v>342</v>
       </c>
       <c r="B208" t="n">
@@ -9465,7 +9465,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="n">
+      <c r="A209" s="1" t="n">
         <v>343</v>
       </c>
       <c r="B209" t="n">
@@ -9515,7 +9515,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="n">
+      <c r="A210" s="1" t="n">
         <v>344</v>
       </c>
       <c r="B210" t="n">
@@ -9565,7 +9565,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="n">
+      <c r="A211" s="1" t="n">
         <v>345</v>
       </c>
       <c r="B211" t="n">
@@ -9615,7 +9615,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="n">
+      <c r="A212" s="1" t="n">
         <v>346</v>
       </c>
       <c r="B212" t="n">
@@ -9665,7 +9665,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="n">
+      <c r="A213" s="1" t="n">
         <v>347</v>
       </c>
       <c r="B213" t="n">
@@ -9715,7 +9715,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="n">
+      <c r="A214" s="1" t="n">
         <v>348</v>
       </c>
       <c r="B214" t="n">
@@ -9765,7 +9765,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="n">
+      <c r="A215" s="1" t="n">
         <v>349</v>
       </c>
       <c r="B215" t="n">
@@ -9815,7 +9815,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="n">
+      <c r="A216" s="1" t="n">
         <v>350</v>
       </c>
       <c r="B216" t="n">
@@ -9865,7 +9865,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="n">
+      <c r="A217" s="1" t="n">
         <v>351</v>
       </c>
       <c r="B217" t="n">
@@ -9915,7 +9915,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="n">
+      <c r="A218" s="1" t="n">
         <v>352</v>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -9935,7 +9935,7 @@
       <c r="P218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" t="n">
+      <c r="A219" s="1" t="n">
         <v>353</v>
       </c>
       <c r="B219" t="n">
@@ -9985,7 +9985,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="n">
+      <c r="A220" s="1" t="n">
         <v>355</v>
       </c>
       <c r="B220" t="n">
@@ -10011,7 +10011,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="n">
+      <c r="A221" s="1" t="n">
         <v>356</v>
       </c>
       <c r="B221" t="n">
@@ -10057,7 +10057,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="n">
+      <c r="A222" s="1" t="n">
         <v>357</v>
       </c>
       <c r="B222" t="n">
@@ -10107,7 +10107,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="n">
+      <c r="A223" s="1" t="n">
         <v>359</v>
       </c>
       <c r="B223" t="n">
@@ -10157,7 +10157,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="n">
+      <c r="A224" s="1" t="n">
         <v>360</v>
       </c>
       <c r="B224" t="n">
@@ -10207,7 +10207,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="n">
+      <c r="A225" s="1" t="n">
         <v>362</v>
       </c>
       <c r="B225" t="n">
@@ -10257,7 +10257,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="n">
+      <c r="A226" s="1" t="n">
         <v>364</v>
       </c>
       <c r="B226" t="n">
@@ -10283,7 +10283,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="n">
+      <c r="A227" s="1" t="n">
         <v>365</v>
       </c>
       <c r="B227" t="n">
@@ -10333,7 +10333,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="n">
+      <c r="A228" s="1" t="n">
         <v>367</v>
       </c>
       <c r="B228" t="n">
@@ -10383,7 +10383,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="n">
+      <c r="A229" s="1" t="n">
         <v>368</v>
       </c>
       <c r="B229" t="n">
@@ -10433,7 +10433,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="n">
+      <c r="A230" s="1" t="n">
         <v>369</v>
       </c>
       <c r="B230" t="n">
@@ -10483,7 +10483,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="n">
+      <c r="A231" s="1" t="n">
         <v>370</v>
       </c>
       <c r="B231" t="n">
@@ -10533,7 +10533,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="n">
+      <c r="A232" s="1" t="n">
         <v>371</v>
       </c>
       <c r="B232" t="n">
@@ -10583,7 +10583,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="n">
+      <c r="A233" s="1" t="n">
         <v>372</v>
       </c>
       <c r="B233" t="n">
@@ -10633,7 +10633,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="n">
+      <c r="A234" s="1" t="n">
         <v>373</v>
       </c>
       <c r="B234" t="n">
@@ -10683,7 +10683,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="n">
+      <c r="A235" s="1" t="n">
         <v>374</v>
       </c>
       <c r="B235" t="n">
@@ -10721,7 +10721,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="n">
+      <c r="A236" s="1" t="n">
         <v>375</v>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -10741,7 +10741,7 @@
       <c r="P236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" t="n">
+      <c r="A237" s="1" t="n">
         <v>376</v>
       </c>
       <c r="B237" t="n">
@@ -10791,7 +10791,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="n">
+      <c r="A238" s="1" t="n">
         <v>377</v>
       </c>
       <c r="B238" t="inlineStr"/>
@@ -10811,7 +10811,7 @@
       <c r="P238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" t="n">
+      <c r="A239" s="1" t="n">
         <v>378</v>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -10831,7 +10831,7 @@
       <c r="P239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" t="n">
+      <c r="A240" s="1" t="n">
         <v>379</v>
       </c>
       <c r="B240" t="n">
@@ -10881,7 +10881,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="n">
+      <c r="A241" s="1" t="n">
         <v>380</v>
       </c>
       <c r="B241" t="n">
@@ -10931,7 +10931,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="n">
+      <c r="A242" s="1" t="n">
         <v>382</v>
       </c>
       <c r="B242" t="n">
@@ -10981,7 +10981,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="n">
+      <c r="A243" s="1" t="n">
         <v>383</v>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -11001,7 +11001,7 @@
       <c r="P243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" t="n">
+      <c r="A244" s="1" t="n">
         <v>384</v>
       </c>
       <c r="B244" t="n">
@@ -11051,7 +11051,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="n">
+      <c r="A245" s="1" t="n">
         <v>385</v>
       </c>
       <c r="B245" t="n">
@@ -11101,7 +11101,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="n">
+      <c r="A246" s="1" t="n">
         <v>386</v>
       </c>
       <c r="B246" t="n">
@@ -11139,7 +11139,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="n">
+      <c r="A247" s="1" t="n">
         <v>387</v>
       </c>
       <c r="B247" t="inlineStr"/>
@@ -11159,7 +11159,7 @@
       <c r="P247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" t="n">
+      <c r="A248" s="1" t="n">
         <v>389</v>
       </c>
       <c r="B248" t="n">
@@ -11209,7 +11209,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="n">
+      <c r="A249" s="1" t="n">
         <v>390</v>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -11229,7 +11229,7 @@
       <c r="P249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" t="n">
+      <c r="A250" s="1" t="n">
         <v>391</v>
       </c>
       <c r="B250" t="n">
@@ -11279,7 +11279,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="n">
+      <c r="A251" s="1" t="n">
         <v>392</v>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -11299,7 +11299,7 @@
       <c r="P251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" t="n">
+      <c r="A252" s="1" t="n">
         <v>393</v>
       </c>
       <c r="B252" t="n">
@@ -11341,7 +11341,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="n">
+      <c r="A253" s="1" t="n">
         <v>394</v>
       </c>
       <c r="B253" t="n">
@@ -11391,7 +11391,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="n">
+      <c r="A254" s="1" t="n">
         <v>395</v>
       </c>
       <c r="B254" t="n">
@@ -11441,7 +11441,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="n">
+      <c r="A255" s="1" t="n">
         <v>396</v>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -11461,7 +11461,7 @@
       <c r="P255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" t="n">
+      <c r="A256" s="1" t="n">
         <v>397</v>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -11481,7 +11481,7 @@
       <c r="P256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" t="n">
+      <c r="A257" s="1" t="n">
         <v>398</v>
       </c>
       <c r="B257" t="n">
@@ -11531,7 +11531,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="n">
+      <c r="A258" s="1" t="n">
         <v>399</v>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -11551,7 +11551,7 @@
       <c r="P258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" t="n">
+      <c r="A259" s="1" t="n">
         <v>400</v>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -11571,7 +11571,7 @@
       <c r="P259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" t="n">
+      <c r="A260" s="1" t="n">
         <v>401</v>
       </c>
       <c r="B260" t="n">
@@ -11621,7 +11621,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="n">
+      <c r="A261" s="1" t="n">
         <v>402</v>
       </c>
       <c r="B261" t="n">
@@ -11671,7 +11671,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="n">
+      <c r="A262" s="1" t="n">
         <v>403</v>
       </c>
       <c r="B262" t="n">
@@ -11697,7 +11697,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="n">
+      <c r="A263" s="1" t="n">
         <v>404</v>
       </c>
       <c r="B263" t="n">
@@ -11747,7 +11747,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="n">
+      <c r="A264" s="1" t="n">
         <v>405</v>
       </c>
       <c r="B264" t="n">
@@ -11797,7 +11797,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="n">
+      <c r="A265" s="1" t="n">
         <v>406</v>
       </c>
       <c r="B265" t="n">
@@ -11847,7 +11847,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="n">
+      <c r="A266" s="1" t="n">
         <v>407</v>
       </c>
       <c r="B266" t="n">
@@ -11897,7 +11897,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="n">
+      <c r="A267" s="1" t="n">
         <v>408</v>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -11917,7 +11917,7 @@
       <c r="P267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" t="n">
+      <c r="A268" s="1" t="n">
         <v>409</v>
       </c>
       <c r="B268" t="n">
@@ -11967,7 +11967,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="n">
+      <c r="A269" s="1" t="n">
         <v>410</v>
       </c>
       <c r="B269" t="n">
@@ -12017,7 +12017,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="n">
+      <c r="A270" s="1" t="n">
         <v>411</v>
       </c>
       <c r="B270" t="n">
@@ -12067,7 +12067,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="n">
+      <c r="A271" s="1" t="n">
         <v>412</v>
       </c>
       <c r="B271" t="n">
@@ -12117,7 +12117,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="n">
+      <c r="A272" s="1" t="n">
         <v>413</v>
       </c>
       <c r="B272" t="n">
@@ -12163,7 +12163,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="n">
+      <c r="A273" s="1" t="n">
         <v>414</v>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -12183,7 +12183,7 @@
       <c r="P273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" t="n">
+      <c r="A274" s="1" t="n">
         <v>415</v>
       </c>
       <c r="B274" t="n">
@@ -12233,7 +12233,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="n">
+      <c r="A275" s="1" t="n">
         <v>416</v>
       </c>
       <c r="B275" t="n">
@@ -12283,7 +12283,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="n">
+      <c r="A276" s="1" t="n">
         <v>417</v>
       </c>
       <c r="B276" t="n">
@@ -12333,7 +12333,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="n">
+      <c r="A277" s="1" t="n">
         <v>418</v>
       </c>
       <c r="B277" t="n">
@@ -12383,7 +12383,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="n">
+      <c r="A278" s="1" t="n">
         <v>419</v>
       </c>
       <c r="B278" t="n">
@@ -12433,7 +12433,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="n">
+      <c r="A279" s="1" t="n">
         <v>420</v>
       </c>
       <c r="B279" t="n">
@@ -12483,7 +12483,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="n">
+      <c r="A280" s="1" t="n">
         <v>421</v>
       </c>
       <c r="B280" t="n">
@@ -12533,7 +12533,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="n">
+      <c r="A281" s="1" t="n">
         <v>422</v>
       </c>
       <c r="B281" t="n">
@@ -12575,7 +12575,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="n">
+      <c r="A282" s="1" t="n">
         <v>423</v>
       </c>
       <c r="B282" t="n">
@@ -12625,7 +12625,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="n">
+      <c r="A283" s="1" t="n">
         <v>424</v>
       </c>
       <c r="B283" t="n">
@@ -12667,7 +12667,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="n">
+      <c r="A284" s="1" t="n">
         <v>425</v>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -12687,7 +12687,7 @@
       <c r="P284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" t="n">
+      <c r="A285" s="1" t="n">
         <v>426</v>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -12707,7 +12707,7 @@
       <c r="P285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" t="n">
+      <c r="A286" s="1" t="n">
         <v>427</v>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -12727,7 +12727,7 @@
       <c r="P286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" t="n">
+      <c r="A287" s="1" t="n">
         <v>428</v>
       </c>
       <c r="B287" t="n">
@@ -12777,7 +12777,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="n">
+      <c r="A288" s="1" t="n">
         <v>429</v>
       </c>
       <c r="B288" t="n">
@@ -12827,7 +12827,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="n">
+      <c r="A289" s="1" t="n">
         <v>431</v>
       </c>
       <c r="B289" t="n">
@@ -12877,7 +12877,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="n">
+      <c r="A290" s="1" t="n">
         <v>432</v>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -12897,7 +12897,7 @@
       <c r="P290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" t="n">
+      <c r="A291" s="1" t="n">
         <v>434</v>
       </c>
       <c r="B291" t="n">
@@ -12947,7 +12947,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="n">
+      <c r="A292" s="1" t="n">
         <v>435</v>
       </c>
       <c r="B292" t="n">
@@ -12997,7 +12997,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="n">
+      <c r="A293" s="1" t="n">
         <v>436</v>
       </c>
       <c r="B293" t="n">
@@ -13027,7 +13027,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="n">
+      <c r="A294" s="1" t="n">
         <v>437</v>
       </c>
       <c r="B294" t="n">
@@ -13077,7 +13077,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="n">
+      <c r="A295" s="1" t="n">
         <v>438</v>
       </c>
       <c r="B295" t="n">
@@ -13119,7 +13119,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="n">
+      <c r="A296" s="1" t="n">
         <v>439</v>
       </c>
       <c r="B296" t="n">
@@ -13169,7 +13169,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="n">
+      <c r="A297" s="1" t="n">
         <v>441</v>
       </c>
       <c r="B297" t="n">
@@ -13219,7 +13219,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="n">
+      <c r="A298" s="1" t="n">
         <v>442</v>
       </c>
       <c r="B298" t="n">
@@ -13253,7 +13253,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="n">
+      <c r="A299" s="1" t="n">
         <v>443</v>
       </c>
       <c r="B299" t="n">
@@ -13303,7 +13303,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="n">
+      <c r="A300" s="1" t="n">
         <v>445</v>
       </c>
       <c r="B300" t="n">
@@ -13353,7 +13353,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="n">
+      <c r="A301" s="1" t="n">
         <v>446</v>
       </c>
       <c r="B301" t="n">
@@ -13403,7 +13403,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="n">
+      <c r="A302" s="1" t="n">
         <v>447</v>
       </c>
       <c r="B302" t="n">
@@ -13441,7 +13441,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="n">
+      <c r="A303" s="1" t="n">
         <v>448</v>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -13461,7 +13461,7 @@
       <c r="P303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" t="n">
+      <c r="A304" s="1" t="n">
         <v>449</v>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -13481,7 +13481,7 @@
       <c r="P304" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" t="n">
+      <c r="A305" s="1" t="n">
         <v>450</v>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -13501,7 +13501,7 @@
       <c r="P305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" t="n">
+      <c r="A306" s="1" t="n">
         <v>451</v>
       </c>
       <c r="B306" t="n">
@@ -13551,7 +13551,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="n">
+      <c r="A307" s="1" t="n">
         <v>452</v>
       </c>
       <c r="B307" t="n">
@@ -13601,7 +13601,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="n">
+      <c r="A308" s="1" t="n">
         <v>453</v>
       </c>
       <c r="B308" t="n">
@@ -13651,7 +13651,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="n">
+      <c r="A309" s="1" t="n">
         <v>455</v>
       </c>
       <c r="B309" t="n">
@@ -13701,7 +13701,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="n">
+      <c r="A310" s="1" t="n">
         <v>456</v>
       </c>
       <c r="B310" t="n">
@@ -13751,7 +13751,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="n">
+      <c r="A311" s="1" t="n">
         <v>457</v>
       </c>
       <c r="B311" t="n">
@@ -13801,7 +13801,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="n">
+      <c r="A312" s="1" t="n">
         <v>458</v>
       </c>
       <c r="B312" t="n">
@@ -13851,7 +13851,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="n">
+      <c r="A313" s="1" t="n">
         <v>459</v>
       </c>
       <c r="B313" t="n">
@@ -13901,7 +13901,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="n">
+      <c r="A314" s="1" t="n">
         <v>460</v>
       </c>
       <c r="B314" t="n">
@@ -13927,7 +13927,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="n">
+      <c r="A315" s="1" t="n">
         <v>461</v>
       </c>
       <c r="B315" t="n">
@@ -13977,7 +13977,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="n">
+      <c r="A316" s="1" t="n">
         <v>462</v>
       </c>
       <c r="B316" t="n">
@@ -14027,7 +14027,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="n">
+      <c r="A317" s="1" t="n">
         <v>463</v>
       </c>
       <c r="B317" t="n">
@@ -14077,7 +14077,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="n">
+      <c r="A318" s="1" t="n">
         <v>464</v>
       </c>
       <c r="B318" t="n">
@@ -14127,7 +14127,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="n">
+      <c r="A319" s="1" t="n">
         <v>465</v>
       </c>
       <c r="B319" t="n">
@@ -14177,107 +14177,107 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="n">
+      <c r="A320" s="1" t="n">
         <v>466</v>
       </c>
       <c r="B320" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C320" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D320" t="n">
         <v>7.9</v>
       </c>
-      <c r="C320" s="2" t="n">
+      <c r="E320" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="D320" t="n">
+      <c r="F320" t="n">
         <v>6.2</v>
       </c>
-      <c r="E320" s="2" t="n">
+      <c r="G320" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F320" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G320" s="2" t="n">
+      <c r="H320" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I320" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H320" t="n">
+      <c r="J320" t="n">
         <v>7</v>
       </c>
-      <c r="I320" s="2" t="n">
+      <c r="K320" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="J320" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K320" s="2" t="n">
+      <c r="L320" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M320" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L320" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M320" s="2" t="n">
+      <c r="N320" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O320" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N320" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O320" s="2" t="n">
-        <v>46069</v>
-      </c>
       <c r="P320" t="n">
-        <v>6.77</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="n">
+      <c r="A321" s="1" t="n">
         <v>467</v>
       </c>
       <c r="B321" t="n">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C321" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D321" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E321" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="D321" t="n">
+      <c r="F321" t="n">
         <v>7.2</v>
       </c>
-      <c r="E321" s="2" t="n">
+      <c r="G321" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="F321" t="n">
+      <c r="H321" t="n">
         <v>6.4</v>
       </c>
-      <c r="G321" s="2" t="n">
+      <c r="I321" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="H321" t="n">
+      <c r="J321" t="n">
         <v>7.5</v>
       </c>
-      <c r="I321" s="2" t="n">
+      <c r="K321" s="2" t="n">
         <v>46087</v>
-      </c>
-      <c r="J321" t="n">
-        <v>7</v>
-      </c>
-      <c r="K321" s="2" t="n">
-        <v>46081</v>
       </c>
       <c r="L321" t="n">
         <v>7</v>
       </c>
       <c r="M321" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="N321" t="n">
+        <v>7</v>
+      </c>
+      <c r="O321" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N321" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O321" s="2" t="n">
-        <v>46068</v>
-      </c>
       <c r="P321" t="n">
-        <v>7.19</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="n">
+      <c r="A322" s="1" t="n">
         <v>468</v>
       </c>
       <c r="B322" t="n">
@@ -14327,57 +14327,57 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="n">
+      <c r="A323" s="1" t="n">
         <v>469</v>
       </c>
       <c r="B323" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C323" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D323" t="n">
         <v>6.9</v>
       </c>
-      <c r="C323" s="2" t="n">
+      <c r="E323" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="D323" t="n">
+      <c r="F323" t="n">
         <v>6.8</v>
       </c>
-      <c r="E323" s="2" t="n">
+      <c r="G323" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="F323" t="n">
+      <c r="H323" t="n">
         <v>6.1</v>
       </c>
-      <c r="G323" s="2" t="n">
+      <c r="I323" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="H323" t="n">
+      <c r="J323" t="n">
         <v>6.8</v>
       </c>
-      <c r="I323" s="2" t="n">
+      <c r="K323" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="J323" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K323" s="2" t="n">
+      <c r="L323" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M323" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="L323" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M323" s="2" t="n">
+      <c r="N323" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O323" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="N323" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O323" s="2" t="n">
-        <v>46059</v>
-      </c>
       <c r="P323" t="n">
-        <v>6.69</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="n">
+      <c r="A324" s="1" t="n">
         <v>470</v>
       </c>
       <c r="B324" t="n">
@@ -14427,7 +14427,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="n">
+      <c r="A325" s="1" t="n">
         <v>471</v>
       </c>
       <c r="B325" t="n">
@@ -14477,7 +14477,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="n">
+      <c r="A326" s="1" t="n">
         <v>472</v>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -14497,7 +14497,7 @@
       <c r="P326" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" t="n">
+      <c r="A327" s="1" t="n">
         <v>473</v>
       </c>
       <c r="B327" t="n">
@@ -14547,7 +14547,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="n">
+      <c r="A328" s="1" t="n">
         <v>474</v>
       </c>
       <c r="B328" t="n">
@@ -14581,7 +14581,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="n">
+      <c r="A329" s="1" t="n">
         <v>475</v>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -14601,7 +14601,7 @@
       <c r="P329" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" t="n">
+      <c r="A330" s="1" t="n">
         <v>476</v>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -14621,7 +14621,7 @@
       <c r="P330" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" t="n">
+      <c r="A331" s="1" t="n">
         <v>477</v>
       </c>
       <c r="B331" t="inlineStr"/>
@@ -14641,7 +14641,7 @@
       <c r="P331" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" t="n">
+      <c r="A332" s="1" t="n">
         <v>478</v>
       </c>
       <c r="B332" t="n">
@@ -14675,7 +14675,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="n">
+      <c r="A333" s="1" t="n">
         <v>479</v>
       </c>
       <c r="B333" t="n">
@@ -14725,7 +14725,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="n">
+      <c r="A334" s="1" t="n">
         <v>480</v>
       </c>
       <c r="B334" t="n">
@@ -14775,7 +14775,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="n">
+      <c r="A335" s="1" t="n">
         <v>481</v>
       </c>
       <c r="B335" t="n">
@@ -14825,7 +14825,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="n">
+      <c r="A336" s="1" t="n">
         <v>482</v>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -14845,7 +14845,7 @@
       <c r="P336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" t="n">
+      <c r="A337" s="1" t="n">
         <v>483</v>
       </c>
       <c r="B337" t="n">
@@ -14895,7 +14895,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="n">
+      <c r="A338" s="1" t="n">
         <v>484</v>
       </c>
       <c r="B338" t="n">
@@ -14945,7 +14945,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="n">
+      <c r="A339" s="1" t="n">
         <v>485</v>
       </c>
       <c r="B339" t="n">
@@ -14995,7 +14995,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="n">
+      <c r="A340" s="1" t="n">
         <v>486</v>
       </c>
       <c r="B340" t="n">
@@ -15045,7 +15045,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="n">
+      <c r="A341" s="1" t="n">
         <v>487</v>
       </c>
       <c r="B341" t="n">
@@ -15095,7 +15095,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="n">
+      <c r="A342" s="1" t="n">
         <v>488</v>
       </c>
       <c r="B342" t="n">
@@ -15145,7 +15145,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="n">
+      <c r="A343" s="1" t="n">
         <v>489</v>
       </c>
       <c r="B343" t="n">
@@ -15195,7 +15195,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="n">
+      <c r="A344" s="1" t="n">
         <v>490</v>
       </c>
       <c r="B344" t="n">
@@ -15245,7 +15245,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="n">
+      <c r="A345" s="1" t="n">
         <v>491</v>
       </c>
       <c r="B345" t="n">
@@ -15295,57 +15295,57 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="n">
+      <c r="A346" s="1" t="n">
         <v>492</v>
       </c>
       <c r="B346" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C346" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D346" t="n">
         <v>6.9</v>
       </c>
-      <c r="C346" s="2" t="n">
+      <c r="E346" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="D346" t="n">
+      <c r="F346" t="n">
         <v>7.2</v>
       </c>
-      <c r="E346" s="2" t="n">
+      <c r="G346" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F346" t="n">
+      <c r="H346" t="n">
         <v>7.6</v>
       </c>
-      <c r="G346" s="2" t="n">
+      <c r="I346" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H346" t="n">
+      <c r="J346" t="n">
         <v>5.8</v>
       </c>
-      <c r="I346" s="2" t="n">
+      <c r="K346" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J346" t="n">
+      <c r="L346" t="n">
         <v>6.9</v>
       </c>
-      <c r="K346" s="2" t="n">
+      <c r="M346" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L346" t="n">
+      <c r="N346" t="n">
         <v>6</v>
       </c>
-      <c r="M346" s="2" t="n">
+      <c r="O346" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="N346" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O346" s="2" t="n">
-        <v>46081</v>
-      </c>
       <c r="P346" t="n">
-        <v>6.71</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="n">
+      <c r="A347" s="1" t="n">
         <v>493</v>
       </c>
       <c r="B347" t="n">
@@ -15395,7 +15395,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="n">
+      <c r="A348" s="1" t="n">
         <v>494</v>
       </c>
       <c r="B348" t="n">
@@ -15445,7 +15445,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="n">
+      <c r="A349" s="1" t="n">
         <v>495</v>
       </c>
       <c r="B349" t="n">
@@ -15495,7 +15495,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="n">
+      <c r="A350" s="1" t="n">
         <v>496</v>
       </c>
       <c r="B350" t="n">
@@ -15533,7 +15533,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="n">
+      <c r="A351" s="1" t="n">
         <v>498</v>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -15553,7 +15553,7 @@
       <c r="P351" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" t="n">
+      <c r="A352" s="1" t="n">
         <v>499</v>
       </c>
       <c r="B352" t="n">
@@ -15603,7 +15603,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="n">
+      <c r="A353" s="1" t="n">
         <v>500</v>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -15623,7 +15623,7 @@
       <c r="P353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" t="n">
+      <c r="A354" s="1" t="n">
         <v>501</v>
       </c>
       <c r="B354" t="n">
@@ -15673,7 +15673,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="n">
+      <c r="A355" s="1" t="n">
         <v>502</v>
       </c>
       <c r="B355" t="n">
@@ -15723,7 +15723,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="n">
+      <c r="A356" s="1" t="n">
         <v>503</v>
       </c>
       <c r="B356" t="n">
@@ -15757,7 +15757,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="n">
+      <c r="A357" s="1" t="n">
         <v>504</v>
       </c>
       <c r="B357" t="n">
@@ -15795,7 +15795,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="n">
+      <c r="A358" s="1" t="n">
         <v>505</v>
       </c>
       <c r="B358" t="n">
@@ -15845,7 +15845,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="n">
+      <c r="A359" s="1" t="n">
         <v>506</v>
       </c>
       <c r="B359" t="n">
@@ -15871,57 +15871,57 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="n">
+      <c r="A360" s="1" t="n">
         <v>507</v>
       </c>
       <c r="B360" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C360" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D360" t="n">
         <v>7.6</v>
       </c>
-      <c r="C360" s="2" t="n">
+      <c r="E360" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="D360" t="n">
+      <c r="F360" t="n">
         <v>6.3</v>
       </c>
-      <c r="E360" s="2" t="n">
+      <c r="G360" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="F360" t="n">
+      <c r="H360" t="n">
         <v>6.8</v>
       </c>
-      <c r="G360" s="2" t="n">
+      <c r="I360" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="H360" t="n">
+      <c r="J360" t="n">
         <v>6.3</v>
       </c>
-      <c r="I360" s="2" t="n">
+      <c r="K360" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J360" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K360" s="2" t="n">
+      <c r="L360" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M360" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="L360" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M360" s="2" t="n">
+      <c r="N360" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O360" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="N360" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O360" s="2" t="n">
-        <v>46081</v>
-      </c>
       <c r="P360" t="n">
-        <v>6.67</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="n">
+      <c r="A361" s="1" t="n">
         <v>508</v>
       </c>
       <c r="B361" t="n">
@@ -15971,7 +15971,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="n">
+      <c r="A362" s="1" t="n">
         <v>509</v>
       </c>
       <c r="B362" t="n">
@@ -16021,57 +16021,57 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="n">
+      <c r="A363" s="1" t="n">
         <v>510</v>
       </c>
       <c r="B363" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C363" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D363" t="n">
         <v>7.2</v>
       </c>
-      <c r="C363" s="2" t="n">
+      <c r="E363" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="D363" t="n">
+      <c r="F363" t="n">
         <v>7</v>
       </c>
-      <c r="E363" s="2" t="n">
+      <c r="G363" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F363" t="n">
+      <c r="H363" t="n">
         <v>6.9</v>
       </c>
-      <c r="G363" s="2" t="n">
+      <c r="I363" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="H363" t="n">
+      <c r="J363" t="n">
         <v>6.4</v>
       </c>
-      <c r="I363" s="2" t="n">
+      <c r="K363" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J363" t="n">
+      <c r="L363" t="n">
         <v>6.1</v>
       </c>
-      <c r="K363" s="2" t="n">
+      <c r="M363" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="L363" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M363" s="2" t="n">
+      <c r="N363" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O363" s="2" t="n">
         <v>46088</v>
-      </c>
-      <c r="N363" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O363" s="2" t="n">
-        <v>46082</v>
       </c>
       <c r="P363" t="n">
         <v>6.73</v>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="n">
+      <c r="A364" s="1" t="n">
         <v>511</v>
       </c>
       <c r="B364" t="n">
@@ -16105,7 +16105,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="n">
+      <c r="A365" s="1" t="n">
         <v>512</v>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -16125,7 +16125,7 @@
       <c r="P365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" t="n">
+      <c r="A366" s="1" t="n">
         <v>513</v>
       </c>
       <c r="B366" t="n">
@@ -16175,7 +16175,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="n">
+      <c r="A367" s="1" t="n">
         <v>514</v>
       </c>
       <c r="B367" t="n">
@@ -16225,7 +16225,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="n">
+      <c r="A368" s="1" t="n">
         <v>515</v>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -16245,7 +16245,7 @@
       <c r="P368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" t="n">
+      <c r="A369" s="1" t="n">
         <v>516</v>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -16265,7 +16265,7 @@
       <c r="P369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" t="n">
+      <c r="A370" s="1" t="n">
         <v>517</v>
       </c>
       <c r="B370" t="n">
@@ -16291,7 +16291,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="n">
+      <c r="A371" s="1" t="n">
         <v>518</v>
       </c>
       <c r="B371" t="n">
@@ -16333,7 +16333,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="n">
+      <c r="A372" s="1" t="n">
         <v>519</v>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -16353,7 +16353,7 @@
       <c r="P372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" t="n">
+      <c r="A373" s="1" t="n">
         <v>520</v>
       </c>
       <c r="B373" t="n">
@@ -16403,7 +16403,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="n">
+      <c r="A374" s="1" t="n">
         <v>521</v>
       </c>
       <c r="B374" t="n">
@@ -16453,7 +16453,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="n">
+      <c r="A375" s="1" t="n">
         <v>522</v>
       </c>
       <c r="B375" t="n">
@@ -16495,7 +16495,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="n">
+      <c r="A376" s="1" t="n">
         <v>523</v>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -16515,7 +16515,7 @@
       <c r="P376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" t="n">
+      <c r="A377" s="1" t="n">
         <v>524</v>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -16535,7 +16535,7 @@
       <c r="P377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" t="n">
+      <c r="A378" s="1" t="n">
         <v>525</v>
       </c>
       <c r="B378" t="n">
@@ -16581,7 +16581,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="n">
+      <c r="A379" s="1" t="n">
         <v>526</v>
       </c>
       <c r="B379" t="n">
@@ -16619,7 +16619,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="n">
+      <c r="A380" s="1" t="n">
         <v>527</v>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -16639,7 +16639,7 @@
       <c r="P380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" t="n">
+      <c r="A381" s="1" t="n">
         <v>528</v>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -16659,7 +16659,7 @@
       <c r="P381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" t="n">
+      <c r="A382" s="1" t="n">
         <v>529</v>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -16679,7 +16679,7 @@
       <c r="P382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" t="n">
+      <c r="A383" s="1" t="n">
         <v>530</v>
       </c>
       <c r="B383" t="n">
@@ -16721,7 +16721,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="n">
+      <c r="A384" s="1" t="n">
         <v>531</v>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -16741,7 +16741,7 @@
       <c r="P384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" t="n">
+      <c r="A385" s="1" t="n">
         <v>533</v>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -16761,7 +16761,7 @@
       <c r="P385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" t="n">
+      <c r="A386" s="1" t="n">
         <v>534</v>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -16781,7 +16781,7 @@
       <c r="P386" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" t="n">
+      <c r="A387" s="1" t="n">
         <v>535</v>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -16801,7 +16801,7 @@
       <c r="P387" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" t="n">
+      <c r="A388" s="1" t="n">
         <v>536</v>
       </c>
       <c r="B388" t="inlineStr"/>
@@ -16821,7 +16821,7 @@
       <c r="P388" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" t="n">
+      <c r="A389" s="1" t="n">
         <v>537</v>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -16841,7 +16841,7 @@
       <c r="P389" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" t="n">
+      <c r="A390" s="1" t="n">
         <v>538</v>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -16861,7 +16861,7 @@
       <c r="P390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" t="n">
+      <c r="A391" s="1" t="n">
         <v>539</v>
       </c>
       <c r="B391" t="inlineStr"/>
@@ -16881,7 +16881,7 @@
       <c r="P391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" t="n">
+      <c r="A392" s="1" t="n">
         <v>540</v>
       </c>
       <c r="B392" t="n">
@@ -16931,7 +16931,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="n">
+      <c r="A393" s="1" t="n">
         <v>541</v>
       </c>
       <c r="B393" t="n">
@@ -16981,7 +16981,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="n">
+      <c r="A394" s="1" t="n">
         <v>542</v>
       </c>
       <c r="B394" t="inlineStr"/>
@@ -17001,7 +17001,7 @@
       <c r="P394" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" t="n">
+      <c r="A395" s="1" t="n">
         <v>543</v>
       </c>
       <c r="B395" t="n">
@@ -17051,7 +17051,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="n">
+      <c r="A396" s="1" t="n">
         <v>544</v>
       </c>
       <c r="B396" t="n">
@@ -17101,7 +17101,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="n">
+      <c r="A397" s="1" t="n">
         <v>545</v>
       </c>
       <c r="B397" t="n">
@@ -17151,7 +17151,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="n">
+      <c r="A398" s="1" t="n">
         <v>546</v>
       </c>
       <c r="B398" t="n">
@@ -17201,7 +17201,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="n">
+      <c r="A399" s="1" t="n">
         <v>547</v>
       </c>
       <c r="B399" t="n">
@@ -17231,7 +17231,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="n">
+      <c r="A400" s="1" t="n">
         <v>548</v>
       </c>
       <c r="B400" t="n">
@@ -17281,7 +17281,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="n">
+      <c r="A401" s="1" t="n">
         <v>549</v>
       </c>
       <c r="B401" t="n">
@@ -17331,7 +17331,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="n">
+      <c r="A402" s="1" t="n">
         <v>550</v>
       </c>
       <c r="B402" t="n">
@@ -17381,7 +17381,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="n">
+      <c r="A403" s="1" t="n">
         <v>551</v>
       </c>
       <c r="B403" t="n">
@@ -17431,7 +17431,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="n">
+      <c r="A404" s="1" t="n">
         <v>552</v>
       </c>
       <c r="B404" t="n">
@@ -17481,7 +17481,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="n">
+      <c r="A405" s="1" t="n">
         <v>553</v>
       </c>
       <c r="B405" t="n">
@@ -17527,7 +17527,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="n">
+      <c r="A406" s="1" t="n">
         <v>554</v>
       </c>
       <c r="B406" t="n">
@@ -17577,7 +17577,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="n">
+      <c r="A407" s="1" t="n">
         <v>555</v>
       </c>
       <c r="B407" t="n">
@@ -17627,7 +17627,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="n">
+      <c r="A408" s="1" t="n">
         <v>556</v>
       </c>
       <c r="B408" t="n">
@@ -17677,7 +17677,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="n">
+      <c r="A409" s="1" t="n">
         <v>557</v>
       </c>
       <c r="B409" t="n">
@@ -17727,7 +17727,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="n">
+      <c r="A410" s="1" t="n">
         <v>558</v>
       </c>
       <c r="B410" t="n">
@@ -17777,7 +17777,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="n">
+      <c r="A411" s="1" t="n">
         <v>559</v>
       </c>
       <c r="B411" t="n">
@@ -17827,7 +17827,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="n">
+      <c r="A412" s="1" t="n">
         <v>560</v>
       </c>
       <c r="B412" t="n">
@@ -17877,7 +17877,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="n">
+      <c r="A413" s="1" t="n">
         <v>561</v>
       </c>
       <c r="B413" t="n">
@@ -17923,7 +17923,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="n">
+      <c r="A414" s="1" t="n">
         <v>562</v>
       </c>
       <c r="B414" t="n">
@@ -17961,7 +17961,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="n">
+      <c r="A415" s="1" t="n">
         <v>563</v>
       </c>
       <c r="B415" t="n">
@@ -18011,7 +18011,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="n">
+      <c r="A416" s="1" t="n">
         <v>564</v>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -18031,7 +18031,7 @@
       <c r="P416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" t="n">
+      <c r="A417" s="1" t="n">
         <v>565</v>
       </c>
       <c r="B417" t="n">
@@ -18081,7 +18081,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="n">
+      <c r="A418" s="1" t="n">
         <v>566</v>
       </c>
       <c r="B418" t="n">
@@ -18119,7 +18119,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="n">
+      <c r="A419" s="1" t="n">
         <v>567</v>
       </c>
       <c r="B419" t="n">
@@ -18169,7 +18169,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="n">
+      <c r="A420" s="1" t="n">
         <v>568</v>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -18189,7 +18189,7 @@
       <c r="P420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" t="n">
+      <c r="A421" s="1" t="n">
         <v>569</v>
       </c>
       <c r="B421" t="n">
@@ -18235,7 +18235,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="n">
+      <c r="A422" s="1" t="n">
         <v>571</v>
       </c>
       <c r="B422" t="n">
@@ -18285,7 +18285,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="n">
+      <c r="A423" s="1" t="n">
         <v>573</v>
       </c>
       <c r="B423" t="n">
@@ -18335,57 +18335,57 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="n">
+      <c r="A424" s="1" t="n">
         <v>574</v>
       </c>
       <c r="B424" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="C424" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="D424" t="n">
         <v>6.1</v>
       </c>
-      <c r="C424" s="2" t="n">
+      <c r="E424" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="D424" t="n">
+      <c r="F424" t="n">
         <v>6.8</v>
       </c>
-      <c r="E424" s="2" t="n">
+      <c r="G424" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="F424" t="n">
+      <c r="H424" t="n">
         <v>7.2</v>
       </c>
-      <c r="G424" s="2" t="n">
+      <c r="I424" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="H424" t="n">
+      <c r="J424" t="n">
         <v>7</v>
       </c>
-      <c r="I424" s="2" t="n">
+      <c r="K424" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="J424" t="n">
+      <c r="L424" t="n">
         <v>6.4</v>
       </c>
-      <c r="K424" s="2" t="n">
+      <c r="M424" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="L424" t="n">
+      <c r="N424" t="n">
         <v>7.5</v>
       </c>
-      <c r="M424" s="2" t="n">
+      <c r="O424" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="N424" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O424" s="2" t="n">
-        <v>45983</v>
-      </c>
       <c r="P424" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="n">
+      <c r="A425" s="1" t="n">
         <v>575</v>
       </c>
       <c r="B425" t="n">
@@ -18431,7 +18431,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="n">
+      <c r="A426" s="1" t="n">
         <v>576</v>
       </c>
       <c r="B426" t="n">
@@ -18481,7 +18481,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="n">
+      <c r="A427" s="1" t="n">
         <v>577</v>
       </c>
       <c r="B427" t="n">
@@ -18531,7 +18531,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="n">
+      <c r="A428" s="1" t="n">
         <v>578</v>
       </c>
       <c r="B428" t="n">
@@ -18581,7 +18581,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="n">
+      <c r="A429" s="1" t="n">
         <v>579</v>
       </c>
       <c r="B429" t="n">
@@ -18631,7 +18631,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="n">
+      <c r="A430" s="1" t="n">
         <v>580</v>
       </c>
       <c r="B430" t="n">
@@ -18681,7 +18681,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="n">
+      <c r="A431" s="1" t="n">
         <v>582</v>
       </c>
       <c r="B431" t="n">
@@ -18731,7 +18731,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="n">
+      <c r="A432" s="1" t="n">
         <v>583</v>
       </c>
       <c r="B432" t="n">
@@ -18773,7 +18773,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="n">
+      <c r="A433" s="1" t="n">
         <v>584</v>
       </c>
       <c r="B433" t="n">
@@ -18823,7 +18823,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="n">
+      <c r="A434" s="1" t="n">
         <v>585</v>
       </c>
       <c r="B434" t="n">
@@ -18869,7 +18869,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="n">
+      <c r="A435" s="1" t="n">
         <v>586</v>
       </c>
       <c r="B435" t="n">
@@ -18919,7 +18919,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="n">
+      <c r="A436" s="1" t="n">
         <v>587</v>
       </c>
       <c r="B436" t="n">
@@ -18969,7 +18969,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="n">
+      <c r="A437" s="1" t="n">
         <v>588</v>
       </c>
       <c r="B437" t="n">
@@ -19019,7 +19019,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="n">
+      <c r="A438" s="1" t="n">
         <v>589</v>
       </c>
       <c r="B438" t="n">
@@ -19069,7 +19069,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="n">
+      <c r="A439" s="1" t="n">
         <v>590</v>
       </c>
       <c r="B439" t="n">
@@ -19119,7 +19119,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="n">
+      <c r="A440" s="1" t="n">
         <v>591</v>
       </c>
       <c r="B440" t="n">
@@ -19169,7 +19169,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="n">
+      <c r="A441" s="1" t="n">
         <v>592</v>
       </c>
       <c r="B441" t="n">
@@ -19219,7 +19219,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="n">
+      <c r="A442" s="1" t="n">
         <v>593</v>
       </c>
       <c r="B442" t="n">
@@ -19269,7 +19269,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="n">
+      <c r="A443" s="1" t="n">
         <v>594</v>
       </c>
       <c r="B443" t="n">
@@ -19319,7 +19319,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="n">
+      <c r="A444" s="1" t="n">
         <v>595</v>
       </c>
       <c r="B444" t="n">
@@ -19369,7 +19369,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="n">
+      <c r="A445" s="1" t="n">
         <v>596</v>
       </c>
       <c r="B445" t="n">
@@ -19419,7 +19419,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="n">
+      <c r="A446" s="1" t="n">
         <v>597</v>
       </c>
       <c r="B446" t="n">
@@ -19469,7 +19469,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="n">
+      <c r="A447" s="1" t="n">
         <v>598</v>
       </c>
       <c r="B447" t="n">
@@ -19519,7 +19519,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="n">
+      <c r="A448" s="1" t="n">
         <v>599</v>
       </c>
       <c r="B448" t="n">
@@ -19545,7 +19545,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="n">
+      <c r="A449" s="1" t="n">
         <v>600</v>
       </c>
       <c r="B449" t="n">
@@ -19595,7 +19595,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="n">
+      <c r="A450" s="1" t="n">
         <v>601</v>
       </c>
       <c r="B450" t="n">
@@ -19645,7 +19645,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="n">
+      <c r="A451" s="1" t="n">
         <v>602</v>
       </c>
       <c r="B451" t="n">
@@ -19687,7 +19687,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="n">
+      <c r="A452" s="1" t="n">
         <v>603</v>
       </c>
       <c r="B452" t="n">
@@ -19737,7 +19737,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="n">
+      <c r="A453" s="1" t="n">
         <v>604</v>
       </c>
       <c r="B453" t="n">
@@ -19787,7 +19787,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="n">
+      <c r="A454" s="1" t="n">
         <v>605</v>
       </c>
       <c r="B454" t="inlineStr"/>
@@ -19807,7 +19807,7 @@
       <c r="P454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" t="n">
+      <c r="A455" s="1" t="n">
         <v>606</v>
       </c>
       <c r="B455" t="n">
@@ -19857,7 +19857,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="n">
+      <c r="A456" s="1" t="n">
         <v>607</v>
       </c>
       <c r="B456" t="n">
@@ -19907,7 +19907,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="n">
+      <c r="A457" s="1" t="n">
         <v>608</v>
       </c>
       <c r="B457" t="n">
@@ -19957,7 +19957,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="n">
+      <c r="A458" s="1" t="n">
         <v>609</v>
       </c>
       <c r="B458" t="n">
@@ -20007,7 +20007,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="n">
+      <c r="A459" s="1" t="n">
         <v>610</v>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -20027,57 +20027,57 @@
       <c r="P459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" t="n">
+      <c r="A460" s="1" t="n">
         <v>611</v>
       </c>
       <c r="B460" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C460" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D460" t="n">
         <v>7.1</v>
       </c>
-      <c r="C460" s="2" t="n">
+      <c r="E460" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="D460" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E460" s="2" t="n">
+      <c r="F460" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G460" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="F460" t="n">
+      <c r="H460" t="n">
         <v>7.1</v>
       </c>
-      <c r="G460" s="2" t="n">
+      <c r="I460" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="H460" t="n">
+      <c r="J460" t="n">
         <v>7.2</v>
       </c>
-      <c r="I460" s="2" t="n">
+      <c r="K460" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="J460" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K460" s="2" t="n">
+      <c r="L460" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M460" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L460" t="n">
+      <c r="N460" t="n">
         <v>7</v>
       </c>
-      <c r="M460" s="2" t="n">
+      <c r="O460" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="N460" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O460" s="2" t="n">
-        <v>46082</v>
-      </c>
       <c r="P460" t="n">
-        <v>6.87</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="n">
+      <c r="A461" s="1" t="n">
         <v>612</v>
       </c>
       <c r="B461" t="n">
@@ -20127,7 +20127,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="n">
+      <c r="A462" s="1" t="n">
         <v>613</v>
       </c>
       <c r="B462" t="n">
@@ -20177,7 +20177,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="n">
+      <c r="A463" s="1" t="n">
         <v>614</v>
       </c>
       <c r="B463" t="n">
@@ -20227,7 +20227,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="n">
+      <c r="A464" s="1" t="n">
         <v>615</v>
       </c>
       <c r="B464" t="n">
@@ -20277,7 +20277,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="n">
+      <c r="A465" s="1" t="n">
         <v>617</v>
       </c>
       <c r="B465" t="n">
@@ -20327,7 +20327,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="n">
+      <c r="A466" s="1" t="n">
         <v>618</v>
       </c>
       <c r="B466" t="n">
@@ -20377,7 +20377,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="n">
+      <c r="A467" s="1" t="n">
         <v>619</v>
       </c>
       <c r="B467" t="n">
@@ -20427,7 +20427,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="n">
+      <c r="A468" s="1" t="n">
         <v>620</v>
       </c>
       <c r="B468" t="n">
@@ -20477,7 +20477,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="n">
+      <c r="A469" s="1" t="n">
         <v>621</v>
       </c>
       <c r="B469" t="n">
@@ -20527,7 +20527,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="n">
+      <c r="A470" s="1" t="n">
         <v>622</v>
       </c>
       <c r="B470" t="n">
@@ -20577,7 +20577,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="n">
+      <c r="A471" s="1" t="n">
         <v>623</v>
       </c>
       <c r="B471" t="n">
@@ -20627,7 +20627,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="n">
+      <c r="A472" s="1" t="n">
         <v>624</v>
       </c>
       <c r="B472" t="n">
@@ -20677,7 +20677,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="n">
+      <c r="A473" s="1" t="n">
         <v>625</v>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -20697,7 +20697,7 @@
       <c r="P473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" t="n">
+      <c r="A474" s="1" t="n">
         <v>626</v>
       </c>
       <c r="B474" t="n">
@@ -20747,7 +20747,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="n">
+      <c r="A475" s="1" t="n">
         <v>627</v>
       </c>
       <c r="B475" t="n">
@@ -20797,7 +20797,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="n">
+      <c r="A476" s="1" t="n">
         <v>628</v>
       </c>
       <c r="B476" t="n">
@@ -20847,7 +20847,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="n">
+      <c r="A477" s="1" t="n">
         <v>629</v>
       </c>
       <c r="B477" t="n">
@@ -20897,7 +20897,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="n">
+      <c r="A478" s="1" t="n">
         <v>630</v>
       </c>
       <c r="B478" t="n">
@@ -20939,7 +20939,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="n">
+      <c r="A479" s="1" t="n">
         <v>631</v>
       </c>
       <c r="B479" t="n">
@@ -20989,7 +20989,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="n">
+      <c r="A480" s="1" t="n">
         <v>632</v>
       </c>
       <c r="B480" t="n">
@@ -21039,7 +21039,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="n">
+      <c r="A481" s="1" t="n">
         <v>633</v>
       </c>
       <c r="B481" t="n">
@@ -21089,7 +21089,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="n">
+      <c r="A482" s="1" t="n">
         <v>634</v>
       </c>
       <c r="B482" t="n">
@@ -21131,7 +21131,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="n">
+      <c r="A483" s="1" t="n">
         <v>635</v>
       </c>
       <c r="B483" t="n">
@@ -21181,7 +21181,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="n">
+      <c r="A484" s="1" t="n">
         <v>636</v>
       </c>
       <c r="B484" t="n">
@@ -21211,7 +21211,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="n">
+      <c r="A485" s="1" t="n">
         <v>637</v>
       </c>
       <c r="B485" t="n">
@@ -21261,7 +21261,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="n">
+      <c r="A486" s="1" t="n">
         <v>638</v>
       </c>
       <c r="B486" t="n">
@@ -21311,7 +21311,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="n">
+      <c r="A487" s="1" t="n">
         <v>639</v>
       </c>
       <c r="B487" t="n">
@@ -21361,7 +21361,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="n">
+      <c r="A488" s="1" t="n">
         <v>640</v>
       </c>
       <c r="B488" t="n">
@@ -21411,7 +21411,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="n">
+      <c r="A489" s="1" t="n">
         <v>641</v>
       </c>
       <c r="B489" t="n">
@@ -21461,7 +21461,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="n">
+      <c r="A490" s="1" t="n">
         <v>642</v>
       </c>
       <c r="B490" t="n">
@@ -21511,7 +21511,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="n">
+      <c r="A491" s="1" t="n">
         <v>643</v>
       </c>
       <c r="B491" t="n">
@@ -21561,7 +21561,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="n">
+      <c r="A492" s="1" t="n">
         <v>644</v>
       </c>
       <c r="B492" t="n">
@@ -21611,7 +21611,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="n">
+      <c r="A493" s="1" t="n">
         <v>645</v>
       </c>
       <c r="B493" t="inlineStr"/>
@@ -21631,7 +21631,7 @@
       <c r="P493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" t="n">
+      <c r="A494" s="1" t="n">
         <v>646</v>
       </c>
       <c r="B494" t="n">
@@ -21681,7 +21681,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="n">
+      <c r="A495" s="1" t="n">
         <v>647</v>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -21701,7 +21701,7 @@
       <c r="P495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" t="n">
+      <c r="A496" s="1" t="n">
         <v>648</v>
       </c>
       <c r="B496" t="n">
@@ -21751,53 +21751,57 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="n">
+      <c r="A497" s="1" t="n">
         <v>649</v>
       </c>
       <c r="B497" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C497" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D497" t="n">
         <v>7</v>
       </c>
-      <c r="C497" s="2" t="n">
+      <c r="E497" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="D497" t="n">
+      <c r="F497" t="n">
         <v>6.4</v>
       </c>
-      <c r="E497" s="2" t="n">
+      <c r="G497" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="F497" t="n">
+      <c r="H497" t="n">
         <v>7.2</v>
       </c>
-      <c r="G497" s="2" t="n">
+      <c r="I497" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="H497" t="n">
+      <c r="J497" t="n">
         <v>6.4</v>
       </c>
-      <c r="I497" s="2" t="n">
+      <c r="K497" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J497" t="n">
+      <c r="L497" t="n">
         <v>7.3</v>
       </c>
-      <c r="K497" s="2" t="n">
+      <c r="M497" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L497" t="n">
+      <c r="N497" t="n">
         <v>8.1</v>
       </c>
-      <c r="M497" s="2" t="n">
+      <c r="O497" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="N497" t="inlineStr"/>
-      <c r="O497" t="inlineStr"/>
       <c r="P497" t="n">
-        <v>7.07</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="n">
+      <c r="A498" s="1" t="n">
         <v>650</v>
       </c>
       <c r="B498" t="n">
@@ -21839,7 +21843,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="n">
+      <c r="A499" s="1" t="n">
         <v>651</v>
       </c>
       <c r="B499" t="n">
@@ -21889,7 +21893,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="n">
+      <c r="A500" s="1" t="n">
         <v>652</v>
       </c>
       <c r="B500" t="n">
@@ -21939,7 +21943,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="n">
+      <c r="A501" s="1" t="n">
         <v>653</v>
       </c>
       <c r="B501" t="n">
@@ -21989,53 +21993,57 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="n">
+      <c r="A502" s="1" t="n">
         <v>654</v>
       </c>
       <c r="B502" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="C502" s="2" t="n">
-        <v>46130</v>
+        <v>46133</v>
       </c>
       <c r="D502" t="n">
         <v>6.9</v>
       </c>
       <c r="E502" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="F502" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G502" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F502" t="n">
+      <c r="H502" t="n">
         <v>7.2</v>
       </c>
-      <c r="G502" s="2" t="n">
+      <c r="I502" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H502" t="n">
+      <c r="J502" t="n">
         <v>7.9</v>
       </c>
-      <c r="I502" s="2" t="n">
+      <c r="K502" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="J502" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K502" s="2" t="n">
+      <c r="L502" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M502" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="L502" t="n">
+      <c r="N502" t="n">
         <v>7.3</v>
       </c>
-      <c r="M502" s="2" t="n">
+      <c r="O502" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="N502" t="inlineStr"/>
-      <c r="O502" t="inlineStr"/>
       <c r="P502" t="n">
-        <v>7.12</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="n">
+      <c r="A503" s="1" t="n">
         <v>655</v>
       </c>
       <c r="B503" t="n">
@@ -22085,7 +22093,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="n">
+      <c r="A504" s="1" t="n">
         <v>656</v>
       </c>
       <c r="B504" t="n">
@@ -22115,7 +22123,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="n">
+      <c r="A505" s="1" t="n">
         <v>657</v>
       </c>
       <c r="B505" t="n">
@@ -22165,7 +22173,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="n">
+      <c r="A506" s="1" t="n">
         <v>658</v>
       </c>
       <c r="B506" t="n">
@@ -22215,7 +22223,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="n">
+      <c r="A507" s="1" t="n">
         <v>659</v>
       </c>
       <c r="B507" t="n">
@@ -22265,7 +22273,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="n">
+      <c r="A508" s="1" t="n">
         <v>660</v>
       </c>
       <c r="B508" t="n">
@@ -22299,7 +22307,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="n">
+      <c r="A509" s="1" t="n">
         <v>661</v>
       </c>
       <c r="B509" t="n">
@@ -22332,6 +22340,218 @@
         <v>7.67</v>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="n">
+        <v>662</v>
+      </c>
+      <c r="B510" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C510" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="D510" t="inlineStr"/>
+      <c r="E510" t="inlineStr"/>
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="inlineStr"/>
+      <c r="H510" t="inlineStr"/>
+      <c r="I510" t="inlineStr"/>
+      <c r="J510" t="inlineStr"/>
+      <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr"/>
+      <c r="N510" t="inlineStr"/>
+      <c r="O510" t="inlineStr"/>
+      <c r="P510" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="n">
+        <v>663</v>
+      </c>
+      <c r="B511" t="n">
+        <v>8</v>
+      </c>
+      <c r="C511" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="D511" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E511" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="F511" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G511" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="H511" t="inlineStr"/>
+      <c r="I511" t="inlineStr"/>
+      <c r="J511" t="inlineStr"/>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr"/>
+      <c r="N511" t="inlineStr"/>
+      <c r="O511" t="inlineStr"/>
+      <c r="P511" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="n">
+        <v>664</v>
+      </c>
+      <c r="B512" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C512" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="D512" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E512" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="F512" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G512" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="H512" t="inlineStr"/>
+      <c r="I512" t="inlineStr"/>
+      <c r="J512" t="inlineStr"/>
+      <c r="K512" t="inlineStr"/>
+      <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr"/>
+      <c r="N512" t="inlineStr"/>
+      <c r="O512" t="inlineStr"/>
+      <c r="P512" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="n">
+        <v>665</v>
+      </c>
+      <c r="B513" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C513" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="D513" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E513" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F513" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G513" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="H513" t="inlineStr"/>
+      <c r="I513" t="inlineStr"/>
+      <c r="J513" t="inlineStr"/>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr"/>
+      <c r="N513" t="inlineStr"/>
+      <c r="O513" t="inlineStr"/>
+      <c r="P513" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="n">
+        <v>666</v>
+      </c>
+      <c r="B514" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C514" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="D514" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E514" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="F514" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G514" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="H514" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I514" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="J514" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K514" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="L514" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M514" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="N514" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O514" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="P514" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="n">
+        <v>667</v>
+      </c>
+      <c r="B515" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C515" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="D515" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E515" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="F515" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G515" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="H515" t="inlineStr"/>
+      <c r="I515" t="inlineStr"/>
+      <c r="J515" t="inlineStr"/>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr"/>
+      <c r="N515" t="inlineStr"/>
+      <c r="O515" t="inlineStr"/>
+      <c r="P515" t="n">
+        <v>7.13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/players_ratings.xlsx
+++ b/players_ratings.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P515"/>
+  <dimension ref="A1:P521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,49 +619,49 @@
         <v>15</v>
       </c>
       <c r="B4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D4" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>46127</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>7.8</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>6.4</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>7.1</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="J4" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K4" s="2" t="n">
+      <c r="L4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>6.4</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="N4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>46073</v>
-      </c>
       <c r="P4" t="n">
-        <v>6.94</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="5">
@@ -849,49 +849,49 @@
         <v>27</v>
       </c>
       <c r="B9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D9" t="n">
         <v>7.2</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>7.6</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="F9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>7.9</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>6.3</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="M9" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M9" s="2" t="n">
+      <c r="N9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O9" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>46094</v>
-      </c>
       <c r="P9" t="n">
-        <v>7.06</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="10">
@@ -1019,49 +1019,49 @@
         <v>34</v>
       </c>
       <c r="B13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D13" t="n">
         <v>5.6</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="E13" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E13" s="2" t="n">
+      <c r="F13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>6.9</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>7.4</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="K13" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>6.2</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="M13" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="L13" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M13" s="2" t="n">
+      <c r="N13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O13" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="N13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>46097</v>
-      </c>
       <c r="P13" t="n">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="14">
@@ -1069,49 +1069,49 @@
         <v>36</v>
       </c>
       <c r="B14" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="C14" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>6.9</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="F14" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>6.3</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="K14" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>7.5</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="M14" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="L14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M14" s="2" t="n">
+      <c r="N14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O14" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="N14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>46075</v>
-      </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="15">
@@ -1195,49 +1195,49 @@
         <v>41</v>
       </c>
       <c r="B17" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="C17" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E17" s="2" t="n">
+      <c r="F17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F17" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>7.2</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="K17" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>6.3</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="M17" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>7.1</v>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="O17" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>46097</v>
-      </c>
       <c r="P17" t="n">
-        <v>6.71</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="18">
@@ -1245,49 +1245,49 @@
         <v>43</v>
       </c>
       <c r="B18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="C18" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>6.8</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>7.4</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="I18" s="2" t="n">
         <v>46130</v>
-      </c>
-      <c r="H18" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>46122</v>
       </c>
       <c r="J18" t="n">
         <v>6.3</v>
       </c>
       <c r="K18" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M18" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="L18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M18" s="2" t="n">
+      <c r="N18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O18" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N18" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P18" t="n">
-        <v>6.63</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="19">
@@ -1345,49 +1345,49 @@
         <v>46</v>
       </c>
       <c r="B20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D20" t="n">
         <v>7.2</v>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="E20" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E20" s="2" t="n">
+      <c r="F20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G20" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
         <v>7.7</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="I20" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>6.8</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="K20" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K20" s="2" t="n">
+      <c r="L20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="L20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M20" s="2" t="n">
+      <c r="N20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O20" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="N20" t="n">
-        <v>7</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>46083</v>
-      </c>
       <c r="P20" t="n">
-        <v>6.9</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="21">
@@ -1991,49 +1991,49 @@
         <v>80</v>
       </c>
       <c r="B35" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D35" t="n">
         <v>7.7</v>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="E35" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>6.8</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="F35" t="n">
+      <c r="H35" t="n">
         <v>6.3</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="I35" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H35" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I35" s="2" t="n">
+      <c r="J35" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K35" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>7.1</v>
       </c>
-      <c r="K35" s="2" t="n">
+      <c r="M35" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L35" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M35" s="2" t="n">
+      <c r="N35" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O35" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>6.8</v>
-      </c>
-      <c r="O35" s="2" t="n">
-        <v>46081</v>
-      </c>
-      <c r="P35" t="n">
-        <v>6.87</v>
       </c>
     </row>
     <row r="36">
@@ -2041,45 +2041,49 @@
         <v>81</v>
       </c>
       <c r="B36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D36" t="n">
         <v>6.9</v>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="E36" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>7.1</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F36" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G36" s="2" t="n">
+      <c r="H36" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I36" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>7.6</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="K36" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>8.4</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="M36" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>6.3</v>
       </c>
-      <c r="M36" s="2" t="n">
+      <c r="O36" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>7.17</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="37">
@@ -2821,49 +2825,49 @@
         <v>133</v>
       </c>
       <c r="B62" t="n">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D62" t="n">
         <v>7.1</v>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="E62" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
         <v>6.1</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F62" t="n">
+      <c r="H62" t="n">
         <v>7.6</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="I62" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H62" t="n">
+      <c r="J62" t="n">
         <v>7.3</v>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="K62" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J62" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K62" s="2" t="n">
+      <c r="L62" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M62" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L62" t="n">
+      <c r="N62" t="n">
         <v>6.1</v>
       </c>
-      <c r="M62" s="2" t="n">
+      <c r="O62" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N62" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O62" s="2" t="n">
-        <v>46088</v>
-      </c>
       <c r="P62" t="n">
-        <v>6.87</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="63">
@@ -2991,49 +2995,49 @@
         <v>143</v>
       </c>
       <c r="B66" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D66" t="n">
         <v>6.8</v>
       </c>
-      <c r="C66" s="2" t="n">
+      <c r="E66" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="D66" t="n">
+      <c r="F66" t="n">
         <v>6.2</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F66" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G66" s="2" t="n">
+      <c r="H66" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I66" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="H66" t="n">
+      <c r="J66" t="n">
         <v>6.3</v>
       </c>
-      <c r="I66" s="2" t="n">
+      <c r="K66" s="2" t="n">
         <v>46076</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>7</v>
       </c>
-      <c r="K66" s="2" t="n">
+      <c r="M66" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L66" t="n">
+      <c r="N66" t="n">
         <v>6</v>
       </c>
-      <c r="M66" s="2" t="n">
+      <c r="O66" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="N66" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O66" s="2" t="n">
-        <v>46057</v>
-      </c>
       <c r="P66" t="n">
-        <v>6.49</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="67">
@@ -3094,46 +3098,46 @@
         <v>6.4</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>46138</v>
+        <v>46145</v>
       </c>
       <c r="D68" t="n">
         <v>6.4</v>
       </c>
       <c r="E68" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="F68" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G68" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F68" t="n">
+      <c r="H68" t="n">
         <v>6.3</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="I68" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H68" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I68" s="2" t="n">
+      <c r="J68" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K68" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="J68" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K68" s="2" t="n">
+      <c r="L68" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M68" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="L68" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M68" s="2" t="n">
+      <c r="N68" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O68" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N68" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O68" s="2" t="n">
-        <v>46069</v>
-      </c>
       <c r="P68" t="n">
-        <v>6.51</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="69">
@@ -3141,49 +3145,49 @@
         <v>146</v>
       </c>
       <c r="B69" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D69" t="n">
         <v>6.3</v>
       </c>
-      <c r="C69" s="2" t="n">
+      <c r="E69" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D69" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E69" s="2" t="n">
+      <c r="F69" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G69" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="F69" t="n">
+      <c r="H69" t="n">
         <v>7.6</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="I69" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="H69" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I69" s="2" t="n">
+      <c r="J69" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K69" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>6.8</v>
       </c>
-      <c r="K69" s="2" t="n">
+      <c r="M69" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L69" t="n">
+      <c r="N69" t="n">
         <v>7.1</v>
       </c>
-      <c r="M69" s="2" t="n">
+      <c r="O69" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="N69" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O69" s="2" t="n">
-        <v>46089</v>
-      </c>
       <c r="P69" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="70">
@@ -3191,49 +3195,49 @@
         <v>147</v>
       </c>
       <c r="B70" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D70" t="n">
         <v>6.2</v>
       </c>
-      <c r="C70" s="2" t="n">
+      <c r="E70" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D70" t="n">
+      <c r="F70" t="n">
         <v>7</v>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="F70" t="n">
+      <c r="H70" t="n">
         <v>6.2</v>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="I70" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="H70" t="n">
+      <c r="J70" t="n">
         <v>6.8</v>
       </c>
-      <c r="I70" s="2" t="n">
+      <c r="K70" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J70" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K70" s="2" t="n">
+      <c r="L70" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M70" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="L70" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M70" s="2" t="n">
+      <c r="N70" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O70" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="N70" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O70" s="2" t="n">
-        <v>46082</v>
-      </c>
       <c r="P70" t="n">
-        <v>6.57</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="71">
@@ -3311,49 +3315,49 @@
         <v>150</v>
       </c>
       <c r="B73" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D73" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="F73" t="n">
         <v>7.1</v>
       </c>
-      <c r="C73" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="D73" t="n">
+      <c r="H73" t="n">
         <v>6.9</v>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="I73" s="2" t="n">
         <v>46127</v>
       </c>
-      <c r="F73" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G73" s="2" t="n">
+      <c r="J73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K73" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H73" t="n">
+      <c r="L73" t="n">
         <v>6.8</v>
       </c>
-      <c r="I73" s="2" t="n">
+      <c r="M73" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J73" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K73" s="2" t="n">
+      <c r="N73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O73" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="L73" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M73" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="N73" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O73" s="2" t="n">
-        <v>46089</v>
-      </c>
       <c r="P73" t="n">
-        <v>6.93</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="74">
@@ -3611,45 +3615,49 @@
         <v>169</v>
       </c>
       <c r="B79" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D79" t="n">
         <v>7</v>
       </c>
-      <c r="C79" s="2" t="n">
+      <c r="E79" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D79" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E79" s="2" t="n">
+      <c r="F79" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G79" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F79" t="n">
+      <c r="H79" t="n">
         <v>6.4</v>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="I79" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H79" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I79" s="2" t="n">
+      <c r="J79" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K79" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="J79" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K79" s="2" t="n">
+      <c r="L79" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M79" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="L79" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M79" s="2" t="n">
+      <c r="N79" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O79" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
-        <v>6.68</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="80">
@@ -3849,49 +3857,49 @@
         <v>175</v>
       </c>
       <c r="B84" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D84" t="n">
         <v>7.3</v>
       </c>
-      <c r="C84" s="2" t="n">
+      <c r="E84" s="2" t="n">
         <v>46131</v>
-      </c>
-      <c r="D84" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>46127</v>
       </c>
       <c r="F84" t="n">
         <v>6.8</v>
       </c>
       <c r="G84" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="H84" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I84" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H84" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I84" s="2" t="n">
+      <c r="J84" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K84" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J84" t="n">
+      <c r="L84" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="K84" s="2" t="n">
+      <c r="M84" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="L84" t="n">
+      <c r="N84" t="n">
         <v>6</v>
       </c>
-      <c r="M84" s="2" t="n">
+      <c r="O84" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="N84" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O84" s="2" t="n">
-        <v>46069</v>
-      </c>
       <c r="P84" t="n">
-        <v>7.01</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="85">
@@ -3983,49 +3991,49 @@
         <v>181</v>
       </c>
       <c r="B87" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>46131</v>
+        <v>46138</v>
       </c>
       <c r="D87" t="n">
         <v>7.1</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>46127</v>
+        <v>46131</v>
       </c>
       <c r="F87" t="n">
         <v>7.1</v>
       </c>
       <c r="G87" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="H87" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I87" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H87" t="n">
+      <c r="J87" t="n">
         <v>7.4</v>
       </c>
-      <c r="I87" s="2" t="n">
+      <c r="K87" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J87" t="n">
+      <c r="L87" t="n">
         <v>6.9</v>
       </c>
-      <c r="K87" s="2" t="n">
+      <c r="M87" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
         <v>7</v>
       </c>
-      <c r="M87" s="2" t="n">
+      <c r="O87" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="N87" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O87" s="2" t="n">
-        <v>46082</v>
-      </c>
       <c r="P87" t="n">
-        <v>7</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="88">
@@ -4341,46 +4349,46 @@
         <v>192</v>
       </c>
       <c r="B95" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D95" t="n">
         <v>6.4</v>
       </c>
-      <c r="C95" s="2" t="n">
+      <c r="E95" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D95" t="n">
+      <c r="F95" t="n">
         <v>7</v>
       </c>
-      <c r="E95" s="2" t="n">
+      <c r="G95" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="F95" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G95" s="2" t="n">
+      <c r="H95" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I95" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H95" t="n">
+      <c r="J95" t="n">
         <v>6.3</v>
       </c>
-      <c r="I95" s="2" t="n">
+      <c r="K95" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J95" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K95" s="2" t="n">
+      <c r="L95" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M95" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="L95" t="n">
+      <c r="N95" t="n">
         <v>7.1</v>
       </c>
-      <c r="M95" s="2" t="n">
+      <c r="O95" s="2" t="n">
         <v>46082</v>
-      </c>
-      <c r="N95" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O95" s="2" t="n">
-        <v>46075</v>
       </c>
       <c r="P95" t="n">
         <v>6.66</v>
@@ -4633,49 +4641,49 @@
         <v>200</v>
       </c>
       <c r="B101" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>46139</v>
+        <v>46145</v>
       </c>
       <c r="D101" t="n">
         <v>7.2</v>
       </c>
       <c r="E101" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="F101" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G101" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F101" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G101" s="2" t="n">
+      <c r="H101" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I101" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H101" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I101" s="2" t="n">
+      <c r="J101" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K101" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="J101" t="n">
+      <c r="L101" t="n">
         <v>7.4</v>
       </c>
-      <c r="K101" s="2" t="n">
+      <c r="M101" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="L101" t="n">
+      <c r="N101" t="n">
         <v>6.3</v>
       </c>
-      <c r="M101" s="2" t="n">
+      <c r="O101" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N101" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O101" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P101" t="n">
-        <v>6.9</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="102">
@@ -4683,49 +4691,49 @@
         <v>201</v>
       </c>
       <c r="B102" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D102" t="n">
         <v>6.2</v>
       </c>
-      <c r="C102" s="2" t="n">
+      <c r="E102" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D102" t="n">
+      <c r="F102" t="n">
         <v>6.1</v>
       </c>
-      <c r="E102" s="2" t="n">
+      <c r="G102" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F102" t="n">
+      <c r="H102" t="n">
         <v>5.9</v>
       </c>
-      <c r="G102" s="2" t="n">
+      <c r="I102" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H102" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I102" s="2" t="n">
+      <c r="J102" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K102" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="J102" t="n">
+      <c r="L102" t="n">
         <v>7.3</v>
       </c>
-      <c r="K102" s="2" t="n">
+      <c r="M102" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="L102" t="n">
+      <c r="N102" t="n">
         <v>5.9</v>
       </c>
-      <c r="M102" s="2" t="n">
+      <c r="O102" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N102" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O102" s="2" t="n">
-        <v>46067</v>
-      </c>
       <c r="P102" t="n">
-        <v>6.23</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="103">
@@ -6039,49 +6047,49 @@
         <v>247</v>
       </c>
       <c r="B136" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C136" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D136" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E136" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D136" t="n">
+      <c r="F136" t="n">
         <v>6.8</v>
       </c>
-      <c r="E136" s="2" t="n">
+      <c r="G136" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F136" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G136" s="2" t="n">
+      <c r="H136" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I136" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="H136" t="n">
+      <c r="J136" t="n">
         <v>6.2</v>
       </c>
-      <c r="I136" s="2" t="n">
+      <c r="K136" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J136" t="n">
+      <c r="L136" t="n">
         <v>7.3</v>
       </c>
-      <c r="K136" s="2" t="n">
+      <c r="M136" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L136" t="n">
+      <c r="N136" t="n">
         <v>7.7</v>
       </c>
-      <c r="M136" s="2" t="n">
+      <c r="O136" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="N136" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O136" s="2" t="n">
-        <v>46087</v>
-      </c>
       <c r="P136" t="n">
-        <v>6.96</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="137">
@@ -6089,49 +6097,49 @@
         <v>248</v>
       </c>
       <c r="B137" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D137" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="C137" s="2" t="n">
+      <c r="E137" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D137" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E137" s="2" t="n">
+      <c r="F137" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G137" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F137" t="n">
+      <c r="H137" t="n">
         <v>6.9</v>
       </c>
-      <c r="G137" s="2" t="n">
+      <c r="I137" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H137" t="n">
+      <c r="J137" t="n">
         <v>6.8</v>
       </c>
-      <c r="I137" s="2" t="n">
+      <c r="K137" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="J137" t="n">
+      <c r="L137" t="n">
         <v>7.5</v>
       </c>
-      <c r="K137" s="2" t="n">
+      <c r="M137" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L137" t="n">
+      <c r="N137" t="n">
         <v>7.3</v>
       </c>
-      <c r="M137" s="2" t="n">
+      <c r="O137" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N137" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O137" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P137" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="138">
@@ -6289,49 +6297,49 @@
         <v>258</v>
       </c>
       <c r="B141" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="D141" t="n">
         <v>7.2</v>
       </c>
-      <c r="C141" s="2" t="n">
+      <c r="E141" s="2" t="n">
         <v>46132</v>
       </c>
-      <c r="D141" t="n">
+      <c r="F141" t="n">
         <v>6.4</v>
       </c>
-      <c r="E141" s="2" t="n">
+      <c r="G141" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="F141" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G141" s="2" t="n">
+      <c r="H141" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I141" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H141" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I141" s="2" t="n">
+      <c r="J141" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K141" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="J141" t="n">
+      <c r="L141" t="n">
         <v>6.3</v>
       </c>
-      <c r="K141" s="2" t="n">
+      <c r="M141" s="2" t="n">
         <v>46005</v>
       </c>
-      <c r="L141" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M141" s="2" t="n">
+      <c r="N141" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O141" s="2" t="n">
         <v>45990</v>
       </c>
-      <c r="N141" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O141" s="2" t="n">
-        <v>45984</v>
-      </c>
       <c r="P141" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="142">
@@ -6389,7 +6397,7 @@
         <v>260</v>
       </c>
       <c r="B143" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C143" s="2" t="n">
         <v>46138</v>
@@ -6431,7 +6439,7 @@
         <v>46090</v>
       </c>
       <c r="P143" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="144">
@@ -6489,49 +6497,49 @@
         <v>263</v>
       </c>
       <c r="B145" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="D145" t="n">
         <v>6.4</v>
       </c>
-      <c r="C145" s="2" t="n">
+      <c r="E145" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="D145" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E145" s="2" t="n">
+      <c r="F145" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G145" s="2" t="n">
         <v>45965</v>
       </c>
-      <c r="F145" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G145" s="2" t="n">
+      <c r="H145" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I145" s="2" t="n">
         <v>45959</v>
       </c>
-      <c r="H145" t="n">
+      <c r="J145" t="n">
         <v>6.9</v>
       </c>
-      <c r="I145" s="2" t="n">
+      <c r="K145" s="2" t="n">
         <v>45955</v>
       </c>
-      <c r="J145" t="n">
+      <c r="L145" t="n">
         <v>6.4</v>
       </c>
-      <c r="K145" s="2" t="n">
+      <c r="M145" s="2" t="n">
         <v>45933</v>
       </c>
-      <c r="L145" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M145" s="2" t="n">
+      <c r="N145" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O145" s="2" t="n">
         <v>45927</v>
       </c>
-      <c r="N145" t="n">
-        <v>7</v>
-      </c>
-      <c r="O145" s="2" t="n">
-        <v>45920</v>
-      </c>
       <c r="P145" t="n">
-        <v>6.64</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="146">
@@ -6609,49 +6617,49 @@
         <v>273</v>
       </c>
       <c r="B148" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D148" t="n">
         <v>6.3</v>
       </c>
-      <c r="C148" s="2" t="n">
+      <c r="E148" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="D148" t="n">
+      <c r="F148" t="n">
         <v>7.7</v>
       </c>
-      <c r="E148" s="2" t="n">
+      <c r="G148" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="F148" t="n">
+      <c r="H148" t="n">
         <v>6.8</v>
       </c>
-      <c r="G148" s="2" t="n">
+      <c r="I148" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="H148" t="n">
+      <c r="J148" t="n">
         <v>6.3</v>
       </c>
-      <c r="I148" s="2" t="n">
+      <c r="K148" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="J148" t="n">
+      <c r="L148" t="n">
         <v>6.9</v>
       </c>
-      <c r="K148" s="2" t="n">
+      <c r="M148" s="2" t="n">
         <v>46089</v>
-      </c>
-      <c r="L148" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M148" s="2" t="n">
-        <v>46085</v>
       </c>
       <c r="N148" t="n">
         <v>6.4</v>
       </c>
       <c r="O148" s="2" t="n">
-        <v>46082</v>
+        <v>46085</v>
       </c>
       <c r="P148" t="n">
-        <v>6.69</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="149">
@@ -7043,46 +7051,46 @@
         <v>282</v>
       </c>
       <c r="B157" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="C157" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D157" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E157" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D157" t="n">
+      <c r="F157" t="n">
         <v>7</v>
       </c>
-      <c r="E157" s="2" t="n">
+      <c r="G157" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F157" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G157" s="2" t="n">
+      <c r="H157" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I157" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="H157" t="n">
+      <c r="J157" t="n">
         <v>6.9</v>
       </c>
-      <c r="I157" s="2" t="n">
+      <c r="K157" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="J157" t="n">
+      <c r="L157" t="n">
         <v>7.8</v>
       </c>
-      <c r="K157" s="2" t="n">
+      <c r="M157" s="2" t="n">
         <v>46103</v>
-      </c>
-      <c r="L157" t="n">
-        <v>7</v>
-      </c>
-      <c r="M157" s="2" t="n">
-        <v>46088</v>
       </c>
       <c r="N157" t="n">
         <v>7</v>
       </c>
       <c r="O157" s="2" t="n">
-        <v>46081</v>
+        <v>46088</v>
       </c>
       <c r="P157" t="n">
         <v>6.99</v>
@@ -7193,49 +7201,49 @@
         <v>286</v>
       </c>
       <c r="B160" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D160" t="n">
         <v>6.4</v>
       </c>
-      <c r="C160" s="2" t="n">
+      <c r="E160" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D160" t="n">
+      <c r="F160" t="n">
         <v>6.9</v>
       </c>
-      <c r="E160" s="2" t="n">
+      <c r="G160" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F160" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G160" s="2" t="n">
+      <c r="H160" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I160" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H160" t="n">
+      <c r="J160" t="n">
         <v>5.8</v>
       </c>
-      <c r="I160" s="2" t="n">
+      <c r="K160" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="J160" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K160" s="2" t="n">
+      <c r="L160" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M160" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="L160" t="n">
+      <c r="N160" t="n">
         <v>6.4</v>
       </c>
-      <c r="M160" s="2" t="n">
+      <c r="O160" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N160" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O160" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P160" t="n">
-        <v>6.51</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="161">
@@ -7293,49 +7301,49 @@
         <v>288</v>
       </c>
       <c r="B162" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C162" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D162" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E162" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D162" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E162" s="2" t="n">
+      <c r="F162" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G162" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F162" t="n">
+      <c r="H162" t="n">
         <v>7.1</v>
       </c>
-      <c r="G162" s="2" t="n">
+      <c r="I162" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="H162" t="n">
+      <c r="J162" t="n">
         <v>6.4</v>
       </c>
-      <c r="I162" s="2" t="n">
+      <c r="K162" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="J162" t="n">
+      <c r="L162" t="n">
         <v>9</v>
       </c>
-      <c r="K162" s="2" t="n">
+      <c r="M162" s="2" t="n">
         <v>46103</v>
-      </c>
-      <c r="L162" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M162" s="2" t="n">
-        <v>46097</v>
       </c>
       <c r="N162" t="n">
         <v>6.4</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>46088</v>
+        <v>46097</v>
       </c>
       <c r="P162" t="n">
-        <v>6.94</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="163">
@@ -7393,49 +7401,49 @@
         <v>290</v>
       </c>
       <c r="B164" t="n">
+        <v>7</v>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D164" t="n">
         <v>7.7</v>
       </c>
-      <c r="C164" s="2" t="n">
+      <c r="E164" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D164" t="n">
+      <c r="F164" t="n">
         <v>7.6</v>
       </c>
-      <c r="E164" s="2" t="n">
+      <c r="G164" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F164" t="n">
+      <c r="H164" t="n">
         <v>9</v>
       </c>
-      <c r="G164" s="2" t="n">
+      <c r="I164" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="H164" t="n">
+      <c r="J164" t="n">
         <v>6.9</v>
       </c>
-      <c r="I164" s="2" t="n">
+      <c r="K164" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J164" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K164" s="2" t="n">
+      <c r="L164" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M164" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L164" t="n">
+      <c r="N164" t="n">
         <v>6.8</v>
       </c>
-      <c r="M164" s="2" t="n">
+      <c r="O164" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="N164" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O164" s="2" t="n">
-        <v>46081</v>
-      </c>
       <c r="P164" t="n">
-        <v>7.29</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="165">
@@ -7443,49 +7451,49 @@
         <v>291</v>
       </c>
       <c r="B165" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="C165" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D165" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E165" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="D165" t="n">
+      <c r="F165" t="n">
         <v>6.3</v>
       </c>
-      <c r="E165" s="2" t="n">
+      <c r="G165" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F165" t="n">
+      <c r="H165" t="n">
         <v>7.9</v>
       </c>
-      <c r="G165" s="2" t="n">
+      <c r="I165" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="H165" t="n">
+      <c r="J165" t="n">
         <v>6.8</v>
       </c>
-      <c r="I165" s="2" t="n">
+      <c r="K165" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J165" t="n">
+      <c r="L165" t="n">
         <v>6.4</v>
       </c>
-      <c r="K165" s="2" t="n">
+      <c r="M165" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L165" t="n">
+      <c r="N165" t="n">
         <v>7</v>
       </c>
-      <c r="M165" s="2" t="n">
+      <c r="O165" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="N165" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O165" s="2" t="n">
-        <v>46081</v>
-      </c>
       <c r="P165" t="n">
-        <v>6.73</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="166">
@@ -7493,49 +7501,49 @@
         <v>292</v>
       </c>
       <c r="B166" t="n">
+        <v>6</v>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D166" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="F166" t="n">
         <v>7</v>
       </c>
-      <c r="C166" s="2" t="n">
+      <c r="G166" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D166" t="n">
+      <c r="H166" t="n">
         <v>7.8</v>
       </c>
-      <c r="E166" s="2" t="n">
+      <c r="I166" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F166" t="n">
+      <c r="J166" t="n">
         <v>6.8</v>
       </c>
-      <c r="G166" s="2" t="n">
+      <c r="K166" s="2" t="n">
         <v>46127</v>
       </c>
-      <c r="H166" t="n">
+      <c r="L166" t="n">
         <v>7.6</v>
       </c>
-      <c r="I166" s="2" t="n">
+      <c r="M166" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J166" t="n">
+      <c r="N166" t="n">
         <v>7</v>
       </c>
-      <c r="K166" s="2" t="n">
+      <c r="O166" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="L166" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="M166" s="2" t="n">
-        <v>46103</v>
-      </c>
-      <c r="N166" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O166" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P166" t="n">
-        <v>7.2</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="167">
@@ -7643,49 +7651,49 @@
         <v>295</v>
       </c>
       <c r="B169" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D169" t="n">
         <v>5.9</v>
       </c>
-      <c r="C169" s="2" t="n">
+      <c r="E169" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D169" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E169" s="2" t="n">
+      <c r="F169" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G169" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F169" t="n">
+      <c r="H169" t="n">
         <v>7.5</v>
       </c>
-      <c r="G169" s="2" t="n">
+      <c r="I169" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H169" t="n">
+      <c r="J169" t="n">
         <v>6.4</v>
       </c>
-      <c r="I169" s="2" t="n">
+      <c r="K169" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="J169" t="n">
+      <c r="L169" t="n">
         <v>7.6</v>
       </c>
-      <c r="K169" s="2" t="n">
+      <c r="M169" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="L169" t="n">
+      <c r="N169" t="n">
         <v>7.1</v>
       </c>
-      <c r="M169" s="2" t="n">
+      <c r="O169" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="N169" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O169" s="2" t="n">
-        <v>46082</v>
-      </c>
       <c r="P169" t="n">
-        <v>7</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="170">
@@ -7743,49 +7751,49 @@
         <v>298</v>
       </c>
       <c r="B171" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D171" t="n">
         <v>6.8</v>
       </c>
-      <c r="C171" s="2" t="n">
+      <c r="E171" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="D171" t="n">
+      <c r="F171" t="n">
         <v>6.9</v>
       </c>
-      <c r="E171" s="2" t="n">
+      <c r="G171" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="F171" t="n">
+      <c r="H171" t="n">
         <v>6.3</v>
       </c>
-      <c r="G171" s="2" t="n">
+      <c r="I171" s="2" t="n">
         <v>45997</v>
       </c>
-      <c r="H171" t="n">
+      <c r="J171" t="n">
         <v>6</v>
       </c>
-      <c r="I171" s="2" t="n">
+      <c r="K171" s="2" t="n">
         <v>45994</v>
       </c>
-      <c r="J171" t="n">
+      <c r="L171" t="n">
         <v>6.1</v>
       </c>
-      <c r="K171" s="2" t="n">
+      <c r="M171" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="L171" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M171" s="2" t="n">
+      <c r="N171" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O171" s="2" t="n">
         <v>45983</v>
       </c>
-      <c r="N171" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O171" s="2" t="n">
-        <v>45970</v>
-      </c>
       <c r="P171" t="n">
-        <v>6.46</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="172">
@@ -7851,49 +7859,49 @@
         <v>302</v>
       </c>
       <c r="B174" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="C174" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D174" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E174" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D174" t="n">
+      <c r="F174" t="n">
         <v>7.2</v>
       </c>
-      <c r="E174" s="2" t="n">
+      <c r="G174" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F174" t="n">
+      <c r="H174" t="n">
         <v>5.7</v>
       </c>
-      <c r="G174" s="2" t="n">
+      <c r="I174" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H174" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I174" s="2" t="n">
+      <c r="J174" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K174" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="J174" t="n">
+      <c r="L174" t="n">
         <v>8.4</v>
       </c>
-      <c r="K174" s="2" t="n">
+      <c r="M174" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="L174" t="n">
+      <c r="N174" t="n">
         <v>6.2</v>
       </c>
-      <c r="M174" s="2" t="n">
+      <c r="O174" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N174" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O174" s="2" t="n">
-        <v>46097</v>
-      </c>
       <c r="P174" t="n">
-        <v>6.7</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="175">
@@ -8151,49 +8159,49 @@
         <v>310</v>
       </c>
       <c r="B180" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="C180" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D180" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E180" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D180" t="n">
+      <c r="F180" t="n">
         <v>7</v>
       </c>
-      <c r="E180" s="2" t="n">
+      <c r="G180" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F180" t="n">
+      <c r="H180" t="n">
         <v>6.8</v>
       </c>
-      <c r="G180" s="2" t="n">
+      <c r="I180" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H180" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I180" s="2" t="n">
+      <c r="J180" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K180" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="J180" t="n">
+      <c r="L180" t="n">
         <v>7.3</v>
       </c>
-      <c r="K180" s="2" t="n">
+      <c r="M180" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="L180" t="n">
+      <c r="N180" t="n">
         <v>7.7</v>
       </c>
-      <c r="M180" s="2" t="n">
+      <c r="O180" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="N180" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O180" s="2" t="n">
-        <v>46082</v>
-      </c>
       <c r="P180" t="n">
-        <v>6.93</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="181">
@@ -8201,49 +8209,49 @@
         <v>311</v>
       </c>
       <c r="B181" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C181" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D181" t="n">
         <v>7.2</v>
       </c>
-      <c r="C181" s="2" t="n">
+      <c r="E181" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D181" t="n">
+      <c r="F181" t="n">
         <v>6.2</v>
       </c>
-      <c r="E181" s="2" t="n">
+      <c r="G181" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F181" t="n">
+      <c r="H181" t="n">
         <v>6.9</v>
       </c>
-      <c r="G181" s="2" t="n">
+      <c r="I181" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="H181" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I181" s="2" t="n">
+      <c r="J181" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K181" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="J181" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K181" s="2" t="n">
+      <c r="L181" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M181" s="2" t="n">
         <v>46097</v>
-      </c>
-      <c r="L181" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M181" s="2" t="n">
-        <v>46082</v>
       </c>
       <c r="N181" t="n">
         <v>6.8</v>
       </c>
       <c r="O181" s="2" t="n">
-        <v>46075</v>
+        <v>46082</v>
       </c>
       <c r="P181" t="n">
-        <v>6.71</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="182">
@@ -8301,45 +8309,49 @@
         <v>313</v>
       </c>
       <c r="B183" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D183" t="n">
         <v>7.2</v>
       </c>
-      <c r="C183" s="2" t="n">
+      <c r="E183" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D183" t="n">
+      <c r="F183" t="n">
         <v>6.1</v>
       </c>
-      <c r="E183" s="2" t="n">
+      <c r="G183" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F183" t="n">
+      <c r="H183" t="n">
         <v>7.9</v>
       </c>
-      <c r="G183" s="2" t="n">
+      <c r="I183" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H183" t="n">
+      <c r="J183" t="n">
         <v>6.1</v>
       </c>
-      <c r="I183" s="2" t="n">
+      <c r="K183" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="J183" t="n">
+      <c r="L183" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K183" s="2" t="n">
+      <c r="M183" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="L183" t="n">
+      <c r="N183" t="n">
         <v>6.2</v>
       </c>
-      <c r="M183" s="2" t="n">
+      <c r="O183" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
       <c r="P183" t="n">
-        <v>6.95</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="184">
@@ -8397,49 +8409,49 @@
         <v>315</v>
       </c>
       <c r="B185" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D185" t="n">
         <v>7.2</v>
       </c>
-      <c r="C185" s="2" t="n">
+      <c r="E185" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D185" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E185" s="2" t="n">
+      <c r="F185" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G185" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="F185" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G185" s="2" t="n">
+      <c r="H185" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I185" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H185" t="n">
+      <c r="J185" t="n">
         <v>6.8</v>
       </c>
-      <c r="I185" s="2" t="n">
+      <c r="K185" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="J185" t="n">
+      <c r="L185" t="n">
         <v>6.2</v>
       </c>
-      <c r="K185" s="2" t="n">
+      <c r="M185" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="L185" t="n">
+      <c r="N185" t="n">
         <v>7.9</v>
       </c>
-      <c r="M185" s="2" t="n">
+      <c r="O185" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="N185" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O185" s="2" t="n">
-        <v>46082</v>
-      </c>
       <c r="P185" t="n">
-        <v>7.01</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="186">
@@ -8547,49 +8559,49 @@
         <v>318</v>
       </c>
       <c r="B188" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C188" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D188" t="n">
         <v>9.1</v>
       </c>
-      <c r="C188" s="2" t="n">
+      <c r="E188" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D188" t="n">
+      <c r="F188" t="n">
         <v>7.3</v>
       </c>
-      <c r="E188" s="2" t="n">
+      <c r="G188" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F188" t="n">
+      <c r="H188" t="n">
         <v>6.4</v>
       </c>
-      <c r="G188" s="2" t="n">
+      <c r="I188" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="H188" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I188" s="2" t="n">
+      <c r="J188" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K188" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="J188" t="n">
+      <c r="L188" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K188" s="2" t="n">
+      <c r="M188" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L188" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M188" s="2" t="n">
+      <c r="N188" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O188" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N188" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O188" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P188" t="n">
-        <v>7.4</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="189">
@@ -8597,49 +8609,49 @@
         <v>319</v>
       </c>
       <c r="B189" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="C189" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D189" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E189" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D189" t="n">
+      <c r="F189" t="n">
         <v>7</v>
       </c>
-      <c r="E189" s="2" t="n">
+      <c r="G189" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="F189" t="n">
+      <c r="H189" t="n">
         <v>6.3</v>
       </c>
-      <c r="G189" s="2" t="n">
+      <c r="I189" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H189" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I189" s="2" t="n">
+      <c r="J189" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K189" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="J189" t="n">
+      <c r="L189" t="n">
         <v>7.4</v>
       </c>
-      <c r="K189" s="2" t="n">
+      <c r="M189" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="L189" t="n">
+      <c r="N189" t="n">
         <v>6.8</v>
       </c>
-      <c r="M189" s="2" t="n">
+      <c r="O189" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N189" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="O189" s="2" t="n">
-        <v>46087</v>
-      </c>
       <c r="P189" t="n">
-        <v>7.1</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="190">
@@ -9143,49 +9155,49 @@
         <v>335</v>
       </c>
       <c r="B201" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="C201" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D201" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E201" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D201" t="n">
+      <c r="F201" t="n">
         <v>6.8</v>
       </c>
-      <c r="E201" s="2" t="n">
+      <c r="G201" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F201" t="n">
+      <c r="H201" t="n">
         <v>6.3</v>
       </c>
-      <c r="G201" s="2" t="n">
+      <c r="I201" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H201" t="n">
+      <c r="J201" t="n">
         <v>6.8</v>
       </c>
-      <c r="I201" s="2" t="n">
+      <c r="K201" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="J201" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K201" s="2" t="n">
+      <c r="L201" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M201" s="2" t="n">
         <v>46095</v>
-      </c>
-      <c r="L201" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M201" s="2" t="n">
-        <v>46089</v>
       </c>
       <c r="N201" t="n">
         <v>6.3</v>
       </c>
       <c r="O201" s="2" t="n">
-        <v>46081</v>
+        <v>46089</v>
       </c>
       <c r="P201" t="n">
-        <v>6.53</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="202">
@@ -9193,46 +9205,46 @@
         <v>336</v>
       </c>
       <c r="B202" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C202" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D202" t="n">
         <v>7.7</v>
       </c>
-      <c r="C202" s="2" t="n">
+      <c r="E202" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D202" t="n">
+      <c r="F202" t="n">
         <v>5.4</v>
       </c>
-      <c r="E202" s="2" t="n">
+      <c r="G202" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F202" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G202" s="2" t="n">
+      <c r="H202" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I202" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H202" t="n">
+      <c r="J202" t="n">
         <v>7.6</v>
       </c>
-      <c r="I202" s="2" t="n">
+      <c r="K202" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="J202" t="n">
+      <c r="L202" t="n">
         <v>6.4</v>
       </c>
-      <c r="K202" s="2" t="n">
+      <c r="M202" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L202" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M202" s="2" t="n">
+      <c r="N202" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O202" s="2" t="n">
         <v>46096</v>
-      </c>
-      <c r="N202" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O202" s="2" t="n">
-        <v>46088</v>
       </c>
       <c r="P202" t="n">
         <v>6.67</v>
@@ -9243,46 +9255,46 @@
         <v>337</v>
       </c>
       <c r="B203" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D203" t="n">
         <v>6.3</v>
       </c>
-      <c r="C203" s="2" t="n">
+      <c r="E203" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="D203" t="n">
+      <c r="F203" t="n">
         <v>7.5</v>
       </c>
-      <c r="E203" s="2" t="n">
+      <c r="G203" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F203" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G203" s="2" t="n">
+      <c r="H203" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I203" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="H203" t="n">
+      <c r="J203" t="n">
         <v>7.7</v>
       </c>
-      <c r="I203" s="2" t="n">
+      <c r="K203" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J203" t="n">
+      <c r="L203" t="n">
         <v>6.8</v>
       </c>
-      <c r="K203" s="2" t="n">
+      <c r="M203" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="L203" t="n">
+      <c r="N203" t="n">
         <v>6.1</v>
       </c>
-      <c r="M203" s="2" t="n">
+      <c r="O203" s="2" t="n">
         <v>46088</v>
-      </c>
-      <c r="N203" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O203" s="2" t="n">
-        <v>46081</v>
       </c>
       <c r="P203" t="n">
         <v>6.83</v>
@@ -9443,49 +9455,49 @@
         <v>342</v>
       </c>
       <c r="B208" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C208" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D208" t="n">
         <v>7</v>
       </c>
-      <c r="C208" s="2" t="n">
+      <c r="E208" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D208" t="n">
+      <c r="F208" t="n">
         <v>6.8</v>
       </c>
-      <c r="E208" s="2" t="n">
+      <c r="G208" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F208" t="n">
+      <c r="H208" t="n">
         <v>5.7</v>
       </c>
-      <c r="G208" s="2" t="n">
+      <c r="I208" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H208" t="n">
+      <c r="J208" t="n">
         <v>6</v>
       </c>
-      <c r="I208" s="2" t="n">
+      <c r="K208" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J208" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K208" s="2" t="n">
+      <c r="L208" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M208" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="L208" t="n">
+      <c r="N208" t="n">
         <v>7.9</v>
       </c>
-      <c r="M208" s="2" t="n">
+      <c r="O208" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N208" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O208" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P208" t="n">
-        <v>6.64</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="209">
@@ -9893,49 +9905,49 @@
         <v>351</v>
       </c>
       <c r="B217" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C217" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D217" t="n">
         <v>7.5</v>
       </c>
-      <c r="C217" s="2" t="n">
+      <c r="E217" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="D217" t="n">
+      <c r="F217" t="n">
         <v>7.3</v>
       </c>
-      <c r="E217" s="2" t="n">
+      <c r="G217" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="F217" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G217" s="2" t="n">
+      <c r="H217" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I217" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="H217" t="n">
+      <c r="J217" t="n">
         <v>5.8</v>
       </c>
-      <c r="I217" s="2" t="n">
+      <c r="K217" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="J217" t="n">
+      <c r="L217" t="n">
         <v>6.8</v>
       </c>
-      <c r="K217" s="2" t="n">
+      <c r="M217" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="L217" t="n">
+      <c r="N217" t="n">
         <v>7.3</v>
       </c>
-      <c r="M217" s="2" t="n">
+      <c r="O217" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="N217" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O217" s="2" t="n">
-        <v>45970</v>
-      </c>
       <c r="P217" t="n">
-        <v>6.79</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="218">
@@ -9963,49 +9975,49 @@
         <v>353</v>
       </c>
       <c r="B219" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C219" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D219" t="n">
         <v>6</v>
       </c>
-      <c r="C219" s="2" t="n">
+      <c r="E219" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D219" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E219" s="2" t="n">
+      <c r="F219" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G219" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F219" t="n">
+      <c r="H219" t="n">
         <v>7.1</v>
       </c>
-      <c r="G219" s="2" t="n">
+      <c r="I219" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="H219" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I219" s="2" t="n">
+      <c r="J219" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K219" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="J219" t="n">
+      <c r="L219" t="n">
         <v>6.4</v>
       </c>
-      <c r="K219" s="2" t="n">
+      <c r="M219" s="2" t="n">
         <v>46100</v>
       </c>
-      <c r="L219" t="n">
+      <c r="N219" t="n">
         <v>7.1</v>
       </c>
-      <c r="M219" s="2" t="n">
+      <c r="O219" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="N219" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O219" s="2" t="n">
-        <v>46081</v>
-      </c>
       <c r="P219" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="220">
@@ -10085,49 +10097,49 @@
         <v>357</v>
       </c>
       <c r="B222" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C222" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D222" t="n">
         <v>7.2</v>
       </c>
-      <c r="C222" s="2" t="n">
+      <c r="E222" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D222" t="n">
+      <c r="F222" t="n">
         <v>6.9</v>
       </c>
-      <c r="E222" s="2" t="n">
+      <c r="G222" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F222" t="n">
+      <c r="H222" t="n">
         <v>6.4</v>
       </c>
-      <c r="G222" s="2" t="n">
+      <c r="I222" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H222" t="n">
+      <c r="J222" t="n">
         <v>5.8</v>
       </c>
-      <c r="I222" s="2" t="n">
+      <c r="K222" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="J222" t="n">
+      <c r="L222" t="n">
         <v>6.9</v>
       </c>
-      <c r="K222" s="2" t="n">
+      <c r="M222" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="L222" t="n">
+      <c r="N222" t="n">
         <v>7.5</v>
       </c>
-      <c r="M222" s="2" t="n">
+      <c r="O222" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="N222" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O222" s="2" t="n">
-        <v>46074</v>
-      </c>
       <c r="P222" t="n">
-        <v>6.83</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="223">
@@ -10185,49 +10197,49 @@
         <v>360</v>
       </c>
       <c r="B224" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C224" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D224" t="n">
         <v>6.8</v>
       </c>
-      <c r="C224" s="2" t="n">
+      <c r="E224" s="2" t="n">
         <v>46128</v>
-      </c>
-      <c r="D224" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E224" s="2" t="n">
-        <v>46123</v>
       </c>
       <c r="F224" t="n">
         <v>6.9</v>
       </c>
       <c r="G224" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="H224" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I224" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="H224" t="n">
+      <c r="J224" t="n">
         <v>6.3</v>
       </c>
-      <c r="I224" s="2" t="n">
+      <c r="K224" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="J224" t="n">
+      <c r="L224" t="n">
         <v>6.9</v>
       </c>
-      <c r="K224" s="2" t="n">
+      <c r="M224" s="2" t="n">
         <v>46086</v>
-      </c>
-      <c r="L224" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="M224" s="2" t="n">
-        <v>46069</v>
       </c>
       <c r="N224" t="n">
         <v>7.2</v>
       </c>
       <c r="O224" s="2" t="n">
-        <v>46061</v>
+        <v>46069</v>
       </c>
       <c r="P224" t="n">
-        <v>6.89</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="225">
@@ -10285,13 +10297,17 @@
         <v>364</v>
       </c>
       <c r="B226" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C226" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D226" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E226" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
@@ -10303,7 +10319,7 @@
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="n">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="227">
@@ -10311,49 +10327,49 @@
         <v>365</v>
       </c>
       <c r="B227" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C227" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D227" t="n">
         <v>7.1</v>
       </c>
-      <c r="C227" s="2" t="n">
+      <c r="E227" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D227" t="n">
+      <c r="F227" t="n">
         <v>6.3</v>
       </c>
-      <c r="E227" s="2" t="n">
+      <c r="G227" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="F227" t="n">
+      <c r="H227" t="n">
         <v>6.2</v>
       </c>
-      <c r="G227" s="2" t="n">
+      <c r="I227" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="H227" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I227" s="2" t="n">
+      <c r="J227" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K227" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="J227" t="n">
+      <c r="L227" t="n">
         <v>7</v>
       </c>
-      <c r="K227" s="2" t="n">
+      <c r="M227" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="L227" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M227" s="2" t="n">
+      <c r="N227" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O227" s="2" t="n">
         <v>45884</v>
       </c>
-      <c r="N227" t="n">
-        <v>7</v>
-      </c>
-      <c r="O227" s="2" t="n">
-        <v>45879</v>
-      </c>
       <c r="P227" t="n">
-        <v>6.67</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="228">
@@ -10461,49 +10477,49 @@
         <v>369</v>
       </c>
       <c r="B230" t="n">
+        <v>7</v>
+      </c>
+      <c r="C230" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D230" t="n">
         <v>6.1</v>
       </c>
-      <c r="C230" s="2" t="n">
+      <c r="E230" s="2" t="n">
         <v>46139</v>
-      </c>
-      <c r="D230" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E230" s="2" t="n">
-        <v>46134</v>
       </c>
       <c r="F230" t="n">
         <v>6.9</v>
       </c>
       <c r="G230" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="H230" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I230" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H230" t="n">
+      <c r="J230" t="n">
         <v>5.9</v>
       </c>
-      <c r="I230" s="2" t="n">
+      <c r="K230" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="J230" t="n">
+      <c r="L230" t="n">
         <v>6.8</v>
       </c>
-      <c r="K230" s="2" t="n">
+      <c r="M230" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="L230" t="n">
+      <c r="N230" t="n">
         <v>7.2</v>
       </c>
-      <c r="M230" s="2" t="n">
+      <c r="O230" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="N230" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O230" s="2" t="n">
-        <v>46097</v>
-      </c>
       <c r="P230" t="n">
-        <v>6.8</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="231">
@@ -10511,49 +10527,49 @@
         <v>370</v>
       </c>
       <c r="B231" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C231" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D231" t="n">
         <v>7</v>
       </c>
-      <c r="C231" s="2" t="n">
+      <c r="E231" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D231" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E231" s="2" t="n">
+      <c r="F231" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G231" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F231" t="n">
+      <c r="H231" t="n">
         <v>7.1</v>
       </c>
-      <c r="G231" s="2" t="n">
+      <c r="I231" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="H231" t="n">
+      <c r="J231" t="n">
         <v>6.2</v>
       </c>
-      <c r="I231" s="2" t="n">
+      <c r="K231" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="J231" t="n">
+      <c r="L231" t="n">
         <v>6.8</v>
       </c>
-      <c r="K231" s="2" t="n">
+      <c r="M231" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L231" t="n">
+      <c r="N231" t="n">
         <v>7.5</v>
       </c>
-      <c r="M231" s="2" t="n">
+      <c r="O231" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="N231" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O231" s="2" t="n">
-        <v>46089</v>
-      </c>
       <c r="P231" t="n">
-        <v>6.86</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="232">
@@ -10561,49 +10577,49 @@
         <v>371</v>
       </c>
       <c r="B232" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C232" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D232" t="n">
         <v>7.6</v>
       </c>
-      <c r="C232" s="2" t="n">
+      <c r="E232" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D232" t="n">
+      <c r="F232" t="n">
         <v>6.4</v>
       </c>
-      <c r="E232" s="2" t="n">
+      <c r="G232" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F232" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G232" s="2" t="n">
+      <c r="H232" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I232" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="H232" t="n">
+      <c r="J232" t="n">
         <v>6.2</v>
       </c>
-      <c r="I232" s="2" t="n">
+      <c r="K232" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J232" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K232" s="2" t="n">
+      <c r="L232" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M232" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L232" t="n">
+      <c r="N232" t="n">
         <v>6.4</v>
       </c>
-      <c r="M232" s="2" t="n">
+      <c r="O232" s="2" t="n">
         <v>45998</v>
       </c>
-      <c r="N232" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O232" s="2" t="n">
-        <v>45991</v>
-      </c>
       <c r="P232" t="n">
-        <v>6.63</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="233">
@@ -10711,41 +10727,45 @@
         <v>374</v>
       </c>
       <c r="B235" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C235" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D235" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="C235" s="2" t="n">
+      <c r="E235" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D235" t="n">
+      <c r="F235" t="n">
         <v>7.3</v>
       </c>
-      <c r="E235" s="2" t="n">
+      <c r="G235" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F235" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G235" s="2" t="n">
+      <c r="H235" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I235" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H235" t="n">
+      <c r="J235" t="n">
         <v>6.8</v>
       </c>
-      <c r="I235" s="2" t="n">
+      <c r="K235" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="J235" t="n">
+      <c r="L235" t="n">
         <v>6.1</v>
       </c>
-      <c r="K235" s="2" t="n">
+      <c r="M235" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="n">
-        <v>7.18</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="236">
@@ -10773,49 +10793,49 @@
         <v>376</v>
       </c>
       <c r="B237" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="C237" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D237" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E237" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D237" t="n">
+      <c r="F237" t="n">
         <v>5.8</v>
       </c>
-      <c r="E237" s="2" t="n">
+      <c r="G237" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="F237" t="n">
+      <c r="H237" t="n">
         <v>7.8</v>
       </c>
-      <c r="G237" s="2" t="n">
+      <c r="I237" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H237" t="n">
+      <c r="J237" t="n">
         <v>6.8</v>
       </c>
-      <c r="I237" s="2" t="n">
+      <c r="K237" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="J237" t="n">
+      <c r="L237" t="n">
         <v>7.4</v>
       </c>
-      <c r="K237" s="2" t="n">
+      <c r="M237" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="L237" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M237" s="2" t="n">
+      <c r="N237" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O237" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="N237" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O237" s="2" t="n">
-        <v>46076</v>
-      </c>
       <c r="P237" t="n">
-        <v>6.77</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="238">
@@ -10863,49 +10883,49 @@
         <v>379</v>
       </c>
       <c r="B240" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C240" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D240" t="n">
         <v>6.8</v>
       </c>
-      <c r="C240" s="2" t="n">
+      <c r="E240" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="D240" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E240" s="2" t="n">
+      <c r="F240" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G240" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="F240" t="n">
+      <c r="H240" t="n">
         <v>6.9</v>
       </c>
-      <c r="G240" s="2" t="n">
+      <c r="I240" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="H240" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I240" s="2" t="n">
+      <c r="J240" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K240" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="J240" t="n">
+      <c r="L240" t="n">
         <v>6.4</v>
       </c>
-      <c r="K240" s="2" t="n">
+      <c r="M240" s="2" t="n">
         <v>46058</v>
       </c>
-      <c r="L240" t="n">
+      <c r="N240" t="n">
         <v>6.8</v>
       </c>
-      <c r="M240" s="2" t="n">
+      <c r="O240" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="N240" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O240" s="2" t="n">
-        <v>46041</v>
-      </c>
       <c r="P240" t="n">
-        <v>6.84</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="241">
@@ -10913,49 +10933,49 @@
         <v>380</v>
       </c>
       <c r="B241" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C241" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D241" t="n">
         <v>7.4</v>
       </c>
-      <c r="C241" s="2" t="n">
+      <c r="E241" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D241" t="n">
+      <c r="F241" t="n">
         <v>6.4</v>
       </c>
-      <c r="E241" s="2" t="n">
+      <c r="G241" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F241" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G241" s="2" t="n">
+      <c r="H241" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I241" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H241" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I241" s="2" t="n">
+      <c r="J241" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K241" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="J241" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K241" s="2" t="n">
+      <c r="L241" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M241" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L241" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M241" s="2" t="n">
+      <c r="N241" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O241" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="N241" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O241" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="P241" t="n">
-        <v>6.61</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="242">
@@ -11133,37 +11153,41 @@
         <v>386</v>
       </c>
       <c r="B246" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="C246" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D246" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E246" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="D246" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E246" s="2" t="n">
+      <c r="F246" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G246" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F246" t="n">
+      <c r="H246" t="n">
         <v>6.8</v>
       </c>
-      <c r="G246" s="2" t="n">
+      <c r="I246" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="H246" t="n">
+      <c r="J246" t="n">
         <v>6.4</v>
       </c>
-      <c r="I246" s="2" t="n">
+      <c r="K246" s="2" t="n">
         <v>45879</v>
       </c>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="n">
-        <v>6.62</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="247">
@@ -11334,42 +11358,46 @@
         <v>6.9</v>
       </c>
       <c r="C252" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D252" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E252" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D252" t="n">
+      <c r="F252" t="n">
         <v>6.1</v>
       </c>
-      <c r="E252" s="2" t="n">
+      <c r="G252" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F252" t="n">
+      <c r="H252" t="n">
         <v>6.9</v>
       </c>
-      <c r="G252" s="2" t="n">
+      <c r="I252" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H252" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I252" s="2" t="n">
+      <c r="J252" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K252" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J252" t="n">
+      <c r="L252" t="n">
         <v>7.3</v>
       </c>
-      <c r="K252" s="2" t="n">
+      <c r="M252" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="L252" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M252" s="2" t="n">
+      <c r="N252" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O252" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="N252" t="inlineStr"/>
-      <c r="O252" t="inlineStr"/>
       <c r="P252" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="253">
@@ -11953,49 +11981,49 @@
         <v>409</v>
       </c>
       <c r="B268" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C268" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D268" t="n">
         <v>6.1</v>
       </c>
-      <c r="C268" s="2" t="n">
+      <c r="E268" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D268" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E268" s="2" t="n">
+      <c r="F268" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G268" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F268" t="n">
+      <c r="H268" t="n">
         <v>6.8</v>
       </c>
-      <c r="G268" s="2" t="n">
+      <c r="I268" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H268" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I268" s="2" t="n">
+      <c r="J268" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K268" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J268" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K268" s="2" t="n">
+      <c r="L268" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M268" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="L268" t="n">
+      <c r="N268" t="n">
         <v>6.8</v>
       </c>
-      <c r="M268" s="2" t="n">
+      <c r="O268" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N268" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O268" s="2" t="n">
-        <v>46088</v>
-      </c>
       <c r="P268" t="n">
-        <v>6.57</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="269">
@@ -12269,49 +12297,49 @@
         <v>416</v>
       </c>
       <c r="B275" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="C275" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D275" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E275" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="D275" t="n">
+      <c r="F275" t="n">
         <v>6.4</v>
       </c>
-      <c r="E275" s="2" t="n">
+      <c r="G275" s="2" t="n">
         <v>46131</v>
-      </c>
-      <c r="F275" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G275" s="2" t="n">
-        <v>46122</v>
       </c>
       <c r="H275" t="n">
         <v>6.3</v>
       </c>
       <c r="I275" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="J275" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K275" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J275" t="n">
+      <c r="L275" t="n">
         <v>7.6</v>
       </c>
-      <c r="K275" s="2" t="n">
+      <c r="M275" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="L275" t="n">
+      <c r="N275" t="n">
         <v>6.3</v>
       </c>
-      <c r="M275" s="2" t="n">
+      <c r="O275" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N275" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O275" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="P275" t="n">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="276">
@@ -12319,49 +12347,49 @@
         <v>417</v>
       </c>
       <c r="B276" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C276" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D276" t="n">
         <v>6.4</v>
       </c>
-      <c r="C276" s="2" t="n">
+      <c r="E276" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="D276" t="n">
+      <c r="F276" t="n">
         <v>6.9</v>
       </c>
-      <c r="E276" s="2" t="n">
+      <c r="G276" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="F276" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G276" s="2" t="n">
+      <c r="H276" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I276" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="H276" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I276" s="2" t="n">
+      <c r="J276" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K276" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="J276" t="n">
+      <c r="L276" t="n">
         <v>8</v>
       </c>
-      <c r="K276" s="2" t="n">
+      <c r="M276" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="L276" t="n">
+      <c r="N276" t="n">
         <v>7.1</v>
       </c>
-      <c r="M276" s="2" t="n">
+      <c r="O276" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N276" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O276" s="2" t="n">
-        <v>46087</v>
-      </c>
       <c r="P276" t="n">
-        <v>6.9</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="277">
@@ -12369,49 +12397,49 @@
         <v>418</v>
       </c>
       <c r="B277" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="C277" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D277" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E277" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D277" t="n">
+      <c r="F277" t="n">
         <v>5.5</v>
       </c>
-      <c r="E277" s="2" t="n">
+      <c r="G277" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="F277" t="n">
+      <c r="H277" t="n">
         <v>7.1</v>
       </c>
-      <c r="G277" s="2" t="n">
+      <c r="I277" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="H277" t="n">
+      <c r="J277" t="n">
         <v>7.7</v>
       </c>
-      <c r="I277" s="2" t="n">
+      <c r="K277" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="J277" t="n">
+      <c r="L277" t="n">
         <v>6.3</v>
       </c>
-      <c r="K277" s="2" t="n">
+      <c r="M277" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="L277" t="n">
+      <c r="N277" t="n">
         <v>7.2</v>
       </c>
-      <c r="M277" s="2" t="n">
+      <c r="O277" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N277" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O277" s="2" t="n">
-        <v>46089</v>
-      </c>
       <c r="P277" t="n">
-        <v>6.7</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="278">
@@ -12767,49 +12795,49 @@
         <v>428</v>
       </c>
       <c r="B287" t="n">
+        <v>8</v>
+      </c>
+      <c r="C287" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D287" t="n">
         <v>6.2</v>
       </c>
-      <c r="C287" s="2" t="n">
+      <c r="E287" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D287" t="n">
+      <c r="F287" t="n">
         <v>6.3</v>
       </c>
-      <c r="E287" s="2" t="n">
+      <c r="G287" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F287" t="n">
+      <c r="H287" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G287" s="2" t="n">
+      <c r="I287" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H287" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I287" s="2" t="n">
+      <c r="J287" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K287" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="J287" t="n">
+      <c r="L287" t="n">
         <v>7.3</v>
       </c>
-      <c r="K287" s="2" t="n">
+      <c r="M287" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="L287" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M287" s="2" t="n">
+      <c r="N287" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O287" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N287" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O287" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P287" t="n">
-        <v>6.77</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="288">
@@ -13159,49 +13187,49 @@
         <v>439</v>
       </c>
       <c r="B296" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="C296" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D296" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E296" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="D296" t="n">
+      <c r="F296" t="n">
         <v>7.4</v>
       </c>
-      <c r="E296" s="2" t="n">
+      <c r="G296" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F296" t="n">
+      <c r="H296" t="n">
         <v>7</v>
       </c>
-      <c r="G296" s="2" t="n">
+      <c r="I296" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H296" t="n">
+      <c r="J296" t="n">
         <v>7.3</v>
       </c>
-      <c r="I296" s="2" t="n">
+      <c r="K296" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J296" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K296" s="2" t="n">
+      <c r="L296" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M296" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L296" t="n">
+      <c r="N296" t="n">
         <v>7.6</v>
       </c>
-      <c r="M296" s="2" t="n">
+      <c r="O296" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="N296" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O296" s="2" t="n">
-        <v>46081</v>
-      </c>
       <c r="P296" t="n">
-        <v>7.07</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="297">
@@ -13259,25 +13287,29 @@
         <v>442</v>
       </c>
       <c r="B298" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C298" s="2" t="n">
-        <v>46123</v>
+        <v>46143</v>
       </c>
       <c r="D298" t="n">
         <v>6.4</v>
       </c>
       <c r="E298" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="F298" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G298" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="F298" t="n">
+      <c r="H298" t="n">
         <v>6.2</v>
       </c>
-      <c r="G298" s="2" t="n">
+      <c r="I298" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H298" t="inlineStr"/>
-      <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr"/>
@@ -13285,7 +13317,7 @@
       <c r="N298" t="inlineStr"/>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="n">
-        <v>6.33</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="299">
@@ -13841,49 +13873,49 @@
         <v>458</v>
       </c>
       <c r="B312" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C312" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="D312" t="n">
         <v>6.3</v>
       </c>
-      <c r="C312" s="2" t="n">
+      <c r="E312" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="D312" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E312" s="2" t="n">
+      <c r="F312" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G312" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F312" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G312" s="2" t="n">
+      <c r="H312" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I312" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="H312" t="n">
+      <c r="J312" t="n">
         <v>6.4</v>
       </c>
-      <c r="I312" s="2" t="n">
+      <c r="K312" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="J312" t="n">
+      <c r="L312" t="n">
         <v>6.8</v>
       </c>
-      <c r="K312" s="2" t="n">
+      <c r="M312" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="L312" t="n">
+      <c r="N312" t="n">
         <v>6.3</v>
       </c>
-      <c r="M312" s="2" t="n">
+      <c r="O312" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="N312" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O312" s="2" t="n">
-        <v>46068</v>
-      </c>
       <c r="P312" t="n">
-        <v>6.59</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="313">
@@ -13891,49 +13923,49 @@
         <v>459</v>
       </c>
       <c r="B313" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C313" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="D313" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E313" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="D313" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E313" s="2" t="n">
+      <c r="F313" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G313" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="F313" t="n">
+      <c r="H313" t="n">
         <v>6.9</v>
       </c>
-      <c r="G313" s="2" t="n">
+      <c r="I313" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H313" t="n">
+      <c r="J313" t="n">
         <v>7.2</v>
       </c>
-      <c r="I313" s="2" t="n">
+      <c r="K313" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="J313" t="n">
+      <c r="L313" t="n">
         <v>8</v>
       </c>
-      <c r="K313" s="2" t="n">
+      <c r="M313" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="L313" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M313" s="2" t="n">
+      <c r="N313" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O313" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="N313" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O313" s="2" t="n">
-        <v>45998</v>
-      </c>
       <c r="P313" t="n">
-        <v>7.04</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="314">
@@ -14217,49 +14249,49 @@
         <v>466</v>
       </c>
       <c r="B320" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C320" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D320" t="n">
         <v>7.3</v>
       </c>
-      <c r="C320" s="2" t="n">
+      <c r="E320" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D320" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E320" s="2" t="n">
+      <c r="F320" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G320" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="F320" t="n">
+      <c r="H320" t="n">
         <v>7.9</v>
       </c>
-      <c r="G320" s="2" t="n">
+      <c r="I320" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="H320" t="n">
+      <c r="J320" t="n">
         <v>6.2</v>
       </c>
-      <c r="I320" s="2" t="n">
+      <c r="K320" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J320" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K320" s="2" t="n">
+      <c r="L320" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M320" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L320" t="n">
+      <c r="N320" t="n">
         <v>7</v>
       </c>
-      <c r="M320" s="2" t="n">
+      <c r="O320" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N320" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O320" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P320" t="n">
-        <v>6.9</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="321">
@@ -14267,49 +14299,49 @@
         <v>467</v>
       </c>
       <c r="B321" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C321" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D321" t="n">
         <v>7</v>
       </c>
-      <c r="C321" s="2" t="n">
+      <c r="E321" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D321" t="n">
+      <c r="F321" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="E321" s="2" t="n">
+      <c r="G321" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="F321" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G321" s="2" t="n">
+      <c r="H321" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I321" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H321" t="n">
+      <c r="J321" t="n">
         <v>7.2</v>
       </c>
-      <c r="I321" s="2" t="n">
+      <c r="K321" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="J321" t="n">
+      <c r="L321" t="n">
         <v>6.4</v>
       </c>
-      <c r="K321" s="2" t="n">
+      <c r="M321" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="L321" t="n">
+      <c r="N321" t="n">
         <v>7.5</v>
       </c>
-      <c r="M321" s="2" t="n">
+      <c r="O321" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="N321" t="n">
-        <v>7</v>
-      </c>
-      <c r="O321" s="2" t="n">
-        <v>46081</v>
-      </c>
       <c r="P321" t="n">
-        <v>7.14</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="322">
@@ -14317,49 +14349,49 @@
         <v>468</v>
       </c>
       <c r="B322" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="C322" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D322" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E322" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="F322" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G322" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="D322" t="n">
+      <c r="H322" t="n">
         <v>6.9</v>
       </c>
-      <c r="E322" s="2" t="n">
+      <c r="I322" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F322" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G322" s="2" t="n">
+      <c r="J322" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K322" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="H322" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I322" s="2" t="n">
+      <c r="L322" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M322" s="2" t="n">
         <v>46089</v>
-      </c>
-      <c r="J322" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K322" s="2" t="n">
-        <v>46074</v>
-      </c>
-      <c r="L322" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M322" s="2" t="n">
-        <v>46068</v>
       </c>
       <c r="N322" t="n">
         <v>6.2</v>
       </c>
       <c r="O322" s="2" t="n">
-        <v>46059</v>
+        <v>46074</v>
       </c>
       <c r="P322" t="n">
-        <v>6.57</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="323">
@@ -14935,46 +14967,46 @@
         <v>484</v>
       </c>
       <c r="B338" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C338" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D338" t="n">
         <v>6.4</v>
       </c>
-      <c r="C338" s="2" t="n">
+      <c r="E338" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D338" t="n">
+      <c r="F338" t="n">
         <v>6</v>
       </c>
-      <c r="E338" s="2" t="n">
+      <c r="G338" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F338" t="n">
+      <c r="H338" t="n">
         <v>6.4</v>
       </c>
-      <c r="G338" s="2" t="n">
+      <c r="I338" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H338" t="n">
+      <c r="J338" t="n">
         <v>6.9</v>
       </c>
-      <c r="I338" s="2" t="n">
+      <c r="K338" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="J338" t="n">
+      <c r="L338" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K338" s="2" t="n">
+      <c r="M338" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L338" t="n">
+      <c r="N338" t="n">
         <v>7</v>
       </c>
-      <c r="M338" s="2" t="n">
+      <c r="O338" s="2" t="n">
         <v>46102</v>
-      </c>
-      <c r="N338" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O338" s="2" t="n">
-        <v>46094</v>
       </c>
       <c r="P338" t="n">
         <v>6.8</v>
@@ -14985,49 +15017,49 @@
         <v>485</v>
       </c>
       <c r="B339" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="C339" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D339" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E339" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D339" t="n">
+      <c r="F339" t="n">
         <v>6.4</v>
       </c>
-      <c r="E339" s="2" t="n">
+      <c r="G339" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F339" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G339" s="2" t="n">
+      <c r="H339" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I339" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H339" t="n">
+      <c r="J339" t="n">
         <v>6.1</v>
       </c>
-      <c r="I339" s="2" t="n">
+      <c r="K339" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="J339" t="n">
+      <c r="L339" t="n">
         <v>7.4</v>
       </c>
-      <c r="K339" s="2" t="n">
+      <c r="M339" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="L339" t="n">
+      <c r="N339" t="n">
         <v>7.3</v>
       </c>
-      <c r="M339" s="2" t="n">
+      <c r="O339" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="N339" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O339" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P339" t="n">
-        <v>6.86</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="340">
@@ -15035,49 +15067,49 @@
         <v>486</v>
       </c>
       <c r="B340" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C340" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D340" t="n">
         <v>6.3</v>
       </c>
-      <c r="C340" s="2" t="n">
+      <c r="E340" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D340" t="n">
+      <c r="F340" t="n">
         <v>6.2</v>
       </c>
-      <c r="E340" s="2" t="n">
+      <c r="G340" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F340" t="n">
+      <c r="H340" t="n">
         <v>6.3</v>
       </c>
-      <c r="G340" s="2" t="n">
+      <c r="I340" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="H340" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I340" s="2" t="n">
+      <c r="J340" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K340" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="J340" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K340" s="2" t="n">
+      <c r="L340" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M340" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="L340" t="n">
+      <c r="N340" t="n">
         <v>6.3</v>
       </c>
-      <c r="M340" s="2" t="n">
+      <c r="O340" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="N340" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O340" s="2" t="n">
-        <v>46073</v>
-      </c>
       <c r="P340" t="n">
-        <v>6.53</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="341">
@@ -15085,49 +15117,49 @@
         <v>487</v>
       </c>
       <c r="B341" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C341" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D341" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E341" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="D341" t="n">
+      <c r="F341" t="n">
         <v>6.9</v>
       </c>
-      <c r="E341" s="2" t="n">
+      <c r="G341" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="F341" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G341" s="2" t="n">
+      <c r="H341" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I341" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="H341" t="n">
+      <c r="J341" t="n">
         <v>6.8</v>
       </c>
-      <c r="I341" s="2" t="n">
+      <c r="K341" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="J341" t="n">
+      <c r="L341" t="n">
         <v>6.1</v>
       </c>
-      <c r="K341" s="2" t="n">
+      <c r="M341" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="L341" t="n">
+      <c r="N341" t="n">
         <v>6.3</v>
       </c>
-      <c r="M341" s="2" t="n">
+      <c r="O341" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="N341" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O341" s="2" t="n">
-        <v>46066</v>
-      </c>
       <c r="P341" t="n">
-        <v>6.51</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="342">
@@ -15138,46 +15170,46 @@
         <v>6.3</v>
       </c>
       <c r="C342" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D342" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E342" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D342" t="n">
+      <c r="F342" t="n">
         <v>6.4</v>
       </c>
-      <c r="E342" s="2" t="n">
+      <c r="G342" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F342" t="n">
+      <c r="H342" t="n">
         <v>6.8</v>
       </c>
-      <c r="G342" s="2" t="n">
+      <c r="I342" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="H342" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I342" s="2" t="n">
+      <c r="J342" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K342" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="J342" t="n">
+      <c r="L342" t="n">
         <v>6.4</v>
       </c>
-      <c r="K342" s="2" t="n">
+      <c r="M342" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="L342" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M342" s="2" t="n">
+      <c r="N342" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O342" s="2" t="n">
         <v>45963</v>
       </c>
-      <c r="N342" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O342" s="2" t="n">
-        <v>45956</v>
-      </c>
       <c r="P342" t="n">
-        <v>6.63</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="343">
@@ -15285,49 +15317,49 @@
         <v>491</v>
       </c>
       <c r="B345" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C345" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="D345" t="n">
         <v>6.8</v>
       </c>
-      <c r="C345" s="2" t="n">
+      <c r="E345" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D345" t="n">
+      <c r="F345" t="n">
         <v>6.4</v>
       </c>
-      <c r="E345" s="2" t="n">
+      <c r="G345" s="2" t="n">
         <v>45968</v>
       </c>
-      <c r="F345" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G345" s="2" t="n">
+      <c r="H345" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I345" s="2" t="n">
         <v>45954</v>
-      </c>
-      <c r="H345" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I345" s="2" t="n">
-        <v>45948</v>
       </c>
       <c r="J345" t="n">
         <v>7.1</v>
       </c>
       <c r="K345" s="2" t="n">
+        <v>45948</v>
+      </c>
+      <c r="L345" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M345" s="2" t="n">
         <v>45933</v>
       </c>
-      <c r="L345" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M345" s="2" t="n">
+      <c r="N345" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O345" s="2" t="n">
         <v>45927</v>
       </c>
-      <c r="N345" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O345" s="2" t="n">
-        <v>45920</v>
-      </c>
       <c r="P345" t="n">
-        <v>6.83</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="346">
@@ -15335,49 +15367,49 @@
         <v>492</v>
       </c>
       <c r="B346" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C346" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="D346" t="n">
         <v>6.2</v>
       </c>
-      <c r="C346" s="2" t="n">
+      <c r="E346" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D346" t="n">
+      <c r="F346" t="n">
         <v>7.2</v>
       </c>
-      <c r="E346" s="2" t="n">
+      <c r="G346" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="F346" t="n">
+      <c r="H346" t="n">
         <v>6.9</v>
       </c>
-      <c r="G346" s="2" t="n">
+      <c r="I346" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="H346" t="n">
+      <c r="J346" t="n">
         <v>7.2</v>
       </c>
-      <c r="I346" s="2" t="n">
+      <c r="K346" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J346" t="n">
+      <c r="L346" t="n">
         <v>7.6</v>
       </c>
-      <c r="K346" s="2" t="n">
+      <c r="M346" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L346" t="n">
+      <c r="N346" t="n">
         <v>5.8</v>
       </c>
-      <c r="M346" s="2" t="n">
+      <c r="O346" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N346" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O346" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P346" t="n">
-        <v>6.83</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="347">
@@ -15388,43 +15420,43 @@
         <v>6.5</v>
       </c>
       <c r="C347" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="D347" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E347" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="D347" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E347" s="2" t="n">
+      <c r="F347" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G347" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="F347" t="n">
+      <c r="H347" t="n">
         <v>6.2</v>
       </c>
-      <c r="G347" s="2" t="n">
+      <c r="I347" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="H347" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I347" s="2" t="n">
+      <c r="J347" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K347" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J347" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K347" s="2" t="n">
+      <c r="L347" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M347" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="L347" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M347" s="2" t="n">
+      <c r="N347" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O347" s="2" t="n">
         <v>45990</v>
-      </c>
-      <c r="N347" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O347" s="2" t="n">
-        <v>45982</v>
       </c>
       <c r="P347" t="n">
         <v>6.5</v>
@@ -15435,49 +15467,49 @@
         <v>494</v>
       </c>
       <c r="B348" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C348" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D348" t="n">
         <v>7</v>
       </c>
-      <c r="C348" s="2" t="n">
+      <c r="E348" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D348" t="n">
+      <c r="F348" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="E348" s="2" t="n">
+      <c r="G348" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="F348" t="n">
+      <c r="H348" t="n">
         <v>7.8</v>
       </c>
-      <c r="G348" s="2" t="n">
+      <c r="I348" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H348" t="n">
+      <c r="J348" t="n">
         <v>6.8</v>
       </c>
-      <c r="I348" s="2" t="n">
+      <c r="K348" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="J348" t="n">
+      <c r="L348" t="n">
         <v>7.2</v>
       </c>
-      <c r="K348" s="2" t="n">
+      <c r="M348" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L348" t="n">
+      <c r="N348" t="n">
         <v>7</v>
       </c>
-      <c r="M348" s="2" t="n">
+      <c r="O348" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="N348" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O348" s="2" t="n">
-        <v>46088</v>
-      </c>
       <c r="P348" t="n">
-        <v>7.36</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="349">
@@ -15911,46 +15943,46 @@
         <v>507</v>
       </c>
       <c r="B360" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C360" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D360" t="n">
         <v>6.3</v>
       </c>
-      <c r="C360" s="2" t="n">
+      <c r="E360" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D360" t="n">
+      <c r="F360" t="n">
         <v>6.2</v>
       </c>
-      <c r="E360" s="2" t="n">
+      <c r="G360" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F360" t="n">
+      <c r="H360" t="n">
         <v>7.6</v>
       </c>
-      <c r="G360" s="2" t="n">
+      <c r="I360" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H360" t="n">
+      <c r="J360" t="n">
         <v>6.3</v>
       </c>
-      <c r="I360" s="2" t="n">
+      <c r="K360" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="J360" t="n">
+      <c r="L360" t="n">
         <v>6.8</v>
       </c>
-      <c r="K360" s="2" t="n">
+      <c r="M360" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="L360" t="n">
+      <c r="N360" t="n">
         <v>6.3</v>
       </c>
-      <c r="M360" s="2" t="n">
+      <c r="O360" s="2" t="n">
         <v>46102</v>
-      </c>
-      <c r="N360" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O360" s="2" t="n">
-        <v>46094</v>
       </c>
       <c r="P360" t="n">
         <v>6.6</v>
@@ -16061,49 +16093,49 @@
         <v>510</v>
       </c>
       <c r="B363" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C363" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D363" t="n">
         <v>6.3</v>
       </c>
-      <c r="C363" s="2" t="n">
+      <c r="E363" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D363" t="n">
+      <c r="F363" t="n">
         <v>6.8</v>
       </c>
-      <c r="E363" s="2" t="n">
+      <c r="G363" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="F363" t="n">
+      <c r="H363" t="n">
         <v>7.2</v>
       </c>
-      <c r="G363" s="2" t="n">
+      <c r="I363" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="H363" t="n">
+      <c r="J363" t="n">
         <v>7</v>
       </c>
-      <c r="I363" s="2" t="n">
+      <c r="K363" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J363" t="n">
+      <c r="L363" t="n">
         <v>6.9</v>
       </c>
-      <c r="K363" s="2" t="n">
+      <c r="M363" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="L363" t="n">
+      <c r="N363" t="n">
         <v>6.4</v>
       </c>
-      <c r="M363" s="2" t="n">
+      <c r="O363" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N363" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O363" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P363" t="n">
-        <v>6.67</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="364">
@@ -16215,49 +16247,49 @@
         <v>514</v>
       </c>
       <c r="B367" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="C367" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D367" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E367" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="D367" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E367" s="2" t="n">
+      <c r="F367" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G367" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="F367" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G367" s="2" t="n">
+      <c r="H367" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I367" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H367" t="n">
+      <c r="J367" t="n">
         <v>6.4</v>
       </c>
-      <c r="I367" s="2" t="n">
+      <c r="K367" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J367" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K367" s="2" t="n">
+      <c r="L367" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M367" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="L367" t="n">
+      <c r="N367" t="n">
         <v>6.3</v>
       </c>
-      <c r="M367" s="2" t="n">
+      <c r="O367" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="N367" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O367" s="2" t="n">
-        <v>46059</v>
-      </c>
       <c r="P367" t="n">
-        <v>6.57</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="368">
@@ -16393,49 +16425,49 @@
         <v>520</v>
       </c>
       <c r="B373" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C373" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D373" t="n">
         <v>7.4</v>
       </c>
-      <c r="C373" s="2" t="n">
+      <c r="E373" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D373" t="n">
+      <c r="F373" t="n">
         <v>7</v>
       </c>
-      <c r="E373" s="2" t="n">
+      <c r="G373" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F373" t="n">
+      <c r="H373" t="n">
         <v>7.3</v>
       </c>
-      <c r="G373" s="2" t="n">
+      <c r="I373" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="H373" t="n">
+      <c r="J373" t="n">
         <v>7.1</v>
       </c>
-      <c r="I373" s="2" t="n">
+      <c r="K373" s="2" t="n">
         <v>46117</v>
-      </c>
-      <c r="J373" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K373" s="2" t="n">
-        <v>46103</v>
       </c>
       <c r="L373" t="n">
         <v>6.8</v>
       </c>
       <c r="M373" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="N373" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O373" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N373" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O373" s="2" t="n">
-        <v>46089</v>
-      </c>
       <c r="P373" t="n">
-        <v>7.09</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="374">
@@ -16443,46 +16475,46 @@
         <v>521</v>
       </c>
       <c r="B374" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C374" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D374" t="n">
         <v>7</v>
       </c>
-      <c r="C374" s="2" t="n">
+      <c r="E374" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D374" t="n">
+      <c r="F374" t="n">
         <v>6.8</v>
       </c>
-      <c r="E374" s="2" t="n">
+      <c r="G374" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F374" t="n">
+      <c r="H374" t="n">
         <v>6</v>
       </c>
-      <c r="G374" s="2" t="n">
+      <c r="I374" s="2" t="n">
         <v>46126</v>
       </c>
-      <c r="H374" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I374" s="2" t="n">
+      <c r="J374" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K374" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="J374" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K374" s="2" t="n">
+      <c r="L374" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M374" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L374" t="n">
+      <c r="N374" t="n">
         <v>6.9</v>
       </c>
-      <c r="M374" s="2" t="n">
+      <c r="O374" s="2" t="n">
         <v>46053</v>
-      </c>
-      <c r="N374" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O374" s="2" t="n">
-        <v>46011</v>
       </c>
       <c r="P374" t="n">
         <v>6.57</v>
@@ -16493,45 +16525,49 @@
         <v>522</v>
       </c>
       <c r="B375" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C375" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D375" t="n">
         <v>6.4</v>
       </c>
-      <c r="C375" s="2" t="n">
+      <c r="E375" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D375" t="n">
+      <c r="F375" t="n">
         <v>7</v>
       </c>
-      <c r="E375" s="2" t="n">
+      <c r="G375" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F375" t="n">
+      <c r="H375" t="n">
         <v>6.4</v>
       </c>
-      <c r="G375" s="2" t="n">
+      <c r="I375" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H375" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I375" s="2" t="n">
+      <c r="J375" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K375" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="J375" t="n">
+      <c r="L375" t="n">
         <v>6.2</v>
       </c>
-      <c r="K375" s="2" t="n">
+      <c r="M375" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="L375" t="n">
+      <c r="N375" t="n">
         <v>6.3</v>
       </c>
-      <c r="M375" s="2" t="n">
+      <c r="O375" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="N375" t="inlineStr"/>
-      <c r="O375" t="inlineStr"/>
       <c r="P375" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="376">
@@ -16579,49 +16615,49 @@
         <v>525</v>
       </c>
       <c r="B378" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C378" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D378" t="n">
         <v>6.3</v>
       </c>
-      <c r="C378" s="2" t="n">
+      <c r="E378" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="F378" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G378" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D378" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E378" s="2" t="n">
+      <c r="H378" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I378" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F378" t="n">
+      <c r="J378" t="n">
         <v>7.1</v>
       </c>
-      <c r="G378" s="2" t="n">
+      <c r="K378" s="2" t="n">
         <v>46127</v>
       </c>
-      <c r="H378" t="n">
+      <c r="L378" t="n">
         <v>7.6</v>
       </c>
-      <c r="I378" s="2" t="n">
+      <c r="M378" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J378" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K378" s="2" t="n">
+      <c r="N378" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O378" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="L378" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M378" s="2" t="n">
-        <v>46103</v>
-      </c>
-      <c r="N378" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O378" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P378" t="n">
-        <v>6.83</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="379">
@@ -16629,41 +16665,45 @@
         <v>526</v>
       </c>
       <c r="B379" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C379" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D379" t="n">
         <v>7</v>
       </c>
-      <c r="C379" s="2" t="n">
+      <c r="E379" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D379" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E379" s="2" t="n">
+      <c r="F379" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G379" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F379" t="n">
+      <c r="H379" t="n">
         <v>6.2</v>
       </c>
-      <c r="G379" s="2" t="n">
+      <c r="I379" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="H379" t="n">
+      <c r="J379" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I379" s="2" t="n">
+      <c r="K379" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J379" t="n">
+      <c r="L379" t="n">
         <v>6</v>
       </c>
-      <c r="K379" s="2" t="n">
+      <c r="M379" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L379" t="inlineStr"/>
-      <c r="M379" t="inlineStr"/>
       <c r="N379" t="inlineStr"/>
       <c r="O379" t="inlineStr"/>
       <c r="P379" t="n">
-        <v>6.82</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="380">
@@ -16731,45 +16771,49 @@
         <v>530</v>
       </c>
       <c r="B383" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C383" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D383" t="n">
         <v>7.1</v>
       </c>
-      <c r="C383" s="2" t="n">
+      <c r="E383" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D383" t="n">
+      <c r="F383" t="n">
         <v>7.5</v>
       </c>
-      <c r="E383" s="2" t="n">
+      <c r="G383" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F383" t="n">
+      <c r="H383" t="n">
         <v>6.4</v>
       </c>
-      <c r="G383" s="2" t="n">
+      <c r="I383" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H383" t="n">
+      <c r="J383" t="n">
         <v>6.3</v>
       </c>
-      <c r="I383" s="2" t="n">
+      <c r="K383" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="J383" t="n">
+      <c r="L383" t="n">
         <v>6.4</v>
       </c>
-      <c r="K383" s="2" t="n">
+      <c r="M383" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L383" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M383" s="2" t="n">
+      <c r="N383" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O383" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="N383" t="inlineStr"/>
-      <c r="O383" t="inlineStr"/>
       <c r="P383" t="n">
-        <v>6.72</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="384">
@@ -17157,49 +17201,49 @@
         <v>545</v>
       </c>
       <c r="B397" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C397" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D397" t="n">
         <v>6.3</v>
       </c>
-      <c r="C397" s="2" t="n">
+      <c r="E397" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D397" t="n">
+      <c r="F397" t="n">
         <v>6.4</v>
       </c>
-      <c r="E397" s="2" t="n">
+      <c r="G397" s="2" t="n">
         <v>46134</v>
-      </c>
-      <c r="F397" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="G397" s="2" t="n">
-        <v>46131</v>
       </c>
       <c r="H397" t="n">
         <v>6.3</v>
       </c>
       <c r="I397" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="J397" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K397" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="J397" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K397" s="2" t="n">
+      <c r="L397" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M397" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="L397" t="n">
+      <c r="N397" t="n">
         <v>6.2</v>
       </c>
-      <c r="M397" s="2" t="n">
+      <c r="O397" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N397" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O397" s="2" t="n">
-        <v>46068</v>
-      </c>
       <c r="P397" t="n">
-        <v>6.3</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="398">
@@ -17487,49 +17531,49 @@
         <v>552</v>
       </c>
       <c r="B404" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="C404" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D404" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E404" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D404" t="n">
+      <c r="F404" t="n">
         <v>7</v>
       </c>
-      <c r="E404" s="2" t="n">
+      <c r="G404" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F404" t="n">
+      <c r="H404" t="n">
         <v>7.1</v>
       </c>
-      <c r="G404" s="2" t="n">
+      <c r="I404" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H404" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I404" s="2" t="n">
+      <c r="J404" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K404" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J404" t="n">
+      <c r="L404" t="n">
         <v>6.4</v>
       </c>
-      <c r="K404" s="2" t="n">
+      <c r="M404" s="2" t="n">
         <v>46100</v>
       </c>
-      <c r="L404" t="n">
+      <c r="N404" t="n">
         <v>6.1</v>
       </c>
-      <c r="M404" s="2" t="n">
+      <c r="O404" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N404" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O404" s="2" t="n">
-        <v>46090</v>
-      </c>
       <c r="P404" t="n">
-        <v>6.59</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="405">
@@ -17733,49 +17777,49 @@
         <v>557</v>
       </c>
       <c r="B409" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C409" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="D409" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E409" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="F409" t="n">
         <v>7</v>
       </c>
-      <c r="C409" s="2" t="n">
+      <c r="G409" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="D409" t="n">
+      <c r="H409" t="n">
         <v>7.2</v>
       </c>
-      <c r="E409" s="2" t="n">
+      <c r="I409" s="2" t="n">
         <v>46127</v>
       </c>
-      <c r="F409" t="n">
+      <c r="J409" t="n">
         <v>7.6</v>
       </c>
-      <c r="G409" s="2" t="n">
+      <c r="K409" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="H409" t="n">
+      <c r="L409" t="n">
         <v>6.4</v>
       </c>
-      <c r="I409" s="2" t="n">
+      <c r="M409" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="J409" t="n">
+      <c r="N409" t="n">
         <v>8</v>
       </c>
-      <c r="K409" s="2" t="n">
+      <c r="O409" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="L409" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="M409" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="N409" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O409" s="2" t="n">
-        <v>46087</v>
-      </c>
       <c r="P409" t="n">
-        <v>7.2</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="410">
@@ -17783,49 +17827,49 @@
         <v>558</v>
       </c>
       <c r="B410" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C410" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="D410" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E410" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="D410" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E410" s="2" t="n">
+      <c r="F410" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G410" s="2" t="n">
         <v>46126</v>
       </c>
-      <c r="F410" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G410" s="2" t="n">
+      <c r="H410" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I410" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="H410" t="n">
+      <c r="J410" t="n">
         <v>6.4</v>
       </c>
-      <c r="I410" s="2" t="n">
+      <c r="K410" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="J410" t="n">
+      <c r="L410" t="n">
         <v>7.1</v>
       </c>
-      <c r="K410" s="2" t="n">
+      <c r="M410" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="L410" t="n">
+      <c r="N410" t="n">
         <v>7.4</v>
       </c>
-      <c r="M410" s="2" t="n">
+      <c r="O410" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="N410" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O410" s="2" t="n">
-        <v>46004</v>
-      </c>
       <c r="P410" t="n">
-        <v>6.77</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="411">
@@ -18017,49 +18061,49 @@
         <v>563</v>
       </c>
       <c r="B415" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C415" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D415" t="n">
         <v>6.3</v>
       </c>
-      <c r="C415" s="2" t="n">
+      <c r="E415" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="D415" t="n">
+      <c r="F415" t="n">
         <v>6.9</v>
       </c>
-      <c r="E415" s="2" t="n">
+      <c r="G415" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="F415" t="n">
+      <c r="H415" t="n">
         <v>7.8</v>
       </c>
-      <c r="G415" s="2" t="n">
+      <c r="I415" s="2" t="n">
         <v>46074</v>
       </c>
-      <c r="H415" t="n">
+      <c r="J415" t="n">
         <v>7</v>
       </c>
-      <c r="I415" s="2" t="n">
+      <c r="K415" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="J415" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K415" s="2" t="n">
+      <c r="L415" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M415" s="2" t="n">
         <v>46060</v>
-      </c>
-      <c r="L415" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M415" s="2" t="n">
-        <v>46004</v>
       </c>
       <c r="N415" t="n">
         <v>6.8</v>
       </c>
       <c r="O415" s="2" t="n">
-        <v>45998</v>
+        <v>46004</v>
       </c>
       <c r="P415" t="n">
-        <v>6.9</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="416">
@@ -18087,49 +18131,49 @@
         <v>565</v>
       </c>
       <c r="B417" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="C417" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D417" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E417" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="D417" t="n">
+      <c r="F417" t="n">
         <v>6.2</v>
       </c>
-      <c r="E417" s="2" t="n">
+      <c r="G417" s="2" t="n">
         <v>46126</v>
       </c>
-      <c r="F417" t="n">
+      <c r="H417" t="n">
         <v>6.4</v>
       </c>
-      <c r="G417" s="2" t="n">
+      <c r="I417" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H417" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I417" s="2" t="n">
+      <c r="J417" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K417" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="J417" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K417" s="2" t="n">
+      <c r="L417" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M417" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="L417" t="n">
+      <c r="N417" t="n">
         <v>7.1</v>
       </c>
-      <c r="M417" s="2" t="n">
+      <c r="O417" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="N417" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O417" s="2" t="n">
-        <v>46075</v>
-      </c>
       <c r="P417" t="n">
-        <v>6.7</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="418">
@@ -18587,49 +18631,49 @@
         <v>578</v>
       </c>
       <c r="B428" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C428" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D428" t="n">
         <v>8.9</v>
       </c>
-      <c r="C428" s="2" t="n">
+      <c r="E428" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D428" t="n">
+      <c r="F428" t="n">
         <v>6.3</v>
       </c>
-      <c r="E428" s="2" t="n">
+      <c r="G428" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F428" t="n">
+      <c r="H428" t="n">
         <v>6.8</v>
       </c>
-      <c r="G428" s="2" t="n">
+      <c r="I428" s="2" t="n">
         <v>46131</v>
-      </c>
-      <c r="H428" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="I428" s="2" t="n">
-        <v>46120</v>
       </c>
       <c r="J428" t="n">
         <v>7.9</v>
       </c>
       <c r="K428" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="L428" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M428" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L428" t="n">
+      <c r="N428" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M428" s="2" t="n">
+      <c r="O428" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N428" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O428" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P428" t="n">
-        <v>7.5</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="429">
@@ -18637,49 +18681,49 @@
         <v>579</v>
       </c>
       <c r="B429" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C429" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D429" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E429" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="D429" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E429" s="2" t="n">
+      <c r="F429" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G429" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="F429" t="n">
+      <c r="H429" t="n">
         <v>6.8</v>
       </c>
-      <c r="G429" s="2" t="n">
+      <c r="I429" s="2" t="n">
         <v>46088</v>
-      </c>
-      <c r="H429" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I429" s="2" t="n">
-        <v>46081</v>
       </c>
       <c r="J429" t="n">
         <v>6.2</v>
       </c>
       <c r="K429" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="L429" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M429" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="L429" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M429" s="2" t="n">
+      <c r="N429" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O429" s="2" t="n">
         <v>46060</v>
       </c>
-      <c r="N429" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O429" s="2" t="n">
-        <v>46054</v>
-      </c>
       <c r="P429" t="n">
-        <v>6.47</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="430">
@@ -18687,49 +18731,49 @@
         <v>580</v>
       </c>
       <c r="B430" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="C430" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D430" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E430" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D430" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E430" s="2" t="n">
+      <c r="F430" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G430" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F430" t="n">
+      <c r="H430" t="n">
         <v>6.1</v>
       </c>
-      <c r="G430" s="2" t="n">
+      <c r="I430" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="H430" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I430" s="2" t="n">
+      <c r="J430" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K430" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="J430" t="n">
+      <c r="L430" t="n">
         <v>5.9</v>
       </c>
-      <c r="K430" s="2" t="n">
+      <c r="M430" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L430" t="n">
+      <c r="N430" t="n">
         <v>7</v>
       </c>
-      <c r="M430" s="2" t="n">
+      <c r="O430" s="2" t="n">
         <v>46006</v>
       </c>
-      <c r="N430" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O430" s="2" t="n">
-        <v>45999</v>
-      </c>
       <c r="P430" t="n">
-        <v>6.4</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="431">
@@ -19025,49 +19069,49 @@
         <v>588</v>
       </c>
       <c r="B437" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C437" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D437" t="n">
         <v>6.8</v>
       </c>
-      <c r="C437" s="2" t="n">
+      <c r="E437" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D437" t="n">
+      <c r="F437" t="n">
         <v>6.1</v>
       </c>
-      <c r="E437" s="2" t="n">
+      <c r="G437" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="F437" t="n">
+      <c r="H437" t="n">
         <v>6.8</v>
       </c>
-      <c r="G437" s="2" t="n">
+      <c r="I437" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="H437" t="n">
+      <c r="J437" t="n">
         <v>5.6</v>
       </c>
-      <c r="I437" s="2" t="n">
+      <c r="K437" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J437" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K437" s="2" t="n">
+      <c r="L437" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M437" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="L437" t="n">
+      <c r="N437" t="n">
         <v>7.1</v>
       </c>
-      <c r="M437" s="2" t="n">
+      <c r="O437" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="N437" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O437" s="2" t="n">
-        <v>46052</v>
-      </c>
       <c r="P437" t="n">
-        <v>6.37</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="438">
@@ -19125,49 +19169,49 @@
         <v>590</v>
       </c>
       <c r="B439" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="C439" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D439" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E439" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D439" t="n">
+      <c r="F439" t="n">
         <v>7.4</v>
       </c>
-      <c r="E439" s="2" t="n">
+      <c r="G439" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F439" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G439" s="2" t="n">
+      <c r="H439" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I439" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="H439" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I439" s="2" t="n">
+      <c r="J439" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K439" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J439" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K439" s="2" t="n">
+      <c r="L439" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M439" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="L439" t="n">
+      <c r="N439" t="n">
         <v>6.4</v>
       </c>
-      <c r="M439" s="2" t="n">
+      <c r="O439" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="N439" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O439" s="2" t="n">
-        <v>45996</v>
-      </c>
       <c r="P439" t="n">
-        <v>7.01</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="440">
@@ -19475,49 +19519,49 @@
         <v>597</v>
       </c>
       <c r="B446" t="n">
+        <v>7</v>
+      </c>
+      <c r="C446" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D446" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E446" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="F446" t="n">
         <v>6.8</v>
       </c>
-      <c r="C446" s="2" t="n">
+      <c r="G446" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="D446" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E446" s="2" t="n">
+      <c r="H446" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I446" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="F446" t="n">
+      <c r="J446" t="n">
         <v>7.5</v>
       </c>
-      <c r="G446" s="2" t="n">
+      <c r="K446" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H446" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I446" s="2" t="n">
+      <c r="L446" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M446" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="J446" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K446" s="2" t="n">
+      <c r="N446" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O446" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="L446" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="M446" s="2" t="n">
-        <v>46074</v>
-      </c>
-      <c r="N446" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O446" s="2" t="n">
-        <v>46068</v>
-      </c>
       <c r="P446" t="n">
-        <v>6.89</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="447">
@@ -19525,49 +19569,49 @@
         <v>598</v>
       </c>
       <c r="B447" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="C447" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D447" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E447" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D447" t="n">
+      <c r="F447" t="n">
         <v>7.6</v>
       </c>
-      <c r="E447" s="2" t="n">
+      <c r="G447" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F447" t="n">
+      <c r="H447" t="n">
         <v>7</v>
       </c>
-      <c r="G447" s="2" t="n">
+      <c r="I447" s="2" t="n">
         <v>46131</v>
-      </c>
-      <c r="H447" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I447" s="2" t="n">
-        <v>46120</v>
       </c>
       <c r="J447" t="n">
         <v>7.5</v>
       </c>
       <c r="K447" s="2" t="n">
-        <v>46116</v>
+        <v>46120</v>
       </c>
       <c r="L447" t="n">
         <v>7.5</v>
       </c>
       <c r="M447" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="N447" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O447" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N447" t="n">
-        <v>8</v>
-      </c>
-      <c r="O447" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P447" t="n">
-        <v>7.4</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="448">
@@ -19701,41 +19745,45 @@
         <v>602</v>
       </c>
       <c r="B451" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="C451" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D451" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E451" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="D451" t="n">
+      <c r="F451" t="n">
         <v>6.4</v>
       </c>
-      <c r="E451" s="2" t="n">
+      <c r="G451" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="F451" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G451" s="2" t="n">
+      <c r="H451" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I451" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="H451" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I451" s="2" t="n">
+      <c r="J451" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K451" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="J451" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K451" s="2" t="n">
+      <c r="L451" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M451" s="2" t="n">
         <v>46061</v>
       </c>
-      <c r="L451" t="inlineStr"/>
-      <c r="M451" t="inlineStr"/>
       <c r="N451" t="inlineStr"/>
       <c r="O451" t="inlineStr"/>
       <c r="P451" t="n">
-        <v>6.6</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="452">
@@ -19913,49 +19961,49 @@
         <v>607</v>
       </c>
       <c r="B456" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="C456" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D456" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E456" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="D456" t="n">
+      <c r="F456" t="n">
         <v>7.3</v>
       </c>
-      <c r="E456" s="2" t="n">
+      <c r="G456" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="F456" t="n">
+      <c r="H456" t="n">
         <v>6.2</v>
       </c>
-      <c r="G456" s="2" t="n">
+      <c r="I456" s="2" t="n">
         <v>46116</v>
-      </c>
-      <c r="H456" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I456" s="2" t="n">
-        <v>46102</v>
       </c>
       <c r="J456" t="n">
         <v>6.8</v>
       </c>
       <c r="K456" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="L456" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M456" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L456" t="n">
+      <c r="N456" t="n">
         <v>7.3</v>
       </c>
-      <c r="M456" s="2" t="n">
+      <c r="O456" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="N456" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O456" s="2" t="n">
-        <v>46074</v>
-      </c>
       <c r="P456" t="n">
-        <v>6.84</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="457">
@@ -20083,49 +20131,49 @@
         <v>611</v>
       </c>
       <c r="B460" t="n">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="C460" s="2" t="n">
-        <v>46139</v>
+        <v>46144</v>
       </c>
       <c r="D460" t="n">
         <v>6.9</v>
       </c>
       <c r="E460" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="F460" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G460" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F460" t="n">
+      <c r="H460" t="n">
         <v>7.1</v>
       </c>
-      <c r="G460" s="2" t="n">
+      <c r="I460" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="H460" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I460" s="2" t="n">
+      <c r="J460" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K460" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="J460" t="n">
+      <c r="L460" t="n">
         <v>7.1</v>
       </c>
-      <c r="K460" s="2" t="n">
+      <c r="M460" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="L460" t="n">
+      <c r="N460" t="n">
         <v>7.2</v>
       </c>
-      <c r="M460" s="2" t="n">
+      <c r="O460" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N460" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O460" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P460" t="n">
-        <v>6.94</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="461">
@@ -20433,49 +20481,49 @@
         <v>619</v>
       </c>
       <c r="B467" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="C467" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="D467" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E467" s="2" t="n">
         <v>46130</v>
-      </c>
-      <c r="D467" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E467" s="2" t="n">
-        <v>46122</v>
       </c>
       <c r="F467" t="n">
         <v>7.1</v>
       </c>
       <c r="G467" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="H467" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I467" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H467" t="n">
+      <c r="J467" t="n">
         <v>7.3</v>
       </c>
-      <c r="I467" s="2" t="n">
+      <c r="K467" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J467" t="n">
+      <c r="L467" t="n">
         <v>6.9</v>
       </c>
-      <c r="K467" s="2" t="n">
+      <c r="M467" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L467" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M467" s="2" t="n">
+      <c r="N467" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O467" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="N467" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O467" s="2" t="n">
-        <v>46081</v>
-      </c>
       <c r="P467" t="n">
-        <v>6.87</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="468">
@@ -20483,49 +20531,49 @@
         <v>620</v>
       </c>
       <c r="B468" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C468" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D468" t="n">
         <v>7.4</v>
       </c>
-      <c r="C468" s="2" t="n">
+      <c r="E468" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D468" t="n">
+      <c r="F468" t="n">
         <v>6.1</v>
       </c>
-      <c r="E468" s="2" t="n">
+      <c r="G468" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F468" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G468" s="2" t="n">
+      <c r="H468" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I468" s="2" t="n">
         <v>46126</v>
       </c>
-      <c r="H468" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I468" s="2" t="n">
+      <c r="J468" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K468" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="J468" t="n">
+      <c r="L468" t="n">
         <v>6.8</v>
       </c>
-      <c r="K468" s="2" t="n">
+      <c r="M468" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L468" t="n">
+      <c r="N468" t="n">
         <v>7.3</v>
       </c>
-      <c r="M468" s="2" t="n">
+      <c r="O468" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N468" t="n">
-        <v>7</v>
-      </c>
-      <c r="O468" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P468" t="n">
-        <v>6.84</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="469">
@@ -20533,49 +20581,49 @@
         <v>621</v>
       </c>
       <c r="B469" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="C469" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D469" t="n">
         <v>6</v>
       </c>
-      <c r="C469" s="2" t="n">
+      <c r="E469" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D469" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E469" s="2" t="n">
+      <c r="F469" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G469" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F469" t="n">
+      <c r="H469" t="n">
         <v>7.3</v>
       </c>
-      <c r="G469" s="2" t="n">
+      <c r="I469" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H469" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I469" s="2" t="n">
+      <c r="J469" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K469" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J469" t="n">
+      <c r="L469" t="n">
         <v>7.7</v>
       </c>
-      <c r="K469" s="2" t="n">
+      <c r="M469" s="2" t="n">
         <v>46096</v>
-      </c>
-      <c r="L469" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M469" s="2" t="n">
-        <v>46088</v>
       </c>
       <c r="N469" t="n">
         <v>6.4</v>
       </c>
       <c r="O469" s="2" t="n">
-        <v>46082</v>
+        <v>46088</v>
       </c>
       <c r="P469" t="n">
-        <v>6.69</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="470">
@@ -20686,46 +20734,46 @@
         <v>7.4</v>
       </c>
       <c r="C472" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D472" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E472" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D472" t="n">
+      <c r="F472" t="n">
         <v>6.2</v>
       </c>
-      <c r="E472" s="2" t="n">
+      <c r="G472" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F472" t="n">
+      <c r="H472" t="n">
         <v>7.8</v>
       </c>
-      <c r="G472" s="2" t="n">
+      <c r="I472" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H472" t="n">
+      <c r="J472" t="n">
         <v>6.1</v>
       </c>
-      <c r="I472" s="2" t="n">
+      <c r="K472" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="J472" t="n">
+      <c r="L472" t="n">
         <v>8.1</v>
       </c>
-      <c r="K472" s="2" t="n">
+      <c r="M472" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L472" t="n">
+      <c r="N472" t="n">
         <v>7.7</v>
       </c>
-      <c r="M472" s="2" t="n">
+      <c r="O472" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N472" t="n">
-        <v>7</v>
-      </c>
-      <c r="O472" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P472" t="n">
-        <v>7.19</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="473">
@@ -20753,49 +20801,49 @@
         <v>626</v>
       </c>
       <c r="B474" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C474" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D474" t="n">
         <v>6.3</v>
       </c>
-      <c r="C474" s="2" t="n">
+      <c r="E474" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D474" t="n">
+      <c r="F474" t="n">
         <v>6.9</v>
       </c>
-      <c r="E474" s="2" t="n">
+      <c r="G474" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F474" t="n">
+      <c r="H474" t="n">
         <v>5.7</v>
       </c>
-      <c r="G474" s="2" t="n">
+      <c r="I474" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="H474" t="n">
+      <c r="J474" t="n">
         <v>7.1</v>
       </c>
-      <c r="I474" s="2" t="n">
+      <c r="K474" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="J474" t="n">
+      <c r="L474" t="n">
         <v>6.4</v>
       </c>
-      <c r="K474" s="2" t="n">
+      <c r="M474" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="L474" t="n">
+      <c r="N474" t="n">
         <v>7.9</v>
       </c>
-      <c r="M474" s="2" t="n">
+      <c r="O474" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="N474" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O474" s="2" t="n">
-        <v>46074</v>
-      </c>
       <c r="P474" t="n">
-        <v>6.97</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="475">
@@ -20903,49 +20951,49 @@
         <v>629</v>
       </c>
       <c r="B477" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="C477" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D477" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E477" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D477" t="n">
+      <c r="F477" t="n">
         <v>6.4</v>
       </c>
-      <c r="E477" s="2" t="n">
+      <c r="G477" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F477" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G477" s="2" t="n">
+      <c r="H477" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I477" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H477" t="n">
+      <c r="J477" t="n">
         <v>6.3</v>
       </c>
-      <c r="I477" s="2" t="n">
+      <c r="K477" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="J477" t="n">
+      <c r="L477" t="n">
         <v>7.9</v>
       </c>
-      <c r="K477" s="2" t="n">
+      <c r="M477" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L477" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M477" s="2" t="n">
+      <c r="N477" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O477" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N477" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O477" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P477" t="n">
-        <v>6.67</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="478">
@@ -21045,49 +21093,49 @@
         <v>632</v>
       </c>
       <c r="B480" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="C480" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D480" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E480" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D480" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E480" s="2" t="n">
+      <c r="F480" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G480" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F480" t="n">
+      <c r="H480" t="n">
         <v>6.1</v>
       </c>
-      <c r="G480" s="2" t="n">
+      <c r="I480" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="H480" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I480" s="2" t="n">
+      <c r="J480" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K480" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="J480" t="n">
+      <c r="L480" t="n">
         <v>5.9</v>
       </c>
-      <c r="K480" s="2" t="n">
+      <c r="M480" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L480" t="n">
+      <c r="N480" t="n">
         <v>7</v>
       </c>
-      <c r="M480" s="2" t="n">
+      <c r="O480" s="2" t="n">
         <v>46006</v>
       </c>
-      <c r="N480" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="O480" s="2" t="n">
-        <v>45999</v>
-      </c>
       <c r="P480" t="n">
-        <v>6.4</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="481">
@@ -21267,49 +21315,49 @@
         <v>637</v>
       </c>
       <c r="B485" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="C485" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D485" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E485" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D485" t="n">
+      <c r="F485" t="n">
         <v>6.8</v>
       </c>
-      <c r="E485" s="2" t="n">
+      <c r="G485" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="F485" t="n">
+      <c r="H485" t="n">
         <v>6.3</v>
       </c>
-      <c r="G485" s="2" t="n">
+      <c r="I485" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="H485" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I485" s="2" t="n">
+      <c r="J485" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K485" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="J485" t="n">
+      <c r="L485" t="n">
         <v>7.2</v>
       </c>
-      <c r="K485" s="2" t="n">
+      <c r="M485" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="L485" t="n">
+      <c r="N485" t="n">
         <v>6.3</v>
       </c>
-      <c r="M485" s="2" t="n">
+      <c r="O485" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="N485" t="n">
-        <v>7</v>
-      </c>
-      <c r="O485" s="2" t="n">
-        <v>46074</v>
-      </c>
       <c r="P485" t="n">
-        <v>6.7</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="486">
@@ -21317,49 +21365,49 @@
         <v>638</v>
       </c>
       <c r="B486" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C486" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D486" t="n">
         <v>6.9</v>
       </c>
-      <c r="C486" s="2" t="n">
+      <c r="E486" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D486" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E486" s="2" t="n">
+      <c r="F486" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G486" s="2" t="n">
         <v>46132</v>
       </c>
-      <c r="F486" t="n">
+      <c r="H486" t="n">
         <v>6.2</v>
       </c>
-      <c r="G486" s="2" t="n">
+      <c r="I486" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H486" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I486" s="2" t="n">
+      <c r="J486" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K486" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J486" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K486" s="2" t="n">
+      <c r="L486" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M486" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="L486" t="n">
+      <c r="N486" t="n">
         <v>6.4</v>
       </c>
-      <c r="M486" s="2" t="n">
+      <c r="O486" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N486" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O486" s="2" t="n">
-        <v>45997</v>
-      </c>
       <c r="P486" t="n">
-        <v>6.71</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="487">
@@ -21617,49 +21665,49 @@
         <v>644</v>
       </c>
       <c r="B492" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C492" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D492" t="n">
         <v>7.7</v>
       </c>
-      <c r="C492" s="2" t="n">
+      <c r="E492" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="D492" t="n">
+      <c r="F492" t="n">
         <v>7.1</v>
       </c>
-      <c r="E492" s="2" t="n">
+      <c r="G492" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F492" t="n">
+      <c r="H492" t="n">
         <v>8</v>
       </c>
-      <c r="G492" s="2" t="n">
+      <c r="I492" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H492" t="n">
+      <c r="J492" t="n">
         <v>6.9</v>
       </c>
-      <c r="I492" s="2" t="n">
+      <c r="K492" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="J492" t="n">
+      <c r="L492" t="n">
         <v>7.8</v>
       </c>
-      <c r="K492" s="2" t="n">
+      <c r="M492" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L492" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M492" s="2" t="n">
+      <c r="N492" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O492" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="N492" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O492" s="2" t="n">
-        <v>46081</v>
-      </c>
       <c r="P492" t="n">
-        <v>7.24</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="493">
@@ -21687,49 +21735,49 @@
         <v>646</v>
       </c>
       <c r="B494" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="C494" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D494" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E494" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="D494" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E494" s="2" t="n">
+      <c r="F494" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G494" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F494" t="n">
+      <c r="H494" t="n">
         <v>7.1</v>
       </c>
-      <c r="G494" s="2" t="n">
+      <c r="I494" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="H494" t="n">
+      <c r="J494" t="n">
         <v>7.3</v>
       </c>
-      <c r="I494" s="2" t="n">
+      <c r="K494" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J494" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K494" s="2" t="n">
+      <c r="L494" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M494" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L494" t="n">
+      <c r="N494" t="n">
         <v>6.4</v>
       </c>
-      <c r="M494" s="2" t="n">
+      <c r="O494" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N494" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O494" s="2" t="n">
-        <v>46088</v>
-      </c>
       <c r="P494" t="n">
-        <v>6.96</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="495">
@@ -21757,49 +21805,49 @@
         <v>648</v>
       </c>
       <c r="B496" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C496" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D496" t="n">
         <v>6.4</v>
       </c>
-      <c r="C496" s="2" t="n">
+      <c r="E496" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D496" t="n">
+      <c r="F496" t="n">
         <v>5.7</v>
       </c>
-      <c r="E496" s="2" t="n">
+      <c r="G496" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="F496" t="n">
+      <c r="H496" t="n">
         <v>6</v>
       </c>
-      <c r="G496" s="2" t="n">
+      <c r="I496" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="H496" t="n">
+      <c r="J496" t="n">
         <v>6.3</v>
       </c>
-      <c r="I496" s="2" t="n">
+      <c r="K496" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="J496" t="n">
+      <c r="L496" t="n">
         <v>6.9</v>
       </c>
-      <c r="K496" s="2" t="n">
+      <c r="M496" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="L496" t="n">
+      <c r="N496" t="n">
         <v>7</v>
       </c>
-      <c r="M496" s="2" t="n">
+      <c r="O496" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="N496" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O496" s="2" t="n">
-        <v>46085</v>
-      </c>
       <c r="P496" t="n">
-        <v>6.36</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="497">
@@ -21857,45 +21905,49 @@
         <v>650</v>
       </c>
       <c r="B498" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C498" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D498" t="n">
         <v>7.7</v>
       </c>
-      <c r="C498" s="2" t="n">
+      <c r="E498" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D498" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E498" s="2" t="n">
+      <c r="F498" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G498" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F498" t="n">
+      <c r="H498" t="n">
         <v>5.8</v>
       </c>
-      <c r="G498" s="2" t="n">
+      <c r="I498" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H498" t="n">
+      <c r="J498" t="n">
         <v>7.7</v>
       </c>
-      <c r="I498" s="2" t="n">
+      <c r="K498" s="2" t="n">
         <v>46119</v>
-      </c>
-      <c r="J498" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="K498" s="2" t="n">
-        <v>46102</v>
       </c>
       <c r="L498" t="n">
         <v>7.8</v>
       </c>
       <c r="M498" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="N498" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O498" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="N498" t="inlineStr"/>
-      <c r="O498" t="inlineStr"/>
       <c r="P498" t="n">
-        <v>7.22</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="499">
@@ -21953,49 +22005,49 @@
         <v>652</v>
       </c>
       <c r="B500" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C500" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D500" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E500" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="F500" t="n">
         <v>7.6</v>
       </c>
-      <c r="C500" s="2" t="n">
+      <c r="G500" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="D500" t="n">
+      <c r="H500" t="n">
         <v>6.9</v>
       </c>
-      <c r="E500" s="2" t="n">
+      <c r="I500" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F500" t="n">
+      <c r="J500" t="n">
         <v>6.9</v>
       </c>
-      <c r="G500" s="2" t="n">
+      <c r="K500" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="H500" t="n">
+      <c r="L500" t="n">
         <v>7.1</v>
       </c>
-      <c r="I500" s="2" t="n">
+      <c r="M500" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="J500" t="n">
+      <c r="N500" t="n">
         <v>7.2</v>
       </c>
-      <c r="K500" s="2" t="n">
+      <c r="O500" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L500" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M500" s="2" t="n">
-        <v>46102</v>
-      </c>
-      <c r="N500" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O500" s="2" t="n">
-        <v>46094</v>
-      </c>
       <c r="P500" t="n">
-        <v>7.11</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="501">
@@ -22053,49 +22105,49 @@
         <v>654</v>
       </c>
       <c r="B502" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C502" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D502" t="n">
         <v>6.8</v>
       </c>
-      <c r="C502" s="2" t="n">
+      <c r="E502" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="D502" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E502" s="2" t="n">
+      <c r="F502" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G502" s="2" t="n">
         <v>46133</v>
-      </c>
-      <c r="F502" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="G502" s="2" t="n">
-        <v>46130</v>
       </c>
       <c r="H502" t="n">
         <v>6.9</v>
       </c>
       <c r="I502" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="J502" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K502" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J502" t="n">
+      <c r="L502" t="n">
         <v>7.2</v>
       </c>
-      <c r="K502" s="2" t="n">
+      <c r="M502" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L502" t="n">
+      <c r="N502" t="n">
         <v>7.9</v>
       </c>
-      <c r="M502" s="2" t="n">
+      <c r="O502" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="N502" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O502" s="2" t="n">
-        <v>46090</v>
-      </c>
       <c r="P502" t="n">
-        <v>6.96</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="503">
@@ -22103,49 +22155,49 @@
         <v>655</v>
       </c>
       <c r="B503" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="C503" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D503" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E503" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D503" t="n">
+      <c r="F503" t="n">
         <v>8.1</v>
       </c>
-      <c r="E503" s="2" t="n">
+      <c r="G503" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F503" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G503" s="2" t="n">
+      <c r="H503" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I503" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H503" t="n">
+      <c r="J503" t="n">
         <v>6.9</v>
       </c>
-      <c r="I503" s="2" t="n">
+      <c r="K503" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="J503" t="n">
+      <c r="L503" t="n">
         <v>6.4</v>
       </c>
-      <c r="K503" s="2" t="n">
+      <c r="M503" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="L503" t="n">
+      <c r="N503" t="n">
         <v>6.9</v>
       </c>
-      <c r="M503" s="2" t="n">
+      <c r="O503" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N503" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O503" s="2" t="n">
-        <v>46094</v>
-      </c>
       <c r="P503" t="n">
-        <v>6.97</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="504">
@@ -22183,49 +22235,49 @@
         <v>657</v>
       </c>
       <c r="B505" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C505" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D505" t="n">
         <v>6.8</v>
       </c>
-      <c r="C505" s="2" t="n">
+      <c r="E505" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D505" t="n">
+      <c r="F505" t="n">
         <v>7</v>
       </c>
-      <c r="E505" s="2" t="n">
+      <c r="G505" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F505" t="n">
+      <c r="H505" t="n">
         <v>6.3</v>
       </c>
-      <c r="G505" s="2" t="n">
+      <c r="I505" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H505" t="n">
+      <c r="J505" t="n">
         <v>7.5</v>
       </c>
-      <c r="I505" s="2" t="n">
+      <c r="K505" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J505" t="n">
+      <c r="L505" t="n">
         <v>7.3</v>
       </c>
-      <c r="K505" s="2" t="n">
+      <c r="M505" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L505" t="n">
+      <c r="N505" t="n">
         <v>7.4</v>
       </c>
-      <c r="M505" s="2" t="n">
+      <c r="O505" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N505" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O505" s="2" t="n">
-        <v>46088</v>
-      </c>
       <c r="P505" t="n">
-        <v>7.09</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="506">
@@ -22233,49 +22285,49 @@
         <v>658</v>
       </c>
       <c r="B506" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="C506" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D506" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E506" s="2" t="n">
         <v>46127</v>
       </c>
-      <c r="D506" t="n">
+      <c r="F506" t="n">
         <v>7.1</v>
       </c>
-      <c r="E506" s="2" t="n">
+      <c r="G506" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F506" t="n">
+      <c r="H506" t="n">
         <v>6.9</v>
       </c>
-      <c r="G506" s="2" t="n">
+      <c r="I506" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H506" t="n">
+      <c r="J506" t="n">
         <v>7.3</v>
       </c>
-      <c r="I506" s="2" t="n">
+      <c r="K506" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="J506" t="n">
+      <c r="L506" t="n">
         <v>7.1</v>
       </c>
-      <c r="K506" s="2" t="n">
+      <c r="M506" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="L506" t="n">
+      <c r="N506" t="n">
         <v>7.6</v>
       </c>
-      <c r="M506" s="2" t="n">
+      <c r="O506" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="N506" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O506" s="2" t="n">
-        <v>46075</v>
-      </c>
       <c r="P506" t="n">
-        <v>7.1</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="507">
@@ -22283,49 +22335,49 @@
         <v>659</v>
       </c>
       <c r="B507" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C507" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D507" t="n">
         <v>7.5</v>
       </c>
-      <c r="C507" s="2" t="n">
+      <c r="E507" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="D507" t="n">
+      <c r="F507" t="n">
         <v>5.9</v>
       </c>
-      <c r="E507" s="2" t="n">
+      <c r="G507" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F507" t="n">
+      <c r="H507" t="n">
         <v>7.6</v>
       </c>
-      <c r="G507" s="2" t="n">
+      <c r="I507" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="H507" t="n">
+      <c r="J507" t="n">
         <v>7.5</v>
       </c>
-      <c r="I507" s="2" t="n">
+      <c r="K507" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J507" t="n">
+      <c r="L507" t="n">
         <v>6.8</v>
       </c>
-      <c r="K507" s="2" t="n">
+      <c r="M507" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L507" t="n">
+      <c r="N507" t="n">
         <v>7.1</v>
       </c>
-      <c r="M507" s="2" t="n">
+      <c r="O507" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N507" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O507" s="2" t="n">
-        <v>46088</v>
-      </c>
       <c r="P507" t="n">
-        <v>6.96</v>
+        <v>7</v>
       </c>
     </row>
     <row r="508">
@@ -22333,37 +22385,41 @@
         <v>660</v>
       </c>
       <c r="B508" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C508" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="D508" t="n">
         <v>7.1</v>
       </c>
-      <c r="C508" s="2" t="n">
+      <c r="E508" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D508" t="n">
+      <c r="F508" t="n">
         <v>6.8</v>
       </c>
-      <c r="E508" s="2" t="n">
+      <c r="G508" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F508" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G508" s="2" t="n">
+      <c r="H508" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I508" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H508" t="n">
+      <c r="J508" t="n">
         <v>7.4</v>
       </c>
-      <c r="I508" s="2" t="n">
+      <c r="K508" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J508" t="inlineStr"/>
-      <c r="K508" t="inlineStr"/>
       <c r="L508" t="inlineStr"/>
       <c r="M508" t="inlineStr"/>
       <c r="N508" t="inlineStr"/>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>6.98</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="509">
@@ -22371,37 +22427,41 @@
         <v>661</v>
       </c>
       <c r="B509" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="C509" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="D509" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E509" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D509" t="n">
+      <c r="F509" t="n">
         <v>7.3</v>
       </c>
-      <c r="E509" s="2" t="n">
+      <c r="G509" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F509" t="n">
+      <c r="H509" t="n">
         <v>7</v>
       </c>
-      <c r="G509" s="2" t="n">
+      <c r="I509" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H509" t="n">
+      <c r="J509" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="I509" s="2" t="n">
+      <c r="K509" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J509" t="inlineStr"/>
-      <c r="K509" t="inlineStr"/>
       <c r="L509" t="inlineStr"/>
       <c r="M509" t="inlineStr"/>
       <c r="N509" t="inlineStr"/>
       <c r="O509" t="inlineStr"/>
       <c r="P509" t="n">
-        <v>7.4</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="510">
@@ -22443,41 +22503,45 @@
         <v>663</v>
       </c>
       <c r="B511" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C511" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D511" t="n">
         <v>6.4</v>
       </c>
-      <c r="C511" s="2" t="n">
+      <c r="E511" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D511" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E511" s="2" t="n">
+      <c r="F511" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G511" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F511" t="n">
+      <c r="H511" t="n">
         <v>8</v>
       </c>
-      <c r="G511" s="2" t="n">
+      <c r="I511" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H511" t="n">
+      <c r="J511" t="n">
         <v>7.3</v>
       </c>
-      <c r="I511" s="2" t="n">
+      <c r="K511" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J511" t="n">
+      <c r="L511" t="n">
         <v>6.9</v>
       </c>
-      <c r="K511" s="2" t="n">
+      <c r="M511" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="L511" t="inlineStr"/>
-      <c r="M511" t="inlineStr"/>
       <c r="N511" t="inlineStr"/>
       <c r="O511" t="inlineStr"/>
       <c r="P511" t="n">
-        <v>7.04</v>
+        <v>7</v>
       </c>
     </row>
     <row r="512">
@@ -22527,37 +22591,41 @@
         <v>665</v>
       </c>
       <c r="B513" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="C513" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D513" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E513" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="D513" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E513" s="2" t="n">
+      <c r="F513" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G513" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F513" t="n">
+      <c r="H513" t="n">
         <v>8.6</v>
       </c>
-      <c r="G513" s="2" t="n">
+      <c r="I513" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="H513" t="n">
+      <c r="J513" t="n">
         <v>8.4</v>
       </c>
-      <c r="I513" s="2" t="n">
+      <c r="K513" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J513" t="inlineStr"/>
-      <c r="K513" t="inlineStr"/>
       <c r="L513" t="inlineStr"/>
       <c r="M513" t="inlineStr"/>
       <c r="N513" t="inlineStr"/>
       <c r="O513" t="inlineStr"/>
       <c r="P513" t="n">
-        <v>7.55</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="514">
@@ -22565,49 +22633,49 @@
         <v>666</v>
       </c>
       <c r="B514" t="n">
+        <v>7</v>
+      </c>
+      <c r="C514" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D514" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E514" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="F514" t="n">
         <v>6.9</v>
       </c>
-      <c r="C514" s="2" t="n">
+      <c r="G514" s="2" t="n">
         <v>46133</v>
-      </c>
-      <c r="D514" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E514" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="F514" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G514" s="2" t="n">
-        <v>46124</v>
       </c>
       <c r="H514" t="n">
         <v>7.2</v>
       </c>
       <c r="I514" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="J514" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K514" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="L514" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M514" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="J514" t="n">
+      <c r="N514" t="n">
         <v>6.9</v>
       </c>
-      <c r="K514" s="2" t="n">
+      <c r="O514" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="L514" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M514" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="N514" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O514" s="2" t="n">
-        <v>46088</v>
-      </c>
       <c r="P514" t="n">
-        <v>6.9</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="515">
@@ -22615,41 +22683,345 @@
         <v>667</v>
       </c>
       <c r="B515" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C515" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D515" t="n">
         <v>6.9</v>
       </c>
-      <c r="C515" s="2" t="n">
+      <c r="E515" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="D515" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E515" s="2" t="n">
+      <c r="F515" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G515" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F515" t="n">
+      <c r="H515" t="n">
         <v>7.4</v>
       </c>
-      <c r="G515" s="2" t="n">
+      <c r="I515" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H515" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I515" s="2" t="n">
+      <c r="J515" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K515" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J515" t="n">
+      <c r="L515" t="n">
         <v>7.3</v>
       </c>
-      <c r="K515" s="2" t="n">
+      <c r="M515" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L515" t="inlineStr"/>
-      <c r="M515" t="inlineStr"/>
       <c r="N515" t="inlineStr"/>
       <c r="O515" t="inlineStr"/>
       <c r="P515" t="n">
-        <v>6.96</v>
+        <v>6.92</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>668</v>
+      </c>
+      <c r="B516" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C516" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="D516" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E516" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="F516" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G516" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="H516" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I516" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="J516" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K516" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="L516" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M516" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="N516" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O516" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="P516" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>669</v>
+      </c>
+      <c r="B517" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C517" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="D517" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E517" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="F517" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G517" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="H517" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I517" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="J517" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K517" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="L517" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M517" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="N517" t="n">
+        <v>8</v>
+      </c>
+      <c r="O517" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="P517" t="n">
+        <v>7.13</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>670</v>
+      </c>
+      <c r="B518" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C518" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="D518" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E518" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="F518" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G518" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="H518" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I518" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="J518" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K518" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="L518" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M518" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="N518" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O518" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="P518" t="n">
+        <v>6.86</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>671</v>
+      </c>
+      <c r="B519" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C519" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="D519" t="n">
+        <v>7</v>
+      </c>
+      <c r="E519" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F519" t="n">
+        <v>8</v>
+      </c>
+      <c r="G519" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="H519" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I519" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="J519" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K519" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="L519" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M519" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="N519" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O519" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="P519" t="n">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>672</v>
+      </c>
+      <c r="B520" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C520" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D520" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E520" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="F520" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G520" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="H520" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I520" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="J520" t="n">
+        <v>7</v>
+      </c>
+      <c r="K520" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="L520" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M520" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="N520" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O520" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="P520" t="n">
+        <v>7.06</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>673</v>
+      </c>
+      <c r="B521" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C521" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="D521" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E521" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F521" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G521" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="H521" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I521" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="J521" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K521" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="L521" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M521" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="N521" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O521" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="P521" t="n">
+        <v>7.07</v>
       </c>
     </row>
   </sheetData>

--- a/players_ratings.xlsx
+++ b/players_ratings.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P521"/>
+  <dimension ref="A1:P527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,49 +619,49 @@
         <v>15</v>
       </c>
       <c r="B4" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C4" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="D4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>46127</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>7.8</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="J4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K4" s="2" t="n">
+      <c r="L4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>7.1</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="N4" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>46085</v>
-      </c>
       <c r="P4" t="n">
-        <v>6.89</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="5">
@@ -1069,49 +1069,49 @@
         <v>36</v>
       </c>
       <c r="B14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D14" t="n">
         <v>6.9</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="E14" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="D14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E14" s="2" t="n">
+      <c r="F14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
         <v>6.9</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="I14" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H14" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I14" s="2" t="n">
+      <c r="J14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K14" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>6.3</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="M14" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>7.5</v>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="O14" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="N14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>46082</v>
-      </c>
       <c r="P14" t="n">
-        <v>6.79</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="15">
@@ -1245,49 +1245,49 @@
         <v>43</v>
       </c>
       <c r="B18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="C18" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="D18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E18" s="2" t="n">
+      <c r="F18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="F18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>6.8</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="K18" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>7.4</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>46130</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>46122</v>
       </c>
       <c r="N18" t="n">
         <v>6.3</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="P18" t="n">
-        <v>6.63</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="19">
@@ -2190,21 +2190,51 @@
       <c r="A40" t="n">
         <v>94</v>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="H40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="J40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="L40" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="N40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="P40" t="n">
+        <v>6.87</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2260,8 +2290,12 @@
       <c r="A42" t="n">
         <v>96</v>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>46152</v>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -2274,7 +2308,9 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2350,41 +2386,93 @@
       <c r="A45" t="n">
         <v>100</v>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D45" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="H45" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="J45" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="L45" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>46118</v>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>6.95</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>101</v>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="H46" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="J46" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="L46" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>46118</v>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>7.18</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2444,21 +2532,47 @@
       <c r="A49" t="n">
         <v>104</v>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D49" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="H49" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="J49" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="L49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>46117</v>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>6.95</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2574,21 +2688,43 @@
       <c r="A54" t="n">
         <v>117</v>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D54" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F54" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="H54" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="J54" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>46123</v>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>6.74</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2684,21 +2820,43 @@
       <c r="A58" t="n">
         <v>122</v>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D58" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="F58" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="H58" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="J58" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>46118</v>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>6.54</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2995,49 +3153,49 @@
         <v>143</v>
       </c>
       <c r="B66" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D66" t="n">
         <v>6.2</v>
       </c>
-      <c r="C66" s="2" t="n">
+      <c r="E66" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="D66" t="n">
+      <c r="F66" t="n">
         <v>6.8</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="F66" t="n">
+      <c r="H66" t="n">
         <v>6.2</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="I66" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="H66" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I66" s="2" t="n">
+      <c r="J66" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K66" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>6.3</v>
       </c>
-      <c r="K66" s="2" t="n">
+      <c r="M66" s="2" t="n">
         <v>46076</v>
       </c>
-      <c r="L66" t="n">
+      <c r="N66" t="n">
         <v>7</v>
       </c>
-      <c r="M66" s="2" t="n">
+      <c r="O66" s="2" t="n">
         <v>46067</v>
       </c>
-      <c r="N66" t="n">
-        <v>6</v>
-      </c>
-      <c r="O66" s="2" t="n">
-        <v>46061</v>
-      </c>
       <c r="P66" t="n">
-        <v>6.44</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="67">
@@ -3465,49 +3623,49 @@
         <v>165</v>
       </c>
       <c r="B76" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D76" t="n">
         <v>7.3</v>
       </c>
-      <c r="C76" s="2" t="n">
+      <c r="E76" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="D76" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E76" s="2" t="n">
+      <c r="F76" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G76" s="2" t="n">
         <v>46128</v>
       </c>
-      <c r="F76" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G76" s="2" t="n">
+      <c r="H76" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I76" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H76" t="n">
+      <c r="J76" t="n">
         <v>6.8</v>
       </c>
-      <c r="I76" s="2" t="n">
+      <c r="K76" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
         <v>6.9</v>
       </c>
-      <c r="K76" s="2" t="n">
+      <c r="M76" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L76" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M76" s="2" t="n">
+      <c r="N76" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O76" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N76" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O76" s="2" t="n">
-        <v>46088</v>
-      </c>
       <c r="P76" t="n">
-        <v>6.74</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="77">
@@ -3857,49 +4015,49 @@
         <v>175</v>
       </c>
       <c r="B84" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D84" t="n">
         <v>8.5</v>
       </c>
-      <c r="C84" s="2" t="n">
+      <c r="E84" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="D84" t="n">
+      <c r="F84" t="n">
         <v>6.8</v>
       </c>
-      <c r="E84" s="2" t="n">
+      <c r="G84" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="F84" t="n">
+      <c r="H84" t="n">
         <v>7.3</v>
       </c>
-      <c r="G84" s="2" t="n">
+      <c r="I84" s="2" t="n">
         <v>46131</v>
-      </c>
-      <c r="H84" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>46127</v>
       </c>
       <c r="J84" t="n">
         <v>6.8</v>
       </c>
       <c r="K84" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="L84" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M84" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="L84" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M84" s="2" t="n">
+      <c r="N84" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O84" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N84" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O84" s="2" t="n">
-        <v>46090</v>
-      </c>
       <c r="P84" t="n">
-        <v>7.39</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="85">
@@ -3991,49 +4149,49 @@
         <v>181</v>
       </c>
       <c r="B87" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D87" t="n">
         <v>7.1</v>
       </c>
-      <c r="C87" s="2" t="n">
+      <c r="E87" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="D87" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E87" s="2" t="n">
+      <c r="F87" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G87" s="2" t="n">
         <v>46138</v>
-      </c>
-      <c r="F87" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>46131</v>
       </c>
       <c r="H87" t="n">
         <v>7.1</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46127</v>
+        <v>46131</v>
       </c>
       <c r="J87" t="n">
         <v>7.1</v>
       </c>
       <c r="K87" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="L87" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M87" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
         <v>7.4</v>
       </c>
-      <c r="M87" s="2" t="n">
+      <c r="O87" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N87" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O87" s="2" t="n">
-        <v>46102</v>
-      </c>
       <c r="P87" t="n">
-        <v>7.06</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="88">
@@ -4349,49 +4507,49 @@
         <v>192</v>
       </c>
       <c r="B95" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D95" t="n">
         <v>7.1</v>
       </c>
-      <c r="C95" s="2" t="n">
+      <c r="E95" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="D95" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E95" s="2" t="n">
+      <c r="F95" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G95" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="F95" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G95" s="2" t="n">
+      <c r="H95" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I95" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="H95" t="n">
+      <c r="J95" t="n">
         <v>7</v>
       </c>
-      <c r="I95" s="2" t="n">
+      <c r="K95" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="J95" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K95" s="2" t="n">
+      <c r="L95" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M95" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L95" t="n">
+      <c r="N95" t="n">
         <v>6.3</v>
       </c>
-      <c r="M95" s="2" t="n">
+      <c r="O95" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="N95" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O95" s="2" t="n">
-        <v>46085</v>
-      </c>
       <c r="P95" t="n">
-        <v>6.66</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="96">
@@ -6047,49 +6205,49 @@
         <v>247</v>
       </c>
       <c r="B136" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D136" t="n">
         <v>7.5</v>
       </c>
-      <c r="C136" s="2" t="n">
+      <c r="E136" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="D136" t="n">
+      <c r="F136" t="n">
         <v>6.8</v>
       </c>
-      <c r="E136" s="2" t="n">
+      <c r="G136" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="F136" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G136" s="2" t="n">
+      <c r="H136" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I136" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="H136" t="n">
+      <c r="J136" t="n">
         <v>6.8</v>
       </c>
-      <c r="I136" s="2" t="n">
+      <c r="K136" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="J136" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K136" s="2" t="n">
+      <c r="L136" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M136" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="L136" t="n">
+      <c r="N136" t="n">
         <v>6.2</v>
       </c>
-      <c r="M136" s="2" t="n">
+      <c r="O136" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N136" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O136" s="2" t="n">
-        <v>46102</v>
-      </c>
       <c r="P136" t="n">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="137">
@@ -6297,49 +6455,49 @@
         <v>258</v>
       </c>
       <c r="B141" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C141" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D141" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E141" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="D141" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E141" s="2" t="n">
+      <c r="F141" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G141" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="F141" t="n">
+      <c r="H141" t="n">
         <v>7.2</v>
       </c>
-      <c r="G141" s="2" t="n">
+      <c r="I141" s="2" t="n">
         <v>46132</v>
       </c>
-      <c r="H141" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I141" s="2" t="n">
+      <c r="J141" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K141" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="J141" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K141" s="2" t="n">
+      <c r="L141" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M141" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L141" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M141" s="2" t="n">
+      <c r="N141" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O141" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="N141" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O141" s="2" t="n">
-        <v>46005</v>
-      </c>
       <c r="P141" t="n">
-        <v>6.61</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="142">
@@ -6347,49 +6505,49 @@
         <v>259</v>
       </c>
       <c r="B142" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D142" t="n">
         <v>7.3</v>
       </c>
-      <c r="C142" s="2" t="n">
+      <c r="E142" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="D142" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E142" s="2" t="n">
+      <c r="F142" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G142" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="F142" t="n">
+      <c r="H142" t="n">
         <v>7.3</v>
       </c>
-      <c r="G142" s="2" t="n">
+      <c r="I142" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="H142" t="n">
+      <c r="J142" t="n">
         <v>6.2</v>
       </c>
-      <c r="I142" s="2" t="n">
+      <c r="K142" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="J142" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K142" s="2" t="n">
+      <c r="L142" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M142" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="L142" t="n">
+      <c r="N142" t="n">
         <v>6.9</v>
       </c>
-      <c r="M142" s="2" t="n">
+      <c r="O142" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N142" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O142" s="2" t="n">
-        <v>46100</v>
-      </c>
       <c r="P142" t="n">
-        <v>7.01</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="143">
@@ -6397,49 +6555,49 @@
         <v>260</v>
       </c>
       <c r="B143" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="C143" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D143" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E143" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="D143" t="n">
+      <c r="F143" t="n">
         <v>7.1</v>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="G143" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="F143" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G143" s="2" t="n">
+      <c r="H143" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I143" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="H143" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I143" s="2" t="n">
+      <c r="J143" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K143" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="J143" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K143" s="2" t="n">
+      <c r="L143" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M143" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="L143" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M143" s="2" t="n">
+      <c r="N143" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O143" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N143" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O143" s="2" t="n">
-        <v>46100</v>
-      </c>
       <c r="P143" t="n">
-        <v>6.57</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="144">
@@ -6617,49 +6775,49 @@
         <v>273</v>
       </c>
       <c r="B148" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C148" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D148" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E148" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="D148" t="n">
+      <c r="F148" t="n">
         <v>6.8</v>
       </c>
-      <c r="E148" s="2" t="n">
+      <c r="G148" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="F148" t="n">
+      <c r="H148" t="n">
         <v>6.3</v>
       </c>
-      <c r="G148" s="2" t="n">
+      <c r="I148" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H148" t="n">
+      <c r="J148" t="n">
         <v>7.7</v>
       </c>
-      <c r="I148" s="2" t="n">
+      <c r="K148" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J148" t="n">
+      <c r="L148" t="n">
         <v>6.8</v>
       </c>
-      <c r="K148" s="2" t="n">
+      <c r="M148" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="L148" t="n">
+      <c r="N148" t="n">
         <v>6.3</v>
       </c>
-      <c r="M148" s="2" t="n">
+      <c r="O148" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="N148" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O148" s="2" t="n">
-        <v>46089</v>
-      </c>
       <c r="P148" t="n">
-        <v>6.79</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="149">
@@ -7401,49 +7559,49 @@
         <v>290</v>
       </c>
       <c r="B164" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D164" t="n">
         <v>7</v>
       </c>
-      <c r="C164" s="2" t="n">
+      <c r="E164" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="D164" t="n">
+      <c r="F164" t="n">
         <v>7.7</v>
       </c>
-      <c r="E164" s="2" t="n">
+      <c r="G164" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="F164" t="n">
+      <c r="H164" t="n">
         <v>7.6</v>
       </c>
-      <c r="G164" s="2" t="n">
+      <c r="I164" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H164" t="n">
+      <c r="J164" t="n">
         <v>9</v>
       </c>
-      <c r="I164" s="2" t="n">
+      <c r="K164" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="J164" t="n">
+      <c r="L164" t="n">
         <v>6.9</v>
       </c>
-      <c r="K164" s="2" t="n">
+      <c r="M164" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L164" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M164" s="2" t="n">
+      <c r="N164" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O164" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N164" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O164" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P164" t="n">
-        <v>7.36</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="165">
@@ -7451,49 +7609,49 @@
         <v>291</v>
       </c>
       <c r="B165" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D165" t="n">
         <v>7.3</v>
       </c>
-      <c r="C165" s="2" t="n">
+      <c r="E165" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="D165" t="n">
+      <c r="F165" t="n">
         <v>7.4</v>
       </c>
-      <c r="E165" s="2" t="n">
+      <c r="G165" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="F165" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G165" s="2" t="n">
+      <c r="H165" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I165" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H165" t="n">
+      <c r="J165" t="n">
         <v>6.3</v>
       </c>
-      <c r="I165" s="2" t="n">
+      <c r="K165" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J165" t="n">
+      <c r="L165" t="n">
         <v>7.9</v>
       </c>
-      <c r="K165" s="2" t="n">
+      <c r="M165" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="L165" t="n">
+      <c r="N165" t="n">
         <v>6.8</v>
       </c>
-      <c r="M165" s="2" t="n">
+      <c r="O165" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N165" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O165" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P165" t="n">
-        <v>6.94</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="166">
@@ -7601,49 +7759,49 @@
         <v>294</v>
       </c>
       <c r="B168" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C168" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D168" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E168" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="D168" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E168" s="2" t="n">
+      <c r="F168" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G168" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="F168" t="n">
+      <c r="H168" t="n">
         <v>6.2</v>
       </c>
-      <c r="G168" s="2" t="n">
+      <c r="I168" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="H168" t="n">
+      <c r="J168" t="n">
         <v>6.3</v>
       </c>
-      <c r="I168" s="2" t="n">
+      <c r="K168" s="2" t="n">
         <v>46098</v>
       </c>
-      <c r="J168" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K168" s="2" t="n">
+      <c r="L168" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M168" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="L168" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M168" s="2" t="n">
+      <c r="N168" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O168" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="N168" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O168" s="2" t="n">
-        <v>45987</v>
-      </c>
       <c r="P168" t="n">
-        <v>6.4</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="169">
@@ -7909,49 +8067,49 @@
         <v>303</v>
       </c>
       <c r="B175" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D175" t="n">
         <v>7.2</v>
       </c>
-      <c r="C175" s="2" t="n">
+      <c r="E175" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="D175" t="n">
+      <c r="F175" t="n">
         <v>7.3</v>
       </c>
-      <c r="E175" s="2" t="n">
+      <c r="G175" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="F175" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G175" s="2" t="n">
+      <c r="H175" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I175" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="H175" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I175" s="2" t="n">
+      <c r="J175" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K175" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="J175" t="n">
+      <c r="L175" t="n">
         <v>7.1</v>
       </c>
-      <c r="K175" s="2" t="n">
+      <c r="M175" s="2" t="n">
         <v>46089</v>
       </c>
-      <c r="L175" t="n">
+      <c r="N175" t="n">
         <v>7.3</v>
       </c>
-      <c r="M175" s="2" t="n">
+      <c r="O175" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="N175" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O175" s="2" t="n">
-        <v>46081</v>
-      </c>
       <c r="P175" t="n">
-        <v>6.97</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="176">
@@ -8755,49 +8913,49 @@
         <v>322</v>
       </c>
       <c r="B192" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D192" t="n">
         <v>7.4</v>
       </c>
-      <c r="C192" s="2" t="n">
+      <c r="E192" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="D192" t="n">
+      <c r="F192" t="n">
         <v>6.9</v>
       </c>
-      <c r="E192" s="2" t="n">
+      <c r="G192" s="2" t="n">
         <v>46144</v>
-      </c>
-      <c r="F192" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G192" s="2" t="n">
-        <v>46136</v>
       </c>
       <c r="H192" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="I192" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="J192" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K192" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="J192" t="n">
+      <c r="L192" t="n">
         <v>8</v>
       </c>
-      <c r="K192" s="2" t="n">
+      <c r="M192" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="L192" t="n">
+      <c r="N192" t="n">
         <v>6.9</v>
       </c>
-      <c r="M192" s="2" t="n">
+      <c r="O192" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="N192" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="O192" s="2" t="n">
-        <v>46114</v>
-      </c>
       <c r="P192" t="n">
-        <v>7.87</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="193">
@@ -8935,49 +9093,49 @@
         <v>326</v>
       </c>
       <c r="B196" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="C196" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D196" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E196" s="2" t="n">
         <v>46149</v>
       </c>
-      <c r="D196" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E196" s="2" t="n">
+      <c r="F196" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G196" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F196" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G196" s="2" t="n">
+      <c r="H196" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I196" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H196" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I196" s="2" t="n">
+      <c r="J196" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K196" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="J196" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K196" s="2" t="n">
+      <c r="L196" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M196" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="L196" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M196" s="2" t="n">
+      <c r="N196" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O196" s="2" t="n">
         <v>45878</v>
       </c>
-      <c r="N196" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O196" s="2" t="n">
-        <v>45870</v>
-      </c>
       <c r="P196" t="n">
-        <v>6.66</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="197">
@@ -9155,49 +9313,49 @@
         <v>335</v>
       </c>
       <c r="B201" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C201" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D201" t="n">
         <v>6.9</v>
       </c>
-      <c r="C201" s="2" t="n">
+      <c r="E201" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="D201" t="n">
+      <c r="F201" t="n">
         <v>7.1</v>
       </c>
-      <c r="E201" s="2" t="n">
+      <c r="G201" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="F201" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G201" s="2" t="n">
+      <c r="H201" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I201" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="H201" t="n">
+      <c r="J201" t="n">
         <v>6.8</v>
       </c>
-      <c r="I201" s="2" t="n">
+      <c r="K201" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="J201" t="n">
+      <c r="L201" t="n">
         <v>6.3</v>
       </c>
-      <c r="K201" s="2" t="n">
+      <c r="M201" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="L201" t="n">
+      <c r="N201" t="n">
         <v>6.8</v>
       </c>
-      <c r="M201" s="2" t="n">
+      <c r="O201" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="N201" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O201" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P201" t="n">
-        <v>6.73</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="202">
@@ -9385,61 +9543,73 @@
         <v>340</v>
       </c>
       <c r="B206" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="C206" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D206" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E206" s="2" t="n">
         <v>46148</v>
       </c>
-      <c r="D206" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E206" s="2" t="n">
+      <c r="F206" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G206" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="F206" t="n">
+      <c r="H206" t="n">
         <v>5.7</v>
       </c>
-      <c r="G206" s="2" t="n">
+      <c r="I206" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="H206" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I206" s="2" t="n">
+      <c r="J206" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K206" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J206" t="n">
+      <c r="L206" t="n">
         <v>7.7</v>
       </c>
-      <c r="K206" s="2" t="n">
+      <c r="M206" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L206" t="n">
+      <c r="N206" t="n">
         <v>6.8</v>
       </c>
-      <c r="M206" s="2" t="n">
+      <c r="O206" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N206" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O206" s="2" t="n">
-        <v>46089</v>
-      </c>
       <c r="P206" t="n">
-        <v>6.73</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
         <v>341</v>
       </c>
-      <c r="B207" t="inlineStr"/>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
+      <c r="B207" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C207" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="D207" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="F207" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>46103</v>
+      </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr"/>
@@ -9448,56 +9618,58 @@
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
+      <c r="P207" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
         <v>342</v>
       </c>
       <c r="B208" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C208" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D208" t="n">
         <v>7.2</v>
       </c>
-      <c r="C208" s="2" t="n">
+      <c r="E208" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="D208" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E208" s="2" t="n">
+      <c r="F208" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G208" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="F208" t="n">
+      <c r="H208" t="n">
         <v>7</v>
       </c>
-      <c r="G208" s="2" t="n">
+      <c r="I208" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="H208" t="n">
+      <c r="J208" t="n">
         <v>6.8</v>
       </c>
-      <c r="I208" s="2" t="n">
+      <c r="K208" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="J208" t="n">
+      <c r="L208" t="n">
         <v>5.7</v>
       </c>
-      <c r="K208" s="2" t="n">
+      <c r="M208" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="L208" t="n">
+      <c r="N208" t="n">
         <v>6</v>
       </c>
-      <c r="M208" s="2" t="n">
+      <c r="O208" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="N208" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O208" s="2" t="n">
-        <v>46118</v>
-      </c>
       <c r="P208" t="n">
-        <v>6.56</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="209">
@@ -9954,21 +10126,47 @@
       <c r="A218" t="n">
         <v>352</v>
       </c>
-      <c r="B218" t="inlineStr"/>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
+      <c r="B218" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C218" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D218" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F218" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G218" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="H218" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I218" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="J218" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K218" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="L218" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M218" s="2" t="n">
+        <v>46119</v>
+      </c>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
+      <c r="P218" t="n">
+        <v>7.78</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -10051,45 +10249,49 @@
         <v>356</v>
       </c>
       <c r="B221" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="C221" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D221" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E221" s="2" t="n">
         <v>46087</v>
       </c>
-      <c r="D221" t="n">
+      <c r="F221" t="n">
         <v>6.8</v>
       </c>
-      <c r="E221" s="2" t="n">
+      <c r="G221" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="F221" t="n">
+      <c r="H221" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G221" s="2" t="n">
+      <c r="I221" s="2" t="n">
         <v>46072</v>
       </c>
-      <c r="H221" t="n">
+      <c r="J221" t="n">
         <v>6.9</v>
       </c>
-      <c r="I221" s="2" t="n">
+      <c r="K221" s="2" t="n">
         <v>46004</v>
       </c>
-      <c r="J221" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K221" s="2" t="n">
+      <c r="L221" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M221" s="2" t="n">
         <v>45920</v>
       </c>
-      <c r="L221" t="n">
+      <c r="N221" t="n">
         <v>7.1</v>
       </c>
-      <c r="M221" s="2" t="n">
+      <c r="O221" s="2" t="n">
         <v>45911</v>
       </c>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
       <c r="P221" t="n">
-        <v>7.03</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="222">
@@ -10327,49 +10529,49 @@
         <v>365</v>
       </c>
       <c r="B227" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="C227" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D227" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F227" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G227" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="D227" t="n">
+      <c r="H227" t="n">
         <v>7.1</v>
       </c>
-      <c r="E227" s="2" t="n">
+      <c r="I227" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="F227" t="n">
+      <c r="J227" t="n">
         <v>6.3</v>
       </c>
-      <c r="G227" s="2" t="n">
+      <c r="K227" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="H227" t="n">
+      <c r="L227" t="n">
         <v>6.2</v>
       </c>
-      <c r="I227" s="2" t="n">
+      <c r="M227" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="J227" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K227" s="2" t="n">
+      <c r="N227" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O227" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="L227" t="n">
-        <v>7</v>
-      </c>
-      <c r="M227" s="2" t="n">
-        <v>46082</v>
-      </c>
-      <c r="N227" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O227" s="2" t="n">
-        <v>45884</v>
-      </c>
       <c r="P227" t="n">
-        <v>6.61</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="228">
@@ -10680,46 +10882,46 @@
         <v>6.6</v>
       </c>
       <c r="C234" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D234" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E234" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="D234" t="n">
+      <c r="F234" t="n">
         <v>6.8</v>
       </c>
-      <c r="E234" s="2" t="n">
+      <c r="G234" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="F234" t="n">
+      <c r="H234" t="n">
         <v>7.2</v>
       </c>
-      <c r="G234" s="2" t="n">
+      <c r="I234" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H234" t="n">
+      <c r="J234" t="n">
         <v>6.9</v>
       </c>
-      <c r="I234" s="2" t="n">
+      <c r="K234" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="J234" t="n">
+      <c r="L234" t="n">
         <v>5.8</v>
       </c>
-      <c r="K234" s="2" t="n">
+      <c r="M234" s="2" t="n">
         <v>46104</v>
       </c>
-      <c r="L234" t="n">
+      <c r="N234" t="n">
         <v>7.1</v>
       </c>
-      <c r="M234" s="2" t="n">
+      <c r="O234" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="N234" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O234" s="2" t="n">
-        <v>46089</v>
-      </c>
       <c r="P234" t="n">
-        <v>6.83</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="235">
@@ -10776,21 +10978,43 @@
       <c r="A236" t="n">
         <v>375</v>
       </c>
-      <c r="B236" t="inlineStr"/>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
+      <c r="B236" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C236" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D236" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="F236" t="n">
+        <v>7</v>
+      </c>
+      <c r="G236" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="H236" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I236" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="J236" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K236" s="2" t="n">
+        <v>46118</v>
+      </c>
       <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
+      <c r="P236" t="n">
+        <v>6.68</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -10846,41 +11070,97 @@
       <c r="A238" t="n">
         <v>377</v>
       </c>
-      <c r="B238" t="inlineStr"/>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
-      <c r="P238" t="inlineStr"/>
+      <c r="B238" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C238" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D238" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F238" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G238" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="H238" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I238" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="J238" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K238" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="L238" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M238" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="N238" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O238" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="P238" t="n">
+        <v>6.69</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
         <v>378</v>
       </c>
-      <c r="B239" t="inlineStr"/>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
+      <c r="B239" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C239" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D239" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="F239" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G239" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="H239" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I239" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="J239" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K239" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="L239" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M239" s="2" t="n">
+        <v>46082</v>
+      </c>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
-      <c r="P239" t="inlineStr"/>
+      <c r="P239" t="n">
+        <v>6.53</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -11036,12 +11316,24 @@
       <c r="A243" t="n">
         <v>383</v>
       </c>
-      <c r="B243" t="inlineStr"/>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
+      <c r="B243" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C243" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D243" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="F243" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G243" s="2" t="n">
+        <v>46116</v>
+      </c>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
@@ -11050,7 +11342,9 @@
       <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
-      <c r="P243" t="inlineStr"/>
+      <c r="P243" t="n">
+        <v>6.73</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -11338,10 +11632,18 @@
       <c r="A251" t="n">
         <v>392</v>
       </c>
-      <c r="B251" t="inlineStr"/>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
+      <c r="B251" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C251" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="D251" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>45872</v>
+      </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
@@ -11352,56 +11654,58 @@
       <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr"/>
-      <c r="P251" t="inlineStr"/>
+      <c r="P251" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
         <v>393</v>
       </c>
       <c r="B252" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C252" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D252" t="n">
         <v>7.7</v>
       </c>
-      <c r="C252" s="2" t="n">
+      <c r="E252" s="2" t="n">
         <v>46151</v>
-      </c>
-      <c r="D252" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E252" s="2" t="n">
-        <v>46145</v>
       </c>
       <c r="F252" t="n">
         <v>6.9</v>
       </c>
       <c r="G252" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="H252" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I252" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="H252" t="n">
+      <c r="J252" t="n">
         <v>6.1</v>
       </c>
-      <c r="I252" s="2" t="n">
+      <c r="K252" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="J252" t="n">
+      <c r="L252" t="n">
         <v>6.9</v>
       </c>
-      <c r="K252" s="2" t="n">
+      <c r="M252" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="L252" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M252" s="2" t="n">
+      <c r="N252" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O252" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N252" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O252" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P252" t="n">
-        <v>6.9</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="253">
@@ -11528,21 +11832,39 @@
       <c r="A256" t="n">
         <v>397</v>
       </c>
-      <c r="B256" t="inlineStr"/>
-      <c r="C256" t="inlineStr"/>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
+      <c r="B256" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C256" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D256" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F256" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G256" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="H256" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I256" s="2" t="n">
+        <v>46116</v>
+      </c>
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
-      <c r="P256" t="inlineStr"/>
+      <c r="P256" t="n">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -11598,12 +11920,24 @@
       <c r="A258" t="n">
         <v>399</v>
       </c>
-      <c r="B258" t="inlineStr"/>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
+      <c r="B258" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C258" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D258" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F258" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G258" s="2" t="n">
+        <v>46102</v>
+      </c>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
@@ -11612,7 +11946,9 @@
       <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr"/>
-      <c r="P258" t="inlineStr"/>
+      <c r="P258" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -12351,49 +12687,49 @@
         <v>417</v>
       </c>
       <c r="B276" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C276" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D276" t="n">
         <v>6.2</v>
       </c>
-      <c r="C276" s="2" t="n">
+      <c r="E276" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="D276" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E276" s="2" t="n">
+      <c r="F276" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G276" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="F276" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G276" s="2" t="n">
+      <c r="H276" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I276" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="H276" t="n">
+      <c r="J276" t="n">
         <v>6.9</v>
       </c>
-      <c r="I276" s="2" t="n">
+      <c r="K276" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="J276" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K276" s="2" t="n">
+      <c r="L276" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M276" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="L276" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M276" s="2" t="n">
+      <c r="N276" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O276" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="N276" t="n">
-        <v>8</v>
-      </c>
-      <c r="O276" s="2" t="n">
-        <v>46101</v>
-      </c>
       <c r="P276" t="n">
-        <v>6.73</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="277">
@@ -12401,49 +12737,49 @@
         <v>418</v>
       </c>
       <c r="B277" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C277" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D277" t="n">
         <v>7.2</v>
       </c>
-      <c r="C277" s="2" t="n">
+      <c r="E277" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="D277" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E277" s="2" t="n">
+      <c r="F277" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G277" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="F277" t="n">
+      <c r="H277" t="n">
         <v>5.5</v>
       </c>
-      <c r="G277" s="2" t="n">
+      <c r="I277" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="H277" t="n">
+      <c r="J277" t="n">
         <v>7.1</v>
       </c>
-      <c r="I277" s="2" t="n">
+      <c r="K277" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="J277" t="n">
+      <c r="L277" t="n">
         <v>7.7</v>
       </c>
-      <c r="K277" s="2" t="n">
+      <c r="M277" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="L277" t="n">
+      <c r="N277" t="n">
         <v>6.3</v>
       </c>
-      <c r="M277" s="2" t="n">
+      <c r="O277" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="N277" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O277" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P277" t="n">
-        <v>6.79</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="278">
@@ -12782,21 +13118,47 @@
       <c r="A286" t="n">
         <v>427</v>
       </c>
-      <c r="B286" t="inlineStr"/>
-      <c r="C286" t="inlineStr"/>
-      <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr"/>
+      <c r="B286" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C286" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D286" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F286" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G286" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="H286" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I286" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="J286" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K286" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="L286" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M286" s="2" t="n">
+        <v>46117</v>
+      </c>
       <c r="N286" t="inlineStr"/>
       <c r="O286" t="inlineStr"/>
-      <c r="P286" t="inlineStr"/>
+      <c r="P286" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -12952,21 +13314,47 @@
       <c r="A290" t="n">
         <v>432</v>
       </c>
-      <c r="B290" t="inlineStr"/>
-      <c r="C290" t="inlineStr"/>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr"/>
+      <c r="B290" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C290" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D290" t="n">
+        <v>7</v>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F290" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G290" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="H290" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I290" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="J290" t="n">
+        <v>7</v>
+      </c>
+      <c r="K290" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="L290" t="n">
+        <v>7</v>
+      </c>
+      <c r="M290" s="2" t="n">
+        <v>46118</v>
+      </c>
       <c r="N290" t="inlineStr"/>
       <c r="O290" t="inlineStr"/>
-      <c r="P290" t="inlineStr"/>
+      <c r="P290" t="n">
+        <v>6.92</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -13544,12 +13932,24 @@
       <c r="A304" t="n">
         <v>449</v>
       </c>
-      <c r="B304" t="inlineStr"/>
-      <c r="C304" t="inlineStr"/>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
+      <c r="B304" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C304" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D304" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F304" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G304" s="2" t="n">
+        <v>46130</v>
+      </c>
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr"/>
@@ -13558,14 +13958,20 @@
       <c r="M304" t="inlineStr"/>
       <c r="N304" t="inlineStr"/>
       <c r="O304" t="inlineStr"/>
-      <c r="P304" t="inlineStr"/>
+      <c r="P304" t="n">
+        <v>6.47</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
         <v>450</v>
       </c>
-      <c r="B305" t="inlineStr"/>
-      <c r="C305" t="inlineStr"/>
+      <c r="B305" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C305" s="2" t="n">
+        <v>46133</v>
+      </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
@@ -13578,7 +13984,9 @@
       <c r="M305" t="inlineStr"/>
       <c r="N305" t="inlineStr"/>
       <c r="O305" t="inlineStr"/>
-      <c r="P305" t="inlineStr"/>
+      <c r="P305" t="n">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -13685,49 +14093,49 @@
         <v>453</v>
       </c>
       <c r="B308" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="C308" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D308" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E308" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="D308" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E308" s="2" t="n">
+      <c r="F308" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G308" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="F308" t="n">
+      <c r="H308" t="n">
         <v>6.3</v>
       </c>
-      <c r="G308" s="2" t="n">
+      <c r="I308" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H308" t="n">
+      <c r="J308" t="n">
         <v>6</v>
       </c>
-      <c r="I308" s="2" t="n">
+      <c r="K308" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="J308" t="n">
+      <c r="L308" t="n">
         <v>6.2</v>
       </c>
-      <c r="K308" s="2" t="n">
+      <c r="M308" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="L308" t="n">
+      <c r="N308" t="n">
         <v>7.2</v>
       </c>
-      <c r="M308" s="2" t="n">
+      <c r="O308" s="2" t="n">
         <v>46094</v>
       </c>
-      <c r="N308" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O308" s="2" t="n">
-        <v>46082</v>
-      </c>
       <c r="P308" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="309">
@@ -13885,49 +14293,49 @@
         <v>458</v>
       </c>
       <c r="B312" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C312" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D312" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E312" s="2" t="n">
         <v>46148</v>
       </c>
-      <c r="D312" t="n">
+      <c r="F312" t="n">
         <v>8.1</v>
       </c>
-      <c r="E312" s="2" t="n">
+      <c r="G312" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="F312" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G312" s="2" t="n">
+      <c r="H312" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I312" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="H312" t="n">
+      <c r="J312" t="n">
         <v>6.3</v>
       </c>
-      <c r="I312" s="2" t="n">
+      <c r="K312" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="J312" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K312" s="2" t="n">
+      <c r="L312" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M312" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="L312" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M312" s="2" t="n">
+      <c r="N312" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O312" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N312" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O312" s="2" t="n">
-        <v>46095</v>
-      </c>
       <c r="P312" t="n">
-        <v>6.7</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="313">
@@ -14211,49 +14619,49 @@
         <v>465</v>
       </c>
       <c r="B319" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="C319" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D319" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E319" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="D319" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E319" s="2" t="n">
+      <c r="F319" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G319" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="F319" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G319" s="2" t="n">
+      <c r="H319" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I319" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="H319" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I319" s="2" t="n">
+      <c r="J319" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K319" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="J319" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K319" s="2" t="n">
+      <c r="L319" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M319" s="2" t="n">
         <v>46088</v>
       </c>
-      <c r="L319" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M319" s="2" t="n">
+      <c r="N319" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O319" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="N319" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O319" s="2" t="n">
-        <v>46075</v>
-      </c>
       <c r="P319" t="n">
-        <v>6.51</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="320">
@@ -14261,49 +14669,49 @@
         <v>466</v>
       </c>
       <c r="B320" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="C320" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D320" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E320" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="D320" t="n">
+      <c r="F320" t="n">
         <v>7.3</v>
       </c>
-      <c r="E320" s="2" t="n">
+      <c r="G320" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="F320" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G320" s="2" t="n">
+      <c r="H320" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I320" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="H320" t="n">
+      <c r="J320" t="n">
         <v>7.9</v>
       </c>
-      <c r="I320" s="2" t="n">
+      <c r="K320" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="J320" t="n">
+      <c r="L320" t="n">
         <v>6.2</v>
       </c>
-      <c r="K320" s="2" t="n">
+      <c r="M320" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="L320" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M320" s="2" t="n">
+      <c r="N320" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O320" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N320" t="n">
-        <v>7</v>
-      </c>
-      <c r="O320" s="2" t="n">
-        <v>46103</v>
-      </c>
       <c r="P320" t="n">
-        <v>6.86</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="321">
@@ -14461,49 +14869,49 @@
         <v>470</v>
       </c>
       <c r="B324" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="C324" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D324" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E324" s="2" t="n">
         <v>46086</v>
-      </c>
-      <c r="D324" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E324" s="2" t="n">
-        <v>46074</v>
       </c>
       <c r="F324" t="n">
         <v>6.3</v>
       </c>
       <c r="G324" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="H324" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I324" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="H324" t="n">
+      <c r="J324" t="n">
         <v>6.2</v>
       </c>
-      <c r="I324" s="2" t="n">
+      <c r="K324" s="2" t="n">
         <v>45997</v>
       </c>
-      <c r="J324" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K324" s="2" t="n">
+      <c r="L324" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M324" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="L324" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M324" s="2" t="n">
+      <c r="N324" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O324" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="N324" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O324" s="2" t="n">
-        <v>45954</v>
-      </c>
       <c r="P324" t="n">
-        <v>6.37</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="325">
@@ -15029,49 +15437,49 @@
         <v>485</v>
       </c>
       <c r="B339" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C339" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D339" t="n">
         <v>7</v>
       </c>
-      <c r="C339" s="2" t="n">
+      <c r="E339" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="D339" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E339" s="2" t="n">
+      <c r="F339" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G339" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="F339" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G339" s="2" t="n">
+      <c r="H339" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I339" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="H339" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I339" s="2" t="n">
+      <c r="J339" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K339" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="J339" t="n">
+      <c r="L339" t="n">
         <v>6.1</v>
       </c>
-      <c r="K339" s="2" t="n">
+      <c r="M339" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="L339" t="n">
+      <c r="N339" t="n">
         <v>7.4</v>
       </c>
-      <c r="M339" s="2" t="n">
+      <c r="O339" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="N339" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O339" s="2" t="n">
-        <v>46101</v>
-      </c>
       <c r="P339" t="n">
-        <v>6.77</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="340">
@@ -16590,32 +16998,70 @@
       <c r="A376" t="n">
         <v>523</v>
       </c>
-      <c r="B376" t="inlineStr"/>
-      <c r="C376" t="inlineStr"/>
-      <c r="D376" t="inlineStr"/>
-      <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
-      <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr"/>
-      <c r="J376" t="inlineStr"/>
-      <c r="K376" t="inlineStr"/>
-      <c r="L376" t="inlineStr"/>
-      <c r="M376" t="inlineStr"/>
+      <c r="B376" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C376" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D376" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E376" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F376" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G376" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="H376" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I376" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="J376" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K376" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="L376" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M376" s="2" t="n">
+        <v>46118</v>
+      </c>
       <c r="N376" t="inlineStr"/>
       <c r="O376" t="inlineStr"/>
-      <c r="P376" t="inlineStr"/>
+      <c r="P376" t="n">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
         <v>524</v>
       </c>
-      <c r="B377" t="inlineStr"/>
-      <c r="C377" t="inlineStr"/>
-      <c r="D377" t="inlineStr"/>
-      <c r="E377" t="inlineStr"/>
-      <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
+      <c r="B377" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C377" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="D377" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E377" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="F377" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G377" s="2" t="n">
+        <v>46119</v>
+      </c>
       <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr"/>
       <c r="J377" t="inlineStr"/>
@@ -16624,7 +17070,9 @@
       <c r="M377" t="inlineStr"/>
       <c r="N377" t="inlineStr"/>
       <c r="O377" t="inlineStr"/>
-      <c r="P377" t="inlineStr"/>
+      <c r="P377" t="n">
+        <v>6.63</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -16750,10 +17198,18 @@
       <c r="A381" t="n">
         <v>528</v>
       </c>
-      <c r="B381" t="inlineStr"/>
-      <c r="C381" t="inlineStr"/>
-      <c r="D381" t="inlineStr"/>
-      <c r="E381" t="inlineStr"/>
+      <c r="B381" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C381" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D381" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E381" s="2" t="n">
+        <v>46145</v>
+      </c>
       <c r="F381" t="inlineStr"/>
       <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr"/>
@@ -16764,7 +17220,9 @@
       <c r="M381" t="inlineStr"/>
       <c r="N381" t="inlineStr"/>
       <c r="O381" t="inlineStr"/>
-      <c r="P381" t="inlineStr"/>
+      <c r="P381" t="n">
+        <v>6.55</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -16840,41 +17298,85 @@
       <c r="A384" t="n">
         <v>531</v>
       </c>
-      <c r="B384" t="inlineStr"/>
-      <c r="C384" t="inlineStr"/>
-      <c r="D384" t="inlineStr"/>
-      <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr"/>
-      <c r="G384" t="inlineStr"/>
-      <c r="H384" t="inlineStr"/>
-      <c r="I384" t="inlineStr"/>
+      <c r="B384" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C384" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D384" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E384" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F384" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G384" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="H384" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I384" s="2" t="n">
+        <v>46130</v>
+      </c>
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr"/>
       <c r="M384" t="inlineStr"/>
       <c r="N384" t="inlineStr"/>
       <c r="O384" t="inlineStr"/>
-      <c r="P384" t="inlineStr"/>
+      <c r="P384" t="n">
+        <v>6.72</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
         <v>533</v>
       </c>
-      <c r="B385" t="inlineStr"/>
-      <c r="C385" t="inlineStr"/>
-      <c r="D385" t="inlineStr"/>
-      <c r="E385" t="inlineStr"/>
-      <c r="F385" t="inlineStr"/>
-      <c r="G385" t="inlineStr"/>
-      <c r="H385" t="inlineStr"/>
-      <c r="I385" t="inlineStr"/>
-      <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr"/>
-      <c r="L385" t="inlineStr"/>
-      <c r="M385" t="inlineStr"/>
+      <c r="B385" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C385" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D385" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E385" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F385" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G385" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="H385" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I385" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="J385" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K385" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="L385" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M385" s="2" t="n">
+        <v>46123</v>
+      </c>
       <c r="N385" t="inlineStr"/>
       <c r="O385" t="inlineStr"/>
-      <c r="P385" t="inlineStr"/>
+      <c r="P385" t="n">
+        <v>6.82</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -16900,12 +17402,24 @@
       <c r="A387" t="n">
         <v>535</v>
       </c>
-      <c r="B387" t="inlineStr"/>
-      <c r="C387" t="inlineStr"/>
-      <c r="D387" t="inlineStr"/>
-      <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr"/>
+      <c r="B387" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C387" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D387" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E387" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F387" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G387" s="2" t="n">
+        <v>46138</v>
+      </c>
       <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr"/>
       <c r="J387" t="inlineStr"/>
@@ -16914,27 +17428,47 @@
       <c r="M387" t="inlineStr"/>
       <c r="N387" t="inlineStr"/>
       <c r="O387" t="inlineStr"/>
-      <c r="P387" t="inlineStr"/>
+      <c r="P387" t="n">
+        <v>6.6</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
         <v>536</v>
       </c>
-      <c r="B388" t="inlineStr"/>
-      <c r="C388" t="inlineStr"/>
-      <c r="D388" t="inlineStr"/>
-      <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
-      <c r="H388" t="inlineStr"/>
-      <c r="I388" t="inlineStr"/>
+      <c r="B388" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C388" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D388" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E388" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="F388" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G388" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="H388" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I388" s="2" t="n">
+        <v>46123</v>
+      </c>
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr"/>
       <c r="M388" t="inlineStr"/>
       <c r="N388" t="inlineStr"/>
       <c r="O388" t="inlineStr"/>
-      <c r="P388" t="inlineStr"/>
+      <c r="P388" t="n">
+        <v>6.72</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -16960,8 +17494,12 @@
       <c r="A390" t="n">
         <v>538</v>
       </c>
-      <c r="B390" t="inlineStr"/>
-      <c r="C390" t="inlineStr"/>
+      <c r="B390" t="n">
+        <v>7</v>
+      </c>
+      <c r="C390" s="2" t="n">
+        <v>46118</v>
+      </c>
       <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr"/>
@@ -16974,27 +17512,51 @@
       <c r="M390" t="inlineStr"/>
       <c r="N390" t="inlineStr"/>
       <c r="O390" t="inlineStr"/>
-      <c r="P390" t="inlineStr"/>
+      <c r="P390" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
         <v>539</v>
       </c>
-      <c r="B391" t="inlineStr"/>
-      <c r="C391" t="inlineStr"/>
-      <c r="D391" t="inlineStr"/>
-      <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr"/>
-      <c r="G391" t="inlineStr"/>
-      <c r="H391" t="inlineStr"/>
-      <c r="I391" t="inlineStr"/>
-      <c r="J391" t="inlineStr"/>
-      <c r="K391" t="inlineStr"/>
+      <c r="B391" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C391" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D391" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E391" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F391" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G391" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="H391" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I391" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="J391" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K391" s="2" t="n">
+        <v>46124</v>
+      </c>
       <c r="L391" t="inlineStr"/>
       <c r="M391" t="inlineStr"/>
       <c r="N391" t="inlineStr"/>
       <c r="O391" t="inlineStr"/>
-      <c r="P391" t="inlineStr"/>
+      <c r="P391" t="n">
+        <v>6.72</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -17804,46 +18366,46 @@
         <v>6.5</v>
       </c>
       <c r="C409" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D409" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E409" s="2" t="n">
         <v>46148</v>
       </c>
-      <c r="D409" t="n">
+      <c r="F409" t="n">
         <v>6.9</v>
       </c>
-      <c r="E409" s="2" t="n">
+      <c r="G409" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="F409" t="n">
+      <c r="H409" t="n">
         <v>7.8</v>
       </c>
-      <c r="G409" s="2" t="n">
+      <c r="I409" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="H409" t="n">
+      <c r="J409" t="n">
         <v>7</v>
       </c>
-      <c r="I409" s="2" t="n">
+      <c r="K409" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="J409" t="n">
+      <c r="L409" t="n">
         <v>7.2</v>
       </c>
-      <c r="K409" s="2" t="n">
+      <c r="M409" s="2" t="n">
         <v>46127</v>
       </c>
-      <c r="L409" t="n">
+      <c r="N409" t="n">
         <v>7.6</v>
       </c>
-      <c r="M409" s="2" t="n">
+      <c r="O409" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="N409" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O409" s="2" t="n">
-        <v>46115</v>
-      </c>
       <c r="P409" t="n">
-        <v>7.06</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="410">
@@ -17851,49 +18413,49 @@
         <v>558</v>
       </c>
       <c r="B410" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C410" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D410" t="n">
         <v>6.3</v>
       </c>
-      <c r="C410" s="2" t="n">
+      <c r="E410" s="2" t="n">
         <v>46147</v>
       </c>
-      <c r="D410" t="n">
+      <c r="F410" t="n">
         <v>6.2</v>
       </c>
-      <c r="E410" s="2" t="n">
+      <c r="G410" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="F410" t="n">
+      <c r="H410" t="n">
         <v>6.8</v>
       </c>
-      <c r="G410" s="2" t="n">
+      <c r="I410" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="H410" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I410" s="2" t="n">
+      <c r="J410" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K410" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="J410" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K410" s="2" t="n">
+      <c r="L410" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M410" s="2" t="n">
         <v>46126</v>
       </c>
-      <c r="L410" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M410" s="2" t="n">
+      <c r="N410" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O410" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="N410" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O410" s="2" t="n">
-        <v>46090</v>
-      </c>
       <c r="P410" t="n">
-        <v>6.47</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="411">
@@ -18292,21 +18854,39 @@
       <c r="A420" t="n">
         <v>568</v>
       </c>
-      <c r="B420" t="inlineStr"/>
-      <c r="C420" t="inlineStr"/>
-      <c r="D420" t="inlineStr"/>
-      <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr"/>
-      <c r="H420" t="inlineStr"/>
-      <c r="I420" t="inlineStr"/>
+      <c r="B420" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C420" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D420" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E420" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F420" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G420" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="H420" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I420" s="2" t="n">
+        <v>46127</v>
+      </c>
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr"/>
       <c r="L420" t="inlineStr"/>
       <c r="M420" t="inlineStr"/>
       <c r="N420" t="inlineStr"/>
       <c r="O420" t="inlineStr"/>
-      <c r="P420" t="inlineStr"/>
+      <c r="P420" t="n">
+        <v>6.55</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -19097,49 +19677,49 @@
         <v>588</v>
       </c>
       <c r="B437" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="C437" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D437" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E437" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="D437" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E437" s="2" t="n">
+      <c r="F437" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G437" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="F437" t="n">
+      <c r="H437" t="n">
         <v>6.8</v>
       </c>
-      <c r="G437" s="2" t="n">
+      <c r="I437" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="H437" t="n">
+      <c r="J437" t="n">
         <v>6.1</v>
       </c>
-      <c r="I437" s="2" t="n">
+      <c r="K437" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="J437" t="n">
+      <c r="L437" t="n">
         <v>6.8</v>
       </c>
-      <c r="K437" s="2" t="n">
+      <c r="M437" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="L437" t="n">
+      <c r="N437" t="n">
         <v>5.6</v>
       </c>
-      <c r="M437" s="2" t="n">
+      <c r="O437" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N437" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O437" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P437" t="n">
-        <v>6.44</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="438">
@@ -19547,49 +20127,49 @@
         <v>597</v>
       </c>
       <c r="B446" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C446" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D446" t="n">
         <v>7.2</v>
       </c>
-      <c r="C446" s="2" t="n">
+      <c r="E446" s="2" t="n">
         <v>46149</v>
       </c>
-      <c r="D446" t="n">
+      <c r="F446" t="n">
         <v>7</v>
       </c>
-      <c r="E446" s="2" t="n">
+      <c r="G446" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="F446" t="n">
+      <c r="H446" t="n">
         <v>6.9</v>
       </c>
-      <c r="G446" s="2" t="n">
+      <c r="I446" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="H446" t="n">
+      <c r="J446" t="n">
         <v>6.8</v>
       </c>
-      <c r="I446" s="2" t="n">
+      <c r="K446" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="J446" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K446" s="2" t="n">
+      <c r="L446" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M446" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="L446" t="n">
+      <c r="N446" t="n">
         <v>7.5</v>
       </c>
-      <c r="M446" s="2" t="n">
+      <c r="O446" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N446" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O446" s="2" t="n">
-        <v>46088</v>
-      </c>
       <c r="P446" t="n">
-        <v>6.93</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="447">
@@ -19647,13 +20227,17 @@
         <v>599</v>
       </c>
       <c r="B448" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C448" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D448" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E448" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="D448" t="inlineStr"/>
-      <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
@@ -19665,7 +20249,7 @@
       <c r="N448" t="inlineStr"/>
       <c r="O448" t="inlineStr"/>
       <c r="P448" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="449">
@@ -19823,49 +20407,49 @@
         <v>603</v>
       </c>
       <c r="B452" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="C452" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D452" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E452" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="D452" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E452" s="2" t="n">
+      <c r="F452" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G452" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="F452" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G452" s="2" t="n">
+      <c r="H452" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I452" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H452" t="n">
+      <c r="J452" t="n">
         <v>6.9</v>
       </c>
-      <c r="I452" s="2" t="n">
+      <c r="K452" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="J452" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K452" s="2" t="n">
+      <c r="L452" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M452" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="L452" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M452" s="2" t="n">
+      <c r="N452" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O452" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N452" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O452" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P452" t="n">
-        <v>6.76</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="453">
@@ -19922,21 +20506,51 @@
       <c r="A454" t="n">
         <v>605</v>
       </c>
-      <c r="B454" t="inlineStr"/>
-      <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
-      <c r="E454" t="inlineStr"/>
-      <c r="F454" t="inlineStr"/>
-      <c r="G454" t="inlineStr"/>
-      <c r="H454" t="inlineStr"/>
-      <c r="I454" t="inlineStr"/>
-      <c r="J454" t="inlineStr"/>
-      <c r="K454" t="inlineStr"/>
-      <c r="L454" t="inlineStr"/>
-      <c r="M454" t="inlineStr"/>
-      <c r="N454" t="inlineStr"/>
-      <c r="O454" t="inlineStr"/>
-      <c r="P454" t="inlineStr"/>
+      <c r="B454" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="C454" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D454" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E454" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F454" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G454" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="H454" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I454" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="J454" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K454" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="L454" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M454" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="N454" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O454" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="P454" t="n">
+        <v>8.460000000000001</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -19993,49 +20607,49 @@
         <v>607</v>
       </c>
       <c r="B456" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="C456" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D456" t="n">
         <v>7</v>
       </c>
-      <c r="C456" s="2" t="n">
+      <c r="E456" s="2" t="n">
         <v>46148</v>
       </c>
-      <c r="D456" t="n">
+      <c r="F456" t="n">
         <v>7.6</v>
       </c>
-      <c r="E456" s="2" t="n">
+      <c r="G456" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="F456" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G456" s="2" t="n">
+      <c r="H456" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I456" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="H456" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I456" s="2" t="n">
+      <c r="J456" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K456" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="J456" t="n">
+      <c r="L456" t="n">
         <v>7.3</v>
       </c>
-      <c r="K456" s="2" t="n">
+      <c r="M456" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="L456" t="n">
+      <c r="N456" t="n">
         <v>6.2</v>
       </c>
-      <c r="M456" s="2" t="n">
+      <c r="O456" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N456" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O456" s="2" t="n">
-        <v>46102</v>
-      </c>
       <c r="P456" t="n">
-        <v>6.86</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="457">
@@ -20263,49 +20877,49 @@
         <v>613</v>
       </c>
       <c r="B462" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C462" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D462" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E462" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="D462" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E462" s="2" t="n">
+      <c r="F462" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G462" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="F462" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G462" s="2" t="n">
+      <c r="H462" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I462" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="H462" t="n">
+      <c r="J462" t="n">
         <v>6.9</v>
       </c>
-      <c r="I462" s="2" t="n">
+      <c r="K462" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="J462" t="n">
+      <c r="L462" t="n">
         <v>7.7</v>
       </c>
-      <c r="K462" s="2" t="n">
+      <c r="M462" s="2" t="n">
         <v>46095</v>
-      </c>
-      <c r="L462" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M462" s="2" t="n">
-        <v>46089</v>
       </c>
       <c r="N462" t="n">
         <v>6.3</v>
       </c>
       <c r="O462" s="2" t="n">
-        <v>46068</v>
+        <v>46089</v>
       </c>
       <c r="P462" t="n">
-        <v>6.7</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="463">
@@ -20563,49 +21177,49 @@
         <v>620</v>
       </c>
       <c r="B468" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C468" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D468" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E468" s="2" t="n">
         <v>46148</v>
       </c>
-      <c r="D468" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E468" s="2" t="n">
+      <c r="F468" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G468" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="F468" t="n">
+      <c r="H468" t="n">
         <v>7.4</v>
       </c>
-      <c r="G468" s="2" t="n">
+      <c r="I468" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="H468" t="n">
+      <c r="J468" t="n">
         <v>6.1</v>
       </c>
-      <c r="I468" s="2" t="n">
+      <c r="K468" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="J468" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K468" s="2" t="n">
+      <c r="L468" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M468" s="2" t="n">
         <v>46126</v>
       </c>
-      <c r="L468" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M468" s="2" t="n">
+      <c r="N468" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O468" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="N468" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O468" s="2" t="n">
-        <v>46116</v>
-      </c>
       <c r="P468" t="n">
-        <v>6.7</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="469">
@@ -20613,49 +21227,49 @@
         <v>621</v>
       </c>
       <c r="B469" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="C469" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D469" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E469" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="D469" t="n">
+      <c r="F469" t="n">
         <v>5.9</v>
       </c>
-      <c r="E469" s="2" t="n">
+      <c r="G469" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="F469" t="n">
+      <c r="H469" t="n">
         <v>6</v>
       </c>
-      <c r="G469" s="2" t="n">
+      <c r="I469" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="H469" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I469" s="2" t="n">
+      <c r="J469" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K469" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="J469" t="n">
+      <c r="L469" t="n">
         <v>7.3</v>
       </c>
-      <c r="K469" s="2" t="n">
+      <c r="M469" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="L469" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M469" s="2" t="n">
+      <c r="N469" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O469" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N469" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O469" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P469" t="n">
-        <v>6.63</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="470">
@@ -20663,49 +21277,49 @@
         <v>622</v>
       </c>
       <c r="B470" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="C470" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="D470" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E470" s="2" t="n">
         <v>46090</v>
       </c>
-      <c r="D470" t="n">
+      <c r="F470" t="n">
         <v>7.1</v>
       </c>
-      <c r="E470" s="2" t="n">
+      <c r="G470" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="F470" t="n">
+      <c r="H470" t="n">
         <v>7</v>
       </c>
-      <c r="G470" s="2" t="n">
+      <c r="I470" s="2" t="n">
         <v>46075</v>
       </c>
-      <c r="H470" t="n">
+      <c r="J470" t="n">
         <v>6.3</v>
       </c>
-      <c r="I470" s="2" t="n">
+      <c r="K470" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="J470" t="n">
+      <c r="L470" t="n">
         <v>7.3</v>
       </c>
-      <c r="K470" s="2" t="n">
+      <c r="M470" s="2" t="n">
         <v>46004</v>
-      </c>
-      <c r="L470" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M470" s="2" t="n">
-        <v>45997</v>
       </c>
       <c r="N470" t="n">
         <v>6.9</v>
       </c>
       <c r="O470" s="2" t="n">
-        <v>45990</v>
+        <v>45997</v>
       </c>
       <c r="P470" t="n">
-        <v>6.84</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="471">
@@ -20883,49 +21497,49 @@
         <v>627</v>
       </c>
       <c r="B475" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="C475" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D475" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E475" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="D475" t="n">
+      <c r="F475" t="n">
         <v>6.2</v>
       </c>
-      <c r="E475" s="2" t="n">
+      <c r="G475" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="F475" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G475" s="2" t="n">
+      <c r="H475" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I475" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="H475" t="n">
+      <c r="J475" t="n">
         <v>7.5</v>
       </c>
-      <c r="I475" s="2" t="n">
+      <c r="K475" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="J475" t="n">
+      <c r="L475" t="n">
         <v>7.9</v>
       </c>
-      <c r="K475" s="2" t="n">
+      <c r="M475" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="L475" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M475" s="2" t="n">
+      <c r="N475" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O475" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N475" t="n">
-        <v>7</v>
-      </c>
-      <c r="O475" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P475" t="n">
-        <v>6.87</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="476">
@@ -21774,43 +22388,43 @@
         <v>6.7</v>
       </c>
       <c r="C494" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D494" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E494" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="D494" t="n">
+      <c r="F494" t="n">
         <v>7</v>
       </c>
-      <c r="E494" s="2" t="n">
+      <c r="G494" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="F494" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G494" s="2" t="n">
+      <c r="H494" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I494" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="H494" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I494" s="2" t="n">
+      <c r="J494" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K494" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="J494" t="n">
+      <c r="L494" t="n">
         <v>7.1</v>
       </c>
-      <c r="K494" s="2" t="n">
+      <c r="M494" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="L494" t="n">
+      <c r="N494" t="n">
         <v>7.3</v>
       </c>
-      <c r="M494" s="2" t="n">
+      <c r="O494" s="2" t="n">
         <v>46116</v>
-      </c>
-      <c r="N494" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O494" s="2" t="n">
-        <v>46102</v>
       </c>
       <c r="P494" t="n">
         <v>6.83</v>
@@ -21841,49 +22455,49 @@
         <v>648</v>
       </c>
       <c r="B496" t="n">
+        <v>8</v>
+      </c>
+      <c r="C496" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D496" t="n">
         <v>7.1</v>
       </c>
-      <c r="C496" s="2" t="n">
+      <c r="E496" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="D496" t="n">
+      <c r="F496" t="n">
         <v>7.2</v>
       </c>
-      <c r="E496" s="2" t="n">
+      <c r="G496" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="F496" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G496" s="2" t="n">
+      <c r="H496" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I496" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="H496" t="n">
+      <c r="J496" t="n">
         <v>5.7</v>
       </c>
-      <c r="I496" s="2" t="n">
+      <c r="K496" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="J496" t="n">
+      <c r="L496" t="n">
         <v>6</v>
       </c>
-      <c r="K496" s="2" t="n">
+      <c r="M496" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="L496" t="n">
+      <c r="N496" t="n">
         <v>6.3</v>
       </c>
-      <c r="M496" s="2" t="n">
+      <c r="O496" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="N496" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O496" s="2" t="n">
-        <v>46096</v>
-      </c>
       <c r="P496" t="n">
-        <v>6.51</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="497">
@@ -22041,49 +22655,49 @@
         <v>652</v>
       </c>
       <c r="B500" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C500" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D500" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="C500" s="2" t="n">
+      <c r="E500" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="D500" t="n">
+      <c r="F500" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="E500" s="2" t="n">
+      <c r="G500" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="F500" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G500" s="2" t="n">
+      <c r="H500" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I500" s="2" t="n">
         <v>46140</v>
       </c>
-      <c r="H500" t="n">
+      <c r="J500" t="n">
         <v>7.6</v>
       </c>
-      <c r="I500" s="2" t="n">
+      <c r="K500" s="2" t="n">
         <v>46134</v>
-      </c>
-      <c r="J500" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K500" s="2" t="n">
-        <v>46130</v>
       </c>
       <c r="L500" t="n">
         <v>6.9</v>
       </c>
       <c r="M500" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="N500" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O500" s="2" t="n">
         <v>46125</v>
       </c>
-      <c r="N500" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O500" s="2" t="n">
-        <v>46120</v>
-      </c>
       <c r="P500" t="n">
-        <v>7.39</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="501">
@@ -22321,49 +22935,49 @@
         <v>658</v>
       </c>
       <c r="B506" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C506" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D506" t="n">
         <v>7</v>
       </c>
-      <c r="C506" s="2" t="n">
+      <c r="E506" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="D506" t="n">
+      <c r="F506" t="n">
         <v>8.4</v>
       </c>
-      <c r="E506" s="2" t="n">
+      <c r="G506" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="F506" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G506" s="2" t="n">
+      <c r="H506" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I506" s="2" t="n">
         <v>46127</v>
       </c>
-      <c r="H506" t="n">
+      <c r="J506" t="n">
         <v>7.1</v>
       </c>
-      <c r="I506" s="2" t="n">
+      <c r="K506" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J506" t="n">
+      <c r="L506" t="n">
         <v>6.9</v>
       </c>
-      <c r="K506" s="2" t="n">
+      <c r="M506" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L506" t="n">
+      <c r="N506" t="n">
         <v>7.3</v>
       </c>
-      <c r="M506" s="2" t="n">
+      <c r="O506" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="N506" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O506" s="2" t="n">
-        <v>46090</v>
-      </c>
       <c r="P506" t="n">
-        <v>7.19</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="507">
@@ -22424,42 +23038,46 @@
         <v>6.5</v>
       </c>
       <c r="C508" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D508" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E508" s="2" t="n">
         <v>46146</v>
       </c>
-      <c r="D508" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E508" s="2" t="n">
+      <c r="F508" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G508" s="2" t="n">
         <v>46141</v>
       </c>
-      <c r="F508" t="n">
+      <c r="H508" t="n">
         <v>7.1</v>
       </c>
-      <c r="G508" s="2" t="n">
+      <c r="I508" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="H508" t="n">
+      <c r="J508" t="n">
         <v>6.8</v>
       </c>
-      <c r="I508" s="2" t="n">
+      <c r="K508" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="J508" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K508" s="2" t="n">
+      <c r="L508" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M508" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="L508" t="n">
+      <c r="N508" t="n">
         <v>7.4</v>
       </c>
-      <c r="M508" s="2" t="n">
+      <c r="O508" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N508" t="inlineStr"/>
-      <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>6.83</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="509">
@@ -22467,41 +23085,45 @@
         <v>661</v>
       </c>
       <c r="B509" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C509" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D509" t="n">
         <v>6.3</v>
       </c>
-      <c r="C509" s="2" t="n">
+      <c r="E509" s="2" t="n">
         <v>46141</v>
       </c>
-      <c r="D509" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E509" s="2" t="n">
+      <c r="F509" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G509" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="F509" t="n">
+      <c r="H509" t="n">
         <v>7.3</v>
       </c>
-      <c r="G509" s="2" t="n">
+      <c r="I509" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H509" t="n">
+      <c r="J509" t="n">
         <v>7</v>
       </c>
-      <c r="I509" s="2" t="n">
+      <c r="K509" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J509" t="n">
+      <c r="L509" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="K509" s="2" t="n">
+      <c r="M509" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="L509" t="inlineStr"/>
-      <c r="M509" t="inlineStr"/>
       <c r="N509" t="inlineStr"/>
       <c r="O509" t="inlineStr"/>
       <c r="P509" t="n">
-        <v>7.18</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="510">
@@ -22747,45 +23369,49 @@
         <v>667</v>
       </c>
       <c r="B515" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="C515" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D515" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E515" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="D515" t="n">
+      <c r="F515" t="n">
         <v>6.9</v>
       </c>
-      <c r="E515" s="2" t="n">
+      <c r="G515" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="F515" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G515" s="2" t="n">
+      <c r="H515" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I515" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="H515" t="n">
+      <c r="J515" t="n">
         <v>7.4</v>
       </c>
-      <c r="I515" s="2" t="n">
+      <c r="K515" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="J515" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K515" s="2" t="n">
+      <c r="L515" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M515" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="L515" t="n">
+      <c r="N515" t="n">
         <v>7.3</v>
       </c>
-      <c r="M515" s="2" t="n">
+      <c r="O515" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N515" t="inlineStr"/>
-      <c r="O515" t="inlineStr"/>
       <c r="P515" t="n">
-        <v>6.92</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="516">
@@ -22793,49 +23419,49 @@
         <v>668</v>
       </c>
       <c r="B516" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="C516" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D516" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E516" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="D516" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E516" s="2" t="n">
+      <c r="F516" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G516" s="2" t="n">
         <v>46128</v>
       </c>
-      <c r="F516" t="n">
+      <c r="H516" t="n">
         <v>6.8</v>
       </c>
-      <c r="G516" s="2" t="n">
+      <c r="I516" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="H516" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I516" s="2" t="n">
+      <c r="J516" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K516" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="J516" t="n">
+      <c r="L516" t="n">
         <v>7.6</v>
       </c>
-      <c r="K516" s="2" t="n">
+      <c r="M516" s="2" t="n">
         <v>46102</v>
       </c>
-      <c r="L516" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M516" s="2" t="n">
+      <c r="N516" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O516" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="N516" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O516" s="2" t="n">
-        <v>46088</v>
-      </c>
       <c r="P516" t="n">
-        <v>6.84</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="517">
@@ -23086,6 +23712,272 @@
       </c>
       <c r="P521" t="n">
         <v>7.07</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>674</v>
+      </c>
+      <c r="B522" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C522" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D522" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E522" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F522" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G522" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="H522" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I522" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="J522" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K522" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="L522" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="M522" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="N522" t="inlineStr"/>
+      <c r="O522" t="inlineStr"/>
+      <c r="P522" t="n">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>675</v>
+      </c>
+      <c r="B523" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C523" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D523" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E523" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="F523" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G523" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="H523" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I523" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="J523" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K523" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="L523" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M523" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="N523" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O523" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="P523" t="n">
+        <v>7.47</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>676</v>
+      </c>
+      <c r="B524" t="inlineStr"/>
+      <c r="C524" t="inlineStr"/>
+      <c r="D524" t="inlineStr"/>
+      <c r="E524" t="inlineStr"/>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr"/>
+      <c r="H524" t="inlineStr"/>
+      <c r="I524" t="inlineStr"/>
+      <c r="J524" t="inlineStr"/>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr"/>
+      <c r="N524" t="inlineStr"/>
+      <c r="O524" t="inlineStr"/>
+      <c r="P524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>677</v>
+      </c>
+      <c r="B525" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C525" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D525" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E525" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F525" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G525" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="H525" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I525" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="J525" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K525" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="L525" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M525" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="N525" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O525" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="P525" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>678</v>
+      </c>
+      <c r="B526" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C526" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D526" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E526" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="F526" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G526" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="H526" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I526" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="J526" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K526" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="L526" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="M526" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="N526" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O526" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P526" t="n">
+        <v>7.33</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>679</v>
+      </c>
+      <c r="B527" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C527" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="D527" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E527" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="F527" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G527" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="H527" t="n">
+        <v>7</v>
+      </c>
+      <c r="I527" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="J527" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K527" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="L527" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M527" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="N527" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O527" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="P527" t="n">
+        <v>6.91</v>
       </c>
     </row>
   </sheetData>

--- a/players_ratings.xlsx
+++ b/players_ratings.xlsx
@@ -519,7 +519,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>46167</v>
@@ -561,7 +561,7 @@
         <v>46081</v>
       </c>
       <c r="P2" t="n">
-        <v>7.13</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="3">
@@ -852,46 +852,46 @@
         <v>6.5</v>
       </c>
       <c r="C9" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>7.7</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>7</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>6.2</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>7.2</v>
       </c>
-      <c r="K9" s="2" t="n">
+      <c r="M9" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>7.6</v>
       </c>
-      <c r="M9" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="N9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P9" t="n">
-        <v>6.97</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="10">
@@ -949,19 +949,19 @@
         <v>46136</v>
       </c>
       <c r="L11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="N11" t="n">
         <v>7.2</v>
       </c>
-      <c r="M11" s="2" t="n">
+      <c r="O11" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="N11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>46120</v>
-      </c>
       <c r="P11" t="n">
-        <v>7.17</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="12">
@@ -1119,49 +1119,49 @@
         <v>38</v>
       </c>
       <c r="B15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D15" t="n">
         <v>5.8</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="E15" s="2" t="n">
         <v>46164</v>
       </c>
-      <c r="D15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E15" s="2" t="n">
+      <c r="F15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="I15" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="H15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I15" s="2" t="n">
+      <c r="J15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K15" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>7</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="M15" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="L15" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M15" s="2" t="n">
+      <c r="N15" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O15" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="N15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>46116</v>
-      </c>
       <c r="P15" t="n">
-        <v>6.44</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="16">
@@ -1245,49 +1245,49 @@
         <v>43</v>
       </c>
       <c r="B18" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="C18" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>46166</v>
       </c>
-      <c r="D18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E18" s="2" t="n">
+      <c r="F18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>46156</v>
       </c>
-      <c r="F18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I18" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="H18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I18" s="2" t="n">
+      <c r="J18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K18" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="J18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K18" s="2" t="n">
+      <c r="L18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M18" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>6.8</v>
       </c>
-      <c r="M18" s="2" t="n">
+      <c r="O18" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="N18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P18" t="n">
-        <v>6.66</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="19">
@@ -2041,49 +2041,49 @@
         <v>81</v>
       </c>
       <c r="B36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D36" t="n">
         <v>7.8</v>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="E36" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>7.1</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F36" t="n">
+      <c r="H36" t="n">
         <v>6.2</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="I36" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="H36" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I36" s="2" t="n">
+      <c r="J36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K36" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>6.9</v>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="M36" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>7.1</v>
       </c>
-      <c r="M36" s="2" t="n">
+      <c r="O36" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="N36" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>46124</v>
-      </c>
       <c r="P36" t="n">
-        <v>6.91</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="37">
@@ -2191,49 +2191,49 @@
         <v>94</v>
       </c>
       <c r="B40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D40" t="n">
         <v>6.9</v>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="E40" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>7.3</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F40" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G40" s="2" t="n">
+      <c r="H40" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I40" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="H40" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I40" s="2" t="n">
+      <c r="J40" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K40" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>6.3</v>
       </c>
-      <c r="K40" s="2" t="n">
+      <c r="M40" s="2" t="n">
         <v>46130</v>
-      </c>
-      <c r="L40" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>46124</v>
       </c>
       <c r="N40" t="n">
         <v>7.6</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>46119</v>
+        <v>46124</v>
       </c>
       <c r="P40" t="n">
-        <v>7.01</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="41">
@@ -2387,49 +2387,49 @@
         <v>100</v>
       </c>
       <c r="B45" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="C45" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D45" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E45" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D45" t="n">
+      <c r="F45" t="n">
         <v>6.8</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F45" t="n">
+      <c r="H45" t="n">
         <v>7.1</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="I45" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>7.6</v>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="K45" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>6.3</v>
       </c>
-      <c r="K45" s="2" t="n">
+      <c r="M45" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="L45" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M45" s="2" t="n">
+      <c r="N45" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O45" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="N45" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>46124</v>
-      </c>
       <c r="P45" t="n">
-        <v>6.93</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="46">
@@ -2437,49 +2437,49 @@
         <v>101</v>
       </c>
       <c r="B46" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="C46" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E46" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D46" t="n">
+      <c r="F46" t="n">
         <v>7.5</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F46" t="n">
+      <c r="H46" t="n">
         <v>6.9</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="I46" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="H46" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I46" s="2" t="n">
+      <c r="J46" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K46" s="2" t="n">
         <v>46153</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>7</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="M46" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="L46" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M46" s="2" t="n">
+      <c r="N46" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O46" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="N46" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O46" s="2" t="n">
-        <v>46131</v>
-      </c>
       <c r="P46" t="n">
-        <v>6.86</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="47">
@@ -2541,49 +2541,49 @@
         <v>104</v>
       </c>
       <c r="B49" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D49" t="n">
         <v>6.8</v>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="E49" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D49" t="n">
+      <c r="F49" t="n">
         <v>8.4</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F49" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G49" s="2" t="n">
+      <c r="H49" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I49" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>7.3</v>
       </c>
-      <c r="I49" s="2" t="n">
+      <c r="K49" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="J49" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K49" s="2" t="n">
+      <c r="L49" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M49" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="L49" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M49" s="2" t="n">
+      <c r="N49" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O49" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="N49" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>46131</v>
-      </c>
       <c r="P49" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="50">
@@ -2640,38 +2640,42 @@
         <v>6.4</v>
       </c>
       <c r="C52" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D52" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E52" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D52" t="n">
+      <c r="F52" t="n">
         <v>6.3</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="F52" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G52" s="2" t="n">
+      <c r="H52" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I52" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="H52" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I52" s="2" t="n">
+      <c r="J52" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K52" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>6</v>
       </c>
-      <c r="K52" s="2" t="n">
+      <c r="M52" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>6.34</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="53">
@@ -2708,46 +2712,46 @@
         <v>6.5</v>
       </c>
       <c r="C54" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D54" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E54" s="2" t="n">
         <v>46167</v>
-      </c>
-      <c r="D54" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>46162</v>
       </c>
       <c r="F54" t="n">
         <v>6.8</v>
       </c>
       <c r="G54" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="H54" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I54" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="H54" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I54" s="2" t="n">
+      <c r="J54" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K54" s="2" t="n">
         <v>46143</v>
-      </c>
-      <c r="J54" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>46137</v>
       </c>
       <c r="L54" t="n">
         <v>6.8</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="N54" t="n">
         <v>6.8</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>46123</v>
+        <v>46130</v>
       </c>
       <c r="P54" t="n">
-        <v>6.71</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="55">
@@ -3015,49 +3019,49 @@
         <v>133</v>
       </c>
       <c r="B62" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="C62" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D62" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G62" s="2" t="n">
         <v>46166</v>
       </c>
-      <c r="D62" t="n">
+      <c r="H62" t="n">
         <v>6.9</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="I62" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F62" t="n">
+      <c r="J62" t="n">
         <v>6.3</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="K62" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="H62" t="n">
+      <c r="L62" t="n">
         <v>7</v>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="M62" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="J62" t="n">
+      <c r="N62" t="n">
         <v>7.1</v>
       </c>
-      <c r="K62" s="2" t="n">
+      <c r="O62" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="L62" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M62" s="2" t="n">
-        <v>46135</v>
-      </c>
-      <c r="N62" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O62" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P62" t="n">
-        <v>6.8</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="63">
@@ -3605,7 +3609,7 @@
         <v>164</v>
       </c>
       <c r="B75" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>46164</v>
@@ -3647,7 +3651,7 @@
         <v>46130</v>
       </c>
       <c r="P75" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="76">
@@ -4149,31 +4153,31 @@
         <v>46136</v>
       </c>
       <c r="H86" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="J86" t="n">
         <v>7.8</v>
       </c>
-      <c r="I86" s="2" t="n">
+      <c r="K86" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="J86" t="n">
+      <c r="L86" t="n">
         <v>7</v>
       </c>
-      <c r="K86" s="2" t="n">
+      <c r="M86" s="2" t="n">
         <v>46120</v>
       </c>
-      <c r="L86" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M86" s="2" t="n">
+      <c r="N86" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O86" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="N86" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O86" s="2" t="n">
-        <v>46101</v>
-      </c>
       <c r="P86" t="n">
-        <v>6.99</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="87">
@@ -4935,49 +4939,49 @@
         <v>202</v>
       </c>
       <c r="B103" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="C103" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D103" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E103" s="2" t="n">
         <v>46159</v>
       </c>
-      <c r="D103" t="n">
+      <c r="F103" t="n">
         <v>6.2</v>
       </c>
-      <c r="E103" s="2" t="n">
+      <c r="G103" s="2" t="n">
         <v>46153</v>
       </c>
-      <c r="F103" t="n">
+      <c r="H103" t="n">
         <v>7.3</v>
       </c>
-      <c r="G103" s="2" t="n">
+      <c r="I103" s="2" t="n">
         <v>46149</v>
       </c>
-      <c r="H103" t="n">
+      <c r="J103" t="n">
         <v>6.8</v>
       </c>
-      <c r="I103" s="2" t="n">
+      <c r="K103" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="J103" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K103" s="2" t="n">
+      <c r="L103" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M103" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="L103" t="n">
+      <c r="N103" t="n">
         <v>6.3</v>
       </c>
-      <c r="M103" s="2" t="n">
+      <c r="O103" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="N103" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O103" s="2" t="n">
-        <v>46109</v>
-      </c>
       <c r="P103" t="n">
-        <v>6.66</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="104">
@@ -8253,49 +8257,49 @@
         <v>307</v>
       </c>
       <c r="B178" t="n">
+        <v>7</v>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D178" t="n">
         <v>6.3</v>
       </c>
-      <c r="C178" s="2" t="n">
+      <c r="E178" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D178" t="n">
+      <c r="F178" t="n">
         <v>6.8</v>
       </c>
-      <c r="E178" s="2" t="n">
+      <c r="G178" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F178" t="n">
+      <c r="H178" t="n">
         <v>6.2</v>
       </c>
-      <c r="G178" s="2" t="n">
+      <c r="I178" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="H178" t="n">
+      <c r="J178" t="n">
         <v>6.9</v>
       </c>
-      <c r="I178" s="2" t="n">
+      <c r="K178" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="J178" t="n">
+      <c r="L178" t="n">
         <v>6</v>
       </c>
-      <c r="K178" s="2" t="n">
+      <c r="M178" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="L178" t="n">
+      <c r="N178" t="n">
         <v>6.9</v>
       </c>
-      <c r="M178" s="2" t="n">
+      <c r="O178" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="N178" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O178" s="2" t="n">
-        <v>46115</v>
-      </c>
       <c r="P178" t="n">
-        <v>6.53</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="179">
@@ -8503,49 +8507,49 @@
         <v>313</v>
       </c>
       <c r="B183" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="C183" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D183" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E183" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D183" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E183" s="2" t="n">
+      <c r="F183" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G183" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F183" t="n">
+      <c r="H183" t="n">
         <v>7.1</v>
       </c>
-      <c r="G183" s="2" t="n">
+      <c r="I183" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="H183" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I183" s="2" t="n">
+      <c r="J183" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K183" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="J183" t="n">
+      <c r="L183" t="n">
         <v>7.2</v>
       </c>
-      <c r="K183" s="2" t="n">
+      <c r="M183" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="L183" t="n">
+      <c r="N183" t="n">
         <v>6.1</v>
       </c>
-      <c r="M183" s="2" t="n">
+      <c r="O183" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="N183" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O183" s="2" t="n">
-        <v>46124</v>
-      </c>
       <c r="P183" t="n">
-        <v>6.87</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="184">
@@ -8949,49 +8953,49 @@
         <v>322</v>
       </c>
       <c r="B192" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D192" t="n">
         <v>7.7</v>
       </c>
-      <c r="C192" s="2" t="n">
+      <c r="E192" s="2" t="n">
         <v>46165</v>
       </c>
-      <c r="D192" t="n">
+      <c r="F192" t="n">
         <v>6.8</v>
       </c>
-      <c r="E192" s="2" t="n">
+      <c r="G192" s="2" t="n">
         <v>46159</v>
       </c>
-      <c r="F192" t="n">
+      <c r="H192" t="n">
         <v>7.3</v>
       </c>
-      <c r="G192" s="2" t="n">
+      <c r="I192" s="2" t="n">
         <v>46155</v>
       </c>
-      <c r="H192" t="n">
+      <c r="J192" t="n">
         <v>7.4</v>
       </c>
-      <c r="I192" s="2" t="n">
+      <c r="K192" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="J192" t="n">
+      <c r="L192" t="n">
         <v>6.9</v>
       </c>
-      <c r="K192" s="2" t="n">
+      <c r="M192" s="2" t="n">
         <v>46144</v>
-      </c>
-      <c r="L192" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="M192" s="2" t="n">
-        <v>46136</v>
       </c>
       <c r="N192" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="O192" s="2" t="n">
-        <v>46130</v>
+        <v>46136</v>
       </c>
       <c r="P192" t="n">
-        <v>7.67</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="193">
@@ -10163,49 +10167,49 @@
         <v>352</v>
       </c>
       <c r="B218" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C218" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D218" t="n">
         <v>7.6</v>
       </c>
-      <c r="C218" s="2" t="n">
+      <c r="E218" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D218" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E218" s="2" t="n">
+      <c r="F218" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G218" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F218" t="n">
+      <c r="H218" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G218" s="2" t="n">
+      <c r="I218" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="H218" t="n">
+      <c r="J218" t="n">
         <v>7.3</v>
       </c>
-      <c r="I218" s="2" t="n">
+      <c r="K218" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="J218" t="n">
+      <c r="L218" t="n">
         <v>7.9</v>
       </c>
-      <c r="K218" s="2" t="n">
+      <c r="M218" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="L218" t="n">
+      <c r="N218" t="n">
         <v>7.8</v>
       </c>
-      <c r="M218" s="2" t="n">
+      <c r="O218" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="N218" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O218" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P218" t="n">
-        <v>7.67</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="219">
@@ -10539,25 +10543,29 @@
         <v>364</v>
       </c>
       <c r="B226" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="C226" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D226" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E226" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D226" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E226" s="2" t="n">
+      <c r="F226" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G226" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="F226" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G226" s="2" t="n">
+      <c r="H226" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I226" s="2" t="n">
         <v>46096</v>
       </c>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
@@ -10565,7 +10573,7 @@
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="n">
-        <v>6.63</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="227">
@@ -10973,49 +10981,49 @@
         <v>374</v>
       </c>
       <c r="B235" t="n">
+        <v>7</v>
+      </c>
+      <c r="C235" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D235" t="n">
         <v>7.1</v>
       </c>
-      <c r="C235" s="2" t="n">
+      <c r="E235" s="2" t="n">
         <v>46166</v>
       </c>
-      <c r="D235" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E235" s="2" t="n">
+      <c r="F235" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G235" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F235" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G235" s="2" t="n">
+      <c r="H235" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I235" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="H235" t="n">
+      <c r="J235" t="n">
         <v>7.2</v>
       </c>
-      <c r="I235" s="2" t="n">
+      <c r="K235" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="J235" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K235" s="2" t="n">
+      <c r="L235" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M235" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="L235" t="n">
+      <c r="N235" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="M235" s="2" t="n">
+      <c r="O235" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="N235" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O235" s="2" t="n">
-        <v>46131</v>
-      </c>
       <c r="P235" t="n">
-        <v>7.23</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="236">
@@ -11119,49 +11127,49 @@
         <v>377</v>
       </c>
       <c r="B238" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="C238" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D238" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E238" s="2" t="n">
         <v>46165</v>
       </c>
-      <c r="D238" t="n">
+      <c r="F238" t="n">
         <v>6.2</v>
       </c>
-      <c r="E238" s="2" t="n">
+      <c r="G238" s="2" t="n">
         <v>46159</v>
       </c>
-      <c r="F238" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G238" s="2" t="n">
+      <c r="H238" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I238" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="H238" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I238" s="2" t="n">
+      <c r="J238" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K238" s="2" t="n">
         <v>46144</v>
-      </c>
-      <c r="J238" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K238" s="2" t="n">
-        <v>46139</v>
       </c>
       <c r="L238" t="n">
         <v>6.8</v>
       </c>
       <c r="M238" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="N238" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O238" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="N238" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O238" s="2" t="n">
-        <v>46131</v>
-      </c>
       <c r="P238" t="n">
-        <v>6.7</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="239">
@@ -11897,45 +11905,49 @@
         <v>397</v>
       </c>
       <c r="B256" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C256" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D256" t="n">
         <v>6.3</v>
       </c>
-      <c r="C256" s="2" t="n">
+      <c r="E256" s="2" t="n">
         <v>46166</v>
       </c>
-      <c r="D256" t="n">
+      <c r="F256" t="n">
         <v>6.8</v>
       </c>
-      <c r="E256" s="2" t="n">
+      <c r="G256" s="2" t="n">
         <v>46160</v>
       </c>
-      <c r="F256" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G256" s="2" t="n">
+      <c r="H256" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I256" s="2" t="n">
         <v>46153</v>
       </c>
-      <c r="H256" t="n">
+      <c r="J256" t="n">
         <v>7.8</v>
       </c>
-      <c r="I256" s="2" t="n">
+      <c r="K256" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="J256" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K256" s="2" t="n">
+      <c r="L256" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M256" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="L256" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M256" s="2" t="n">
+      <c r="N256" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O256" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr"/>
       <c r="P256" t="n">
-        <v>6.72</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="257">
@@ -13059,49 +13071,49 @@
         <v>423</v>
       </c>
       <c r="B282" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C282" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="D282" t="n">
         <v>7.8</v>
       </c>
-      <c r="C282" s="2" t="n">
+      <c r="E282" s="2" t="n">
         <v>46159</v>
       </c>
-      <c r="D282" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E282" s="2" t="n">
+      <c r="F282" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G282" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="F282" t="n">
+      <c r="H282" t="n">
         <v>6.2</v>
       </c>
-      <c r="G282" s="2" t="n">
+      <c r="I282" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="H282" t="n">
+      <c r="J282" t="n">
         <v>9.1</v>
       </c>
-      <c r="I282" s="2" t="n">
+      <c r="K282" s="2" t="n">
         <v>46132</v>
       </c>
-      <c r="J282" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K282" s="2" t="n">
+      <c r="L282" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M282" s="2" t="n">
         <v>46101</v>
       </c>
-      <c r="L282" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M282" s="2" t="n">
+      <c r="N282" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O282" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="N282" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O282" s="2" t="n">
-        <v>46088</v>
-      </c>
       <c r="P282" t="n">
-        <v>7.04</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="283">
@@ -13199,46 +13211,46 @@
         <v>427</v>
       </c>
       <c r="B286" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="C286" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D286" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E286" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D286" t="n">
+      <c r="F286" t="n">
         <v>6.9</v>
       </c>
-      <c r="E286" s="2" t="n">
+      <c r="G286" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F286" t="n">
+      <c r="H286" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="G286" s="2" t="n">
+      <c r="I286" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="H286" t="n">
+      <c r="J286" t="n">
         <v>8.1</v>
       </c>
-      <c r="I286" s="2" t="n">
+      <c r="K286" s="2" t="n">
         <v>46152</v>
-      </c>
-      <c r="J286" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K286" s="2" t="n">
-        <v>46143</v>
       </c>
       <c r="L286" t="n">
         <v>6.9</v>
       </c>
       <c r="M286" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="N286" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O286" s="2" t="n">
         <v>46138</v>
-      </c>
-      <c r="N286" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O286" s="2" t="n">
-        <v>46130</v>
       </c>
       <c r="P286" t="n">
         <v>7.41</v>
@@ -13399,49 +13411,49 @@
         <v>432</v>
       </c>
       <c r="B290" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="C290" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D290" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E290" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D290" t="n">
+      <c r="F290" t="n">
         <v>8</v>
       </c>
-      <c r="E290" s="2" t="n">
+      <c r="G290" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F290" t="n">
+      <c r="H290" t="n">
         <v>6.9</v>
       </c>
-      <c r="G290" s="2" t="n">
+      <c r="I290" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="H290" t="n">
+      <c r="J290" t="n">
         <v>7.3</v>
       </c>
-      <c r="I290" s="2" t="n">
+      <c r="K290" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="J290" t="n">
+      <c r="L290" t="n">
         <v>7</v>
       </c>
-      <c r="K290" s="2" t="n">
+      <c r="M290" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="L290" t="n">
+      <c r="N290" t="n">
         <v>6.9</v>
       </c>
-      <c r="M290" s="2" t="n">
+      <c r="O290" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="N290" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O290" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P290" t="n">
-        <v>6.97</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="291">
@@ -14029,25 +14041,29 @@
         <v>449</v>
       </c>
       <c r="B304" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C304" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D304" t="n">
         <v>6.2</v>
       </c>
-      <c r="C304" s="2" t="n">
+      <c r="E304" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="D304" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E304" s="2" t="n">
+      <c r="F304" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G304" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="F304" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G304" s="2" t="n">
+      <c r="H304" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I304" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H304" t="inlineStr"/>
-      <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr"/>
@@ -14055,7 +14071,7 @@
       <c r="N304" t="inlineStr"/>
       <c r="O304" t="inlineStr"/>
       <c r="P304" t="n">
-        <v>6.47</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="305">
@@ -15483,49 +15499,49 @@
         <v>484</v>
       </c>
       <c r="B338" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="C338" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D338" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E338" s="2" t="n">
         <v>46165</v>
       </c>
-      <c r="D338" t="n">
+      <c r="F338" t="n">
         <v>6.8</v>
       </c>
-      <c r="E338" s="2" t="n">
+      <c r="G338" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F338" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G338" s="2" t="n">
+      <c r="H338" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I338" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="H338" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I338" s="2" t="n">
+      <c r="J338" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K338" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="J338" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K338" s="2" t="n">
+      <c r="L338" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M338" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="L338" t="n">
+      <c r="N338" t="n">
         <v>6</v>
       </c>
-      <c r="M338" s="2" t="n">
+      <c r="O338" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="N338" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O338" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P338" t="n">
-        <v>6.47</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="339">
@@ -15836,46 +15852,46 @@
         <v>6.7</v>
       </c>
       <c r="C345" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D345" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E345" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D345" t="n">
+      <c r="F345" t="n">
         <v>7</v>
       </c>
-      <c r="E345" s="2" t="n">
+      <c r="G345" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F345" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G345" s="2" t="n">
+      <c r="H345" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I345" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="H345" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I345" s="2" t="n">
+      <c r="J345" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K345" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="J345" t="n">
+      <c r="L345" t="n">
         <v>6.8</v>
       </c>
-      <c r="K345" s="2" t="n">
+      <c r="M345" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="L345" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M345" s="2" t="n">
+      <c r="N345" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O345" s="2" t="n">
         <v>45968</v>
       </c>
-      <c r="N345" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O345" s="2" t="n">
-        <v>45954</v>
-      </c>
       <c r="P345" t="n">
-        <v>6.67</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="346">
@@ -15883,49 +15899,49 @@
         <v>492</v>
       </c>
       <c r="B346" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C346" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D346" t="n">
         <v>6.9</v>
       </c>
-      <c r="C346" s="2" t="n">
+      <c r="E346" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D346" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E346" s="2" t="n">
+      <c r="F346" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G346" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F346" t="n">
+      <c r="H346" t="n">
         <v>7.4</v>
       </c>
-      <c r="G346" s="2" t="n">
+      <c r="I346" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="H346" t="n">
+      <c r="J346" t="n">
         <v>7.9</v>
       </c>
-      <c r="I346" s="2" t="n">
+      <c r="K346" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="J346" t="n">
+      <c r="L346" t="n">
         <v>6.2</v>
       </c>
-      <c r="K346" s="2" t="n">
+      <c r="M346" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="L346" t="n">
+      <c r="N346" t="n">
         <v>7.2</v>
       </c>
-      <c r="M346" s="2" t="n">
+      <c r="O346" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="N346" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O346" s="2" t="n">
-        <v>46129</v>
-      </c>
       <c r="P346" t="n">
-        <v>7.01</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="347">
@@ -15933,46 +15949,46 @@
         <v>493</v>
       </c>
       <c r="B347" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="C347" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D347" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E347" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D347" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E347" s="2" t="n">
+      <c r="F347" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G347" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F347" t="n">
+      <c r="H347" t="n">
         <v>7.2</v>
       </c>
-      <c r="G347" s="2" t="n">
+      <c r="I347" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="H347" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I347" s="2" t="n">
+      <c r="J347" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K347" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="J347" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K347" s="2" t="n">
+      <c r="L347" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M347" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="L347" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M347" s="2" t="n">
+      <c r="N347" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O347" s="2" t="n">
         <v>46129</v>
-      </c>
-      <c r="N347" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O347" s="2" t="n">
-        <v>46122</v>
       </c>
       <c r="P347" t="n">
         <v>6.57</v>
@@ -15983,49 +15999,49 @@
         <v>494</v>
       </c>
       <c r="B348" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="C348" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D348" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E348" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="D348" t="n">
+      <c r="F348" t="n">
         <v>5.9</v>
       </c>
-      <c r="E348" s="2" t="n">
+      <c r="G348" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="F348" t="n">
+      <c r="H348" t="n">
         <v>7.1</v>
       </c>
-      <c r="G348" s="2" t="n">
+      <c r="I348" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="H348" t="n">
+      <c r="J348" t="n">
         <v>7</v>
       </c>
-      <c r="I348" s="2" t="n">
+      <c r="K348" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="J348" t="n">
+      <c r="L348" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K348" s="2" t="n">
+      <c r="M348" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="L348" t="n">
+      <c r="N348" t="n">
         <v>7.8</v>
       </c>
-      <c r="M348" s="2" t="n">
+      <c r="O348" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="N348" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O348" s="2" t="n">
-        <v>46115</v>
-      </c>
       <c r="P348" t="n">
-        <v>7.07</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="349">
@@ -17103,49 +17119,49 @@
         <v>523</v>
       </c>
       <c r="B376" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C376" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D376" t="n">
         <v>8</v>
       </c>
-      <c r="C376" s="2" t="n">
+      <c r="E376" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D376" t="n">
+      <c r="F376" t="n">
         <v>6.9</v>
       </c>
-      <c r="E376" s="2" t="n">
+      <c r="G376" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F376" t="n">
+      <c r="H376" t="n">
         <v>7.4</v>
       </c>
-      <c r="G376" s="2" t="n">
+      <c r="I376" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="H376" t="n">
+      <c r="J376" t="n">
         <v>6.8</v>
       </c>
-      <c r="I376" s="2" t="n">
+      <c r="K376" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="J376" t="n">
+      <c r="L376" t="n">
         <v>7.5</v>
       </c>
-      <c r="K376" s="2" t="n">
+      <c r="M376" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="L376" t="n">
+      <c r="N376" t="n">
         <v>7.3</v>
       </c>
-      <c r="M376" s="2" t="n">
+      <c r="O376" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="N376" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O376" s="2" t="n">
-        <v>46131</v>
-      </c>
       <c r="P376" t="n">
-        <v>7.19</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="377">
@@ -17191,46 +17207,46 @@
         <v>525</v>
       </c>
       <c r="B378" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="C378" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D378" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E378" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D378" t="n">
+      <c r="F378" t="n">
         <v>6.9</v>
       </c>
-      <c r="E378" s="2" t="n">
+      <c r="G378" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F378" t="n">
+      <c r="H378" t="n">
         <v>7</v>
       </c>
-      <c r="G378" s="2" t="n">
+      <c r="I378" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="H378" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I378" s="2" t="n">
+      <c r="J378" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K378" s="2" t="n">
         <v>46145</v>
-      </c>
-      <c r="J378" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K378" s="2" t="n">
-        <v>46141</v>
       </c>
       <c r="L378" t="n">
         <v>6.3</v>
       </c>
       <c r="M378" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="N378" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O378" s="2" t="n">
         <v>46138</v>
-      </c>
-      <c r="N378" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O378" s="2" t="n">
-        <v>46131</v>
       </c>
       <c r="P378" t="n">
         <v>6.61</v>
@@ -17311,41 +17327,45 @@
         <v>528</v>
       </c>
       <c r="B381" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C381" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D381" t="n">
         <v>7</v>
       </c>
-      <c r="C381" s="2" t="n">
+      <c r="E381" s="2" t="n">
         <v>46166</v>
       </c>
-      <c r="D381" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E381" s="2" t="n">
+      <c r="F381" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G381" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F381" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G381" s="2" t="n">
+      <c r="H381" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I381" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="H381" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I381" s="2" t="n">
+      <c r="J381" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K381" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="J381" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K381" s="2" t="n">
+      <c r="L381" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M381" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="L381" t="inlineStr"/>
-      <c r="M381" t="inlineStr"/>
       <c r="N381" t="inlineStr"/>
       <c r="O381" t="inlineStr"/>
       <c r="P381" t="n">
-        <v>6.68</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="382">
@@ -17373,46 +17393,46 @@
         <v>530</v>
       </c>
       <c r="B383" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C383" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D383" t="n">
         <v>6.9</v>
       </c>
-      <c r="C383" s="2" t="n">
+      <c r="E383" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D383" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E383" s="2" t="n">
+      <c r="F383" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G383" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F383" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G383" s="2" t="n">
+      <c r="H383" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I383" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="H383" t="n">
+      <c r="J383" t="n">
         <v>6.8</v>
       </c>
-      <c r="I383" s="2" t="n">
+      <c r="K383" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="J383" t="n">
+      <c r="L383" t="n">
         <v>7.1</v>
       </c>
-      <c r="K383" s="2" t="n">
+      <c r="M383" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="L383" t="n">
+      <c r="N383" t="n">
         <v>7.5</v>
       </c>
-      <c r="M383" s="2" t="n">
+      <c r="O383" s="2" t="n">
         <v>46130</v>
-      </c>
-      <c r="N383" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O383" s="2" t="n">
-        <v>46124</v>
       </c>
       <c r="P383" t="n">
         <v>6.86</v>
@@ -17423,49 +17443,49 @@
         <v>531</v>
       </c>
       <c r="B384" t="n">
+        <v>7</v>
+      </c>
+      <c r="C384" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D384" t="n">
         <v>8</v>
       </c>
-      <c r="C384" s="2" t="n">
+      <c r="E384" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D384" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E384" s="2" t="n">
+      <c r="F384" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G384" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F384" t="n">
+      <c r="H384" t="n">
         <v>7.2</v>
       </c>
-      <c r="G384" s="2" t="n">
+      <c r="I384" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="H384" t="n">
+      <c r="J384" t="n">
         <v>6.8</v>
       </c>
-      <c r="I384" s="2" t="n">
+      <c r="K384" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="J384" t="n">
+      <c r="L384" t="n">
         <v>7.1</v>
       </c>
-      <c r="K384" s="2" t="n">
+      <c r="M384" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="L384" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M384" s="2" t="n">
+      <c r="N384" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O384" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="N384" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O384" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P384" t="n">
-        <v>6.94</v>
+        <v>7</v>
       </c>
     </row>
     <row r="385">
@@ -17669,49 +17689,49 @@
         <v>539</v>
       </c>
       <c r="B391" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C391" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D391" t="n">
         <v>7</v>
       </c>
-      <c r="C391" s="2" t="n">
+      <c r="E391" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D391" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E391" s="2" t="n">
+      <c r="F391" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G391" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F391" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G391" s="2" t="n">
+      <c r="H391" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I391" s="2" t="n">
         <v>46158</v>
-      </c>
-      <c r="H391" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I391" s="2" t="n">
-        <v>46150</v>
       </c>
       <c r="J391" t="n">
         <v>6.8</v>
       </c>
       <c r="K391" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="L391" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="M391" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="L391" t="n">
+      <c r="N391" t="n">
         <v>6.3</v>
       </c>
-      <c r="M391" s="2" t="n">
+      <c r="O391" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="N391" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O391" s="2" t="n">
-        <v>46129</v>
-      </c>
       <c r="P391" t="n">
-        <v>6.77</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="392">
@@ -17719,49 +17739,49 @@
         <v>540</v>
       </c>
       <c r="B392" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C392" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="D392" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E392" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="F392" t="n">
         <v>7</v>
       </c>
-      <c r="C392" s="2" t="n">
+      <c r="G392" s="2" t="n">
         <v>46159</v>
       </c>
-      <c r="D392" t="n">
+      <c r="H392" t="n">
         <v>7</v>
       </c>
-      <c r="E392" s="2" t="n">
+      <c r="I392" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="F392" t="n">
+      <c r="J392" t="n">
         <v>7.2</v>
       </c>
-      <c r="G392" s="2" t="n">
+      <c r="K392" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="H392" t="n">
+      <c r="L392" t="n">
         <v>6.8</v>
       </c>
-      <c r="I392" s="2" t="n">
+      <c r="M392" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="J392" t="n">
+      <c r="N392" t="n">
         <v>6.3</v>
       </c>
-      <c r="K392" s="2" t="n">
+      <c r="O392" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="L392" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="M392" s="2" t="n">
-        <v>46124</v>
-      </c>
-      <c r="N392" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O392" s="2" t="n">
-        <v>46102</v>
-      </c>
       <c r="P392" t="n">
-        <v>6.76</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="393">
@@ -19991,49 +20011,49 @@
         <v>591</v>
       </c>
       <c r="B440" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C440" s="2" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D440" t="n">
         <v>7.3</v>
       </c>
-      <c r="C440" s="2" t="n">
+      <c r="E440" s="2" t="n">
         <v>46168</v>
       </c>
-      <c r="D440" t="n">
+      <c r="F440" t="n">
         <v>7.4</v>
       </c>
-      <c r="E440" s="2" t="n">
+      <c r="G440" s="2" t="n">
         <v>46165</v>
       </c>
-      <c r="F440" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G440" s="2" t="n">
+      <c r="H440" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I440" s="2" t="n">
         <v>46159</v>
       </c>
-      <c r="H440" t="n">
+      <c r="J440" t="n">
         <v>7.4</v>
       </c>
-      <c r="I440" s="2" t="n">
+      <c r="K440" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="J440" t="n">
+      <c r="L440" t="n">
         <v>6.9</v>
       </c>
-      <c r="K440" s="2" t="n">
+      <c r="M440" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="L440" t="n">
+      <c r="N440" t="n">
         <v>7.1</v>
       </c>
-      <c r="M440" s="2" t="n">
+      <c r="O440" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="N440" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O440" s="2" t="n">
-        <v>46129</v>
-      </c>
       <c r="P440" t="n">
-        <v>7.11</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="441">
@@ -20679,49 +20699,49 @@
         <v>605</v>
       </c>
       <c r="B454" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C454" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D454" t="n">
         <v>8.5</v>
       </c>
-      <c r="C454" s="2" t="n">
+      <c r="E454" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D454" t="n">
+      <c r="F454" t="n">
         <v>9.4</v>
       </c>
-      <c r="E454" s="2" t="n">
+      <c r="G454" s="2" t="n">
         <v>46156</v>
       </c>
-      <c r="F454" t="n">
+      <c r="H454" t="n">
         <v>8.5</v>
       </c>
-      <c r="G454" s="2" t="n">
+      <c r="I454" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="H454" t="n">
+      <c r="J454" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I454" s="2" t="n">
+      <c r="K454" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="J454" t="n">
+      <c r="L454" t="n">
         <v>8.4</v>
       </c>
-      <c r="K454" s="2" t="n">
+      <c r="M454" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="L454" t="n">
+      <c r="N454" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="M454" s="2" t="n">
+      <c r="O454" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="N454" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O454" s="2" t="n">
-        <v>46123</v>
-      </c>
       <c r="P454" t="n">
-        <v>8.66</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="455">
@@ -22107,25 +22127,29 @@
         <v>636</v>
       </c>
       <c r="B484" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C484" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D484" t="n">
         <v>7.8</v>
       </c>
-      <c r="C484" s="2" t="n">
+      <c r="E484" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D484" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E484" s="2" t="n">
+      <c r="F484" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G484" s="2" t="n">
         <v>46103</v>
       </c>
-      <c r="F484" t="n">
+      <c r="H484" t="n">
         <v>7</v>
       </c>
-      <c r="G484" s="2" t="n">
+      <c r="I484" s="2" t="n">
         <v>46095</v>
       </c>
-      <c r="H484" t="inlineStr"/>
-      <c r="I484" t="inlineStr"/>
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr"/>
       <c r="L484" t="inlineStr"/>
@@ -22133,7 +22157,7 @@
       <c r="N484" t="inlineStr"/>
       <c r="O484" t="inlineStr"/>
       <c r="P484" t="n">
-        <v>7.17</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="485">
@@ -22191,46 +22215,46 @@
         <v>638</v>
       </c>
       <c r="B486" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C486" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="D486" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E486" s="2" t="n">
         <v>46159</v>
       </c>
-      <c r="D486" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E486" s="2" t="n">
+      <c r="F486" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G486" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="F486" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G486" s="2" t="n">
+      <c r="H486" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I486" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="H486" t="n">
+      <c r="J486" t="n">
         <v>6.9</v>
       </c>
-      <c r="I486" s="2" t="n">
+      <c r="K486" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="J486" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K486" s="2" t="n">
+      <c r="L486" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M486" s="2" t="n">
         <v>46132</v>
       </c>
-      <c r="L486" t="n">
+      <c r="N486" t="n">
         <v>6.2</v>
       </c>
-      <c r="M486" s="2" t="n">
+      <c r="O486" s="2" t="n">
         <v>46124</v>
-      </c>
-      <c r="N486" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O486" s="2" t="n">
-        <v>46102</v>
       </c>
       <c r="P486" t="n">
         <v>6.59</v>
@@ -22561,49 +22585,49 @@
         <v>646</v>
       </c>
       <c r="B494" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="C494" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="D494" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E494" s="2" t="n">
         <v>46164</v>
       </c>
-      <c r="D494" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E494" s="2" t="n">
+      <c r="F494" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G494" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F494" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G494" s="2" t="n">
+      <c r="H494" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I494" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="H494" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I494" s="2" t="n">
+      <c r="J494" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K494" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="J494" t="n">
+      <c r="L494" t="n">
         <v>7</v>
       </c>
-      <c r="K494" s="2" t="n">
+      <c r="M494" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="L494" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M494" s="2" t="n">
+      <c r="N494" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O494" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="N494" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O494" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P494" t="n">
-        <v>6.61</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="495">
@@ -22681,49 +22705,49 @@
         <v>649</v>
       </c>
       <c r="B497" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="C497" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D497" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E497" s="2" t="n">
         <v>46168</v>
       </c>
-      <c r="D497" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E497" s="2" t="n">
+      <c r="F497" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G497" s="2" t="n">
         <v>46164</v>
       </c>
-      <c r="F497" t="n">
+      <c r="H497" t="n">
         <v>7.5</v>
       </c>
-      <c r="G497" s="2" t="n">
+      <c r="I497" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="H497" t="n">
+      <c r="J497" t="n">
         <v>8.1</v>
       </c>
-      <c r="I497" s="2" t="n">
+      <c r="K497" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="J497" t="n">
+      <c r="L497" t="n">
         <v>7</v>
       </c>
-      <c r="K497" s="2" t="n">
+      <c r="M497" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="L497" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M497" s="2" t="n">
+      <c r="N497" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O497" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="N497" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O497" s="2" t="n">
-        <v>46120</v>
-      </c>
       <c r="P497" t="n">
-        <v>7.04</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="498">
@@ -22731,49 +22755,49 @@
         <v>650</v>
       </c>
       <c r="B498" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C498" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D498" t="n">
         <v>7.4</v>
       </c>
-      <c r="C498" s="2" t="n">
+      <c r="E498" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="D498" t="n">
+      <c r="F498" t="n">
         <v>6.9</v>
       </c>
-      <c r="E498" s="2" t="n">
+      <c r="G498" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F498" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G498" s="2" t="n">
+      <c r="H498" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I498" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="H498" t="n">
+      <c r="J498" t="n">
         <v>7.7</v>
       </c>
-      <c r="I498" s="2" t="n">
+      <c r="K498" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="J498" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K498" s="2" t="n">
+      <c r="L498" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M498" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="L498" t="n">
+      <c r="N498" t="n">
         <v>5.8</v>
       </c>
-      <c r="M498" s="2" t="n">
+      <c r="O498" s="2" t="n">
         <v>46124</v>
       </c>
-      <c r="N498" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O498" s="2" t="n">
-        <v>46119</v>
-      </c>
       <c r="P498" t="n">
-        <v>6.94</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="499">
@@ -22831,49 +22855,49 @@
         <v>652</v>
       </c>
       <c r="B500" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="C500" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="D500" t="n">
+        <v>7</v>
+      </c>
+      <c r="E500" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D500" t="n">
+      <c r="F500" t="n">
         <v>7.2</v>
       </c>
-      <c r="E500" s="2" t="n">
+      <c r="G500" s="2" t="n">
         <v>46163</v>
       </c>
-      <c r="F500" t="n">
+      <c r="H500" t="n">
         <v>7.1</v>
       </c>
-      <c r="G500" s="2" t="n">
+      <c r="I500" s="2" t="n">
         <v>46159</v>
       </c>
-      <c r="H500" t="n">
+      <c r="J500" t="n">
         <v>7.3</v>
       </c>
-      <c r="I500" s="2" t="n">
+      <c r="K500" s="2" t="n">
         <v>46155</v>
       </c>
-      <c r="J500" t="n">
+      <c r="L500" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K500" s="2" t="n">
+      <c r="M500" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="L500" t="n">
+      <c r="N500" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="M500" s="2" t="n">
+      <c r="O500" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="N500" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O500" s="2" t="n">
-        <v>46140</v>
-      </c>
       <c r="P500" t="n">
-        <v>7.39</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="501">
@@ -22931,49 +22955,49 @@
         <v>654</v>
       </c>
       <c r="B502" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="C502" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D502" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E502" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D502" t="n">
+      <c r="F502" t="n">
         <v>6.8</v>
       </c>
-      <c r="E502" s="2" t="n">
+      <c r="G502" s="2" t="n">
         <v>46157</v>
       </c>
-      <c r="F502" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G502" s="2" t="n">
+      <c r="H502" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I502" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="H502" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I502" s="2" t="n">
+      <c r="J502" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K502" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="J502" t="n">
+      <c r="L502" t="n">
         <v>6.8</v>
       </c>
-      <c r="K502" s="2" t="n">
+      <c r="M502" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="L502" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M502" s="2" t="n">
+      <c r="N502" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O502" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="N502" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O502" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P502" t="n">
-        <v>6.69</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="503">
@@ -23211,49 +23235,49 @@
         <v>660</v>
       </c>
       <c r="B508" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="C508" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D508" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E508" s="2" t="n">
         <v>46164</v>
       </c>
-      <c r="D508" t="n">
+      <c r="F508" t="n">
         <v>7.1</v>
       </c>
-      <c r="E508" s="2" t="n">
+      <c r="G508" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F508" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G508" s="2" t="n">
+      <c r="H508" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I508" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="H508" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I508" s="2" t="n">
+      <c r="J508" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K508" s="2" t="n">
         <v>46146</v>
       </c>
-      <c r="J508" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K508" s="2" t="n">
+      <c r="L508" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M508" s="2" t="n">
         <v>46141</v>
       </c>
-      <c r="L508" t="n">
+      <c r="N508" t="n">
         <v>7.1</v>
       </c>
-      <c r="M508" s="2" t="n">
+      <c r="O508" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="N508" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O508" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P508" t="n">
-        <v>6.71</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="509">
@@ -23261,45 +23285,49 @@
         <v>661</v>
       </c>
       <c r="B509" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="C509" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D509" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E509" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="D509" t="n">
+      <c r="F509" t="n">
         <v>6.3</v>
       </c>
-      <c r="E509" s="2" t="n">
+      <c r="G509" s="2" t="n">
         <v>46141</v>
       </c>
-      <c r="F509" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G509" s="2" t="n">
+      <c r="H509" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I509" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="H509" t="n">
+      <c r="J509" t="n">
         <v>7.3</v>
       </c>
-      <c r="I509" s="2" t="n">
+      <c r="K509" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="J509" t="n">
+      <c r="L509" t="n">
         <v>7</v>
       </c>
-      <c r="K509" s="2" t="n">
+      <c r="M509" s="2" t="n">
         <v>46123</v>
       </c>
-      <c r="L509" t="n">
+      <c r="N509" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="M509" s="2" t="n">
+      <c r="O509" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="N509" t="inlineStr"/>
-      <c r="O509" t="inlineStr"/>
       <c r="P509" t="n">
-        <v>7.07</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="510">
@@ -23307,49 +23335,49 @@
         <v>662</v>
       </c>
       <c r="B510" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C510" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D510" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="C510" s="2" t="n">
+      <c r="E510" s="2" t="n">
         <v>46165</v>
       </c>
-      <c r="D510" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E510" s="2" t="n">
+      <c r="F510" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G510" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F510" t="n">
+      <c r="H510" t="n">
         <v>6.1</v>
       </c>
-      <c r="G510" s="2" t="n">
+      <c r="I510" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="H510" t="n">
+      <c r="J510" t="n">
         <v>6.2</v>
       </c>
-      <c r="I510" s="2" t="n">
+      <c r="K510" s="2" t="n">
         <v>46146</v>
       </c>
-      <c r="J510" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K510" s="2" t="n">
+      <c r="L510" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M510" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="L510" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M510" s="2" t="n">
+      <c r="N510" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O510" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="N510" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O510" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P510" t="n">
-        <v>6.77</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="511">
@@ -23360,46 +23388,46 @@
         <v>7.2</v>
       </c>
       <c r="C511" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D511" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E511" s="2" t="n">
         <v>46159</v>
       </c>
-      <c r="D511" t="n">
+      <c r="F511" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="E511" s="2" t="n">
+      <c r="G511" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="F511" t="n">
+      <c r="H511" t="n">
         <v>6.8</v>
       </c>
-      <c r="G511" s="2" t="n">
+      <c r="I511" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="H511" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I511" s="2" t="n">
+      <c r="J511" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K511" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="J511" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K511" s="2" t="n">
+      <c r="L511" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M511" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="L511" t="n">
+      <c r="N511" t="n">
         <v>8</v>
       </c>
-      <c r="M511" s="2" t="n">
+      <c r="O511" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="N511" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="O511" s="2" t="n">
-        <v>46123</v>
-      </c>
       <c r="P511" t="n">
-        <v>7.23</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="512">
@@ -23457,49 +23485,49 @@
         <v>665</v>
       </c>
       <c r="B513" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C513" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D513" t="n">
         <v>6.9</v>
       </c>
-      <c r="C513" s="2" t="n">
+      <c r="E513" s="2" t="n">
         <v>46164</v>
       </c>
-      <c r="D513" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E513" s="2" t="n">
+      <c r="F513" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G513" s="2" t="n">
         <v>46160</v>
       </c>
-      <c r="F513" t="n">
+      <c r="H513" t="n">
         <v>6.9</v>
       </c>
-      <c r="G513" s="2" t="n">
+      <c r="I513" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="H513" t="n">
+      <c r="J513" t="n">
         <v>7.3</v>
       </c>
-      <c r="I513" s="2" t="n">
+      <c r="K513" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="J513" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K513" s="2" t="n">
+      <c r="L513" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M513" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="L513" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M513" s="2" t="n">
+      <c r="N513" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O513" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="N513" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O513" s="2" t="n">
-        <v>46122</v>
-      </c>
       <c r="P513" t="n">
-        <v>7.07</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="514">
@@ -23507,49 +23535,49 @@
         <v>666</v>
       </c>
       <c r="B514" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="C514" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D514" t="n">
         <v>6.2</v>
       </c>
-      <c r="C514" s="2" t="n">
+      <c r="E514" s="2" t="n">
         <v>46168</v>
       </c>
-      <c r="D514" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E514" s="2" t="n">
+      <c r="F514" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G514" s="2" t="n">
         <v>46163</v>
       </c>
-      <c r="F514" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="G514" s="2" t="n">
+      <c r="H514" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I514" s="2" t="n">
         <v>46159</v>
       </c>
-      <c r="H514" t="n">
+      <c r="J514" t="n">
         <v>5.7</v>
       </c>
-      <c r="I514" s="2" t="n">
+      <c r="K514" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="J514" t="n">
+      <c r="L514" t="n">
         <v>7</v>
       </c>
-      <c r="K514" s="2" t="n">
+      <c r="M514" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="L514" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M514" s="2" t="n">
+      <c r="N514" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O514" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="N514" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O514" s="2" t="n">
-        <v>46133</v>
-      </c>
       <c r="P514" t="n">
-        <v>6.5</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="515">
@@ -23557,49 +23585,49 @@
         <v>667</v>
       </c>
       <c r="B515" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="C515" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D515" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E515" s="2" t="n">
         <v>46165</v>
       </c>
-      <c r="D515" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E515" s="2" t="n">
+      <c r="F515" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G515" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F515" t="n">
+      <c r="H515" t="n">
         <v>6.8</v>
       </c>
-      <c r="G515" s="2" t="n">
+      <c r="I515" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="H515" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I515" s="2" t="n">
+      <c r="J515" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K515" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="J515" t="n">
+      <c r="L515" t="n">
         <v>6.9</v>
       </c>
-      <c r="K515" s="2" t="n">
+      <c r="M515" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="L515" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M515" s="2" t="n">
+      <c r="N515" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O515" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="N515" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O515" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P515" t="n">
-        <v>6.81</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="516">
@@ -23807,46 +23835,46 @@
         <v>672</v>
       </c>
       <c r="B520" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="C520" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D520" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E520" s="2" t="n">
         <v>46166</v>
       </c>
-      <c r="D520" t="n">
+      <c r="F520" t="n">
         <v>8</v>
       </c>
-      <c r="E520" s="2" t="n">
+      <c r="G520" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F520" t="n">
+      <c r="H520" t="n">
         <v>6.2</v>
       </c>
-      <c r="G520" s="2" t="n">
+      <c r="I520" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="H520" t="n">
+      <c r="J520" t="n">
         <v>7.6</v>
       </c>
-      <c r="I520" s="2" t="n">
+      <c r="K520" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="J520" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K520" s="2" t="n">
+      <c r="L520" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M520" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="L520" t="n">
+      <c r="N520" t="n">
         <v>7.5</v>
       </c>
-      <c r="M520" s="2" t="n">
+      <c r="O520" s="2" t="n">
         <v>46134</v>
-      </c>
-      <c r="N520" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O520" s="2" t="n">
-        <v>46129</v>
       </c>
       <c r="P520" t="n">
         <v>7.01</v>
@@ -23907,49 +23935,49 @@
         <v>674</v>
       </c>
       <c r="B522" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="C522" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D522" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E522" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D522" t="n">
+      <c r="F522" t="n">
         <v>6.9</v>
       </c>
-      <c r="E522" s="2" t="n">
+      <c r="G522" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="F522" t="n">
+      <c r="H522" t="n">
         <v>7.3</v>
       </c>
-      <c r="G522" s="2" t="n">
+      <c r="I522" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="H522" t="n">
+      <c r="J522" t="n">
         <v>7.6</v>
       </c>
-      <c r="I522" s="2" t="n">
+      <c r="K522" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="J522" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K522" s="2" t="n">
+      <c r="L522" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M522" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="L522" t="n">
+      <c r="N522" t="n">
         <v>7.4</v>
       </c>
-      <c r="M522" s="2" t="n">
+      <c r="O522" s="2" t="n">
         <v>46138</v>
       </c>
-      <c r="N522" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O522" s="2" t="n">
-        <v>46130</v>
-      </c>
       <c r="P522" t="n">
-        <v>7.16</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="523">
@@ -23957,49 +23985,49 @@
         <v>675</v>
       </c>
       <c r="B523" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C523" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D523" t="n">
         <v>7</v>
       </c>
-      <c r="C523" s="2" t="n">
+      <c r="E523" s="2" t="n">
         <v>46168</v>
       </c>
-      <c r="D523" t="n">
+      <c r="F523" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E523" s="2" t="n">
+      <c r="G523" s="2" t="n">
         <v>46164</v>
       </c>
-      <c r="F523" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G523" s="2" t="n">
+      <c r="H523" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I523" s="2" t="n">
         <v>46159</v>
       </c>
-      <c r="H523" t="n">
+      <c r="J523" t="n">
         <v>7</v>
       </c>
-      <c r="I523" s="2" t="n">
+      <c r="K523" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="J523" t="n">
+      <c r="L523" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="K523" s="2" t="n">
+      <c r="M523" s="2" t="n">
         <v>46149</v>
       </c>
-      <c r="L523" t="n">
+      <c r="N523" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M523" s="2" t="n">
+      <c r="O523" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="N523" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O523" s="2" t="n">
-        <v>46138</v>
-      </c>
       <c r="P523" t="n">
-        <v>7.51</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="524">
@@ -24127,49 +24155,49 @@
         <v>679</v>
       </c>
       <c r="B527" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C527" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D527" t="n">
         <v>6.8</v>
       </c>
-      <c r="C527" s="2" t="n">
+      <c r="E527" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="D527" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="E527" s="2" t="n">
+      <c r="F527" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G527" s="2" t="n">
         <v>46158</v>
       </c>
-      <c r="F527" t="n">
+      <c r="H527" t="n">
         <v>7.4</v>
       </c>
-      <c r="G527" s="2" t="n">
+      <c r="I527" s="2" t="n">
         <v>46151</v>
       </c>
-      <c r="H527" t="n">
+      <c r="J527" t="n">
         <v>7.7</v>
       </c>
-      <c r="I527" s="2" t="n">
+      <c r="K527" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="J527" t="n">
+      <c r="L527" t="n">
         <v>6.3</v>
       </c>
-      <c r="K527" s="2" t="n">
+      <c r="M527" s="2" t="n">
         <v>46137</v>
       </c>
-      <c r="L527" t="n">
+      <c r="N527" t="n">
         <v>7</v>
       </c>
-      <c r="M527" s="2" t="n">
+      <c r="O527" s="2" t="n">
         <v>46133</v>
       </c>
-      <c r="N527" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O527" s="2" t="n">
-        <v>46129</v>
-      </c>
       <c r="P527" t="n">
-        <v>6.93</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="528">
@@ -24177,49 +24205,49 @@
         <v>680</v>
       </c>
       <c r="B528" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="C528" s="2" t="n">
+        <v>46172</v>
+      </c>
+      <c r="D528" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E528" s="2" t="n">
         <v>46165</v>
       </c>
-      <c r="D528" t="n">
+      <c r="F528" t="n">
         <v>7.1</v>
       </c>
-      <c r="E528" s="2" t="n">
+      <c r="G528" s="2" t="n">
         <v>46150</v>
       </c>
-      <c r="F528" t="n">
+      <c r="H528" t="n">
         <v>6.9</v>
       </c>
-      <c r="G528" s="2" t="n">
+      <c r="I528" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="H528" t="n">
+      <c r="J528" t="n">
         <v>7</v>
       </c>
-      <c r="I528" s="2" t="n">
+      <c r="K528" s="2" t="n">
         <v>46136</v>
-      </c>
-      <c r="J528" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K528" s="2" t="n">
-        <v>46130</v>
       </c>
       <c r="L528" t="n">
         <v>7.1</v>
       </c>
       <c r="M528" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="N528" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O528" s="2" t="n">
         <v>46122</v>
       </c>
-      <c r="N528" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O528" s="2" t="n">
-        <v>46116</v>
-      </c>
       <c r="P528" t="n">
-        <v>6.9</v>
+        <v>7.07</v>
       </c>
     </row>
   </sheetData>
